--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -7,16 +7,11 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="V54L7MJz/w6WJPCyfHdr8+beGetGPHg0QFtXVUIxsLc="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
   <si>
     <t>Company</t>
   </si>
@@ -57,6 +52,9 @@
     <t>APT</t>
   </si>
   <si>
+    <t>Currently qualifies</t>
+  </si>
+  <si>
     <t>News Archive for APT</t>
   </si>
   <si>
@@ -81,9 +79,6 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>Currently qualifies</t>
-  </si>
-  <si>
     <t>News Archive for AMPY</t>
   </si>
   <si>
@@ -96,18 +91,6 @@
     <t>News Archive for CTRM</t>
   </si>
   <si>
-    <t>Clarus Corporation</t>
-  </si>
-  <si>
-    <t>CLAR</t>
-  </si>
-  <si>
-    <t>Earnings probation 2024Q2</t>
-  </si>
-  <si>
-    <t>News Archive for CLAR</t>
-  </si>
-  <si>
     <t>Core Molding Technologies, Inc.</t>
   </si>
   <si>
@@ -135,7 +118,7 @@
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
-    <t>(2/24/25) DMC Global Inc. (BOOM)</t>
+    <t>News Archive for BOOM</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -153,7 +136,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(2/26/25) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -216,7 +199,7 @@
     <t>LSEA</t>
   </si>
   <si>
-    <t>(2/27/25) Landsea Homes Corporation (LSEA)</t>
+    <t>News Archive for LSEA</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -246,6 +229,12 @@
     <t>News Archive for NGS</t>
   </si>
   <si>
+    <t>NCS Multistage Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>NCSM</t>
+  </si>
+  <si>
     <t>Nortech Systems Incorporated</t>
   </si>
   <si>
@@ -288,7 +277,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>(2/25/25) Rocky Brands, Inc. (RCKY)</t>
+    <t>News Archive for RCKY</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -315,7 +304,7 @@
     <t>TITN</t>
   </si>
   <si>
-    <t>News Archive for TITN</t>
+    <t>(3/20/25) Titan Machinery Inc. (TITN)</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -633,7 +622,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.4</v>
+        <v>5.02</v>
       </c>
       <c r="D2" s="3">
         <v>6.92</v>
@@ -642,86 +631,86 @@
         <v>4.64</v>
       </c>
       <c r="F2" s="2">
-        <v>59.4</v>
+        <v>54.3</v>
       </c>
       <c r="G2" s="2">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>35.0</v>
+        <v>42.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.14</v>
+        <v>4.54</v>
       </c>
       <c r="D3" s="3">
-        <v>14.28</v>
+        <v>13.13</v>
       </c>
       <c r="E3" s="3">
         <v>4.26</v>
       </c>
       <c r="F3" s="2">
-        <v>148.0</v>
+        <v>130.7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="I3" s="4">
-        <v>42.0</v>
+        <v>26.0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>4.85</v>
+        <v>3.75</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
       </c>
       <c r="E4" s="3">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="F4" s="2">
-        <v>193.7</v>
+        <v>151.2</v>
       </c>
       <c r="G4" s="2">
-        <v>3.1</v>
+        <v>12.1</v>
       </c>
       <c r="H4" s="3">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="I4" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>21</v>
+        <v>11.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -735,25 +724,25 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
       </c>
       <c r="E5" s="3">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="F5" s="2">
-        <v>23.4</v>
+        <v>24.7</v>
       </c>
       <c r="G5" s="2">
-        <v>1.0</v>
+        <v>1.1</v>
       </c>
       <c r="H5" s="3">
         <v>0.05</v>
       </c>
       <c r="I5" s="4">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -767,95 +756,92 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>4.6</v>
+        <v>14.96</v>
       </c>
       <c r="D6" s="3">
-        <v>7.55</v>
+        <v>21.0</v>
       </c>
       <c r="E6" s="3">
-        <v>3.89</v>
+        <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>176.5</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>128.9</v>
+      </c>
+      <c r="G6" s="2">
+        <v>9.9</v>
       </c>
       <c r="H6" s="3">
-        <v>0.6</v>
+        <v>0.88</v>
       </c>
       <c r="I6" s="4">
-        <v>64.0</v>
-      </c>
-      <c r="J6" s="2" t="s">
+        <v>32.0</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3">
+        <v>22.55</v>
+      </c>
+      <c r="D7" s="3">
+        <v>30.77</v>
+      </c>
+      <c r="E7" s="3">
+        <v>21.52</v>
+      </c>
+      <c r="F7" s="2">
+        <v>598.7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>17.6</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1.36</v>
+      </c>
+      <c r="I7" s="4">
+        <v>36.0</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" s="3">
-        <v>13.73</v>
-      </c>
-      <c r="D7" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>118.8</v>
-      </c>
-      <c r="G7" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.86</v>
-      </c>
-      <c r="I7" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="3">
+        <v>8.77</v>
+      </c>
+      <c r="D8" s="3">
+        <v>19.72</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6.65</v>
+      </c>
+      <c r="F8" s="2">
+        <v>177.5</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I8" s="4">
+        <v>18.0</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C8" s="3">
-        <v>25.17</v>
-      </c>
-      <c r="D8" s="3">
-        <v>30.77</v>
-      </c>
-      <c r="E8" s="3">
-        <v>21.52</v>
-      </c>
-      <c r="F8" s="2">
-        <v>663.5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>19.7</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="4">
-        <v>48.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
@@ -869,537 +855,537 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>8.48</v>
+        <v>20.23</v>
       </c>
       <c r="D9" s="3">
-        <v>19.72</v>
+        <v>25.75</v>
       </c>
       <c r="E9" s="3">
-        <v>6.65</v>
+        <v>18.88</v>
       </c>
       <c r="F9" s="2">
-        <v>171.7</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>526.2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>12.8</v>
       </c>
       <c r="H9" s="3">
-        <v>0.38</v>
+        <v>1.5</v>
       </c>
       <c r="I9" s="4">
-        <v>19.0</v>
-      </c>
-      <c r="J9" s="2" t="s">
+        <v>34.0</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="3">
+        <v>14.79</v>
+      </c>
+      <c r="D10" s="3">
+        <v>16.99</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12.34</v>
+      </c>
+      <c r="F10" s="2">
+        <v>202.2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="I10" s="4">
+        <v>70.0</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" s="3">
-        <v>21.2</v>
-      </c>
-      <c r="D10" s="3">
-        <v>25.75</v>
-      </c>
-      <c r="E10" s="3">
-        <v>18.88</v>
-      </c>
-      <c r="F10" s="2">
-        <v>551.5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>13.4</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1.58</v>
-      </c>
-      <c r="I10" s="4">
-        <v>39.0</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="3">
+        <v>13.84</v>
+      </c>
+      <c r="D11" s="3">
+        <v>22.39</v>
+      </c>
+      <c r="E11" s="3">
+        <v>13.27</v>
+      </c>
+      <c r="F11" s="2">
+        <v>87.6</v>
+      </c>
+      <c r="G11" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.56</v>
+      </c>
+      <c r="I11" s="4">
+        <v>28.0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" s="3">
-        <v>15.23</v>
-      </c>
-      <c r="D11" s="3">
-        <v>16.99</v>
-      </c>
-      <c r="E11" s="3">
-        <v>12.34</v>
-      </c>
-      <c r="F11" s="2">
-        <v>211.4</v>
-      </c>
-      <c r="G11" s="2">
-        <v>16.4</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1.22</v>
-      </c>
-      <c r="I11" s="4">
-        <v>71.0</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="3">
+        <v>17.2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>19.52</v>
+      </c>
+      <c r="E12" s="3">
+        <v>13.4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>119.9</v>
+      </c>
+      <c r="G12" s="2">
+        <v>21.2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="I12" s="4">
+        <v>84.0</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" s="3">
-        <v>14.94</v>
-      </c>
-      <c r="D12" s="3">
-        <v>23.41</v>
-      </c>
-      <c r="E12" s="3">
-        <v>14.05</v>
-      </c>
-      <c r="F12" s="2">
-        <v>94.6</v>
-      </c>
-      <c r="G12" s="2">
-        <v>12.7</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="I12" s="4">
-        <v>34.0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8.05</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4.04</v>
+      </c>
+      <c r="F13" s="2">
+        <v>376.3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="I13" s="4">
+        <v>90.0</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C13" s="3">
-        <v>16.41</v>
-      </c>
-      <c r="D13" s="3">
-        <v>19.52</v>
-      </c>
-      <c r="E13" s="3">
-        <v>13.4</v>
-      </c>
-      <c r="F13" s="2">
-        <v>114.4</v>
-      </c>
-      <c r="G13" s="2">
-        <v>20.2</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.89</v>
-      </c>
-      <c r="I13" s="4">
-        <v>68.0</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="3">
+        <v>11.61</v>
+      </c>
+      <c r="D14" s="3">
+        <v>24.18</v>
+      </c>
+      <c r="E14" s="3">
+        <v>11.17</v>
+      </c>
+      <c r="F14" s="2">
+        <v>122.4</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="I14" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" s="3">
-        <v>7.11</v>
-      </c>
-      <c r="D14" s="3">
-        <v>8.05</v>
-      </c>
-      <c r="E14" s="3">
-        <v>4.04</v>
-      </c>
-      <c r="F14" s="2">
-        <v>405.4</v>
-      </c>
-      <c r="G14" s="2">
-        <v>16.3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1.33</v>
-      </c>
-      <c r="I14" s="4">
-        <v>93.0</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="3">
+        <v>16.99</v>
+      </c>
+      <c r="D15" s="3">
+        <v>24.45</v>
+      </c>
+      <c r="E15" s="3">
+        <v>15.94</v>
+      </c>
+      <c r="F15" s="2">
+        <v>417.2</v>
+      </c>
+      <c r="G15" s="2">
+        <v>53.1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.78</v>
+      </c>
+      <c r="I15" s="4">
+        <v>46.0</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C15" s="3">
-        <v>13.07</v>
-      </c>
-      <c r="D15" s="3">
-        <v>24.82</v>
-      </c>
-      <c r="E15" s="3">
-        <v>12.06</v>
-      </c>
-      <c r="F15" s="2">
-        <v>137.8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.61</v>
-      </c>
-      <c r="I15" s="4">
-        <v>30.0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3">
+        <v>18.76</v>
+      </c>
+      <c r="D16" s="3">
+        <v>27.28</v>
+      </c>
+      <c r="E16" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>178.2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.13</v>
+      </c>
+      <c r="I16" s="4">
+        <v>48.0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C16" s="3">
-        <v>18.02</v>
-      </c>
-      <c r="D16" s="3">
-        <v>24.45</v>
-      </c>
-      <c r="E16" s="3">
-        <v>16.36</v>
-      </c>
-      <c r="F16" s="2">
-        <v>442.5</v>
-      </c>
-      <c r="G16" s="2">
-        <v>56.3</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.83</v>
-      </c>
-      <c r="I16" s="4">
-        <v>55.0</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="3">
+        <v>6.96</v>
+      </c>
+      <c r="D17" s="3">
+        <v>14.91</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6.54</v>
+      </c>
+      <c r="F17" s="2">
+        <v>252.7</v>
+      </c>
+      <c r="G17" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="I17" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C17" s="3">
-        <v>23.6</v>
-      </c>
-      <c r="D17" s="3">
-        <v>27.28</v>
-      </c>
-      <c r="E17" s="3">
-        <v>15.1</v>
-      </c>
-      <c r="F17" s="2">
-        <v>224.2</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1.42</v>
-      </c>
-      <c r="I17" s="4">
-        <v>54.0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="3">
+        <v>10.58</v>
+      </c>
+      <c r="D18" s="3">
+        <v>12.44</v>
+      </c>
+      <c r="E18" s="3">
+        <v>7.45</v>
+      </c>
+      <c r="F18" s="2">
+        <v>328.3</v>
+      </c>
+      <c r="G18" s="2">
+        <v>17.6</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="I18" s="4">
+        <v>57.0</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C18" s="3">
-        <v>7.12</v>
-      </c>
-      <c r="D18" s="3">
-        <v>14.91</v>
-      </c>
-      <c r="E18" s="3">
-        <v>6.54</v>
-      </c>
-      <c r="F18" s="2">
-        <v>258.3</v>
-      </c>
-      <c r="G18" s="2">
-        <v>15.1</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.38</v>
-      </c>
-      <c r="I18" s="4">
-        <v>11.0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="3">
+        <v>34.19</v>
+      </c>
+      <c r="D19" s="3">
+        <v>34.78</v>
+      </c>
+      <c r="E19" s="3">
+        <v>25.19</v>
+      </c>
+      <c r="F19" s="2">
+        <v>254.1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="I19" s="4">
+        <v>87.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C19" s="3">
-        <v>9.84</v>
-      </c>
-      <c r="D19" s="3">
-        <v>12.44</v>
-      </c>
-      <c r="E19" s="3">
-        <v>7.45</v>
-      </c>
-      <c r="F19" s="2">
-        <v>305.1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>27.7</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1.6</v>
-      </c>
-      <c r="I19" s="4">
-        <v>31.0</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="3">
+        <v>21.65</v>
+      </c>
+      <c r="D20" s="3">
+        <v>29.74</v>
+      </c>
+      <c r="E20" s="3">
+        <v>16.7</v>
+      </c>
+      <c r="F20" s="2">
+        <v>270.8</v>
+      </c>
+      <c r="G20" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="I20" s="4">
+        <v>74.0</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C20" s="3">
-        <v>32.28</v>
-      </c>
-      <c r="D20" s="3">
-        <v>34.74</v>
-      </c>
-      <c r="E20" s="3">
-        <v>25.19</v>
-      </c>
-      <c r="F20" s="2">
-        <v>235.5</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.62</v>
-      </c>
-      <c r="I20" s="4">
-        <v>76.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C21" s="3">
-        <v>25.71</v>
+        <v>37.3</v>
       </c>
       <c r="D21" s="3">
-        <v>29.74</v>
+        <v>37.74</v>
       </c>
       <c r="E21" s="3">
-        <v>16.42</v>
+        <v>15.25</v>
       </c>
       <c r="F21" s="2">
-        <v>321.1</v>
+        <v>94.8</v>
       </c>
       <c r="G21" s="2">
-        <v>20.1</v>
+        <v>14.6</v>
       </c>
       <c r="H21" s="3">
-        <v>1.35</v>
+        <v>0.82</v>
       </c>
       <c r="I21" s="4">
-        <v>77.0</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>75</v>
+        <v>96.0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="D22" s="3">
         <v>19.15</v>
       </c>
       <c r="E22" s="3">
-        <v>9.53</v>
+        <v>9.5</v>
       </c>
       <c r="F22" s="2">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="G22" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H22" s="3">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I22" s="4">
-        <v>27.0</v>
+        <v>35.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="3">
+        <v>5.35</v>
+      </c>
+      <c r="D23" s="3">
+        <v>8.32</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4.69</v>
+      </c>
+      <c r="F23" s="2">
+        <v>351.1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="I23" s="4">
+        <v>31.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="3">
-        <v>5.12</v>
-      </c>
-      <c r="D23" s="3">
-        <v>8.58</v>
-      </c>
-      <c r="E23" s="3">
-        <v>4.82</v>
-      </c>
-      <c r="F23" s="2">
-        <v>332.6</v>
-      </c>
-      <c r="G23" s="2">
-        <v>10.8</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0.63</v>
-      </c>
-      <c r="I23" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>24.2</v>
+        <v>22.0</v>
       </c>
       <c r="D24" s="3">
         <v>34.5</v>
       </c>
       <c r="E24" s="3">
-        <v>22.74</v>
+        <v>21.0</v>
       </c>
       <c r="F24" s="2">
-        <v>323.4</v>
+        <v>298.3</v>
       </c>
       <c r="G24" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="H24" s="3">
-        <v>1.09</v>
+        <v>0.89</v>
       </c>
       <c r="I24" s="4">
-        <v>27.0</v>
+        <v>25.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>22.49</v>
+        <v>17.7</v>
       </c>
       <c r="D25" s="3">
         <v>35.5</v>
@@ -1408,97 +1394,100 @@
         <v>3.87</v>
       </c>
       <c r="F25" s="2">
-        <v>54.8</v>
+        <v>43.1</v>
       </c>
       <c r="G25" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H25" s="3">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="I25" s="4">
-        <v>54.0</v>
+        <v>24.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>20.34</v>
+        <v>17.85</v>
       </c>
       <c r="D26" s="3">
         <v>40.14</v>
       </c>
       <c r="E26" s="3">
-        <v>19.5</v>
+        <v>17.8</v>
       </c>
       <c r="F26" s="2">
-        <v>151.6</v>
+        <v>133.2</v>
       </c>
       <c r="G26" s="2">
-        <v>13.4</v>
+        <v>11.7</v>
       </c>
       <c r="H26" s="3">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="I26" s="4">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>11.25</v>
+        <v>12.6</v>
       </c>
       <c r="D27" s="3">
-        <v>24.67</v>
+        <v>23.56</v>
       </c>
       <c r="E27" s="3">
         <v>10.75</v>
       </c>
       <c r="F27" s="2">
-        <v>70.4</v>
+        <v>78.9</v>
       </c>
       <c r="G27" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0.4</v>
+        <v>22.9</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="I27" s="4">
-        <v>23.0</v>
+        <v>35.0</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>5.67</v>
+        <v>5.78</v>
       </c>
       <c r="D28" s="3">
         <v>8.84</v>
@@ -1507,86 +1496,86 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>208.3</v>
+        <v>212.4</v>
       </c>
       <c r="G28" s="2">
         <v>3.0</v>
       </c>
       <c r="H28" s="3">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="I28" s="4">
-        <v>48.0</v>
+        <v>32.0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>17.19</v>
+        <v>17.05</v>
       </c>
       <c r="D29" s="3">
-        <v>27.13</v>
+        <v>24.92</v>
       </c>
       <c r="E29" s="3">
         <v>12.3</v>
       </c>
       <c r="F29" s="2">
-        <v>391.8</v>
-      </c>
-      <c r="G29" s="2">
-        <v>12.8</v>
+        <v>388.5</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H29" s="3">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="I29" s="4">
-        <v>80.0</v>
+        <v>85.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C30" s="3">
-        <v>23.54</v>
+        <v>22.88</v>
       </c>
       <c r="D30" s="3">
-        <v>35.54</v>
+        <v>35.52</v>
       </c>
       <c r="E30" s="3">
         <v>20.83</v>
       </c>
       <c r="F30" s="2">
-        <v>312.1</v>
+        <v>303.3</v>
       </c>
       <c r="G30" s="2">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="H30" s="3">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="I30" s="4">
-        <v>34.0</v>
+        <v>49.0</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -7,11 +7,16 @@
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="bOFQe4t1qAvwWULT0ZpyXPYdx2LJO/op72ZsXNalUL4="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="101">
   <si>
     <t>Company</t>
   </si>
@@ -241,7 +246,7 @@
     <t>NSYS</t>
   </si>
   <si>
-    <t>News Archive for NSYS</t>
+    <t>(3/31/25) Nortech Systems Incorporated (NSYS)</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
@@ -304,7 +309,7 @@
     <t>TITN</t>
   </si>
   <si>
-    <t>(3/20/25) Titan Machinery Inc. (TITN)</t>
+    <t>News Archive for TITN</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -622,25 +627,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.02</v>
+        <v>4.38</v>
       </c>
       <c r="D2" s="3">
-        <v>6.92</v>
+        <v>6.91</v>
       </c>
       <c r="E2" s="3">
-        <v>4.64</v>
+        <v>4.26</v>
       </c>
       <c r="F2" s="2">
-        <v>54.3</v>
+        <v>47.4</v>
       </c>
       <c r="G2" s="2">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="H2" s="3">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="I2" s="4">
-        <v>42.0</v>
+        <v>37.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -657,25 +662,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.54</v>
+        <v>3.8</v>
       </c>
       <c r="D3" s="3">
-        <v>13.13</v>
+        <v>12.74</v>
       </c>
       <c r="E3" s="3">
-        <v>4.26</v>
+        <v>3.7</v>
       </c>
       <c r="F3" s="2">
-        <v>130.7</v>
+        <v>109.4</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I3" s="4">
-        <v>26.0</v>
+        <v>35.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -692,25 +697,25 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>3.75</v>
+        <v>2.91</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
       </c>
       <c r="E4" s="3">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="F4" s="2">
-        <v>151.2</v>
+        <v>117.4</v>
       </c>
       <c r="G4" s="2">
-        <v>12.1</v>
+        <v>9.4</v>
       </c>
       <c r="H4" s="3">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="I4" s="4">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -724,22 +729,22 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
       </c>
       <c r="E5" s="3">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="F5" s="2">
-        <v>24.7</v>
+        <v>21.1</v>
       </c>
       <c r="G5" s="2">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H5" s="3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I5" s="4">
         <v>13.0</v>
@@ -756,7 +761,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>14.96</v>
+        <v>14.97</v>
       </c>
       <c r="D6" s="3">
         <v>21.0</v>
@@ -765,7 +770,7 @@
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>128.9</v>
+        <v>129.0</v>
       </c>
       <c r="G6" s="2">
         <v>9.9</v>
@@ -774,7 +779,7 @@
         <v>0.88</v>
       </c>
       <c r="I6" s="4">
-        <v>32.0</v>
+        <v>62.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -788,25 +793,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>22.55</v>
+        <v>19.86</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
       </c>
       <c r="E7" s="3">
-        <v>21.52</v>
+        <v>18.8</v>
       </c>
       <c r="F7" s="2">
-        <v>598.7</v>
+        <v>527.3</v>
       </c>
       <c r="G7" s="2">
-        <v>17.6</v>
+        <v>15.5</v>
       </c>
       <c r="H7" s="3">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="I7" s="4">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -820,25 +825,25 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>8.77</v>
+        <v>7.02</v>
       </c>
       <c r="D8" s="3">
-        <v>19.72</v>
+        <v>19.13</v>
       </c>
       <c r="E8" s="3">
-        <v>6.65</v>
+        <v>6.41</v>
       </c>
       <c r="F8" s="2">
-        <v>177.5</v>
+        <v>142.1</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I8" s="4">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -855,7 +860,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>20.23</v>
+        <v>19.4</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
@@ -864,16 +869,16 @@
         <v>18.88</v>
       </c>
       <c r="F9" s="2">
-        <v>526.2</v>
+        <v>504.6</v>
       </c>
       <c r="G9" s="2">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="I9" s="4">
-        <v>34.0</v>
+        <v>45.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -887,7 +892,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>14.79</v>
+        <v>16.1</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
@@ -896,16 +901,16 @@
         <v>12.34</v>
       </c>
       <c r="F10" s="2">
-        <v>202.2</v>
+        <v>220.0</v>
       </c>
       <c r="G10" s="2">
-        <v>15.9</v>
+        <v>17.3</v>
       </c>
       <c r="H10" s="3">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="I10" s="4">
-        <v>70.0</v>
+        <v>87.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -919,25 +924,25 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>13.84</v>
+        <v>13.38</v>
       </c>
       <c r="D11" s="3">
-        <v>22.39</v>
+        <v>20.18</v>
       </c>
       <c r="E11" s="3">
         <v>13.27</v>
       </c>
       <c r="F11" s="2">
-        <v>87.6</v>
+        <v>84.7</v>
       </c>
       <c r="G11" s="2">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H11" s="3">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
       <c r="I11" s="4">
-        <v>28.0</v>
+        <v>49.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -954,7 +959,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>17.2</v>
+        <v>13.83</v>
       </c>
       <c r="D12" s="3">
         <v>19.52</v>
@@ -963,16 +968,16 @@
         <v>13.4</v>
       </c>
       <c r="F12" s="2">
-        <v>119.9</v>
+        <v>96.4</v>
       </c>
       <c r="G12" s="2">
-        <v>21.2</v>
+        <v>17.0</v>
       </c>
       <c r="H12" s="3">
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
       <c r="I12" s="4">
-        <v>84.0</v>
+        <v>51.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -986,7 +991,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>6.6</v>
+        <v>5.52</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -995,16 +1000,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>376.3</v>
+        <v>315.0</v>
       </c>
       <c r="G13" s="2">
-        <v>15.1</v>
+        <v>12.7</v>
       </c>
       <c r="H13" s="3">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="I13" s="4">
-        <v>90.0</v>
+        <v>81.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1018,22 +1023,22 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>11.61</v>
+        <v>9.16</v>
       </c>
       <c r="D14" s="3">
-        <v>24.18</v>
+        <v>23.73</v>
       </c>
       <c r="E14" s="3">
-        <v>11.17</v>
+        <v>8.03</v>
       </c>
       <c r="F14" s="2">
-        <v>122.4</v>
+        <v>96.6</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="I14" s="4">
         <v>15.0</v>
@@ -1053,25 +1058,28 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>16.99</v>
+        <v>13.28</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
       </c>
       <c r="E15" s="3">
-        <v>15.94</v>
+        <v>12.57</v>
       </c>
       <c r="F15" s="2">
-        <v>417.2</v>
+        <v>326.1</v>
       </c>
       <c r="G15" s="2">
-        <v>53.1</v>
+        <v>41.5</v>
       </c>
       <c r="H15" s="3">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="I15" s="4">
-        <v>46.0</v>
+        <v>36.0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
@@ -1085,7 +1093,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>18.76</v>
+        <v>17.85</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
@@ -1094,16 +1102,16 @@
         <v>15.1</v>
       </c>
       <c r="F16" s="2">
-        <v>178.2</v>
+        <v>169.6</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="I16" s="4">
-        <v>48.0</v>
+        <v>60.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1120,25 +1128,25 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>6.96</v>
+        <v>6.25</v>
       </c>
       <c r="D17" s="3">
-        <v>14.91</v>
+        <v>14.04</v>
       </c>
       <c r="E17" s="3">
-        <v>6.54</v>
+        <v>5.62</v>
       </c>
       <c r="F17" s="2">
-        <v>252.7</v>
+        <v>227.1</v>
       </c>
       <c r="G17" s="2">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="I17" s="4">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1152,7 +1160,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>10.58</v>
+        <v>9.32</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
@@ -1161,16 +1169,16 @@
         <v>7.45</v>
       </c>
       <c r="F18" s="2">
-        <v>328.3</v>
+        <v>289.2</v>
       </c>
       <c r="G18" s="2">
-        <v>17.6</v>
+        <v>15.5</v>
       </c>
       <c r="H18" s="3">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="I18" s="4">
-        <v>57.0</v>
+        <v>46.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1184,7 +1192,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>34.19</v>
+        <v>31.68</v>
       </c>
       <c r="D19" s="3">
         <v>34.78</v>
@@ -1193,13 +1201,13 @@
         <v>25.19</v>
       </c>
       <c r="F19" s="2">
-        <v>254.1</v>
+        <v>235.5</v>
       </c>
       <c r="G19" s="2">
-        <v>7.5</v>
+        <v>7.0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="I19" s="4">
         <v>87.0</v>
@@ -1219,7 +1227,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>21.65</v>
+        <v>17.95</v>
       </c>
       <c r="D20" s="3">
         <v>29.74</v>
@@ -1228,16 +1236,19 @@
         <v>16.7</v>
       </c>
       <c r="F20" s="2">
-        <v>270.8</v>
+        <v>224.5</v>
       </c>
       <c r="G20" s="2">
-        <v>15.8</v>
+        <v>13.1</v>
       </c>
       <c r="H20" s="3">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="I20" s="4">
-        <v>74.0</v>
+        <v>60.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1251,22 +1262,22 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>37.3</v>
+        <v>30.47</v>
       </c>
       <c r="D21" s="3">
-        <v>37.74</v>
+        <v>38.95</v>
       </c>
       <c r="E21" s="3">
-        <v>15.25</v>
+        <v>15.35</v>
       </c>
       <c r="F21" s="2">
-        <v>94.8</v>
+        <v>77.4</v>
       </c>
       <c r="G21" s="2">
-        <v>14.6</v>
+        <v>11.9</v>
       </c>
       <c r="H21" s="3">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="I21" s="4">
         <v>96.0</v>
@@ -1283,22 +1294,22 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>9.94</v>
+        <v>9.0</v>
       </c>
       <c r="D22" s="3">
         <v>19.15</v>
       </c>
       <c r="E22" s="3">
-        <v>9.5</v>
+        <v>8.01</v>
       </c>
       <c r="F22" s="2">
-        <v>27.4</v>
-      </c>
-      <c r="G22" s="2">
-        <v>6.4</v>
+        <v>24.8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H22" s="3">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="I22" s="4">
         <v>35.0</v>
@@ -1315,25 +1326,25 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>5.35</v>
+        <v>4.12</v>
       </c>
       <c r="D23" s="3">
         <v>8.32</v>
       </c>
       <c r="E23" s="3">
-        <v>4.69</v>
+        <v>3.93</v>
       </c>
       <c r="F23" s="2">
-        <v>351.1</v>
+        <v>270.1</v>
       </c>
       <c r="G23" s="2">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="H23" s="3">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="I23" s="4">
-        <v>31.0</v>
+        <v>18.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1350,25 +1361,25 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>22.0</v>
+        <v>19.4</v>
       </c>
       <c r="D24" s="3">
         <v>34.5</v>
       </c>
       <c r="E24" s="3">
-        <v>21.0</v>
+        <v>18.54</v>
       </c>
       <c r="F24" s="2">
-        <v>298.3</v>
+        <v>263.0</v>
       </c>
       <c r="G24" s="2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="H24" s="3">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="I24" s="4">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1385,7 +1396,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>17.7</v>
+        <v>17.82</v>
       </c>
       <c r="D25" s="3">
         <v>35.5</v>
@@ -1394,16 +1405,16 @@
         <v>3.87</v>
       </c>
       <c r="F25" s="2">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="G25" s="2">
         <v>0.5</v>
       </c>
       <c r="H25" s="3">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I25" s="4">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1420,25 +1431,25 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>17.85</v>
+        <v>15.82</v>
       </c>
       <c r="D26" s="3">
         <v>40.14</v>
       </c>
       <c r="E26" s="3">
-        <v>17.8</v>
+        <v>14.86</v>
       </c>
       <c r="F26" s="2">
-        <v>133.2</v>
+        <v>118.1</v>
       </c>
       <c r="G26" s="2">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="H26" s="3">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="I26" s="4">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1455,7 +1466,7 @@
         <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>12.6</v>
+        <v>11.77</v>
       </c>
       <c r="D27" s="3">
         <v>23.56</v>
@@ -1464,16 +1475,19 @@
         <v>10.75</v>
       </c>
       <c r="F27" s="2">
-        <v>78.9</v>
+        <v>75.8</v>
       </c>
       <c r="G27" s="2">
-        <v>22.9</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>21.4</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0.43</v>
       </c>
       <c r="I27" s="4">
-        <v>35.0</v>
+        <v>47.0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>91</v>
@@ -1487,7 +1501,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>5.78</v>
+        <v>5.12</v>
       </c>
       <c r="D28" s="3">
         <v>8.84</v>
@@ -1496,16 +1510,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>212.4</v>
+        <v>188.1</v>
       </c>
       <c r="G28" s="2">
-        <v>3.0</v>
+        <v>2.7</v>
       </c>
       <c r="H28" s="3">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="I28" s="4">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1522,25 +1536,25 @@
         <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>17.05</v>
+        <v>15.0</v>
       </c>
       <c r="D29" s="3">
-        <v>24.92</v>
+        <v>24.31</v>
       </c>
       <c r="E29" s="3">
         <v>12.3</v>
       </c>
       <c r="F29" s="2">
-        <v>388.5</v>
+        <v>341.8</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="3">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="I29" s="4">
-        <v>85.0</v>
+        <v>82.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>97</v>
@@ -1554,25 +1568,28 @@
         <v>99</v>
       </c>
       <c r="C30" s="3">
-        <v>22.88</v>
+        <v>20.44</v>
       </c>
       <c r="D30" s="3">
-        <v>35.52</v>
+        <v>35.11</v>
       </c>
       <c r="E30" s="3">
-        <v>20.83</v>
+        <v>19.16</v>
       </c>
       <c r="F30" s="2">
-        <v>303.3</v>
+        <v>271.0</v>
       </c>
       <c r="G30" s="2">
-        <v>30.9</v>
+        <v>27.6</v>
       </c>
       <c r="H30" s="3">
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
       <c r="I30" s="4">
-        <v>49.0</v>
+        <v>44.0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>100</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="bOFQe4t1qAvwWULT0ZpyXPYdx2LJO/op72ZsXNalUL4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="qexYYMELXQcUNI+xJtusD2Wl8+KAQLopP50c3b6ggYg="/>
     </ext>
   </extLst>
 </workbook>
@@ -195,7 +195,7 @@
     <t>LAKE</t>
   </si>
   <si>
-    <t>News Archive for LAKE</t>
+    <t>(4/9/25) Lakeland Industries, Inc. (LAKE)</t>
   </si>
   <si>
     <t>Landsea Homes Corporation</t>
@@ -246,7 +246,7 @@
     <t>NSYS</t>
   </si>
   <si>
-    <t>(3/31/25) Nortech Systems Incorporated (NSYS)</t>
+    <t>News Archive for NSYS</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
@@ -627,25 +627,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.38</v>
+        <v>4.16</v>
       </c>
       <c r="D2" s="3">
-        <v>6.91</v>
+        <v>6.44</v>
       </c>
       <c r="E2" s="3">
-        <v>4.26</v>
+        <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>47.4</v>
+        <v>45.0</v>
       </c>
       <c r="G2" s="2">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="H2" s="3">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="I2" s="4">
-        <v>37.0</v>
+        <v>31.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -662,16 +662,16 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="D3" s="3">
-        <v>12.74</v>
+        <v>12.67</v>
       </c>
       <c r="E3" s="3">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="F3" s="2">
-        <v>109.4</v>
+        <v>108.2</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
@@ -680,7 +680,7 @@
         <v>0.29</v>
       </c>
       <c r="I3" s="4">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -697,25 +697,25 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.91</v>
+        <v>2.39</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
       </c>
       <c r="E4" s="3">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="F4" s="2">
-        <v>117.4</v>
+        <v>96.4</v>
       </c>
       <c r="G4" s="2">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="H4" s="3">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="I4" s="4">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -729,16 +729,16 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
       </c>
       <c r="E5" s="3">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="F5" s="2">
-        <v>21.1</v>
+        <v>20.5</v>
       </c>
       <c r="G5" s="2">
         <v>0.9</v>
@@ -761,7 +761,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>14.97</v>
+        <v>15.08</v>
       </c>
       <c r="D6" s="3">
         <v>21.0</v>
@@ -770,16 +770,16 @@
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>129.0</v>
+        <v>129.9</v>
       </c>
       <c r="G6" s="2">
-        <v>9.9</v>
+        <v>10.0</v>
       </c>
       <c r="H6" s="3">
         <v>0.88</v>
       </c>
       <c r="I6" s="4">
-        <v>62.0</v>
+        <v>55.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -793,25 +793,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>19.86</v>
+        <v>19.16</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
       </c>
       <c r="E7" s="3">
-        <v>18.8</v>
+        <v>17.98</v>
       </c>
       <c r="F7" s="2">
-        <v>527.3</v>
+        <v>508.7</v>
       </c>
       <c r="G7" s="2">
-        <v>15.5</v>
+        <v>15.0</v>
       </c>
       <c r="H7" s="3">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="I7" s="4">
-        <v>38.0</v>
+        <v>34.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -825,25 +825,25 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>7.02</v>
+        <v>6.56</v>
       </c>
       <c r="D8" s="3">
-        <v>19.13</v>
+        <v>18.51</v>
       </c>
       <c r="E8" s="3">
-        <v>6.41</v>
+        <v>6.02</v>
       </c>
       <c r="F8" s="2">
-        <v>142.1</v>
+        <v>132.8</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="4">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -860,25 +860,25 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>19.4</v>
+        <v>19.31</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
       </c>
       <c r="E9" s="3">
-        <v>18.88</v>
+        <v>18.46</v>
       </c>
       <c r="F9" s="2">
-        <v>504.6</v>
+        <v>502.3</v>
       </c>
       <c r="G9" s="2">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="H9" s="3">
         <v>1.44</v>
       </c>
       <c r="I9" s="4">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -892,7 +892,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>16.1</v>
+        <v>15.11</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
@@ -901,16 +901,16 @@
         <v>12.34</v>
       </c>
       <c r="F10" s="2">
-        <v>220.0</v>
+        <v>206.5</v>
       </c>
       <c r="G10" s="2">
-        <v>17.3</v>
+        <v>16.2</v>
       </c>
       <c r="H10" s="3">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="I10" s="4">
-        <v>87.0</v>
+        <v>85.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -924,25 +924,25 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>13.38</v>
+        <v>12.1</v>
       </c>
       <c r="D11" s="3">
-        <v>20.18</v>
+        <v>18.68</v>
       </c>
       <c r="E11" s="3">
-        <v>13.27</v>
+        <v>12.1</v>
       </c>
       <c r="F11" s="2">
-        <v>84.7</v>
+        <v>76.6</v>
       </c>
       <c r="G11" s="2">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="H11" s="3">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="I11" s="4">
-        <v>49.0</v>
+        <v>36.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -959,25 +959,25 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>13.83</v>
+        <v>15.5</v>
       </c>
       <c r="D12" s="3">
         <v>19.52</v>
       </c>
       <c r="E12" s="3">
-        <v>13.4</v>
+        <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>96.4</v>
+        <v>108.0</v>
       </c>
       <c r="G12" s="2">
-        <v>17.0</v>
+        <v>19.1</v>
       </c>
       <c r="H12" s="3">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="I12" s="4">
-        <v>51.0</v>
+        <v>66.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -991,7 +991,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>5.52</v>
+        <v>5.97</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1000,16 +1000,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>315.0</v>
+        <v>340.7</v>
       </c>
       <c r="G13" s="2">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="H13" s="3">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="I13" s="4">
-        <v>81.0</v>
+        <v>87.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1023,25 +1023,25 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>9.16</v>
+        <v>8.49</v>
       </c>
       <c r="D14" s="3">
-        <v>23.73</v>
+        <v>20.9</v>
       </c>
       <c r="E14" s="3">
-        <v>8.03</v>
+        <v>7.77</v>
       </c>
       <c r="F14" s="2">
-        <v>96.6</v>
+        <v>89.5</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="I14" s="4">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>18</v>
@@ -1058,25 +1058,25 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>13.28</v>
+        <v>13.54</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
       </c>
       <c r="E15" s="3">
-        <v>12.57</v>
+        <v>12.41</v>
       </c>
       <c r="F15" s="2">
-        <v>326.1</v>
+        <v>332.5</v>
       </c>
       <c r="G15" s="2">
-        <v>41.5</v>
+        <v>42.3</v>
       </c>
       <c r="H15" s="3">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I15" s="4">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1093,7 +1093,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>17.85</v>
+        <v>16.03</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
@@ -1102,16 +1102,16 @@
         <v>15.1</v>
       </c>
       <c r="F16" s="2">
-        <v>169.6</v>
+        <v>152.3</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="I16" s="4">
-        <v>60.0</v>
+        <v>44.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1128,25 +1128,25 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="D17" s="3">
         <v>14.04</v>
       </c>
       <c r="E17" s="3">
-        <v>5.62</v>
+        <v>5.41</v>
       </c>
       <c r="F17" s="2">
-        <v>227.1</v>
+        <v>208.9</v>
       </c>
       <c r="G17" s="2">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="H17" s="3">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="I17" s="4">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1160,7 +1160,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>9.32</v>
+        <v>9.33</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
@@ -1169,10 +1169,10 @@
         <v>7.45</v>
       </c>
       <c r="F18" s="2">
-        <v>289.2</v>
+        <v>289.5</v>
       </c>
       <c r="G18" s="2">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H18" s="3">
         <v>1.45</v>
@@ -1192,25 +1192,25 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>31.68</v>
+        <v>36.43</v>
       </c>
       <c r="D19" s="3">
-        <v>34.78</v>
+        <v>39.65</v>
       </c>
       <c r="E19" s="3">
         <v>25.19</v>
       </c>
       <c r="F19" s="2">
-        <v>235.5</v>
+        <v>270.8</v>
       </c>
       <c r="G19" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="I19" s="4">
-        <v>87.0</v>
+        <v>93.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1227,7 +1227,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>17.95</v>
+        <v>18.52</v>
       </c>
       <c r="D20" s="3">
         <v>29.74</v>
@@ -1236,16 +1236,16 @@
         <v>16.7</v>
       </c>
       <c r="F20" s="2">
-        <v>224.5</v>
+        <v>231.6</v>
       </c>
       <c r="G20" s="2">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="I20" s="4">
-        <v>60.0</v>
+        <v>57.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1262,7 +1262,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>30.47</v>
+        <v>25.37</v>
       </c>
       <c r="D21" s="3">
         <v>38.95</v>
@@ -1271,16 +1271,16 @@
         <v>15.35</v>
       </c>
       <c r="F21" s="2">
-        <v>77.4</v>
+        <v>64.5</v>
       </c>
       <c r="G21" s="2">
-        <v>11.9</v>
+        <v>9.9</v>
       </c>
       <c r="H21" s="3">
-        <v>0.67</v>
+        <v>0.56</v>
       </c>
       <c r="I21" s="4">
-        <v>96.0</v>
+        <v>94.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1294,25 +1294,25 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>9.0</v>
+        <v>7.96</v>
       </c>
       <c r="D22" s="3">
         <v>19.15</v>
       </c>
       <c r="E22" s="3">
-        <v>8.01</v>
+        <v>7.25</v>
       </c>
       <c r="F22" s="2">
-        <v>24.8</v>
+        <v>22.0</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="3">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="I22" s="4">
-        <v>35.0</v>
+        <v>22.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1326,7 +1326,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>4.12</v>
+        <v>4.3</v>
       </c>
       <c r="D23" s="3">
         <v>8.32</v>
@@ -1335,16 +1335,16 @@
         <v>3.93</v>
       </c>
       <c r="F23" s="2">
-        <v>270.1</v>
+        <v>282.2</v>
       </c>
       <c r="G23" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H23" s="3">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="I23" s="4">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1361,25 +1361,25 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>19.4</v>
+        <v>19.49</v>
       </c>
       <c r="D24" s="3">
         <v>34.5</v>
       </c>
       <c r="E24" s="3">
-        <v>18.54</v>
+        <v>18.23</v>
       </c>
       <c r="F24" s="2">
-        <v>263.0</v>
+        <v>264.2</v>
       </c>
       <c r="G24" s="2">
         <v>6.1</v>
       </c>
       <c r="H24" s="3">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I24" s="4">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1396,7 +1396,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>17.82</v>
+        <v>16.13</v>
       </c>
       <c r="D25" s="3">
         <v>35.5</v>
@@ -1405,16 +1405,16 @@
         <v>3.87</v>
       </c>
       <c r="F25" s="2">
-        <v>43.4</v>
+        <v>39.3</v>
       </c>
       <c r="G25" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H25" s="3">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="I25" s="4">
-        <v>23.0</v>
+        <v>19.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1431,25 +1431,25 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>15.82</v>
+        <v>13.03</v>
       </c>
       <c r="D26" s="3">
         <v>40.14</v>
       </c>
       <c r="E26" s="3">
-        <v>14.86</v>
+        <v>12.71</v>
       </c>
       <c r="F26" s="2">
-        <v>118.1</v>
+        <v>97.2</v>
       </c>
       <c r="G26" s="2">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="I26" s="4">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1466,7 +1466,7 @@
         <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>11.77</v>
+        <v>11.35</v>
       </c>
       <c r="D27" s="3">
         <v>23.56</v>
@@ -1475,16 +1475,16 @@
         <v>10.75</v>
       </c>
       <c r="F27" s="2">
-        <v>75.8</v>
+        <v>73.1</v>
       </c>
       <c r="G27" s="2">
-        <v>21.4</v>
+        <v>20.6</v>
       </c>
       <c r="H27" s="3">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="I27" s="4">
-        <v>47.0</v>
+        <v>41.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1501,7 +1501,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="D28" s="3">
         <v>8.84</v>
@@ -1510,7 +1510,7 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>188.1</v>
+        <v>190.0</v>
       </c>
       <c r="G28" s="2">
         <v>2.7</v>
@@ -1519,7 +1519,7 @@
         <v>0.29</v>
       </c>
       <c r="I28" s="4">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1536,25 +1536,25 @@
         <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>15.0</v>
+        <v>16.34</v>
       </c>
       <c r="D29" s="3">
-        <v>24.31</v>
+        <v>24.28</v>
       </c>
       <c r="E29" s="3">
         <v>12.3</v>
       </c>
       <c r="F29" s="2">
-        <v>341.8</v>
+        <v>369.8</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="3">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="I29" s="4">
-        <v>82.0</v>
+        <v>87.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>97</v>
@@ -1568,25 +1568,25 @@
         <v>99</v>
       </c>
       <c r="C30" s="3">
-        <v>20.44</v>
+        <v>20.03</v>
       </c>
       <c r="D30" s="3">
         <v>35.11</v>
       </c>
       <c r="E30" s="3">
-        <v>19.16</v>
+        <v>18.57</v>
       </c>
       <c r="F30" s="2">
-        <v>271.0</v>
+        <v>265.5</v>
       </c>
       <c r="G30" s="2">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="H30" s="3">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="I30" s="4">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>13</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="qexYYMELXQcUNI+xJtusD2Wl8+KAQLopP50c3b6ggYg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="fFLYGIzfwHlT293pPsf/qiAGCGdXI3BT3rBOgUubkF8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
   <si>
     <t>Company</t>
   </si>
@@ -111,7 +111,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>News Archive for CVLG</t>
+    <t>(4/23/25) Covenant Logistics Group, Inc. (CVLG)</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -132,7 +132,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>News Archive for EBF</t>
+    <t>(4/21/25) Ennis, Inc. (EBF)</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -195,7 +195,7 @@
     <t>LAKE</t>
   </si>
   <si>
-    <t>(4/9/25) Lakeland Industries, Inc. (LAKE)</t>
+    <t>News Archive for LAKE</t>
   </si>
   <si>
     <t>Landsea Homes Corporation</t>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>NSYS</t>
+  </si>
+  <si>
+    <t>Earnings probation 2024Q4</t>
   </si>
   <si>
     <t>News Archive for NSYS</t>
@@ -627,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.16</v>
+        <v>4.47</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -636,16 +639,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>45.0</v>
+        <v>48.3</v>
       </c>
       <c r="G2" s="2">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
       <c r="H2" s="3">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="I2" s="4">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -662,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="D3" s="3">
         <v>12.67</v>
@@ -671,13 +674,13 @@
         <v>3.28</v>
       </c>
       <c r="F3" s="2">
-        <v>108.2</v>
+        <v>118.3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="I3" s="4">
         <v>30.0</v>
@@ -697,25 +700,25 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
       </c>
       <c r="E4" s="3">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="F4" s="2">
-        <v>96.4</v>
+        <v>108.5</v>
       </c>
       <c r="G4" s="2">
-        <v>7.7</v>
+        <v>8.7</v>
       </c>
       <c r="H4" s="3">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="I4" s="4">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -729,7 +732,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
@@ -738,7 +741,7 @@
         <v>1.98</v>
       </c>
       <c r="F5" s="2">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="G5" s="2">
         <v>0.9</v>
@@ -747,7 +750,7 @@
         <v>0.04</v>
       </c>
       <c r="I5" s="4">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -761,7 +764,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>15.08</v>
+        <v>15.09</v>
       </c>
       <c r="D6" s="3">
         <v>21.0</v>
@@ -770,7 +773,7 @@
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>129.9</v>
+        <v>135.5</v>
       </c>
       <c r="G6" s="2">
         <v>10.0</v>
@@ -779,7 +782,7 @@
         <v>0.88</v>
       </c>
       <c r="I6" s="4">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -793,25 +796,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>19.16</v>
+        <v>19.78</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
       </c>
       <c r="E7" s="3">
-        <v>17.98</v>
+        <v>17.46</v>
       </c>
       <c r="F7" s="2">
-        <v>508.7</v>
+        <v>525.3</v>
       </c>
       <c r="G7" s="2">
-        <v>15.0</v>
+        <v>14.3</v>
       </c>
       <c r="H7" s="3">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="I7" s="4">
-        <v>34.0</v>
+        <v>30.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -825,25 +828,25 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>6.56</v>
+        <v>6.82</v>
       </c>
       <c r="D8" s="3">
-        <v>18.51</v>
+        <v>17.14</v>
       </c>
       <c r="E8" s="3">
         <v>6.02</v>
       </c>
       <c r="F8" s="2">
-        <v>132.8</v>
+        <v>140.2</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I8" s="4">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -860,25 +863,25 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>19.31</v>
+        <v>17.92</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
       </c>
       <c r="E9" s="3">
-        <v>18.46</v>
+        <v>17.15</v>
       </c>
       <c r="F9" s="2">
-        <v>502.3</v>
+        <v>466.1</v>
       </c>
       <c r="G9" s="2">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="H9" s="3">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="I9" s="4">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -892,7 +895,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>15.11</v>
+        <v>14.59</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
@@ -901,16 +904,16 @@
         <v>12.34</v>
       </c>
       <c r="F10" s="2">
-        <v>206.5</v>
+        <v>199.4</v>
       </c>
       <c r="G10" s="2">
-        <v>16.2</v>
+        <v>15.7</v>
       </c>
       <c r="H10" s="3">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="I10" s="4">
-        <v>85.0</v>
+        <v>75.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -924,25 +927,25 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>12.1</v>
+        <v>12.02</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
       </c>
       <c r="E11" s="3">
-        <v>12.1</v>
+        <v>12.02</v>
       </c>
       <c r="F11" s="2">
-        <v>76.6</v>
+        <v>76.1</v>
       </c>
       <c r="G11" s="2">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="H11" s="3">
         <v>0.49</v>
       </c>
       <c r="I11" s="4">
-        <v>36.0</v>
+        <v>33.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -959,25 +962,25 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>15.5</v>
+        <v>17.15</v>
       </c>
       <c r="D12" s="3">
-        <v>19.52</v>
+        <v>19.47</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>108.0</v>
+        <v>119.5</v>
       </c>
       <c r="G12" s="2">
-        <v>19.1</v>
+        <v>21.1</v>
       </c>
       <c r="H12" s="3">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="I12" s="4">
-        <v>66.0</v>
+        <v>86.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -991,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>5.97</v>
+        <v>6.36</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1000,16 +1003,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>340.7</v>
+        <v>362.6</v>
       </c>
       <c r="G13" s="2">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H13" s="3">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="I13" s="4">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1023,22 +1026,22 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>8.49</v>
+        <v>8.85</v>
       </c>
       <c r="D14" s="3">
-        <v>20.9</v>
+        <v>19.79</v>
       </c>
       <c r="E14" s="3">
-        <v>7.77</v>
+        <v>7.34</v>
       </c>
       <c r="F14" s="2">
-        <v>89.5</v>
+        <v>93.4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="I14" s="4">
         <v>13.0</v>
@@ -1058,7 +1061,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>13.54</v>
+        <v>14.57</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
@@ -1067,16 +1070,16 @@
         <v>12.41</v>
       </c>
       <c r="F15" s="2">
-        <v>332.5</v>
+        <v>357.8</v>
       </c>
       <c r="G15" s="2">
-        <v>42.3</v>
+        <v>45.5</v>
       </c>
       <c r="H15" s="3">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="I15" s="4">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1093,25 +1096,25 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>16.03</v>
+        <v>16.81</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
       </c>
       <c r="E16" s="3">
-        <v>15.1</v>
+        <v>14.58</v>
       </c>
       <c r="F16" s="2">
-        <v>152.3</v>
+        <v>159.7</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="I16" s="4">
-        <v>44.0</v>
+        <v>34.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1128,7 +1131,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>5.75</v>
+        <v>6.13</v>
       </c>
       <c r="D17" s="3">
         <v>14.04</v>
@@ -1137,13 +1140,13 @@
         <v>5.41</v>
       </c>
       <c r="F17" s="2">
-        <v>208.9</v>
+        <v>222.7</v>
       </c>
       <c r="G17" s="2">
-        <v>12.2</v>
+        <v>13.0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="I17" s="4">
         <v>13.0</v>
@@ -1160,7 +1163,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>9.33</v>
+        <v>9.19</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
@@ -1169,16 +1172,16 @@
         <v>7.45</v>
       </c>
       <c r="F18" s="2">
-        <v>289.5</v>
+        <v>287.7</v>
       </c>
       <c r="G18" s="2">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="H18" s="3">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="I18" s="4">
-        <v>46.0</v>
+        <v>38.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1192,7 +1195,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>36.43</v>
+        <v>35.65</v>
       </c>
       <c r="D19" s="3">
         <v>39.65</v>
@@ -1201,16 +1204,16 @@
         <v>25.19</v>
       </c>
       <c r="F19" s="2">
-        <v>270.8</v>
+        <v>265.0</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>7.8</v>
       </c>
       <c r="H19" s="3">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="I19" s="4">
-        <v>93.0</v>
+        <v>89.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1227,7 +1230,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>18.52</v>
+        <v>19.52</v>
       </c>
       <c r="D20" s="3">
         <v>29.74</v>
@@ -1236,19 +1239,16 @@
         <v>16.7</v>
       </c>
       <c r="F20" s="2">
-        <v>231.6</v>
+        <v>244.1</v>
       </c>
       <c r="G20" s="2">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="H20" s="3">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I20" s="4">
-        <v>57.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>63.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1262,25 +1262,25 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>25.37</v>
+        <v>30.28</v>
       </c>
       <c r="D21" s="3">
         <v>38.95</v>
       </c>
       <c r="E21" s="3">
-        <v>15.35</v>
+        <v>15.9</v>
       </c>
       <c r="F21" s="2">
-        <v>64.5</v>
+        <v>76.9</v>
       </c>
       <c r="G21" s="2">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="H21" s="3">
-        <v>0.56</v>
+        <v>0.67</v>
       </c>
       <c r="I21" s="4">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1294,7 +1294,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>7.96</v>
+        <v>8.45</v>
       </c>
       <c r="D22" s="3">
         <v>19.15</v>
@@ -1303,30 +1303,33 @@
         <v>7.25</v>
       </c>
       <c r="F22" s="2">
-        <v>22.0</v>
+        <v>23.3</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="3">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I22" s="4">
         <v>22.0</v>
       </c>
+      <c r="J22" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="K22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="D23" s="3">
         <v>8.32</v>
@@ -1335,10 +1338,10 @@
         <v>3.93</v>
       </c>
       <c r="F23" s="2">
-        <v>282.2</v>
+        <v>277.0</v>
       </c>
       <c r="G23" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H23" s="3">
         <v>0.41</v>
@@ -1346,57 +1349,54 @@
       <c r="I23" s="4">
         <v>22.0</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="K23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>19.49</v>
+        <v>19.3</v>
       </c>
       <c r="D24" s="3">
         <v>34.5</v>
       </c>
       <c r="E24" s="3">
-        <v>18.23</v>
+        <v>17.9</v>
       </c>
       <c r="F24" s="2">
-        <v>264.2</v>
+        <v>261.6</v>
       </c>
       <c r="G24" s="2">
         <v>6.1</v>
       </c>
       <c r="H24" s="3">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I24" s="4">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>16.13</v>
+        <v>18.18</v>
       </c>
       <c r="D25" s="3">
         <v>35.5</v>
@@ -1405,68 +1405,68 @@
         <v>3.87</v>
       </c>
       <c r="F25" s="2">
-        <v>39.3</v>
+        <v>44.3</v>
       </c>
       <c r="G25" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H25" s="3">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="I25" s="4">
-        <v>19.0</v>
+        <v>25.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>13.03</v>
+        <v>13.7</v>
       </c>
       <c r="D26" s="3">
         <v>40.14</v>
       </c>
       <c r="E26" s="3">
-        <v>12.71</v>
+        <v>11.93</v>
       </c>
       <c r="F26" s="2">
-        <v>97.2</v>
+        <v>102.2</v>
       </c>
       <c r="G26" s="2">
-        <v>8.6</v>
+        <v>9.0</v>
       </c>
       <c r="H26" s="3">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="I26" s="4">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>11.35</v>
+        <v>11.5</v>
       </c>
       <c r="D27" s="3">
         <v>23.56</v>
@@ -1475,33 +1475,33 @@
         <v>10.75</v>
       </c>
       <c r="F27" s="2">
-        <v>73.1</v>
+        <v>74.1</v>
       </c>
       <c r="G27" s="2">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="H27" s="3">
         <v>0.42</v>
       </c>
       <c r="I27" s="4">
-        <v>41.0</v>
+        <v>37.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>5.17</v>
+        <v>5.45</v>
       </c>
       <c r="D28" s="3">
         <v>8.84</v>
@@ -1510,33 +1510,33 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>190.0</v>
+        <v>200.2</v>
       </c>
       <c r="G28" s="2">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="H28" s="3">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="I28" s="4">
-        <v>36.0</v>
+        <v>45.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>16.34</v>
+        <v>17.07</v>
       </c>
       <c r="D29" s="3">
         <v>24.28</v>
@@ -1545,30 +1545,33 @@
         <v>12.3</v>
       </c>
       <c r="F29" s="2">
-        <v>369.8</v>
+        <v>386.3</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="3">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="I29" s="4">
-        <v>87.0</v>
+        <v>82.0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" s="3">
-        <v>20.03</v>
+        <v>21.9</v>
       </c>
       <c r="D30" s="3">
         <v>35.11</v>
@@ -1577,22 +1580,22 @@
         <v>18.57</v>
       </c>
       <c r="F30" s="2">
-        <v>265.5</v>
+        <v>290.3</v>
       </c>
       <c r="G30" s="2">
-        <v>27.1</v>
+        <v>29.6</v>
       </c>
       <c r="H30" s="3">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="I30" s="4">
-        <v>47.0</v>
+        <v>57.0</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="fFLYGIzfwHlT293pPsf/qiAGCGdXI3BT3rBOgUubkF8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="P1ex5wSmmTb1puO8zahiUFDJNtiuDQ0tifIlZsXdTIM="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="102">
   <si>
     <t>Company</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Currently qualifies</t>
   </si>
   <si>
-    <t>News Archive for APT</t>
+    <t>(5/8/25) Alpha Pro Tech, Ltd. (APT)</t>
   </si>
   <si>
     <t>American Vanguard Corporation</t>
@@ -102,7 +102,7 @@
     <t>CMT</t>
   </si>
   <si>
-    <t>News Archive for CMT</t>
+    <t>(5/8/25) Core Molding Technologies, Inc. (CMT)</t>
   </si>
   <si>
     <t>Covenant Logistics Group, Inc.</t>
@@ -111,7 +111,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>(4/23/25) Covenant Logistics Group, Inc. (CVLG)</t>
+    <t>News Archive for CVLG</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -132,7 +132,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>(4/21/25) Ennis, Inc. (EBF)</t>
+    <t>News Archive for EBF</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -141,7 +141,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>News Archive for ESCA</t>
+    <t>(5/5/25) Escalade, Incorporated (ESCA)</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -186,7 +186,7 @@
     <t>KE</t>
   </si>
   <si>
-    <t>News Archive for KE</t>
+    <t>(5/6/25) Kimball Electronics, Inc. (KE)</t>
   </si>
   <si>
     <t>Lakeland Industries, Inc.</t>
@@ -213,7 +213,7 @@
     <t>MG</t>
   </si>
   <si>
-    <t>News Archive for MG</t>
+    <t>(5/7/25) Mistras Group, Inc. (MG)</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -267,7 +267,7 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>News Archive for PKOH</t>
+    <t>(5/6/25) Park-Ohio Holdings Corp. (PKOH)</t>
   </si>
   <si>
     <t>Regis Corporation</t>
@@ -321,7 +321,7 @@
     <t>VPG</t>
   </si>
   <si>
-    <t>News Archive for VPG</t>
+    <t>(5/6/25) Vishay Precision Group, Inc. (VPG)</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.47</v>
+        <v>4.68</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -639,16 +639,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.3</v>
+        <v>50.6</v>
       </c>
       <c r="G2" s="2">
-        <v>12.8</v>
+        <v>13.0</v>
       </c>
       <c r="H2" s="3">
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,25 +665,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.11</v>
+        <v>4.45</v>
       </c>
       <c r="D3" s="3">
-        <v>12.67</v>
+        <v>12.15</v>
       </c>
       <c r="E3" s="3">
         <v>3.28</v>
       </c>
       <c r="F3" s="2">
-        <v>118.3</v>
+        <v>128.1</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="I3" s="4">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -700,7 +700,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
@@ -709,13 +709,13 @@
         <v>2.27</v>
       </c>
       <c r="F4" s="2">
-        <v>108.5</v>
+        <v>116.6</v>
       </c>
       <c r="G4" s="2">
-        <v>8.7</v>
+        <v>9.3</v>
       </c>
       <c r="H4" s="3">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="I4" s="4">
         <v>8.0</v>
@@ -732,7 +732,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
@@ -741,16 +741,16 @@
         <v>1.98</v>
       </c>
       <c r="F5" s="2">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="G5" s="2">
-        <v>0.9</v>
+        <v>1.0</v>
       </c>
       <c r="H5" s="3">
         <v>0.04</v>
       </c>
       <c r="I5" s="4">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -764,7 +764,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>15.09</v>
+        <v>15.59</v>
       </c>
       <c r="D6" s="3">
         <v>21.0</v>
@@ -773,16 +773,16 @@
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>135.5</v>
+        <v>139.9</v>
       </c>
       <c r="G6" s="2">
-        <v>10.0</v>
+        <v>11.7</v>
       </c>
       <c r="H6" s="3">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I6" s="4">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -796,7 +796,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>19.78</v>
+        <v>20.98</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
@@ -805,16 +805,16 @@
         <v>17.46</v>
       </c>
       <c r="F7" s="2">
-        <v>525.3</v>
+        <v>557.1</v>
       </c>
       <c r="G7" s="2">
-        <v>14.3</v>
+        <v>15.2</v>
       </c>
       <c r="H7" s="3">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="I7" s="4">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -828,16 +828,16 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>6.82</v>
+        <v>6.93</v>
       </c>
       <c r="D8" s="3">
-        <v>17.14</v>
+        <v>15.14</v>
       </c>
       <c r="E8" s="3">
         <v>6.02</v>
       </c>
       <c r="F8" s="2">
-        <v>140.2</v>
+        <v>142.0</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -846,7 +846,7 @@
         <v>0.31</v>
       </c>
       <c r="I8" s="4">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -863,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>17.92</v>
+        <v>18.96</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
@@ -872,16 +872,16 @@
         <v>17.15</v>
       </c>
       <c r="F9" s="2">
-        <v>466.1</v>
+        <v>493.2</v>
       </c>
       <c r="G9" s="2">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="I9" s="4">
-        <v>46.0</v>
+        <v>50.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -895,25 +895,25 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>14.59</v>
+        <v>14.75</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
       </c>
       <c r="E10" s="3">
-        <v>12.34</v>
+        <v>12.53</v>
       </c>
       <c r="F10" s="2">
-        <v>199.4</v>
+        <v>203.4</v>
       </c>
       <c r="G10" s="2">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="I10" s="4">
-        <v>75.0</v>
+        <v>67.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -927,22 +927,22 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>12.02</v>
+        <v>12.39</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
       </c>
       <c r="E11" s="3">
-        <v>12.02</v>
+        <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>76.1</v>
+        <v>78.4</v>
       </c>
       <c r="G11" s="2">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="H11" s="3">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="4">
         <v>33.0</v>
@@ -962,25 +962,25 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>17.15</v>
+        <v>15.8</v>
       </c>
       <c r="D12" s="3">
-        <v>19.47</v>
+        <v>19.18</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>119.5</v>
+        <v>110.1</v>
       </c>
       <c r="G12" s="2">
-        <v>21.1</v>
+        <v>19.4</v>
       </c>
       <c r="H12" s="3">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="I12" s="4">
-        <v>86.0</v>
+        <v>77.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>6.36</v>
+        <v>6.52</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1003,16 +1003,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>362.6</v>
+        <v>372.1</v>
       </c>
       <c r="G13" s="2">
-        <v>14.6</v>
+        <v>15.0</v>
       </c>
       <c r="H13" s="3">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="I13" s="4">
-        <v>89.0</v>
+        <v>85.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1026,7 +1026,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>8.85</v>
+        <v>9.24</v>
       </c>
       <c r="D14" s="3">
         <v>19.79</v>
@@ -1035,16 +1035,16 @@
         <v>7.34</v>
       </c>
       <c r="F14" s="2">
-        <v>93.4</v>
+        <v>97.5</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="I14" s="4">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>18</v>
@@ -1061,7 +1061,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>14.57</v>
+        <v>18.24</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
@@ -1070,19 +1070,16 @@
         <v>12.41</v>
       </c>
       <c r="F15" s="2">
-        <v>357.8</v>
+        <v>444.7</v>
       </c>
       <c r="G15" s="2">
-        <v>45.5</v>
+        <v>25.7</v>
       </c>
       <c r="H15" s="3">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="I15" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>51.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
@@ -1096,7 +1093,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>16.81</v>
+        <v>17.06</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
@@ -1105,16 +1102,16 @@
         <v>14.58</v>
       </c>
       <c r="F16" s="2">
-        <v>159.7</v>
+        <v>162.0</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I16" s="4">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1131,7 +1128,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>6.13</v>
+        <v>6.55</v>
       </c>
       <c r="D17" s="3">
         <v>14.04</v>
@@ -1140,16 +1137,16 @@
         <v>5.41</v>
       </c>
       <c r="F17" s="2">
-        <v>222.7</v>
+        <v>238.0</v>
       </c>
       <c r="G17" s="2">
-        <v>13.0</v>
+        <v>13.9</v>
       </c>
       <c r="H17" s="3">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="I17" s="4">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1163,25 +1160,25 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>9.19</v>
+        <v>7.82</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
       </c>
       <c r="E18" s="3">
-        <v>7.45</v>
+        <v>7.06</v>
       </c>
       <c r="F18" s="2">
-        <v>287.7</v>
+        <v>245.0</v>
       </c>
       <c r="G18" s="2">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="H18" s="3">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="I18" s="4">
-        <v>38.0</v>
+        <v>45.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1195,7 +1192,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>35.65</v>
+        <v>33.56</v>
       </c>
       <c r="D19" s="3">
         <v>39.65</v>
@@ -1204,16 +1201,16 @@
         <v>25.19</v>
       </c>
       <c r="F19" s="2">
-        <v>265.0</v>
+        <v>249.8</v>
       </c>
       <c r="G19" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="H19" s="3">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="I19" s="4">
-        <v>89.0</v>
+        <v>71.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1230,7 +1227,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>19.52</v>
+        <v>20.46</v>
       </c>
       <c r="D20" s="3">
         <v>29.74</v>
@@ -1239,13 +1236,13 @@
         <v>16.7</v>
       </c>
       <c r="F20" s="2">
-        <v>244.1</v>
+        <v>256.0</v>
       </c>
       <c r="G20" s="2">
-        <v>14.2</v>
+        <v>14.9</v>
       </c>
       <c r="H20" s="3">
-        <v>0.95</v>
+        <v>1.0</v>
       </c>
       <c r="I20" s="4">
         <v>63.0</v>
@@ -1262,7 +1259,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>30.28</v>
+        <v>31.56</v>
       </c>
       <c r="D21" s="3">
         <v>38.95</v>
@@ -1271,16 +1268,16 @@
         <v>15.9</v>
       </c>
       <c r="F21" s="2">
-        <v>76.9</v>
+        <v>80.2</v>
       </c>
       <c r="G21" s="2">
-        <v>11.9</v>
+        <v>9.7</v>
       </c>
       <c r="H21" s="3">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="I21" s="4">
-        <v>96.0</v>
+        <v>93.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1294,25 +1291,25 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>8.45</v>
+        <v>8.65</v>
       </c>
       <c r="D22" s="3">
-        <v>19.15</v>
+        <v>17.89</v>
       </c>
       <c r="E22" s="3">
         <v>7.25</v>
       </c>
       <c r="F22" s="2">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="3">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="I22" s="4">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>76</v>
@@ -1329,7 +1326,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>4.22</v>
+        <v>4.01</v>
       </c>
       <c r="D23" s="3">
         <v>8.32</v>
@@ -1338,16 +1335,16 @@
         <v>3.93</v>
       </c>
       <c r="F23" s="2">
-        <v>277.0</v>
+        <v>263.2</v>
       </c>
       <c r="G23" s="2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H23" s="3">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="I23" s="4">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1361,22 +1358,22 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>19.3</v>
+        <v>19.55</v>
       </c>
       <c r="D24" s="3">
         <v>34.5</v>
       </c>
       <c r="E24" s="3">
-        <v>17.9</v>
+        <v>17.58</v>
       </c>
       <c r="F24" s="2">
-        <v>261.6</v>
+        <v>278.2</v>
       </c>
       <c r="G24" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I24" s="4">
         <v>21.0</v>
@@ -1396,7 +1393,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>18.18</v>
+        <v>19.11</v>
       </c>
       <c r="D25" s="3">
         <v>35.5</v>
@@ -1405,16 +1402,16 @@
         <v>3.87</v>
       </c>
       <c r="F25" s="2">
-        <v>44.3</v>
+        <v>46.6</v>
       </c>
       <c r="G25" s="2">
         <v>0.5</v>
       </c>
       <c r="H25" s="3">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="I25" s="4">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1431,7 +1428,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>13.7</v>
+        <v>20.42</v>
       </c>
       <c r="D26" s="3">
         <v>40.14</v>
@@ -1440,16 +1437,16 @@
         <v>11.93</v>
       </c>
       <c r="F26" s="2">
-        <v>102.2</v>
+        <v>152.4</v>
       </c>
       <c r="G26" s="2">
-        <v>9.0</v>
+        <v>11.1</v>
       </c>
       <c r="H26" s="3">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="I26" s="4">
-        <v>11.0</v>
+        <v>63.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1466,28 +1463,25 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>11.5</v>
+        <v>11.77</v>
       </c>
       <c r="D27" s="3">
-        <v>23.56</v>
+        <v>21.41</v>
       </c>
       <c r="E27" s="3">
         <v>10.75</v>
       </c>
       <c r="F27" s="2">
-        <v>74.1</v>
+        <v>75.8</v>
       </c>
       <c r="G27" s="2">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="H27" s="3">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="I27" s="4">
-        <v>37.0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>41.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>92</v>
@@ -1501,7 +1495,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>5.45</v>
+        <v>5.37</v>
       </c>
       <c r="D28" s="3">
         <v>8.84</v>
@@ -1510,16 +1504,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>200.2</v>
+        <v>198.6</v>
       </c>
       <c r="G28" s="2">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H28" s="3">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="4">
-        <v>45.0</v>
+        <v>53.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1536,7 +1530,7 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>17.07</v>
+        <v>19.36</v>
       </c>
       <c r="D29" s="3">
         <v>24.28</v>
@@ -1545,16 +1539,16 @@
         <v>12.3</v>
       </c>
       <c r="F29" s="2">
-        <v>386.3</v>
+        <v>437.4</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="3">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="I29" s="4">
-        <v>82.0</v>
+        <v>91.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>76</v>
@@ -1571,7 +1565,7 @@
         <v>100</v>
       </c>
       <c r="C30" s="3">
-        <v>21.9</v>
+        <v>24.58</v>
       </c>
       <c r="D30" s="3">
         <v>35.11</v>
@@ -1580,19 +1574,16 @@
         <v>18.57</v>
       </c>
       <c r="F30" s="2">
-        <v>290.3</v>
+        <v>325.9</v>
       </c>
       <c r="G30" s="2">
-        <v>29.6</v>
+        <v>107.3</v>
       </c>
       <c r="H30" s="3">
-        <v>0.9</v>
+        <v>1.01</v>
       </c>
       <c r="I30" s="4">
-        <v>57.0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>13</v>
+        <v>76.0</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>101</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="P1ex5wSmmTb1puO8zahiUFDJNtiuDQ0tifIlZsXdTIM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lumVIXqZwST8vFf0/C1MJvI1P7v198C8qWp1guo9PW0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>Company</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Currently qualifies</t>
   </si>
   <si>
-    <t>(5/8/25) Alpha Pro Tech, Ltd. (APT)</t>
+    <t>News Archive for APT</t>
   </si>
   <si>
     <t>American Vanguard Corporation</t>
@@ -84,7 +84,7 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>News Archive for AMPY</t>
+    <t>(5/12/25) Amplify Energy Corp. (AMPY)</t>
   </si>
   <si>
     <t>Castor Maritime Inc.</t>
@@ -93,7 +93,7 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>News Archive for CTRM</t>
+    <t>(5/14/25) Castor Maritime Inc. (CTRM)</t>
   </si>
   <si>
     <t>Core Molding Technologies, Inc.</t>
@@ -102,7 +102,7 @@
     <t>CMT</t>
   </si>
   <si>
-    <t>(5/8/25) Core Molding Technologies, Inc. (CMT)</t>
+    <t>News Archive for CMT</t>
   </si>
   <si>
     <t>Covenant Logistics Group, Inc.</t>
@@ -141,7 +141,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(5/5/25) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -150,7 +150,7 @@
     <t>FONR</t>
   </si>
   <si>
-    <t>News Archive for FONR</t>
+    <t>(5/15/25) FONAR Corporation (FONR)</t>
   </si>
   <si>
     <t>Friedman Industries, Incorporated</t>
@@ -186,7 +186,7 @@
     <t>KE</t>
   </si>
   <si>
-    <t>(5/6/25) Kimball Electronics, Inc. (KE)</t>
+    <t>News Archive for KE</t>
   </si>
   <si>
     <t>Lakeland Industries, Inc.</t>
@@ -204,7 +204,7 @@
     <t>LSEA</t>
   </si>
   <si>
-    <t>News Archive for LSEA</t>
+    <t>(5/12/25) Landsea Homes Corporation (LSEA)</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -213,7 +213,7 @@
     <t>MG</t>
   </si>
   <si>
-    <t>(5/7/25) Mistras Group, Inc. (MG)</t>
+    <t>News Archive for MG</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -222,7 +222,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>News Archive for NC</t>
+    <t>(5/15/25) NACCO Industries, Inc. (NC)</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -231,7 +231,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>News Archive for NGS</t>
+    <t>(5/12/25) Natural Gas Services Group, Inc. (NGS)</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -249,7 +249,7 @@
     <t>Earnings probation 2024Q4</t>
   </si>
   <si>
-    <t>News Archive for NSYS</t>
+    <t>(5/14/25) Nortech Systems Incorporated (NSYS)</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
@@ -258,7 +258,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>News Archive for PANL</t>
+    <t>(5/12/25) Pangaea Logistics Solutions, Ltd. (PANL)</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -267,7 +267,7 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>(5/6/25) Park-Ohio Holdings Corp. (PKOH)</t>
+    <t>News Archive for PKOH</t>
   </si>
   <si>
     <t>Regis Corporation</t>
@@ -276,7 +276,7 @@
     <t>RGS</t>
   </si>
   <si>
-    <t>News Archive for RGS</t>
+    <t>(5/13/25) Regis Corporation (RGS)</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -321,7 +321,7 @@
     <t>VPG</t>
   </si>
   <si>
-    <t>(5/6/25) Vishay Precision Group, Inc. (VPG)</t>
+    <t>News Archive for VPG</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.68</v>
+        <v>4.46</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -639,16 +639,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>50.6</v>
+        <v>47.3</v>
       </c>
       <c r="G2" s="2">
-        <v>13.0</v>
+        <v>12.4</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="I2" s="4">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,25 +665,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.45</v>
+        <v>4.09</v>
       </c>
       <c r="D3" s="3">
-        <v>12.15</v>
+        <v>9.84</v>
       </c>
       <c r="E3" s="3">
         <v>3.28</v>
       </c>
       <c r="F3" s="2">
-        <v>128.1</v>
+        <v>117.7</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="I3" s="4">
-        <v>35.0</v>
+        <v>21.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -700,7 +700,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
@@ -709,13 +709,13 @@
         <v>2.27</v>
       </c>
       <c r="F4" s="2">
-        <v>116.6</v>
+        <v>117.4</v>
       </c>
       <c r="G4" s="2">
-        <v>9.3</v>
+        <v>7.4</v>
       </c>
       <c r="H4" s="3">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="I4" s="4">
         <v>8.0</v>
@@ -732,7 +732,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
@@ -741,16 +741,16 @@
         <v>1.98</v>
       </c>
       <c r="F5" s="2">
-        <v>22.1</v>
+        <v>22.8</v>
       </c>
       <c r="G5" s="2">
-        <v>1.0</v>
+        <v>6.2</v>
       </c>
       <c r="H5" s="3">
         <v>0.04</v>
       </c>
       <c r="I5" s="4">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -764,16 +764,16 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>15.59</v>
+        <v>15.6</v>
       </c>
       <c r="D6" s="3">
-        <v>21.0</v>
+        <v>20.29</v>
       </c>
       <c r="E6" s="3">
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>139.9</v>
+        <v>134.3</v>
       </c>
       <c r="G6" s="2">
         <v>11.7</v>
@@ -782,7 +782,7 @@
         <v>0.91</v>
       </c>
       <c r="I6" s="4">
-        <v>64.0</v>
+        <v>52.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -796,7 +796,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>20.98</v>
+        <v>23.23</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
@@ -805,16 +805,16 @@
         <v>17.46</v>
       </c>
       <c r="F7" s="2">
-        <v>557.1</v>
+        <v>616.9</v>
       </c>
       <c r="G7" s="2">
-        <v>15.2</v>
+        <v>16.8</v>
       </c>
       <c r="H7" s="3">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="I7" s="4">
-        <v>34.0</v>
+        <v>28.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -846,7 +846,7 @@
         <v>0.31</v>
       </c>
       <c r="I8" s="4">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -863,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>18.96</v>
+        <v>19.5</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
@@ -872,16 +872,16 @@
         <v>17.15</v>
       </c>
       <c r="F9" s="2">
-        <v>493.2</v>
+        <v>508.0</v>
       </c>
       <c r="G9" s="2">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="I9" s="4">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -895,7 +895,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>14.75</v>
+        <v>15.12</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
@@ -904,16 +904,16 @@
         <v>12.53</v>
       </c>
       <c r="F10" s="2">
-        <v>203.4</v>
+        <v>208.5</v>
       </c>
       <c r="G10" s="2">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="H10" s="3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="I10" s="4">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -927,7 +927,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>12.39</v>
+        <v>12.9</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -936,16 +936,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>78.4</v>
+        <v>81.7</v>
       </c>
       <c r="G11" s="2">
         <v>10.6</v>
       </c>
       <c r="H11" s="3">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="I11" s="4">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,25 +962,25 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>15.8</v>
+        <v>16.35</v>
       </c>
       <c r="D12" s="3">
-        <v>19.18</v>
+        <v>19.12</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>110.1</v>
+        <v>114.0</v>
       </c>
       <c r="G12" s="2">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="H12" s="3">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="I12" s="4">
-        <v>77.0</v>
+        <v>76.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>6.52</v>
+        <v>6.68</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1003,16 +1003,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>372.1</v>
+        <v>381.2</v>
       </c>
       <c r="G13" s="2">
-        <v>15.0</v>
+        <v>15.3</v>
       </c>
       <c r="H13" s="3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="I13" s="4">
-        <v>85.0</v>
+        <v>81.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1026,7 +1026,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>9.24</v>
+        <v>9.75</v>
       </c>
       <c r="D14" s="3">
         <v>19.79</v>
@@ -1035,13 +1035,13 @@
         <v>7.34</v>
       </c>
       <c r="F14" s="2">
-        <v>97.5</v>
+        <v>102.9</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="I14" s="4">
         <v>12.0</v>
@@ -1061,7 +1061,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>18.24</v>
+        <v>17.61</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
@@ -1070,16 +1070,16 @@
         <v>12.41</v>
       </c>
       <c r="F15" s="2">
-        <v>444.7</v>
+        <v>429.3</v>
       </c>
       <c r="G15" s="2">
-        <v>25.7</v>
+        <v>24.8</v>
       </c>
       <c r="H15" s="3">
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
       <c r="I15" s="4">
-        <v>51.0</v>
+        <v>43.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
@@ -1093,7 +1093,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>17.06</v>
+        <v>19.08</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
@@ -1102,16 +1102,16 @@
         <v>14.58</v>
       </c>
       <c r="F16" s="2">
-        <v>162.0</v>
+        <v>181.5</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="I16" s="4">
-        <v>37.0</v>
+        <v>51.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1128,7 +1128,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>6.55</v>
+        <v>11.24</v>
       </c>
       <c r="D17" s="3">
         <v>14.04</v>
@@ -1137,16 +1137,16 @@
         <v>5.41</v>
       </c>
       <c r="F17" s="2">
-        <v>238.0</v>
+        <v>409.2</v>
       </c>
       <c r="G17" s="2">
-        <v>13.9</v>
+        <v>42.9</v>
       </c>
       <c r="H17" s="3">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="I17" s="4">
-        <v>14.0</v>
+        <v>71.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1160,7 +1160,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>7.82</v>
+        <v>7.95</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
@@ -1169,16 +1169,16 @@
         <v>7.06</v>
       </c>
       <c r="F18" s="2">
-        <v>245.0</v>
+        <v>249.1</v>
       </c>
       <c r="G18" s="2">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="H18" s="3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="I18" s="4">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1192,7 +1192,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>33.56</v>
+        <v>36.15</v>
       </c>
       <c r="D19" s="3">
         <v>39.65</v>
@@ -1201,16 +1201,16 @@
         <v>25.19</v>
       </c>
       <c r="F19" s="2">
-        <v>249.8</v>
+        <v>269.0</v>
       </c>
       <c r="G19" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="H19" s="3">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="I19" s="4">
-        <v>71.0</v>
+        <v>79.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1227,7 +1227,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>20.46</v>
+        <v>24.87</v>
       </c>
       <c r="D20" s="3">
         <v>29.74</v>
@@ -1236,16 +1236,16 @@
         <v>16.7</v>
       </c>
       <c r="F20" s="2">
-        <v>256.0</v>
+        <v>311.6</v>
       </c>
       <c r="G20" s="2">
-        <v>14.9</v>
+        <v>18.5</v>
       </c>
       <c r="H20" s="3">
-        <v>1.0</v>
+        <v>1.22</v>
       </c>
       <c r="I20" s="4">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1259,7 +1259,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>31.56</v>
+        <v>31.99</v>
       </c>
       <c r="D21" s="3">
         <v>38.95</v>
@@ -1268,16 +1268,16 @@
         <v>15.9</v>
       </c>
       <c r="F21" s="2">
-        <v>80.2</v>
+        <v>81.3</v>
       </c>
       <c r="G21" s="2">
-        <v>9.7</v>
+        <v>9.8</v>
       </c>
       <c r="H21" s="3">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I21" s="4">
-        <v>93.0</v>
+        <v>90.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1291,25 +1291,25 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>8.65</v>
+        <v>8.76</v>
       </c>
       <c r="D22" s="3">
-        <v>17.89</v>
+        <v>15.55</v>
       </c>
       <c r="E22" s="3">
         <v>7.25</v>
       </c>
       <c r="F22" s="2">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="3">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I22" s="4">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>76</v>
@@ -1326,7 +1326,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>4.01</v>
+        <v>4.38</v>
       </c>
       <c r="D23" s="3">
         <v>8.32</v>
@@ -1335,13 +1335,13 @@
         <v>3.93</v>
       </c>
       <c r="F23" s="2">
-        <v>263.2</v>
+        <v>287.4</v>
       </c>
       <c r="G23" s="2">
-        <v>6.4</v>
+        <v>14.4</v>
       </c>
       <c r="H23" s="3">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="I23" s="4">
         <v>18.0</v>
@@ -1358,7 +1358,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>19.55</v>
+        <v>19.69</v>
       </c>
       <c r="D24" s="3">
         <v>34.5</v>
@@ -1367,7 +1367,7 @@
         <v>17.58</v>
       </c>
       <c r="F24" s="2">
-        <v>278.2</v>
+        <v>267.0</v>
       </c>
       <c r="G24" s="2">
         <v>6.6</v>
@@ -1376,7 +1376,7 @@
         <v>0.79</v>
       </c>
       <c r="I24" s="4">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1393,7 +1393,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>19.11</v>
+        <v>20.72</v>
       </c>
       <c r="D25" s="3">
         <v>35.5</v>
@@ -1402,19 +1402,16 @@
         <v>3.87</v>
       </c>
       <c r="F25" s="2">
-        <v>46.6</v>
+        <v>50.5</v>
       </c>
       <c r="G25" s="2">
         <v>0.5</v>
       </c>
       <c r="H25" s="3">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="I25" s="4">
-        <v>35.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>13</v>
+        <v>74.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1428,7 +1425,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>20.42</v>
+        <v>20.98</v>
       </c>
       <c r="D26" s="3">
         <v>40.14</v>
@@ -1437,16 +1434,16 @@
         <v>11.93</v>
       </c>
       <c r="F26" s="2">
-        <v>152.4</v>
+        <v>156.5</v>
       </c>
       <c r="G26" s="2">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="H26" s="3">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="I26" s="4">
-        <v>63.0</v>
+        <v>56.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1463,25 +1460,25 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>11.77</v>
+        <v>12.51</v>
       </c>
       <c r="D27" s="3">
-        <v>21.41</v>
+        <v>20.29</v>
       </c>
       <c r="E27" s="3">
         <v>10.75</v>
       </c>
       <c r="F27" s="2">
-        <v>75.8</v>
+        <v>80.6</v>
       </c>
       <c r="G27" s="2">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
       <c r="H27" s="3">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="I27" s="4">
-        <v>41.0</v>
+        <v>60.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>92</v>
@@ -1495,7 +1492,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>5.37</v>
+        <v>5.51</v>
       </c>
       <c r="D28" s="3">
         <v>8.84</v>
@@ -1504,16 +1501,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>198.6</v>
+        <v>203.8</v>
       </c>
       <c r="G28" s="2">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H28" s="3">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I28" s="4">
-        <v>53.0</v>
+        <v>47.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1530,25 +1527,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>19.36</v>
+        <v>21.53</v>
       </c>
       <c r="D29" s="3">
-        <v>24.28</v>
+        <v>24.17</v>
       </c>
       <c r="E29" s="3">
         <v>12.3</v>
       </c>
       <c r="F29" s="2">
-        <v>437.4</v>
+        <v>486.4</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="3">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="I29" s="4">
-        <v>91.0</v>
+        <v>94.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>76</v>
@@ -1565,7 +1562,7 @@
         <v>100</v>
       </c>
       <c r="C30" s="3">
-        <v>24.58</v>
+        <v>26.79</v>
       </c>
       <c r="D30" s="3">
         <v>35.11</v>
@@ -1574,16 +1571,16 @@
         <v>18.57</v>
       </c>
       <c r="F30" s="2">
-        <v>325.9</v>
+        <v>355.2</v>
       </c>
       <c r="G30" s="2">
-        <v>107.3</v>
+        <v>117.0</v>
       </c>
       <c r="H30" s="3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I30" s="4">
-        <v>76.0</v>
+        <v>84.0</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>101</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lumVIXqZwST8vFf0/C1MJvI1P7v198C8qWp1guo9PW0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="yM8AbNkK5KV/WgF7lJ2FkLXksAio2hyP/xS7xInPC2o="/>
     </ext>
   </extLst>
 </workbook>
@@ -84,7 +84,7 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>(5/12/25) Amplify Energy Corp. (AMPY)</t>
+    <t>News Archive for AMPY</t>
   </si>
   <si>
     <t>Castor Maritime Inc.</t>
@@ -93,7 +93,7 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>(5/14/25) Castor Maritime Inc. (CTRM)</t>
+    <t>News Archive for CTRM</t>
   </si>
   <si>
     <t>Core Molding Technologies, Inc.</t>
@@ -150,7 +150,7 @@
     <t>FONR</t>
   </si>
   <si>
-    <t>(5/15/25) FONAR Corporation (FONR)</t>
+    <t>News Archive for FONR</t>
   </si>
   <si>
     <t>Friedman Industries, Incorporated</t>
@@ -168,7 +168,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>News Archive for GILT</t>
+    <t>(5/19/25) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Hooker Furnishings Corporation</t>
@@ -204,7 +204,7 @@
     <t>LSEA</t>
   </si>
   <si>
-    <t>(5/12/25) Landsea Homes Corporation (LSEA)</t>
+    <t>News Archive for LSEA</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -222,7 +222,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>(5/15/25) NACCO Industries, Inc. (NC)</t>
+    <t>News Archive for NC</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -231,7 +231,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>(5/12/25) Natural Gas Services Group, Inc. (NGS)</t>
+    <t>News Archive for NGS</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -249,7 +249,7 @@
     <t>Earnings probation 2024Q4</t>
   </si>
   <si>
-    <t>(5/14/25) Nortech Systems Incorporated (NSYS)</t>
+    <t>News Archive for NSYS</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
@@ -258,7 +258,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>(5/12/25) Pangaea Logistics Solutions, Ltd. (PANL)</t>
+    <t>News Archive for PANL</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -276,7 +276,7 @@
     <t>RGS</t>
   </si>
   <si>
-    <t>(5/13/25) Regis Corporation (RGS)</t>
+    <t>News Archive for RGS</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -312,7 +312,7 @@
     <t>TITN</t>
   </si>
   <si>
-    <t>News Archive for TITN</t>
+    <t>(5/22/25) Titan Machinery Inc. (TITN)</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.46</v>
+        <v>4.53</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -639,13 +639,13 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>47.3</v>
+        <v>48.0</v>
       </c>
       <c r="G2" s="2">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="H2" s="3">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I2" s="4">
         <v>38.0</v>
@@ -665,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="D3" s="3">
         <v>9.84</v>
@@ -674,16 +674,16 @@
         <v>3.28</v>
       </c>
       <c r="F3" s="2">
-        <v>117.7</v>
+        <v>119.2</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I3" s="4">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -700,7 +700,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
@@ -709,16 +709,16 @@
         <v>2.27</v>
       </c>
       <c r="F4" s="2">
-        <v>117.4</v>
+        <v>108.9</v>
       </c>
       <c r="G4" s="2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H4" s="3">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="I4" s="4">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -732,7 +732,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
@@ -741,16 +741,16 @@
         <v>1.98</v>
       </c>
       <c r="F5" s="2">
-        <v>22.8</v>
+        <v>21.0</v>
       </c>
       <c r="G5" s="2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H5" s="3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I5" s="4">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -764,25 +764,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>15.6</v>
+        <v>15.67</v>
       </c>
       <c r="D6" s="3">
-        <v>20.29</v>
+        <v>20.0</v>
       </c>
       <c r="E6" s="3">
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>134.3</v>
+        <v>134.9</v>
       </c>
       <c r="G6" s="2">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="H6" s="3">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I6" s="4">
-        <v>52.0</v>
+        <v>58.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -796,7 +796,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>23.23</v>
+        <v>22.0</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
@@ -805,16 +805,16 @@
         <v>17.46</v>
       </c>
       <c r="F7" s="2">
-        <v>616.9</v>
+        <v>584.2</v>
       </c>
       <c r="G7" s="2">
-        <v>16.8</v>
+        <v>16.0</v>
       </c>
       <c r="H7" s="3">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="I7" s="4">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -828,7 +828,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>6.93</v>
+        <v>6.81</v>
       </c>
       <c r="D8" s="3">
         <v>15.14</v>
@@ -837,7 +837,7 @@
         <v>6.02</v>
       </c>
       <c r="F8" s="2">
-        <v>142.0</v>
+        <v>139.5</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -846,7 +846,7 @@
         <v>0.31</v>
       </c>
       <c r="I8" s="4">
-        <v>31.0</v>
+        <v>47.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -863,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>19.5</v>
+        <v>18.63</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
@@ -872,13 +872,13 @@
         <v>17.15</v>
       </c>
       <c r="F9" s="2">
-        <v>508.0</v>
+        <v>485.4</v>
       </c>
       <c r="G9" s="2">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="H9" s="3">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="I9" s="4">
         <v>45.0</v>
@@ -895,7 +895,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>15.12</v>
+        <v>13.61</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
@@ -904,16 +904,16 @@
         <v>12.53</v>
       </c>
       <c r="F10" s="2">
-        <v>208.5</v>
+        <v>187.6</v>
       </c>
       <c r="G10" s="2">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="H10" s="3">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="I10" s="4">
-        <v>68.0</v>
+        <v>52.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -927,7 +927,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>12.9</v>
+        <v>14.13</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -936,16 +936,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>81.7</v>
+        <v>89.5</v>
       </c>
       <c r="G11" s="2">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>36.0</v>
+        <v>55.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>16.35</v>
+        <v>16.27</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -971,16 +971,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>114.0</v>
+        <v>113.4</v>
       </c>
       <c r="G12" s="2">
-        <v>20.1</v>
+        <v>20.0</v>
       </c>
       <c r="H12" s="3">
         <v>0.89</v>
       </c>
       <c r="I12" s="4">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>6.68</v>
+        <v>5.48</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1003,16 +1003,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>381.2</v>
+        <v>312.7</v>
       </c>
       <c r="G13" s="2">
-        <v>15.3</v>
+        <v>22.8</v>
       </c>
       <c r="H13" s="3">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="I13" s="4">
-        <v>81.0</v>
+        <v>62.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1026,7 +1026,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>9.75</v>
+        <v>9.12</v>
       </c>
       <c r="D14" s="3">
         <v>19.79</v>
@@ -1035,16 +1035,16 @@
         <v>7.34</v>
       </c>
       <c r="F14" s="2">
-        <v>102.9</v>
+        <v>96.2</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="I14" s="4">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>18</v>
@@ -1061,7 +1061,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>17.61</v>
+        <v>17.5</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
@@ -1070,16 +1070,16 @@
         <v>12.41</v>
       </c>
       <c r="F15" s="2">
-        <v>429.3</v>
+        <v>426.7</v>
       </c>
       <c r="G15" s="2">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="H15" s="3">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="I15" s="4">
-        <v>43.0</v>
+        <v>49.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
@@ -1093,7 +1093,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>19.08</v>
+        <v>18.24</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
@@ -1102,16 +1102,16 @@
         <v>14.58</v>
       </c>
       <c r="F16" s="2">
-        <v>181.5</v>
+        <v>173.5</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>0.98</v>
+        <v>0.94</v>
       </c>
       <c r="I16" s="4">
-        <v>51.0</v>
+        <v>38.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1128,7 +1128,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>11.24</v>
+        <v>11.29</v>
       </c>
       <c r="D17" s="3">
         <v>14.04</v>
@@ -1137,16 +1137,16 @@
         <v>5.41</v>
       </c>
       <c r="F17" s="2">
-        <v>409.2</v>
+        <v>411.1</v>
       </c>
       <c r="G17" s="2">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="H17" s="3">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I17" s="4">
-        <v>71.0</v>
+        <v>68.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1160,7 +1160,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>7.95</v>
+        <v>7.39</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
@@ -1169,16 +1169,16 @@
         <v>7.06</v>
       </c>
       <c r="F18" s="2">
-        <v>249.1</v>
+        <v>231.5</v>
       </c>
       <c r="G18" s="2">
-        <v>16.8</v>
+        <v>15.6</v>
       </c>
       <c r="H18" s="3">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="I18" s="4">
-        <v>40.0</v>
+        <v>32.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1192,7 +1192,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>36.15</v>
+        <v>35.58</v>
       </c>
       <c r="D19" s="3">
         <v>39.65</v>
@@ -1201,16 +1201,16 @@
         <v>25.19</v>
       </c>
       <c r="F19" s="2">
-        <v>269.0</v>
+        <v>264.8</v>
       </c>
       <c r="G19" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="H19" s="3">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I19" s="4">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1227,7 +1227,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>24.87</v>
+        <v>24.17</v>
       </c>
       <c r="D20" s="3">
         <v>29.74</v>
@@ -1236,16 +1236,16 @@
         <v>16.7</v>
       </c>
       <c r="F20" s="2">
-        <v>311.6</v>
+        <v>302.8</v>
       </c>
       <c r="G20" s="2">
-        <v>18.5</v>
+        <v>18.0</v>
       </c>
       <c r="H20" s="3">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="I20" s="4">
-        <v>64.0</v>
+        <v>52.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1259,7 +1259,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>31.99</v>
+        <v>30.95</v>
       </c>
       <c r="D21" s="3">
         <v>38.95</v>
@@ -1268,16 +1268,16 @@
         <v>15.9</v>
       </c>
       <c r="F21" s="2">
-        <v>81.3</v>
+        <v>78.6</v>
       </c>
       <c r="G21" s="2">
-        <v>9.8</v>
+        <v>9.5</v>
       </c>
       <c r="H21" s="3">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="I21" s="4">
-        <v>90.0</v>
+        <v>86.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1291,7 +1291,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>8.76</v>
+        <v>9.03</v>
       </c>
       <c r="D22" s="3">
         <v>15.55</v>
@@ -1300,16 +1300,16 @@
         <v>7.25</v>
       </c>
       <c r="F22" s="2">
-        <v>24.2</v>
+        <v>24.9</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="3">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I22" s="4">
-        <v>25.0</v>
+        <v>48.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>76</v>
@@ -1326,7 +1326,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>4.38</v>
+        <v>4.6</v>
       </c>
       <c r="D23" s="3">
         <v>8.32</v>
@@ -1335,16 +1335,16 @@
         <v>3.93</v>
       </c>
       <c r="F23" s="2">
-        <v>287.4</v>
+        <v>301.9</v>
       </c>
       <c r="G23" s="2">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="H23" s="3">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="I23" s="4">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1358,7 +1358,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>19.69</v>
+        <v>18.14</v>
       </c>
       <c r="D24" s="3">
         <v>34.5</v>
@@ -1367,16 +1367,16 @@
         <v>17.58</v>
       </c>
       <c r="F24" s="2">
-        <v>267.0</v>
+        <v>246.0</v>
       </c>
       <c r="G24" s="2">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H24" s="3">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="I24" s="4">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1393,7 +1393,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>20.72</v>
+        <v>23.37</v>
       </c>
       <c r="D25" s="3">
         <v>35.5</v>
@@ -1402,16 +1402,16 @@
         <v>3.87</v>
       </c>
       <c r="F25" s="2">
-        <v>50.5</v>
+        <v>56.9</v>
       </c>
       <c r="G25" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H25" s="3">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="I25" s="4">
-        <v>74.0</v>
+        <v>85.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1425,25 +1425,25 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>20.98</v>
+        <v>20.78</v>
       </c>
       <c r="D26" s="3">
-        <v>40.14</v>
+        <v>39.7</v>
       </c>
       <c r="E26" s="3">
         <v>11.93</v>
       </c>
       <c r="F26" s="2">
-        <v>156.5</v>
+        <v>155.0</v>
       </c>
       <c r="G26" s="2">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H26" s="3">
         <v>0.67</v>
       </c>
       <c r="I26" s="4">
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1460,25 +1460,25 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>12.51</v>
+        <v>12.29</v>
       </c>
       <c r="D27" s="3">
-        <v>20.29</v>
+        <v>19.88</v>
       </c>
       <c r="E27" s="3">
         <v>10.75</v>
       </c>
       <c r="F27" s="2">
-        <v>80.6</v>
+        <v>79.2</v>
       </c>
       <c r="G27" s="2">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="H27" s="3">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I27" s="4">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>92</v>
@@ -1492,7 +1492,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>5.51</v>
+        <v>5.34</v>
       </c>
       <c r="D28" s="3">
         <v>8.84</v>
@@ -1501,16 +1501,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>203.8</v>
+        <v>197.5</v>
       </c>
       <c r="G28" s="2">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H28" s="3">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="4">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1527,25 +1527,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>21.53</v>
+        <v>19.91</v>
       </c>
       <c r="D29" s="3">
-        <v>24.17</v>
+        <v>23.41</v>
       </c>
       <c r="E29" s="3">
         <v>12.3</v>
       </c>
       <c r="F29" s="2">
-        <v>486.4</v>
+        <v>449.8</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="3">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="I29" s="4">
-        <v>94.0</v>
+        <v>91.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>76</v>
@@ -1562,7 +1562,7 @@
         <v>100</v>
       </c>
       <c r="C30" s="3">
-        <v>26.79</v>
+        <v>25.99</v>
       </c>
       <c r="D30" s="3">
         <v>35.11</v>
@@ -1571,13 +1571,13 @@
         <v>18.57</v>
       </c>
       <c r="F30" s="2">
-        <v>355.2</v>
+        <v>344.6</v>
       </c>
       <c r="G30" s="2">
-        <v>117.0</v>
+        <v>113.5</v>
       </c>
       <c r="H30" s="3">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="I30" s="4">
         <v>84.0</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="yM8AbNkK5KV/WgF7lJ2FkLXksAio2hyP/xS7xInPC2o="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="X0gV/sjEVWGPyk6BTgFT4fETtq7M7+++y6AEbnZrFu4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="102">
   <si>
     <t>Company</t>
   </si>
@@ -168,7 +168,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>(5/19/25) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>News Archive for GILT</t>
   </si>
   <si>
     <t>Hooker Furnishings Corporation</t>
@@ -303,7 +303,7 @@
     <t>GASS</t>
   </si>
   <si>
-    <t>News Archive for GASS</t>
+    <t>(5/28/25) StealthGas Inc. (GASS)</t>
   </si>
   <si>
     <t>Titan Machinery Inc.</t>
@@ -312,7 +312,7 @@
     <t>TITN</t>
   </si>
   <si>
-    <t>(5/22/25) Titan Machinery Inc. (TITN)</t>
+    <t>News Archive for TITN</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.53</v>
+        <v>4.72</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -639,16 +639,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G2" s="2">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="H2" s="3">
-        <v>0.78</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>38.0</v>
+        <v>44.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.14</v>
+        <v>4.92</v>
       </c>
       <c r="D3" s="3">
         <v>9.84</v>
@@ -674,16 +674,16 @@
         <v>3.28</v>
       </c>
       <c r="F3" s="2">
-        <v>119.2</v>
+        <v>141.9</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="I3" s="4">
-        <v>17.0</v>
+        <v>41.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -700,7 +700,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
@@ -709,16 +709,16 @@
         <v>2.27</v>
       </c>
       <c r="F4" s="2">
-        <v>108.9</v>
+        <v>115.8</v>
       </c>
       <c r="G4" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H4" s="3">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I4" s="4">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -732,7 +732,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
@@ -741,7 +741,7 @@
         <v>1.98</v>
       </c>
       <c r="F5" s="2">
-        <v>21.0</v>
+        <v>21.2</v>
       </c>
       <c r="G5" s="2">
         <v>5.8</v>
@@ -750,7 +750,7 @@
         <v>0.03</v>
       </c>
       <c r="I5" s="4">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -764,25 +764,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>15.67</v>
+        <v>16.67</v>
       </c>
       <c r="D6" s="3">
-        <v>20.0</v>
+        <v>19.39</v>
       </c>
       <c r="E6" s="3">
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>134.9</v>
+        <v>143.5</v>
       </c>
       <c r="G6" s="2">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="H6" s="3">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="I6" s="4">
-        <v>58.0</v>
+        <v>55.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -796,7 +796,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>22.0</v>
+        <v>22.7</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
@@ -805,16 +805,16 @@
         <v>17.46</v>
       </c>
       <c r="F7" s="2">
-        <v>584.2</v>
+        <v>602.8</v>
       </c>
       <c r="G7" s="2">
-        <v>16.0</v>
+        <v>16.5</v>
       </c>
       <c r="H7" s="3">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="I7" s="4">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -828,7 +828,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>6.81</v>
+        <v>6.46</v>
       </c>
       <c r="D8" s="3">
         <v>15.14</v>
@@ -837,16 +837,16 @@
         <v>6.02</v>
       </c>
       <c r="F8" s="2">
-        <v>139.5</v>
+        <v>132.4</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="I8" s="4">
-        <v>47.0</v>
+        <v>36.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -863,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>18.63</v>
+        <v>18.67</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
@@ -872,7 +872,7 @@
         <v>17.15</v>
       </c>
       <c r="F9" s="2">
-        <v>485.4</v>
+        <v>486.4</v>
       </c>
       <c r="G9" s="2">
         <v>12.1</v>
@@ -881,7 +881,7 @@
         <v>1.61</v>
       </c>
       <c r="I9" s="4">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -895,7 +895,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>13.61</v>
+        <v>14.84</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
@@ -904,16 +904,16 @@
         <v>12.53</v>
       </c>
       <c r="F10" s="2">
-        <v>187.6</v>
+        <v>204.6</v>
       </c>
       <c r="G10" s="2">
-        <v>13.8</v>
+        <v>15.0</v>
       </c>
       <c r="H10" s="3">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I10" s="4">
-        <v>52.0</v>
+        <v>57.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -927,7 +927,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>14.13</v>
+        <v>14.5</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -936,16 +936,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>89.5</v>
+        <v>91.3</v>
       </c>
       <c r="G11" s="2">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="H11" s="3">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I11" s="4">
-        <v>55.0</v>
+        <v>46.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>16.27</v>
+        <v>16.2</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -971,16 +971,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>113.4</v>
+        <v>112.9</v>
       </c>
       <c r="G12" s="2">
-        <v>20.0</v>
+        <v>19.9</v>
       </c>
       <c r="H12" s="3">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="I12" s="4">
-        <v>80.0</v>
+        <v>73.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>5.48</v>
+        <v>5.57</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1003,16 +1003,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>312.7</v>
+        <v>317.8</v>
       </c>
       <c r="G13" s="2">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="H13" s="3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I13" s="4">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1026,7 +1026,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>9.12</v>
+        <v>9.82</v>
       </c>
       <c r="D14" s="3">
         <v>19.79</v>
@@ -1035,13 +1035,13 @@
         <v>7.34</v>
       </c>
       <c r="F14" s="2">
-        <v>96.2</v>
+        <v>103.6</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="I14" s="4">
         <v>10.0</v>
@@ -1061,7 +1061,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>17.5</v>
+        <v>18.1</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
@@ -1070,16 +1070,16 @@
         <v>12.41</v>
       </c>
       <c r="F15" s="2">
-        <v>426.7</v>
+        <v>441.3</v>
       </c>
       <c r="G15" s="2">
-        <v>24.6</v>
+        <v>25.5</v>
       </c>
       <c r="H15" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="I15" s="4">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
@@ -1093,7 +1093,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>18.24</v>
+        <v>19.06</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
@@ -1102,16 +1102,16 @@
         <v>14.58</v>
       </c>
       <c r="F16" s="2">
-        <v>173.5</v>
+        <v>181.3</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
       <c r="I16" s="4">
-        <v>38.0</v>
+        <v>46.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1128,7 +1128,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>11.29</v>
+        <v>11.27</v>
       </c>
       <c r="D17" s="3">
         <v>14.04</v>
@@ -1137,16 +1137,16 @@
         <v>5.41</v>
       </c>
       <c r="F17" s="2">
-        <v>411.1</v>
+        <v>410.3</v>
       </c>
       <c r="G17" s="2">
-        <v>43.1</v>
+        <v>43.0</v>
       </c>
       <c r="H17" s="3">
         <v>0.61</v>
       </c>
       <c r="I17" s="4">
-        <v>68.0</v>
+        <v>59.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1160,7 +1160,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>7.39</v>
+        <v>7.55</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
@@ -1169,16 +1169,16 @@
         <v>7.06</v>
       </c>
       <c r="F18" s="2">
-        <v>231.5</v>
+        <v>236.5</v>
       </c>
       <c r="G18" s="2">
-        <v>15.6</v>
+        <v>16.0</v>
       </c>
       <c r="H18" s="3">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I18" s="4">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1186,408 +1186,473 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3">
-        <v>35.58</v>
+        <v>7.55</v>
       </c>
       <c r="D19" s="3">
-        <v>39.65</v>
+        <v>12.44</v>
       </c>
       <c r="E19" s="3">
-        <v>25.19</v>
+        <v>7.06</v>
       </c>
       <c r="F19" s="2">
-        <v>264.8</v>
+        <v>236.5</v>
       </c>
       <c r="G19" s="2">
-        <v>7.7</v>
+        <v>16.0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.65</v>
+        <v>1.18</v>
       </c>
       <c r="I19" s="4">
-        <v>80.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>35.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C20" s="3">
-        <v>24.17</v>
+        <v>35.86</v>
       </c>
       <c r="D20" s="3">
-        <v>29.74</v>
+        <v>39.65</v>
       </c>
       <c r="E20" s="3">
-        <v>16.7</v>
+        <v>25.19</v>
       </c>
       <c r="F20" s="2">
-        <v>302.8</v>
+        <v>266.9</v>
       </c>
       <c r="G20" s="2">
-        <v>18.0</v>
+        <v>7.8</v>
       </c>
       <c r="H20" s="3">
-        <v>1.18</v>
+        <v>0.65</v>
       </c>
       <c r="I20" s="4">
-        <v>52.0</v>
+        <v>76.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>30.95</v>
+        <v>23.97</v>
       </c>
       <c r="D21" s="3">
-        <v>38.95</v>
+        <v>29.74</v>
       </c>
       <c r="E21" s="3">
-        <v>15.9</v>
+        <v>16.7</v>
       </c>
       <c r="F21" s="2">
-        <v>78.6</v>
+        <v>300.3</v>
       </c>
       <c r="G21" s="2">
-        <v>9.5</v>
+        <v>17.9</v>
       </c>
       <c r="H21" s="3">
-        <v>0.68</v>
+        <v>1.17</v>
       </c>
       <c r="I21" s="4">
-        <v>86.0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>45.0</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22" s="3">
-        <v>9.03</v>
+        <v>29.26</v>
       </c>
       <c r="D22" s="3">
-        <v>15.55</v>
+        <v>38.95</v>
       </c>
       <c r="E22" s="3">
-        <v>7.25</v>
+        <v>15.9</v>
       </c>
       <c r="F22" s="2">
-        <v>24.9</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>17</v>
+        <v>74.3</v>
+      </c>
+      <c r="G22" s="2">
+        <v>9.0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="I22" s="4">
-        <v>48.0</v>
+        <v>87.0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>4.6</v>
+        <v>9.07</v>
       </c>
       <c r="D23" s="3">
-        <v>8.32</v>
+        <v>15.55</v>
       </c>
       <c r="E23" s="3">
-        <v>3.93</v>
+        <v>7.25</v>
       </c>
       <c r="F23" s="2">
-        <v>301.9</v>
-      </c>
-      <c r="G23" s="2">
-        <v>15.1</v>
+        <v>25.0</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H23" s="3">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="I23" s="4">
-        <v>27.0</v>
+        <v>47.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C24" s="3">
-        <v>18.14</v>
+        <v>4.5</v>
       </c>
       <c r="D24" s="3">
-        <v>34.5</v>
+        <v>8.32</v>
       </c>
       <c r="E24" s="3">
-        <v>17.58</v>
+        <v>3.93</v>
       </c>
       <c r="F24" s="2">
-        <v>246.0</v>
+        <v>295.3</v>
       </c>
       <c r="G24" s="2">
-        <v>6.1</v>
+        <v>14.8</v>
       </c>
       <c r="H24" s="3">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="I24" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>31.0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C25" s="3">
-        <v>23.37</v>
+        <v>18.3</v>
       </c>
       <c r="D25" s="3">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="E25" s="3">
-        <v>3.87</v>
+        <v>17.58</v>
       </c>
       <c r="F25" s="2">
-        <v>56.9</v>
+        <v>248.2</v>
       </c>
       <c r="G25" s="2">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="H25" s="3">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
       <c r="I25" s="4">
-        <v>85.0</v>
+        <v>12.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C26" s="3">
-        <v>20.78</v>
+        <v>21.76</v>
       </c>
       <c r="D26" s="3">
-        <v>39.7</v>
+        <v>35.5</v>
       </c>
       <c r="E26" s="3">
-        <v>11.93</v>
+        <v>3.87</v>
       </c>
       <c r="F26" s="2">
-        <v>155.0</v>
+        <v>53.0</v>
       </c>
       <c r="G26" s="2">
-        <v>11.3</v>
+        <v>0.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.67</v>
+        <v>0.96</v>
       </c>
       <c r="I26" s="4">
-        <v>61.0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>13</v>
+        <v>67.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C27" s="3">
-        <v>12.29</v>
+        <v>22.75</v>
       </c>
       <c r="D27" s="3">
-        <v>19.88</v>
+        <v>39.7</v>
       </c>
       <c r="E27" s="3">
-        <v>10.75</v>
+        <v>11.93</v>
       </c>
       <c r="F27" s="2">
-        <v>79.2</v>
+        <v>169.7</v>
       </c>
       <c r="G27" s="2">
-        <v>22.5</v>
+        <v>12.4</v>
       </c>
       <c r="H27" s="3">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="I27" s="4">
         <v>64.0</v>
       </c>
+      <c r="J27" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="K27" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C28" s="3">
-        <v>5.34</v>
+        <v>12.25</v>
       </c>
       <c r="D28" s="3">
-        <v>8.84</v>
+        <v>17.85</v>
       </c>
       <c r="E28" s="3">
-        <v>4.82</v>
+        <v>10.75</v>
       </c>
       <c r="F28" s="2">
-        <v>197.5</v>
+        <v>78.9</v>
       </c>
       <c r="G28" s="2">
-        <v>2.8</v>
+        <v>22.4</v>
       </c>
       <c r="H28" s="3">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="I28" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>55.0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C29" s="3">
-        <v>19.91</v>
+        <v>5.96</v>
       </c>
       <c r="D29" s="3">
-        <v>23.41</v>
+        <v>8.84</v>
       </c>
       <c r="E29" s="3">
-        <v>12.3</v>
+        <v>4.82</v>
       </c>
       <c r="F29" s="2">
-        <v>449.8</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>17</v>
+        <v>220.4</v>
+      </c>
+      <c r="G29" s="2">
+        <v>3.3</v>
       </c>
       <c r="H29" s="3">
-        <v>0.74</v>
+        <v>0.34</v>
       </c>
       <c r="I29" s="4">
-        <v>91.0</v>
+        <v>68.0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="3">
+        <v>5.96</v>
+      </c>
+      <c r="D30" s="3">
+        <v>8.84</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4.82</v>
+      </c>
+      <c r="F30" s="2">
+        <v>220.4</v>
+      </c>
+      <c r="G30" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="I30" s="4">
+        <v>68.0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="3">
+        <v>18.68</v>
+      </c>
+      <c r="D31" s="3">
+        <v>23.41</v>
+      </c>
+      <c r="E31" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>422.0</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="I31" s="4">
+        <v>83.0</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="3">
-        <v>25.99</v>
-      </c>
-      <c r="D30" s="3">
+      <c r="C32" s="3">
+        <v>25.72</v>
+      </c>
+      <c r="D32" s="3">
         <v>35.11</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E32" s="3">
         <v>18.57</v>
       </c>
-      <c r="F30" s="2">
-        <v>344.6</v>
-      </c>
-      <c r="G30" s="2">
-        <v>113.5</v>
-      </c>
-      <c r="H30" s="3">
-        <v>1.07</v>
-      </c>
-      <c r="I30" s="4">
-        <v>84.0</v>
-      </c>
-      <c r="K30" s="2" t="s">
+      <c r="F32" s="2">
+        <v>341.0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>112.3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="I32" s="4">
+        <v>78.0</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="X0gV/sjEVWGPyk6BTgFT4fETtq7M7+++y6AEbnZrFu4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="9/SeJwzNlpqcQh+TtJjOyGl72+oS0H4EddGzzcrBxLA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="102">
   <si>
     <t>Company</t>
   </si>
@@ -75,7 +75,7 @@
     <t>Earnings probation 2024Q3</t>
   </si>
   <si>
-    <t>News Archive for AVD</t>
+    <t>(6/6/25) American Vanguard Corporation (AVD)</t>
   </si>
   <si>
     <t>Amplify Energy Corp.</t>
@@ -303,7 +303,7 @@
     <t>GASS</t>
   </si>
   <si>
-    <t>(5/28/25) StealthGas Inc. (GASS)</t>
+    <t>News Archive for GASS</t>
   </si>
   <si>
     <t>Titan Machinery Inc.</t>
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.72</v>
+        <v>4.56</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -639,16 +639,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>50.0</v>
+        <v>48.3</v>
       </c>
       <c r="G2" s="2">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="I2" s="4">
-        <v>44.0</v>
+        <v>42.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.92</v>
+        <v>4.94</v>
       </c>
       <c r="D3" s="3">
         <v>9.84</v>
@@ -674,16 +674,16 @@
         <v>3.28</v>
       </c>
       <c r="F3" s="2">
-        <v>141.9</v>
+        <v>142.5</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="3">
-        <v>0.6</v>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="I3" s="4">
-        <v>41.0</v>
+        <v>32.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -700,7 +700,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="D4" s="3">
         <v>8.15</v>
@@ -709,16 +709,16 @@
         <v>2.27</v>
       </c>
       <c r="F4" s="2">
-        <v>115.8</v>
+        <v>131.1</v>
       </c>
       <c r="G4" s="2">
-        <v>7.3</v>
+        <v>8.2</v>
       </c>
       <c r="H4" s="3">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I4" s="4">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -732,7 +732,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="D5" s="3">
         <v>5.49</v>
@@ -741,16 +741,16 @@
         <v>1.98</v>
       </c>
       <c r="F5" s="2">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="G5" s="2">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="H5" s="3">
         <v>0.03</v>
       </c>
       <c r="I5" s="4">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -764,25 +764,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>16.67</v>
+        <v>16.05</v>
       </c>
       <c r="D6" s="3">
-        <v>19.39</v>
+        <v>19.2</v>
       </c>
       <c r="E6" s="3">
         <v>12.25</v>
       </c>
       <c r="F6" s="2">
-        <v>143.5</v>
+        <v>138.2</v>
       </c>
       <c r="G6" s="2">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="H6" s="3">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="I6" s="4">
-        <v>55.0</v>
+        <v>53.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -796,7 +796,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>22.7</v>
+        <v>22.76</v>
       </c>
       <c r="D7" s="3">
         <v>30.77</v>
@@ -805,13 +805,13 @@
         <v>17.46</v>
       </c>
       <c r="F7" s="2">
-        <v>602.8</v>
+        <v>604.4</v>
       </c>
       <c r="G7" s="2">
         <v>16.5</v>
       </c>
       <c r="H7" s="3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I7" s="4">
         <v>31.0</v>
@@ -828,7 +828,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>6.46</v>
+        <v>7.19</v>
       </c>
       <c r="D8" s="3">
         <v>15.14</v>
@@ -837,16 +837,16 @@
         <v>6.02</v>
       </c>
       <c r="F8" s="2">
-        <v>132.4</v>
+        <v>147.3</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="I8" s="4">
-        <v>36.0</v>
+        <v>47.0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -863,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>18.67</v>
+        <v>18.55</v>
       </c>
       <c r="D9" s="3">
         <v>25.75</v>
@@ -872,16 +872,16 @@
         <v>17.15</v>
       </c>
       <c r="F9" s="2">
-        <v>486.4</v>
+        <v>483.3</v>
       </c>
       <c r="G9" s="2">
-        <v>12.1</v>
+        <v>12.0</v>
       </c>
       <c r="H9" s="3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I9" s="4">
-        <v>46.0</v>
+        <v>42.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -895,7 +895,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>14.84</v>
+        <v>15.04</v>
       </c>
       <c r="D10" s="3">
         <v>16.99</v>
@@ -904,16 +904,16 @@
         <v>12.53</v>
       </c>
       <c r="F10" s="2">
-        <v>204.6</v>
+        <v>207.4</v>
       </c>
       <c r="G10" s="2">
-        <v>15.0</v>
+        <v>15.2</v>
       </c>
       <c r="H10" s="3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I10" s="4">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -927,7 +927,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>14.5</v>
+        <v>14.49</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -936,16 +936,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>91.3</v>
+        <v>91.2</v>
       </c>
       <c r="G11" s="2">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H11" s="3">
         <v>0.58</v>
       </c>
       <c r="I11" s="4">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>16.2</v>
+        <v>16.86</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -971,16 +971,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>112.9</v>
+        <v>117.5</v>
       </c>
       <c r="G12" s="2">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="H12" s="3">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="I12" s="4">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>5.57</v>
+        <v>5.98</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1003,16 +1003,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>317.8</v>
+        <v>341.2</v>
       </c>
       <c r="G13" s="2">
-        <v>23.2</v>
+        <v>24.9</v>
       </c>
       <c r="H13" s="3">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I13" s="4">
-        <v>64.0</v>
+        <v>59.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>50</v>
@@ -1026,7 +1026,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>9.82</v>
+        <v>11.0</v>
       </c>
       <c r="D14" s="3">
         <v>19.79</v>
@@ -1035,16 +1035,16 @@
         <v>7.34</v>
       </c>
       <c r="F14" s="2">
-        <v>103.6</v>
+        <v>116.1</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="I14" s="4">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>18</v>
@@ -1061,7 +1061,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>18.1</v>
+        <v>18.51</v>
       </c>
       <c r="D15" s="3">
         <v>24.45</v>
@@ -1070,16 +1070,16 @@
         <v>12.41</v>
       </c>
       <c r="F15" s="2">
-        <v>441.3</v>
+        <v>451.3</v>
       </c>
       <c r="G15" s="2">
-        <v>25.5</v>
+        <v>26.0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="I15" s="4">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
@@ -1093,7 +1093,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>19.06</v>
+        <v>18.02</v>
       </c>
       <c r="D16" s="3">
         <v>27.28</v>
@@ -1102,16 +1102,16 @@
         <v>14.58</v>
       </c>
       <c r="F16" s="2">
-        <v>181.3</v>
+        <v>171.4</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="3">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="I16" s="4">
-        <v>46.0</v>
+        <v>32.0</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -1128,7 +1128,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
       <c r="D17" s="3">
         <v>14.04</v>
@@ -1137,7 +1137,7 @@
         <v>5.41</v>
       </c>
       <c r="F17" s="2">
-        <v>410.3</v>
+        <v>410.0</v>
       </c>
       <c r="G17" s="2">
         <v>43.0</v>
@@ -1146,7 +1146,7 @@
         <v>0.61</v>
       </c>
       <c r="I17" s="4">
-        <v>59.0</v>
+        <v>57.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1160,7 +1160,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>7.55</v>
+        <v>7.67</v>
       </c>
       <c r="D18" s="3">
         <v>12.44</v>
@@ -1169,16 +1169,16 @@
         <v>7.06</v>
       </c>
       <c r="F18" s="2">
-        <v>236.5</v>
+        <v>240.3</v>
       </c>
       <c r="G18" s="2">
-        <v>16.0</v>
+        <v>16.2</v>
       </c>
       <c r="H18" s="3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I18" s="4">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1192,7 +1192,7 @@
         <v>64</v>
       </c>
       <c r="C19" s="3">
-        <v>7.55</v>
+        <v>7.67</v>
       </c>
       <c r="D19" s="3">
         <v>12.44</v>
@@ -1201,16 +1201,16 @@
         <v>7.06</v>
       </c>
       <c r="F19" s="2">
-        <v>236.5</v>
+        <v>240.3</v>
       </c>
       <c r="G19" s="2">
-        <v>16.0</v>
+        <v>16.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I19" s="4">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>65</v>
@@ -1224,7 +1224,7 @@
         <v>67</v>
       </c>
       <c r="C20" s="3">
-        <v>35.86</v>
+        <v>37.74</v>
       </c>
       <c r="D20" s="3">
         <v>39.65</v>
@@ -1233,16 +1233,16 @@
         <v>25.19</v>
       </c>
       <c r="F20" s="2">
-        <v>266.9</v>
+        <v>280.9</v>
       </c>
       <c r="G20" s="2">
-        <v>7.8</v>
+        <v>8.2</v>
       </c>
       <c r="H20" s="3">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="I20" s="4">
-        <v>76.0</v>
+        <v>81.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1259,7 +1259,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>23.97</v>
+        <v>25.19</v>
       </c>
       <c r="D21" s="3">
         <v>29.74</v>
@@ -1268,16 +1268,16 @@
         <v>16.7</v>
       </c>
       <c r="F21" s="2">
-        <v>300.3</v>
+        <v>315.6</v>
       </c>
       <c r="G21" s="2">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="H21" s="3">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="I21" s="4">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>71</v>
@@ -1291,7 +1291,7 @@
         <v>73</v>
       </c>
       <c r="C22" s="3">
-        <v>29.26</v>
+        <v>30.6</v>
       </c>
       <c r="D22" s="3">
         <v>38.95</v>
@@ -1300,16 +1300,16 @@
         <v>15.9</v>
       </c>
       <c r="F22" s="2">
-        <v>74.3</v>
+        <v>77.7</v>
       </c>
       <c r="G22" s="2">
-        <v>9.0</v>
+        <v>9.4</v>
       </c>
       <c r="H22" s="3">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="I22" s="4">
-        <v>87.0</v>
+        <v>81.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>13</v>
@@ -1323,7 +1323,7 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>9.07</v>
+        <v>8.93</v>
       </c>
       <c r="D23" s="3">
         <v>15.55</v>
@@ -1332,16 +1332,16 @@
         <v>7.25</v>
       </c>
       <c r="F23" s="2">
-        <v>25.0</v>
+        <v>24.7</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H23" s="3">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I23" s="4">
-        <v>47.0</v>
+        <v>37.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>76</v>
@@ -1358,22 +1358,22 @@
         <v>79</v>
       </c>
       <c r="C24" s="3">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="D24" s="3">
-        <v>8.32</v>
+        <v>8.0</v>
       </c>
       <c r="E24" s="3">
         <v>3.93</v>
       </c>
       <c r="F24" s="2">
-        <v>295.3</v>
+        <v>305.1</v>
       </c>
       <c r="G24" s="2">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="H24" s="3">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="I24" s="4">
         <v>31.0</v>
@@ -1390,25 +1390,25 @@
         <v>82</v>
       </c>
       <c r="C25" s="3">
-        <v>18.3</v>
+        <v>17.69</v>
       </c>
       <c r="D25" s="3">
         <v>34.5</v>
       </c>
       <c r="E25" s="3">
-        <v>17.58</v>
+        <v>17.27</v>
       </c>
       <c r="F25" s="2">
-        <v>248.2</v>
+        <v>239.8</v>
       </c>
       <c r="G25" s="2">
-        <v>6.2</v>
+        <v>6.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="I25" s="4">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1425,7 +1425,7 @@
         <v>85</v>
       </c>
       <c r="C26" s="3">
-        <v>21.76</v>
+        <v>23.09</v>
       </c>
       <c r="D26" s="3">
         <v>35.5</v>
@@ -1434,16 +1434,16 @@
         <v>3.87</v>
       </c>
       <c r="F26" s="2">
-        <v>53.0</v>
+        <v>56.2</v>
       </c>
       <c r="G26" s="2">
         <v>0.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="I26" s="4">
-        <v>67.0</v>
+        <v>53.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>86</v>
@@ -1457,25 +1457,25 @@
         <v>88</v>
       </c>
       <c r="C27" s="3">
-        <v>22.75</v>
+        <v>23.29</v>
       </c>
       <c r="D27" s="3">
-        <v>39.7</v>
+        <v>38.31</v>
       </c>
       <c r="E27" s="3">
         <v>11.93</v>
       </c>
       <c r="F27" s="2">
-        <v>169.7</v>
+        <v>173.8</v>
       </c>
       <c r="G27" s="2">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H27" s="3">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="I27" s="4">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1492,25 +1492,25 @@
         <v>91</v>
       </c>
       <c r="C28" s="3">
-        <v>12.25</v>
+        <v>12.85</v>
       </c>
       <c r="D28" s="3">
-        <v>17.85</v>
+        <v>17.35</v>
       </c>
       <c r="E28" s="3">
         <v>10.75</v>
       </c>
       <c r="F28" s="2">
-        <v>78.9</v>
+        <v>82.8</v>
       </c>
       <c r="G28" s="2">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="H28" s="3">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="I28" s="4">
-        <v>55.0</v>
+        <v>69.0</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>92</v>
@@ -1524,25 +1524,25 @@
         <v>94</v>
       </c>
       <c r="C29" s="3">
-        <v>5.96</v>
+        <v>6.28</v>
       </c>
       <c r="D29" s="3">
-        <v>8.84</v>
+        <v>8.53</v>
       </c>
       <c r="E29" s="3">
         <v>4.82</v>
       </c>
       <c r="F29" s="2">
-        <v>220.4</v>
+        <v>232.2</v>
       </c>
       <c r="G29" s="2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H29" s="3">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="I29" s="4">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>13</v>
@@ -1559,25 +1559,25 @@
         <v>94</v>
       </c>
       <c r="C30" s="3">
-        <v>5.96</v>
+        <v>6.28</v>
       </c>
       <c r="D30" s="3">
-        <v>8.84</v>
+        <v>8.53</v>
       </c>
       <c r="E30" s="3">
         <v>4.82</v>
       </c>
       <c r="F30" s="2">
-        <v>220.4</v>
+        <v>232.2</v>
       </c>
       <c r="G30" s="2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H30" s="3">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="I30" s="4">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>13</v>
@@ -1594,7 +1594,7 @@
         <v>97</v>
       </c>
       <c r="C31" s="3">
-        <v>18.68</v>
+        <v>18.78</v>
       </c>
       <c r="D31" s="3">
         <v>23.41</v>
@@ -1603,16 +1603,16 @@
         <v>12.3</v>
       </c>
       <c r="F31" s="2">
-        <v>422.0</v>
+        <v>424.3</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="3">
-        <v>0.69</v>
+      <c r="H31" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="I31" s="4">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>76</v>
@@ -1629,7 +1629,7 @@
         <v>100</v>
       </c>
       <c r="C32" s="3">
-        <v>25.72</v>
+        <v>28.02</v>
       </c>
       <c r="D32" s="3">
         <v>35.11</v>
@@ -1638,16 +1638,16 @@
         <v>18.57</v>
       </c>
       <c r="F32" s="2">
-        <v>341.0</v>
+        <v>371.5</v>
       </c>
       <c r="G32" s="2">
-        <v>112.3</v>
+        <v>122.4</v>
       </c>
       <c r="H32" s="3">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="I32" s="4">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>101</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="9/SeJwzNlpqcQh+TtJjOyGl72+oS0H4EddGzzcrBxLA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Wl9BLOzNn8YzLmP3ldlgebPevkGBvMxgqVZBpzbcumo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="93">
   <si>
     <t>Company</t>
   </si>
@@ -63,63 +63,51 @@
     <t>News Archive for APT</t>
   </si>
   <si>
-    <t>American Vanguard Corporation</t>
-  </si>
-  <si>
-    <t>AVD</t>
+    <t>Amplify Energy Corp.</t>
+  </si>
+  <si>
+    <t>AMPY</t>
+  </si>
+  <si>
+    <t>News Archive for AMPY</t>
+  </si>
+  <si>
+    <t>Castor Maritime Inc.</t>
+  </si>
+  <si>
+    <t>CTRM</t>
+  </si>
+  <si>
+    <t>News Archive for CTRM</t>
+  </si>
+  <si>
+    <t>Core Molding Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>News Archive for CMT</t>
+  </si>
+  <si>
+    <t>Covenant Logistics Group, Inc.</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>News Archive for CVLG</t>
+  </si>
+  <si>
+    <t>DMC Global Inc.</t>
+  </si>
+  <si>
+    <t>BOOM</t>
   </si>
   <si>
     <t>nmf</t>
   </si>
   <si>
-    <t>Earnings probation 2024Q3</t>
-  </si>
-  <si>
-    <t>(6/6/25) American Vanguard Corporation (AVD)</t>
-  </si>
-  <si>
-    <t>Amplify Energy Corp.</t>
-  </si>
-  <si>
-    <t>AMPY</t>
-  </si>
-  <si>
-    <t>News Archive for AMPY</t>
-  </si>
-  <si>
-    <t>Castor Maritime Inc.</t>
-  </si>
-  <si>
-    <t>CTRM</t>
-  </si>
-  <si>
-    <t>News Archive for CTRM</t>
-  </si>
-  <si>
-    <t>Core Molding Technologies, Inc.</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>News Archive for CMT</t>
-  </si>
-  <si>
-    <t>Covenant Logistics Group, Inc.</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>News Archive for CVLG</t>
-  </si>
-  <si>
-    <t>DMC Global Inc.</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
@@ -144,6 +132,12 @@
     <t>News Archive for ESCA</t>
   </si>
   <si>
+    <t>Euroseas Ltd. *</t>
+  </si>
+  <si>
+    <t>ESEA*</t>
+  </si>
+  <si>
     <t>FONAR Corporation</t>
   </si>
   <si>
@@ -171,15 +165,6 @@
     <t>News Archive for GILT</t>
   </si>
   <si>
-    <t>Hooker Furnishings Corporation</t>
-  </si>
-  <si>
-    <t>HOFT</t>
-  </si>
-  <si>
-    <t>News Archive for HOFT</t>
-  </si>
-  <si>
     <t>Kimball Electronics, Inc.</t>
   </si>
   <si>
@@ -195,16 +180,10 @@
     <t>LAKE</t>
   </si>
   <si>
-    <t>News Archive for LAKE</t>
-  </si>
-  <si>
-    <t>Landsea Homes Corporation</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>News Archive for LSEA</t>
+    <t>Earnings probation 2025Q1</t>
+  </si>
+  <si>
+    <t>(6/9/25) Lakeland Industries, Inc. (LAKE)</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -240,16 +219,16 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>Nortech Systems Incorporated</t>
-  </si>
-  <si>
-    <t>NSYS</t>
-  </si>
-  <si>
-    <t>Earnings probation 2024Q4</t>
-  </si>
-  <si>
-    <t>News Archive for NSYS</t>
+    <t>Oil States International, Inc. *</t>
+  </si>
+  <si>
+    <t>OIS*</t>
+  </si>
+  <si>
+    <t>Olympic Steel, Inc. *</t>
+  </si>
+  <si>
+    <t>ZEUS*</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
@@ -297,22 +276,16 @@
     <t>News Archive for SGA</t>
   </si>
   <si>
+    <t>Smith Douglas Homes Corp. *</t>
+  </si>
+  <si>
+    <t>SDHC*</t>
+  </si>
+  <si>
     <t>StealthGas Inc.</t>
   </si>
   <si>
     <t>GASS</t>
-  </si>
-  <si>
-    <t>News Archive for GASS</t>
-  </si>
-  <si>
-    <t>Titan Machinery Inc.</t>
-  </si>
-  <si>
-    <t>TITN</t>
-  </si>
-  <si>
-    <t>News Archive for TITN</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -630,7 +603,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -639,16 +612,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.3</v>
+        <v>50.5</v>
       </c>
       <c r="G2" s="2">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="H2" s="3">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I2" s="4">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,156 +638,156 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.94</v>
+        <v>3.56</v>
       </c>
       <c r="D3" s="3">
-        <v>9.84</v>
+        <v>8.15</v>
       </c>
       <c r="E3" s="3">
-        <v>3.28</v>
+        <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>142.5</v>
-      </c>
-      <c r="G3" s="2" t="s">
+        <v>133.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="I3" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="4">
-        <v>32.0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2.49</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.49</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="F4" s="2">
+        <v>22.3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="I4" s="4">
+        <v>18.0</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3.25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>8.15</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2.27</v>
-      </c>
-      <c r="F4" s="2">
-        <v>131.1</v>
-      </c>
-      <c r="G4" s="2">
-        <v>8.2</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.32</v>
-      </c>
-      <c r="I4" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3">
+        <v>16.47</v>
+      </c>
+      <c r="D5" s="3">
+        <v>19.2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>12.25</v>
+      </c>
+      <c r="F5" s="2">
+        <v>143.6</v>
+      </c>
+      <c r="G5" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="I5" s="4">
+        <v>64.0</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2.26</v>
-      </c>
-      <c r="D5" s="3">
-        <v>5.49</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1.98</v>
-      </c>
-      <c r="F5" s="2">
-        <v>21.8</v>
-      </c>
-      <c r="G5" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="I5" s="4">
-        <v>17.0</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3">
+        <v>22.76</v>
+      </c>
+      <c r="D6" s="3">
+        <v>30.77</v>
+      </c>
+      <c r="E6" s="3">
+        <v>17.46</v>
+      </c>
+      <c r="F6" s="2">
+        <v>616.4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="4">
+        <v>31.0</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="3">
-        <v>16.05</v>
-      </c>
-      <c r="D6" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>12.25</v>
-      </c>
-      <c r="F6" s="2">
-        <v>138.2</v>
-      </c>
-      <c r="G6" s="2">
-        <v>12.1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="I6" s="4">
-        <v>53.0</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7.87</v>
+      </c>
+      <c r="D7" s="3">
+        <v>15.14</v>
+      </c>
+      <c r="E7" s="3">
+        <v>6.02</v>
+      </c>
+      <c r="F7" s="2">
+        <v>164.7</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="H7" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="I7" s="4">
+        <v>58.0</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="3">
-        <v>22.76</v>
-      </c>
-      <c r="D7" s="3">
-        <v>30.77</v>
-      </c>
-      <c r="E7" s="3">
-        <v>17.46</v>
-      </c>
-      <c r="F7" s="2">
-        <v>604.4</v>
-      </c>
-      <c r="G7" s="2">
-        <v>16.5</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1.38</v>
-      </c>
-      <c r="I7" s="4">
-        <v>31.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -828,106 +801,103 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>7.19</v>
+        <v>18.44</v>
       </c>
       <c r="D8" s="3">
-        <v>15.14</v>
+        <v>25.75</v>
       </c>
       <c r="E8" s="3">
-        <v>6.02</v>
+        <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>147.3</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
+        <v>486.2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>12.2</v>
       </c>
       <c r="H8" s="3">
-        <v>0.33</v>
+        <v>1.62</v>
       </c>
       <c r="I8" s="4">
-        <v>47.0</v>
-      </c>
-      <c r="J8" s="2" t="s">
+        <v>43.0</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="3">
+        <v>13.83</v>
+      </c>
+      <c r="D9" s="3">
+        <v>16.99</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12.53</v>
+      </c>
+      <c r="F9" s="2">
+        <v>199.1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="I9" s="4">
+        <v>45.0</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" s="3">
-        <v>18.55</v>
-      </c>
-      <c r="D9" s="3">
-        <v>25.75</v>
-      </c>
-      <c r="E9" s="3">
-        <v>17.15</v>
-      </c>
-      <c r="F9" s="2">
-        <v>483.3</v>
-      </c>
-      <c r="G9" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1.6</v>
-      </c>
-      <c r="I9" s="4">
-        <v>42.0</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C10" s="3">
-        <v>15.04</v>
+        <v>43.61</v>
       </c>
       <c r="D10" s="3">
-        <v>16.99</v>
+        <v>50.92</v>
       </c>
       <c r="E10" s="3">
-        <v>12.53</v>
+        <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>207.4</v>
+        <v>305.5</v>
       </c>
       <c r="G10" s="2">
-        <v>15.2</v>
+        <v>2.7</v>
       </c>
       <c r="H10" s="3">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="I10" s="4">
-        <v>55.0</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>41</v>
+        <v>79.0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>14.49</v>
+        <v>14.55</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -936,33 +906,33 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="G11" s="2">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="H11" s="3">
         <v>0.58</v>
       </c>
       <c r="I11" s="4">
-        <v>47.0</v>
+        <v>51.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>16.86</v>
+        <v>16.7</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -971,30 +941,30 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="G12" s="2">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="H12" s="3">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I12" s="4">
-        <v>70.0</v>
+        <v>52.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>5.98</v>
+        <v>6.08</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -1003,252 +973,249 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>341.2</v>
+        <v>359.5</v>
       </c>
       <c r="G13" s="2">
-        <v>24.9</v>
+        <v>26.3</v>
       </c>
       <c r="H13" s="3">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="I13" s="4">
-        <v>59.0</v>
+        <v>64.0</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3">
+        <v>18.41</v>
+      </c>
+      <c r="D14" s="3">
+        <v>24.45</v>
+      </c>
+      <c r="E14" s="3">
+        <v>12.41</v>
+      </c>
+      <c r="F14" s="2">
+        <v>464.9</v>
+      </c>
+      <c r="G14" s="2">
+        <v>26.8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="I14" s="4">
+        <v>60.0</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="D14" s="3">
-        <v>19.79</v>
-      </c>
-      <c r="E14" s="3">
-        <v>7.34</v>
-      </c>
-      <c r="F14" s="2">
-        <v>116.1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.57</v>
-      </c>
-      <c r="I14" s="4">
-        <v>13.0</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="3">
+        <v>13.92</v>
+      </c>
+      <c r="D15" s="3">
+        <v>27.28</v>
+      </c>
+      <c r="E15" s="3">
+        <v>14.0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>146.0</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="I15" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C15" s="3">
-        <v>18.51</v>
-      </c>
-      <c r="D15" s="3">
-        <v>24.45</v>
-      </c>
-      <c r="E15" s="3">
-        <v>12.41</v>
-      </c>
-      <c r="F15" s="2">
-        <v>451.3</v>
-      </c>
-      <c r="G15" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="I15" s="4">
-        <v>53.0</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3">
+        <v>7.67</v>
+      </c>
+      <c r="D16" s="3">
+        <v>12.44</v>
+      </c>
+      <c r="E16" s="3">
+        <v>7.06</v>
+      </c>
+      <c r="F16" s="2">
+        <v>243.4</v>
+      </c>
+      <c r="G16" s="2">
+        <v>16.4</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="I16" s="4">
+        <v>37.0</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C16" s="3">
-        <v>18.02</v>
-      </c>
-      <c r="D16" s="3">
-        <v>27.28</v>
-      </c>
-      <c r="E16" s="3">
-        <v>14.58</v>
-      </c>
-      <c r="F16" s="2">
-        <v>171.4</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.93</v>
-      </c>
-      <c r="I16" s="4">
-        <v>32.0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="3">
+        <v>36.23</v>
+      </c>
+      <c r="D17" s="3">
+        <v>39.65</v>
+      </c>
+      <c r="E17" s="3">
+        <v>25.19</v>
+      </c>
+      <c r="F17" s="2">
+        <v>271.4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="I17" s="4">
+        <v>81.0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C17" s="3">
-        <v>11.26</v>
-      </c>
-      <c r="D17" s="3">
-        <v>14.04</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5.41</v>
-      </c>
-      <c r="F17" s="2">
-        <v>410.0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>43.0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.61</v>
-      </c>
-      <c r="I17" s="4">
-        <v>57.0</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="3">
+        <v>25.61</v>
+      </c>
+      <c r="D18" s="3">
+        <v>29.74</v>
+      </c>
+      <c r="E18" s="3">
+        <v>16.7</v>
+      </c>
+      <c r="F18" s="2">
+        <v>320.6</v>
+      </c>
+      <c r="G18" s="2">
+        <v>19.1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="I18" s="4">
+        <v>58.0</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C18" s="3">
-        <v>7.67</v>
-      </c>
-      <c r="D18" s="3">
-        <v>12.44</v>
-      </c>
-      <c r="E18" s="3">
-        <v>7.06</v>
-      </c>
-      <c r="F18" s="2">
-        <v>240.3</v>
-      </c>
-      <c r="G18" s="2">
-        <v>16.2</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="I18" s="4">
-        <v>38.0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>7.67</v>
+        <v>30.9</v>
       </c>
       <c r="D19" s="3">
-        <v>12.44</v>
+        <v>38.95</v>
       </c>
       <c r="E19" s="3">
-        <v>7.06</v>
+        <v>15.9</v>
       </c>
       <c r="F19" s="2">
-        <v>240.3</v>
+        <v>76.4</v>
       </c>
       <c r="G19" s="2">
-        <v>16.2</v>
+        <v>9.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.2</v>
+        <v>0.66</v>
       </c>
       <c r="I19" s="4">
-        <v>38.0</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>65</v>
+        <v>82.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>37.74</v>
+        <v>5.29</v>
       </c>
       <c r="D20" s="3">
-        <v>39.65</v>
+        <v>5.86</v>
       </c>
       <c r="E20" s="3">
-        <v>25.19</v>
+        <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>280.9</v>
+        <v>318.0</v>
       </c>
       <c r="G20" s="2">
-        <v>8.2</v>
+        <v>63.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.69</v>
+        <v>0.45</v>
       </c>
       <c r="I20" s="4">
-        <v>81.0</v>
+        <v>58.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1259,60 +1226,60 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>25.19</v>
+        <v>30.49</v>
       </c>
       <c r="D21" s="3">
-        <v>29.74</v>
+        <v>51.66</v>
       </c>
       <c r="E21" s="3">
-        <v>16.7</v>
+        <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>315.6</v>
+        <v>347.2</v>
       </c>
       <c r="G21" s="2">
-        <v>18.8</v>
+        <v>21.8</v>
       </c>
       <c r="H21" s="3">
-        <v>1.23</v>
+        <v>0.64</v>
       </c>
       <c r="I21" s="4">
-        <v>49.0</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>71</v>
+        <v>23.0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="3">
+        <v>4.66</v>
+      </c>
+      <c r="D22" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.93</v>
+      </c>
+      <c r="F22" s="2">
+        <v>312.4</v>
+      </c>
+      <c r="G22" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="I22" s="4">
+        <v>38.0</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C22" s="3">
-        <v>30.6</v>
-      </c>
-      <c r="D22" s="3">
-        <v>38.95</v>
-      </c>
-      <c r="E22" s="3">
-        <v>15.9</v>
-      </c>
-      <c r="F22" s="2">
-        <v>77.7</v>
-      </c>
-      <c r="G22" s="2">
-        <v>9.4</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0.68</v>
-      </c>
-      <c r="I22" s="4">
-        <v>81.0</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1323,336 +1290,231 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>8.93</v>
+        <v>17.24</v>
       </c>
       <c r="D23" s="3">
-        <v>15.55</v>
+        <v>34.5</v>
       </c>
       <c r="E23" s="3">
-        <v>7.25</v>
+        <v>17.27</v>
       </c>
       <c r="F23" s="2">
-        <v>24.7</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>17</v>
+        <v>244.1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>6.1</v>
       </c>
       <c r="H23" s="3">
         <v>0.73</v>
       </c>
       <c r="I23" s="4">
-        <v>37.0</v>
+        <v>13.0</v>
       </c>
       <c r="J23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="3">
+        <v>22.96</v>
+      </c>
+      <c r="D24" s="3">
+        <v>35.5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4.26</v>
+      </c>
+      <c r="F24" s="2">
+        <v>55.0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="I24" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C24" s="3">
-        <v>4.65</v>
-      </c>
-      <c r="D24" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>3.93</v>
-      </c>
-      <c r="F24" s="2">
-        <v>305.1</v>
-      </c>
-      <c r="G24" s="2">
-        <v>15.2</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0.63</v>
-      </c>
-      <c r="I24" s="4">
-        <v>31.0</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C25" s="3">
-        <v>17.69</v>
+        <v>21.54</v>
       </c>
       <c r="D25" s="3">
-        <v>34.5</v>
+        <v>38.31</v>
       </c>
       <c r="E25" s="3">
-        <v>17.27</v>
+        <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>239.8</v>
+        <v>162.0</v>
       </c>
       <c r="G25" s="2">
-        <v>6.0</v>
+        <v>11.8</v>
       </c>
       <c r="H25" s="3">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I25" s="4">
-        <v>10.0</v>
+        <v>55.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="3">
+        <v>12.08</v>
+      </c>
+      <c r="D26" s="3">
+        <v>16.81</v>
+      </c>
+      <c r="E26" s="3">
+        <v>10.75</v>
+      </c>
+      <c r="F26" s="2">
+        <v>81.7</v>
+      </c>
+      <c r="G26" s="2">
+        <v>23.2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="I26" s="4">
+        <v>70.0</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C26" s="3">
-        <v>23.09</v>
-      </c>
-      <c r="D26" s="3">
-        <v>35.5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>3.87</v>
-      </c>
-      <c r="F26" s="2">
-        <v>56.2</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1.02</v>
-      </c>
-      <c r="I26" s="4">
-        <v>53.0</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="C27" s="3">
-        <v>23.29</v>
+        <v>17.72</v>
       </c>
       <c r="D27" s="3">
-        <v>38.31</v>
+        <v>39.5</v>
       </c>
       <c r="E27" s="3">
-        <v>11.93</v>
+        <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>173.8</v>
+        <v>174.7</v>
       </c>
       <c r="G27" s="2">
-        <v>12.7</v>
+        <v>81.0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="I27" s="4">
-        <v>68.0</v>
+        <v>12.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" s="3">
-        <v>12.85</v>
+        <v>6.73</v>
       </c>
       <c r="D28" s="3">
-        <v>17.35</v>
+        <v>8.0</v>
       </c>
       <c r="E28" s="3">
-        <v>10.75</v>
+        <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>82.8</v>
+        <v>237.8</v>
       </c>
       <c r="G28" s="2">
-        <v>23.5</v>
+        <v>3.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="I28" s="4">
-        <v>69.0</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>92</v>
+        <v>84.0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C29" s="3">
-        <v>6.28</v>
+        <v>25.85</v>
       </c>
       <c r="D29" s="3">
-        <v>8.53</v>
+        <v>35.11</v>
       </c>
       <c r="E29" s="3">
-        <v>4.82</v>
+        <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>232.2</v>
+        <v>359.1</v>
       </c>
       <c r="G29" s="2">
-        <v>3.5</v>
+        <v>118.3</v>
       </c>
       <c r="H29" s="3">
-        <v>0.36</v>
+        <v>1.12</v>
       </c>
       <c r="I29" s="4">
-        <v>79.0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>13</v>
+        <v>76.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="3">
-        <v>6.28</v>
-      </c>
-      <c r="D30" s="3">
-        <v>8.53</v>
-      </c>
-      <c r="E30" s="3">
-        <v>4.82</v>
-      </c>
-      <c r="F30" s="2">
-        <v>232.2</v>
-      </c>
-      <c r="G30" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="H30" s="3">
-        <v>0.36</v>
-      </c>
-      <c r="I30" s="4">
-        <v>79.0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="3">
-        <v>18.78</v>
-      </c>
-      <c r="D31" s="3">
-        <v>23.41</v>
-      </c>
-      <c r="E31" s="3">
-        <v>12.3</v>
-      </c>
-      <c r="F31" s="2">
-        <v>424.3</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="4">
-        <v>84.0</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="3">
-        <v>28.02</v>
-      </c>
-      <c r="D32" s="3">
-        <v>35.11</v>
-      </c>
-      <c r="E32" s="3">
-        <v>18.57</v>
-      </c>
-      <c r="F32" s="2">
-        <v>371.5</v>
-      </c>
-      <c r="G32" s="2">
-        <v>122.4</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1.15</v>
-      </c>
-      <c r="I32" s="4">
-        <v>79.0</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Wl9BLOzNn8YzLmP3ldlgebPevkGBvMxgqVZBpzbcumo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="tnwvkDN4RzO4QoLBeGfRbAP5uLbthU4eMXrtpm9yE8c="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
   <si>
     <t>Company</t>
   </si>
@@ -183,7 +183,7 @@
     <t>Earnings probation 2025Q1</t>
   </si>
   <si>
-    <t>(6/9/25) Lakeland Industries, Inc. (LAKE)</t>
+    <t>News Archive for LAKE</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -603,7 +603,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -612,16 +612,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
       <c r="G2" s="2">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="H2" s="3">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>40.0</v>
+        <v>47.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -638,7 +638,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="D3" s="3">
         <v>8.15</v>
@@ -647,16 +647,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>133.5</v>
+        <v>147.6</v>
       </c>
       <c r="G3" s="2">
-        <v>8.4</v>
+        <v>9.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="I3" s="4">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -670,7 +670,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="D4" s="3">
         <v>5.49</v>
@@ -679,16 +679,16 @@
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="G4" s="2">
-        <v>6.1</v>
+        <v>6.0</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>18.0</v>
+        <v>28.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -702,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.47</v>
+        <v>16.44</v>
       </c>
       <c r="D5" s="3">
         <v>19.2</v>
@@ -711,13 +711,13 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>143.6</v>
+        <v>141.5</v>
       </c>
       <c r="G5" s="2">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="H5" s="3">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="I5" s="4">
         <v>64.0</v>
@@ -734,7 +734,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>22.76</v>
+        <v>22.85</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -743,16 +743,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>616.4</v>
+        <v>606.8</v>
       </c>
       <c r="G6" s="2">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="H6" s="3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="I6" s="4">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -766,7 +766,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>7.87</v>
+        <v>7.82</v>
       </c>
       <c r="D7" s="3">
         <v>15.14</v>
@@ -775,16 +775,16 @@
         <v>6.02</v>
       </c>
       <c r="F7" s="2">
-        <v>164.7</v>
+        <v>160.2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="4">
-        <v>58.0</v>
+        <v>72.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -801,7 +801,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.44</v>
+        <v>18.24</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -810,16 +810,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>486.2</v>
+        <v>470.5</v>
       </c>
       <c r="G8" s="2">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="I8" s="4">
-        <v>43.0</v>
+        <v>38.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -833,25 +833,25 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.83</v>
+        <v>13.9</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
       </c>
       <c r="E9" s="3">
-        <v>12.53</v>
+        <v>12.54</v>
       </c>
       <c r="F9" s="2">
-        <v>199.1</v>
+        <v>191.6</v>
       </c>
       <c r="G9" s="2">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="H9" s="3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="I9" s="4">
-        <v>45.0</v>
+        <v>50.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -865,7 +865,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>43.61</v>
+        <v>44.78</v>
       </c>
       <c r="D10" s="3">
         <v>50.92</v>
@@ -874,16 +874,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>305.5</v>
+        <v>313.8</v>
       </c>
       <c r="G10" s="2">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H10" s="3">
         <v>0.84</v>
       </c>
       <c r="I10" s="4">
-        <v>79.0</v>
+        <v>86.0</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>13</v>
@@ -897,7 +897,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>14.55</v>
+        <v>14.18</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -906,16 +906,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>91.3</v>
+        <v>89.3</v>
       </c>
       <c r="G11" s="2">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="I11" s="4">
-        <v>51.0</v>
+        <v>46.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -932,7 +932,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>16.7</v>
+        <v>16.71</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -941,16 +941,19 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>118.5</v>
+        <v>118.0</v>
       </c>
       <c r="G12" s="2">
-        <v>20.9</v>
+        <v>19.2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="I12" s="4">
-        <v>52.0</v>
+        <v>71.0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>45</v>
@@ -964,7 +967,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>6.08</v>
+        <v>6.49</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -973,16 +976,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>359.5</v>
+        <v>370.3</v>
       </c>
       <c r="G13" s="2">
-        <v>26.3</v>
+        <v>27.0</v>
       </c>
       <c r="H13" s="3">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="I13" s="4">
-        <v>64.0</v>
+        <v>69.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>48</v>
@@ -996,7 +999,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>18.41</v>
+        <v>18.85</v>
       </c>
       <c r="D14" s="3">
         <v>24.45</v>
@@ -1005,16 +1008,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>464.9</v>
+        <v>459.6</v>
       </c>
       <c r="G14" s="2">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="H14" s="3">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="I14" s="4">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1028,25 +1031,25 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>13.92</v>
+        <v>13.3</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
       </c>
       <c r="E15" s="3">
-        <v>14.0</v>
+        <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>146.0</v>
+        <v>126.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="I15" s="4">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1063,7 +1066,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.67</v>
+        <v>7.55</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1072,16 +1075,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>243.4</v>
+        <v>236.5</v>
       </c>
       <c r="G16" s="2">
-        <v>16.4</v>
+        <v>16.0</v>
       </c>
       <c r="H16" s="3">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="I16" s="4">
-        <v>37.0</v>
+        <v>33.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1095,7 +1098,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>36.23</v>
+        <v>38.7</v>
       </c>
       <c r="D17" s="3">
         <v>39.65</v>
@@ -1104,16 +1107,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>271.4</v>
+        <v>288.0</v>
       </c>
       <c r="G17" s="2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="I17" s="4">
-        <v>81.0</v>
+        <v>86.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1130,7 +1133,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>25.61</v>
+        <v>26.93</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1139,16 +1142,16 @@
         <v>16.7</v>
       </c>
       <c r="F18" s="2">
-        <v>320.6</v>
+        <v>337.4</v>
       </c>
       <c r="G18" s="2">
-        <v>19.1</v>
+        <v>20.1</v>
       </c>
       <c r="H18" s="3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="I18" s="4">
-        <v>58.0</v>
+        <v>68.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1162,7 +1165,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>30.9</v>
+        <v>32.32</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
@@ -1171,13 +1174,13 @@
         <v>15.9</v>
       </c>
       <c r="F19" s="2">
-        <v>76.4</v>
+        <v>82.1</v>
       </c>
       <c r="G19" s="2">
-        <v>9.2</v>
+        <v>9.9</v>
       </c>
       <c r="H19" s="3">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="I19" s="4">
         <v>82.0</v>
@@ -1194,7 +1197,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>5.29</v>
+        <v>5.55</v>
       </c>
       <c r="D20" s="3">
         <v>5.86</v>
@@ -1203,16 +1206,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>318.0</v>
+        <v>343.4</v>
       </c>
       <c r="G20" s="2">
-        <v>63.5</v>
+        <v>68.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="I20" s="4">
-        <v>58.0</v>
+        <v>73.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1226,7 +1229,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>30.49</v>
+        <v>29.78</v>
       </c>
       <c r="D21" s="3">
         <v>51.66</v>
@@ -1235,16 +1238,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>347.2</v>
+        <v>332.4</v>
       </c>
       <c r="G21" s="2">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="H21" s="3">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="I21" s="4">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1258,7 +1261,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>4.66</v>
+        <v>4.89</v>
       </c>
       <c r="D22" s="3">
         <v>8.0</v>
@@ -1267,16 +1270,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>312.4</v>
+        <v>320.9</v>
       </c>
       <c r="G22" s="2">
-        <v>15.6</v>
+        <v>16.0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="I22" s="4">
-        <v>38.0</v>
+        <v>51.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1290,25 +1293,25 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>17.24</v>
+        <v>17.12</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
       </c>
       <c r="E23" s="3">
-        <v>17.27</v>
+        <v>16.81</v>
       </c>
       <c r="F23" s="2">
-        <v>244.1</v>
+        <v>232.2</v>
       </c>
       <c r="G23" s="2">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="H23" s="3">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="I23" s="4">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1325,25 +1328,28 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>22.96</v>
+        <v>20.75</v>
       </c>
       <c r="D24" s="3">
         <v>35.5</v>
       </c>
       <c r="E24" s="3">
-        <v>4.26</v>
+        <v>4.76</v>
       </c>
       <c r="F24" s="2">
-        <v>55.0</v>
+        <v>50.5</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.99</v>
+        <v>0.74</v>
       </c>
       <c r="I24" s="4">
-        <v>51.0</v>
+        <v>40.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>79</v>
@@ -1357,25 +1363,25 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>21.54</v>
+        <v>20.91</v>
       </c>
       <c r="D25" s="3">
-        <v>38.31</v>
+        <v>37.8</v>
       </c>
       <c r="E25" s="3">
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>162.0</v>
+        <v>156.0</v>
       </c>
       <c r="G25" s="2">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H25" s="3">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="I25" s="4">
-        <v>55.0</v>
+        <v>42.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1392,25 +1398,25 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>12.08</v>
+        <v>12.13</v>
       </c>
       <c r="D26" s="3">
-        <v>16.81</v>
+        <v>16.57</v>
       </c>
       <c r="E26" s="3">
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>81.7</v>
+        <v>78.1</v>
       </c>
       <c r="G26" s="2">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="H26" s="3">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="I26" s="4">
-        <v>70.0</v>
+        <v>62.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1424,7 +1430,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>17.72</v>
+        <v>18.26</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1433,19 +1439,16 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>174.7</v>
+        <v>164.2</v>
       </c>
       <c r="G27" s="2">
-        <v>81.0</v>
+        <v>76.1</v>
       </c>
       <c r="H27" s="3">
-        <v>0.43</v>
+        <v>2.14</v>
       </c>
       <c r="I27" s="4">
         <v>12.0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -1456,25 +1459,25 @@
         <v>89</v>
       </c>
       <c r="C28" s="3">
-        <v>6.73</v>
+        <v>6.59</v>
       </c>
       <c r="D28" s="3">
-        <v>8.0</v>
+        <v>7.68</v>
       </c>
       <c r="E28" s="3">
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>237.8</v>
+        <v>243.7</v>
       </c>
       <c r="G28" s="2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H28" s="3">
         <v>0.37</v>
       </c>
       <c r="I28" s="4">
-        <v>84.0</v>
+        <v>89.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1488,7 +1491,7 @@
         <v>91</v>
       </c>
       <c r="C29" s="3">
-        <v>25.85</v>
+        <v>25.93</v>
       </c>
       <c r="D29" s="3">
         <v>35.11</v>
@@ -1497,16 +1500,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>359.1</v>
+        <v>343.8</v>
       </c>
       <c r="G29" s="2">
-        <v>118.3</v>
+        <v>113.2</v>
       </c>
       <c r="H29" s="3">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="I29" s="4">
-        <v>76.0</v>
+        <v>70.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>92</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="tnwvkDN4RzO4QoLBeGfRbAP5uLbthU4eMXrtpm9yE8c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TIMm+w8VMXR8N8gph+D/k8T7XlOP7mkVWzSwyhVlowk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t>Company</t>
   </si>
@@ -120,7 +120,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>News Archive for EBF</t>
+    <t>(6/23/25) Ennis, Inc. (EBF)</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>SDHC*</t>
+  </si>
+  <si>
+    <t>Approaching value limit</t>
   </si>
   <si>
     <t>StealthGas Inc.</t>
@@ -603,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -612,16 +615,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="G2" s="2">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="H2" s="3">
         <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>47.0</v>
+        <v>37.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -638,7 +641,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.66</v>
+        <v>3.33</v>
       </c>
       <c r="D3" s="3">
         <v>8.15</v>
@@ -647,16 +650,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>147.6</v>
+        <v>134.3</v>
       </c>
       <c r="G3" s="2">
-        <v>9.3</v>
+        <v>8.4</v>
       </c>
       <c r="H3" s="3">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="I3" s="4">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -670,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="D4" s="3">
         <v>5.49</v>
@@ -679,16 +682,16 @@
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>21.9</v>
+        <v>20.8</v>
       </c>
       <c r="G4" s="2">
-        <v>6.0</v>
+        <v>5.7</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>28.0</v>
+        <v>22.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -702,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.44</v>
+        <v>16.86</v>
       </c>
       <c r="D5" s="3">
         <v>19.2</v>
@@ -711,16 +714,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>141.5</v>
+        <v>145.1</v>
       </c>
       <c r="G5" s="2">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H5" s="3">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="I5" s="4">
-        <v>64.0</v>
+        <v>57.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -734,7 +737,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>22.85</v>
+        <v>24.29</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -743,16 +746,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>606.8</v>
+        <v>645.0</v>
       </c>
       <c r="G6" s="2">
-        <v>16.6</v>
+        <v>17.6</v>
       </c>
       <c r="H6" s="3">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="I6" s="4">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -766,7 +769,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>7.82</v>
+        <v>8.16</v>
       </c>
       <c r="D7" s="3">
         <v>15.14</v>
@@ -775,16 +778,16 @@
         <v>6.02</v>
       </c>
       <c r="F7" s="2">
-        <v>160.2</v>
+        <v>167.2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="I7" s="4">
-        <v>72.0</v>
+        <v>79.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -801,7 +804,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.24</v>
+        <v>18.32</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -810,16 +813,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>470.5</v>
+        <v>472.6</v>
       </c>
       <c r="G8" s="2">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I8" s="4">
-        <v>38.0</v>
+        <v>34.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -833,7 +836,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.9</v>
+        <v>14.21</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -842,16 +845,16 @@
         <v>12.54</v>
       </c>
       <c r="F9" s="2">
-        <v>191.6</v>
+        <v>195.9</v>
       </c>
       <c r="G9" s="2">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="H9" s="3">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I9" s="4">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -865,7 +868,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>44.78</v>
+        <v>45.53</v>
       </c>
       <c r="D10" s="3">
         <v>50.92</v>
@@ -874,16 +877,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>313.8</v>
+        <v>319.0</v>
       </c>
       <c r="G10" s="2">
         <v>2.4</v>
       </c>
       <c r="H10" s="3">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I10" s="4">
-        <v>86.0</v>
+        <v>85.0</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>13</v>
@@ -897,7 +900,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>14.18</v>
+        <v>14.88</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -906,16 +909,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>89.3</v>
+        <v>93.7</v>
       </c>
       <c r="G11" s="2">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="H11" s="3">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="I11" s="4">
-        <v>46.0</v>
+        <v>52.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -932,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>16.71</v>
+        <v>16.08</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -941,16 +944,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>118.0</v>
+        <v>113.5</v>
       </c>
       <c r="G12" s="2">
-        <v>19.2</v>
+        <v>18.5</v>
       </c>
       <c r="H12" s="3">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="I12" s="4">
-        <v>71.0</v>
+        <v>54.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -967,7 +970,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>6.49</v>
+        <v>7.02</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -976,16 +979,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>370.3</v>
+        <v>400.6</v>
       </c>
       <c r="G13" s="2">
-        <v>27.0</v>
+        <v>29.3</v>
       </c>
       <c r="H13" s="3">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="I13" s="4">
-        <v>69.0</v>
+        <v>78.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>48</v>
@@ -999,7 +1002,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>18.85</v>
+        <v>19.23</v>
       </c>
       <c r="D14" s="3">
         <v>24.45</v>
@@ -1008,16 +1011,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>459.6</v>
+        <v>468.8</v>
       </c>
       <c r="G14" s="2">
-        <v>26.5</v>
+        <v>27.0</v>
       </c>
       <c r="H14" s="3">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="I14" s="4">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1031,7 +1034,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>13.3</v>
+        <v>13.18</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1040,16 +1043,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>126.5</v>
+        <v>125.4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I15" s="4">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1066,7 +1069,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.55</v>
+        <v>7.88</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1075,16 +1078,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>236.5</v>
+        <v>246.9</v>
       </c>
       <c r="G16" s="2">
-        <v>16.0</v>
+        <v>16.7</v>
       </c>
       <c r="H16" s="3">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="I16" s="4">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1098,25 +1101,25 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>38.7</v>
+        <v>43.48</v>
       </c>
       <c r="D17" s="3">
-        <v>39.65</v>
+        <v>43.48</v>
       </c>
       <c r="E17" s="3">
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>288.0</v>
+        <v>323.6</v>
       </c>
       <c r="G17" s="2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="I17" s="4">
-        <v>86.0</v>
+        <v>92.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1133,7 +1136,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>26.93</v>
+        <v>26.9</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1142,7 +1145,7 @@
         <v>16.7</v>
       </c>
       <c r="F18" s="2">
-        <v>337.4</v>
+        <v>337.1</v>
       </c>
       <c r="G18" s="2">
         <v>20.1</v>
@@ -1151,7 +1154,7 @@
         <v>1.29</v>
       </c>
       <c r="I18" s="4">
-        <v>68.0</v>
+        <v>66.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1165,7 +1168,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>32.32</v>
+        <v>29.74</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
@@ -1174,16 +1177,16 @@
         <v>15.9</v>
       </c>
       <c r="F19" s="2">
-        <v>82.1</v>
+        <v>75.6</v>
       </c>
       <c r="G19" s="2">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="H19" s="3">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="I19" s="4">
-        <v>82.0</v>
+        <v>79.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1197,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>5.55</v>
+        <v>5.49</v>
       </c>
       <c r="D20" s="3">
         <v>5.86</v>
@@ -1206,16 +1209,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>343.4</v>
+        <v>339.7</v>
       </c>
       <c r="G20" s="2">
-        <v>68.5</v>
+        <v>67.8</v>
       </c>
       <c r="H20" s="3">
         <v>0.5</v>
       </c>
       <c r="I20" s="4">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1229,7 +1232,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>29.78</v>
+        <v>33.03</v>
       </c>
       <c r="D21" s="3">
         <v>51.66</v>
@@ -1238,16 +1241,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>332.4</v>
+        <v>368.7</v>
       </c>
       <c r="G21" s="2">
-        <v>20.8</v>
+        <v>23.1</v>
       </c>
       <c r="H21" s="3">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="I21" s="4">
-        <v>25.0</v>
+        <v>51.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1261,7 +1264,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>4.89</v>
+        <v>4.83</v>
       </c>
       <c r="D22" s="3">
         <v>8.0</v>
@@ -1270,16 +1273,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>320.9</v>
+        <v>317.0</v>
       </c>
       <c r="G22" s="2">
-        <v>16.0</v>
+        <v>15.8</v>
       </c>
       <c r="H22" s="3">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I22" s="4">
-        <v>51.0</v>
+        <v>49.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1293,7 +1296,7 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>17.12</v>
+        <v>17.91</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1302,16 +1305,16 @@
         <v>16.81</v>
       </c>
       <c r="F23" s="2">
-        <v>232.2</v>
+        <v>242.9</v>
       </c>
       <c r="G23" s="2">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="I23" s="4">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1328,25 +1331,25 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>20.75</v>
+        <v>22.65</v>
       </c>
       <c r="D24" s="3">
         <v>35.5</v>
       </c>
       <c r="E24" s="3">
-        <v>4.76</v>
+        <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>50.5</v>
+        <v>55.2</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="I24" s="4">
-        <v>40.0</v>
+        <v>33.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1363,7 +1366,7 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>20.91</v>
+        <v>22.35</v>
       </c>
       <c r="D25" s="3">
         <v>37.8</v>
@@ -1372,16 +1375,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>156.0</v>
+        <v>166.8</v>
       </c>
       <c r="G25" s="2">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="H25" s="3">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="I25" s="4">
-        <v>42.0</v>
+        <v>51.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1398,25 +1401,25 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>12.13</v>
+        <v>12.88</v>
       </c>
       <c r="D26" s="3">
-        <v>16.57</v>
+        <v>16.48</v>
       </c>
       <c r="E26" s="3">
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>78.1</v>
+        <v>83.0</v>
       </c>
       <c r="G26" s="2">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="I26" s="4">
-        <v>62.0</v>
+        <v>68.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1430,7 +1433,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>18.26</v>
+        <v>19.5</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1439,27 +1442,30 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>164.2</v>
+        <v>175.3</v>
       </c>
       <c r="G27" s="2">
-        <v>76.1</v>
+        <v>81.3</v>
       </c>
       <c r="H27" s="3">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="I27" s="4">
-        <v>12.0</v>
+        <v>19.0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>6.59</v>
+        <v>6.56</v>
       </c>
       <c r="D28" s="3">
         <v>7.68</v>
@@ -1468,7 +1474,7 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>243.7</v>
+        <v>242.6</v>
       </c>
       <c r="G28" s="2">
         <v>3.7</v>
@@ -1477,7 +1483,7 @@
         <v>0.37</v>
       </c>
       <c r="I28" s="4">
-        <v>89.0</v>
+        <v>84.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1485,13 +1491,13 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>25.93</v>
+        <v>28.31</v>
       </c>
       <c r="D29" s="3">
         <v>35.11</v>
@@ -1500,19 +1506,19 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>343.8</v>
+        <v>375.3</v>
       </c>
       <c r="G29" s="2">
-        <v>113.2</v>
+        <v>123.6</v>
       </c>
       <c r="H29" s="3">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="I29" s="4">
-        <v>70.0</v>
+        <v>81.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TIMm+w8VMXR8N8gph+D/k8T7XlOP7mkVWzSwyhVlowk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YCBQlkMt9Os54CtEvVK8AQlzLucPHxU1aL2nVv6ixzg="/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>News Archive for AMPY</t>
+    <t>(7/1/25) Amplify Energy Corp. (AMPY)</t>
   </si>
   <si>
     <t>Castor Maritime Inc.</t>
@@ -120,7 +120,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>(6/23/25) Ennis, Inc. (EBF)</t>
+    <t>News Archive for EBF</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -606,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -615,16 +615,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="G2" s="2">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="H2" s="3">
         <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>37.0</v>
+        <v>33.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -641,7 +641,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="D3" s="3">
         <v>8.15</v>
@@ -650,16 +650,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>134.3</v>
+        <v>131.1</v>
       </c>
       <c r="G3" s="2">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
       <c r="H3" s="3">
         <v>0.33</v>
       </c>
       <c r="I3" s="4">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -673,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="D4" s="3">
         <v>5.49</v>
@@ -682,16 +682,16 @@
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>20.8</v>
+        <v>21.9</v>
       </c>
       <c r="G4" s="2">
-        <v>5.7</v>
+        <v>6.0</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>22.0</v>
+        <v>27.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.86</v>
+        <v>17.3</v>
       </c>
       <c r="D5" s="3">
         <v>19.2</v>
@@ -714,16 +714,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>145.1</v>
+        <v>148.9</v>
       </c>
       <c r="G5" s="2">
-        <v>12.7</v>
+        <v>13.0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="I5" s="4">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -737,7 +737,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>24.29</v>
+        <v>25.73</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -746,16 +746,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>645.0</v>
+        <v>683.3</v>
       </c>
       <c r="G6" s="2">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
       <c r="H6" s="3">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="I6" s="4">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>8.16</v>
+        <v>8.43</v>
       </c>
       <c r="D7" s="3">
         <v>15.14</v>
@@ -778,16 +778,16 @@
         <v>6.02</v>
       </c>
       <c r="F7" s="2">
-        <v>167.2</v>
+        <v>172.7</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="I7" s="4">
-        <v>79.0</v>
+        <v>75.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -804,7 +804,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.32</v>
+        <v>18.66</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -813,16 +813,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>472.6</v>
+        <v>481.3</v>
       </c>
       <c r="G8" s="2">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="4">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -836,7 +836,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.21</v>
+        <v>14.98</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -845,16 +845,16 @@
         <v>12.54</v>
       </c>
       <c r="F9" s="2">
-        <v>195.9</v>
+        <v>206.5</v>
       </c>
       <c r="G9" s="2">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="H9" s="3">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="I9" s="4">
-        <v>51.0</v>
+        <v>58.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -868,7 +868,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>45.53</v>
+        <v>47.51</v>
       </c>
       <c r="D10" s="3">
         <v>50.92</v>
@@ -877,16 +877,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>319.0</v>
+        <v>332.8</v>
       </c>
       <c r="G10" s="2">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H10" s="3">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="I10" s="4">
-        <v>85.0</v>
+        <v>88.0</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>13</v>
@@ -900,7 +900,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>14.88</v>
+        <v>15.6</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -909,16 +909,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>93.7</v>
+        <v>98.2</v>
       </c>
       <c r="G11" s="2">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="H11" s="3">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -935,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>16.08</v>
+        <v>16.67</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -944,16 +944,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>113.5</v>
+        <v>117.7</v>
       </c>
       <c r="G12" s="2">
-        <v>18.5</v>
+        <v>19.2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="I12" s="4">
-        <v>54.0</v>
+        <v>66.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -970,7 +970,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>7.02</v>
+        <v>7.21</v>
       </c>
       <c r="D13" s="3">
         <v>8.05</v>
@@ -979,16 +979,16 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>400.6</v>
+        <v>411.4</v>
       </c>
       <c r="G13" s="2">
-        <v>29.3</v>
+        <v>30.0</v>
       </c>
       <c r="H13" s="3">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="I13" s="4">
-        <v>78.0</v>
+        <v>75.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>48</v>
@@ -1002,7 +1002,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>19.23</v>
+        <v>20.28</v>
       </c>
       <c r="D14" s="3">
         <v>24.45</v>
@@ -1011,16 +1011,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>468.8</v>
+        <v>494.4</v>
       </c>
       <c r="G14" s="2">
-        <v>27.0</v>
+        <v>28.5</v>
       </c>
       <c r="H14" s="3">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="I14" s="4">
-        <v>57.0</v>
+        <v>64.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1034,7 +1034,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>13.18</v>
+        <v>13.88</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1043,16 +1043,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>125.4</v>
+        <v>132.1</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="I15" s="4">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1069,7 +1069,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.88</v>
+        <v>8.15</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1078,16 +1078,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>246.9</v>
+        <v>255.3</v>
       </c>
       <c r="G16" s="2">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="I16" s="4">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1101,25 +1101,25 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>43.48</v>
+        <v>42.42</v>
       </c>
       <c r="D17" s="3">
-        <v>43.48</v>
+        <v>45.5</v>
       </c>
       <c r="E17" s="3">
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>323.6</v>
+        <v>315.7</v>
       </c>
       <c r="G17" s="2">
-        <v>9.4</v>
+        <v>9.2</v>
       </c>
       <c r="H17" s="3">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="I17" s="4">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1136,7 +1136,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>26.9</v>
+        <v>25.51</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1145,16 +1145,16 @@
         <v>16.7</v>
       </c>
       <c r="F18" s="2">
-        <v>337.1</v>
+        <v>319.6</v>
       </c>
       <c r="G18" s="2">
-        <v>20.1</v>
+        <v>19.0</v>
       </c>
       <c r="H18" s="3">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I18" s="4">
-        <v>66.0</v>
+        <v>39.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1168,7 +1168,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>29.74</v>
+        <v>30.03</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
@@ -1177,16 +1177,16 @@
         <v>15.9</v>
       </c>
       <c r="F19" s="2">
-        <v>75.6</v>
+        <v>76.3</v>
       </c>
       <c r="G19" s="2">
-        <v>9.1</v>
+        <v>9.2</v>
       </c>
       <c r="H19" s="3">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I19" s="4">
-        <v>79.0</v>
+        <v>74.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>5.49</v>
+        <v>5.63</v>
       </c>
       <c r="D20" s="3">
         <v>5.86</v>
@@ -1209,16 +1209,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>339.7</v>
+        <v>348.3</v>
       </c>
       <c r="G20" s="2">
-        <v>67.8</v>
+        <v>69.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I20" s="4">
-        <v>74.0</v>
+        <v>71.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1232,7 +1232,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>33.03</v>
+        <v>34.81</v>
       </c>
       <c r="D21" s="3">
         <v>51.66</v>
@@ -1241,16 +1241,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>368.7</v>
+        <v>388.6</v>
       </c>
       <c r="G21" s="2">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I21" s="4">
-        <v>51.0</v>
+        <v>61.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1264,7 +1264,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="D22" s="3">
         <v>8.0</v>
@@ -1273,16 +1273,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>317.0</v>
+        <v>337.3</v>
       </c>
       <c r="G22" s="2">
-        <v>15.8</v>
+        <v>16.9</v>
       </c>
       <c r="H22" s="3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="I22" s="4">
-        <v>49.0</v>
+        <v>44.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1296,7 +1296,7 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>17.91</v>
+        <v>19.22</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1305,16 +1305,16 @@
         <v>16.81</v>
       </c>
       <c r="F23" s="2">
-        <v>242.9</v>
+        <v>260.6</v>
       </c>
       <c r="G23" s="2">
-        <v>6.0</v>
+        <v>6.5</v>
       </c>
       <c r="H23" s="3">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="I23" s="4">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1331,7 +1331,7 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>22.65</v>
+        <v>23.18</v>
       </c>
       <c r="D24" s="3">
         <v>35.5</v>
@@ -1340,16 +1340,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>55.2</v>
+        <v>56.5</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="I24" s="4">
-        <v>33.0</v>
+        <v>38.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1366,7 +1366,7 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>22.35</v>
+        <v>23.74</v>
       </c>
       <c r="D25" s="3">
         <v>37.8</v>
@@ -1375,16 +1375,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>166.8</v>
+        <v>177.1</v>
       </c>
       <c r="G25" s="2">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="H25" s="3">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="I25" s="4">
-        <v>51.0</v>
+        <v>59.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1401,7 +1401,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>12.88</v>
+        <v>13.2</v>
       </c>
       <c r="D26" s="3">
         <v>16.48</v>
@@ -1410,16 +1410,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="G26" s="2">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="H26" s="3">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="I26" s="4">
-        <v>68.0</v>
+        <v>76.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1433,7 +1433,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>19.5</v>
+        <v>19.98</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1442,16 +1442,16 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>175.3</v>
+        <v>179.6</v>
       </c>
       <c r="G27" s="2">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="H27" s="3">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I27" s="4">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>88</v>
@@ -1465,25 +1465,25 @@
         <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>6.56</v>
+        <v>6.44</v>
       </c>
       <c r="D28" s="3">
-        <v>7.68</v>
+        <v>7.6</v>
       </c>
       <c r="E28" s="3">
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>242.6</v>
+        <v>238.1</v>
       </c>
       <c r="G28" s="2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I28" s="4">
-        <v>84.0</v>
+        <v>71.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1497,7 +1497,7 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>28.31</v>
+        <v>29.58</v>
       </c>
       <c r="D29" s="3">
         <v>35.11</v>
@@ -1506,16 +1506,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>375.3</v>
+        <v>392.2</v>
       </c>
       <c r="G29" s="2">
-        <v>123.6</v>
+        <v>129.2</v>
       </c>
       <c r="H29" s="3">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="I29" s="4">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>93</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YCBQlkMt9Os54CtEvVK8AQlzLucPHxU1aL2nVv6ixzg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="fECPHhDGT4uQmd3pztkOevZFvoA78LP6t3ak+YBIS8c="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
   <si>
     <t>Company</t>
   </si>
@@ -69,7 +69,7 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>(7/1/25) Amplify Energy Corp. (AMPY)</t>
+    <t>News Archive for AMPY</t>
   </si>
   <si>
     <t>Castor Maritime Inc.</t>
@@ -606,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -615,16 +615,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.6</v>
+        <v>52.0</v>
       </c>
       <c r="G2" s="2">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="I2" s="4">
-        <v>33.0</v>
+        <v>28.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -641,7 +641,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="D3" s="3">
         <v>8.15</v>
@@ -650,16 +650,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>131.1</v>
+        <v>136.7</v>
       </c>
       <c r="G3" s="2">
-        <v>8.2</v>
+        <v>8.6</v>
       </c>
       <c r="H3" s="3">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="I3" s="4">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -673,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="D4" s="3">
         <v>5.49</v>
@@ -682,16 +682,16 @@
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>21.9</v>
+        <v>23.1</v>
       </c>
       <c r="G4" s="2">
-        <v>6.0</v>
+        <v>6.3</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>17.3</v>
+        <v>17.02</v>
       </c>
       <c r="D5" s="3">
         <v>19.2</v>
@@ -714,16 +714,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>148.9</v>
+        <v>146.5</v>
       </c>
       <c r="G5" s="2">
-        <v>13.0</v>
+        <v>12.8</v>
       </c>
       <c r="H5" s="3">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="I5" s="4">
-        <v>58.0</v>
+        <v>67.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -737,7 +737,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>25.73</v>
+        <v>25.22</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -746,16 +746,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>683.3</v>
+        <v>669.7</v>
       </c>
       <c r="G6" s="2">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="H6" s="3">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="I6" s="4">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -769,7 +769,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>8.43</v>
+        <v>8.52</v>
       </c>
       <c r="D7" s="3">
         <v>15.14</v>
@@ -778,16 +778,16 @@
         <v>6.02</v>
       </c>
       <c r="F7" s="2">
-        <v>172.7</v>
+        <v>174.6</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="I7" s="4">
-        <v>75.0</v>
+        <v>65.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -804,7 +804,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.66</v>
+        <v>18.2</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -813,16 +813,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>481.3</v>
+        <v>469.5</v>
       </c>
       <c r="G8" s="2">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="I8" s="4">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -836,7 +836,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.98</v>
+        <v>14.16</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -845,16 +845,16 @@
         <v>12.54</v>
       </c>
       <c r="F9" s="2">
-        <v>206.5</v>
+        <v>195.2</v>
       </c>
       <c r="G9" s="2">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="I9" s="4">
-        <v>58.0</v>
+        <v>47.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -868,7 +868,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>47.51</v>
+        <v>49.11</v>
       </c>
       <c r="D10" s="3">
         <v>50.92</v>
@@ -877,19 +877,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>332.8</v>
+        <v>344.1</v>
       </c>
       <c r="G10" s="2">
         <v>2.6</v>
       </c>
       <c r="H10" s="3">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="I10" s="4">
-        <v>88.0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>13</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="11">
@@ -900,7 +897,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>15.6</v>
+        <v>15.85</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -909,16 +906,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>98.2</v>
+        <v>99.8</v>
       </c>
       <c r="G11" s="2">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="H11" s="3">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I11" s="4">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -935,7 +932,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>16.67</v>
+        <v>16.55</v>
       </c>
       <c r="D12" s="3">
         <v>19.12</v>
@@ -944,16 +941,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>117.7</v>
+        <v>116.8</v>
       </c>
       <c r="G12" s="2">
-        <v>19.2</v>
+        <v>19.0</v>
       </c>
       <c r="H12" s="3">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I12" s="4">
-        <v>66.0</v>
+        <v>64.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -970,25 +967,25 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>7.21</v>
+        <v>7.53</v>
       </c>
       <c r="D13" s="3">
-        <v>8.05</v>
+        <v>8.07</v>
       </c>
       <c r="E13" s="3">
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>411.4</v>
+        <v>429.7</v>
       </c>
       <c r="G13" s="2">
-        <v>30.0</v>
+        <v>31.4</v>
       </c>
       <c r="H13" s="3">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="I13" s="4">
-        <v>75.0</v>
+        <v>73.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>48</v>
@@ -1002,7 +999,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>20.28</v>
+        <v>19.54</v>
       </c>
       <c r="D14" s="3">
         <v>24.45</v>
@@ -1011,16 +1008,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>494.4</v>
+        <v>476.4</v>
       </c>
       <c r="G14" s="2">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="H14" s="3">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="I14" s="4">
-        <v>64.0</v>
+        <v>58.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1034,7 +1031,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>13.88</v>
+        <v>14.31</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1043,16 +1040,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>132.1</v>
+        <v>136.2</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="I15" s="4">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1069,7 +1066,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>8.15</v>
+        <v>8.14</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1078,16 +1075,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>255.3</v>
+        <v>255.0</v>
       </c>
       <c r="G16" s="2">
         <v>17.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I16" s="4">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1101,7 +1098,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>42.42</v>
+        <v>40.39</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1110,16 +1107,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>315.7</v>
+        <v>300.6</v>
       </c>
       <c r="G17" s="2">
-        <v>9.2</v>
+        <v>8.8</v>
       </c>
       <c r="H17" s="3">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="I17" s="4">
-        <v>90.0</v>
+        <v>84.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1136,7 +1133,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>25.51</v>
+        <v>24.4</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1145,13 +1142,13 @@
         <v>16.7</v>
       </c>
       <c r="F18" s="2">
-        <v>319.6</v>
+        <v>305.7</v>
       </c>
       <c r="G18" s="2">
-        <v>19.0</v>
+        <v>18.2</v>
       </c>
       <c r="H18" s="3">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="I18" s="4">
         <v>39.0</v>
@@ -1168,16 +1165,16 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
       </c>
       <c r="E19" s="3">
-        <v>15.9</v>
+        <v>16.2</v>
       </c>
       <c r="F19" s="2">
-        <v>76.3</v>
+        <v>76.1</v>
       </c>
       <c r="G19" s="2">
         <v>9.2</v>
@@ -1186,7 +1183,7 @@
         <v>0.74</v>
       </c>
       <c r="I19" s="4">
-        <v>74.0</v>
+        <v>58.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1200,7 +1197,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="D20" s="3">
         <v>5.86</v>
@@ -1209,16 +1206,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>348.3</v>
+        <v>348.9</v>
       </c>
       <c r="G20" s="2">
-        <v>69.5</v>
+        <v>69.6</v>
       </c>
       <c r="H20" s="3">
         <v>0.51</v>
       </c>
       <c r="I20" s="4">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1232,7 +1229,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>34.81</v>
+        <v>34.66</v>
       </c>
       <c r="D21" s="3">
         <v>51.66</v>
@@ -1241,16 +1238,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>388.6</v>
+        <v>386.9</v>
       </c>
       <c r="G21" s="2">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="H21" s="3">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I21" s="4">
-        <v>61.0</v>
+        <v>64.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1264,22 +1261,22 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="D22" s="3">
-        <v>8.0</v>
+        <v>7.75</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>337.3</v>
+        <v>342.5</v>
       </c>
       <c r="G22" s="2">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="H22" s="3">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="I22" s="4">
         <v>44.0</v>
@@ -1296,7 +1293,7 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>19.22</v>
+        <v>18.33</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1305,16 +1302,16 @@
         <v>16.81</v>
       </c>
       <c r="F23" s="2">
-        <v>260.6</v>
+        <v>248.6</v>
       </c>
       <c r="G23" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H23" s="3">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="I23" s="4">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1331,7 +1328,7 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>23.18</v>
+        <v>23.09</v>
       </c>
       <c r="D24" s="3">
         <v>35.5</v>
@@ -1340,7 +1337,7 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>56.5</v>
+        <v>56.2</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
@@ -1349,7 +1346,7 @@
         <v>0.82</v>
       </c>
       <c r="I24" s="4">
-        <v>38.0</v>
+        <v>46.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1366,7 +1363,7 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>23.74</v>
+        <v>24.09</v>
       </c>
       <c r="D25" s="3">
         <v>37.8</v>
@@ -1375,16 +1372,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>177.1</v>
+        <v>179.7</v>
       </c>
       <c r="G25" s="2">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="H25" s="3">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I25" s="4">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1401,7 +1398,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>13.2</v>
+        <v>13.42</v>
       </c>
       <c r="D26" s="3">
         <v>16.48</v>
@@ -1410,16 +1407,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>85.0</v>
+        <v>86.5</v>
       </c>
       <c r="G26" s="2">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="I26" s="4">
-        <v>76.0</v>
+        <v>72.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1433,7 +1430,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>19.98</v>
+        <v>20.84</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1442,16 +1439,16 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>179.6</v>
+        <v>187.4</v>
       </c>
       <c r="G27" s="2">
-        <v>83.3</v>
+        <v>86.8</v>
       </c>
       <c r="H27" s="3">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="I27" s="4">
-        <v>21.0</v>
+        <v>35.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>88</v>
@@ -1465,25 +1462,25 @@
         <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>6.44</v>
+        <v>6.76</v>
       </c>
       <c r="D28" s="3">
-        <v>7.6</v>
+        <v>7.26</v>
       </c>
       <c r="E28" s="3">
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>238.1</v>
+        <v>250.0</v>
       </c>
       <c r="G28" s="2">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H28" s="3">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="I28" s="4">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1497,7 +1494,7 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>29.58</v>
+        <v>28.51</v>
       </c>
       <c r="D29" s="3">
         <v>35.11</v>
@@ -1506,16 +1503,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>392.2</v>
+        <v>378.0</v>
       </c>
       <c r="G29" s="2">
-        <v>129.2</v>
+        <v>124.5</v>
       </c>
       <c r="H29" s="3">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="I29" s="4">
-        <v>82.0</v>
+        <v>81.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>93</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="fECPHhDGT4uQmd3pztkOevZFvoA78LP6t3ak+YBIS8c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Pn1oJGI5j/S8jfDpOavehSDUBuN563mCddSSj29Gs6U="/>
     </ext>
   </extLst>
 </workbook>
@@ -132,10 +132,10 @@
     <t>News Archive for ESCA</t>
   </si>
   <si>
-    <t>Euroseas Ltd. *</t>
-  </si>
-  <si>
-    <t>ESEA*</t>
+    <t>Euroseas Ltd.</t>
+  </si>
+  <si>
+    <t>ESEA</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -219,16 +219,16 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>Oil States International, Inc. *</t>
-  </si>
-  <si>
-    <t>OIS*</t>
-  </si>
-  <si>
-    <t>Olympic Steel, Inc. *</t>
-  </si>
-  <si>
-    <t>ZEUS*</t>
+    <t>Oil States International, Inc.</t>
+  </si>
+  <si>
+    <t>OIS</t>
+  </si>
+  <si>
+    <t>Olympic Steel, Inc.</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
@@ -276,10 +276,10 @@
     <t>News Archive for SGA</t>
   </si>
   <si>
-    <t>Smith Douglas Homes Corp. *</t>
-  </si>
-  <si>
-    <t>SDHC*</t>
+    <t>Smith Douglas Homes Corp.</t>
+  </si>
+  <si>
+    <t>SDHC</t>
   </si>
   <si>
     <t>Approaching value limit</t>
@@ -606,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -615,16 +615,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>52.0</v>
+        <v>51.6</v>
       </c>
       <c r="G2" s="2">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="H2" s="3">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -641,7 +641,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="D3" s="3">
         <v>8.15</v>
@@ -650,16 +650,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>136.7</v>
+        <v>131.5</v>
       </c>
       <c r="G3" s="2">
-        <v>8.6</v>
+        <v>8.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="I3" s="4">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -673,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="D4" s="3">
         <v>5.49</v>
@@ -682,16 +682,16 @@
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="G4" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H4" s="3">
         <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>17.02</v>
+        <v>16.85</v>
       </c>
       <c r="D5" s="3">
         <v>19.2</v>
@@ -714,16 +714,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>146.5</v>
+        <v>145.0</v>
       </c>
       <c r="G5" s="2">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H5" s="3">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="I5" s="4">
-        <v>67.0</v>
+        <v>64.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -737,7 +737,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>25.22</v>
+        <v>23.55</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -746,16 +746,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>669.7</v>
+        <v>625.4</v>
       </c>
       <c r="G6" s="2">
-        <v>18.3</v>
+        <v>17.1</v>
       </c>
       <c r="H6" s="3">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="I6" s="4">
-        <v>41.0</v>
+        <v>30.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -769,25 +769,25 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>8.52</v>
+        <v>7.76</v>
       </c>
       <c r="D7" s="3">
-        <v>15.14</v>
+        <v>14.43</v>
       </c>
       <c r="E7" s="3">
         <v>6.02</v>
       </c>
       <c r="F7" s="2">
-        <v>174.6</v>
+        <v>159.0</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.69</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="4">
-        <v>65.0</v>
+        <v>55.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -804,7 +804,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.2</v>
+        <v>17.75</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -813,16 +813,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>469.5</v>
+        <v>457.9</v>
       </c>
       <c r="G8" s="2">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="I8" s="4">
-        <v>34.0</v>
+        <v>30.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -836,25 +836,25 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.16</v>
+        <v>12.22</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
       </c>
       <c r="E9" s="3">
-        <v>12.54</v>
+        <v>12.04</v>
       </c>
       <c r="F9" s="2">
-        <v>195.2</v>
+        <v>168.5</v>
       </c>
       <c r="G9" s="2">
-        <v>14.3</v>
+        <v>12.4</v>
       </c>
       <c r="H9" s="3">
-        <v>1.15</v>
+        <v>1.0</v>
       </c>
       <c r="I9" s="4">
-        <v>47.0</v>
+        <v>26.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -868,7 +868,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>49.11</v>
+        <v>49.42</v>
       </c>
       <c r="D10" s="3">
         <v>50.92</v>
@@ -877,16 +877,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>344.1</v>
+        <v>346.3</v>
       </c>
       <c r="G10" s="2">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="H10" s="3">
         <v>0.92</v>
       </c>
       <c r="I10" s="4">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="11">
@@ -897,7 +897,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>15.85</v>
+        <v>16.01</v>
       </c>
       <c r="D11" s="3">
         <v>18.68</v>
@@ -906,16 +906,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>99.8</v>
+        <v>100.8</v>
       </c>
       <c r="G11" s="2">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="H11" s="3">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I11" s="4">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -932,25 +932,25 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>16.55</v>
+        <v>15.33</v>
       </c>
       <c r="D12" s="3">
-        <v>19.12</v>
+        <v>18.48</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>116.8</v>
+        <v>108.2</v>
       </c>
       <c r="G12" s="2">
-        <v>19.0</v>
+        <v>17.6</v>
       </c>
       <c r="H12" s="3">
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
       <c r="I12" s="4">
-        <v>64.0</v>
+        <v>63.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -967,25 +967,25 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>7.53</v>
+        <v>7.89</v>
       </c>
       <c r="D13" s="3">
-        <v>8.07</v>
+        <v>8.17</v>
       </c>
       <c r="E13" s="3">
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>429.7</v>
+        <v>450.2</v>
       </c>
       <c r="G13" s="2">
-        <v>31.4</v>
+        <v>32.9</v>
       </c>
       <c r="H13" s="3">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="4">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>48</v>
@@ -999,7 +999,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>19.54</v>
+        <v>19.38</v>
       </c>
       <c r="D14" s="3">
         <v>24.45</v>
@@ -1008,16 +1008,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>476.4</v>
+        <v>472.5</v>
       </c>
       <c r="G14" s="2">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="H14" s="3">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I14" s="4">
-        <v>58.0</v>
+        <v>54.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1031,7 +1031,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>14.31</v>
+        <v>14.04</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1040,16 +1040,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>136.2</v>
+        <v>133.6</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="I15" s="4">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1066,7 +1066,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>8.14</v>
+        <v>7.94</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1075,16 +1075,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>255.0</v>
+        <v>248.8</v>
       </c>
       <c r="G16" s="2">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="H16" s="3">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="I16" s="4">
-        <v>38.0</v>
+        <v>28.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1098,7 +1098,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>40.39</v>
+        <v>39.77</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1107,16 +1107,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>300.6</v>
+        <v>296.0</v>
       </c>
       <c r="G17" s="2">
-        <v>8.8</v>
+        <v>8.6</v>
       </c>
       <c r="H17" s="3">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I17" s="4">
-        <v>84.0</v>
+        <v>80.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1133,7 +1133,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>24.4</v>
+        <v>24.39</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1142,7 +1142,7 @@
         <v>16.7</v>
       </c>
       <c r="F18" s="2">
-        <v>305.7</v>
+        <v>305.6</v>
       </c>
       <c r="G18" s="2">
         <v>18.2</v>
@@ -1151,7 +1151,7 @@
         <v>1.17</v>
       </c>
       <c r="I18" s="4">
-        <v>39.0</v>
+        <v>33.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1165,25 +1165,25 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>29.94</v>
+        <v>31.5</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
       </c>
       <c r="E19" s="3">
-        <v>16.2</v>
+        <v>16.66</v>
       </c>
       <c r="F19" s="2">
-        <v>76.1</v>
+        <v>80.0</v>
       </c>
       <c r="G19" s="2">
-        <v>9.2</v>
+        <v>9.6</v>
       </c>
       <c r="H19" s="3">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="I19" s="4">
-        <v>58.0</v>
+        <v>72.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1197,7 +1197,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>5.64</v>
+        <v>5.43</v>
       </c>
       <c r="D20" s="3">
         <v>5.86</v>
@@ -1206,16 +1206,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>348.9</v>
+        <v>335.9</v>
       </c>
       <c r="G20" s="2">
-        <v>69.6</v>
+        <v>67.0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="I20" s="4">
-        <v>63.0</v>
+        <v>43.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1229,7 +1229,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>34.66</v>
+        <v>33.13</v>
       </c>
       <c r="D21" s="3">
         <v>51.66</v>
@@ -1238,16 +1238,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>386.9</v>
+        <v>369.8</v>
       </c>
       <c r="G21" s="2">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="H21" s="3">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="I21" s="4">
-        <v>64.0</v>
+        <v>48.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1261,25 +1261,25 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>5.22</v>
+        <v>5.02</v>
       </c>
       <c r="D22" s="3">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>342.5</v>
+        <v>329.4</v>
       </c>
       <c r="G22" s="2">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="H22" s="3">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="I22" s="4">
-        <v>44.0</v>
+        <v>33.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1293,25 +1293,25 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>18.33</v>
+        <v>16.49</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
       </c>
       <c r="E23" s="3">
-        <v>16.81</v>
+        <v>16.46</v>
       </c>
       <c r="F23" s="2">
-        <v>248.6</v>
+        <v>223.6</v>
       </c>
       <c r="G23" s="2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H23" s="3">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="I23" s="4">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1328,7 +1328,7 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>23.09</v>
+        <v>22.44</v>
       </c>
       <c r="D24" s="3">
         <v>35.5</v>
@@ -1337,16 +1337,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>56.2</v>
+        <v>54.7</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="I24" s="4">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1363,7 +1363,7 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>24.09</v>
+        <v>22.96</v>
       </c>
       <c r="D25" s="3">
         <v>37.8</v>
@@ -1372,16 +1372,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>179.7</v>
+        <v>171.3</v>
       </c>
       <c r="G25" s="2">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="H25" s="3">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="I25" s="4">
-        <v>61.0</v>
+        <v>47.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1398,7 +1398,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>13.42</v>
+        <v>13.26</v>
       </c>
       <c r="D26" s="3">
         <v>16.48</v>
@@ -1407,16 +1407,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>86.5</v>
+        <v>85.4</v>
       </c>
       <c r="G26" s="2">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="I26" s="4">
-        <v>72.0</v>
+        <v>68.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1430,7 +1430,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>20.84</v>
+        <v>19.35</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1439,16 +1439,16 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>187.4</v>
+        <v>174.0</v>
       </c>
       <c r="G27" s="2">
-        <v>86.8</v>
+        <v>80.6</v>
       </c>
       <c r="H27" s="3">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="I27" s="4">
-        <v>35.0</v>
+        <v>22.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>88</v>
@@ -1462,7 +1462,7 @@
         <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>6.76</v>
+        <v>6.52</v>
       </c>
       <c r="D28" s="3">
         <v>7.26</v>
@@ -1471,16 +1471,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>250.0</v>
+        <v>241.1</v>
       </c>
       <c r="G28" s="2">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="I28" s="4">
-        <v>72.0</v>
+        <v>64.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1494,7 +1494,7 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>28.51</v>
+        <v>28.02</v>
       </c>
       <c r="D29" s="3">
         <v>35.11</v>
@@ -1503,16 +1503,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>378.0</v>
+        <v>371.5</v>
       </c>
       <c r="G29" s="2">
-        <v>124.5</v>
+        <v>122.4</v>
       </c>
       <c r="H29" s="3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="I29" s="4">
-        <v>81.0</v>
+        <v>76.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>93</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Pn1oJGI5j/S8jfDpOavehSDUBuN563mCddSSj29Gs6U="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Qsu867S/zDWeC9f9DB0pnClaxQZw1/8MELZJZZXiE/0="/>
     </ext>
   </extLst>
 </workbook>
@@ -606,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.75</v>
+        <v>4.84</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -615,16 +615,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="G2" s="2">
         <v>13.2</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="I2" s="4">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -641,25 +641,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.26</v>
+        <v>3.86</v>
       </c>
       <c r="D3" s="3">
-        <v>8.15</v>
+        <v>8.0</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>131.5</v>
+        <v>155.7</v>
       </c>
       <c r="G3" s="2">
-        <v>8.3</v>
+        <v>9.8</v>
       </c>
       <c r="H3" s="3">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="I3" s="4">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -682,16 +682,16 @@
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>22.5</v>
+        <v>23.1</v>
       </c>
       <c r="G4" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H4" s="3">
         <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.85</v>
+        <v>17.3</v>
       </c>
       <c r="D5" s="3">
         <v>19.2</v>
@@ -714,16 +714,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>145.0</v>
+        <v>147.9</v>
       </c>
       <c r="G5" s="2">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="H5" s="3">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="I5" s="4">
-        <v>64.0</v>
+        <v>72.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -737,7 +737,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>23.55</v>
+        <v>25.36</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -746,16 +746,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>625.4</v>
+        <v>668.9</v>
       </c>
       <c r="G6" s="2">
-        <v>17.1</v>
+        <v>19.2</v>
       </c>
       <c r="H6" s="3">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="I6" s="4">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -769,25 +769,25 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>7.76</v>
+        <v>8.46</v>
       </c>
       <c r="D7" s="3">
-        <v>14.43</v>
+        <v>14.36</v>
       </c>
       <c r="E7" s="3">
         <v>6.02</v>
       </c>
       <c r="F7" s="2">
-        <v>159.0</v>
+        <v>171.9</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="I7" s="4">
-        <v>55.0</v>
+        <v>73.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -804,7 +804,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>17.75</v>
+        <v>18.1</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -813,16 +813,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>457.9</v>
+        <v>465.3</v>
       </c>
       <c r="G8" s="2">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H8" s="3">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="I8" s="4">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -836,7 +836,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>12.22</v>
+        <v>12.61</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -845,13 +845,13 @@
         <v>12.04</v>
       </c>
       <c r="F9" s="2">
-        <v>168.5</v>
+        <v>173.9</v>
       </c>
       <c r="G9" s="2">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="H9" s="3">
-        <v>1.0</v>
+        <v>1.03</v>
       </c>
       <c r="I9" s="4">
         <v>26.0</v>
@@ -868,25 +868,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>49.42</v>
+        <v>51.67</v>
       </c>
       <c r="D10" s="3">
-        <v>50.92</v>
+        <v>51.89</v>
       </c>
       <c r="E10" s="3">
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>346.3</v>
+        <v>363.6</v>
       </c>
       <c r="G10" s="2">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H10" s="3">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="I10" s="4">
-        <v>88.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="11">
@@ -897,25 +897,25 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>16.01</v>
+        <v>16.0</v>
       </c>
       <c r="D11" s="3">
-        <v>18.68</v>
+        <v>18.64</v>
       </c>
       <c r="E11" s="3">
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>100.8</v>
+        <v>99.9</v>
       </c>
       <c r="G11" s="2">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="H11" s="3">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I11" s="4">
-        <v>59.0</v>
+        <v>55.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -932,7 +932,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>15.33</v>
+        <v>15.9</v>
       </c>
       <c r="D12" s="3">
         <v>18.48</v>
@@ -941,16 +941,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>108.2</v>
+        <v>111.1</v>
       </c>
       <c r="G12" s="2">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="H12" s="3">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="I12" s="4">
-        <v>63.0</v>
+        <v>68.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -967,25 +967,25 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>7.89</v>
+        <v>7.74</v>
       </c>
       <c r="D13" s="3">
-        <v>8.17</v>
+        <v>8.55</v>
       </c>
       <c r="E13" s="3">
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>450.2</v>
+        <v>445.1</v>
       </c>
       <c r="G13" s="2">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="H13" s="3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="I13" s="4">
-        <v>75.0</v>
+        <v>65.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>48</v>
@@ -999,7 +999,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>19.38</v>
+        <v>18.93</v>
       </c>
       <c r="D14" s="3">
         <v>24.45</v>
@@ -1008,16 +1008,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>472.5</v>
+        <v>457.9</v>
       </c>
       <c r="G14" s="2">
-        <v>27.3</v>
+        <v>26.4</v>
       </c>
       <c r="H14" s="3">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="I14" s="4">
-        <v>54.0</v>
+        <v>48.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1031,7 +1031,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>14.04</v>
+        <v>14.94</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1040,16 +1040,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>133.6</v>
+        <v>141.2</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="I15" s="4">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1066,7 +1066,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.94</v>
+        <v>8.33</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1075,16 +1075,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>248.8</v>
+        <v>258.8</v>
       </c>
       <c r="G16" s="2">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="H16" s="3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="I16" s="4">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1098,7 +1098,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>39.77</v>
+        <v>40.49</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1107,16 +1107,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>296.0</v>
+        <v>303.3</v>
       </c>
       <c r="G17" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="H17" s="3">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="I17" s="4">
-        <v>80.0</v>
+        <v>83.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1133,7 +1133,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>24.39</v>
+        <v>24.44</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1142,16 +1142,16 @@
         <v>16.7</v>
       </c>
       <c r="F18" s="2">
-        <v>305.6</v>
+        <v>304.2</v>
       </c>
       <c r="G18" s="2">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="H18" s="3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="I18" s="4">
-        <v>33.0</v>
+        <v>27.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1165,7 +1165,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>31.5</v>
+        <v>30.69</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
@@ -1174,16 +1174,16 @@
         <v>16.66</v>
       </c>
       <c r="F19" s="2">
-        <v>80.0</v>
+        <v>78.1</v>
       </c>
       <c r="G19" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H19" s="3">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="I19" s="4">
-        <v>72.0</v>
+        <v>55.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1197,7 +1197,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>5.43</v>
+        <v>5.77</v>
       </c>
       <c r="D20" s="3">
         <v>5.86</v>
@@ -1206,16 +1206,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="G20" s="2">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="I20" s="4">
-        <v>43.0</v>
+        <v>54.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1229,7 +1229,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>33.13</v>
+        <v>32.8</v>
       </c>
       <c r="D21" s="3">
         <v>51.66</v>
@@ -1238,16 +1238,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>369.8</v>
+        <v>365.9</v>
       </c>
       <c r="G21" s="2">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="H21" s="3">
         <v>0.64</v>
       </c>
       <c r="I21" s="4">
-        <v>48.0</v>
+        <v>44.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1261,7 +1261,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="D22" s="3">
         <v>7.5</v>
@@ -1270,16 +1270,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>329.4</v>
+        <v>333.4</v>
       </c>
       <c r="G22" s="2">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="H22" s="3">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I22" s="4">
-        <v>33.0</v>
+        <v>41.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1293,25 +1293,25 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>16.49</v>
+        <v>17.68</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
       </c>
       <c r="E23" s="3">
-        <v>16.46</v>
+        <v>16.26</v>
       </c>
       <c r="F23" s="2">
-        <v>223.6</v>
+        <v>235.3</v>
       </c>
       <c r="G23" s="2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H23" s="3">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="I23" s="4">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1328,7 +1328,7 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>22.44</v>
+        <v>21.1</v>
       </c>
       <c r="D24" s="3">
         <v>35.5</v>
@@ -1337,16 +1337,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>54.7</v>
+        <v>51.6</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I24" s="4">
-        <v>47.0</v>
+        <v>30.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1363,7 +1363,7 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>22.96</v>
+        <v>23.34</v>
       </c>
       <c r="D25" s="3">
         <v>37.8</v>
@@ -1372,16 +1372,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>171.3</v>
+        <v>174.1</v>
       </c>
       <c r="G25" s="2">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="H25" s="3">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="I25" s="4">
-        <v>47.0</v>
+        <v>40.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1398,7 +1398,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>13.26</v>
+        <v>13.55</v>
       </c>
       <c r="D26" s="3">
         <v>16.48</v>
@@ -1407,16 +1407,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>85.4</v>
+        <v>86.5</v>
       </c>
       <c r="G26" s="2">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="I26" s="4">
-        <v>68.0</v>
+        <v>63.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1430,7 +1430,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>19.35</v>
+        <v>21.04</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1439,16 +1439,16 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>174.0</v>
+        <v>187.2</v>
       </c>
       <c r="G27" s="2">
-        <v>80.6</v>
+        <v>86.8</v>
       </c>
       <c r="H27" s="3">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="I27" s="4">
-        <v>22.0</v>
+        <v>27.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>88</v>
@@ -1462,7 +1462,7 @@
         <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>6.52</v>
+        <v>6.68</v>
       </c>
       <c r="D28" s="3">
         <v>7.26</v>
@@ -1471,16 +1471,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>241.1</v>
+        <v>247.0</v>
       </c>
       <c r="G28" s="2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H28" s="3">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I28" s="4">
-        <v>64.0</v>
+        <v>73.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1494,7 +1494,7 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>28.02</v>
+        <v>27.25</v>
       </c>
       <c r="D29" s="3">
         <v>35.11</v>
@@ -1503,16 +1503,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>371.5</v>
+        <v>361.7</v>
       </c>
       <c r="G29" s="2">
-        <v>122.4</v>
+        <v>119.1</v>
       </c>
       <c r="H29" s="3">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="I29" s="4">
-        <v>76.0</v>
+        <v>73.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>93</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Qsu867S/zDWeC9f9DB0pnClaxQZw1/8MELZJZZXiE/0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="xJozn3x/dxC0c4mzlea9tZVW4Bi6QRZJmywhhTEk5E4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="95">
   <si>
     <t>Company</t>
   </si>
@@ -129,7 +129,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>News Archive for ESCA</t>
+    <t>(8/1/25) Escalade, Incorporated (ESCA)</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -210,7 +210,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>News Archive for NGS</t>
+    <t>(7/30/25) Natural Gas Services Group, Inc. (NGS)</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -225,6 +225,9 @@
     <t>OIS</t>
   </si>
   <si>
+    <t>(7/31/25) Oil States International, Inc. (OIS)</t>
+  </si>
+  <si>
     <t>Olympic Steel, Inc.</t>
   </si>
   <si>
@@ -264,7 +267,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>News Archive for RCKY</t>
+    <t>(7/29/25) Rocky Brands, Inc. (RCKY)</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -606,7 +609,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -615,16 +618,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.9</v>
+        <v>52.5</v>
       </c>
       <c r="G2" s="2">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="H2" s="3">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I2" s="4">
-        <v>33.0</v>
+        <v>44.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -641,25 +644,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.86</v>
+        <v>3.63</v>
       </c>
       <c r="D3" s="3">
-        <v>8.0</v>
+        <v>7.76</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>155.7</v>
+        <v>146.4</v>
       </c>
       <c r="G3" s="2">
-        <v>9.8</v>
+        <v>9.2</v>
       </c>
       <c r="H3" s="3">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="I3" s="4">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -673,25 +676,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="D4" s="3">
-        <v>5.49</v>
+        <v>5.25</v>
       </c>
       <c r="E4" s="3">
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>23.1</v>
+        <v>20.9</v>
       </c>
       <c r="G4" s="2">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="H4" s="3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -705,22 +708,22 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>17.3</v>
+        <v>16.5</v>
       </c>
       <c r="D5" s="3">
-        <v>19.2</v>
+        <v>18.71</v>
       </c>
       <c r="E5" s="3">
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>147.9</v>
+        <v>142.0</v>
       </c>
       <c r="G5" s="2">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="H5" s="3">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="I5" s="4">
         <v>72.0</v>
@@ -737,7 +740,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>25.36</v>
+        <v>23.27</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -746,16 +749,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>668.9</v>
+        <v>618.0</v>
       </c>
       <c r="G6" s="2">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
       <c r="H6" s="3">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="I6" s="4">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -769,25 +772,25 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>8.46</v>
+        <v>7.79</v>
       </c>
       <c r="D7" s="3">
-        <v>14.36</v>
+        <v>13.77</v>
       </c>
       <c r="E7" s="3">
         <v>6.02</v>
       </c>
       <c r="F7" s="2">
-        <v>171.9</v>
+        <v>159.6</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="4">
-        <v>73.0</v>
+        <v>46.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -804,7 +807,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.1</v>
+        <v>17.57</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -813,16 +816,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>465.3</v>
+        <v>453.2</v>
       </c>
       <c r="G8" s="2">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="H8" s="3">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="4">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -836,25 +839,25 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>12.61</v>
+        <v>11.87</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
       </c>
       <c r="E9" s="3">
-        <v>12.04</v>
+        <v>11.76</v>
       </c>
       <c r="F9" s="2">
-        <v>173.9</v>
+        <v>163.7</v>
       </c>
       <c r="G9" s="2">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H9" s="3">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="I9" s="4">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -868,25 +871,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>51.67</v>
+        <v>51.44</v>
       </c>
       <c r="D10" s="3">
-        <v>51.89</v>
+        <v>53.05</v>
       </c>
       <c r="E10" s="3">
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>363.6</v>
+        <v>360.4</v>
       </c>
       <c r="G10" s="2">
         <v>2.8</v>
       </c>
       <c r="H10" s="3">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I10" s="4">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="11">
@@ -897,25 +900,25 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>16.0</v>
+        <v>15.64</v>
       </c>
       <c r="D11" s="3">
-        <v>18.64</v>
+        <v>18.31</v>
       </c>
       <c r="E11" s="3">
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>99.9</v>
+        <v>98.5</v>
       </c>
       <c r="G11" s="2">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H11" s="3">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -932,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>15.9</v>
+        <v>14.94</v>
       </c>
       <c r="D12" s="3">
         <v>18.48</v>
@@ -941,13 +944,13 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>111.1</v>
+        <v>105.5</v>
       </c>
       <c r="G12" s="2">
-        <v>18.1</v>
+        <v>17.2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="I12" s="4">
         <v>68.0</v>
@@ -967,7 +970,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>7.74</v>
+        <v>7.35</v>
       </c>
       <c r="D13" s="3">
         <v>8.55</v>
@@ -976,13 +979,13 @@
         <v>4.04</v>
       </c>
       <c r="F13" s="2">
-        <v>445.1</v>
+        <v>420.5</v>
       </c>
       <c r="G13" s="2">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="H13" s="3">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="I13" s="4">
         <v>65.0</v>
@@ -999,25 +1002,25 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>18.93</v>
+        <v>18.26</v>
       </c>
       <c r="D14" s="3">
-        <v>24.45</v>
+        <v>21.9</v>
       </c>
       <c r="E14" s="3">
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>457.9</v>
+        <v>445.2</v>
       </c>
       <c r="G14" s="2">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="H14" s="3">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="I14" s="4">
-        <v>48.0</v>
+        <v>59.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1031,7 +1034,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>14.94</v>
+        <v>13.35</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1040,16 +1043,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>141.2</v>
+        <v>127.0</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.98</v>
+        <v>0.89</v>
       </c>
       <c r="I15" s="4">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1066,7 +1069,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>8.33</v>
+        <v>7.83</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1075,16 +1078,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>258.8</v>
+        <v>245.3</v>
       </c>
       <c r="G16" s="2">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="H16" s="3">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="I16" s="4">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1098,7 +1101,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>40.49</v>
+        <v>36.52</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1107,16 +1110,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>303.3</v>
+        <v>271.8</v>
       </c>
       <c r="G17" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="H17" s="3">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="I17" s="4">
-        <v>83.0</v>
+        <v>75.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1133,7 +1136,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>24.44</v>
+        <v>23.29</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1142,16 +1145,16 @@
         <v>16.7</v>
       </c>
       <c r="F18" s="2">
-        <v>304.2</v>
+        <v>291.8</v>
       </c>
       <c r="G18" s="2">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="H18" s="3">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="I18" s="4">
-        <v>27.0</v>
+        <v>38.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1165,7 +1168,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>30.69</v>
+        <v>31.64</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
@@ -1174,16 +1177,16 @@
         <v>16.66</v>
       </c>
       <c r="F19" s="2">
-        <v>78.1</v>
+        <v>80.4</v>
       </c>
       <c r="G19" s="2">
-        <v>9.4</v>
+        <v>6.7</v>
       </c>
       <c r="H19" s="3">
         <v>0.76</v>
       </c>
       <c r="I19" s="4">
-        <v>55.0</v>
+        <v>68.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1197,57 +1200,60 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>5.77</v>
+        <v>4.88</v>
       </c>
       <c r="D20" s="3">
-        <v>5.86</v>
+        <v>5.99</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>355.7</v>
+        <v>295.7</v>
       </c>
       <c r="G20" s="2">
-        <v>71.0</v>
+        <v>44.4</v>
       </c>
       <c r="H20" s="3">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="I20" s="4">
-        <v>54.0</v>
+        <v>48.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="K20" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="3">
-        <v>32.8</v>
+        <v>31.48</v>
       </c>
       <c r="D21" s="3">
-        <v>51.66</v>
+        <v>45.23</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>365.9</v>
+        <v>351.4</v>
       </c>
       <c r="G21" s="2">
-        <v>22.9</v>
+        <v>25.7</v>
       </c>
       <c r="H21" s="3">
         <v>0.64</v>
       </c>
       <c r="I21" s="4">
-        <v>44.0</v>
+        <v>41.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1255,13 +1261,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" s="3">
-        <v>5.08</v>
+        <v>4.59</v>
       </c>
       <c r="D22" s="3">
         <v>7.5</v>
@@ -1270,135 +1276,135 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>333.4</v>
+        <v>301.2</v>
       </c>
       <c r="G22" s="2">
-        <v>16.7</v>
+        <v>15.0</v>
       </c>
       <c r="H22" s="3">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="I22" s="4">
-        <v>41.0</v>
+        <v>36.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="3">
-        <v>17.68</v>
+        <v>15.56</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
       </c>
       <c r="E23" s="3">
-        <v>16.26</v>
+        <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>235.3</v>
+        <v>211.0</v>
       </c>
       <c r="G23" s="2">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="H23" s="3">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="I23" s="4">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="3">
-        <v>21.1</v>
+        <v>18.93</v>
       </c>
       <c r="D24" s="3">
-        <v>35.5</v>
+        <v>29.28</v>
       </c>
       <c r="E24" s="3">
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>51.6</v>
+        <v>46.1</v>
       </c>
       <c r="G24" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H24" s="3">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="I24" s="4">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" s="3">
-        <v>23.34</v>
+        <v>25.08</v>
       </c>
       <c r="D25" s="3">
-        <v>37.8</v>
+        <v>33.04</v>
       </c>
       <c r="E25" s="3">
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>174.1</v>
+        <v>187.1</v>
       </c>
       <c r="G25" s="2">
-        <v>12.7</v>
+        <v>10.1</v>
       </c>
       <c r="H25" s="3">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="I25" s="4">
-        <v>40.0</v>
+        <v>56.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" s="3">
-        <v>13.55</v>
+        <v>12.78</v>
       </c>
       <c r="D26" s="3">
         <v>16.48</v>
@@ -1407,30 +1413,30 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>86.5</v>
+        <v>82.3</v>
       </c>
       <c r="G26" s="2">
-        <v>24.6</v>
+        <v>23.4</v>
       </c>
       <c r="H26" s="3">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="I26" s="4">
         <v>63.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" s="3">
-        <v>21.04</v>
+        <v>19.43</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1439,30 +1445,30 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>187.2</v>
+        <v>174.7</v>
       </c>
       <c r="G27" s="2">
-        <v>86.8</v>
+        <v>81.0</v>
       </c>
       <c r="H27" s="3">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="I27" s="4">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" s="3">
-        <v>6.68</v>
+        <v>6.59</v>
       </c>
       <c r="D28" s="3">
         <v>7.26</v>
@@ -1471,7 +1477,7 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>247.0</v>
+        <v>243.7</v>
       </c>
       <c r="G28" s="2">
         <v>3.7</v>
@@ -1480,7 +1486,7 @@
         <v>0.37</v>
       </c>
       <c r="I28" s="4">
-        <v>73.0</v>
+        <v>77.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1488,34 +1494,34 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C29" s="3">
-        <v>27.25</v>
+        <v>25.8</v>
       </c>
       <c r="D29" s="3">
-        <v>35.11</v>
+        <v>32.68</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>361.7</v>
+        <v>342.0</v>
       </c>
       <c r="G29" s="2">
-        <v>119.1</v>
+        <v>112.7</v>
       </c>
       <c r="H29" s="3">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="I29" s="4">
-        <v>73.0</v>
+        <v>71.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="xJozn3x/dxC0c4mzlea9tZVW4Bi6QRZJmywhhTEk5E4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="b6/GtTcpiqDYZh79IxqbvYUpeZm+rU8cbmQ2TA8CWJI="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
   <si>
     <t>Company</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Currently qualifies</t>
   </si>
   <si>
-    <t>News Archive for APT</t>
+    <t>(8/7/25) Alpha Pro Tech, Ltd. (APT)</t>
   </si>
   <si>
     <t>Amplify Energy Corp.</t>
@@ -87,7 +87,7 @@
     <t>CMT</t>
   </si>
   <si>
-    <t>News Archive for CMT</t>
+    <t>(8/5/25) Core Molding Technologies, Inc. (CMT)</t>
   </si>
   <si>
     <t>Covenant Logistics Group, Inc.</t>
@@ -111,7 +111,7 @@
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
-    <t>News Archive for BOOM</t>
+    <t>(8/5/25) DMC Global Inc. (BOOM)</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -129,7 +129,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(8/1/25) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -153,7 +153,7 @@
     <t>FRD</t>
   </si>
   <si>
-    <t>News Archive for FRD</t>
+    <t>(8/7/25) Friedman Industries, Incorporated (FRD)</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
@@ -162,7 +162,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>News Archive for GILT</t>
+    <t>(8/6/25) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -192,7 +192,7 @@
     <t>MG</t>
   </si>
   <si>
-    <t>News Archive for MG</t>
+    <t>(8/6/25) Mistras Group, Inc. (MG)</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -201,7 +201,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>News Archive for NC</t>
+    <t>(8/6/25) NACCO Industries, Inc. (NC)</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -210,7 +210,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>(7/30/25) Natural Gas Services Group, Inc. (NGS)</t>
+    <t>News Archive for NGS</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -225,7 +225,7 @@
     <t>OIS</t>
   </si>
   <si>
-    <t>(7/31/25) Oil States International, Inc. (OIS)</t>
+    <t>News Archive for OIS</t>
   </si>
   <si>
     <t>Olympic Steel, Inc.</t>
@@ -240,7 +240,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>News Archive for PANL</t>
+    <t>(8/7/25) Pangaea Logistics Solutions, Ltd. (PANL)</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -249,7 +249,7 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>News Archive for PKOH</t>
+    <t>(8/6/25) Park-Ohio Holdings Corp. (PKOH)</t>
   </si>
   <si>
     <t>Regis Corporation</t>
@@ -267,7 +267,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>(7/29/25) Rocky Brands, Inc. (RCKY)</t>
+    <t>News Archive for RCKY</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -276,7 +276,7 @@
     <t>SGA</t>
   </si>
   <si>
-    <t>News Archive for SGA</t>
+    <t>(8/7/25) Saga Communications, Inc. (SGA)</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -285,7 +285,7 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>Approaching value limit</t>
+    <t>(8/6/25) Smith Douglas Homes Corp. (SDHC)</t>
   </si>
   <si>
     <t>StealthGas Inc.</t>
@@ -300,7 +300,7 @@
     <t>VPG</t>
   </si>
   <si>
-    <t>News Archive for VPG</t>
+    <t>(8/5/25) Vishay Precision Group, Inc. (VPG)</t>
   </si>
 </sst>
 </file>
@@ -609,7 +609,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="D2" s="3">
         <v>6.44</v>
@@ -618,16 +618,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>52.5</v>
+        <v>49.1</v>
       </c>
       <c r="G2" s="2">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="I2" s="4">
-        <v>44.0</v>
+        <v>35.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -644,7 +644,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="D3" s="3">
         <v>7.76</v>
@@ -653,16 +653,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>146.4</v>
+        <v>143.6</v>
       </c>
       <c r="G3" s="2">
         <v>9.2</v>
       </c>
       <c r="H3" s="3">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="I3" s="4">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -676,7 +676,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="D4" s="3">
         <v>5.25</v>
@@ -685,16 +685,16 @@
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="G4" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.5</v>
+        <v>17.02</v>
       </c>
       <c r="D5" s="3">
         <v>18.71</v>
@@ -717,16 +717,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>142.0</v>
+        <v>145.7</v>
       </c>
       <c r="G5" s="2">
-        <v>12.4</v>
+        <v>15.8</v>
       </c>
       <c r="H5" s="3">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="I5" s="4">
-        <v>72.0</v>
+        <v>77.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -740,7 +740,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>23.27</v>
+        <v>23.11</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -749,13 +749,13 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>618.0</v>
+        <v>613.7</v>
       </c>
       <c r="G6" s="2">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="H6" s="3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I6" s="4">
         <v>31.0</v>
@@ -772,25 +772,25 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>7.79</v>
+        <v>5.85</v>
       </c>
       <c r="D7" s="3">
         <v>13.77</v>
       </c>
       <c r="E7" s="3">
-        <v>6.02</v>
+        <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>159.6</v>
+        <v>120.4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="I7" s="4">
-        <v>46.0</v>
+        <v>21.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -807,7 +807,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>17.57</v>
+        <v>18.16</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -816,16 +816,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>453.2</v>
+        <v>468.4</v>
       </c>
       <c r="G8" s="2">
-        <v>11.6</v>
+        <v>12.0</v>
       </c>
       <c r="H8" s="3">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="I8" s="4">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -839,25 +839,25 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>11.87</v>
+        <v>11.8</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
       </c>
       <c r="E9" s="3">
-        <v>11.76</v>
+        <v>11.75</v>
       </c>
       <c r="F9" s="2">
-        <v>163.7</v>
+        <v>162.9</v>
       </c>
       <c r="G9" s="2">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H9" s="3">
         <v>0.97</v>
       </c>
       <c r="I9" s="4">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -871,25 +871,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>51.44</v>
+        <v>49.93</v>
       </c>
       <c r="D10" s="3">
-        <v>53.05</v>
+        <v>53.49</v>
       </c>
       <c r="E10" s="3">
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>360.4</v>
+        <v>349.8</v>
       </c>
       <c r="G10" s="2">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H10" s="3">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="I10" s="4">
-        <v>94.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="11">
@@ -900,25 +900,25 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>15.64</v>
+        <v>15.41</v>
       </c>
       <c r="D11" s="3">
-        <v>18.31</v>
+        <v>17.98</v>
       </c>
       <c r="E11" s="3">
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>98.5</v>
+        <v>97.0</v>
       </c>
       <c r="G11" s="2">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="I11" s="4">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -935,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>14.94</v>
+        <v>16.04</v>
       </c>
       <c r="D12" s="3">
         <v>18.48</v>
@@ -944,16 +944,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>105.5</v>
+        <v>113.2</v>
       </c>
       <c r="G12" s="2">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="I12" s="4">
-        <v>68.0</v>
+        <v>47.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -970,25 +970,25 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>7.35</v>
+        <v>8.79</v>
       </c>
       <c r="D13" s="3">
-        <v>8.55</v>
+        <v>9.4</v>
       </c>
       <c r="E13" s="3">
-        <v>4.04</v>
+        <v>4.3</v>
       </c>
       <c r="F13" s="2">
-        <v>420.5</v>
+        <v>501.6</v>
       </c>
       <c r="G13" s="2">
-        <v>30.6</v>
+        <v>22.4</v>
       </c>
       <c r="H13" s="3">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="I13" s="4">
-        <v>65.0</v>
+        <v>76.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>48</v>
@@ -1002,25 +1002,25 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>18.26</v>
+        <v>19.92</v>
       </c>
       <c r="D14" s="3">
-        <v>21.9</v>
+        <v>21.52</v>
       </c>
       <c r="E14" s="3">
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>445.2</v>
+        <v>485.7</v>
       </c>
       <c r="G14" s="2">
-        <v>25.7</v>
+        <v>28.0</v>
       </c>
       <c r="H14" s="3">
-        <v>0.81</v>
+        <v>0.89</v>
       </c>
       <c r="I14" s="4">
-        <v>59.0</v>
+        <v>74.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1034,7 +1034,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>13.35</v>
+        <v>14.13</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1043,16 +1043,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>127.0</v>
+        <v>134.4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.89</v>
+        <v>0.94</v>
       </c>
       <c r="I15" s="4">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -1069,7 +1069,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.83</v>
+        <v>8.73</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1078,16 +1078,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>245.3</v>
+        <v>275.3</v>
       </c>
       <c r="G16" s="2">
-        <v>16.6</v>
+        <v>23.8</v>
       </c>
       <c r="H16" s="3">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="I16" s="4">
-        <v>26.0</v>
+        <v>36.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1101,7 +1101,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>36.52</v>
+        <v>37.14</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1110,16 +1110,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>271.8</v>
+        <v>276.8</v>
       </c>
       <c r="G17" s="2">
-        <v>7.9</v>
+        <v>8.8</v>
       </c>
       <c r="H17" s="3">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="I17" s="4">
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1136,25 +1136,25 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>23.29</v>
+        <v>24.78</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
       </c>
       <c r="E18" s="3">
-        <v>16.7</v>
+        <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>291.8</v>
+        <v>310.5</v>
       </c>
       <c r="G18" s="2">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="H18" s="3">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="I18" s="4">
-        <v>38.0</v>
+        <v>48.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1168,25 +1168,25 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>31.64</v>
+        <v>33.03</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
       </c>
       <c r="E19" s="3">
-        <v>16.66</v>
+        <v>16.81</v>
       </c>
       <c r="F19" s="2">
-        <v>80.4</v>
+        <v>83.9</v>
       </c>
       <c r="G19" s="2">
-        <v>6.7</v>
+        <v>7.0</v>
       </c>
       <c r="H19" s="3">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="I19" s="4">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1200,7 +1200,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>4.88</v>
+        <v>5.02</v>
       </c>
       <c r="D20" s="3">
         <v>5.99</v>
@@ -1209,16 +1209,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>295.7</v>
+        <v>304.2</v>
       </c>
       <c r="G20" s="2">
-        <v>44.4</v>
+        <v>46.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="I20" s="4">
-        <v>48.0</v>
+        <v>52.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1235,25 +1235,25 @@
         <v>71</v>
       </c>
       <c r="C21" s="3">
-        <v>31.48</v>
+        <v>31.13</v>
       </c>
       <c r="D21" s="3">
-        <v>45.23</v>
+        <v>43.6</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>351.4</v>
+        <v>348.6</v>
       </c>
       <c r="G21" s="2">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="I21" s="4">
-        <v>41.0</v>
+        <v>39.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1267,7 +1267,7 @@
         <v>73</v>
       </c>
       <c r="C22" s="3">
-        <v>4.59</v>
+        <v>4.91</v>
       </c>
       <c r="D22" s="3">
         <v>7.5</v>
@@ -1276,16 +1276,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>301.2</v>
+        <v>322.2</v>
       </c>
       <c r="G22" s="2">
-        <v>15.0</v>
+        <v>30.5</v>
       </c>
       <c r="H22" s="3">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="I22" s="4">
-        <v>36.0</v>
+        <v>44.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>74</v>
@@ -1299,7 +1299,7 @@
         <v>76</v>
       </c>
       <c r="C23" s="3">
-        <v>15.56</v>
+        <v>17.78</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1308,16 +1308,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>211.0</v>
+        <v>241.1</v>
       </c>
       <c r="G23" s="2">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="H23" s="3">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="I23" s="4">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1334,7 +1334,7 @@
         <v>79</v>
       </c>
       <c r="C24" s="3">
-        <v>18.93</v>
+        <v>19.42</v>
       </c>
       <c r="D24" s="3">
         <v>29.28</v>
@@ -1343,16 +1343,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>46.1</v>
+        <v>47.3</v>
       </c>
       <c r="G24" s="2">
         <v>0.5</v>
       </c>
       <c r="H24" s="3">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="I24" s="4">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1369,7 +1369,7 @@
         <v>82</v>
       </c>
       <c r="C25" s="3">
-        <v>25.08</v>
+        <v>26.57</v>
       </c>
       <c r="D25" s="3">
         <v>33.04</v>
@@ -1378,16 +1378,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>187.1</v>
+        <v>198.4</v>
       </c>
       <c r="G25" s="2">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="H25" s="3">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="I25" s="4">
-        <v>56.0</v>
+        <v>69.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1404,25 +1404,28 @@
         <v>85</v>
       </c>
       <c r="C26" s="3">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="D26" s="3">
-        <v>16.48</v>
+        <v>16.03</v>
       </c>
       <c r="E26" s="3">
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>82.3</v>
+        <v>83.1</v>
       </c>
       <c r="G26" s="2">
-        <v>23.4</v>
+        <v>39.8</v>
       </c>
       <c r="H26" s="3">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I26" s="4">
-        <v>63.0</v>
+        <v>57.0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>86</v>
@@ -1436,7 +1439,7 @@
         <v>88</v>
       </c>
       <c r="C27" s="3">
-        <v>19.43</v>
+        <v>18.39</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1445,18 +1448,18 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>174.7</v>
-      </c>
-      <c r="G27" s="2">
-        <v>81.0</v>
+        <v>165.8</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="H27" s="3">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="I27" s="4">
-        <v>26.0</v>
-      </c>
-      <c r="J27" s="2" t="s">
+        <v>23.0</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1468,7 +1471,7 @@
         <v>91</v>
       </c>
       <c r="C28" s="3">
-        <v>6.59</v>
+        <v>6.67</v>
       </c>
       <c r="D28" s="3">
         <v>7.26</v>
@@ -1477,7 +1480,7 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>243.7</v>
+        <v>246.6</v>
       </c>
       <c r="G28" s="2">
         <v>3.7</v>
@@ -1486,7 +1489,7 @@
         <v>0.37</v>
       </c>
       <c r="I28" s="4">
-        <v>77.0</v>
+        <v>76.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1500,25 +1503,25 @@
         <v>93</v>
       </c>
       <c r="C29" s="3">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="D29" s="3">
-        <v>32.68</v>
+        <v>30.11</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>342.0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>112.7</v>
+        <v>361.2</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="H29" s="3">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="I29" s="4">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>94</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="b6/GtTcpiqDYZh79IxqbvYUpeZm+rU8cbmQ2TA8CWJI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="w5H35OOGiFUjd0Er1Dr3GWwTKJgGKavT3QX4A12c6lA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="97">
   <si>
     <t>Company</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Currently qualifies</t>
   </si>
   <si>
-    <t>(8/7/25) Alpha Pro Tech, Ltd. (APT)</t>
+    <t>News Archive for APT</t>
   </si>
   <si>
     <t>Amplify Energy Corp.</t>
@@ -78,6 +78,9 @@
     <t>CTRM</t>
   </si>
   <si>
+    <t>nmf</t>
+  </si>
+  <si>
     <t>News Archive for CTRM</t>
   </si>
   <si>
@@ -87,7 +90,7 @@
     <t>CMT</t>
   </si>
   <si>
-    <t>(8/5/25) Core Molding Technologies, Inc. (CMT)</t>
+    <t>News Archive for CMT</t>
   </si>
   <si>
     <t>Covenant Logistics Group, Inc.</t>
@@ -105,13 +108,10 @@
     <t>BOOM</t>
   </si>
   <si>
-    <t>nmf</t>
-  </si>
-  <si>
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
-    <t>(8/5/25) DMC Global Inc. (BOOM)</t>
+    <t>News Archive for BOOM</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -138,6 +138,9 @@
     <t>ESEA</t>
   </si>
   <si>
+    <t>News Archive for ESEA</t>
+  </si>
+  <si>
     <t>FONAR Corporation</t>
   </si>
   <si>
@@ -153,7 +156,7 @@
     <t>FRD</t>
   </si>
   <si>
-    <t>(8/7/25) Friedman Industries, Incorporated (FRD)</t>
+    <t>News Archive for FRD</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
@@ -162,7 +165,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>(8/6/25) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>News Archive for GILT</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -192,7 +195,7 @@
     <t>MG</t>
   </si>
   <si>
-    <t>(8/6/25) Mistras Group, Inc. (MG)</t>
+    <t>News Archive for MG</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -201,7 +204,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>(8/6/25) NACCO Industries, Inc. (NC)</t>
+    <t>News Archive for NC</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -240,7 +243,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>(8/7/25) Pangaea Logistics Solutions, Ltd. (PANL)</t>
+    <t>News Archive for PANL</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -249,7 +252,7 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>(8/6/25) Park-Ohio Holdings Corp. (PKOH)</t>
+    <t>News Archive for PKOH</t>
   </si>
   <si>
     <t>Regis Corporation</t>
@@ -276,7 +279,7 @@
     <t>SGA</t>
   </si>
   <si>
-    <t>(8/7/25) Saga Communications, Inc. (SGA)</t>
+    <t>News Archive for SGA</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -285,7 +288,10 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>(8/6/25) Smith Douglas Homes Corp. (SDHC)</t>
+    <t>TTM adjusted earnings positive Approaching value limit</t>
+  </si>
+  <si>
+    <t>News Archive for SDHC</t>
   </si>
   <si>
     <t>StealthGas Inc.</t>
@@ -300,7 +306,7 @@
     <t>VPG</t>
   </si>
   <si>
-    <t>(8/5/25) Vishay Precision Group, Inc. (VPG)</t>
+    <t>News Archive for VPG</t>
   </si>
 </sst>
 </file>
@@ -609,25 +615,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.71</v>
+        <v>4.84</v>
       </c>
       <c r="D2" s="3">
-        <v>6.44</v>
+        <v>6.39</v>
       </c>
       <c r="E2" s="3">
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>49.1</v>
+        <v>50.7</v>
       </c>
       <c r="G2" s="2">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="H2" s="3">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>35.0</v>
+        <v>26.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -644,25 +650,28 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.56</v>
+        <v>4.13</v>
       </c>
       <c r="D3" s="3">
-        <v>7.76</v>
+        <v>7.35</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>143.6</v>
+        <v>167.1</v>
       </c>
       <c r="G3" s="2">
-        <v>9.2</v>
+        <v>11.0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="I3" s="4">
-        <v>16.0</v>
+        <v>22.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -676,71 +685,71 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="D4" s="3">
-        <v>5.25</v>
+        <v>4.98</v>
       </c>
       <c r="E4" s="3">
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="G4" s="2">
-        <v>5.6</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.04</v>
+        <v>5.8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I4" s="4">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>17.02</v>
+        <v>19.47</v>
       </c>
       <c r="D5" s="3">
-        <v>18.71</v>
+        <v>19.47</v>
       </c>
       <c r="E5" s="3">
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>145.7</v>
+        <v>166.7</v>
       </c>
       <c r="G5" s="2">
-        <v>15.8</v>
+        <v>18.1</v>
       </c>
       <c r="H5" s="3">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="I5" s="4">
-        <v>77.0</v>
+        <v>88.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>23.11</v>
+        <v>25.03</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -749,30 +758,30 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>613.7</v>
+        <v>626.2</v>
       </c>
       <c r="G6" s="2">
-        <v>17.6</v>
+        <v>19.1</v>
       </c>
       <c r="H6" s="3">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="4">
-        <v>31.0</v>
+        <v>42.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>5.85</v>
+        <v>6.93</v>
       </c>
       <c r="D7" s="3">
         <v>13.77</v>
@@ -781,16 +790,16 @@
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>120.4</v>
+        <v>142.6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>0.47</v>
+        <v>0.56</v>
       </c>
       <c r="I7" s="4">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -807,7 +816,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.16</v>
+        <v>18.7</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -816,16 +825,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>468.4</v>
+        <v>482.4</v>
       </c>
       <c r="G8" s="2">
-        <v>12.0</v>
+        <v>12.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="4">
-        <v>37.0</v>
+        <v>31.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -839,25 +848,25 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>11.8</v>
+        <v>13.4</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
       </c>
       <c r="E9" s="3">
-        <v>11.75</v>
+        <v>11.74</v>
       </c>
       <c r="F9" s="2">
-        <v>162.9</v>
+        <v>185.0</v>
       </c>
       <c r="G9" s="2">
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="H9" s="3">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="I9" s="4">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -871,36 +880,39 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>49.93</v>
+        <v>64.6</v>
       </c>
       <c r="D10" s="3">
-        <v>53.49</v>
+        <v>65.5</v>
       </c>
       <c r="E10" s="3">
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>349.8</v>
+        <v>452.6</v>
       </c>
       <c r="G10" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.93</v>
+        <v>3.5</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I10" s="4">
-        <v>92.0</v>
+        <v>95.0</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>15.41</v>
+        <v>15.24</v>
       </c>
       <c r="D11" s="3">
         <v>17.98</v>
@@ -909,33 +921,33 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>97.0</v>
+        <v>96.0</v>
       </c>
       <c r="G11" s="2">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="H11" s="3">
         <v>0.56</v>
       </c>
       <c r="I11" s="4">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>16.04</v>
+        <v>17.53</v>
       </c>
       <c r="D12" s="3">
         <v>18.48</v>
@@ -944,97 +956,97 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>113.2</v>
+        <v>123.8</v>
       </c>
       <c r="G12" s="2">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="H12" s="3">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="I12" s="4">
-        <v>47.0</v>
+        <v>52.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>8.79</v>
+        <v>9.39</v>
       </c>
       <c r="D13" s="3">
-        <v>9.4</v>
+        <v>9.63</v>
       </c>
       <c r="E13" s="3">
         <v>4.3</v>
       </c>
       <c r="F13" s="2">
-        <v>501.6</v>
+        <v>535.8</v>
       </c>
       <c r="G13" s="2">
-        <v>22.4</v>
+        <v>23.9</v>
       </c>
       <c r="H13" s="3">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="I13" s="4">
         <v>76.0</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>19.92</v>
+        <v>28.34</v>
       </c>
       <c r="D14" s="3">
-        <v>21.52</v>
+        <v>28.86</v>
       </c>
       <c r="E14" s="3">
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>485.7</v>
+        <v>690.9</v>
       </c>
       <c r="G14" s="2">
-        <v>28.0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.89</v>
+        <v>39.9</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I14" s="4">
-        <v>74.0</v>
+        <v>91.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>14.13</v>
+        <v>15.5</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1043,33 +1055,33 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>134.4</v>
+        <v>147.5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H15" s="3">
-        <v>0.94</v>
+        <v>1.03</v>
       </c>
       <c r="I15" s="4">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>8.73</v>
+        <v>9.61</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1078,30 +1090,30 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>275.3</v>
+        <v>303.1</v>
       </c>
       <c r="G16" s="2">
-        <v>23.8</v>
+        <v>26.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="I16" s="4">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>37.14</v>
+        <v>38.39</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1110,33 +1122,33 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>276.8</v>
+        <v>286.1</v>
       </c>
       <c r="G17" s="2">
-        <v>8.8</v>
+        <v>9.1</v>
       </c>
       <c r="H17" s="3">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="I17" s="4">
-        <v>77.0</v>
+        <v>69.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>24.78</v>
+        <v>26.68</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1145,30 +1157,30 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>310.5</v>
+        <v>334.6</v>
       </c>
       <c r="G18" s="2">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="H18" s="3">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="I18" s="4">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>33.03</v>
+        <v>37.0</v>
       </c>
       <c r="D19" s="3">
         <v>38.95</v>
@@ -1177,16 +1189,16 @@
         <v>16.81</v>
       </c>
       <c r="F19" s="2">
-        <v>83.9</v>
+        <v>94.0</v>
       </c>
       <c r="G19" s="2">
-        <v>7.0</v>
+        <v>7.9</v>
       </c>
       <c r="H19" s="3">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="I19" s="4">
-        <v>70.0</v>
+        <v>81.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1194,13 +1206,13 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>5.02</v>
+        <v>5.45</v>
       </c>
       <c r="D20" s="3">
         <v>5.99</v>
@@ -1209,33 +1221,33 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>304.2</v>
+        <v>330.2</v>
       </c>
       <c r="G20" s="2">
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="I20" s="4">
-        <v>52.0</v>
+        <v>67.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>31.13</v>
+        <v>33.56</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1244,16 +1256,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>348.6</v>
+        <v>375.8</v>
       </c>
       <c r="G21" s="2">
-        <v>25.4</v>
+        <v>27.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="I21" s="4">
-        <v>39.0</v>
+        <v>29.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1261,13 +1273,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>4.91</v>
+        <v>5.29</v>
       </c>
       <c r="D22" s="3">
         <v>7.5</v>
@@ -1276,30 +1288,30 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>322.2</v>
+        <v>345.1</v>
       </c>
       <c r="G22" s="2">
-        <v>30.5</v>
+        <v>32.9</v>
       </c>
       <c r="H22" s="3">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="I22" s="4">
-        <v>44.0</v>
+        <v>48.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>17.78</v>
+        <v>19.96</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1308,33 +1320,33 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>241.1</v>
+        <v>278.2</v>
       </c>
       <c r="G23" s="2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="H23" s="3">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="I23" s="4">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>19.42</v>
+        <v>19.95</v>
       </c>
       <c r="D24" s="3">
         <v>29.28</v>
@@ -1343,33 +1355,33 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>47.3</v>
+        <v>48.6</v>
       </c>
       <c r="G24" s="2">
         <v>0.5</v>
       </c>
       <c r="H24" s="3">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="I24" s="4">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>26.57</v>
+        <v>27.9</v>
       </c>
       <c r="D25" s="3">
         <v>33.04</v>
@@ -1378,68 +1390,68 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>198.4</v>
+        <v>208.4</v>
       </c>
       <c r="G25" s="2">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="H25" s="3">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="I25" s="4">
-        <v>69.0</v>
+        <v>73.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="D26" s="3">
-        <v>16.03</v>
+        <v>15.29</v>
       </c>
       <c r="E26" s="3">
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>83.1</v>
+        <v>85.7</v>
       </c>
       <c r="G26" s="2">
-        <v>39.8</v>
+        <v>40.5</v>
       </c>
       <c r="H26" s="3">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="I26" s="4">
-        <v>57.0</v>
+        <v>61.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>18.39</v>
+        <v>20.63</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1448,62 +1460,62 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>165.8</v>
+        <v>186.0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H27" s="3">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="I27" s="4">
-        <v>23.0</v>
+        <v>28.0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>6.67</v>
+        <v>7.24</v>
       </c>
       <c r="D28" s="3">
-        <v>7.26</v>
+        <v>7.37</v>
       </c>
       <c r="E28" s="3">
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>246.6</v>
+        <v>267.7</v>
       </c>
       <c r="G28" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="H28" s="3">
-        <v>0.37</v>
+        <v>3.8</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I28" s="4">
-        <v>76.0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>27.2</v>
+        <v>28.67</v>
       </c>
       <c r="D29" s="3">
         <v>30.11</v>
@@ -1512,19 +1524,19 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>361.2</v>
+        <v>380.7</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H29" s="3">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="I29" s="4">
-        <v>73.0</v>
+        <v>65.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="w5H35OOGiFUjd0Er1Dr3GWwTKJgGKavT3QX4A12c6lA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="33z9py41hdmaMlib+OE1HRliRg2RHrDYhXMjz1Hqol4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
   <si>
     <t>Company</t>
   </si>
@@ -288,9 +288,6 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>TTM adjusted earnings positive Approaching value limit</t>
-  </si>
-  <si>
     <t>News Archive for SDHC</t>
   </si>
   <si>
@@ -298,6 +295,9 @@
   </si>
   <si>
     <t>GASS</t>
+  </si>
+  <si>
+    <t>(8/25/25) StealthGas Inc. (GASS)</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -615,25 +615,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="D2" s="3">
-        <v>6.39</v>
+        <v>6.2</v>
       </c>
       <c r="E2" s="3">
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="G2" s="2">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="I2" s="4">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -650,7 +650,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="D3" s="3">
         <v>7.35</v>
@@ -659,13 +659,13 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>167.1</v>
+        <v>164.7</v>
       </c>
       <c r="G3" s="2">
-        <v>11.0</v>
+        <v>10.8</v>
       </c>
       <c r="H3" s="3">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I3" s="4">
         <v>22.0</v>
@@ -685,25 +685,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="D4" s="3">
-        <v>4.98</v>
+        <v>4.64</v>
       </c>
       <c r="E4" s="3">
         <v>1.98</v>
       </c>
       <c r="F4" s="2">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="G4" s="2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="4">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>21</v>
@@ -717,7 +717,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>19.47</v>
+        <v>19.2</v>
       </c>
       <c r="D5" s="3">
         <v>19.47</v>
@@ -726,16 +726,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>166.7</v>
+        <v>164.4</v>
       </c>
       <c r="G5" s="2">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="H5" s="3">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="I5" s="4">
-        <v>88.0</v>
+        <v>84.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -749,7 +749,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>25.03</v>
+        <v>24.13</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -758,16 +758,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>626.2</v>
+        <v>603.7</v>
       </c>
       <c r="G6" s="2">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="H6" s="3">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="I6" s="4">
-        <v>42.0</v>
+        <v>37.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -781,7 +781,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>6.93</v>
+        <v>6.7</v>
       </c>
       <c r="D7" s="3">
         <v>13.77</v>
@@ -790,16 +790,16 @@
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>142.6</v>
+        <v>137.9</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
       <c r="I7" s="4">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -816,7 +816,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.7</v>
+        <v>18.27</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -825,16 +825,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>482.4</v>
+        <v>471.3</v>
       </c>
       <c r="G8" s="2">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="I8" s="4">
-        <v>31.0</v>
+        <v>24.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -848,7 +848,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -857,16 +857,16 @@
         <v>11.74</v>
       </c>
       <c r="F9" s="2">
-        <v>185.0</v>
+        <v>173.9</v>
       </c>
       <c r="G9" s="2">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="I9" s="4">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -880,7 +880,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>64.6</v>
+        <v>62.27</v>
       </c>
       <c r="D10" s="3">
         <v>65.5</v>
@@ -889,16 +889,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>452.6</v>
+        <v>436.3</v>
       </c>
       <c r="G10" s="2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="4">
-        <v>95.0</v>
+        <v>93.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -912,7 +912,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>15.24</v>
+        <v>15.98</v>
       </c>
       <c r="D11" s="3">
         <v>17.98</v>
@@ -921,16 +921,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>96.0</v>
+        <v>100.6</v>
       </c>
       <c r="G11" s="2">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="H11" s="3">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="I11" s="4">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -947,28 +947,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>17.53</v>
+        <v>19.09</v>
       </c>
       <c r="D12" s="3">
-        <v>18.48</v>
+        <v>19.15</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>123.8</v>
+        <v>134.8</v>
       </c>
       <c r="G12" s="2">
-        <v>14.5</v>
+        <v>15.8</v>
       </c>
       <c r="H12" s="3">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="I12" s="4">
-        <v>52.0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>67.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,16 +979,16 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>9.39</v>
+        <v>9.41</v>
       </c>
       <c r="D13" s="3">
-        <v>9.63</v>
+        <v>10.09</v>
       </c>
       <c r="E13" s="3">
         <v>4.3</v>
       </c>
       <c r="F13" s="2">
-        <v>535.8</v>
+        <v>537.0</v>
       </c>
       <c r="G13" s="2">
         <v>23.9</v>
@@ -1000,7 +997,7 @@
         <v>1.7</v>
       </c>
       <c r="I13" s="4">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>49</v>
@@ -1014,25 +1011,25 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>28.34</v>
+        <v>28.87</v>
       </c>
       <c r="D14" s="3">
-        <v>28.86</v>
+        <v>29.11</v>
       </c>
       <c r="E14" s="3">
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>690.9</v>
+        <v>699.2</v>
       </c>
       <c r="G14" s="2">
-        <v>39.9</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>20</v>
+        <v>42.5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1.23</v>
       </c>
       <c r="I14" s="4">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1046,7 +1043,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>15.5</v>
+        <v>15.19</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1055,16 +1052,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>147.5</v>
+        <v>144.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="I15" s="4">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>55</v>
@@ -1081,7 +1078,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>9.61</v>
+        <v>9.56</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1090,16 +1087,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>303.1</v>
+        <v>301.5</v>
       </c>
       <c r="G16" s="2">
-        <v>26.2</v>
+        <v>26.0</v>
       </c>
       <c r="H16" s="3">
         <v>1.4</v>
       </c>
       <c r="I16" s="4">
-        <v>40.0</v>
+        <v>39.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>59</v>
@@ -1113,7 +1110,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>38.39</v>
+        <v>39.12</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1122,16 +1119,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>286.1</v>
+        <v>291.5</v>
       </c>
       <c r="G17" s="2">
-        <v>9.1</v>
+        <v>9.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="I17" s="4">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1148,7 +1145,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>26.68</v>
+        <v>26.16</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1157,13 +1154,13 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>334.6</v>
+        <v>328.1</v>
       </c>
       <c r="G18" s="2">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="H18" s="3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="I18" s="4">
         <v>46.0</v>
@@ -1180,28 +1177,25 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>37.0</v>
+        <v>38.11</v>
       </c>
       <c r="D19" s="3">
-        <v>38.95</v>
+        <v>41.75</v>
       </c>
       <c r="E19" s="3">
         <v>16.81</v>
       </c>
       <c r="F19" s="2">
-        <v>94.0</v>
+        <v>96.8</v>
       </c>
       <c r="G19" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="H19" s="3">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I19" s="4">
-        <v>81.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1212,7 +1206,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="D20" s="3">
         <v>5.99</v>
@@ -1221,16 +1215,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>330.2</v>
+        <v>339.3</v>
       </c>
       <c r="G20" s="2">
-        <v>50.5</v>
+        <v>51.9</v>
       </c>
       <c r="H20" s="3">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I20" s="4">
-        <v>67.0</v>
+        <v>48.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1247,7 +1241,7 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>33.56</v>
+        <v>33.71</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1256,16 +1250,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>375.8</v>
+        <v>377.5</v>
       </c>
       <c r="G21" s="2">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="H21" s="3">
         <v>0.65</v>
       </c>
       <c r="I21" s="4">
-        <v>29.0</v>
+        <v>46.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1279,7 +1273,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="D22" s="3">
         <v>7.5</v>
@@ -1288,16 +1282,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>345.1</v>
+        <v>347.7</v>
       </c>
       <c r="G22" s="2">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="H22" s="3">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I22" s="4">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>75</v>
@@ -1311,7 +1305,7 @@
         <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>19.96</v>
+        <v>20.2</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1320,16 +1314,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>278.2</v>
+        <v>281.6</v>
       </c>
       <c r="G23" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="H23" s="3">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I23" s="4">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1346,7 +1340,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>19.95</v>
+        <v>22.15</v>
       </c>
       <c r="D24" s="3">
         <v>29.28</v>
@@ -1355,16 +1349,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>48.6</v>
+        <v>54.0</v>
       </c>
       <c r="G24" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="I24" s="4">
-        <v>34.0</v>
+        <v>41.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1381,7 +1375,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>27.9</v>
+        <v>30.43</v>
       </c>
       <c r="D25" s="3">
         <v>33.04</v>
@@ -1390,19 +1384,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>208.4</v>
+        <v>227.3</v>
       </c>
       <c r="G25" s="2">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="H25" s="3">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="I25" s="4">
-        <v>73.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>13</v>
+        <v>88.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>84</v>
@@ -1416,25 +1407,25 @@
         <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>13.3</v>
+        <v>12.0</v>
       </c>
       <c r="D26" s="3">
-        <v>15.29</v>
+        <v>15.1</v>
       </c>
       <c r="E26" s="3">
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>85.7</v>
+        <v>77.3</v>
       </c>
       <c r="G26" s="2">
-        <v>40.5</v>
+        <v>36.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="I26" s="4">
-        <v>61.0</v>
+        <v>54.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1451,7 +1442,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>20.63</v>
+        <v>19.61</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1460,51 +1451,54 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>186.0</v>
+        <v>176.8</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="3">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="I27" s="4">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
       <c r="J27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C28" s="3">
-        <v>7.24</v>
+        <v>7.63</v>
       </c>
       <c r="D28" s="3">
-        <v>7.37</v>
+        <v>8.18</v>
       </c>
       <c r="E28" s="3">
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>267.7</v>
+        <v>282.1</v>
       </c>
       <c r="G28" s="2">
-        <v>3.8</v>
+        <v>4.0</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I28" s="4">
-        <v>73.0</v>
+        <v>82.0</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1515,7 +1509,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>28.67</v>
+        <v>28.42</v>
       </c>
       <c r="D29" s="3">
         <v>30.11</v>
@@ -1524,16 +1518,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>380.7</v>
+        <v>377.4</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I29" s="4">
-        <v>65.0</v>
+        <v>72.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>96</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="33z9py41hdmaMlib+OE1HRliRg2RHrDYhXMjz1Hqol4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="f9dwIIPK1x/aH9+hkwciK6U2vPTkRbFPoBlckZdEYfY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -78,36 +78,36 @@
     <t>CTRM</t>
   </si>
   <si>
+    <t>News Archive for CTRM</t>
+  </si>
+  <si>
+    <t>Core Molding Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>News Archive for CMT</t>
+  </si>
+  <si>
+    <t>Covenant Logistics Group, Inc.</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>News Archive for CVLG</t>
+  </si>
+  <si>
+    <t>DMC Global Inc.</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
     <t>nmf</t>
   </si>
   <si>
-    <t>News Archive for CTRM</t>
-  </si>
-  <si>
-    <t>Core Molding Technologies, Inc.</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>News Archive for CMT</t>
-  </si>
-  <si>
-    <t>Covenant Logistics Group, Inc.</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>News Archive for CVLG</t>
-  </si>
-  <si>
-    <t>DMC Global Inc.</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
@@ -261,7 +261,7 @@
     <t>RGS</t>
   </si>
   <si>
-    <t>News Archive for RGS</t>
+    <t>(9/3/25) Regis Corporation (RGS)</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -288,6 +288,9 @@
     <t>SDHC</t>
   </si>
   <si>
+    <t>TTM adjusted earnings positive Approaching value limit</t>
+  </si>
+  <si>
     <t>News Archive for SDHC</t>
   </si>
   <si>
@@ -297,7 +300,7 @@
     <t>GASS</t>
   </si>
   <si>
-    <t>(8/25/25) StealthGas Inc. (GASS)</t>
+    <t>News Archive for GASS</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -615,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.78</v>
+        <v>4.89</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -624,16 +627,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>50.1</v>
+        <v>51.2</v>
       </c>
       <c r="G2" s="2">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="H2" s="3">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="I2" s="4">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -650,7 +653,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.07</v>
+        <v>3.84</v>
       </c>
       <c r="D3" s="3">
         <v>7.35</v>
@@ -659,19 +662,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>164.7</v>
+        <v>155.4</v>
       </c>
       <c r="G3" s="2">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="H3" s="3">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="I3" s="4">
-        <v>22.0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>13</v>
+        <v>41.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -685,71 +685,71 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="D4" s="3">
-        <v>4.64</v>
+        <v>4.55</v>
       </c>
       <c r="E4" s="3">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="F4" s="2">
-        <v>20.6</v>
+        <v>19.0</v>
       </c>
       <c r="G4" s="2">
-        <v>5.6</v>
-      </c>
-      <c r="H4" s="2" t="s">
+        <v>5.2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="I4" s="4">
+        <v>17.0</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="I4" s="4">
-        <v>26.0</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C5" s="3">
-        <v>19.2</v>
+        <v>19.79</v>
       </c>
       <c r="D5" s="3">
-        <v>19.47</v>
+        <v>19.79</v>
       </c>
       <c r="E5" s="3">
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>164.4</v>
+        <v>169.4</v>
       </c>
       <c r="G5" s="2">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="H5" s="3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="I5" s="4">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C6" s="3">
-        <v>24.13</v>
+        <v>23.93</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -758,30 +758,30 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>603.7</v>
+        <v>598.7</v>
       </c>
       <c r="G6" s="2">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="H6" s="3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I6" s="4">
-        <v>37.0</v>
+        <v>35.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="C7" s="3">
-        <v>6.7</v>
+        <v>7.09</v>
       </c>
       <c r="D7" s="3">
         <v>13.77</v>
@@ -790,16 +790,16 @@
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>137.9</v>
+        <v>145.9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="I7" s="4">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -816,7 +816,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.27</v>
+        <v>18.48</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -825,16 +825,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>471.3</v>
+        <v>476.7</v>
       </c>
       <c r="G8" s="2">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="H8" s="3">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="I8" s="4">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -848,7 +848,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>12.6</v>
+        <v>12.86</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -857,16 +857,16 @@
         <v>11.74</v>
       </c>
       <c r="F9" s="2">
-        <v>173.9</v>
+        <v>177.5</v>
       </c>
       <c r="G9" s="2">
-        <v>13.7</v>
+        <v>14.0</v>
       </c>
       <c r="H9" s="3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="I9" s="4">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -880,7 +880,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>62.27</v>
+        <v>61.89</v>
       </c>
       <c r="D10" s="3">
         <v>65.5</v>
@@ -889,13 +889,13 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>436.3</v>
+        <v>433.6</v>
       </c>
       <c r="G10" s="2">
         <v>3.3</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>20</v>
+      <c r="H10" s="3">
+        <v>1.16</v>
       </c>
       <c r="I10" s="4">
         <v>93.0</v>
@@ -912,7 +912,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>15.98</v>
+        <v>15.6</v>
       </c>
       <c r="D11" s="3">
         <v>17.98</v>
@@ -921,16 +921,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>100.6</v>
+        <v>98.2</v>
       </c>
       <c r="G11" s="2">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="H11" s="3">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>55.0</v>
+        <v>51.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -947,25 +947,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.09</v>
+        <v>21.72</v>
       </c>
       <c r="D12" s="3">
-        <v>19.15</v>
+        <v>21.97</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>134.8</v>
+        <v>153.3</v>
       </c>
       <c r="G12" s="2">
-        <v>15.8</v>
+        <v>17.9</v>
       </c>
       <c r="H12" s="3">
-        <v>0.98</v>
+        <v>1.12</v>
       </c>
       <c r="I12" s="4">
-        <v>67.0</v>
+        <v>81.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -979,7 +979,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>9.41</v>
+        <v>9.97</v>
       </c>
       <c r="D13" s="3">
         <v>10.09</v>
@@ -988,16 +988,16 @@
         <v>4.3</v>
       </c>
       <c r="F13" s="2">
-        <v>537.0</v>
+        <v>568.9</v>
       </c>
       <c r="G13" s="2">
-        <v>23.9</v>
+        <v>25.4</v>
       </c>
       <c r="H13" s="3">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="I13" s="4">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>49</v>
@@ -1011,25 +1011,25 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>28.87</v>
+        <v>29.9</v>
       </c>
       <c r="D14" s="3">
-        <v>29.11</v>
+        <v>29.99</v>
       </c>
       <c r="E14" s="3">
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>699.2</v>
+        <v>724.1</v>
       </c>
       <c r="G14" s="2">
-        <v>42.5</v>
+        <v>44.0</v>
       </c>
       <c r="H14" s="3">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="I14" s="4">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1043,7 +1043,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>15.19</v>
+        <v>14.98</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1052,16 +1052,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>144.5</v>
+        <v>142.5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="I15" s="4">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>55</v>
@@ -1078,7 +1078,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>9.56</v>
+        <v>9.73</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1087,16 +1087,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>301.5</v>
+        <v>306.9</v>
       </c>
       <c r="G16" s="2">
-        <v>26.0</v>
+        <v>26.5</v>
       </c>
       <c r="H16" s="3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="I16" s="4">
-        <v>39.0</v>
+        <v>32.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>59</v>
@@ -1110,7 +1110,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>39.12</v>
+        <v>37.96</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1119,16 +1119,16 @@
         <v>25.19</v>
       </c>
       <c r="F17" s="2">
-        <v>291.5</v>
+        <v>282.9</v>
       </c>
       <c r="G17" s="2">
-        <v>9.3</v>
+        <v>9.0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="I17" s="4">
-        <v>72.0</v>
+        <v>59.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1145,7 +1145,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>26.16</v>
+        <v>26.5</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1154,16 +1154,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>328.1</v>
+        <v>332.4</v>
       </c>
       <c r="G18" s="2">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="H18" s="3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I18" s="4">
-        <v>46.0</v>
+        <v>71.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1177,25 +1177,25 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>38.11</v>
+        <v>43.55</v>
       </c>
       <c r="D19" s="3">
-        <v>41.75</v>
+        <v>44.5</v>
       </c>
       <c r="E19" s="3">
         <v>16.81</v>
       </c>
       <c r="F19" s="2">
-        <v>96.8</v>
+        <v>110.7</v>
       </c>
       <c r="G19" s="2">
-        <v>8.1</v>
+        <v>9.2</v>
       </c>
       <c r="H19" s="3">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="I19" s="4">
-        <v>82.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1206,7 +1206,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>5.6</v>
+        <v>5.51</v>
       </c>
       <c r="D20" s="3">
         <v>5.99</v>
@@ -1215,16 +1215,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>339.3</v>
+        <v>333.9</v>
       </c>
       <c r="G20" s="2">
-        <v>51.9</v>
+        <v>51.0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="I20" s="4">
-        <v>48.0</v>
+        <v>63.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1241,7 +1241,7 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>33.71</v>
+        <v>33.81</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1250,16 +1250,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>377.5</v>
+        <v>378.6</v>
       </c>
       <c r="G21" s="2">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="H21" s="3">
         <v>0.65</v>
       </c>
       <c r="I21" s="4">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1273,7 +1273,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>5.33</v>
+        <v>5.35</v>
       </c>
       <c r="D22" s="3">
         <v>7.5</v>
@@ -1282,16 +1282,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>347.7</v>
+        <v>349.0</v>
       </c>
       <c r="G22" s="2">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="H22" s="3">
         <v>0.84</v>
       </c>
       <c r="I22" s="4">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>75</v>
@@ -1305,7 +1305,7 @@
         <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>20.2</v>
+        <v>21.05</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1314,16 +1314,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>281.6</v>
+        <v>293.4</v>
       </c>
       <c r="G23" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="H23" s="3">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="I23" s="4">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1340,7 +1340,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>22.15</v>
+        <v>24.17</v>
       </c>
       <c r="D24" s="3">
         <v>29.28</v>
@@ -1349,16 +1349,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>54.0</v>
+        <v>58.9</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
       <c r="I24" s="4">
-        <v>41.0</v>
+        <v>72.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1375,7 +1375,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>30.43</v>
+        <v>29.12</v>
       </c>
       <c r="D25" s="3">
         <v>33.04</v>
@@ -1384,16 +1384,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>227.3</v>
+        <v>217.5</v>
       </c>
       <c r="G25" s="2">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="H25" s="3">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="I25" s="4">
-        <v>88.0</v>
+        <v>87.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>84</v>
@@ -1407,7 +1407,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>12.0</v>
+        <v>11.9</v>
       </c>
       <c r="D26" s="3">
         <v>15.1</v>
@@ -1416,16 +1416,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>77.3</v>
+        <v>76.6</v>
       </c>
       <c r="G26" s="2">
-        <v>36.6</v>
+        <v>36.3</v>
       </c>
       <c r="H26" s="3">
         <v>0.47</v>
       </c>
       <c r="I26" s="4">
-        <v>54.0</v>
+        <v>46.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1442,7 +1442,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>19.61</v>
+        <v>21.01</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1451,33 +1451,33 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>176.8</v>
+        <v>189.5</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H27" s="3">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="I27" s="4">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>7.63</v>
+        <v>7.43</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1486,30 +1486,33 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>282.1</v>
+        <v>274.8</v>
       </c>
       <c r="G28" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>20</v>
+        <v>3.9</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.44</v>
       </c>
       <c r="I28" s="4">
-        <v>82.0</v>
+        <v>79.0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>28.42</v>
+        <v>29.67</v>
       </c>
       <c r="D29" s="3">
         <v>30.11</v>
@@ -1518,19 +1521,19 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>377.4</v>
+        <v>394.0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H29" s="3">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="I29" s="4">
-        <v>72.0</v>
+        <v>80.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="f9dwIIPK1x/aH9+hkwciK6U2vPTkRbFPoBlckZdEYfY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="n5Rq3sI0Oxfejbw+WSDye9zCtU+Q7Kk7ZZGNkgfsZF0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
   <si>
     <t>Company</t>
   </si>
@@ -147,7 +147,7 @@
     <t>FONR</t>
   </si>
   <si>
-    <t>News Archive for FONR</t>
+    <t>(9/11/25) FONAR Corporation (FONR)</t>
   </si>
   <si>
     <t>Friedman Industries, Incorporated</t>
@@ -186,7 +186,7 @@
     <t>Earnings probation 2025Q1</t>
   </si>
   <si>
-    <t>News Archive for LAKE</t>
+    <t>(9/9/25) Lakeland Industries, Inc. (LAKE)</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -261,7 +261,7 @@
     <t>RGS</t>
   </si>
   <si>
-    <t>(9/3/25) Regis Corporation (RGS)</t>
+    <t>News Archive for RGS</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -286,9 +286,6 @@
   </si>
   <si>
     <t>SDHC</t>
-  </si>
-  <si>
-    <t>TTM adjusted earnings positive Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for SDHC</t>
@@ -630,13 +627,13 @@
         <v>51.2</v>
       </c>
       <c r="G2" s="2">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H2" s="3">
         <v>0.82</v>
       </c>
       <c r="I2" s="4">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -653,7 +650,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="D3" s="3">
         <v>7.35</v>
@@ -662,16 +659,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>155.4</v>
+        <v>160.2</v>
       </c>
       <c r="G3" s="2">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="H3" s="3">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="I3" s="4">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -685,25 +682,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="D4" s="3">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="E4" s="3">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="F4" s="2">
-        <v>19.0</v>
+        <v>19.2</v>
       </c>
       <c r="G4" s="2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -717,25 +714,25 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>19.79</v>
+        <v>21.22</v>
       </c>
       <c r="D5" s="3">
-        <v>19.79</v>
+        <v>21.42</v>
       </c>
       <c r="E5" s="3">
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>169.4</v>
+        <v>181.7</v>
       </c>
       <c r="G5" s="2">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
       <c r="H5" s="3">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="I5" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -749,7 +746,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>23.93</v>
+        <v>23.04</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -758,16 +755,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>598.7</v>
+        <v>576.5</v>
       </c>
       <c r="G6" s="2">
-        <v>18.3</v>
+        <v>17.6</v>
       </c>
       <c r="H6" s="3">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="I6" s="4">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -781,7 +778,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>7.09</v>
+        <v>7.03</v>
       </c>
       <c r="D7" s="3">
         <v>13.77</v>
@@ -790,16 +787,16 @@
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>145.9</v>
+        <v>144.7</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I7" s="4">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -816,7 +813,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.48</v>
+        <v>17.98</v>
       </c>
       <c r="D8" s="3">
         <v>25.75</v>
@@ -825,16 +822,16 @@
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>476.7</v>
+        <v>463.8</v>
       </c>
       <c r="G8" s="2">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="H8" s="3">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="I8" s="4">
-        <v>23.0</v>
+        <v>18.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -848,7 +845,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>12.86</v>
+        <v>12.4</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -857,16 +854,16 @@
         <v>11.74</v>
       </c>
       <c r="F9" s="2">
-        <v>177.5</v>
+        <v>171.2</v>
       </c>
       <c r="G9" s="2">
-        <v>14.0</v>
+        <v>13.5</v>
       </c>
       <c r="H9" s="3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="I9" s="4">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -880,7 +877,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>61.89</v>
+        <v>63.97</v>
       </c>
       <c r="D10" s="3">
         <v>65.5</v>
@@ -889,13 +886,13 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>433.6</v>
+        <v>448.2</v>
       </c>
       <c r="G10" s="2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H10" s="3">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I10" s="4">
         <v>93.0</v>
@@ -912,7 +909,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>15.6</v>
+        <v>15.69</v>
       </c>
       <c r="D11" s="3">
         <v>17.98</v>
@@ -921,16 +918,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="G11" s="2">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="H11" s="3">
         <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -947,25 +944,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>21.72</v>
+        <v>21.13</v>
       </c>
       <c r="D12" s="3">
-        <v>21.97</v>
+        <v>22.96</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>153.3</v>
+        <v>149.2</v>
       </c>
       <c r="G12" s="2">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="H12" s="3">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="I12" s="4">
-        <v>81.0</v>
+        <v>77.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -979,25 +976,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>9.97</v>
+        <v>10.82</v>
       </c>
       <c r="D13" s="3">
-        <v>10.09</v>
+        <v>11.06</v>
       </c>
       <c r="E13" s="3">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="F13" s="2">
-        <v>568.9</v>
+        <v>617.5</v>
       </c>
       <c r="G13" s="2">
-        <v>25.4</v>
+        <v>27.5</v>
       </c>
       <c r="H13" s="3">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="I13" s="4">
-        <v>82.0</v>
+        <v>86.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>49</v>
@@ -1011,22 +1008,22 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>29.9</v>
+        <v>30.59</v>
       </c>
       <c r="D14" s="3">
-        <v>29.99</v>
+        <v>30.85</v>
       </c>
       <c r="E14" s="3">
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>724.1</v>
+        <v>740.8</v>
       </c>
       <c r="G14" s="2">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="H14" s="3">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="I14" s="4">
         <v>92.0</v>
@@ -1043,7 +1040,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>14.98</v>
+        <v>14.63</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1052,16 +1049,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>142.5</v>
+        <v>140.0</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.99</v>
+        <v>1.9</v>
       </c>
       <c r="I15" s="4">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>55</v>
@@ -1078,7 +1075,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>9.73</v>
+        <v>9.48</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1087,16 +1084,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>306.9</v>
+        <v>299.0</v>
       </c>
       <c r="G16" s="2">
-        <v>26.5</v>
+        <v>25.8</v>
       </c>
       <c r="H16" s="3">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="I16" s="4">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>59</v>
@@ -1110,25 +1107,25 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>37.96</v>
+        <v>39.81</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
       </c>
       <c r="E17" s="3">
-        <v>25.19</v>
+        <v>25.52</v>
       </c>
       <c r="F17" s="2">
-        <v>282.9</v>
+        <v>296.7</v>
       </c>
       <c r="G17" s="2">
-        <v>9.0</v>
+        <v>9.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="I17" s="4">
-        <v>59.0</v>
+        <v>65.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1145,7 +1142,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>26.5</v>
+        <v>26.68</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1154,16 +1151,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>332.4</v>
+        <v>334.6</v>
       </c>
       <c r="G18" s="2">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="H18" s="3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I18" s="4">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1177,25 +1174,25 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>43.55</v>
+        <v>48.23</v>
       </c>
       <c r="D19" s="3">
-        <v>44.5</v>
+        <v>51.49</v>
       </c>
       <c r="E19" s="3">
         <v>16.81</v>
       </c>
       <c r="F19" s="2">
-        <v>110.7</v>
+        <v>122.5</v>
       </c>
       <c r="G19" s="2">
-        <v>9.2</v>
+        <v>10.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="I19" s="4">
-        <v>91.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1206,7 +1203,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>5.51</v>
+        <v>5.62</v>
       </c>
       <c r="D20" s="3">
         <v>5.99</v>
@@ -1215,16 +1212,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>333.9</v>
+        <v>340.5</v>
       </c>
       <c r="G20" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I20" s="4">
-        <v>63.0</v>
+        <v>56.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1241,7 +1238,7 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>33.81</v>
+        <v>32.87</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1250,16 +1247,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>378.6</v>
+        <v>368.1</v>
       </c>
       <c r="G21" s="2">
-        <v>27.6</v>
+        <v>26.8</v>
       </c>
       <c r="H21" s="3">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I21" s="4">
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1273,7 +1270,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="D22" s="3">
         <v>7.5</v>
@@ -1282,16 +1279,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>349.0</v>
+        <v>358.8</v>
       </c>
       <c r="G22" s="2">
-        <v>33.2</v>
+        <v>34.2</v>
       </c>
       <c r="H22" s="3">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="I22" s="4">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>75</v>
@@ -1305,7 +1302,7 @@
         <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>21.05</v>
+        <v>21.45</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1314,16 +1311,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>293.4</v>
+        <v>299.0</v>
       </c>
       <c r="G23" s="2">
-        <v>7.8</v>
+        <v>8.0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="I23" s="4">
-        <v>25.0</v>
+        <v>36.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1340,7 +1337,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>24.17</v>
+        <v>29.05</v>
       </c>
       <c r="D24" s="3">
         <v>29.28</v>
@@ -1349,16 +1346,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>58.9</v>
+        <v>70.8</v>
       </c>
       <c r="G24" s="2">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>72.0</v>
+        <v>89.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1375,7 +1372,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>29.12</v>
+        <v>28.85</v>
       </c>
       <c r="D25" s="3">
         <v>33.04</v>
@@ -1384,16 +1381,19 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>217.5</v>
+        <v>215.5</v>
       </c>
       <c r="G25" s="2">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="H25" s="3">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I25" s="4">
-        <v>87.0</v>
+        <v>86.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>84</v>
@@ -1407,7 +1407,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>11.9</v>
+        <v>12.0</v>
       </c>
       <c r="D26" s="3">
         <v>15.1</v>
@@ -1416,16 +1416,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>76.6</v>
+        <v>77.3</v>
       </c>
       <c r="G26" s="2">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="H26" s="3">
         <v>0.47</v>
       </c>
       <c r="I26" s="4">
-        <v>46.0</v>
+        <v>36.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1442,7 +1442,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>21.01</v>
+        <v>19.29</v>
       </c>
       <c r="D27" s="3">
         <v>39.5</v>
@@ -1451,33 +1451,33 @@
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>189.5</v>
+        <v>173.9</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H27" s="3">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="I27" s="4">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="J27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C28" s="3">
-        <v>7.43</v>
+        <v>7.3</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1486,54 +1486,54 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>274.8</v>
+        <v>269.9</v>
       </c>
       <c r="G28" s="2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H28" s="3">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="I28" s="4">
-        <v>79.0</v>
+        <v>73.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="C29" s="3">
-        <v>29.67</v>
+        <v>31.3</v>
       </c>
       <c r="D29" s="3">
-        <v>30.11</v>
+        <v>31.99</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>394.0</v>
+        <v>415.6</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H29" s="3">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="I29" s="4">
         <v>80.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="n5Rq3sI0Oxfejbw+WSDye9zCtU+Q7Kk7ZZGNkgfsZF0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="GnBfIQfVtyyycSugqp4FcVgVFl3Q83ufXy8BMkt+5+A="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -78,7 +78,7 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>News Archive for CTRM</t>
+    <t>(10/1/25) Castor Maritime Inc. (CTRM)</t>
   </si>
   <si>
     <t>Core Molding Technologies, Inc.</t>
@@ -108,85 +108,88 @@
     <t>nmf</t>
   </si>
   <si>
+    <t>Earnings probation 2025Q2</t>
+  </si>
+  <si>
+    <t>News Archive for BOOM</t>
+  </si>
+  <si>
+    <t>Ennis, Inc.</t>
+  </si>
+  <si>
+    <t>EBF</t>
+  </si>
+  <si>
+    <t>News Archive for EBF</t>
+  </si>
+  <si>
+    <t>Escalade, Incorporated</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>(9/29/25) Escalade, Incorporated (ESCA)</t>
+  </si>
+  <si>
+    <t>Euroseas Ltd.</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>News Archive for ESEA</t>
+  </si>
+  <si>
+    <t>FONAR Corporation</t>
+  </si>
+  <si>
+    <t>FONR</t>
+  </si>
+  <si>
+    <t>News Archive for FONR</t>
+  </si>
+  <si>
+    <t>Friedman Industries, Incorporated</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>News Archive for FRD</t>
+  </si>
+  <si>
+    <t>Gilat Satellite Networks Ltd.</t>
+  </si>
+  <si>
+    <t>GILT</t>
+  </si>
+  <si>
+    <t>Approaching value limit</t>
+  </si>
+  <si>
+    <t>News Archive for GILT</t>
+  </si>
+  <si>
+    <t>Kimball Electronics, Inc.</t>
+  </si>
+  <si>
+    <t>KE</t>
+  </si>
+  <si>
+    <t>News Archive for KE</t>
+  </si>
+  <si>
+    <t>Lakeland Industries, Inc.</t>
+  </si>
+  <si>
+    <t>LAKE</t>
+  </si>
+  <si>
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
-    <t>News Archive for BOOM</t>
-  </si>
-  <si>
-    <t>Ennis, Inc.</t>
-  </si>
-  <si>
-    <t>EBF</t>
-  </si>
-  <si>
-    <t>News Archive for EBF</t>
-  </si>
-  <si>
-    <t>Escalade, Incorporated</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>News Archive for ESCA</t>
-  </si>
-  <si>
-    <t>Euroseas Ltd.</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>News Archive for ESEA</t>
-  </si>
-  <si>
-    <t>FONAR Corporation</t>
-  </si>
-  <si>
-    <t>FONR</t>
-  </si>
-  <si>
-    <t>(9/11/25) FONAR Corporation (FONR)</t>
-  </si>
-  <si>
-    <t>Friedman Industries, Incorporated</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>News Archive for FRD</t>
-  </si>
-  <si>
-    <t>Gilat Satellite Networks Ltd.</t>
-  </si>
-  <si>
-    <t>GILT</t>
-  </si>
-  <si>
-    <t>News Archive for GILT</t>
-  </si>
-  <si>
-    <t>Kimball Electronics, Inc.</t>
-  </si>
-  <si>
-    <t>KE</t>
-  </si>
-  <si>
-    <t>News Archive for KE</t>
-  </si>
-  <si>
-    <t>Lakeland Industries, Inc.</t>
-  </si>
-  <si>
-    <t>LAKE</t>
-  </si>
-  <si>
-    <t>Earnings probation 2025Q1</t>
-  </si>
-  <si>
-    <t>(9/9/25) Lakeland Industries, Inc. (LAKE)</t>
+    <t>News Archive for LAKE</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -615,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.89</v>
+        <v>4.77</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -624,16 +627,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.2</v>
+        <v>49.9</v>
       </c>
       <c r="G2" s="2">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="H2" s="3">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="I2" s="4">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -650,7 +653,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.96</v>
+        <v>5.02</v>
       </c>
       <c r="D3" s="3">
         <v>7.35</v>
@@ -659,16 +662,19 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>160.2</v>
+        <v>196.3</v>
       </c>
       <c r="G3" s="2">
-        <v>10.5</v>
+        <v>12.9</v>
       </c>
       <c r="H3" s="3">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="I3" s="4">
-        <v>43.0</v>
+        <v>72.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -682,25 +688,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="D4" s="3">
-        <v>4.48</v>
+        <v>4.25</v>
       </c>
       <c r="E4" s="3">
         <v>1.91</v>
       </c>
       <c r="F4" s="2">
-        <v>19.2</v>
+        <v>21.0</v>
       </c>
       <c r="G4" s="2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>15.0</v>
+        <v>29.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -714,25 +720,25 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>21.22</v>
+        <v>18.88</v>
       </c>
       <c r="D5" s="3">
-        <v>21.42</v>
+        <v>22.29</v>
       </c>
       <c r="E5" s="3">
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>181.7</v>
+        <v>165.7</v>
       </c>
       <c r="G5" s="2">
-        <v>19.7</v>
+        <v>18.0</v>
       </c>
       <c r="H5" s="3">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="I5" s="4">
-        <v>86.0</v>
+        <v>65.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -746,7 +752,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>23.04</v>
+        <v>21.63</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -755,16 +761,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>576.5</v>
+        <v>525.2</v>
       </c>
       <c r="G6" s="2">
-        <v>17.6</v>
+        <v>16.0</v>
       </c>
       <c r="H6" s="3">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="I6" s="4">
-        <v>36.0</v>
+        <v>25.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -778,7 +784,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>7.03</v>
+        <v>8.11</v>
       </c>
       <c r="D7" s="3">
         <v>13.77</v>
@@ -787,16 +793,16 @@
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>144.7</v>
+        <v>171.6</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="I7" s="4">
-        <v>21.0</v>
+        <v>34.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -813,25 +819,25 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>17.98</v>
+        <v>18.16</v>
       </c>
       <c r="D8" s="3">
-        <v>25.75</v>
+        <v>24.76</v>
       </c>
       <c r="E8" s="3">
         <v>17.15</v>
       </c>
       <c r="F8" s="2">
-        <v>463.8</v>
+        <v>466.6</v>
       </c>
       <c r="G8" s="2">
-        <v>11.9</v>
+        <v>12.0</v>
       </c>
       <c r="H8" s="3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I8" s="4">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -845,7 +851,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>12.4</v>
+        <v>12.73</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -854,7 +860,7 @@
         <v>11.74</v>
       </c>
       <c r="F9" s="2">
-        <v>171.2</v>
+        <v>171.3</v>
       </c>
       <c r="G9" s="2">
         <v>13.5</v>
@@ -863,7 +869,7 @@
         <v>1.02</v>
       </c>
       <c r="I9" s="4">
-        <v>17.0</v>
+        <v>12.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -877,25 +883,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>63.97</v>
+        <v>57.78</v>
       </c>
       <c r="D10" s="3">
-        <v>65.5</v>
+        <v>66.0</v>
       </c>
       <c r="E10" s="3">
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>448.2</v>
+        <v>408.3</v>
       </c>
       <c r="G10" s="2">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H10" s="3">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="I10" s="4">
-        <v>93.0</v>
+        <v>90.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -909,25 +915,25 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>15.69</v>
+        <v>16.08</v>
       </c>
       <c r="D11" s="3">
-        <v>17.98</v>
+        <v>17.62</v>
       </c>
       <c r="E11" s="3">
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>98.8</v>
+        <v>101.2</v>
       </c>
       <c r="G11" s="2">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="H11" s="3">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I11" s="4">
-        <v>55.0</v>
+        <v>62.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -947,22 +953,22 @@
         <v>21.13</v>
       </c>
       <c r="D12" s="3">
-        <v>22.96</v>
+        <v>22.98</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>149.2</v>
+        <v>147.6</v>
       </c>
       <c r="G12" s="2">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="H12" s="3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I12" s="4">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -976,71 +982,74 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>10.82</v>
+        <v>13.47</v>
       </c>
       <c r="D13" s="3">
-        <v>11.06</v>
+        <v>13.99</v>
       </c>
       <c r="E13" s="3">
-        <v>4.45</v>
+        <v>4.83</v>
       </c>
       <c r="F13" s="2">
-        <v>617.5</v>
+        <v>873.2</v>
       </c>
       <c r="G13" s="2">
-        <v>27.5</v>
+        <v>34.6</v>
       </c>
       <c r="H13" s="3">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="I13" s="4">
-        <v>86.0</v>
+        <v>93.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>30.59</v>
+        <v>29.22</v>
       </c>
       <c r="D14" s="3">
-        <v>30.85</v>
+        <v>33.19</v>
       </c>
       <c r="E14" s="3">
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>740.8</v>
+        <v>734.1</v>
       </c>
       <c r="G14" s="2">
-        <v>45.0</v>
+        <v>44.6</v>
       </c>
       <c r="H14" s="3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I14" s="4">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>14.63</v>
+        <v>15.43</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1049,33 +1058,33 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>140.0</v>
+        <v>141.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I15" s="4">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>9.48</v>
+        <v>9.77</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1084,65 +1093,65 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>299.0</v>
+        <v>314.1</v>
       </c>
       <c r="G16" s="2">
-        <v>25.8</v>
+        <v>27.1</v>
       </c>
       <c r="H16" s="3">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="I16" s="4">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>39.81</v>
+        <v>41.67</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
       </c>
       <c r="E17" s="3">
-        <v>25.52</v>
+        <v>26.15</v>
       </c>
       <c r="F17" s="2">
-        <v>296.7</v>
+        <v>308.1</v>
       </c>
       <c r="G17" s="2">
-        <v>9.4</v>
+        <v>9.8</v>
       </c>
       <c r="H17" s="3">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="I17" s="4">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>26.68</v>
+        <v>27.09</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1151,94 +1160,94 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>334.6</v>
+        <v>335.4</v>
       </c>
       <c r="G18" s="2">
         <v>18.8</v>
       </c>
       <c r="H18" s="3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I18" s="4">
-        <v>63.0</v>
+        <v>61.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>48.23</v>
+        <v>42.59</v>
       </c>
       <c r="D19" s="3">
-        <v>51.49</v>
+        <v>53.69</v>
       </c>
       <c r="E19" s="3">
         <v>16.81</v>
       </c>
       <c r="F19" s="2">
-        <v>122.5</v>
+        <v>120.2</v>
       </c>
       <c r="G19" s="2">
-        <v>10.2</v>
+        <v>10.0</v>
       </c>
       <c r="H19" s="3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="I19" s="4">
-        <v>89.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>5.62</v>
+        <v>6.29</v>
       </c>
       <c r="D20" s="3">
-        <v>5.99</v>
+        <v>6.42</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>340.5</v>
+        <v>369.0</v>
       </c>
       <c r="G20" s="2">
-        <v>52.0</v>
+        <v>56.4</v>
       </c>
       <c r="H20" s="3">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="I20" s="4">
-        <v>56.0</v>
+        <v>59.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>32.87</v>
+        <v>30.77</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1247,16 +1256,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>368.1</v>
+        <v>339.3</v>
       </c>
       <c r="G21" s="2">
-        <v>26.8</v>
+        <v>24.7</v>
       </c>
       <c r="H21" s="3">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="I21" s="4">
-        <v>42.0</v>
+        <v>31.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1264,45 +1273,45 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>5.5</v>
+        <v>5.09</v>
       </c>
       <c r="D22" s="3">
-        <v>7.5</v>
+        <v>7.09</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>358.8</v>
+        <v>329.5</v>
       </c>
       <c r="G22" s="2">
-        <v>34.2</v>
+        <v>31.4</v>
       </c>
       <c r="H22" s="3">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="I22" s="4">
-        <v>55.0</v>
+        <v>43.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>21.45</v>
+        <v>20.88</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1311,103 +1320,100 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>299.0</v>
+        <v>292.6</v>
       </c>
       <c r="G23" s="2">
-        <v>8.0</v>
+        <v>7.8</v>
       </c>
       <c r="H23" s="3">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="I23" s="4">
-        <v>36.0</v>
+        <v>30.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>29.05</v>
+        <v>29.58</v>
       </c>
       <c r="D24" s="3">
-        <v>29.28</v>
+        <v>30.29</v>
       </c>
       <c r="E24" s="3">
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>70.8</v>
+        <v>71.7</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="I24" s="4">
-        <v>89.0</v>
+        <v>83.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>28.85</v>
+        <v>30.48</v>
       </c>
       <c r="D25" s="3">
-        <v>33.04</v>
+        <v>31.42</v>
       </c>
       <c r="E25" s="3">
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>215.5</v>
+        <v>228.0</v>
       </c>
       <c r="G25" s="2">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="H25" s="3">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I25" s="4">
         <v>86.0</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="K25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>12.0</v>
+        <v>12.98</v>
       </c>
       <c r="D26" s="3">
         <v>15.1</v>
@@ -1416,68 +1422,68 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>77.3</v>
+        <v>81.5</v>
       </c>
       <c r="G26" s="2">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="H26" s="3">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="I26" s="4">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>19.29</v>
+        <v>17.58</v>
       </c>
       <c r="D27" s="3">
-        <v>39.5</v>
+        <v>39.46</v>
       </c>
       <c r="E27" s="3">
         <v>16.28</v>
       </c>
       <c r="F27" s="2">
-        <v>173.9</v>
+        <v>162.8</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H27" s="3">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="I27" s="4">
-        <v>36.0</v>
+        <v>28.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>7.3</v>
+        <v>6.49</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1486,54 +1492,57 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>269.9</v>
+        <v>238.5</v>
       </c>
       <c r="G28" s="2">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H28" s="3">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="I28" s="4">
-        <v>73.0</v>
+        <v>51.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>31.3</v>
+        <v>32.4</v>
       </c>
       <c r="D29" s="3">
-        <v>31.99</v>
+        <v>33.81</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>415.6</v>
+        <v>431.3</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H29" s="3">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="I29" s="4">
-        <v>80.0</v>
+        <v>57.0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="GnBfIQfVtyyycSugqp4FcVgVFl3Q83ufXy8BMkt+5+A="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="cfqPkrsokf+cg8h+jSJ7xOuybmABKwQ21onsIeKsQCg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -78,7 +78,10 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>(10/1/25) Castor Maritime Inc. (CTRM)</t>
+    <t>nmf</t>
+  </si>
+  <si>
+    <t>News Archive for CTRM</t>
   </si>
   <si>
     <t>Core Molding Technologies, Inc.</t>
@@ -105,9 +108,6 @@
     <t>BOOM</t>
   </si>
   <si>
-    <t>nmf</t>
-  </si>
-  <si>
     <t>Earnings probation 2025Q2</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(9/29/25) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -618,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -627,16 +627,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="G2" s="2">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I2" s="4">
-        <v>33.0</v>
+        <v>46.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -653,25 +653,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.02</v>
+        <v>4.7</v>
       </c>
       <c r="D3" s="3">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>196.3</v>
+        <v>190.2</v>
       </c>
       <c r="G3" s="2">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="H3" s="3">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I3" s="4">
-        <v>72.0</v>
+        <v>88.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -688,39 +688,39 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="D4" s="3">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="E4" s="3">
         <v>1.91</v>
       </c>
       <c r="F4" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>5.8</v>
+        <v>20.1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>18.88</v>
+        <v>18.05</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -729,30 +729,30 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>165.7</v>
+        <v>154.5</v>
       </c>
       <c r="G5" s="2">
-        <v>18.0</v>
+        <v>16.8</v>
       </c>
       <c r="H5" s="3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="I5" s="4">
-        <v>65.0</v>
+        <v>57.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>21.63</v>
+        <v>20.54</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -761,48 +761,48 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>525.2</v>
+        <v>513.9</v>
       </c>
       <c r="G6" s="2">
-        <v>16.0</v>
+        <v>15.7</v>
       </c>
       <c r="H6" s="3">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="I6" s="4">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>8.11</v>
+        <v>7.09</v>
       </c>
       <c r="D7" s="3">
-        <v>13.77</v>
+        <v>13.6</v>
       </c>
       <c r="E7" s="3">
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>171.6</v>
+        <v>145.9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="I7" s="4">
-        <v>34.0</v>
+        <v>41.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -819,25 +819,25 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.16</v>
+        <v>17.02</v>
       </c>
       <c r="D8" s="3">
-        <v>24.76</v>
+        <v>22.29</v>
       </c>
       <c r="E8" s="3">
-        <v>17.15</v>
+        <v>17.01</v>
       </c>
       <c r="F8" s="2">
-        <v>466.6</v>
+        <v>436.2</v>
       </c>
       <c r="G8" s="2">
-        <v>12.0</v>
+        <v>10.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="I8" s="4">
-        <v>23.0</v>
+        <v>18.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -851,25 +851,25 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>12.73</v>
+        <v>11.55</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
       </c>
       <c r="E9" s="3">
-        <v>11.74</v>
+        <v>11.55</v>
       </c>
       <c r="F9" s="2">
-        <v>171.3</v>
+        <v>159.4</v>
       </c>
       <c r="G9" s="2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="H9" s="3">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="I9" s="4">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -883,7 +883,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>57.78</v>
+        <v>53.4</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -892,16 +892,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>408.3</v>
+        <v>374.2</v>
       </c>
       <c r="G10" s="2">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.09</v>
+        <v>1.0</v>
       </c>
       <c r="I10" s="4">
-        <v>90.0</v>
+        <v>87.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -915,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>16.08</v>
+        <v>15.62</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -924,16 +924,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>101.2</v>
+        <v>98.3</v>
       </c>
       <c r="G11" s="2">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="H11" s="3">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>62.0</v>
+        <v>61.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -950,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>21.13</v>
+        <v>19.83</v>
       </c>
       <c r="D12" s="3">
         <v>22.98</v>
@@ -959,16 +959,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>147.6</v>
+        <v>140.0</v>
       </c>
       <c r="G12" s="2">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="H12" s="3">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="I12" s="4">
-        <v>78.0</v>
+        <v>65.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,16 +982,16 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>13.47</v>
+        <v>13.6</v>
       </c>
       <c r="D13" s="3">
-        <v>13.99</v>
+        <v>14.65</v>
       </c>
       <c r="E13" s="3">
         <v>4.83</v>
       </c>
       <c r="F13" s="2">
-        <v>873.2</v>
+        <v>873.9</v>
       </c>
       <c r="G13" s="2">
         <v>34.6</v>
@@ -1000,7 +1000,7 @@
         <v>2.46</v>
       </c>
       <c r="I13" s="4">
-        <v>93.0</v>
+        <v>92.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1017,7 +1017,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>29.22</v>
+        <v>27.46</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1026,13 +1026,13 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>734.1</v>
+        <v>665.0</v>
       </c>
       <c r="G14" s="2">
-        <v>44.6</v>
+        <v>40.4</v>
       </c>
       <c r="H14" s="3">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="I14" s="4">
         <v>90.0</v>
@@ -1049,7 +1049,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>15.43</v>
+        <v>16.88</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1058,16 +1058,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>141.5</v>
+        <v>161.5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H15" s="3">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="I15" s="4">
-        <v>10.0</v>
+        <v>38.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1084,7 +1084,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>9.77</v>
+        <v>9.39</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1093,13 +1093,13 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>314.1</v>
+        <v>296.1</v>
       </c>
       <c r="G16" s="2">
-        <v>27.1</v>
+        <v>25.6</v>
       </c>
       <c r="H16" s="3">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="I16" s="4">
         <v>31.0</v>
@@ -1116,25 +1116,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>41.67</v>
+        <v>39.89</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
       </c>
       <c r="E17" s="3">
-        <v>26.15</v>
+        <v>26.31</v>
       </c>
       <c r="F17" s="2">
-        <v>308.1</v>
+        <v>297.2</v>
       </c>
       <c r="G17" s="2">
-        <v>9.8</v>
+        <v>9.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="I17" s="4">
-        <v>66.0</v>
+        <v>40.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1151,7 +1151,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>27.09</v>
+        <v>25.68</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1160,16 +1160,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>335.4</v>
+        <v>322.1</v>
       </c>
       <c r="G18" s="2">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="H18" s="3">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="I18" s="4">
-        <v>61.0</v>
+        <v>72.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1183,7 +1183,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>42.59</v>
+        <v>41.79</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1192,16 +1192,16 @@
         <v>16.81</v>
       </c>
       <c r="F19" s="2">
-        <v>120.2</v>
+        <v>106.2</v>
       </c>
       <c r="G19" s="2">
-        <v>10.0</v>
+        <v>8.9</v>
       </c>
       <c r="H19" s="3">
-        <v>1.13</v>
+        <v>1.0</v>
       </c>
       <c r="I19" s="4">
-        <v>72.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1212,25 +1212,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>6.29</v>
+        <v>5.58</v>
       </c>
       <c r="D20" s="3">
-        <v>6.42</v>
+        <v>6.47</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>369.0</v>
+        <v>338.1</v>
       </c>
       <c r="G20" s="2">
-        <v>56.4</v>
+        <v>51.7</v>
       </c>
       <c r="H20" s="3">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="I20" s="4">
-        <v>59.0</v>
+        <v>82.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1247,7 +1247,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>30.77</v>
+        <v>27.2</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1256,16 +1256,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>339.3</v>
+        <v>304.6</v>
       </c>
       <c r="G21" s="2">
-        <v>24.7</v>
+        <v>22.2</v>
       </c>
       <c r="H21" s="3">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="I21" s="4">
-        <v>31.0</v>
+        <v>20.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1279,25 +1279,25 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>5.09</v>
+        <v>4.56</v>
       </c>
       <c r="D22" s="3">
-        <v>7.09</v>
+        <v>6.8</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>329.5</v>
+        <v>297.5</v>
       </c>
       <c r="G22" s="2">
-        <v>31.4</v>
+        <v>28.3</v>
       </c>
       <c r="H22" s="3">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="I22" s="4">
-        <v>43.0</v>
+        <v>39.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1311,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>20.88</v>
+        <v>19.34</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1320,16 +1320,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>292.6</v>
+        <v>269.6</v>
       </c>
       <c r="G23" s="2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H23" s="3">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="I23" s="4">
-        <v>30.0</v>
+        <v>29.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1346,25 +1346,25 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>29.58</v>
+        <v>29.26</v>
       </c>
       <c r="D24" s="3">
-        <v>30.29</v>
+        <v>30.93</v>
       </c>
       <c r="E24" s="3">
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>71.7</v>
+        <v>71.3</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1381,25 +1381,28 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>30.48</v>
+        <v>26.58</v>
       </c>
       <c r="D25" s="3">
-        <v>31.42</v>
+        <v>31.38</v>
       </c>
       <c r="E25" s="3">
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>228.0</v>
+        <v>198.5</v>
       </c>
       <c r="G25" s="2">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="H25" s="3">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="I25" s="4">
-        <v>86.0</v>
+        <v>89.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>85</v>
@@ -1413,7 +1416,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>12.98</v>
+        <v>12.5</v>
       </c>
       <c r="D26" s="3">
         <v>15.1</v>
@@ -1422,16 +1425,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>81.5</v>
+        <v>80.5</v>
       </c>
       <c r="G26" s="2">
-        <v>38.6</v>
+        <v>38.1</v>
       </c>
       <c r="H26" s="3">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I26" s="4">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1448,25 +1451,25 @@
         <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>17.58</v>
+        <v>15.44</v>
       </c>
       <c r="D27" s="3">
-        <v>39.46</v>
+        <v>38.06</v>
       </c>
       <c r="E27" s="3">
-        <v>16.28</v>
+        <v>15.19</v>
       </c>
       <c r="F27" s="2">
-        <v>162.8</v>
+        <v>139.2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H27" s="3">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="I27" s="4">
-        <v>28.0</v>
+        <v>14.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>56</v>
@@ -1483,7 +1486,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>6.49</v>
+        <v>6.26</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1492,16 +1495,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>238.5</v>
+        <v>231.5</v>
       </c>
       <c r="G28" s="2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H28" s="3">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I28" s="4">
-        <v>51.0</v>
+        <v>59.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1518,7 +1521,7 @@
         <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>32.4</v>
+        <v>30.75</v>
       </c>
       <c r="D29" s="3">
         <v>33.81</v>
@@ -1527,16 +1530,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>431.3</v>
+        <v>408.3</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H29" s="3">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="I29" s="4">
-        <v>57.0</v>
+        <v>78.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>56</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="cfqPkrsokf+cg8h+jSJ7xOuybmABKwQ21onsIeKsQCg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OmVZNIin38Hhf1Bb8g9nnVOSFKIClwxtYKmS9KMVDUM="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -81,6 +81,9 @@
     <t>nmf</t>
   </si>
   <si>
+    <t>TTM adjusted earnings positive</t>
+  </si>
+  <si>
     <t>News Archive for CTRM</t>
   </si>
   <si>
@@ -184,9 +187,6 @@
   </si>
   <si>
     <t>LAKE</t>
-  </si>
-  <si>
-    <t>TTM adjusted earnings positive</t>
   </si>
   <si>
     <t>News Archive for LAKE</t>
@@ -618,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -627,16 +627,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>49.2</v>
+        <v>48.2</v>
       </c>
       <c r="G2" s="2">
-        <v>14.3</v>
+        <v>14.0</v>
       </c>
       <c r="H2" s="3">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="I2" s="4">
-        <v>46.0</v>
+        <v>41.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -653,7 +653,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="D3" s="3">
         <v>7.23</v>
@@ -662,16 +662,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>190.2</v>
+        <v>186.5</v>
       </c>
       <c r="G3" s="2">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I3" s="4">
-        <v>88.0</v>
+        <v>86.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -688,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="D4" s="3">
         <v>4.19</v>
@@ -697,7 +697,7 @@
         <v>1.91</v>
       </c>
       <c r="F4" s="2">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -708,19 +708,22 @@
       <c r="I4" s="4">
         <v>28.0</v>
       </c>
+      <c r="J4" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="K4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.05</v>
+        <v>18.49</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -729,30 +732,30 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>154.5</v>
+        <v>159.3</v>
       </c>
       <c r="G5" s="2">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I5" s="4">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>20.54</v>
+        <v>21.43</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -761,65 +764,65 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>513.9</v>
+        <v>542.7</v>
       </c>
       <c r="G6" s="2">
-        <v>15.7</v>
+        <v>16.6</v>
       </c>
       <c r="H6" s="3">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="I6" s="4">
-        <v>35.0</v>
+        <v>58.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>7.09</v>
+        <v>7.25</v>
       </c>
       <c r="D7" s="3">
-        <v>13.6</v>
+        <v>13.31</v>
       </c>
       <c r="E7" s="3">
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>145.9</v>
+        <v>155.4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="I7" s="4">
-        <v>41.0</v>
+        <v>56.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>17.02</v>
+        <v>17.2</v>
       </c>
       <c r="D8" s="3">
         <v>22.29</v>
@@ -828,30 +831,30 @@
         <v>17.01</v>
       </c>
       <c r="F8" s="2">
-        <v>436.2</v>
+        <v>446.5</v>
       </c>
       <c r="G8" s="2">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H8" s="3">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="I8" s="4">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>11.55</v>
+        <v>11.82</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -860,30 +863,30 @@
         <v>11.55</v>
       </c>
       <c r="F9" s="2">
-        <v>159.4</v>
+        <v>163.2</v>
       </c>
       <c r="G9" s="2">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="H9" s="3">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="I9" s="4">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>53.4</v>
+        <v>55.52</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -892,30 +895,30 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>374.2</v>
+        <v>389.2</v>
       </c>
       <c r="G10" s="2">
-        <v>2.9</v>
+        <v>3.0</v>
       </c>
       <c r="H10" s="3">
-        <v>1.0</v>
+        <v>1.04</v>
       </c>
       <c r="I10" s="4">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>15.62</v>
+        <v>15.5</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -924,7 +927,7 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>98.3</v>
+        <v>98.4</v>
       </c>
       <c r="G11" s="2">
         <v>12.4</v>
@@ -933,24 +936,24 @@
         <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>61.0</v>
+        <v>64.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>19.83</v>
+        <v>19.64</v>
       </c>
       <c r="D12" s="3">
         <v>22.98</v>
@@ -959,65 +962,65 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>140.0</v>
+        <v>142.2</v>
       </c>
       <c r="G12" s="2">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="H12" s="3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I12" s="4">
-        <v>65.0</v>
+        <v>55.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>13.6</v>
+        <v>13.71</v>
       </c>
       <c r="D13" s="3">
-        <v>14.65</v>
+        <v>14.95</v>
       </c>
       <c r="E13" s="3">
         <v>4.83</v>
       </c>
       <c r="F13" s="2">
-        <v>873.9</v>
+        <v>889.3</v>
       </c>
       <c r="G13" s="2">
-        <v>34.6</v>
+        <v>35.2</v>
       </c>
       <c r="H13" s="3">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="I13" s="4">
         <v>92.0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>27.46</v>
+        <v>28.31</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1026,30 +1029,30 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>665.0</v>
+        <v>713.8</v>
       </c>
       <c r="G14" s="2">
-        <v>40.4</v>
+        <v>43.0</v>
       </c>
       <c r="H14" s="3">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="I14" s="4">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>16.88</v>
+        <v>15.95</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1058,19 +1061,19 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>161.5</v>
+        <v>153.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="3">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="I15" s="4">
-        <v>38.0</v>
+        <v>31.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>57</v>
@@ -1084,7 +1087,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>9.39</v>
+        <v>9.5</v>
       </c>
       <c r="D16" s="3">
         <v>12.44</v>
@@ -1093,16 +1096,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>296.1</v>
+        <v>305.0</v>
       </c>
       <c r="G16" s="2">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="H16" s="3">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="I16" s="4">
-        <v>31.0</v>
+        <v>36.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1116,25 +1119,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>39.89</v>
+        <v>44.75</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
       </c>
       <c r="E17" s="3">
-        <v>26.31</v>
+        <v>26.8</v>
       </c>
       <c r="F17" s="2">
-        <v>297.2</v>
+        <v>331.2</v>
       </c>
       <c r="G17" s="2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H17" s="3">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="I17" s="4">
-        <v>40.0</v>
+        <v>53.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1151,7 +1154,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>25.68</v>
+        <v>25.85</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1160,16 +1163,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>322.1</v>
+        <v>327.2</v>
       </c>
       <c r="G18" s="2">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="H18" s="3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I18" s="4">
-        <v>72.0</v>
+        <v>68.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1183,25 +1186,25 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>41.79</v>
+        <v>36.43</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
       </c>
       <c r="E19" s="3">
-        <v>16.81</v>
+        <v>17.3</v>
       </c>
       <c r="F19" s="2">
-        <v>106.2</v>
+        <v>97.8</v>
       </c>
       <c r="G19" s="2">
-        <v>8.9</v>
+        <v>8.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.0</v>
+        <v>0.92</v>
       </c>
       <c r="I19" s="4">
-        <v>79.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1212,7 +1215,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>5.58</v>
+        <v>5.82</v>
       </c>
       <c r="D20" s="3">
         <v>6.47</v>
@@ -1221,16 +1224,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>338.1</v>
+        <v>360.5</v>
       </c>
       <c r="G20" s="2">
-        <v>51.7</v>
+        <v>55.1</v>
       </c>
       <c r="H20" s="3">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="I20" s="4">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1247,7 +1250,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>27.2</v>
+        <v>27.52</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1256,10 +1259,10 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>304.6</v>
+        <v>308.4</v>
       </c>
       <c r="G21" s="2">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="H21" s="3">
         <v>0.53</v>
@@ -1279,7 +1282,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>4.56</v>
+        <v>4.81</v>
       </c>
       <c r="D22" s="3">
         <v>6.8</v>
@@ -1288,16 +1291,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>297.5</v>
+        <v>321.0</v>
       </c>
       <c r="G22" s="2">
-        <v>28.3</v>
+        <v>30.6</v>
       </c>
       <c r="H22" s="3">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="I22" s="4">
-        <v>39.0</v>
+        <v>52.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1311,7 +1314,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>19.34</v>
+        <v>20.21</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1320,16 +1323,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>269.6</v>
+        <v>283.3</v>
       </c>
       <c r="G23" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="H23" s="3">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="I23" s="4">
-        <v>29.0</v>
+        <v>45.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1346,25 +1349,25 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>29.26</v>
+        <v>30.29</v>
       </c>
       <c r="D24" s="3">
-        <v>30.93</v>
+        <v>31.5</v>
       </c>
       <c r="E24" s="3">
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>71.3</v>
+        <v>74.2</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="I24" s="4">
-        <v>85.0</v>
+        <v>84.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1381,7 +1384,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>26.58</v>
+        <v>27.06</v>
       </c>
       <c r="D25" s="3">
         <v>31.38</v>
@@ -1390,16 +1393,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>198.5</v>
+        <v>201.4</v>
       </c>
       <c r="G25" s="2">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="H25" s="3">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I25" s="4">
-        <v>89.0</v>
+        <v>91.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>13</v>
@@ -1416,7 +1419,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>12.5</v>
+        <v>12.34</v>
       </c>
       <c r="D26" s="3">
         <v>15.1</v>
@@ -1425,7 +1428,7 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>80.5</v>
+        <v>80.4</v>
       </c>
       <c r="G26" s="2">
         <v>38.1</v>
@@ -1434,7 +1437,7 @@
         <v>0.49</v>
       </c>
       <c r="I26" s="4">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1451,28 +1454,28 @@
         <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>15.44</v>
+        <v>16.45</v>
       </c>
       <c r="D27" s="3">
-        <v>38.06</v>
+        <v>37.9</v>
       </c>
       <c r="E27" s="3">
-        <v>15.19</v>
+        <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>139.2</v>
+        <v>143.7</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="3">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="I27" s="4">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>91</v>
@@ -1486,7 +1489,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>6.26</v>
+        <v>6.34</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1495,16 +1498,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>231.5</v>
+        <v>235.2</v>
       </c>
       <c r="G28" s="2">
         <v>3.3</v>
       </c>
       <c r="H28" s="3">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I28" s="4">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1521,28 +1524,28 @@
         <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>30.75</v>
+        <v>34.37</v>
       </c>
       <c r="D29" s="3">
-        <v>33.81</v>
+        <v>38.02</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>408.3</v>
+        <v>484.8</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="3">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="I29" s="4">
-        <v>78.0</v>
+        <v>85.0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>97</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OmVZNIin38Hhf1Bb8g9nnVOSFKIClwxtYKmS9KMVDUM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="CKRlpdPmlmk6mokoPUn6yvS4GrS+U4kYhBelD1oiVY8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -102,7 +102,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>News Archive for CVLG</t>
+    <t>(10/22/25) Covenant Logistics Group, Inc. (CVLG)</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -618,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -627,16 +627,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="G2" s="2">
-        <v>14.0</v>
+        <v>14.1</v>
       </c>
       <c r="H2" s="3">
         <v>0.77</v>
       </c>
       <c r="I2" s="4">
-        <v>41.0</v>
+        <v>38.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -653,7 +653,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.2</v>
+        <v>4.76</v>
       </c>
       <c r="D3" s="3">
         <v>7.23</v>
@@ -662,16 +662,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>186.5</v>
+        <v>192.2</v>
       </c>
       <c r="G3" s="2">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="H3" s="3">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="I3" s="4">
-        <v>86.0</v>
+        <v>89.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -688,16 +688,16 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="D4" s="3">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="E4" s="3">
         <v>1.91</v>
       </c>
       <c r="F4" s="2">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -723,7 +723,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.49</v>
+        <v>19.11</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -732,16 +732,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>159.3</v>
+        <v>164.1</v>
       </c>
       <c r="G5" s="2">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="H5" s="3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I5" s="4">
-        <v>59.0</v>
+        <v>65.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -755,7 +755,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>21.43</v>
+        <v>20.03</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -764,16 +764,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>542.7</v>
+        <v>499.4</v>
       </c>
       <c r="G6" s="2">
-        <v>16.6</v>
+        <v>15.2</v>
       </c>
       <c r="H6" s="3">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I6" s="4">
-        <v>58.0</v>
+        <v>28.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -787,25 +787,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>7.25</v>
+        <v>8.42</v>
       </c>
       <c r="D7" s="3">
-        <v>13.31</v>
+        <v>10.43</v>
       </c>
       <c r="E7" s="3">
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>155.4</v>
+        <v>168.4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="I7" s="4">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -822,25 +822,25 @@
         <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>17.2</v>
+        <v>16.95</v>
       </c>
       <c r="D8" s="3">
         <v>22.29</v>
       </c>
       <c r="E8" s="3">
-        <v>17.01</v>
+        <v>16.83</v>
       </c>
       <c r="F8" s="2">
-        <v>446.5</v>
+        <v>434.9</v>
       </c>
       <c r="G8" s="2">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="I8" s="4">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
@@ -854,7 +854,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>11.82</v>
+        <v>11.94</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -863,16 +863,16 @@
         <v>11.55</v>
       </c>
       <c r="F9" s="2">
-        <v>163.2</v>
+        <v>164.0</v>
       </c>
       <c r="G9" s="2">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H9" s="3">
         <v>0.97</v>
       </c>
       <c r="I9" s="4">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -886,7 +886,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>55.52</v>
+        <v>55.47</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -895,7 +895,7 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>389.2</v>
+        <v>390.3</v>
       </c>
       <c r="G10" s="2">
         <v>3.0</v>
@@ -918,7 +918,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>15.5</v>
+        <v>15.46</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -927,16 +927,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>98.4</v>
+        <v>97.0</v>
       </c>
       <c r="G11" s="2">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H11" s="3">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="I11" s="4">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -953,7 +953,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>19.64</v>
+        <v>21.24</v>
       </c>
       <c r="D12" s="3">
         <v>22.98</v>
@@ -962,16 +962,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>142.2</v>
+        <v>140.7</v>
       </c>
       <c r="G12" s="2">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="H12" s="3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I12" s="4">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -985,7 +985,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>13.71</v>
+        <v>14.86</v>
       </c>
       <c r="D13" s="3">
         <v>14.95</v>
@@ -994,16 +994,16 @@
         <v>4.83</v>
       </c>
       <c r="F13" s="2">
-        <v>889.3</v>
+        <v>921.4</v>
       </c>
       <c r="G13" s="2">
-        <v>35.2</v>
+        <v>36.5</v>
       </c>
       <c r="H13" s="3">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="I13" s="4">
-        <v>92.0</v>
+        <v>94.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>50</v>
@@ -1020,7 +1020,7 @@
         <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>28.31</v>
+        <v>29.7</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1029,13 +1029,13 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>713.8</v>
+        <v>733.3</v>
       </c>
       <c r="G14" s="2">
-        <v>43.0</v>
+        <v>44.2</v>
       </c>
       <c r="H14" s="3">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="I14" s="4">
         <v>92.0</v>
@@ -1052,7 +1052,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>15.95</v>
+        <v>16.8</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1061,13 +1061,13 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>153.5</v>
+        <v>157.0</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="3">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="I15" s="4">
         <v>31.0</v>
@@ -1087,25 +1087,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>9.5</v>
+        <v>10.03</v>
       </c>
       <c r="D16" s="3">
-        <v>12.44</v>
+        <v>11.45</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>305.0</v>
+        <v>312.9</v>
       </c>
       <c r="G16" s="2">
-        <v>26.3</v>
+        <v>27.0</v>
       </c>
       <c r="H16" s="3">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="I16" s="4">
-        <v>36.0</v>
+        <v>43.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1119,7 +1119,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>44.75</v>
+        <v>43.93</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1128,16 +1128,16 @@
         <v>26.8</v>
       </c>
       <c r="F17" s="2">
-        <v>331.2</v>
+        <v>328.0</v>
       </c>
       <c r="G17" s="2">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I17" s="4">
-        <v>53.0</v>
+        <v>62.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1154,7 +1154,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>25.85</v>
+        <v>27.71</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1163,16 +1163,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>327.2</v>
+        <v>351.2</v>
       </c>
       <c r="G18" s="2">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
       <c r="H18" s="3">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="I18" s="4">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1186,7 +1186,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>36.43</v>
+        <v>41.58</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1195,16 +1195,16 @@
         <v>17.3</v>
       </c>
       <c r="F19" s="2">
-        <v>97.8</v>
+        <v>104.3</v>
       </c>
       <c r="G19" s="2">
-        <v>8.2</v>
+        <v>8.7</v>
       </c>
       <c r="H19" s="3">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="I19" s="4">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1215,28 +1215,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>5.82</v>
+        <v>6.65</v>
       </c>
       <c r="D20" s="3">
-        <v>6.47</v>
+        <v>6.75</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>360.5</v>
+        <v>407.8</v>
       </c>
       <c r="G20" s="2">
-        <v>55.1</v>
+        <v>62.3</v>
       </c>
       <c r="H20" s="3">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="I20" s="4">
-        <v>84.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>90.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1250,7 +1247,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>27.52</v>
+        <v>29.35</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1259,16 +1256,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>308.4</v>
+        <v>328.9</v>
       </c>
       <c r="G21" s="2">
-        <v>22.4</v>
+        <v>23.9</v>
       </c>
       <c r="H21" s="3">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="I21" s="4">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -1282,7 +1279,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>4.81</v>
+        <v>4.83</v>
       </c>
       <c r="D22" s="3">
         <v>6.8</v>
@@ -1291,16 +1288,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>321.0</v>
+        <v>314.5</v>
       </c>
       <c r="G22" s="2">
-        <v>30.6</v>
+        <v>29.9</v>
       </c>
       <c r="H22" s="3">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="I22" s="4">
-        <v>52.0</v>
+        <v>51.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1314,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>20.21</v>
+        <v>20.51</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1323,16 +1320,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>283.3</v>
+        <v>290.9</v>
       </c>
       <c r="G23" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H23" s="3">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="I23" s="4">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1349,7 +1346,7 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>30.29</v>
+        <v>30.46</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1358,16 +1355,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>74.2</v>
+        <v>72.0</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I24" s="4">
-        <v>84.0</v>
+        <v>82.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1384,7 +1381,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>27.06</v>
+        <v>29.92</v>
       </c>
       <c r="D25" s="3">
         <v>31.38</v>
@@ -1393,19 +1390,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>201.4</v>
+        <v>219.8</v>
       </c>
       <c r="G25" s="2">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="H25" s="3">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="I25" s="4">
-        <v>91.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>13</v>
+        <v>93.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>85</v>
@@ -1419,7 +1413,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>12.34</v>
+        <v>12.45</v>
       </c>
       <c r="D26" s="3">
         <v>15.1</v>
@@ -1428,16 +1422,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>80.4</v>
+        <v>80.8</v>
       </c>
       <c r="G26" s="2">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="H26" s="3">
         <v>0.49</v>
       </c>
       <c r="I26" s="4">
-        <v>46.0</v>
+        <v>44.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1454,7 +1448,7 @@
         <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>16.45</v>
+        <v>17.74</v>
       </c>
       <c r="D27" s="3">
         <v>37.9</v>
@@ -1463,13 +1457,13 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>143.7</v>
+        <v>157.2</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="3">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="I27" s="4">
         <v>18.0</v>
@@ -1489,7 +1483,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>6.34</v>
+        <v>6.48</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1498,16 +1492,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>235.2</v>
+        <v>244.1</v>
       </c>
       <c r="G28" s="2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H28" s="3">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="I28" s="4">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1524,7 +1518,7 @@
         <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>34.37</v>
+        <v>36.49</v>
       </c>
       <c r="D29" s="3">
         <v>38.02</v>
@@ -1533,16 +1527,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>484.8</v>
+        <v>493.5</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="3">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="I29" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>21</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="CKRlpdPmlmk6mokoPUn6yvS4GrS+U4kYhBelD1oiVY8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="3Ar3KpUvinJZ34BsAWomhz6NeE+ge2Uv6hp2sCrpzaw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -102,7 +102,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>(10/22/25) Covenant Logistics Group, Inc. (CVLG)</t>
+    <t>News Archive for CVLG</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -132,7 +132,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>News Archive for ESCA</t>
+    <t>(10/30/25) Escalade, Incorporated (ESCA)</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -240,6 +240,9 @@
     <t>ZEUS</t>
   </si>
   <si>
+    <t>(10/28/25) Olympic Steel, Inc. (ZEUS)</t>
+  </si>
+  <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
   </si>
   <si>
@@ -273,7 +276,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>News Archive for RCKY</t>
+    <t>(10/28/25) Rocky Brands, Inc. (RCKY)</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -618,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -627,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.5</v>
+        <v>47.7</v>
       </c>
       <c r="G2" s="2">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="H2" s="3">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="I2" s="4">
-        <v>38.0</v>
+        <v>43.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -653,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.76</v>
+        <v>4.54</v>
       </c>
       <c r="D3" s="3">
         <v>7.23</v>
@@ -662,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>192.2</v>
+        <v>183.7</v>
       </c>
       <c r="G3" s="2">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="H3" s="3">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="I3" s="4">
-        <v>89.0</v>
+        <v>86.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -688,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="D4" s="3">
         <v>4.18</v>
@@ -697,7 +700,7 @@
         <v>1.91</v>
       </c>
       <c r="F4" s="2">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -706,7 +709,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>21</v>
@@ -723,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>19.11</v>
+        <v>17.91</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -732,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>164.1</v>
+        <v>153.3</v>
       </c>
       <c r="G5" s="2">
-        <v>17.8</v>
+        <v>16.6</v>
       </c>
       <c r="H5" s="3">
-        <v>1.07</v>
+        <v>1.0</v>
       </c>
       <c r="I5" s="4">
-        <v>65.0</v>
+        <v>58.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -755,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>20.03</v>
+        <v>20.17</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -764,16 +767,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>499.4</v>
+        <v>504.6</v>
       </c>
       <c r="G6" s="2">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="H6" s="3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I6" s="4">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -787,25 +790,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.42</v>
+        <v>8.06</v>
       </c>
       <c r="D7" s="3">
-        <v>10.43</v>
+        <v>10.14</v>
       </c>
       <c r="E7" s="3">
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>168.4</v>
+        <v>165.9</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I7" s="4">
-        <v>63.0</v>
+        <v>51.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -822,25 +825,25 @@
         <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>16.95</v>
+        <v>16.4</v>
       </c>
       <c r="D8" s="3">
         <v>22.29</v>
       </c>
       <c r="E8" s="3">
-        <v>16.83</v>
+        <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>434.9</v>
+        <v>420.3</v>
       </c>
       <c r="G8" s="2">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="I8" s="4">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
@@ -854,22 +857,22 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>11.94</v>
+        <v>11.51</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
       </c>
       <c r="E9" s="3">
-        <v>11.55</v>
+        <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>164.0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>12.9</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.97</v>
+        <v>158.9</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I9" s="4">
         <v>13.0</v>
@@ -886,7 +889,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>55.47</v>
+        <v>57.54</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -895,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>390.3</v>
+        <v>403.2</v>
       </c>
       <c r="G10" s="2">
-        <v>3.0</v>
+        <v>3.1</v>
       </c>
       <c r="H10" s="3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I10" s="4">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -918,7 +921,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>15.46</v>
+        <v>15.23</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -927,16 +930,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>97.0</v>
+        <v>95.9</v>
       </c>
       <c r="G11" s="2">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H11" s="3">
         <v>0.56</v>
       </c>
       <c r="I11" s="4">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>140.7</v>
+        <v>149.9</v>
       </c>
       <c r="G12" s="2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="H12" s="3">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I12" s="4">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -985,22 +988,22 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>14.86</v>
+        <v>14.49</v>
       </c>
       <c r="D13" s="3">
-        <v>14.95</v>
+        <v>15.24</v>
       </c>
       <c r="E13" s="3">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="F13" s="2">
-        <v>921.4</v>
+        <v>931.1</v>
       </c>
       <c r="G13" s="2">
-        <v>36.5</v>
+        <v>36.9</v>
       </c>
       <c r="H13" s="3">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="I13" s="4">
         <v>94.0</v>
@@ -1020,7 +1023,7 @@
         <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>29.7</v>
+        <v>29.08</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1029,16 +1032,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>733.3</v>
+        <v>709.1</v>
       </c>
       <c r="G14" s="2">
-        <v>44.2</v>
+        <v>42.8</v>
       </c>
       <c r="H14" s="3">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="I14" s="4">
-        <v>92.0</v>
+        <v>91.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>54</v>
@@ -1052,7 +1055,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>16.8</v>
+        <v>16.46</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1061,16 +1064,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>157.0</v>
+        <v>157.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="3">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="I15" s="4">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>21</v>
@@ -1087,25 +1090,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>10.03</v>
+        <v>9.54</v>
       </c>
       <c r="D16" s="3">
-        <v>11.45</v>
+        <v>10.95</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>312.9</v>
+        <v>300.9</v>
       </c>
       <c r="G16" s="2">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="H16" s="3">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="I16" s="4">
-        <v>43.0</v>
+        <v>40.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1119,25 +1122,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>43.93</v>
+        <v>42.28</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
       </c>
       <c r="E17" s="3">
-        <v>26.8</v>
+        <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>328.0</v>
+        <v>315.1</v>
       </c>
       <c r="G17" s="2">
-        <v>10.4</v>
+        <v>10.0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="I17" s="4">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1154,7 +1157,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>27.71</v>
+        <v>27.84</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1163,16 +1166,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>351.2</v>
+        <v>349.2</v>
       </c>
       <c r="G18" s="2">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="H18" s="3">
         <v>1.31</v>
       </c>
       <c r="I18" s="4">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1186,25 +1189,28 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>41.58</v>
+        <v>36.7</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
       </c>
       <c r="E19" s="3">
-        <v>17.3</v>
+        <v>19.18</v>
       </c>
       <c r="F19" s="2">
-        <v>104.3</v>
+        <v>93.2</v>
       </c>
       <c r="G19" s="2">
-        <v>8.7</v>
+        <v>7.8</v>
       </c>
       <c r="H19" s="3">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="I19" s="4">
-        <v>75.0</v>
+        <v>50.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1215,25 +1221,28 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>6.65</v>
+        <v>5.97</v>
       </c>
       <c r="D20" s="3">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>407.8</v>
+        <v>361.7</v>
       </c>
       <c r="G20" s="2">
-        <v>62.3</v>
+        <v>55.3</v>
       </c>
       <c r="H20" s="3">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="I20" s="4">
-        <v>90.0</v>
+        <v>76.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1247,7 +1256,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>29.35</v>
+        <v>37.0</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1256,30 +1265,30 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>328.9</v>
+        <v>414.3</v>
       </c>
       <c r="G21" s="2">
-        <v>23.9</v>
+        <v>30.2</v>
       </c>
       <c r="H21" s="3">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="I21" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>47.0</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>4.83</v>
+        <v>4.95</v>
       </c>
       <c r="D22" s="3">
         <v>6.8</v>
@@ -1288,30 +1297,30 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>314.5</v>
+        <v>322.9</v>
       </c>
       <c r="G22" s="2">
-        <v>29.9</v>
+        <v>30.7</v>
       </c>
       <c r="H22" s="3">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="I22" s="4">
-        <v>51.0</v>
+        <v>61.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>20.51</v>
+        <v>20.63</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1320,33 +1329,33 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>290.9</v>
+        <v>287.6</v>
       </c>
       <c r="G23" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I23" s="4">
-        <v>42.0</v>
+        <v>38.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>30.46</v>
+        <v>29.93</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1355,7 +1364,7 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>72.0</v>
+        <v>72.9</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
@@ -1364,24 +1373,24 @@
         <v>0.39</v>
       </c>
       <c r="I24" s="4">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>29.92</v>
+        <v>28.19</v>
       </c>
       <c r="D25" s="3">
         <v>31.38</v>
@@ -1390,65 +1399,68 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>219.8</v>
+        <v>210.5</v>
       </c>
       <c r="G25" s="2">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="H25" s="3">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="I25" s="4">
-        <v>93.0</v>
+        <v>82.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>12.45</v>
+        <v>12.25</v>
       </c>
       <c r="D26" s="3">
-        <v>15.1</v>
+        <v>14.27</v>
       </c>
       <c r="E26" s="3">
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>80.8</v>
+        <v>78.9</v>
       </c>
       <c r="G26" s="2">
-        <v>38.3</v>
+        <v>37.3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="I26" s="4">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>17.74</v>
+        <v>17.47</v>
       </c>
       <c r="D27" s="3">
         <v>37.9</v>
@@ -1457,7 +1469,7 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>157.2</v>
+        <v>157.5</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -1466,24 +1478,24 @@
         <v>1.97</v>
       </c>
       <c r="I27" s="4">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>6.48</v>
+        <v>6.85</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1492,57 +1504,57 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>244.1</v>
+        <v>253.3</v>
       </c>
       <c r="G28" s="2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="I28" s="4">
-        <v>63.0</v>
+        <v>68.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>36.49</v>
+        <v>37.46</v>
       </c>
       <c r="D29" s="3">
-        <v>38.02</v>
+        <v>38.9</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>493.5</v>
+        <v>497.4</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I29" s="4">
-        <v>86.0</v>
+        <v>79.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="3Ar3KpUvinJZ34BsAWomhz6NeE+ge2Uv6hp2sCrpzaw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="XvjxrgyqpD/KhIQjotnvGmnTX/8mdoz4PL3oDliTUtU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -69,6 +69,9 @@
     <t>AMPY</t>
   </si>
   <si>
+    <t>nmf</t>
+  </si>
+  <si>
     <t>News Archive for AMPY</t>
   </si>
   <si>
@@ -78,9 +81,6 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>nmf</t>
-  </si>
-  <si>
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(10/30/25) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -240,7 +240,7 @@
     <t>ZEUS</t>
   </si>
   <si>
-    <t>(10/28/25) Olympic Steel, Inc. (ZEUS)</t>
+    <t>News Archive for ZEUS</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions, Ltd.</t>
@@ -276,7 +276,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>(10/28/25) Rocky Brands, Inc. (RCKY)</t>
+    <t>News Archive for RCKY</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.55</v>
+        <v>4.69</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>47.7</v>
+        <v>48.6</v>
       </c>
       <c r="G2" s="2">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="H2" s="3">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="I2" s="4">
-        <v>43.0</v>
+        <v>41.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,60 +656,57 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.54</v>
+        <v>5.36</v>
       </c>
       <c r="D3" s="3">
-        <v>7.23</v>
+        <v>7.1</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>183.7</v>
-      </c>
-      <c r="G3" s="2">
-        <v>12.1</v>
+        <v>198.3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="I3" s="4">
-        <v>86.0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>13</v>
+        <v>89.0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="D4" s="3">
         <v>4.18</v>
       </c>
       <c r="E4" s="3">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="F4" s="2">
-        <v>19.4</v>
+        <v>17.9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>26.0</v>
+        <v>23.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>21</v>
@@ -726,7 +723,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>17.91</v>
+        <v>19.24</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +732,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>153.3</v>
+        <v>163.2</v>
       </c>
       <c r="G5" s="2">
-        <v>16.6</v>
+        <v>20.6</v>
       </c>
       <c r="H5" s="3">
-        <v>1.0</v>
+        <v>1.05</v>
       </c>
       <c r="I5" s="4">
-        <v>58.0</v>
+        <v>72.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,7 +755,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>20.17</v>
+        <v>19.58</v>
       </c>
       <c r="D6" s="3">
         <v>30.77</v>
@@ -767,16 +764,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>504.6</v>
+        <v>485.6</v>
       </c>
       <c r="G6" s="2">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="H6" s="3">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="I6" s="4">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,25 +787,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.06</v>
+        <v>6.04</v>
       </c>
       <c r="D7" s="3">
-        <v>10.14</v>
+        <v>9.92</v>
       </c>
       <c r="E7" s="3">
         <v>5.78</v>
       </c>
       <c r="F7" s="2">
-        <v>165.9</v>
+        <v>127.5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="4">
-        <v>51.0</v>
+        <v>28.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -825,7 +822,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>16.4</v>
+        <v>16.97</v>
       </c>
       <c r="D8" s="3">
         <v>22.29</v>
@@ -834,13 +831,13 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>420.3</v>
+        <v>434.2</v>
       </c>
       <c r="G8" s="2">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="I8" s="4">
         <v>26.0</v>
@@ -857,7 +854,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>11.51</v>
+        <v>11.91</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>158.9</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>20</v>
+        <v>159.3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.92</v>
       </c>
       <c r="I9" s="4">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -889,7 +886,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>57.54</v>
+        <v>57.91</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,16 +895,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>403.2</v>
+        <v>398.8</v>
       </c>
       <c r="G10" s="2">
         <v>3.1</v>
       </c>
       <c r="H10" s="3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I10" s="4">
-        <v>89.0</v>
+        <v>87.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -921,7 +918,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>15.23</v>
+        <v>14.7</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -930,16 +927,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>95.9</v>
+        <v>93.0</v>
       </c>
       <c r="G11" s="2">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="H11" s="3">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
       <c r="I11" s="4">
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +953,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>21.24</v>
+        <v>21.03</v>
       </c>
       <c r="D12" s="3">
         <v>22.98</v>
@@ -974,7 +971,7 @@
         <v>1.09</v>
       </c>
       <c r="I12" s="4">
-        <v>64.0</v>
+        <v>75.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -988,7 +985,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>14.49</v>
+        <v>12.4</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
@@ -997,16 +994,16 @@
         <v>4.86</v>
       </c>
       <c r="F13" s="2">
-        <v>931.1</v>
+        <v>807.0</v>
       </c>
       <c r="G13" s="2">
-        <v>36.9</v>
+        <v>32.0</v>
       </c>
       <c r="H13" s="3">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="I13" s="4">
-        <v>94.0</v>
+        <v>92.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>50</v>
@@ -1023,7 +1020,7 @@
         <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>29.08</v>
+        <v>27.23</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,16 +1029,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>709.1</v>
+        <v>686.7</v>
       </c>
       <c r="G14" s="2">
-        <v>42.8</v>
+        <v>41.4</v>
       </c>
       <c r="H14" s="3">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="I14" s="4">
-        <v>91.0</v>
+        <v>85.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>54</v>
@@ -1055,7 +1052,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>16.46</v>
+        <v>15.94</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1064,16 +1061,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>157.5</v>
+        <v>153.3</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="I15" s="4">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>21</v>
@@ -1090,25 +1087,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>9.54</v>
+        <v>12.02</v>
       </c>
       <c r="D16" s="3">
-        <v>10.95</v>
+        <v>11.88</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>300.9</v>
+        <v>366.8</v>
       </c>
       <c r="G16" s="2">
-        <v>26.0</v>
+        <v>31.7</v>
       </c>
       <c r="H16" s="3">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="I16" s="4">
-        <v>40.0</v>
+        <v>83.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1122,7 +1119,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>42.28</v>
+        <v>44.24</v>
       </c>
       <c r="D17" s="3">
         <v>45.5</v>
@@ -1131,16 +1128,16 @@
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>315.1</v>
+        <v>327.0</v>
       </c>
       <c r="G17" s="2">
-        <v>10.0</v>
+        <v>11.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I17" s="4">
-        <v>65.0</v>
+        <v>75.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1157,7 +1154,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>27.84</v>
+        <v>29.21</v>
       </c>
       <c r="D18" s="3">
         <v>29.74</v>
@@ -1166,16 +1163,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>349.2</v>
+        <v>362.0</v>
       </c>
       <c r="G18" s="2">
-        <v>19.6</v>
+        <v>20.3</v>
       </c>
       <c r="H18" s="3">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="I18" s="4">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1189,25 +1186,25 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>36.7</v>
+        <v>37.0</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
       </c>
       <c r="E19" s="3">
-        <v>19.18</v>
+        <v>20.0</v>
       </c>
       <c r="F19" s="2">
-        <v>93.2</v>
+        <v>95.4</v>
       </c>
       <c r="G19" s="2">
-        <v>7.8</v>
+        <v>8.3</v>
       </c>
       <c r="H19" s="3">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I19" s="4">
-        <v>50.0</v>
+        <v>66.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1221,7 +1218,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>5.97</v>
+        <v>6.15</v>
       </c>
       <c r="D20" s="3">
         <v>6.88</v>
@@ -1230,16 +1227,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>361.7</v>
+        <v>363.3</v>
       </c>
       <c r="G20" s="2">
-        <v>55.3</v>
+        <v>16.0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="I20" s="4">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1256,7 +1253,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>37.0</v>
+        <v>34.35</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1265,16 +1262,19 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>414.3</v>
+        <v>385.3</v>
       </c>
       <c r="G21" s="2">
-        <v>30.2</v>
+        <v>29.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="I21" s="4">
-        <v>47.0</v>
+        <v>50.0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1288,7 +1288,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>4.95</v>
+        <v>5.82</v>
       </c>
       <c r="D22" s="3">
         <v>6.8</v>
@@ -1297,16 +1297,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>322.9</v>
+        <v>321.6</v>
       </c>
       <c r="G22" s="2">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="H22" s="3">
         <v>0.78</v>
       </c>
       <c r="I22" s="4">
-        <v>61.0</v>
+        <v>66.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1320,7 +1320,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>20.63</v>
+        <v>19.33</v>
       </c>
       <c r="D23" s="3">
         <v>34.5</v>
@@ -1329,16 +1329,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>287.6</v>
+        <v>267.5</v>
       </c>
       <c r="G23" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="H23" s="3">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="I23" s="4">
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1355,7 +1355,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>29.93</v>
+        <v>27.5</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1364,16 +1364,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>72.9</v>
+        <v>70.8</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1390,28 +1390,25 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>28.19</v>
+        <v>29.74</v>
       </c>
       <c r="D25" s="3">
-        <v>31.38</v>
+        <v>33.4</v>
       </c>
       <c r="E25" s="3">
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>210.5</v>
+        <v>222.8</v>
       </c>
       <c r="G25" s="2">
-        <v>11.4</v>
+        <v>12.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="I25" s="4">
         <v>82.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1425,7 +1422,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>12.25</v>
+        <v>12.38</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1434,10 +1431,10 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>78.9</v>
+        <v>78.0</v>
       </c>
       <c r="G26" s="2">
-        <v>37.3</v>
+        <v>36.9</v>
       </c>
       <c r="H26" s="3">
         <v>0.48</v>
@@ -1460,7 +1457,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>17.47</v>
+        <v>17.33</v>
       </c>
       <c r="D27" s="3">
         <v>37.9</v>
@@ -1469,16 +1466,16 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>157.5</v>
+        <v>151.1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="I27" s="4">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>21</v>
@@ -1495,7 +1492,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>6.85</v>
+        <v>6.78</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1504,16 +1501,16 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>253.3</v>
+        <v>248.9</v>
       </c>
       <c r="G28" s="2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H28" s="3">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I28" s="4">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1530,7 +1527,7 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>37.46</v>
+        <v>32.96</v>
       </c>
       <c r="D29" s="3">
         <v>38.9</v>
@@ -1539,16 +1536,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>497.4</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>20</v>
+        <v>439.7</v>
+      </c>
+      <c r="G29" s="2">
+        <v>55.4</v>
       </c>
       <c r="H29" s="3">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I29" s="4">
-        <v>79.0</v>
+        <v>78.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>21</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="XvjxrgyqpD/KhIQjotnvGmnTX/8mdoz4PL3oDliTUtU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/MtaA3IDMzuVnF6ur91rZVkhf5HVvRJvXS6maUJvruA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="97">
   <si>
     <t>Company</t>
   </si>
@@ -72,6 +72,9 @@
     <t>nmf</t>
   </si>
   <si>
+    <t>TTM adjusted earnings positive</t>
+  </si>
+  <si>
     <t>News Archive for AMPY</t>
   </si>
   <si>
@@ -81,9 +84,6 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>TTM adjusted earnings positive</t>
-  </si>
-  <si>
     <t>News Archive for CTRM</t>
   </si>
   <si>
@@ -111,9 +111,6 @@
     <t>BOOM</t>
   </si>
   <si>
-    <t>Earnings probation 2025Q2</t>
-  </si>
-  <si>
     <t>News Archive for BOOM</t>
   </si>
   <si>
@@ -159,7 +156,7 @@
     <t>FRD</t>
   </si>
   <si>
-    <t>News Archive for FRD</t>
+    <t>(11/10/25) Friedman Industries, Incorporated (FRD)</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
@@ -168,10 +165,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Approaching value limit</t>
-  </si>
-  <si>
-    <t>News Archive for GILT</t>
+    <t>(11/12/25) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -216,7 +210,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>News Archive for NGS</t>
+    <t>(11/10/25) Natural Gas Services Group, Inc. (NGS)</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -621,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.69</v>
+        <v>4.49</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +624,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.6</v>
+        <v>46.5</v>
       </c>
       <c r="G2" s="2">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="H2" s="3">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="I2" s="4">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +650,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.36</v>
+        <v>5.77</v>
       </c>
       <c r="D3" s="3">
         <v>7.1</v>
@@ -665,39 +659,42 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>198.3</v>
+        <v>233.5</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="I3" s="4">
-        <v>89.0</v>
+        <v>94.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="D4" s="3">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="E4" s="3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>17.9</v>
+        <v>19.0</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -706,10 +703,10 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -723,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>19.24</v>
+        <v>18.54</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -732,16 +729,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>163.2</v>
+        <v>158.7</v>
       </c>
       <c r="G5" s="2">
-        <v>20.6</v>
+        <v>20.0</v>
       </c>
       <c r="H5" s="3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="I5" s="4">
-        <v>72.0</v>
+        <v>68.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -755,25 +752,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>19.58</v>
+        <v>19.12</v>
       </c>
       <c r="D6" s="3">
-        <v>30.77</v>
+        <v>30.12</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>485.6</v>
+        <v>478.9</v>
       </c>
       <c r="G6" s="2">
-        <v>14.8</v>
+        <v>17.9</v>
       </c>
       <c r="H6" s="3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="I6" s="4">
-        <v>29.0</v>
+        <v>23.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -787,51 +784,51 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>6.04</v>
+        <v>5.87</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
       </c>
       <c r="E7" s="3">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="F7" s="2">
-        <v>127.5</v>
+        <v>120.9</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="I7" s="4">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="C8" s="3">
-        <v>16.97</v>
+        <v>16.9</v>
       </c>
       <c r="D8" s="3">
-        <v>22.29</v>
+        <v>22.01</v>
       </c>
       <c r="E8" s="3">
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>434.2</v>
+        <v>433.1</v>
       </c>
       <c r="G8" s="2">
         <v>10.4</v>
@@ -840,21 +837,21 @@
         <v>1.42</v>
       </c>
       <c r="I8" s="4">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C9" s="3">
-        <v>11.91</v>
+        <v>13.15</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -863,30 +860,30 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>159.3</v>
+        <v>181.5</v>
       </c>
       <c r="G9" s="2">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="H9" s="3">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="I9" s="4">
-        <v>16.0</v>
+        <v>27.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C10" s="3">
-        <v>57.91</v>
+        <v>59.74</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -895,30 +892,30 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>398.8</v>
+        <v>418.5</v>
       </c>
       <c r="G10" s="2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H10" s="3">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="I10" s="4">
         <v>87.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C11" s="3">
-        <v>14.7</v>
+        <v>14.71</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -927,13 +924,13 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>93.0</v>
+        <v>92.6</v>
       </c>
       <c r="G11" s="2">
-        <v>11.7</v>
+        <v>14.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I11" s="4">
         <v>63.0</v>
@@ -942,50 +939,50 @@
         <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C12" s="3">
-        <v>21.03</v>
+        <v>22.62</v>
       </c>
       <c r="D12" s="3">
-        <v>22.98</v>
+        <v>23.5</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>149.9</v>
+        <v>160.9</v>
       </c>
       <c r="G12" s="2">
-        <v>17.5</v>
+        <v>13.9</v>
       </c>
       <c r="H12" s="3">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="I12" s="4">
-        <v>75.0</v>
+        <v>81.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C13" s="3">
-        <v>12.4</v>
+        <v>11.77</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
@@ -994,33 +991,30 @@
         <v>4.86</v>
       </c>
       <c r="F13" s="2">
-        <v>807.0</v>
+        <v>756.0</v>
       </c>
       <c r="G13" s="2">
-        <v>32.0</v>
+        <v>29.9</v>
       </c>
       <c r="H13" s="3">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="I13" s="4">
-        <v>92.0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>50</v>
+        <v>91.0</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>27.23</v>
+        <v>28.34</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1029,30 +1023,30 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>686.7</v>
+        <v>689.7</v>
       </c>
       <c r="G14" s="2">
-        <v>41.4</v>
+        <v>29.5</v>
       </c>
       <c r="H14" s="3">
         <v>1.2</v>
       </c>
       <c r="I14" s="4">
-        <v>85.0</v>
+        <v>89.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>15.94</v>
+        <v>15.77</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1061,132 +1055,132 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>153.3</v>
+        <v>150.9</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="I15" s="4">
-        <v>33.0</v>
+        <v>23.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>12.02</v>
+        <v>12.45</v>
       </c>
       <c r="D16" s="3">
-        <v>11.88</v>
+        <v>13.43</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>366.8</v>
+        <v>392.8</v>
       </c>
       <c r="G16" s="2">
-        <v>31.7</v>
+        <v>21.8</v>
       </c>
       <c r="H16" s="3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I16" s="4">
-        <v>83.0</v>
+        <v>88.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>44.24</v>
+        <v>51.69</v>
       </c>
       <c r="D17" s="3">
-        <v>45.5</v>
+        <v>52.41</v>
       </c>
       <c r="E17" s="3">
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>327.0</v>
+        <v>385.6</v>
       </c>
       <c r="G17" s="2">
-        <v>11.3</v>
+        <v>13.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="I17" s="4">
-        <v>75.0</v>
+        <v>83.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>29.21</v>
+        <v>29.56</v>
       </c>
       <c r="D18" s="3">
-        <v>29.74</v>
+        <v>30.73</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>362.0</v>
+        <v>371.5</v>
       </c>
       <c r="G18" s="2">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="H18" s="3">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="I18" s="4">
-        <v>81.0</v>
+        <v>68.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>37.0</v>
+        <v>37.05</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1195,16 +1189,16 @@
         <v>20.0</v>
       </c>
       <c r="F19" s="2">
-        <v>95.4</v>
+        <v>94.1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="H19" s="3">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="I19" s="4">
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1212,13 +1206,13 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
       <c r="D20" s="3">
         <v>6.88</v>
@@ -1227,33 +1221,33 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>363.3</v>
+        <v>376.4</v>
       </c>
       <c r="G20" s="2">
-        <v>16.0</v>
+        <v>16.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="I20" s="4">
-        <v>77.0</v>
+        <v>80.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" s="3">
-        <v>34.35</v>
+        <v>33.98</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1262,100 +1256,100 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>385.3</v>
+        <v>380.5</v>
       </c>
       <c r="G21" s="2">
-        <v>29.4</v>
+        <v>29.0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="I21" s="4">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>5.82</v>
+        <v>6.48</v>
       </c>
       <c r="D22" s="3">
-        <v>6.8</v>
+        <v>6.56</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>321.6</v>
+        <v>421.0</v>
       </c>
       <c r="G22" s="2">
-        <v>30.6</v>
+        <v>24.3</v>
       </c>
       <c r="H22" s="3">
-        <v>0.78</v>
+        <v>1.0</v>
       </c>
       <c r="I22" s="4">
-        <v>66.0</v>
+        <v>85.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>19.33</v>
+        <v>20.37</v>
       </c>
       <c r="D23" s="3">
-        <v>34.5</v>
+        <v>33.63</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>267.5</v>
+        <v>279.8</v>
       </c>
       <c r="G23" s="2">
-        <v>7.1</v>
+        <v>9.8</v>
       </c>
       <c r="H23" s="3">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="I23" s="4">
-        <v>37.0</v>
+        <v>49.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>27.5</v>
+        <v>26.15</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1364,33 +1358,33 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>70.8</v>
+        <v>63.7</v>
       </c>
       <c r="G24" s="2">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="I24" s="4">
-        <v>85.0</v>
+        <v>74.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>29.74</v>
+        <v>30.14</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1399,30 +1393,30 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>222.8</v>
+        <v>225.9</v>
       </c>
       <c r="G25" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I25" s="4">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>12.38</v>
+        <v>12.01</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1431,68 +1425,65 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>78.0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>36.9</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0.48</v>
+        <v>77.3</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="I26" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>13</v>
+        <v>39.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>17.33</v>
+        <v>17.57</v>
       </c>
       <c r="D27" s="3">
-        <v>37.9</v>
+        <v>34.48</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>151.1</v>
+        <v>158.4</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="I27" s="4">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>6.78</v>
+        <v>6.75</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1501,33 +1492,33 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>248.9</v>
+        <v>249.6</v>
       </c>
       <c r="G28" s="2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H28" s="3">
         <v>0.4</v>
       </c>
       <c r="I28" s="4">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>32.96</v>
+        <v>31.95</v>
       </c>
       <c r="D29" s="3">
         <v>38.9</v>
@@ -1536,22 +1527,19 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>439.7</v>
+        <v>424.3</v>
       </c>
       <c r="G29" s="2">
-        <v>55.4</v>
+        <v>53.4</v>
       </c>
       <c r="H29" s="3">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="I29" s="4">
-        <v>78.0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>21</v>
+        <v>68.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/MtaA3IDMzuVnF6ur91rZVkhf5HVvRJvXS6maUJvruA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ULmE7OefQl4fFDohFPKUWegKDyxFAINeuecTGrquhto="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
   <si>
     <t>Company</t>
   </si>
@@ -120,7 +120,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>News Archive for EBF</t>
+    <t>(11/17/25) Ennis, Inc. (EBF)</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -138,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>News Archive for ESEA</t>
+    <t>(11/18/25) Euroseas Ltd. (ESEA)</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -156,7 +156,7 @@
     <t>FRD</t>
   </si>
   <si>
-    <t>(11/10/25) Friedman Industries, Incorporated (FRD)</t>
+    <t>News Archive for FRD</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
@@ -165,7 +165,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>(11/12/25) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>News Archive for GILT</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -201,7 +201,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>News Archive for NC</t>
+    <t>(11/18/25) NACCO Industries, Inc. (NC)</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -210,7 +210,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>(11/10/25) Natural Gas Services Group, Inc. (NGS)</t>
+    <t>News Archive for NGS</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -615,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.49</v>
+        <v>4.61</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -624,13 +624,13 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>46.5</v>
+        <v>47.8</v>
       </c>
       <c r="G2" s="2">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="H2" s="3">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I2" s="4">
         <v>46.0</v>
@@ -650,7 +650,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.77</v>
+        <v>5.32</v>
       </c>
       <c r="D3" s="3">
         <v>7.1</v>
@@ -659,13 +659,13 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>233.5</v>
+        <v>215.3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="I3" s="4">
         <v>94.0</v>
@@ -685,16 +685,16 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="D4" s="3">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>19.0</v>
+        <v>18.5</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -703,7 +703,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -720,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.54</v>
+        <v>18.78</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -729,16 +729,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>158.7</v>
+        <v>160.8</v>
       </c>
       <c r="G5" s="2">
-        <v>20.0</v>
+        <v>20.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I5" s="4">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -752,7 +752,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>19.12</v>
+        <v>19.1</v>
       </c>
       <c r="D6" s="3">
         <v>30.12</v>
@@ -761,7 +761,7 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>478.9</v>
+        <v>478.4</v>
       </c>
       <c r="G6" s="2">
         <v>17.9</v>
@@ -770,7 +770,7 @@
         <v>1.13</v>
       </c>
       <c r="I6" s="4">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -784,25 +784,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>5.87</v>
+        <v>5.65</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
       </c>
       <c r="E7" s="3">
-        <v>5.7</v>
+        <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>120.9</v>
+        <v>116.3</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I7" s="4">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -819,7 +819,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>16.9</v>
+        <v>17.07</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -828,16 +828,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>433.1</v>
+        <v>437.5</v>
       </c>
       <c r="G8" s="2">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I8" s="4">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -851,7 +851,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.15</v>
+        <v>13.23</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -860,16 +860,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>181.5</v>
+        <v>182.6</v>
       </c>
       <c r="G9" s="2">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H9" s="3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I9" s="4">
-        <v>27.0</v>
+        <v>40.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -883,7 +883,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>59.74</v>
+        <v>57.92</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -892,13 +892,13 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>418.5</v>
+        <v>405.8</v>
       </c>
       <c r="G10" s="2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H10" s="3">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="I10" s="4">
         <v>87.0</v>
@@ -915,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>14.71</v>
+        <v>14.29</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -924,16 +924,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>92.6</v>
+        <v>93.6</v>
       </c>
       <c r="G11" s="2">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="H11" s="3">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="I11" s="4">
-        <v>63.0</v>
+        <v>45.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -950,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>22.62</v>
+        <v>19.68</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -959,16 +959,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>160.9</v>
+        <v>140.0</v>
       </c>
       <c r="G12" s="2">
-        <v>13.9</v>
+        <v>12.1</v>
       </c>
       <c r="H12" s="3">
-        <v>1.15</v>
+        <v>1.0</v>
       </c>
       <c r="I12" s="4">
-        <v>81.0</v>
+        <v>70.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,25 +982,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>11.77</v>
+        <v>10.87</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
       </c>
       <c r="E13" s="3">
-        <v>4.86</v>
+        <v>5.2</v>
       </c>
       <c r="F13" s="2">
-        <v>756.0</v>
+        <v>698.5</v>
       </c>
       <c r="G13" s="2">
-        <v>29.9</v>
+        <v>27.7</v>
       </c>
       <c r="H13" s="3">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="I13" s="4">
-        <v>91.0</v>
+        <v>94.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>49</v>
@@ -1014,7 +1014,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>28.34</v>
+        <v>27.05</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1023,16 +1023,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>689.7</v>
+        <v>658.4</v>
       </c>
       <c r="G14" s="2">
-        <v>29.5</v>
+        <v>28.2</v>
       </c>
       <c r="H14" s="3">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="I14" s="4">
-        <v>89.0</v>
+        <v>87.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1046,7 +1046,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>15.77</v>
+        <v>14.12</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1055,16 +1055,16 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>150.9</v>
+        <v>135.1</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>2.05</v>
+        <v>0.92</v>
       </c>
       <c r="I15" s="4">
-        <v>23.0</v>
+        <v>19.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>18</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>12.45</v>
+        <v>11.78</v>
       </c>
       <c r="D16" s="3">
         <v>13.43</v>
@@ -1090,13 +1090,13 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>392.8</v>
+        <v>371.6</v>
       </c>
       <c r="G16" s="2">
-        <v>21.8</v>
+        <v>20.7</v>
       </c>
       <c r="H16" s="3">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="I16" s="4">
         <v>88.0</v>
@@ -1113,25 +1113,25 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>51.69</v>
+        <v>49.53</v>
       </c>
       <c r="D17" s="3">
-        <v>52.41</v>
+        <v>53.88</v>
       </c>
       <c r="E17" s="3">
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>385.6</v>
+        <v>369.5</v>
       </c>
       <c r="G17" s="2">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="H17" s="3">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="I17" s="4">
-        <v>83.0</v>
+        <v>82.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1148,25 +1148,25 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>29.56</v>
+        <v>30.04</v>
       </c>
       <c r="D18" s="3">
-        <v>30.73</v>
+        <v>32.03</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>371.5</v>
+        <v>377.6</v>
       </c>
       <c r="G18" s="2">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="H18" s="3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="I18" s="4">
-        <v>68.0</v>
+        <v>73.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1180,7 +1180,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>37.05</v>
+        <v>37.15</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1189,16 +1189,16 @@
         <v>20.0</v>
       </c>
       <c r="F19" s="2">
-        <v>94.1</v>
+        <v>94.4</v>
       </c>
       <c r="G19" s="2">
         <v>8.2</v>
       </c>
       <c r="H19" s="3">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I19" s="4">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1212,7 +1212,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>6.3</v>
+        <v>6.12</v>
       </c>
       <c r="D20" s="3">
         <v>6.88</v>
@@ -1221,16 +1221,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>376.4</v>
+        <v>365.6</v>
       </c>
       <c r="G20" s="2">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="H20" s="3">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="I20" s="4">
-        <v>80.0</v>
+        <v>83.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1247,7 +1247,7 @@
         <v>71</v>
       </c>
       <c r="C21" s="3">
-        <v>33.98</v>
+        <v>36.27</v>
       </c>
       <c r="D21" s="3">
         <v>43.6</v>
@@ -1256,19 +1256,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>380.5</v>
+        <v>406.1</v>
       </c>
       <c r="G21" s="2">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="I21" s="4">
-        <v>53.0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>70.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>72</v>
@@ -1282,25 +1279,25 @@
         <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>6.48</v>
+        <v>6.8</v>
       </c>
       <c r="D22" s="3">
-        <v>6.56</v>
+        <v>7.0</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>421.0</v>
+        <v>441.8</v>
       </c>
       <c r="G22" s="2">
-        <v>24.3</v>
+        <v>25.5</v>
       </c>
       <c r="H22" s="3">
-        <v>1.0</v>
+        <v>1.05</v>
       </c>
       <c r="I22" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>75</v>
@@ -1314,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>20.37</v>
+        <v>19.67</v>
       </c>
       <c r="D23" s="3">
         <v>33.63</v>
@@ -1323,16 +1320,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>279.8</v>
+        <v>270.2</v>
       </c>
       <c r="G23" s="2">
-        <v>9.8</v>
+        <v>9.5</v>
       </c>
       <c r="H23" s="3">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="I23" s="4">
-        <v>49.0</v>
+        <v>55.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1349,7 +1346,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>26.15</v>
+        <v>26.79</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1358,16 +1355,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>63.7</v>
+        <v>66.5</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="I24" s="4">
-        <v>74.0</v>
+        <v>63.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1384,7 +1381,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>30.14</v>
+        <v>29.92</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1393,16 +1390,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>225.9</v>
+        <v>224.2</v>
       </c>
       <c r="G25" s="2">
-        <v>11.0</v>
+        <v>10.9</v>
       </c>
       <c r="H25" s="3">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I25" s="4">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>84</v>
@@ -1416,7 +1413,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>12.01</v>
+        <v>12.03</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1425,16 +1422,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>77.3</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>17</v>
+        <v>77.5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>250.6</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.48</v>
       </c>
       <c r="I26" s="4">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>87</v>
@@ -1448,7 +1445,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>17.57</v>
+        <v>17.41</v>
       </c>
       <c r="D27" s="3">
         <v>34.48</v>
@@ -1457,16 +1454,16 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>158.4</v>
+        <v>157.0</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I27" s="4">
-        <v>30.0</v>
+        <v>45.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -1483,7 +1480,7 @@
         <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1492,7 +1489,7 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>249.6</v>
+        <v>250.7</v>
       </c>
       <c r="G28" s="2">
         <v>3.6</v>
@@ -1501,7 +1498,7 @@
         <v>0.4</v>
       </c>
       <c r="I28" s="4">
-        <v>71.0</v>
+        <v>75.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1518,7 +1515,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>31.95</v>
+        <v>31.13</v>
       </c>
       <c r="D29" s="3">
         <v>38.9</v>
@@ -1527,16 +1524,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>424.3</v>
+        <v>413.4</v>
       </c>
       <c r="G29" s="2">
-        <v>53.4</v>
+        <v>52.1</v>
       </c>
       <c r="H29" s="3">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="I29" s="4">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>96</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ULmE7OefQl4fFDohFPKUWegKDyxFAINeuecTGrquhto="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="K90Hq8y5e2YKDvZkmlGZKvhOj+uMtN0m1XTn9W0mZzo="/>
     </ext>
   </extLst>
 </workbook>
@@ -120,7 +120,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>(11/17/25) Ennis, Inc. (EBF)</t>
+    <t>News Archive for EBF</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -138,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>(11/18/25) Euroseas Ltd. (ESEA)</t>
+    <t>News Archive for ESEA</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -201,7 +201,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>(11/18/25) NACCO Industries, Inc. (NC)</t>
+    <t>News Archive for NC</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -615,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -624,16 +624,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>47.8</v>
+        <v>47.1</v>
       </c>
       <c r="G2" s="2">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="H2" s="3">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I2" s="4">
-        <v>46.0</v>
+        <v>38.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -650,16 +650,16 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.32</v>
+        <v>5.5</v>
       </c>
       <c r="D3" s="3">
-        <v>7.1</v>
+        <v>6.79</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>215.3</v>
+        <v>214.5</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
@@ -668,7 +668,7 @@
         <v>0.55</v>
       </c>
       <c r="I3" s="4">
-        <v>94.0</v>
+        <v>92.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -685,7 +685,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="D4" s="3">
         <v>3.64</v>
@@ -694,7 +694,7 @@
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>18.5</v>
+        <v>19.0</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -703,7 +703,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -720,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.78</v>
+        <v>18.9</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -729,16 +729,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>160.8</v>
+        <v>161.5</v>
       </c>
       <c r="G5" s="2">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="H5" s="3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I5" s="4">
-        <v>69.0</v>
+        <v>60.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -752,7 +752,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>19.1</v>
+        <v>19.94</v>
       </c>
       <c r="D6" s="3">
         <v>30.12</v>
@@ -761,16 +761,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>478.4</v>
+        <v>499.9</v>
       </c>
       <c r="G6" s="2">
-        <v>17.9</v>
+        <v>18.7</v>
       </c>
       <c r="H6" s="3">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="I6" s="4">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>5.65</v>
+        <v>6.21</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -793,16 +793,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>116.3</v>
+        <v>125.4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="4">
-        <v>23.0</v>
+        <v>29.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -819,7 +819,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>17.07</v>
+        <v>17.44</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -828,13 +828,13 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>437.5</v>
+        <v>442.4</v>
       </c>
       <c r="G8" s="2">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H8" s="3">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="I8" s="4">
         <v>32.0</v>
@@ -851,7 +851,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.23</v>
+        <v>13.26</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -860,7 +860,7 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>182.6</v>
+        <v>183.0</v>
       </c>
       <c r="G9" s="2">
         <v>14.4</v>
@@ -869,7 +869,7 @@
         <v>1.06</v>
       </c>
       <c r="I9" s="4">
-        <v>40.0</v>
+        <v>29.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -883,7 +883,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>57.92</v>
+        <v>60.29</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -892,13 +892,13 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>405.8</v>
+        <v>419.5</v>
       </c>
       <c r="G10" s="2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H10" s="3">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="I10" s="4">
         <v>87.0</v>
@@ -915,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>14.29</v>
+        <v>14.03</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -924,16 +924,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>93.6</v>
+        <v>92.2</v>
       </c>
       <c r="G11" s="2">
-        <v>13.2</v>
+        <v>13.0</v>
       </c>
       <c r="H11" s="3">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I11" s="4">
-        <v>45.0</v>
+        <v>39.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -950,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.68</v>
+        <v>20.29</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -959,16 +959,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>140.0</v>
+        <v>141.2</v>
       </c>
       <c r="G12" s="2">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="H12" s="3">
-        <v>1.0</v>
+        <v>1.01</v>
       </c>
       <c r="I12" s="4">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,22 +982,22 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>10.87</v>
+        <v>11.64</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
       </c>
       <c r="E13" s="3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>698.5</v>
+        <v>740.2</v>
       </c>
       <c r="G13" s="2">
-        <v>27.7</v>
+        <v>29.3</v>
       </c>
       <c r="H13" s="3">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="I13" s="4">
         <v>94.0</v>
@@ -1014,7 +1014,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>27.05</v>
+        <v>28.9</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1023,16 +1023,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>658.4</v>
+        <v>702.4</v>
       </c>
       <c r="G14" s="2">
-        <v>28.2</v>
+        <v>30.1</v>
       </c>
       <c r="H14" s="3">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="I14" s="4">
-        <v>87.0</v>
+        <v>86.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1046,7 +1046,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>14.12</v>
+        <v>15.18</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1055,13 +1055,13 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>135.1</v>
+        <v>144.7</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="I15" s="4">
         <v>19.0</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>11.78</v>
+        <v>11.99</v>
       </c>
       <c r="D16" s="3">
         <v>13.43</v>
@@ -1090,13 +1090,13 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>371.6</v>
+        <v>374.2</v>
       </c>
       <c r="G16" s="2">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="H16" s="3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I16" s="4">
         <v>88.0</v>
@@ -1113,7 +1113,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>49.53</v>
+        <v>48.24</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1122,16 +1122,16 @@
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>369.5</v>
+        <v>357.9</v>
       </c>
       <c r="G17" s="2">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="I17" s="4">
-        <v>82.0</v>
+        <v>76.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1148,7 +1148,7 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>30.04</v>
+        <v>30.97</v>
       </c>
       <c r="D18" s="3">
         <v>32.03</v>
@@ -1157,16 +1157,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>377.6</v>
+        <v>392.7</v>
       </c>
       <c r="G18" s="2">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
       <c r="H18" s="3">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="I18" s="4">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1180,7 +1180,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>37.15</v>
+        <v>36.06</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1189,16 +1189,16 @@
         <v>20.0</v>
       </c>
       <c r="F19" s="2">
-        <v>94.4</v>
+        <v>95.1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.2</v>
+        <v>8.3</v>
       </c>
       <c r="H19" s="3">
         <v>0.86</v>
       </c>
       <c r="I19" s="4">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>13</v>
@@ -1212,7 +1212,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>6.12</v>
+        <v>6.3</v>
       </c>
       <c r="D20" s="3">
         <v>6.88</v>
@@ -1221,16 +1221,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>365.6</v>
+        <v>369.2</v>
       </c>
       <c r="G20" s="2">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="H20" s="3">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="I20" s="4">
-        <v>83.0</v>
+        <v>80.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1247,25 +1247,25 @@
         <v>71</v>
       </c>
       <c r="C21" s="3">
-        <v>36.27</v>
+        <v>38.89</v>
       </c>
       <c r="D21" s="3">
-        <v>43.6</v>
+        <v>43.32</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>406.1</v>
+        <v>430.2</v>
       </c>
       <c r="G21" s="2">
-        <v>31.0</v>
+        <v>32.8</v>
       </c>
       <c r="H21" s="3">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="I21" s="4">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>72</v>
@@ -1279,25 +1279,25 @@
         <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>6.8</v>
+        <v>7.02</v>
       </c>
       <c r="D22" s="3">
-        <v>7.0</v>
+        <v>7.23</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>441.8</v>
+        <v>460.7</v>
       </c>
       <c r="G22" s="2">
-        <v>25.5</v>
+        <v>26.6</v>
       </c>
       <c r="H22" s="3">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="I22" s="4">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>75</v>
@@ -1311,25 +1311,25 @@
         <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>19.67</v>
+        <v>21.41</v>
       </c>
       <c r="D23" s="3">
-        <v>33.63</v>
+        <v>32.96</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>270.2</v>
+        <v>283.8</v>
       </c>
       <c r="G23" s="2">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H23" s="3">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="I23" s="4">
-        <v>55.0</v>
+        <v>61.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1346,7 +1346,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>26.79</v>
+        <v>26.86</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1355,7 +1355,7 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>66.5</v>
+        <v>67.0</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
@@ -1364,7 +1364,7 @@
         <v>0.35</v>
       </c>
       <c r="I24" s="4">
-        <v>63.0</v>
+        <v>67.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1381,7 +1381,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>29.92</v>
+        <v>30.37</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1390,16 +1390,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>224.2</v>
+        <v>230.1</v>
       </c>
       <c r="G25" s="2">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="H25" s="3">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I25" s="4">
-        <v>84.0</v>
+        <v>78.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>84</v>
@@ -1413,7 +1413,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>12.03</v>
+        <v>11.8</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1422,16 +1422,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>77.5</v>
+        <v>75.5</v>
       </c>
       <c r="G26" s="2">
-        <v>250.6</v>
+        <v>244.2</v>
       </c>
       <c r="H26" s="3">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="I26" s="4">
-        <v>41.0</v>
+        <v>36.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>87</v>
@@ -1445,25 +1445,25 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>17.41</v>
+        <v>19.42</v>
       </c>
       <c r="D27" s="3">
-        <v>34.48</v>
+        <v>34.0</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>157.0</v>
+        <v>174.7</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="I27" s="4">
-        <v>45.0</v>
+        <v>43.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -1480,7 +1480,7 @@
         <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>6.78</v>
+        <v>6.86</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1489,7 +1489,7 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>250.7</v>
+        <v>250.3</v>
       </c>
       <c r="G28" s="2">
         <v>3.6</v>
@@ -1498,7 +1498,7 @@
         <v>0.4</v>
       </c>
       <c r="I28" s="4">
-        <v>75.0</v>
+        <v>62.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1515,7 +1515,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>31.13</v>
+        <v>34.14</v>
       </c>
       <c r="D29" s="3">
         <v>38.9</v>
@@ -1524,16 +1524,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>413.4</v>
+        <v>452.2</v>
       </c>
       <c r="G29" s="2">
-        <v>52.1</v>
+        <v>56.9</v>
       </c>
       <c r="H29" s="3">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="I29" s="4">
-        <v>69.0</v>
+        <v>75.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>96</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="K90Hq8y5e2YKDvZkmlGZKvhOj+uMtN0m1XTn9W0mZzo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6FNLgFuFMsfJnWqwJsW0z/+El1RJgDNV33YqEczvZDc="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -57,96 +57,96 @@
     <t>APT</t>
   </si>
   <si>
+    <t>News Archive for APT</t>
+  </si>
+  <si>
+    <t>Amplify Energy Corp.</t>
+  </si>
+  <si>
+    <t>AMPY</t>
+  </si>
+  <si>
+    <t>nmf</t>
+  </si>
+  <si>
+    <t>TTM adjusted earnings positive</t>
+  </si>
+  <si>
+    <t>News Archive for AMPY</t>
+  </si>
+  <si>
+    <t>Castor Maritime Inc.</t>
+  </si>
+  <si>
+    <t>CTRM</t>
+  </si>
+  <si>
+    <t>(12/3/25) Castor Maritime Inc. (CTRM)</t>
+  </si>
+  <si>
+    <t>Core Molding Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>News Archive for CMT</t>
+  </si>
+  <si>
+    <t>Covenant Logistics Group, Inc.</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>News Archive for CVLG</t>
+  </si>
+  <si>
+    <t>DMC Global Inc.</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>News Archive for BOOM</t>
+  </si>
+  <si>
+    <t>Ennis, Inc.</t>
+  </si>
+  <si>
+    <t>EBF</t>
+  </si>
+  <si>
+    <t>News Archive for EBF</t>
+  </si>
+  <si>
+    <t>Escalade, Incorporated</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>News Archive for ESCA</t>
+  </si>
+  <si>
+    <t>Euroseas Ltd.</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>News Archive for ESEA</t>
+  </si>
+  <si>
+    <t>FONAR Corporation</t>
+  </si>
+  <si>
+    <t>FONR</t>
+  </si>
+  <si>
     <t>Currently qualifies</t>
   </si>
   <si>
-    <t>News Archive for APT</t>
-  </si>
-  <si>
-    <t>Amplify Energy Corp.</t>
-  </si>
-  <si>
-    <t>AMPY</t>
-  </si>
-  <si>
-    <t>nmf</t>
-  </si>
-  <si>
-    <t>TTM adjusted earnings positive</t>
-  </si>
-  <si>
-    <t>News Archive for AMPY</t>
-  </si>
-  <si>
-    <t>Castor Maritime Inc.</t>
-  </si>
-  <si>
-    <t>CTRM</t>
-  </si>
-  <si>
-    <t>News Archive for CTRM</t>
-  </si>
-  <si>
-    <t>Core Molding Technologies, Inc.</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>News Archive for CMT</t>
-  </si>
-  <si>
-    <t>Covenant Logistics Group, Inc.</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>News Archive for CVLG</t>
-  </si>
-  <si>
-    <t>DMC Global Inc.</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>News Archive for BOOM</t>
-  </si>
-  <si>
-    <t>Ennis, Inc.</t>
-  </si>
-  <si>
-    <t>EBF</t>
-  </si>
-  <si>
-    <t>News Archive for EBF</t>
-  </si>
-  <si>
-    <t>Escalade, Incorporated</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>News Archive for ESCA</t>
-  </si>
-  <si>
-    <t>Euroseas Ltd.</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>News Archive for ESEA</t>
-  </si>
-  <si>
-    <t>FONAR Corporation</t>
-  </si>
-  <si>
-    <t>FONR</t>
-  </si>
-  <si>
     <t>News Archive for FONR</t>
   </si>
   <si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>SDHC</t>
+  </si>
+  <si>
+    <t>TTM adjusted earnings positive Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for SDHC</t>
@@ -624,103 +627,100 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="G2" s="2">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="H2" s="3">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I2" s="4">
-        <v>38.0</v>
-      </c>
-      <c r="J2" s="2" t="s">
+        <v>40.0</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C3" s="3">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="D3" s="3">
-        <v>6.79</v>
+        <v>6.62</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>214.5</v>
+        <v>229.5</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="I3" s="4">
+        <v>91.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="3">
-        <v>0.55</v>
-      </c>
-      <c r="I3" s="4">
-        <v>92.0</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="3">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="D4" s="3">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>19.0</v>
+        <v>19.6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="C5" s="3">
-        <v>18.9</v>
+        <v>18.75</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -729,30 +729,30 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>161.5</v>
+        <v>160.4</v>
       </c>
       <c r="G5" s="2">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="H5" s="3">
         <v>1.04</v>
       </c>
       <c r="I5" s="4">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C6" s="3">
-        <v>19.94</v>
+        <v>21.72</v>
       </c>
       <c r="D6" s="3">
         <v>30.12</v>
@@ -761,30 +761,30 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>499.9</v>
+        <v>541.8</v>
       </c>
       <c r="G6" s="2">
-        <v>18.7</v>
+        <v>20.2</v>
       </c>
       <c r="H6" s="3">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="I6" s="4">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="C7" s="3">
-        <v>6.21</v>
+        <v>6.32</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -793,33 +793,33 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>125.4</v>
+        <v>127.9</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="I7" s="4">
+        <v>28.0</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="4">
-        <v>29.0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C8" s="3">
-        <v>17.44</v>
+        <v>17.79</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -828,30 +828,30 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>442.4</v>
+        <v>451.1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="I8" s="4">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C9" s="3">
-        <v>13.26</v>
+        <v>12.57</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -860,30 +860,30 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>183.0</v>
+        <v>174.6</v>
       </c>
       <c r="G9" s="2">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="H9" s="3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="I9" s="4">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C10" s="3">
-        <v>60.29</v>
+        <v>61.78</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -892,30 +892,30 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>419.5</v>
+        <v>437.7</v>
       </c>
       <c r="G10" s="2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H10" s="3">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="I10" s="4">
-        <v>87.0</v>
+        <v>86.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C11" s="3">
-        <v>14.03</v>
+        <v>14.61</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -924,19 +924,19 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>92.2</v>
+        <v>95.9</v>
       </c>
       <c r="G11" s="2">
-        <v>13.0</v>
+        <v>13.5</v>
       </c>
       <c r="H11" s="3">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="I11" s="4">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>43</v>
@@ -950,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>20.29</v>
+        <v>19.52</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -959,16 +959,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>141.2</v>
+        <v>139.5</v>
       </c>
       <c r="G12" s="2">
-        <v>12.2</v>
+        <v>12.0</v>
       </c>
       <c r="H12" s="3">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="I12" s="4">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,7 +982,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>11.64</v>
+        <v>11.86</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
@@ -991,16 +991,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>740.2</v>
+        <v>756.9</v>
       </c>
       <c r="G13" s="2">
-        <v>29.3</v>
+        <v>29.6</v>
       </c>
       <c r="H13" s="3">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="I13" s="4">
-        <v>94.0</v>
+        <v>93.0</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>49</v>
@@ -1014,7 +1014,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>28.9</v>
+        <v>29.51</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1023,16 +1023,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>702.4</v>
+        <v>717.3</v>
       </c>
       <c r="G14" s="2">
-        <v>30.1</v>
+        <v>30.7</v>
       </c>
       <c r="H14" s="3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="I14" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1046,7 +1046,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>15.18</v>
+        <v>15.33</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1055,19 +1055,19 @@
         <v>12.76</v>
       </c>
       <c r="F15" s="2">
-        <v>144.7</v>
+        <v>145.7</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="I15" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="I15" s="4">
-        <v>19.0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>55</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>11.99</v>
+        <v>11.53</v>
       </c>
       <c r="D16" s="3">
         <v>13.43</v>
@@ -1090,16 +1090,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>374.2</v>
+        <v>372.6</v>
       </c>
       <c r="G16" s="2">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="H16" s="3">
         <v>1.64</v>
       </c>
       <c r="I16" s="4">
-        <v>88.0</v>
+        <v>86.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1113,7 +1113,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>48.24</v>
+        <v>48.36</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1122,7 +1122,7 @@
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>357.9</v>
+        <v>359.6</v>
       </c>
       <c r="G17" s="2">
         <v>12.4</v>
@@ -1131,10 +1131,10 @@
         <v>0.84</v>
       </c>
       <c r="I17" s="4">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>61</v>
@@ -1148,25 +1148,25 @@
         <v>63</v>
       </c>
       <c r="C18" s="3">
-        <v>30.97</v>
+        <v>32.18</v>
       </c>
       <c r="D18" s="3">
-        <v>32.03</v>
+        <v>32.47</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>392.7</v>
+        <v>405.9</v>
       </c>
       <c r="G18" s="2">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="H18" s="3">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="I18" s="4">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>64</v>
@@ -1180,28 +1180,25 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>36.06</v>
+        <v>39.28</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
       </c>
       <c r="E19" s="3">
-        <v>20.0</v>
+        <v>23.03</v>
       </c>
       <c r="F19" s="2">
-        <v>95.1</v>
+        <v>100.4</v>
       </c>
       <c r="G19" s="2">
-        <v>8.3</v>
+        <v>8.7</v>
       </c>
       <c r="H19" s="3">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="I19" s="4">
-        <v>67.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1212,28 +1209,25 @@
         <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="D20" s="3">
-        <v>6.88</v>
+        <v>6.9</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>369.2</v>
+        <v>410.5</v>
       </c>
       <c r="G20" s="2">
-        <v>16.2</v>
+        <v>18.0</v>
       </c>
       <c r="H20" s="3">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="I20" s="4">
-        <v>80.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>86.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>69</v>
@@ -1247,25 +1241,25 @@
         <v>71</v>
       </c>
       <c r="C21" s="3">
-        <v>38.89</v>
+        <v>40.45</v>
       </c>
       <c r="D21" s="3">
-        <v>43.32</v>
+        <v>42.98</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>430.2</v>
+        <v>456.0</v>
       </c>
       <c r="G21" s="2">
-        <v>32.8</v>
+        <v>34.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="I21" s="4">
-        <v>73.0</v>
+        <v>72.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>72</v>
@@ -1279,7 +1273,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>7.02</v>
+        <v>7.16</v>
       </c>
       <c r="D22" s="3">
         <v>7.23</v>
@@ -1288,13 +1282,13 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>460.7</v>
+        <v>467.2</v>
       </c>
       <c r="G22" s="2">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="H22" s="3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I22" s="4">
         <v>87.0</v>
@@ -1311,28 +1305,28 @@
         <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>21.41</v>
+        <v>21.7</v>
       </c>
       <c r="D23" s="3">
-        <v>32.96</v>
+        <v>32.29</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>283.8</v>
+        <v>294.5</v>
       </c>
       <c r="G23" s="2">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="H23" s="3">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="I23" s="4">
-        <v>61.0</v>
+        <v>68.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>78</v>
@@ -1346,7 +1340,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>26.86</v>
+        <v>28.9</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1355,19 +1349,19 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>67.0</v>
+        <v>71.8</v>
       </c>
       <c r="G24" s="2">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>67.0</v>
+        <v>75.0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>81</v>
@@ -1381,7 +1375,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>30.37</v>
+        <v>29.12</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1390,16 +1384,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>230.1</v>
+        <v>218.9</v>
       </c>
       <c r="G25" s="2">
-        <v>11.2</v>
+        <v>11.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="I25" s="4">
-        <v>78.0</v>
+        <v>75.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>84</v>
@@ -1413,7 +1407,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>11.8</v>
+        <v>11.51</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1422,16 +1416,16 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>75.5</v>
+        <v>74.9</v>
       </c>
       <c r="G26" s="2">
-        <v>244.2</v>
+        <v>242.4</v>
       </c>
       <c r="H26" s="3">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I26" s="4">
-        <v>36.0</v>
+        <v>26.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>87</v>
@@ -1445,42 +1439,42 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>19.42</v>
+        <v>20.67</v>
       </c>
       <c r="D27" s="3">
-        <v>34.0</v>
+        <v>33.72</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>174.7</v>
+        <v>186.6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H27" s="3">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="I27" s="4">
-        <v>43.0</v>
+        <v>46.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3">
-        <v>6.86</v>
+        <v>7.03</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1489,33 +1483,33 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>250.3</v>
+        <v>255.9</v>
       </c>
       <c r="G28" s="2">
         <v>3.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="I28" s="4">
-        <v>62.0</v>
+        <v>54.0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="3">
-        <v>34.14</v>
+        <v>39.01</v>
       </c>
       <c r="D29" s="3">
         <v>38.9</v>
@@ -1524,19 +1518,19 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>452.2</v>
+        <v>495.6</v>
       </c>
       <c r="G29" s="2">
-        <v>56.9</v>
+        <v>62.4</v>
       </c>
       <c r="H29" s="3">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="I29" s="4">
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6FNLgFuFMsfJnWqwJsW0z/+El1RJgDNV33YqEczvZDc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6wEthsCvLvie7/RZGDxsjSagcJo5+qmfMY5qpqpsxrk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -81,7 +81,7 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>(12/3/25) Castor Maritime Inc. (CTRM)</t>
+    <t>News Archive for CTRM</t>
   </si>
   <si>
     <t>Core Molding Technologies, Inc.</t>
@@ -135,7 +135,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>News Archive for ESEA</t>
+    <t>(12/9/25) Euroseas Ltd. (ESEA)</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -165,6 +165,9 @@
     <t>GILT</t>
   </si>
   <si>
+    <t>Approaching value limit</t>
+  </si>
+  <si>
     <t>News Archive for GILT</t>
   </si>
   <si>
@@ -183,7 +186,7 @@
     <t>LAKE</t>
   </si>
   <si>
-    <t>News Archive for LAKE</t>
+    <t>(12/9/25) Lakeland Industries, Inc. (LAKE)</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -201,7 +204,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>News Archive for NC</t>
+    <t>(12/10/25) NACCO Industries, Inc. (NC)</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -618,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -627,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="G2" s="2">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="H2" s="3">
         <v>0.76</v>
       </c>
       <c r="I2" s="4">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>13</v>
@@ -650,7 +653,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="3">
-        <v>5.56</v>
+        <v>4.85</v>
       </c>
       <c r="D3" s="3">
         <v>6.62</v>
@@ -659,16 +662,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>229.5</v>
+        <v>203.6</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="3">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="I3" s="4">
-        <v>91.0</v>
+        <v>86.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>17</v>
@@ -685,16 +688,16 @@
         <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="D4" s="3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>19.6</v>
+        <v>22.1</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>16</v>
@@ -703,7 +706,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>26.0</v>
+        <v>40.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>17</v>
@@ -720,7 +723,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>18.75</v>
+        <v>20.47</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -729,16 +732,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>160.4</v>
+        <v>177.1</v>
       </c>
       <c r="G5" s="2">
-        <v>20.3</v>
+        <v>22.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="I5" s="4">
-        <v>64.0</v>
+        <v>70.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -752,25 +755,25 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>21.72</v>
+        <v>23.16</v>
       </c>
       <c r="D6" s="3">
-        <v>30.12</v>
+        <v>29.91</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>541.8</v>
+        <v>587.9</v>
       </c>
       <c r="G6" s="2">
-        <v>20.2</v>
+        <v>21.9</v>
       </c>
       <c r="H6" s="3">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="I6" s="4">
-        <v>34.0</v>
+        <v>42.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -784,7 +787,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>6.32</v>
+        <v>6.65</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -793,16 +796,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>127.9</v>
+        <v>139.4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="3">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="I7" s="4">
-        <v>28.0</v>
+        <v>23.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>17</v>
@@ -819,7 +822,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>17.79</v>
+        <v>18.36</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -828,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>451.1</v>
+        <v>467.2</v>
       </c>
       <c r="G8" s="2">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="H8" s="3">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="I8" s="4">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>33</v>
@@ -851,7 +854,7 @@
         <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>12.57</v>
+        <v>13.1</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -860,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>174.6</v>
+        <v>181.4</v>
       </c>
       <c r="G9" s="2">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="I9" s="4">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
@@ -883,7 +886,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>61.78</v>
+        <v>55.14</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -892,16 +895,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>437.7</v>
+        <v>407.7</v>
       </c>
       <c r="G10" s="2">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H10" s="3">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="I10" s="4">
-        <v>86.0</v>
+        <v>77.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
@@ -915,7 +918,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>14.61</v>
+        <v>14.75</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -924,16 +927,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>95.9</v>
+        <v>97.4</v>
       </c>
       <c r="G11" s="2">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H11" s="3">
-        <v>0.55</v>
+        <v>0.56</v>
       </c>
       <c r="I11" s="4">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>42</v>
@@ -950,7 +953,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.52</v>
+        <v>20.41</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -959,16 +962,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>139.5</v>
+        <v>143.9</v>
       </c>
       <c r="G12" s="2">
-        <v>12.0</v>
+        <v>12.4</v>
       </c>
       <c r="H12" s="3">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="I12" s="4">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,7 +985,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>11.86</v>
+        <v>12.68</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
@@ -991,30 +994,33 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>756.9</v>
+        <v>839.8</v>
       </c>
       <c r="G13" s="2">
-        <v>29.6</v>
+        <v>33.3</v>
       </c>
       <c r="H13" s="3">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="I13" s="4">
-        <v>93.0</v>
+        <v>94.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>29.51</v>
+        <v>30.34</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1023,65 +1029,65 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>717.3</v>
+        <v>762.5</v>
       </c>
       <c r="G14" s="2">
-        <v>30.7</v>
+        <v>32.6</v>
       </c>
       <c r="H14" s="3">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="I14" s="4">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>15.33</v>
+        <v>8.99</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
       </c>
       <c r="E15" s="3">
-        <v>12.76</v>
+        <v>8.31</v>
       </c>
       <c r="F15" s="2">
-        <v>145.7</v>
+        <v>89.6</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="3">
-        <v>0.99</v>
+        <v>0.67</v>
       </c>
       <c r="I15" s="4">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>11.53</v>
+        <v>12.31</v>
       </c>
       <c r="D16" s="3">
         <v>13.43</v>
@@ -1090,30 +1096,30 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>372.6</v>
+        <v>389.6</v>
       </c>
       <c r="G16" s="2">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="H16" s="3">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="I16" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>48.36</v>
+        <v>49.42</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1122,65 +1128,65 @@
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>359.6</v>
+        <v>366.4</v>
       </c>
       <c r="G17" s="2">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H17" s="3">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="I17" s="4">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>32.18</v>
+        <v>33.44</v>
       </c>
       <c r="D18" s="3">
-        <v>32.47</v>
+        <v>33.82</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>405.9</v>
+        <v>420.9</v>
       </c>
       <c r="G18" s="2">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="H18" s="3">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="I18" s="4">
         <v>75.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>39.28</v>
+        <v>42.58</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1189,158 +1195,158 @@
         <v>23.03</v>
       </c>
       <c r="F19" s="2">
-        <v>100.4</v>
+        <v>106.7</v>
       </c>
       <c r="G19" s="2">
-        <v>8.7</v>
+        <v>9.3</v>
       </c>
       <c r="H19" s="3">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="I19" s="4">
-        <v>76.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>6.8</v>
+        <v>7.07</v>
       </c>
       <c r="D20" s="3">
-        <v>6.9</v>
+        <v>7.19</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>410.5</v>
+        <v>423.6</v>
       </c>
       <c r="G20" s="2">
-        <v>18.0</v>
+        <v>18.6</v>
       </c>
       <c r="H20" s="3">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I20" s="4">
-        <v>86.0</v>
+        <v>80.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>40.45</v>
+        <v>42.71</v>
       </c>
       <c r="D21" s="3">
-        <v>42.98</v>
+        <v>43.12</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>456.0</v>
+        <v>477.5</v>
       </c>
       <c r="G21" s="2">
-        <v>34.4</v>
+        <v>36.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="I21" s="4">
-        <v>72.0</v>
+        <v>79.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>7.16</v>
+        <v>7.15</v>
       </c>
       <c r="D22" s="3">
-        <v>7.23</v>
+        <v>7.38</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>467.2</v>
+        <v>459.4</v>
       </c>
       <c r="G22" s="2">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="H22" s="3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I22" s="4">
-        <v>87.0</v>
+        <v>85.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>21.7</v>
+        <v>22.86</v>
       </c>
       <c r="D23" s="3">
-        <v>32.29</v>
+        <v>31.45</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>294.5</v>
+        <v>321.6</v>
       </c>
       <c r="G23" s="2">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="H23" s="3">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="I23" s="4">
-        <v>68.0</v>
+        <v>75.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>28.9</v>
+        <v>29.0</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1349,33 +1355,33 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>71.8</v>
+        <v>70.8</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I24" s="4">
-        <v>75.0</v>
+        <v>72.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>42</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>29.12</v>
+        <v>31.24</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1384,30 +1390,30 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>218.9</v>
+        <v>232.1</v>
       </c>
       <c r="G25" s="2">
-        <v>11.0</v>
+        <v>11.3</v>
       </c>
       <c r="H25" s="3">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="I25" s="4">
-        <v>75.0</v>
+        <v>83.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>11.51</v>
+        <v>11.7</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1416,65 +1422,65 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>74.9</v>
+        <v>76.2</v>
       </c>
       <c r="G26" s="2">
-        <v>242.4</v>
+        <v>246.5</v>
       </c>
       <c r="H26" s="3">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="I26" s="4">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>20.67</v>
+        <v>22.16</v>
       </c>
       <c r="D27" s="3">
-        <v>33.72</v>
+        <v>33.18</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>186.6</v>
+        <v>197.2</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H27" s="3">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="I27" s="4">
-        <v>46.0</v>
+        <v>58.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1483,54 +1489,54 @@
         <v>4.82</v>
       </c>
       <c r="F28" s="2">
-        <v>255.9</v>
+        <v>263.3</v>
       </c>
       <c r="G28" s="2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H28" s="3">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I28" s="4">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>42</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>39.01</v>
+        <v>37.92</v>
       </c>
       <c r="D29" s="3">
-        <v>38.9</v>
+        <v>39.44</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>495.6</v>
+        <v>517.8</v>
       </c>
       <c r="G29" s="2">
-        <v>62.4</v>
+        <v>65.2</v>
       </c>
       <c r="H29" s="3">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="I29" s="4">
-        <v>79.0</v>
+        <v>83.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6wEthsCvLvie7/RZGDxsjSagcJo5+qmfMY5qpqpsxrk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="xyrDUfYSKRuK6e06aiEmpCBwQvvh1TXKhfJxdYxDUV8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -57,6 +57,9 @@
     <t>APT</t>
   </si>
   <si>
+    <t>Currently qualifies</t>
+  </si>
+  <si>
     <t>News Archive for APT</t>
   </si>
   <si>
@@ -126,7 +129,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>News Archive for ESCA</t>
+    <t>(12/16/25) Escalade, Incorporated (ESCA)</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -135,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>(12/9/25) Euroseas Ltd. (ESEA)</t>
+    <t>News Archive for ESEA</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -144,9 +147,6 @@
     <t>FONR</t>
   </si>
   <si>
-    <t>Currently qualifies</t>
-  </si>
-  <si>
     <t>News Archive for FONR</t>
   </si>
   <si>
@@ -165,9 +165,6 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Approaching value limit</t>
-  </si>
-  <si>
     <t>News Archive for GILT</t>
   </si>
   <si>
@@ -186,7 +183,10 @@
     <t>LAKE</t>
   </si>
   <si>
-    <t>(12/9/25) Lakeland Industries, Inc. (LAKE)</t>
+    <t>Earnings probation 2025Q3</t>
+  </si>
+  <si>
+    <t>News Archive for LAKE</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -204,7 +204,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>(12/10/25) NACCO Industries, Inc. (NC)</t>
+    <t>News Archive for NC</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -282,7 +282,7 @@
     <t>SGA</t>
   </si>
   <si>
-    <t>News Archive for SGA</t>
+    <t>(12/15/25) Saga Communications, Inc. (SGA)</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.59</v>
+        <v>4.42</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,30 +630,33 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.2</v>
+        <v>46.5</v>
       </c>
       <c r="G2" s="2">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="H2" s="3">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="I2" s="4">
-        <v>41.0</v>
+        <v>33.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="D3" s="3">
         <v>6.62</v>
@@ -662,68 +665,68 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>203.6</v>
+        <v>186.0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="I3" s="4">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="D4" s="3">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>20.47</v>
+        <v>21.29</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -732,62 +735,62 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>177.1</v>
+        <v>180.2</v>
       </c>
       <c r="G5" s="2">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="H5" s="3">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I5" s="4">
-        <v>70.0</v>
+        <v>74.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>23.16</v>
+        <v>22.62</v>
       </c>
       <c r="D6" s="3">
-        <v>29.91</v>
+        <v>29.47</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>587.9</v>
+        <v>574.8</v>
       </c>
       <c r="G6" s="2">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="H6" s="3">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="I6" s="4">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>6.65</v>
+        <v>6.4</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -796,33 +799,33 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>139.4</v>
+        <v>132.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="I7" s="4">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.36</v>
+        <v>18.07</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -831,30 +834,30 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>467.2</v>
+        <v>472.0</v>
       </c>
       <c r="G8" s="2">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H8" s="3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I8" s="4">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.1</v>
+        <v>12.79</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -863,30 +866,30 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>181.4</v>
+        <v>180.1</v>
       </c>
       <c r="G9" s="2">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="H9" s="3">
         <v>1.05</v>
       </c>
       <c r="I9" s="4">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>55.14</v>
+        <v>54.01</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -895,30 +898,30 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>407.7</v>
+        <v>378.6</v>
       </c>
       <c r="G10" s="2">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="I10" s="4">
-        <v>77.0</v>
+        <v>66.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>14.75</v>
+        <v>14.94</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -927,19 +930,19 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>97.4</v>
+        <v>99.1</v>
       </c>
       <c r="G11" s="2">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H11" s="3">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
       <c r="I11" s="4">
-        <v>44.0</v>
+        <v>49.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>43</v>
@@ -953,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>20.41</v>
+        <v>21.41</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -962,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>143.9</v>
+        <v>151.8</v>
       </c>
       <c r="G12" s="2">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="H12" s="3">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="I12" s="4">
-        <v>65.0</v>
+        <v>75.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -985,7 +988,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>12.68</v>
+        <v>11.81</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
@@ -994,33 +997,30 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>839.8</v>
+        <v>728.0</v>
       </c>
       <c r="G13" s="2">
-        <v>33.3</v>
+        <v>28.8</v>
       </c>
       <c r="H13" s="3">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="I13" s="4">
-        <v>94.0</v>
-      </c>
-      <c r="J13" s="2" t="s">
+        <v>92.0</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C14" s="3">
-        <v>30.34</v>
+        <v>28.52</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1029,51 +1029,51 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>762.5</v>
+        <v>689.0</v>
       </c>
       <c r="G14" s="2">
-        <v>32.6</v>
+        <v>29.5</v>
       </c>
       <c r="H14" s="3">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="I14" s="4">
-        <v>89.0</v>
+        <v>86.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C15" s="3">
-        <v>8.99</v>
+        <v>7.94</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
       </c>
       <c r="E15" s="3">
-        <v>8.31</v>
+        <v>7.97</v>
       </c>
       <c r="F15" s="2">
-        <v>89.6</v>
+        <v>81.2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="I15" s="4">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
@@ -1087,7 +1087,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="3">
-        <v>12.31</v>
+        <v>12.8</v>
       </c>
       <c r="D16" s="3">
         <v>13.43</v>
@@ -1096,16 +1096,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>389.6</v>
+        <v>398.8</v>
       </c>
       <c r="G16" s="2">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="I16" s="4">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>59</v>
@@ -1119,7 +1119,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="3">
-        <v>49.42</v>
+        <v>49.18</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1128,19 +1128,19 @@
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>366.4</v>
+        <v>375.7</v>
       </c>
       <c r="G17" s="2">
-        <v>12.7</v>
+        <v>13.0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="I17" s="4">
-        <v>78.0</v>
+        <v>75.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>62</v>
@@ -1154,7 +1154,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>33.44</v>
+        <v>32.48</v>
       </c>
       <c r="D18" s="3">
         <v>33.82</v>
@@ -1163,16 +1163,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>420.9</v>
+        <v>399.8</v>
       </c>
       <c r="G18" s="2">
-        <v>22.8</v>
+        <v>21.6</v>
       </c>
       <c r="H18" s="3">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="I18" s="4">
-        <v>75.0</v>
+        <v>64.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1186,7 +1186,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>42.58</v>
+        <v>39.8</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1195,16 +1195,16 @@
         <v>23.03</v>
       </c>
       <c r="F19" s="2">
-        <v>106.7</v>
+        <v>106.0</v>
       </c>
       <c r="G19" s="2">
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="H19" s="3">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I19" s="4">
-        <v>81.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1215,7 +1215,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>7.07</v>
+        <v>6.87</v>
       </c>
       <c r="D20" s="3">
         <v>7.19</v>
@@ -1224,16 +1224,19 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>423.6</v>
+        <v>399.1</v>
       </c>
       <c r="G20" s="2">
-        <v>18.6</v>
+        <v>17.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="I20" s="4">
-        <v>80.0</v>
+        <v>66.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>70</v>
@@ -1247,25 +1250,25 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>42.71</v>
+        <v>43.65</v>
       </c>
       <c r="D21" s="3">
-        <v>43.12</v>
+        <v>44.85</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>477.5</v>
+        <v>493.6</v>
       </c>
       <c r="G21" s="2">
-        <v>36.4</v>
+        <v>37.7</v>
       </c>
       <c r="H21" s="3">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="I21" s="4">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>73</v>
@@ -1279,25 +1282,25 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>7.15</v>
+        <v>6.94</v>
       </c>
       <c r="D22" s="3">
-        <v>7.38</v>
+        <v>7.42</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>459.4</v>
+        <v>472.7</v>
       </c>
       <c r="G22" s="2">
-        <v>26.5</v>
+        <v>27.2</v>
       </c>
       <c r="H22" s="3">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I22" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1311,28 +1314,28 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>22.86</v>
+        <v>22.55</v>
       </c>
       <c r="D23" s="3">
-        <v>31.45</v>
+        <v>27.7</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>321.6</v>
+        <v>316.3</v>
       </c>
       <c r="G23" s="2">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="H23" s="3">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="I23" s="4">
-        <v>75.0</v>
+        <v>78.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>79</v>
@@ -1355,19 +1358,19 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>70.8</v>
+        <v>71.2</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>72.0</v>
+        <v>81.0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>82</v>
@@ -1381,7 +1384,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>31.24</v>
+        <v>29.87</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1390,10 +1393,10 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>232.1</v>
+        <v>230.4</v>
       </c>
       <c r="G25" s="2">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="H25" s="3">
         <v>0.94</v>
@@ -1413,7 +1416,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>11.7</v>
+        <v>11.35</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1422,13 +1425,13 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>76.2</v>
+        <v>73.4</v>
       </c>
       <c r="G26" s="2">
-        <v>246.5</v>
+        <v>237.5</v>
       </c>
       <c r="H26" s="3">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="I26" s="4">
         <v>33.0</v>
@@ -1445,25 +1448,25 @@
         <v>90</v>
       </c>
       <c r="C27" s="3">
-        <v>22.16</v>
+        <v>20.06</v>
       </c>
       <c r="D27" s="3">
-        <v>33.18</v>
+        <v>31.46</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>197.2</v>
+        <v>184.5</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="I27" s="4">
-        <v>58.0</v>
+        <v>56.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>91</v>
@@ -1480,28 +1483,28 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.18</v>
+        <v>6.82</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
       </c>
       <c r="E28" s="3">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="F28" s="2">
-        <v>263.3</v>
+        <v>254.4</v>
       </c>
       <c r="G28" s="2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I28" s="4">
-        <v>55.0</v>
+        <v>42.0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>95</v>
@@ -1515,25 +1518,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>37.92</v>
+        <v>38.76</v>
       </c>
       <c r="D29" s="3">
-        <v>39.44</v>
+        <v>39.86</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>517.8</v>
+        <v>506.7</v>
       </c>
       <c r="G29" s="2">
-        <v>65.2</v>
+        <v>63.8</v>
       </c>
       <c r="H29" s="3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="I29" s="4">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="xyrDUfYSKRuK6e06aiEmpCBwQvvh1TXKhfJxdYxDUV8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="KjR9akEwbB95qOXZKMwcm3TcdnH0OpepmQSgcR1btsg="/>
     </ext>
   </extLst>
 </workbook>
@@ -129,7 +129,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(12/16/25) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -165,6 +165,9 @@
     <t>GILT</t>
   </si>
   <si>
+    <t>Approaching value limit</t>
+  </si>
+  <si>
     <t>News Archive for GILT</t>
   </si>
   <si>
@@ -282,16 +285,13 @@
     <t>SGA</t>
   </si>
   <si>
-    <t>(12/15/25) Saga Communications, Inc. (SGA)</t>
+    <t>News Archive for SGA</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
   </si>
   <si>
     <t>SDHC</t>
-  </si>
-  <si>
-    <t>TTM adjusted earnings positive Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for SDHC</t>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="G2" s="2">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="H2" s="3">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I2" s="4">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="D3" s="3">
         <v>6.62</v>
@@ -665,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>186.0</v>
+        <v>190.6</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="I3" s="4">
-        <v>72.0</v>
+        <v>79.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,25 +691,25 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="D4" s="3">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>36.0</v>
+        <v>56.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>21.29</v>
+        <v>21.28</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>180.2</v>
+        <v>176.6</v>
       </c>
       <c r="G5" s="2">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="I5" s="4">
-        <v>74.0</v>
+        <v>68.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>22.62</v>
+        <v>22.43</v>
       </c>
       <c r="D6" s="3">
         <v>29.47</v>
@@ -767,16 +767,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>574.8</v>
+        <v>566.8</v>
       </c>
       <c r="G6" s="2">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H6" s="3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="I6" s="4">
-        <v>41.0</v>
+        <v>35.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,16 +799,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>132.0</v>
+        <v>135.7</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="I7" s="4">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.07</v>
+        <v>18.29</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>472.0</v>
+        <v>464.7</v>
       </c>
       <c r="G8" s="2">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="H8" s="3">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="I8" s="4">
-        <v>42.0</v>
+        <v>39.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>12.79</v>
+        <v>13.38</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +866,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>180.1</v>
+        <v>182.5</v>
       </c>
       <c r="G9" s="2">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="H9" s="3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I9" s="4">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>54.01</v>
+        <v>54.41</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>378.6</v>
+        <v>381.7</v>
       </c>
       <c r="G10" s="2">
         <v>2.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I10" s="4">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>14.94</v>
+        <v>14.45</v>
       </c>
       <c r="D11" s="3">
         <v>17.62</v>
@@ -930,16 +930,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>99.1</v>
+        <v>95.2</v>
       </c>
       <c r="G11" s="2">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="H11" s="3">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="I11" s="4">
-        <v>49.0</v>
+        <v>43.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>21.41</v>
+        <v>20.67</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -965,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>151.8</v>
+        <v>147.9</v>
       </c>
       <c r="G12" s="2">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="H12" s="3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="I12" s="4">
-        <v>75.0</v>
+        <v>74.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,7 +988,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>11.81</v>
+        <v>12.59</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
@@ -997,30 +997,33 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>728.0</v>
+        <v>814.8</v>
       </c>
       <c r="G13" s="2">
-        <v>28.8</v>
+        <v>32.3</v>
       </c>
       <c r="H13" s="3">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="I13" s="4">
         <v>92.0</v>
       </c>
+      <c r="J13" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="K13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>28.52</v>
+        <v>29.21</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1029,65 +1032,65 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>689.0</v>
+        <v>705.3</v>
       </c>
       <c r="G14" s="2">
-        <v>29.5</v>
+        <v>30.2</v>
       </c>
       <c r="H14" s="3">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="I14" s="4">
         <v>86.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>7.94</v>
+        <v>8.64</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
       </c>
       <c r="E15" s="3">
-        <v>7.97</v>
+        <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>81.2</v>
+        <v>85.7</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="I15" s="4">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>12.8</v>
+        <v>13.16</v>
       </c>
       <c r="D16" s="3">
         <v>13.43</v>
@@ -1096,30 +1099,30 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>398.8</v>
+        <v>414.9</v>
       </c>
       <c r="G16" s="2">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="H16" s="3">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="I16" s="4">
-        <v>90.0</v>
+        <v>89.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>49.18</v>
+        <v>48.69</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1128,94 +1131,94 @@
         <v>27.47</v>
       </c>
       <c r="F17" s="2">
-        <v>375.7</v>
+        <v>363.9</v>
       </c>
       <c r="G17" s="2">
-        <v>13.0</v>
+        <v>12.6</v>
       </c>
       <c r="H17" s="3">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="I17" s="4">
-        <v>75.0</v>
+        <v>65.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>32.48</v>
+        <v>33.35</v>
       </c>
       <c r="D18" s="3">
-        <v>33.82</v>
+        <v>34.37</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>399.8</v>
+        <v>427.5</v>
       </c>
       <c r="G18" s="2">
-        <v>21.6</v>
+        <v>23.1</v>
       </c>
       <c r="H18" s="3">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="I18" s="4">
-        <v>64.0</v>
+        <v>75.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>39.8</v>
+        <v>40.41</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
       </c>
       <c r="E19" s="3">
-        <v>23.03</v>
+        <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>106.0</v>
+        <v>105.2</v>
       </c>
       <c r="G19" s="2">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
       <c r="H19" s="3">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="I19" s="4">
-        <v>75.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>6.87</v>
+        <v>6.78</v>
       </c>
       <c r="D20" s="3">
         <v>7.19</v>
@@ -1224,65 +1227,62 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>399.1</v>
+        <v>411.6</v>
       </c>
       <c r="G20" s="2">
-        <v>17.5</v>
+        <v>18.1</v>
       </c>
       <c r="H20" s="3">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="I20" s="4">
-        <v>66.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>75.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>43.65</v>
+        <v>44.77</v>
       </c>
       <c r="D21" s="3">
-        <v>44.85</v>
+        <v>45.41</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>493.6</v>
+        <v>498.7</v>
       </c>
       <c r="G21" s="2">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="H21" s="3">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I21" s="4">
-        <v>85.0</v>
+        <v>80.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>6.94</v>
+        <v>6.91</v>
       </c>
       <c r="D22" s="3">
         <v>7.42</v>
@@ -1291,65 +1291,65 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>472.7</v>
+        <v>452.2</v>
       </c>
       <c r="G22" s="2">
-        <v>27.2</v>
+        <v>26.1</v>
       </c>
       <c r="H22" s="3">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="I22" s="4">
-        <v>86.0</v>
+        <v>85.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>22.55</v>
+        <v>21.09</v>
       </c>
       <c r="D23" s="3">
-        <v>27.7</v>
+        <v>27.3</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>316.3</v>
+        <v>291.3</v>
       </c>
       <c r="G23" s="2">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="H23" s="3">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="I23" s="4">
-        <v>78.0</v>
+        <v>67.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>29.0</v>
+        <v>27.39</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1358,33 +1358,33 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>71.2</v>
+        <v>69.6</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I24" s="4">
-        <v>81.0</v>
+        <v>75.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>29.87</v>
+        <v>30.02</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1393,30 +1393,30 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>230.4</v>
+        <v>226.5</v>
       </c>
       <c r="G25" s="2">
-        <v>11.2</v>
+        <v>11.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="I25" s="4">
-        <v>83.0</v>
+        <v>81.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.35</v>
+        <v>11.44</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1425,7 +1425,7 @@
         <v>10.75</v>
       </c>
       <c r="F26" s="2">
-        <v>73.4</v>
+        <v>72.6</v>
       </c>
       <c r="G26" s="2">
         <v>237.5</v>
@@ -1434,42 +1434,42 @@
         <v>0.45</v>
       </c>
       <c r="I26" s="4">
-        <v>33.0</v>
+        <v>29.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>20.06</v>
+        <v>17.59</v>
       </c>
       <c r="D27" s="3">
-        <v>31.46</v>
+        <v>27.69</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>184.5</v>
+        <v>158.7</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="I27" s="4">
-        <v>56.0</v>
+        <v>37.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>92</v>
@@ -1483,16 +1483,16 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>6.82</v>
+        <v>7.01</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
       </c>
       <c r="E28" s="3">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>254.4</v>
+        <v>254.0</v>
       </c>
       <c r="G28" s="2">
         <v>3.6</v>
@@ -1501,7 +1501,7 @@
         <v>0.41</v>
       </c>
       <c r="I28" s="4">
-        <v>42.0</v>
+        <v>50.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1518,25 +1518,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>38.76</v>
+        <v>39.69</v>
       </c>
       <c r="D29" s="3">
-        <v>39.86</v>
+        <v>40.32</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>506.7</v>
+        <v>524.1</v>
       </c>
       <c r="G29" s="2">
-        <v>63.8</v>
+        <v>66.0</v>
       </c>
       <c r="H29" s="3">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="I29" s="4">
-        <v>85.0</v>
+        <v>82.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="KjR9akEwbB95qOXZKMwcm3TcdnH0OpepmQSgcR1btsg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OJ+A5WIT+hA9W7eGb/92miPC0x/8kHXIyB1wL4IZn4Y="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,7 +630,7 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>46.1</v>
+        <v>46.0</v>
       </c>
       <c r="G2" s="2">
         <v>13.1</v>
@@ -639,7 +639,7 @@
         <v>0.73</v>
       </c>
       <c r="I2" s="4">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="D3" s="3">
         <v>6.62</v>
@@ -665,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>190.6</v>
+        <v>185.0</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="I3" s="4">
-        <v>79.0</v>
+        <v>84.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,25 +691,25 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="D4" s="3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>22.8</v>
+        <v>20.0</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>56.0</v>
+        <v>39.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>21.28</v>
+        <v>19.46</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>176.6</v>
+        <v>171.7</v>
       </c>
       <c r="G5" s="2">
-        <v>22.3</v>
+        <v>21.7</v>
       </c>
       <c r="H5" s="3">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="I5" s="4">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>22.43</v>
+        <v>22.3</v>
       </c>
       <c r="D6" s="3">
         <v>29.47</v>
@@ -767,16 +767,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>566.8</v>
+        <v>552.0</v>
       </c>
       <c r="G6" s="2">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="H6" s="3">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="I6" s="4">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>6.67</v>
+        <v>6.85</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,7 +799,7 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>135.7</v>
+        <v>137.8</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
@@ -808,7 +808,7 @@
         <v>0.54</v>
       </c>
       <c r="I7" s="4">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.29</v>
+        <v>18.0</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>464.7</v>
+        <v>461.6</v>
       </c>
       <c r="G8" s="2">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I8" s="4">
-        <v>39.0</v>
+        <v>43.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.38</v>
+        <v>13.69</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +866,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>182.5</v>
+        <v>186.2</v>
       </c>
       <c r="G9" s="2">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I9" s="4">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>54.41</v>
+        <v>54.22</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,7 +898,7 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>381.7</v>
+        <v>382.6</v>
       </c>
       <c r="G10" s="2">
         <v>2.9</v>
@@ -907,7 +907,7 @@
         <v>1.02</v>
       </c>
       <c r="I10" s="4">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,25 +921,25 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>14.45</v>
+        <v>18.52</v>
       </c>
       <c r="D11" s="3">
-        <v>17.62</v>
+        <v>18.86</v>
       </c>
       <c r="E11" s="3">
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>95.2</v>
+        <v>121.6</v>
       </c>
       <c r="G11" s="2">
-        <v>13.4</v>
+        <v>17.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>43.0</v>
+        <v>72.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>20.67</v>
+        <v>20.24</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -965,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>147.9</v>
+        <v>145.7</v>
       </c>
       <c r="G12" s="2">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="H12" s="3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I12" s="4">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,7 +988,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>12.59</v>
+        <v>13.41</v>
       </c>
       <c r="D13" s="3">
         <v>15.24</v>
@@ -997,16 +997,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>814.8</v>
+        <v>831.5</v>
       </c>
       <c r="G13" s="2">
-        <v>32.3</v>
+        <v>32.9</v>
       </c>
       <c r="H13" s="3">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I13" s="4">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>29.21</v>
+        <v>28.79</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,16 +1032,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>705.3</v>
+        <v>677.1</v>
       </c>
       <c r="G14" s="2">
-        <v>30.2</v>
+        <v>29.0</v>
       </c>
       <c r="H14" s="3">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="I14" s="4">
-        <v>86.0</v>
+        <v>84.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1055,7 +1055,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>8.64</v>
+        <v>8.85</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1064,7 +1064,7 @@
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>85.7</v>
+        <v>86.7</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
@@ -1073,7 +1073,7 @@
         <v>0.64</v>
       </c>
       <c r="I15" s="4">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,7 +1090,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>13.16</v>
+        <v>12.92</v>
       </c>
       <c r="D16" s="3">
         <v>13.43</v>
@@ -1099,13 +1099,13 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>414.9</v>
+        <v>399.1</v>
       </c>
       <c r="G16" s="2">
-        <v>23.1</v>
+        <v>22.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="I16" s="4">
         <v>89.0</v>
@@ -1122,25 +1122,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>48.69</v>
+        <v>47.89</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
       </c>
       <c r="E17" s="3">
-        <v>27.47</v>
+        <v>29.54</v>
       </c>
       <c r="F17" s="2">
-        <v>363.9</v>
+        <v>365.8</v>
       </c>
       <c r="G17" s="2">
         <v>12.6</v>
       </c>
       <c r="H17" s="3">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I17" s="4">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1157,25 +1157,25 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>33.35</v>
+        <v>34.39</v>
       </c>
       <c r="D18" s="3">
-        <v>34.37</v>
+        <v>34.57</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>427.5</v>
+        <v>422.9</v>
       </c>
       <c r="G18" s="2">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="H18" s="3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I18" s="4">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1189,7 +1189,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>40.41</v>
+        <v>39.65</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1198,16 +1198,16 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>105.2</v>
+        <v>100.3</v>
       </c>
       <c r="G19" s="2">
-        <v>9.1</v>
+        <v>8.7</v>
       </c>
       <c r="H19" s="3">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="I19" s="4">
-        <v>78.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1218,7 +1218,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>6.78</v>
+        <v>7.07</v>
       </c>
       <c r="D20" s="3">
         <v>7.19</v>
@@ -1227,16 +1227,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>411.6</v>
+        <v>404.5</v>
       </c>
       <c r="G20" s="2">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="H20" s="3">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I20" s="4">
-        <v>75.0</v>
+        <v>73.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1250,7 +1250,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>44.77</v>
+        <v>43.87</v>
       </c>
       <c r="D21" s="3">
         <v>45.41</v>
@@ -1259,16 +1259,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>498.7</v>
+        <v>479.1</v>
       </c>
       <c r="G21" s="2">
-        <v>38.1</v>
+        <v>36.6</v>
       </c>
       <c r="H21" s="3">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="I21" s="4">
-        <v>80.0</v>
+        <v>76.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1282,7 +1282,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>6.91</v>
+        <v>6.68</v>
       </c>
       <c r="D22" s="3">
         <v>7.42</v>
@@ -1291,16 +1291,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>452.2</v>
+        <v>447.0</v>
       </c>
       <c r="G22" s="2">
-        <v>26.1</v>
+        <v>25.8</v>
       </c>
       <c r="H22" s="3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I22" s="4">
-        <v>85.0</v>
+        <v>83.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1314,7 +1314,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>21.09</v>
+        <v>20.79</v>
       </c>
       <c r="D23" s="3">
         <v>27.3</v>
@@ -1323,16 +1323,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>291.3</v>
+        <v>287.7</v>
       </c>
       <c r="G23" s="2">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H23" s="3">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I23" s="4">
-        <v>67.0</v>
+        <v>63.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1349,7 +1349,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>27.39</v>
+        <v>26.74</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1358,13 +1358,13 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>69.6</v>
+        <v>68.8</v>
       </c>
       <c r="G24" s="2">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I24" s="4">
         <v>75.0</v>
@@ -1384,7 +1384,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>30.02</v>
+        <v>28.67</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1393,16 +1393,19 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>226.5</v>
+        <v>219.8</v>
       </c>
       <c r="G25" s="2">
-        <v>11.0</v>
+        <v>10.7</v>
       </c>
       <c r="H25" s="3">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="I25" s="4">
-        <v>81.0</v>
+        <v>75.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1416,25 +1419,25 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.44</v>
+        <v>11.5</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
       </c>
       <c r="E26" s="3">
-        <v>10.75</v>
+        <v>10.8</v>
       </c>
       <c r="F26" s="2">
-        <v>72.6</v>
+        <v>73.0</v>
       </c>
       <c r="G26" s="2">
-        <v>237.5</v>
+        <v>238.5</v>
       </c>
       <c r="H26" s="3">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I26" s="4">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1448,25 +1451,25 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>17.59</v>
+        <v>16.85</v>
       </c>
       <c r="D27" s="3">
-        <v>27.69</v>
+        <v>26.23</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>158.7</v>
+        <v>151.2</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="I27" s="4">
-        <v>37.0</v>
+        <v>26.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -1483,7 +1486,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.01</v>
+        <v>7.04</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1492,16 +1495,16 @@
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>254.0</v>
+        <v>259.6</v>
       </c>
       <c r="G28" s="2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H28" s="3">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I28" s="4">
-        <v>50.0</v>
+        <v>56.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1518,7 +1521,7 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>39.69</v>
+        <v>39.28</v>
       </c>
       <c r="D29" s="3">
         <v>40.32</v>
@@ -1527,16 +1530,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>524.1</v>
+        <v>511.2</v>
       </c>
       <c r="G29" s="2">
-        <v>66.0</v>
+        <v>64.4</v>
       </c>
       <c r="H29" s="3">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="I29" s="4">
-        <v>82.0</v>
+        <v>81.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OJ+A5WIT+hA9W7eGb/92miPC0x/8kHXIyB1wL4IZn4Y="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ZB++cI3zmhD2KhUQTZjJf7M5lW/ze29pATb+fzczXjc="/>
     </ext>
   </extLst>
 </workbook>
@@ -165,7 +165,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Approaching value limit</t>
+    <t>Approaching size limit Exceeds value limit</t>
   </si>
   <si>
     <t>News Archive for GILT</t>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.55</v>
+        <v>4.66</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>46.0</v>
+        <v>48.3</v>
       </c>
       <c r="G2" s="2">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="H2" s="3">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="I2" s="4">
-        <v>35.0</v>
+        <v>39.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="D3" s="3">
         <v>6.62</v>
@@ -665,7 +665,7 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>185.0</v>
+        <v>185.4</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
@@ -674,7 +674,7 @@
         <v>0.47</v>
       </c>
       <c r="I3" s="4">
-        <v>84.0</v>
+        <v>81.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,16 +691,16 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="D4" s="3">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>20.0</v>
+        <v>20.4</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -709,7 +709,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>39.0</v>
+        <v>30.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>19.46</v>
+        <v>19.17</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>171.7</v>
+        <v>168.5</v>
       </c>
       <c r="G5" s="2">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="I5" s="4">
-        <v>69.0</v>
+        <v>64.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>22.3</v>
+        <v>25.21</v>
       </c>
       <c r="D6" s="3">
         <v>29.47</v>
@@ -767,16 +767,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>552.0</v>
+        <v>630.4</v>
       </c>
       <c r="G6" s="2">
-        <v>20.6</v>
+        <v>23.5</v>
       </c>
       <c r="H6" s="3">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="I6" s="4">
-        <v>29.0</v>
+        <v>41.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>6.85</v>
+        <v>7.38</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,16 +799,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>137.8</v>
+        <v>149.1</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="I7" s="4">
-        <v>22.0</v>
+        <v>27.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.0</v>
+        <v>18.43</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>461.6</v>
+        <v>464.2</v>
       </c>
       <c r="G8" s="2">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="H8" s="3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="4">
-        <v>43.0</v>
+        <v>40.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.69</v>
+        <v>13.72</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +866,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>186.2</v>
+        <v>194.6</v>
       </c>
       <c r="G9" s="2">
-        <v>14.7</v>
+        <v>15.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="I9" s="4">
-        <v>38.0</v>
+        <v>43.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>54.22</v>
+        <v>55.06</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>382.6</v>
+        <v>385.0</v>
       </c>
       <c r="G10" s="2">
-        <v>2.9</v>
+        <v>3.0</v>
       </c>
       <c r="H10" s="3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I10" s="4">
-        <v>70.0</v>
+        <v>66.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.52</v>
+        <v>18.55</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -939,7 +939,7 @@
         <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>72.0</v>
+        <v>65.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>20.24</v>
+        <v>19.69</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -965,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>145.7</v>
+        <v>138.8</v>
       </c>
       <c r="G12" s="2">
-        <v>12.6</v>
+        <v>12.0</v>
       </c>
       <c r="H12" s="3">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="I12" s="4">
-        <v>75.0</v>
+        <v>64.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,25 +988,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>13.41</v>
+        <v>15.06</v>
       </c>
       <c r="D13" s="3">
-        <v>15.24</v>
+        <v>15.25</v>
       </c>
       <c r="E13" s="3">
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>831.5</v>
+        <v>1097.9</v>
       </c>
       <c r="G13" s="2">
-        <v>32.9</v>
+        <v>38.2</v>
       </c>
       <c r="H13" s="3">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="I13" s="4">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>28.79</v>
+        <v>28.35</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,13 +1032,13 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>677.1</v>
+        <v>689.7</v>
       </c>
       <c r="G14" s="2">
-        <v>29.0</v>
+        <v>29.5</v>
       </c>
       <c r="H14" s="3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="I14" s="4">
         <v>84.0</v>
@@ -1055,7 +1055,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>8.85</v>
+        <v>8.87</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1064,7 +1064,7 @@
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>86.7</v>
+        <v>86.3</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
@@ -1073,7 +1073,7 @@
         <v>0.64</v>
       </c>
       <c r="I15" s="4">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,25 +1090,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>12.92</v>
+        <v>13.75</v>
       </c>
       <c r="D16" s="3">
-        <v>13.43</v>
+        <v>13.76</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>399.1</v>
+        <v>424.6</v>
       </c>
       <c r="G16" s="2">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="H16" s="3">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="I16" s="4">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1122,25 +1122,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>47.89</v>
+        <v>47.56</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
       </c>
       <c r="E17" s="3">
-        <v>29.54</v>
+        <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>365.8</v>
+        <v>356.6</v>
       </c>
       <c r="G17" s="2">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="I17" s="4">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1160,22 +1160,22 @@
         <v>34.39</v>
       </c>
       <c r="D18" s="3">
-        <v>34.57</v>
+        <v>35.01</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>422.9</v>
+        <v>438.5</v>
       </c>
       <c r="G18" s="2">
-        <v>22.9</v>
+        <v>23.7</v>
       </c>
       <c r="H18" s="3">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="I18" s="4">
-        <v>80.0</v>
+        <v>83.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1189,7 +1189,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>39.65</v>
+        <v>37.77</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1198,16 +1198,19 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>100.3</v>
+        <v>97.0</v>
       </c>
       <c r="G19" s="2">
-        <v>8.7</v>
+        <v>8.4</v>
       </c>
       <c r="H19" s="3">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="I19" s="4">
-        <v>81.0</v>
+        <v>76.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1218,25 +1221,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>7.07</v>
+        <v>8.04</v>
       </c>
       <c r="D20" s="3">
-        <v>7.19</v>
+        <v>8.01</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>404.5</v>
+        <v>473.8</v>
       </c>
       <c r="G20" s="2">
-        <v>17.8</v>
+        <v>20.8</v>
       </c>
       <c r="H20" s="3">
-        <v>0.59</v>
+        <v>0.69</v>
       </c>
       <c r="I20" s="4">
-        <v>73.0</v>
+        <v>83.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1250,25 +1253,25 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>43.87</v>
+        <v>48.09</v>
       </c>
       <c r="D21" s="3">
-        <v>45.41</v>
+        <v>47.14</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>479.1</v>
+        <v>523.9</v>
       </c>
       <c r="G21" s="2">
-        <v>36.6</v>
+        <v>40.0</v>
       </c>
       <c r="H21" s="3">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="4">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1282,7 +1285,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>6.68</v>
+        <v>6.82</v>
       </c>
       <c r="D22" s="3">
         <v>7.42</v>
@@ -1291,16 +1294,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>447.0</v>
+        <v>445.1</v>
       </c>
       <c r="G22" s="2">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="H22" s="3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I22" s="4">
-        <v>83.0</v>
+        <v>79.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1314,25 +1317,25 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>20.79</v>
+        <v>22.41</v>
       </c>
       <c r="D23" s="3">
-        <v>27.3</v>
+        <v>26.31</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>287.7</v>
+        <v>299.8</v>
       </c>
       <c r="G23" s="2">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H23" s="3">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="4">
-        <v>63.0</v>
+        <v>68.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1349,7 +1352,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>26.74</v>
+        <v>25.0</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1358,16 +1361,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>68.8</v>
+        <v>59.5</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="I24" s="4">
-        <v>75.0</v>
+        <v>47.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1384,7 +1387,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>28.67</v>
+        <v>30.43</v>
       </c>
       <c r="D25" s="3">
         <v>33.4</v>
@@ -1393,19 +1396,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>219.8</v>
+        <v>228.3</v>
       </c>
       <c r="G25" s="2">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="H25" s="3">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="I25" s="4">
-        <v>75.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>13</v>
+        <v>74.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1419,25 +1419,25 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.5</v>
+        <v>11.06</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
       </c>
       <c r="E26" s="3">
-        <v>10.8</v>
+        <v>10.68</v>
       </c>
       <c r="F26" s="2">
-        <v>73.0</v>
+        <v>70.7</v>
       </c>
       <c r="G26" s="2">
-        <v>238.5</v>
+        <v>231.3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I26" s="4">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1451,25 +1451,25 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>16.85</v>
+        <v>19.29</v>
       </c>
       <c r="D27" s="3">
-        <v>26.23</v>
+        <v>26.12</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>151.2</v>
+        <v>157.7</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="I27" s="4">
-        <v>26.0</v>
+        <v>23.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -1486,7 +1486,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.04</v>
+        <v>7.86</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1495,16 +1495,16 @@
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>259.6</v>
+        <v>289.2</v>
       </c>
       <c r="G28" s="2">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="H28" s="3">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="I28" s="4">
-        <v>56.0</v>
+        <v>67.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1521,25 +1521,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>39.28</v>
+        <v>41.67</v>
       </c>
       <c r="D29" s="3">
-        <v>40.32</v>
+        <v>41.65</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>511.2</v>
+        <v>536.2</v>
       </c>
       <c r="G29" s="2">
-        <v>64.4</v>
+        <v>67.5</v>
       </c>
       <c r="H29" s="3">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="I29" s="4">
-        <v>81.0</v>
+        <v>83.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ZB++cI3zmhD2KhUQTZjJf7M5lW/ze29pATb+fzczXjc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6dqTGRMwibUn3uGGNfdzRIbHzmjLOEH4YMlg2nAKxWY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="100">
   <si>
     <t>Company</t>
   </si>
@@ -165,7 +165,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Approaching size limit Exceeds value limit</t>
+    <t>Exceeds size limit Exceeds value limit</t>
   </si>
   <si>
     <t>News Archive for GILT</t>
@@ -243,7 +243,7 @@
     <t>News Archive for ZEUS</t>
   </si>
   <si>
-    <t>Pangaea Logistics Solutions, Ltd.</t>
+    <t>Pangaea Logistics Solutions Ltd.</t>
   </si>
   <si>
     <t>PANL</t>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>SDHC</t>
+  </si>
+  <si>
+    <t>TTM adjusted earnings positive Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for SDHC</t>
@@ -621,7 +624,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.66</v>
+        <v>4.73</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +633,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.3</v>
+        <v>48.8</v>
       </c>
       <c r="G2" s="2">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H2" s="3">
         <v>0.77</v>
       </c>
       <c r="I2" s="4">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,25 +659,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.59</v>
+        <v>4.78</v>
       </c>
       <c r="D3" s="3">
-        <v>6.62</v>
+        <v>6.55</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>185.4</v>
+        <v>194.3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="I3" s="4">
-        <v>81.0</v>
+        <v>84.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="D4" s="3">
         <v>2.92</v>
@@ -709,7 +712,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +729,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>19.17</v>
+        <v>18.82</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +738,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>168.5</v>
+        <v>161.9</v>
       </c>
       <c r="G5" s="2">
-        <v>21.3</v>
+        <v>20.4</v>
       </c>
       <c r="H5" s="3">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="I5" s="4">
-        <v>64.0</v>
+        <v>60.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,7 +761,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>25.21</v>
+        <v>25.89</v>
       </c>
       <c r="D6" s="3">
         <v>29.47</v>
@@ -767,16 +770,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>630.4</v>
+        <v>654.2</v>
       </c>
       <c r="G6" s="2">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="H6" s="3">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="I6" s="4">
-        <v>41.0</v>
+        <v>53.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +793,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>7.38</v>
+        <v>8.44</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,16 +802,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>149.1</v>
+        <v>177.3</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="I7" s="4">
-        <v>27.0</v>
+        <v>53.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +828,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>18.43</v>
+        <v>19.27</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +837,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>464.2</v>
+        <v>485.1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="H8" s="3">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="I8" s="4">
-        <v>40.0</v>
+        <v>53.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +860,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>13.72</v>
+        <v>14.06</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +869,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>194.6</v>
+        <v>193.0</v>
       </c>
       <c r="G9" s="2">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="H9" s="3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I9" s="4">
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +892,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>55.06</v>
+        <v>53.87</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,7 +901,7 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>385.0</v>
+        <v>386.4</v>
       </c>
       <c r="G10" s="2">
         <v>3.0</v>
@@ -907,7 +910,7 @@
         <v>1.03</v>
       </c>
       <c r="I10" s="4">
-        <v>66.0</v>
+        <v>58.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,7 +924,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.55</v>
+        <v>18.64</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -930,16 +933,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.6</v>
+        <v>122.1</v>
       </c>
       <c r="G11" s="2">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="H11" s="3">
         <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +959,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.69</v>
+        <v>19.4</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -965,16 +968,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>138.8</v>
+        <v>145.2</v>
       </c>
       <c r="G12" s="2">
-        <v>12.0</v>
+        <v>12.5</v>
       </c>
       <c r="H12" s="3">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="I12" s="4">
-        <v>64.0</v>
+        <v>77.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,25 +991,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>15.06</v>
+        <v>17.86</v>
       </c>
       <c r="D13" s="3">
-        <v>15.25</v>
+        <v>17.89</v>
       </c>
       <c r="E13" s="3">
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1097.9</v>
+        <v>1292.5</v>
       </c>
       <c r="G13" s="2">
-        <v>38.2</v>
+        <v>45.0</v>
       </c>
       <c r="H13" s="3">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="I13" s="4">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1026,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>28.35</v>
+        <v>30.83</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,16 +1035,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>689.7</v>
+        <v>763.7</v>
       </c>
       <c r="G14" s="2">
-        <v>29.5</v>
+        <v>32.7</v>
       </c>
       <c r="H14" s="3">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="I14" s="4">
-        <v>84.0</v>
+        <v>89.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1055,7 +1058,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>8.87</v>
+        <v>9.34</v>
       </c>
       <c r="D15" s="3">
         <v>27.28</v>
@@ -1064,16 +1067,16 @@
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>86.3</v>
+        <v>91.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I15" s="4">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,25 +1093,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>13.75</v>
+        <v>14.46</v>
       </c>
       <c r="D16" s="3">
-        <v>13.76</v>
+        <v>14.42</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>424.6</v>
+        <v>451.8</v>
       </c>
       <c r="G16" s="2">
-        <v>23.6</v>
+        <v>25.1</v>
       </c>
       <c r="H16" s="3">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="I16" s="4">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1122,7 +1125,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>47.56</v>
+        <v>46.22</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1131,16 +1134,16 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>356.6</v>
+        <v>346.7</v>
       </c>
       <c r="G17" s="2">
-        <v>12.3</v>
+        <v>12.0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="I17" s="4">
-        <v>67.0</v>
+        <v>63.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1157,25 +1160,25 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>34.39</v>
+        <v>33.64</v>
       </c>
       <c r="D18" s="3">
-        <v>35.01</v>
+        <v>35.12</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>438.5</v>
+        <v>429.9</v>
       </c>
       <c r="G18" s="2">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="H18" s="3">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="I18" s="4">
-        <v>83.0</v>
+        <v>81.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1189,7 +1192,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>37.77</v>
+        <v>39.91</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1198,19 +1201,16 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>97.0</v>
+        <v>99.7</v>
       </c>
       <c r="G19" s="2">
-        <v>8.4</v>
+        <v>8.7</v>
       </c>
       <c r="H19" s="3">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I19" s="4">
-        <v>76.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1221,25 +1221,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>8.04</v>
+        <v>8.18</v>
       </c>
       <c r="D20" s="3">
-        <v>8.01</v>
+        <v>8.28</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>473.8</v>
+        <v>489.3</v>
       </c>
       <c r="G20" s="2">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="H20" s="3">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="I20" s="4">
-        <v>83.0</v>
+        <v>87.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1253,25 +1253,25 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>48.09</v>
+        <v>48.97</v>
       </c>
       <c r="D21" s="3">
-        <v>47.14</v>
+        <v>50.87</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>523.9</v>
+        <v>568.7</v>
       </c>
       <c r="G21" s="2">
-        <v>40.0</v>
+        <v>43.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="I21" s="4">
-        <v>80.0</v>
+        <v>86.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1285,7 +1285,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>6.82</v>
+        <v>6.7</v>
       </c>
       <c r="D22" s="3">
         <v>7.42</v>
@@ -1294,13 +1294,13 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>445.1</v>
+        <v>455.5</v>
       </c>
       <c r="G22" s="2">
-        <v>25.7</v>
+        <v>26.3</v>
       </c>
       <c r="H22" s="3">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="I22" s="4">
         <v>79.0</v>
@@ -1317,7 +1317,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>22.41</v>
+        <v>23.03</v>
       </c>
       <c r="D23" s="3">
         <v>26.31</v>
@@ -1326,16 +1326,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>299.8</v>
+        <v>319.3</v>
       </c>
       <c r="G23" s="2">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="H23" s="3">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="I23" s="4">
-        <v>68.0</v>
+        <v>77.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1352,7 +1352,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>25.0</v>
+        <v>23.75</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1361,16 +1361,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>59.5</v>
+        <v>61.5</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="I24" s="4">
-        <v>47.0</v>
+        <v>51.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1387,25 +1387,25 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>30.43</v>
+        <v>32.35</v>
       </c>
       <c r="D25" s="3">
-        <v>33.4</v>
+        <v>33.53</v>
       </c>
       <c r="E25" s="3">
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>228.3</v>
+        <v>247.4</v>
       </c>
       <c r="G25" s="2">
-        <v>11.1</v>
+        <v>12.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.93</v>
+        <v>1.0</v>
       </c>
       <c r="I25" s="4">
-        <v>74.0</v>
+        <v>82.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1419,7 +1419,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.06</v>
+        <v>11.31</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1428,16 +1428,16 @@
         <v>10.68</v>
       </c>
       <c r="F26" s="2">
-        <v>70.7</v>
+        <v>72.9</v>
       </c>
       <c r="G26" s="2">
-        <v>231.3</v>
+        <v>238.3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="I26" s="4">
-        <v>22.0</v>
+        <v>27.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1451,7 +1451,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>19.29</v>
+        <v>20.9</v>
       </c>
       <c r="D27" s="3">
         <v>26.12</v>
@@ -1460,33 +1460,33 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>157.7</v>
+        <v>198.8</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="I27" s="4">
-        <v>23.0</v>
+        <v>57.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" s="3">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1495,13 +1495,13 @@
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>289.2</v>
+        <v>291.8</v>
       </c>
       <c r="G28" s="2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H28" s="3">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="I28" s="4">
         <v>67.0</v>
@@ -1510,39 +1510,39 @@
         <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" s="3">
-        <v>41.67</v>
+        <v>43.61</v>
       </c>
       <c r="D29" s="3">
-        <v>41.65</v>
+        <v>44.4</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>536.2</v>
+        <v>580.3</v>
       </c>
       <c r="G29" s="2">
-        <v>67.5</v>
+        <v>73.1</v>
       </c>
       <c r="H29" s="3">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="I29" s="4">
-        <v>83.0</v>
+        <v>88.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6dqTGRMwibUn3uGGNfdzRIbHzmjLOEH4YMlg2nAKxWY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BHeUnKMRnKZG0Ijy2nKhZ4VPBeI/Sof9Z3kU18EAMWE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -168,7 +168,7 @@
     <t>Exceeds size limit Exceeds value limit</t>
   </si>
   <si>
-    <t>News Archive for GILT</t>
+    <t>(1/20/26) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -294,10 +294,7 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>TTM adjusted earnings positive Approaching value limit</t>
-  </si>
-  <si>
-    <t>News Archive for SDHC</t>
+    <t>(1/17/26) Smith Douglas Homes Corp. (SDHC)</t>
   </si>
   <si>
     <t>StealthGas Inc.</t>
@@ -642,7 +639,7 @@
         <v>0.77</v>
       </c>
       <c r="I2" s="4">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -659,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -668,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>194.3</v>
+        <v>187.0</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="I3" s="4">
-        <v>84.0</v>
+        <v>68.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -694,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="D4" s="3">
         <v>2.92</v>
@@ -712,7 +709,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -729,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.82</v>
+        <v>18.7</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -738,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>161.9</v>
+        <v>166.3</v>
       </c>
       <c r="G5" s="2">
-        <v>20.4</v>
+        <v>21.0</v>
       </c>
       <c r="H5" s="3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I5" s="4">
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -761,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>25.89</v>
+        <v>26.59</v>
       </c>
       <c r="D6" s="3">
         <v>29.47</v>
@@ -770,16 +767,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>654.2</v>
+        <v>678.0</v>
       </c>
       <c r="G6" s="2">
-        <v>24.4</v>
+        <v>25.3</v>
       </c>
       <c r="H6" s="3">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="I6" s="4">
-        <v>53.0</v>
+        <v>59.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -793,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.44</v>
+        <v>8.57</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -802,16 +799,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>177.3</v>
+        <v>181.0</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="I7" s="4">
-        <v>53.0</v>
+        <v>43.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -828,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -837,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>485.1</v>
+        <v>498.3</v>
       </c>
       <c r="G8" s="2">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="H8" s="3">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="I8" s="4">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -860,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.06</v>
+        <v>14.14</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -869,13 +866,13 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>193.0</v>
+        <v>198.9</v>
       </c>
       <c r="G9" s="2">
-        <v>15.2</v>
+        <v>15.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I9" s="4">
         <v>56.0</v>
@@ -892,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>53.87</v>
+        <v>53.34</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -901,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>386.4</v>
+        <v>376.7</v>
       </c>
       <c r="G10" s="2">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.03</v>
+        <v>1.0</v>
       </c>
       <c r="I10" s="4">
-        <v>58.0</v>
+        <v>52.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -924,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.64</v>
+        <v>18.61</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -933,7 +930,7 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>122.1</v>
+        <v>122.0</v>
       </c>
       <c r="G11" s="2">
         <v>17.2</v>
@@ -942,7 +939,7 @@
         <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>64.0</v>
+        <v>63.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -959,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.4</v>
+        <v>19.41</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -968,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>145.2</v>
+        <v>139.8</v>
       </c>
       <c r="G12" s="2">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="H12" s="3">
-        <v>1.03</v>
+        <v>1.0</v>
       </c>
       <c r="I12" s="4">
-        <v>77.0</v>
+        <v>70.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -991,22 +988,22 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>17.86</v>
+        <v>18.65</v>
       </c>
       <c r="D13" s="3">
-        <v>17.89</v>
+        <v>18.45</v>
       </c>
       <c r="E13" s="3">
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1292.5</v>
+        <v>1348.0</v>
       </c>
       <c r="G13" s="2">
-        <v>45.0</v>
+        <v>46.9</v>
       </c>
       <c r="H13" s="3">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="I13" s="4">
         <v>96.0</v>
@@ -1026,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>30.83</v>
+        <v>29.62</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1035,16 +1032,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>763.7</v>
+        <v>754.5</v>
       </c>
       <c r="G14" s="2">
-        <v>32.7</v>
+        <v>32.3</v>
       </c>
       <c r="H14" s="3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I14" s="4">
-        <v>89.0</v>
+        <v>88.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1058,16 +1055,16 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.34</v>
+        <v>9.22</v>
       </c>
       <c r="D15" s="3">
-        <v>27.28</v>
+        <v>25.53</v>
       </c>
       <c r="E15" s="3">
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>91.5</v>
+        <v>91.4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
@@ -1076,7 +1073,7 @@
         <v>0.68</v>
       </c>
       <c r="I15" s="4">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1093,25 +1090,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>14.46</v>
+        <v>14.15</v>
       </c>
       <c r="D16" s="3">
-        <v>14.42</v>
+        <v>14.7</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>451.8</v>
+        <v>454.0</v>
       </c>
       <c r="G16" s="2">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.99</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="4">
-        <v>92.0</v>
+        <v>91.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1125,7 +1122,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>46.22</v>
+        <v>48.95</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1134,16 +1131,16 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>346.7</v>
+        <v>372.1</v>
       </c>
       <c r="G17" s="2">
-        <v>12.0</v>
+        <v>12.9</v>
       </c>
       <c r="H17" s="3">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="I17" s="4">
-        <v>63.0</v>
+        <v>71.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1160,7 +1157,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>33.64</v>
+        <v>34.9</v>
       </c>
       <c r="D18" s="3">
         <v>35.12</v>
@@ -1169,16 +1166,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>429.9</v>
+        <v>435.1</v>
       </c>
       <c r="G18" s="2">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="H18" s="3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I18" s="4">
-        <v>81.0</v>
+        <v>83.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1192,7 +1189,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>39.91</v>
+        <v>39.52</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1201,16 +1198,16 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>99.7</v>
+        <v>102.9</v>
       </c>
       <c r="G19" s="2">
-        <v>8.7</v>
+        <v>8.9</v>
       </c>
       <c r="H19" s="3">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I19" s="4">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1221,25 +1218,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>8.18</v>
+        <v>8.46</v>
       </c>
       <c r="D20" s="3">
-        <v>8.28</v>
+        <v>8.56</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>489.3</v>
+        <v>510.2</v>
       </c>
       <c r="G20" s="2">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="H20" s="3">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="I20" s="4">
-        <v>87.0</v>
+        <v>86.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1253,25 +1250,25 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>48.97</v>
+        <v>49.99</v>
       </c>
       <c r="D21" s="3">
-        <v>50.87</v>
+        <v>51.82</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>568.7</v>
+        <v>577.5</v>
       </c>
       <c r="G21" s="2">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="H21" s="3">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I21" s="4">
-        <v>86.0</v>
+        <v>84.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1285,25 +1282,25 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>6.7</v>
+        <v>8.16</v>
       </c>
       <c r="D22" s="3">
-        <v>7.42</v>
+        <v>9.17</v>
       </c>
       <c r="E22" s="3">
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>455.5</v>
+        <v>539.9</v>
       </c>
       <c r="G22" s="2">
-        <v>26.3</v>
+        <v>31.1</v>
       </c>
       <c r="H22" s="3">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="I22" s="4">
-        <v>79.0</v>
+        <v>89.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1317,7 +1314,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>23.03</v>
+        <v>22.96</v>
       </c>
       <c r="D23" s="3">
         <v>26.31</v>
@@ -1326,16 +1323,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>319.3</v>
+        <v>322.0</v>
       </c>
       <c r="G23" s="2">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H23" s="3">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I23" s="4">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1352,7 +1349,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>23.75</v>
+        <v>24.98</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1361,16 +1358,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>61.5</v>
+        <v>61.3</v>
       </c>
       <c r="G24" s="2">
         <v>0.6</v>
       </c>
       <c r="H24" s="3">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="I24" s="4">
-        <v>51.0</v>
+        <v>63.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1387,22 +1384,22 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>32.35</v>
+        <v>33.2</v>
       </c>
       <c r="D25" s="3">
-        <v>33.53</v>
+        <v>34.36</v>
       </c>
       <c r="E25" s="3">
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>247.4</v>
+        <v>251.3</v>
       </c>
       <c r="G25" s="2">
-        <v>12.0</v>
+        <v>12.2</v>
       </c>
       <c r="H25" s="3">
-        <v>1.0</v>
+        <v>1.02</v>
       </c>
       <c r="I25" s="4">
         <v>82.0</v>
@@ -1419,7 +1416,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.31</v>
+        <v>11.21</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1428,10 +1425,10 @@
         <v>10.68</v>
       </c>
       <c r="F26" s="2">
-        <v>72.9</v>
+        <v>72.0</v>
       </c>
       <c r="G26" s="2">
-        <v>238.3</v>
+        <v>235.4</v>
       </c>
       <c r="H26" s="3">
         <v>0.45</v>
@@ -1451,42 +1448,42 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>20.9</v>
+        <v>19.19</v>
       </c>
       <c r="D27" s="3">
-        <v>26.12</v>
+        <v>25.46</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>198.8</v>
+        <v>184.0</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="I27" s="4">
-        <v>57.0</v>
+        <v>32.0</v>
       </c>
       <c r="J27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="C28" s="3">
-        <v>7.84</v>
+        <v>7.74</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1495,54 +1492,54 @@
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>291.8</v>
+        <v>286.6</v>
       </c>
       <c r="G28" s="2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H28" s="3">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I28" s="4">
-        <v>67.0</v>
+        <v>62.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="C29" s="3">
-        <v>43.61</v>
+        <v>44.14</v>
       </c>
       <c r="D29" s="3">
-        <v>44.4</v>
+        <v>50.5</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>580.3</v>
+        <v>634.6</v>
       </c>
       <c r="G29" s="2">
-        <v>73.1</v>
+        <v>79.9</v>
       </c>
       <c r="H29" s="3">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="I29" s="4">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BHeUnKMRnKZG0Ijy2nKhZ4VPBeI/Sof9Z3kU18EAMWE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="irW5rFt7Ju2tX2PK9KLkM4C00HssQ88atBXcbePte6o="/>
     </ext>
   </extLst>
 </workbook>
@@ -102,7 +102,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>News Archive for CVLG</t>
+    <t>(1/29/26) Covenant Logistics Group, Inc. (CVLG)</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -168,7 +168,7 @@
     <t>Exceeds size limit Exceeds value limit</t>
   </si>
   <si>
-    <t>(1/20/26) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>News Archive for GILT</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -294,7 +294,7 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>(1/17/26) Smith Douglas Homes Corp. (SDHC)</t>
+    <t>News Archive for SDHC</t>
   </si>
   <si>
     <t>StealthGas Inc.</t>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.73</v>
+        <v>5.04</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>48.8</v>
+        <v>51.4</v>
       </c>
       <c r="G2" s="2">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="H2" s="3">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="I2" s="4">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.71</v>
+        <v>5.02</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -665,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>187.0</v>
+        <v>195.5</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="I3" s="4">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="D4" s="3">
         <v>2.92</v>
@@ -700,16 +700,16 @@
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>20.4</v>
+        <v>22.8</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>30.0</v>
+        <v>65.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.7</v>
+        <v>19.52</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,7 +735,7 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>166.3</v>
+        <v>161.0</v>
       </c>
       <c r="G5" s="2">
         <v>21.0</v>
@@ -744,7 +744,7 @@
         <v>1.07</v>
       </c>
       <c r="I5" s="4">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,25 +758,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>26.59</v>
+        <v>24.6</v>
       </c>
       <c r="D6" s="3">
-        <v>29.47</v>
+        <v>28.5</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>678.0</v>
+        <v>636.2</v>
       </c>
       <c r="G6" s="2">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="H6" s="3">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="I6" s="4">
-        <v>59.0</v>
+        <v>50.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.57</v>
+        <v>8.6</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,16 +799,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>181.0</v>
+        <v>179.8</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I7" s="4">
-        <v>43.0</v>
+        <v>55.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>19.32</v>
+        <v>19.49</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>498.3</v>
+        <v>480.1</v>
       </c>
       <c r="G8" s="2">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="I8" s="4">
-        <v>55.0</v>
+        <v>51.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.14</v>
+        <v>14.54</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +866,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>198.9</v>
+        <v>194.6</v>
       </c>
       <c r="G9" s="2">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="H9" s="3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I9" s="4">
-        <v>56.0</v>
+        <v>60.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>53.34</v>
+        <v>57.18</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>376.7</v>
+        <v>398.5</v>
       </c>
       <c r="G10" s="2">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H10" s="3">
-        <v>1.0</v>
+        <v>1.08</v>
       </c>
       <c r="I10" s="4">
-        <v>52.0</v>
+        <v>58.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.61</v>
+        <v>18.64</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -930,7 +930,7 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>122.0</v>
+        <v>122.2</v>
       </c>
       <c r="G11" s="2">
         <v>17.2</v>
@@ -939,7 +939,7 @@
         <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.41</v>
+        <v>19.63</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -965,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>139.8</v>
+        <v>132.4</v>
       </c>
       <c r="G12" s="2">
-        <v>12.1</v>
+        <v>12.0</v>
       </c>
       <c r="H12" s="3">
-        <v>1.0</v>
+        <v>0.99</v>
       </c>
       <c r="I12" s="4">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,25 +988,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>18.65</v>
+        <v>19.29</v>
       </c>
       <c r="D13" s="3">
-        <v>18.45</v>
+        <v>20.1</v>
       </c>
       <c r="E13" s="3">
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1348.0</v>
+        <v>1460.7</v>
       </c>
       <c r="G13" s="2">
-        <v>46.9</v>
+        <v>50.8</v>
       </c>
       <c r="H13" s="3">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="I13" s="4">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>29.62</v>
+        <v>30.21</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,13 +1032,13 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>754.5</v>
+        <v>707.0</v>
       </c>
       <c r="G14" s="2">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="H14" s="3">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="I14" s="4">
         <v>88.0</v>
@@ -1055,7 +1055,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.22</v>
+        <v>9.42</v>
       </c>
       <c r="D15" s="3">
         <v>25.53</v>
@@ -1064,16 +1064,16 @@
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>91.4</v>
+        <v>88.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I15" s="4">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,7 +1090,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="D16" s="3">
         <v>14.7</v>
@@ -1099,13 +1099,13 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>454.0</v>
+        <v>438.2</v>
       </c>
       <c r="G16" s="2">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="H16" s="3">
-        <v>2.0</v>
+        <v>1.96</v>
       </c>
       <c r="I16" s="4">
         <v>91.0</v>
@@ -1122,7 +1122,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>48.95</v>
+        <v>49.23</v>
       </c>
       <c r="D17" s="3">
         <v>53.88</v>
@@ -1131,16 +1131,16 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>372.1</v>
+        <v>356.2</v>
       </c>
       <c r="G17" s="2">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="H17" s="3">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="I17" s="4">
-        <v>71.0</v>
+        <v>69.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1157,16 +1157,16 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>34.9</v>
+        <v>34.64</v>
       </c>
       <c r="D18" s="3">
-        <v>35.12</v>
+        <v>35.57</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>435.1</v>
+        <v>419.4</v>
       </c>
       <c r="G18" s="2">
         <v>23.5</v>
@@ -1175,7 +1175,7 @@
         <v>1.6</v>
       </c>
       <c r="I18" s="4">
-        <v>83.0</v>
+        <v>82.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1189,7 +1189,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>39.52</v>
+        <v>39.88</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1198,16 +1198,16 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>102.9</v>
+        <v>102.3</v>
       </c>
       <c r="G19" s="2">
-        <v>8.9</v>
+        <v>8.8</v>
       </c>
       <c r="H19" s="3">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I19" s="4">
-        <v>80.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1218,19 +1218,19 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>8.46</v>
+        <v>8.47</v>
       </c>
       <c r="D20" s="3">
-        <v>8.56</v>
+        <v>8.88</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>510.2</v>
+        <v>501.3</v>
       </c>
       <c r="G20" s="2">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="H20" s="3">
         <v>0.74</v>
@@ -1250,7 +1250,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>49.99</v>
+        <v>48.09</v>
       </c>
       <c r="D21" s="3">
         <v>51.82</v>
@@ -1259,16 +1259,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>577.5</v>
+        <v>528.4</v>
       </c>
       <c r="G21" s="2">
-        <v>43.8</v>
+        <v>41.1</v>
       </c>
       <c r="H21" s="3">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="I21" s="4">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1282,7 +1282,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>8.16</v>
+        <v>8.48</v>
       </c>
       <c r="D22" s="3">
         <v>9.17</v>
@@ -1291,16 +1291,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>539.9</v>
+        <v>547.1</v>
       </c>
       <c r="G22" s="2">
-        <v>31.1</v>
+        <v>31.8</v>
       </c>
       <c r="H22" s="3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="I22" s="4">
-        <v>89.0</v>
+        <v>91.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1314,7 +1314,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>22.96</v>
+        <v>22.56</v>
       </c>
       <c r="D23" s="3">
         <v>26.31</v>
@@ -1323,13 +1323,13 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>322.0</v>
+        <v>294.8</v>
       </c>
       <c r="G23" s="2">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="I23" s="4">
         <v>78.0</v>
@@ -1349,7 +1349,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>24.98</v>
+        <v>22.56</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1358,16 +1358,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>61.3</v>
+        <v>59.6</v>
       </c>
       <c r="G24" s="2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H24" s="3">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="I24" s="4">
-        <v>63.0</v>
+        <v>69.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1384,7 +1384,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>33.2</v>
+        <v>32.19</v>
       </c>
       <c r="D25" s="3">
         <v>34.36</v>
@@ -1393,16 +1393,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>251.3</v>
+        <v>235.6</v>
       </c>
       <c r="G25" s="2">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="H25" s="3">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="I25" s="4">
-        <v>82.0</v>
+        <v>68.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1416,7 +1416,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.21</v>
+        <v>11.38</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1425,16 +1425,16 @@
         <v>10.68</v>
       </c>
       <c r="F26" s="2">
-        <v>72.0</v>
+        <v>72.8</v>
       </c>
       <c r="G26" s="2">
-        <v>235.4</v>
+        <v>239.4</v>
       </c>
       <c r="H26" s="3">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I26" s="4">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1448,7 +1448,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>19.19</v>
+        <v>18.04</v>
       </c>
       <c r="D27" s="3">
         <v>25.46</v>
@@ -1457,16 +1457,16 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>184.0</v>
+        <v>162.2</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="I27" s="4">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -1483,7 +1483,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.74</v>
+        <v>7.73</v>
       </c>
       <c r="D28" s="3">
         <v>8.18</v>
@@ -1492,7 +1492,7 @@
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>286.6</v>
+        <v>292.1</v>
       </c>
       <c r="G28" s="2">
         <v>4.1</v>
@@ -1501,7 +1501,7 @@
         <v>0.46</v>
       </c>
       <c r="I28" s="4">
-        <v>62.0</v>
+        <v>61.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1518,25 +1518,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>44.14</v>
+        <v>50.08</v>
       </c>
       <c r="D29" s="3">
-        <v>50.5</v>
+        <v>50.55</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>634.6</v>
+        <v>589.2</v>
       </c>
       <c r="G29" s="2">
-        <v>79.9</v>
+        <v>84.2</v>
       </c>
       <c r="H29" s="3">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="I29" s="4">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="irW5rFt7Ju2tX2PK9KLkM4C00HssQ88atBXcbePte6o="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="pf9jbj4F2hEDjvzmvW5cIdrkeh1dZUX3C5TAegsxD/Q="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -102,7 +102,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>(1/29/26) Covenant Logistics Group, Inc. (CVLG)</t>
+    <t>News Archive for CVLG</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.4</v>
+        <v>52.6</v>
       </c>
       <c r="G2" s="2">
-        <v>14.6</v>
+        <v>15.0</v>
       </c>
       <c r="H2" s="3">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="I2" s="4">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.02</v>
+        <v>5.18</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -665,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>195.5</v>
+        <v>196.3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="I3" s="4">
-        <v>79.0</v>
+        <v>75.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="D4" s="3">
         <v>2.92</v>
@@ -700,16 +700,16 @@
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>22.8</v>
+        <v>20.5</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>65.0</v>
+        <v>43.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>19.52</v>
+        <v>20.45</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>161.0</v>
+        <v>175.9</v>
       </c>
       <c r="G5" s="2">
-        <v>21.0</v>
+        <v>22.2</v>
       </c>
       <c r="H5" s="3">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="I5" s="4">
-        <v>62.0</v>
+        <v>67.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,25 +758,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>24.6</v>
+        <v>29.11</v>
       </c>
       <c r="D6" s="3">
-        <v>28.5</v>
+        <v>29.18</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>636.2</v>
+        <v>721.6</v>
       </c>
       <c r="G6" s="2">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="H6" s="3">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="I6" s="4">
-        <v>50.0</v>
+        <v>67.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.6</v>
+        <v>8.15</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,16 +799,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>179.8</v>
+        <v>161.6</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="I7" s="4">
-        <v>55.0</v>
+        <v>64.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>19.49</v>
+        <v>20.41</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>480.1</v>
+        <v>517.2</v>
       </c>
       <c r="G8" s="2">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="H8" s="3">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="I8" s="4">
-        <v>51.0</v>
+        <v>59.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.54</v>
+        <v>14.31</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +866,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>194.6</v>
+        <v>202.4</v>
       </c>
       <c r="G9" s="2">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="H9" s="3">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="I9" s="4">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>57.18</v>
+        <v>53.5</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>398.5</v>
+        <v>372.1</v>
       </c>
       <c r="G10" s="2">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="I10" s="4">
-        <v>58.0</v>
+        <v>43.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.64</v>
+        <v>18.56</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -930,16 +930,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>122.2</v>
+        <v>121.4</v>
       </c>
       <c r="G11" s="2">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>65.0</v>
+        <v>62.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.63</v>
+        <v>20.14</v>
       </c>
       <c r="D12" s="3">
         <v>23.5</v>
@@ -965,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>132.4</v>
+        <v>142.8</v>
       </c>
       <c r="G12" s="2">
-        <v>12.0</v>
+        <v>12.3</v>
       </c>
       <c r="H12" s="3">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="I12" s="4">
-        <v>73.0</v>
+        <v>77.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,25 +988,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>19.29</v>
+        <v>18.46</v>
       </c>
       <c r="D13" s="3">
-        <v>20.1</v>
+        <v>20.38</v>
       </c>
       <c r="E13" s="3">
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1460.7</v>
+        <v>1420.5</v>
       </c>
       <c r="G13" s="2">
-        <v>50.8</v>
+        <v>49.4</v>
       </c>
       <c r="H13" s="3">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="I13" s="4">
-        <v>97.0</v>
+        <v>96.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>30.21</v>
+        <v>26.29</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,16 +1032,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>707.0</v>
+        <v>573.2</v>
       </c>
       <c r="G14" s="2">
-        <v>31.9</v>
+        <v>24.5</v>
       </c>
       <c r="H14" s="3">
-        <v>1.29</v>
+        <v>0.99</v>
       </c>
       <c r="I14" s="4">
-        <v>88.0</v>
+        <v>70.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1055,7 +1055,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.42</v>
+        <v>9.65</v>
       </c>
       <c r="D15" s="3">
         <v>25.53</v>
@@ -1064,16 +1064,16 @@
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>88.5</v>
+        <v>91.9</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="I15" s="4">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,25 +1090,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>14.14</v>
+        <v>14.67</v>
       </c>
       <c r="D16" s="3">
-        <v>14.7</v>
+        <v>14.85</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>438.2</v>
+        <v>444.5</v>
       </c>
       <c r="G16" s="2">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="H16" s="3">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I16" s="4">
-        <v>91.0</v>
+        <v>93.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1122,28 +1122,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>49.23</v>
+        <v>54.2</v>
       </c>
       <c r="D17" s="3">
-        <v>53.88</v>
+        <v>56.29</v>
       </c>
       <c r="E17" s="3">
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>356.2</v>
+        <v>398.0</v>
       </c>
       <c r="G17" s="2">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
       <c r="H17" s="3">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="I17" s="4">
-        <v>69.0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>82.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>63</v>
@@ -1157,25 +1154,25 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>34.64</v>
+        <v>36.48</v>
       </c>
       <c r="D18" s="3">
-        <v>35.57</v>
+        <v>35.69</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>419.4</v>
+        <v>437.0</v>
       </c>
       <c r="G18" s="2">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="H18" s="3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I18" s="4">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1189,7 +1186,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>39.88</v>
+        <v>38.67</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1198,16 +1195,19 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>102.3</v>
+        <v>96.8</v>
       </c>
       <c r="G19" s="2">
-        <v>8.8</v>
+        <v>8.4</v>
       </c>
       <c r="H19" s="3">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="I19" s="4">
-        <v>77.0</v>
+        <v>69.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1218,16 +1218,16 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>8.47</v>
+        <v>9.1</v>
       </c>
       <c r="D20" s="3">
-        <v>8.88</v>
+        <v>9.07</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>501.3</v>
+        <v>512.0</v>
       </c>
       <c r="G20" s="2">
         <v>22.5</v>
@@ -1236,7 +1236,7 @@
         <v>0.74</v>
       </c>
       <c r="I20" s="4">
-        <v>86.0</v>
+        <v>92.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1250,25 +1250,25 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>48.09</v>
+        <v>51.14</v>
       </c>
       <c r="D21" s="3">
-        <v>51.82</v>
+        <v>52.65</v>
       </c>
       <c r="E21" s="3">
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>528.4</v>
+        <v>571.2</v>
       </c>
       <c r="G21" s="2">
-        <v>41.1</v>
+        <v>43.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="I21" s="4">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1282,7 +1282,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>8.48</v>
+        <v>8.71</v>
       </c>
       <c r="D22" s="3">
         <v>9.17</v>
@@ -1291,16 +1291,16 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>547.1</v>
+        <v>524.3</v>
       </c>
       <c r="G22" s="2">
-        <v>31.8</v>
+        <v>30.2</v>
       </c>
       <c r="H22" s="3">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="I22" s="4">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1314,7 +1314,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>22.56</v>
+        <v>24.94</v>
       </c>
       <c r="D23" s="3">
         <v>26.31</v>
@@ -1323,19 +1323,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>294.8</v>
+        <v>343.9</v>
       </c>
       <c r="G23" s="2">
-        <v>10.7</v>
+        <v>12.0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.81</v>
+        <v>0.92</v>
       </c>
       <c r="I23" s="4">
-        <v>78.0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>89.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1349,7 +1346,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>22.56</v>
+        <v>22.05</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1358,16 +1355,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>59.6</v>
+        <v>53.3</v>
       </c>
       <c r="G24" s="2">
         <v>0.5</v>
       </c>
       <c r="H24" s="3">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="I24" s="4">
-        <v>69.0</v>
+        <v>54.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1384,7 +1381,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>32.19</v>
+        <v>33.34</v>
       </c>
       <c r="D25" s="3">
         <v>34.36</v>
@@ -1393,16 +1390,16 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>235.6</v>
+        <v>248.8</v>
       </c>
       <c r="G25" s="2">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="H25" s="3">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="I25" s="4">
-        <v>68.0</v>
+        <v>65.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1416,7 +1413,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1425,16 +1422,16 @@
         <v>10.68</v>
       </c>
       <c r="F26" s="2">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="G26" s="2">
-        <v>239.4</v>
+        <v>237.7</v>
       </c>
       <c r="H26" s="3">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I26" s="4">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1448,25 +1445,25 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>18.04</v>
+        <v>17.9</v>
       </c>
       <c r="D27" s="3">
-        <v>25.46</v>
+        <v>24.75</v>
       </c>
       <c r="E27" s="3">
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>162.2</v>
+        <v>161.8</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I27" s="4">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -1483,16 +1480,16 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.73</v>
+        <v>7.96</v>
       </c>
       <c r="D28" s="3">
-        <v>8.18</v>
+        <v>8.24</v>
       </c>
       <c r="E28" s="3">
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>292.1</v>
+        <v>286.6</v>
       </c>
       <c r="G28" s="2">
         <v>4.1</v>
@@ -1501,7 +1498,7 @@
         <v>0.46</v>
       </c>
       <c r="I28" s="4">
-        <v>61.0</v>
+        <v>59.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1518,25 +1515,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>50.08</v>
+        <v>55.98</v>
       </c>
       <c r="D29" s="3">
-        <v>50.55</v>
+        <v>55.81</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>589.2</v>
+        <v>691.0</v>
       </c>
       <c r="G29" s="2">
-        <v>84.2</v>
+        <v>87.0</v>
       </c>
       <c r="H29" s="3">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="I29" s="4">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="pf9jbj4F2hEDjvzmvW5cIdrkeh1dZUX3C5TAegsxD/Q="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eaAklKRLMG0XMgyPL1WmpKqbHmk4kbGcsW3nbKFSqs0="/>
     </ext>
   </extLst>
 </workbook>
@@ -138,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>News Archive for ESEA</t>
+    <t>(2/11/26) Euroseas Ltd. (ESEA)</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -156,7 +156,7 @@
     <t>FRD</t>
   </si>
   <si>
-    <t>News Archive for FRD</t>
+    <t>(2/9/26) Friedman Industries, Incorporated (FRD)</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
@@ -165,10 +165,10 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Exceeds size limit Exceeds value limit</t>
-  </si>
-  <si>
-    <t>News Archive for GILT</t>
+    <t>Approaching size limit Approaching value limit</t>
+  </si>
+  <si>
+    <t>(2/10/26) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -312,7 +312,7 @@
     <t>VPG</t>
   </si>
   <si>
-    <t>News Archive for VPG</t>
+    <t>(2/11/26) Vishay Precision Group, Inc. (VPG)</t>
   </si>
 </sst>
 </file>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.96</v>
+        <v>5.19</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>52.6</v>
+        <v>53.8</v>
       </c>
       <c r="G2" s="2">
-        <v>15.0</v>
+        <v>15.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>48.0</v>
+        <v>60.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.18</v>
+        <v>5.42</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -665,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>196.3</v>
+        <v>219.4</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.5</v>
+        <v>0.56</v>
       </c>
       <c r="I3" s="4">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="D4" s="3">
         <v>2.92</v>
@@ -700,7 +700,7 @@
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>20.5</v>
+        <v>21.0</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -709,7 +709,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>20.45</v>
+        <v>19.16</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>175.9</v>
+        <v>164.0</v>
       </c>
       <c r="G5" s="2">
-        <v>22.2</v>
+        <v>20.7</v>
       </c>
       <c r="H5" s="3">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="I5" s="4">
-        <v>67.0</v>
+        <v>55.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,25 +758,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>29.11</v>
+        <v>28.57</v>
       </c>
       <c r="D6" s="3">
-        <v>29.18</v>
+        <v>30.19</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>721.6</v>
+        <v>715.6</v>
       </c>
       <c r="G6" s="2">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="H6" s="3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I6" s="4">
-        <v>67.0</v>
+        <v>65.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.15</v>
+        <v>8.49</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,16 +799,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>161.6</v>
+        <v>174.8</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.64</v>
+        <v>0.69</v>
       </c>
       <c r="I7" s="4">
-        <v>64.0</v>
+        <v>80.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>20.41</v>
+        <v>20.76</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>517.2</v>
+        <v>525.1</v>
       </c>
       <c r="G8" s="2">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="I8" s="4">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.31</v>
+        <v>14.05</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +866,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>202.4</v>
+        <v>193.9</v>
       </c>
       <c r="G9" s="2">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="I9" s="4">
-        <v>64.0</v>
+        <v>59.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>53.5</v>
+        <v>56.55</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>372.1</v>
+        <v>396.2</v>
       </c>
       <c r="G10" s="2">
-        <v>2.9</v>
+        <v>3.0</v>
       </c>
       <c r="H10" s="3">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="I10" s="4">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.56</v>
+        <v>18.55</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -930,16 +930,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.4</v>
+        <v>121.5</v>
       </c>
       <c r="G11" s="2">
         <v>17.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>62.0</v>
+        <v>70.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,25 +956,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>20.14</v>
+        <v>19.34</v>
       </c>
       <c r="D12" s="3">
-        <v>23.5</v>
+        <v>24.37</v>
       </c>
       <c r="E12" s="3">
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>142.8</v>
+        <v>137.5</v>
       </c>
       <c r="G12" s="2">
-        <v>12.3</v>
+        <v>8.7</v>
       </c>
       <c r="H12" s="3">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="I12" s="4">
-        <v>77.0</v>
+        <v>57.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,7 +988,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>18.46</v>
+        <v>13.77</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -997,16 +997,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1420.5</v>
+        <v>1007.2</v>
       </c>
       <c r="G13" s="2">
-        <v>49.4</v>
+        <v>35.0</v>
       </c>
       <c r="H13" s="3">
-        <v>3.52</v>
+        <v>2.49</v>
       </c>
       <c r="I13" s="4">
-        <v>96.0</v>
+        <v>88.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>26.29</v>
+        <v>24.09</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,16 +1032,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>573.2</v>
+        <v>583.3</v>
       </c>
       <c r="G14" s="2">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="H14" s="3">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="I14" s="4">
-        <v>70.0</v>
+        <v>41.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1055,7 +1055,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.65</v>
+        <v>9.87</v>
       </c>
       <c r="D15" s="3">
         <v>25.53</v>
@@ -1064,16 +1064,16 @@
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>91.9</v>
+        <v>96.8</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="I15" s="4">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,25 +1090,25 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>14.67</v>
+        <v>14.56</v>
       </c>
       <c r="D16" s="3">
-        <v>14.85</v>
+        <v>15.22</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>444.5</v>
+        <v>459.3</v>
       </c>
       <c r="G16" s="2">
-        <v>24.7</v>
+        <v>25.5</v>
       </c>
       <c r="H16" s="3">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="I16" s="4">
-        <v>93.0</v>
+        <v>89.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1122,7 +1122,7 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>54.2</v>
+        <v>55.5</v>
       </c>
       <c r="D17" s="3">
         <v>56.29</v>
@@ -1131,16 +1131,16 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>398.0</v>
+        <v>414.0</v>
       </c>
       <c r="G17" s="2">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="I17" s="4">
-        <v>82.0</v>
+        <v>86.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>63</v>
@@ -1154,25 +1154,25 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>36.48</v>
+        <v>37.11</v>
       </c>
       <c r="D18" s="3">
-        <v>35.69</v>
+        <v>37.55</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>437.0</v>
+        <v>466.4</v>
       </c>
       <c r="G18" s="2">
-        <v>23.6</v>
+        <v>25.2</v>
       </c>
       <c r="H18" s="3">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="I18" s="4">
-        <v>84.0</v>
+        <v>87.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1186,7 +1186,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>38.67</v>
+        <v>38.7</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1195,13 +1195,13 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>96.8</v>
+        <v>98.3</v>
       </c>
       <c r="G19" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H19" s="3">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I19" s="4">
         <v>69.0</v>
@@ -1218,25 +1218,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="D20" s="3">
-        <v>9.07</v>
+        <v>9.51</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>512.0</v>
+        <v>561.6</v>
       </c>
       <c r="G20" s="2">
-        <v>22.5</v>
+        <v>24.7</v>
       </c>
       <c r="H20" s="3">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="I20" s="4">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1250,7 +1250,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>51.14</v>
+        <v>47.86</v>
       </c>
       <c r="D21" s="3">
         <v>52.65</v>
@@ -1259,16 +1259,16 @@
         <v>26.32</v>
       </c>
       <c r="F21" s="2">
-        <v>571.2</v>
+        <v>539.0</v>
       </c>
       <c r="G21" s="2">
-        <v>43.4</v>
+        <v>40.9</v>
       </c>
       <c r="H21" s="3">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="I21" s="4">
-        <v>91.0</v>
+        <v>84.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1282,7 +1282,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>8.71</v>
+        <v>8.48</v>
       </c>
       <c r="D22" s="3">
         <v>9.17</v>
@@ -1291,13 +1291,13 @@
         <v>3.93</v>
       </c>
       <c r="F22" s="2">
-        <v>524.3</v>
+        <v>551.0</v>
       </c>
       <c r="G22" s="2">
-        <v>30.2</v>
+        <v>31.8</v>
       </c>
       <c r="H22" s="3">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="I22" s="4">
         <v>90.0</v>
@@ -1314,25 +1314,25 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>24.94</v>
+        <v>28.0</v>
       </c>
       <c r="D23" s="3">
-        <v>26.31</v>
+        <v>28.5</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>343.9</v>
+        <v>384.7</v>
       </c>
       <c r="G23" s="2">
-        <v>12.0</v>
+        <v>13.5</v>
       </c>
       <c r="H23" s="3">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="I23" s="4">
-        <v>89.0</v>
+        <v>82.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1346,7 +1346,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>22.05</v>
+        <v>22.1</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1355,16 +1355,16 @@
         <v>15.0</v>
       </c>
       <c r="F24" s="2">
-        <v>53.3</v>
+        <v>55.2</v>
       </c>
       <c r="G24" s="2">
         <v>0.5</v>
       </c>
       <c r="H24" s="3">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="I24" s="4">
-        <v>54.0</v>
+        <v>60.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1381,7 +1381,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>33.34</v>
+        <v>33.11</v>
       </c>
       <c r="D25" s="3">
         <v>34.36</v>
@@ -1390,7 +1390,7 @@
         <v>11.93</v>
       </c>
       <c r="F25" s="2">
-        <v>248.8</v>
+        <v>248.1</v>
       </c>
       <c r="G25" s="2">
         <v>12.1</v>
@@ -1399,7 +1399,7 @@
         <v>1.01</v>
       </c>
       <c r="I25" s="4">
-        <v>65.0</v>
+        <v>71.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1413,7 +1413,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.32</v>
+        <v>11.19</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1422,16 +1422,16 @@
         <v>10.68</v>
       </c>
       <c r="F26" s="2">
-        <v>72.7</v>
+        <v>71.3</v>
       </c>
       <c r="G26" s="2">
-        <v>237.7</v>
+        <v>233.1</v>
       </c>
       <c r="H26" s="3">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I26" s="4">
-        <v>37.0</v>
+        <v>27.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1445,7 +1445,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="D27" s="3">
         <v>24.75</v>
@@ -1454,13 +1454,13 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>161.8</v>
+        <v>166.8</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="I27" s="4">
         <v>35.0</v>
@@ -1480,16 +1480,16 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.96</v>
+        <v>7.86</v>
       </c>
       <c r="D28" s="3">
-        <v>8.24</v>
+        <v>8.35</v>
       </c>
       <c r="E28" s="3">
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>286.6</v>
+        <v>290.7</v>
       </c>
       <c r="G28" s="2">
         <v>4.1</v>
@@ -1515,25 +1515,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>55.98</v>
+        <v>44.2</v>
       </c>
       <c r="D29" s="3">
-        <v>55.81</v>
+        <v>56.25</v>
       </c>
       <c r="E29" s="3">
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>691.0</v>
+        <v>586.9</v>
       </c>
       <c r="G29" s="2">
-        <v>87.0</v>
+        <v>73.9</v>
       </c>
       <c r="H29" s="3">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="I29" s="4">
-        <v>94.0</v>
+        <v>89.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eaAklKRLMG0XMgyPL1WmpKqbHmk4kbGcsW3nbKFSqs0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="4QW16EOmL82BOWLre8nQbQ5uul74aSy/7azH2Bp6zkY="/>
     </ext>
   </extLst>
 </workbook>
@@ -138,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>(2/11/26) Euroseas Ltd. (ESEA)</t>
+    <t>News Archive for ESEA</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -156,7 +156,7 @@
     <t>FRD</t>
   </si>
   <si>
-    <t>(2/9/26) Friedman Industries, Incorporated (FRD)</t>
+    <t>News Archive for FRD</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
@@ -165,10 +165,10 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Approaching size limit Approaching value limit</t>
-  </si>
-  <si>
-    <t>(2/10/26) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>Approaching size limit Exceeds value limit</t>
+  </si>
+  <si>
+    <t>(2/17/26) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -189,7 +189,7 @@
     <t>Earnings probation 2025Q3</t>
   </si>
   <si>
-    <t>News Archive for LAKE</t>
+    <t>(2/17/26) Lakeland Industries, Inc. (LAKE)</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -234,15 +234,6 @@
     <t>News Archive for OIS</t>
   </si>
   <si>
-    <t>Olympic Steel, Inc.</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>News Archive for ZEUS</t>
-  </si>
-  <si>
     <t>Pangaea Logistics Solutions Ltd.</t>
   </si>
   <si>
@@ -279,6 +270,15 @@
     <t>News Archive for RCKY</t>
   </si>
   <si>
+    <t>Ryerson Holding Corporation</t>
+  </si>
+  <si>
+    <t>RYI</t>
+  </si>
+  <si>
+    <t>Merged with Olympic Steel (ZEUS)</t>
+  </si>
+  <si>
     <t>Saga Communications, Inc.</t>
   </si>
   <si>
@@ -312,7 +312,7 @@
     <t>VPG</t>
   </si>
   <si>
-    <t>(2/11/26) Vishay Precision Group, Inc. (VPG)</t>
+    <t>News Archive for VPG</t>
   </si>
 </sst>
 </file>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.19</v>
+        <v>5.2</v>
       </c>
       <c r="D2" s="3">
         <v>6.2</v>
@@ -630,16 +630,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="G2" s="2">
         <v>15.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I2" s="4">
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.42</v>
+        <v>5.71</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -665,16 +665,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>219.4</v>
+        <v>227.9</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.56</v>
+        <v>0.58</v>
       </c>
       <c r="I3" s="4">
-        <v>80.0</v>
+        <v>85.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,25 +691,25 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="D4" s="3">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>21.0</v>
+        <v>22.7</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>19.16</v>
+        <v>19.32</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +735,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>164.0</v>
+        <v>166.7</v>
       </c>
       <c r="G5" s="2">
-        <v>20.7</v>
+        <v>21.0</v>
       </c>
       <c r="H5" s="3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I5" s="4">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>28.57</v>
+        <v>29.64</v>
       </c>
       <c r="D6" s="3">
         <v>30.19</v>
@@ -767,16 +767,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>715.6</v>
+        <v>736.4</v>
       </c>
       <c r="G6" s="2">
-        <v>26.7</v>
+        <v>27.5</v>
       </c>
       <c r="H6" s="3">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="I6" s="4">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.49</v>
+        <v>8.6</v>
       </c>
       <c r="D7" s="3">
         <v>9.92</v>
@@ -799,16 +799,16 @@
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>174.8</v>
+        <v>178.9</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="I7" s="4">
-        <v>80.0</v>
+        <v>78.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +825,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>20.76</v>
+        <v>20.46</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +834,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>525.1</v>
+        <v>518.3</v>
       </c>
       <c r="G8" s="2">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I8" s="4">
-        <v>60.0</v>
+        <v>58.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.05</v>
+        <v>14.18</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +866,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>193.9</v>
+        <v>192.6</v>
       </c>
       <c r="G9" s="2">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="H9" s="3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I9" s="4">
-        <v>59.0</v>
+        <v>56.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>56.55</v>
+        <v>61.26</v>
       </c>
       <c r="D10" s="3">
         <v>66.0</v>
@@ -898,16 +898,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>396.2</v>
+        <v>419.3</v>
       </c>
       <c r="G10" s="2">
-        <v>3.0</v>
+        <v>3.2</v>
       </c>
       <c r="H10" s="3">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="I10" s="4">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -930,13 +930,13 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.5</v>
+        <v>121.6</v>
       </c>
       <c r="G11" s="2">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="H11" s="3">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="I11" s="4">
         <v>70.0</v>
@@ -956,7 +956,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>19.34</v>
+        <v>18.19</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -965,16 +965,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>137.5</v>
+        <v>129.7</v>
       </c>
       <c r="G12" s="2">
-        <v>8.7</v>
+        <v>8.2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="I12" s="4">
-        <v>57.0</v>
+        <v>51.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,7 +988,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>13.77</v>
+        <v>14.67</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -997,16 +997,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1007.2</v>
+        <v>1092.8</v>
       </c>
       <c r="G13" s="2">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="H13" s="3">
-        <v>2.49</v>
+        <v>2.71</v>
       </c>
       <c r="I13" s="4">
-        <v>88.0</v>
+        <v>91.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1023,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>24.09</v>
+        <v>25.13</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,16 +1032,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>583.3</v>
+        <v>598.3</v>
       </c>
       <c r="G14" s="2">
-        <v>24.8</v>
+        <v>25.5</v>
       </c>
       <c r="H14" s="3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I14" s="4">
-        <v>41.0</v>
+        <v>34.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1055,7 +1055,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.87</v>
+        <v>9.58</v>
       </c>
       <c r="D15" s="3">
         <v>25.53</v>
@@ -1064,16 +1064,16 @@
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>96.8</v>
+        <v>92.2</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="I15" s="4">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,7 +1090,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>14.56</v>
+        <v>14.8</v>
       </c>
       <c r="D16" s="3">
         <v>15.22</v>
@@ -1099,13 +1099,13 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>459.3</v>
+        <v>468.2</v>
       </c>
       <c r="G16" s="2">
-        <v>25.5</v>
+        <v>26.0</v>
       </c>
       <c r="H16" s="3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I16" s="4">
         <v>89.0</v>
@@ -1122,25 +1122,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="D17" s="3">
-        <v>56.29</v>
+        <v>58.74</v>
       </c>
       <c r="E17" s="3">
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>414.0</v>
+        <v>417.7</v>
       </c>
       <c r="G17" s="2">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I17" s="4">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>63</v>
@@ -1154,25 +1154,25 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>37.11</v>
+        <v>37.84</v>
       </c>
       <c r="D18" s="3">
-        <v>37.55</v>
+        <v>38.37</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>466.4</v>
+        <v>472.0</v>
       </c>
       <c r="G18" s="2">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="H18" s="3">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I18" s="4">
-        <v>87.0</v>
+        <v>85.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1186,7 +1186,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>38.7</v>
+        <v>39.73</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1195,19 +1195,16 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>98.3</v>
+        <v>101.3</v>
       </c>
       <c r="G19" s="2">
-        <v>8.5</v>
+        <v>8.8</v>
       </c>
       <c r="H19" s="3">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="I19" s="4">
-        <v>69.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1218,25 +1215,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>9.4</v>
+        <v>12.38</v>
       </c>
       <c r="D20" s="3">
-        <v>9.51</v>
+        <v>10.05</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>561.6</v>
+        <v>597.5</v>
       </c>
       <c r="G20" s="2">
-        <v>24.7</v>
+        <v>26.2</v>
       </c>
       <c r="H20" s="3">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="I20" s="4">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1250,25 +1247,25 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>47.86</v>
+        <v>9.25</v>
       </c>
       <c r="D21" s="3">
-        <v>52.65</v>
+        <v>9.17</v>
       </c>
       <c r="E21" s="3">
-        <v>26.32</v>
+        <v>3.93</v>
       </c>
       <c r="F21" s="2">
-        <v>539.0</v>
+        <v>586.7</v>
       </c>
       <c r="G21" s="2">
-        <v>40.9</v>
+        <v>33.8</v>
       </c>
       <c r="H21" s="3">
-        <v>0.93</v>
+        <v>1.4</v>
       </c>
       <c r="I21" s="4">
-        <v>84.0</v>
+        <v>92.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1282,25 +1279,25 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>8.48</v>
+        <v>27.3</v>
       </c>
       <c r="D22" s="3">
-        <v>9.17</v>
+        <v>28.5</v>
       </c>
       <c r="E22" s="3">
-        <v>3.93</v>
+        <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>551.0</v>
+        <v>370.7</v>
       </c>
       <c r="G22" s="2">
-        <v>31.8</v>
+        <v>13.0</v>
       </c>
       <c r="H22" s="3">
-        <v>1.31</v>
+        <v>0.99</v>
       </c>
       <c r="I22" s="4">
-        <v>90.0</v>
+        <v>82.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1314,25 +1311,28 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>28.0</v>
+        <v>23.05</v>
       </c>
       <c r="D23" s="3">
-        <v>28.5</v>
+        <v>31.5</v>
       </c>
       <c r="E23" s="3">
-        <v>15.52</v>
+        <v>15.0</v>
       </c>
       <c r="F23" s="2">
-        <v>384.7</v>
+        <v>56.5</v>
       </c>
       <c r="G23" s="2">
-        <v>13.5</v>
+        <v>0.5</v>
       </c>
       <c r="H23" s="3">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
       <c r="I23" s="4">
-        <v>82.0</v>
+        <v>63.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1346,28 +1346,25 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>22.1</v>
+        <v>33.92</v>
       </c>
       <c r="D24" s="3">
-        <v>31.5</v>
+        <v>34.61</v>
       </c>
       <c r="E24" s="3">
-        <v>15.0</v>
+        <v>11.93</v>
       </c>
       <c r="F24" s="2">
-        <v>55.2</v>
+        <v>251.0</v>
       </c>
       <c r="G24" s="2">
-        <v>0.5</v>
+        <v>12.2</v>
       </c>
       <c r="H24" s="3">
-        <v>0.29</v>
+        <v>1.02</v>
       </c>
       <c r="I24" s="4">
-        <v>60.0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>74.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>83</v>
@@ -1381,27 +1378,27 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>33.11</v>
+        <v>27.9</v>
       </c>
       <c r="D25" s="3">
-        <v>34.36</v>
+        <v>30.9</v>
       </c>
       <c r="E25" s="3">
-        <v>11.93</v>
+        <v>19.02</v>
       </c>
       <c r="F25" s="2">
-        <v>248.1</v>
-      </c>
-      <c r="G25" s="2">
-        <v>12.1</v>
+        <v>769.9</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H25" s="3">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="I25" s="4">
-        <v>71.0</v>
-      </c>
-      <c r="K25" s="2" t="s">
+        <v>51.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1413,7 +1410,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>11.19</v>
+        <v>11.95</v>
       </c>
       <c r="D26" s="3">
         <v>14.27</v>
@@ -1422,16 +1419,16 @@
         <v>10.68</v>
       </c>
       <c r="F26" s="2">
-        <v>71.3</v>
+        <v>74.7</v>
       </c>
       <c r="G26" s="2">
-        <v>233.1</v>
+        <v>244.4</v>
       </c>
       <c r="H26" s="3">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="I26" s="4">
-        <v>27.0</v>
+        <v>32.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1445,7 +1442,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>18.5</v>
+        <v>16.91</v>
       </c>
       <c r="D27" s="3">
         <v>24.75</v>
@@ -1454,16 +1451,16 @@
         <v>15.0</v>
       </c>
       <c r="F27" s="2">
-        <v>166.8</v>
+        <v>153.8</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="I27" s="4">
-        <v>35.0</v>
+        <v>27.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -1480,7 +1477,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>7.86</v>
+        <v>8.32</v>
       </c>
       <c r="D28" s="3">
         <v>8.35</v>
@@ -1489,16 +1486,16 @@
         <v>4.9</v>
       </c>
       <c r="F28" s="2">
-        <v>290.7</v>
+        <v>302.5</v>
       </c>
       <c r="G28" s="2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H28" s="3">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="I28" s="4">
-        <v>59.0</v>
+        <v>65.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1515,7 +1512,7 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>44.2</v>
+        <v>47.56</v>
       </c>
       <c r="D29" s="3">
         <v>56.25</v>
@@ -1524,16 +1521,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>586.9</v>
+        <v>622.9</v>
       </c>
       <c r="G29" s="2">
-        <v>73.9</v>
+        <v>78.4</v>
       </c>
       <c r="H29" s="3">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="I29" s="4">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="4QW16EOmL82BOWLre8nQbQ5uul74aSy/7azH2Bp6zkY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BdaOcEXdtXAr6EuJH4snlPomggR0UTaySYgNs1HdPTs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
   <si>
     <t>Company</t>
   </si>
@@ -111,7 +111,7 @@
     <t>BOOM</t>
   </si>
   <si>
-    <t>News Archive for BOOM</t>
+    <t>(2/23/26) DMC Global Inc. (BOOM)</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -138,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>News Archive for ESEA</t>
+    <t>(2/25/26) Euroseas Ltd. (ESEA)</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -168,7 +168,7 @@
     <t>Approaching size limit Exceeds value limit</t>
   </si>
   <si>
-    <t>(2/17/26) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>(2/24/26) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -189,7 +189,7 @@
     <t>Earnings probation 2025Q3</t>
   </si>
   <si>
-    <t>(2/17/26) Lakeland Industries, Inc. (LAKE)</t>
+    <t>News Archive for LAKE</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -252,31 +252,25 @@
     <t>News Archive for PKOH</t>
   </si>
   <si>
-    <t>Regis Corporation</t>
-  </si>
-  <si>
-    <t>RGS</t>
-  </si>
-  <si>
-    <t>News Archive for RGS</t>
-  </si>
-  <si>
     <t>Rocky Brands, Inc.</t>
   </si>
   <si>
     <t>RCKY</t>
   </si>
   <si>
-    <t>News Archive for RCKY</t>
+    <t>(2/24/26) Rocky Brands, Inc. (RCKY)</t>
   </si>
   <si>
     <t>Ryerson Holding Corporation</t>
   </si>
   <si>
-    <t>RYI</t>
-  </si>
-  <si>
-    <t>Merged with Olympic Steel (ZEUS)</t>
+    <t>RYZ</t>
+  </si>
+  <si>
+    <t>Merged with Olympic Steel (ZEUS) Exceeds size limit</t>
+  </si>
+  <si>
+    <t>News Archive for RYZ</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -335,7 +329,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -621,25 +614,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="D2" s="3">
-        <v>6.2</v>
+        <v>5.64</v>
       </c>
       <c r="E2" s="3">
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>53.9</v>
+        <v>54.0</v>
       </c>
       <c r="G2" s="2">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="H2" s="3">
         <v>0.86</v>
       </c>
       <c r="I2" s="4">
-        <v>59.0</v>
+        <v>55.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +649,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.71</v>
+        <v>5.74</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -665,16 +658,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>227.9</v>
+        <v>232.3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I3" s="4">
-        <v>85.0</v>
+        <v>83.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -691,7 +684,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="3">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="D4" s="3">
         <v>2.84</v>
@@ -700,13 +693,13 @@
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>22.7</v>
+        <v>21.2</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
         <v>49.0</v>
@@ -726,7 +719,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>19.32</v>
+        <v>18.25</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -735,16 +728,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>166.7</v>
+        <v>156.2</v>
       </c>
       <c r="G5" s="2">
-        <v>21.0</v>
+        <v>19.7</v>
       </c>
       <c r="H5" s="3">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="I5" s="4">
-        <v>52.0</v>
+        <v>40.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -758,25 +751,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>29.64</v>
+        <v>29.49</v>
       </c>
       <c r="D6" s="3">
-        <v>30.19</v>
+        <v>30.38</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>736.4</v>
+        <v>738.6</v>
       </c>
       <c r="G6" s="2">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="H6" s="3">
         <v>1.74</v>
       </c>
       <c r="I6" s="4">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,25 +783,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>8.6</v>
+        <v>5.89</v>
       </c>
       <c r="D7" s="3">
-        <v>9.92</v>
+        <v>9.2</v>
       </c>
       <c r="E7" s="3">
         <v>5.46</v>
       </c>
       <c r="F7" s="2">
-        <v>178.9</v>
+        <v>120.7</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="4">
-        <v>78.0</v>
+        <v>35.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -825,7 +818,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>20.46</v>
+        <v>21.11</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -834,16 +827,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>518.3</v>
+        <v>533.9</v>
       </c>
       <c r="G8" s="2">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H8" s="3">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="I8" s="4">
-        <v>58.0</v>
+        <v>63.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -857,7 +850,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.18</v>
+        <v>14.4</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -866,16 +859,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>192.6</v>
+        <v>198.8</v>
       </c>
       <c r="G9" s="2">
-        <v>15.2</v>
+        <v>15.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I9" s="4">
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -889,25 +882,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>61.26</v>
+        <v>68.74</v>
       </c>
       <c r="D10" s="3">
-        <v>66.0</v>
+        <v>69.48</v>
       </c>
       <c r="E10" s="3">
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>419.3</v>
+        <v>485.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="H10" s="3">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="I10" s="4">
-        <v>40.0</v>
+        <v>59.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -921,7 +914,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.55</v>
+        <v>18.6</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -930,7 +923,7 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.6</v>
+        <v>121.9</v>
       </c>
       <c r="G11" s="2">
         <v>16.9</v>
@@ -939,7 +932,7 @@
         <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -956,7 +949,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>18.19</v>
+        <v>18.63</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -965,16 +958,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>129.7</v>
+        <v>132.5</v>
       </c>
       <c r="G12" s="2">
-        <v>8.2</v>
+        <v>8.4</v>
       </c>
       <c r="H12" s="3">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I12" s="4">
-        <v>51.0</v>
+        <v>44.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -988,7 +981,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>14.67</v>
+        <v>15.9</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -997,16 +990,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1092.8</v>
+        <v>1163.0</v>
       </c>
       <c r="G13" s="2">
-        <v>38.0</v>
+        <v>40.5</v>
       </c>
       <c r="H13" s="3">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="I13" s="4">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1023,7 +1016,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>25.13</v>
+        <v>24.99</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1032,16 +1025,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>598.3</v>
+        <v>605.1</v>
       </c>
       <c r="G14" s="2">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="H14" s="3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I14" s="4">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1055,25 +1048,25 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.58</v>
+        <v>9.17</v>
       </c>
       <c r="D15" s="3">
-        <v>25.53</v>
+        <v>23.94</v>
       </c>
       <c r="E15" s="3">
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>92.2</v>
+        <v>89.9</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I15" s="4">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1090,22 +1083,22 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>14.8</v>
+        <v>15.28</v>
       </c>
       <c r="D16" s="3">
-        <v>15.22</v>
+        <v>15.53</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>468.2</v>
+        <v>482.1</v>
       </c>
       <c r="G16" s="2">
-        <v>26.0</v>
+        <v>26.8</v>
       </c>
       <c r="H16" s="3">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="I16" s="4">
         <v>89.0</v>
@@ -1122,25 +1115,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>55.7</v>
+        <v>57.38</v>
       </c>
       <c r="D17" s="3">
-        <v>58.74</v>
+        <v>59.01</v>
       </c>
       <c r="E17" s="3">
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>417.7</v>
+        <v>428.1</v>
       </c>
       <c r="G17" s="2">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="H17" s="3">
-        <v>0.98</v>
+        <v>1.0</v>
       </c>
       <c r="I17" s="4">
-        <v>87.0</v>
+        <v>85.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>63</v>
@@ -1154,25 +1147,25 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>37.84</v>
+        <v>38.26</v>
       </c>
       <c r="D18" s="3">
-        <v>38.37</v>
+        <v>39.67</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>472.0</v>
+        <v>480.9</v>
       </c>
       <c r="G18" s="2">
-        <v>25.5</v>
+        <v>26.0</v>
       </c>
       <c r="H18" s="3">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="I18" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1186,7 +1179,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>39.73</v>
+        <v>39.84</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1195,7 +1188,7 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>101.3</v>
+        <v>101.2</v>
       </c>
       <c r="G19" s="2">
         <v>8.8</v>
@@ -1204,7 +1197,7 @@
         <v>0.92</v>
       </c>
       <c r="I19" s="4">
-        <v>61.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1215,25 +1208,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>12.38</v>
+        <v>13.09</v>
       </c>
       <c r="D20" s="3">
-        <v>10.05</v>
+        <v>14.5</v>
       </c>
       <c r="E20" s="3">
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>597.5</v>
+        <v>782.1</v>
       </c>
       <c r="G20" s="2">
-        <v>26.2</v>
+        <v>34.4</v>
       </c>
       <c r="H20" s="3">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="I20" s="4">
-        <v>94.0</v>
+        <v>97.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1247,22 +1240,22 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>9.25</v>
+        <v>9.35</v>
       </c>
       <c r="D21" s="3">
-        <v>9.17</v>
+        <v>9.39</v>
       </c>
       <c r="E21" s="3">
         <v>3.93</v>
       </c>
       <c r="F21" s="2">
-        <v>586.7</v>
+        <v>607.5</v>
       </c>
       <c r="G21" s="2">
-        <v>33.8</v>
+        <v>35.0</v>
       </c>
       <c r="H21" s="3">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="I21" s="4">
         <v>92.0</v>
@@ -1279,7 +1272,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>27.3</v>
+        <v>25.74</v>
       </c>
       <c r="D22" s="3">
         <v>28.5</v>
@@ -1288,16 +1281,16 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>370.7</v>
+        <v>353.6</v>
       </c>
       <c r="G22" s="2">
-        <v>13.0</v>
+        <v>12.4</v>
       </c>
       <c r="H22" s="3">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="I22" s="4">
-        <v>82.0</v>
+        <v>78.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1311,28 +1304,25 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>23.05</v>
+        <v>45.2</v>
       </c>
       <c r="D23" s="3">
-        <v>31.5</v>
+        <v>48.7</v>
       </c>
       <c r="E23" s="3">
-        <v>15.0</v>
+        <v>11.93</v>
       </c>
       <c r="F23" s="2">
-        <v>56.5</v>
+        <v>338.7</v>
       </c>
       <c r="G23" s="2">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="H23" s="3">
-        <v>0.3</v>
+        <v>1.38</v>
       </c>
       <c r="I23" s="4">
-        <v>63.0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>86.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1346,196 +1336,168 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>33.92</v>
+        <v>26.16</v>
       </c>
       <c r="D24" s="3">
-        <v>34.61</v>
+        <v>30.9</v>
       </c>
       <c r="E24" s="3">
-        <v>11.93</v>
+        <v>19.02</v>
       </c>
       <c r="F24" s="2">
-        <v>251.0</v>
-      </c>
-      <c r="G24" s="2">
-        <v>12.2</v>
+        <v>1346.8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H24" s="3">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="I24" s="4">
-        <v>74.0</v>
+        <v>64.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="3">
-        <v>27.9</v>
+        <v>11.74</v>
       </c>
       <c r="D25" s="3">
-        <v>30.9</v>
+        <v>14.27</v>
       </c>
       <c r="E25" s="3">
-        <v>19.02</v>
+        <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>769.9</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>17</v>
+        <v>74.8</v>
+      </c>
+      <c r="G25" s="2">
+        <v>244.6</v>
       </c>
       <c r="H25" s="3">
-        <v>0.98</v>
+        <v>0.47</v>
       </c>
       <c r="I25" s="4">
-        <v>51.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>86</v>
+        <v>40.0</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" s="3">
-        <v>11.95</v>
+        <v>15.7</v>
       </c>
       <c r="D26" s="3">
-        <v>14.27</v>
+        <v>23.5</v>
       </c>
       <c r="E26" s="3">
-        <v>10.68</v>
+        <v>15.0</v>
       </c>
       <c r="F26" s="2">
-        <v>74.7</v>
-      </c>
-      <c r="G26" s="2">
-        <v>244.4</v>
+        <v>141.6</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H26" s="3">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I26" s="4">
-        <v>32.0</v>
+        <v>25.0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" s="3">
-        <v>16.91</v>
+        <v>8.95</v>
       </c>
       <c r="D27" s="3">
-        <v>24.75</v>
+        <v>8.96</v>
       </c>
       <c r="E27" s="3">
-        <v>15.0</v>
+        <v>4.9</v>
       </c>
       <c r="F27" s="2">
-        <v>153.8</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>17</v>
+        <v>331.0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4.7</v>
       </c>
       <c r="H27" s="3">
-        <v>1.87</v>
+        <v>0.53</v>
       </c>
       <c r="I27" s="4">
-        <v>27.0</v>
+        <v>66.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" s="3">
-        <v>8.32</v>
+        <v>46.07</v>
       </c>
       <c r="D28" s="3">
-        <v>8.35</v>
+        <v>56.25</v>
       </c>
       <c r="E28" s="3">
-        <v>4.9</v>
+        <v>18.57</v>
       </c>
       <c r="F28" s="2">
-        <v>302.5</v>
+        <v>611.8</v>
       </c>
       <c r="G28" s="2">
-        <v>4.3</v>
+        <v>77.0</v>
       </c>
       <c r="H28" s="3">
-        <v>0.48</v>
+        <v>1.81</v>
       </c>
       <c r="I28" s="4">
-        <v>65.0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>89.0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="3">
-        <v>47.56</v>
-      </c>
-      <c r="D29" s="3">
-        <v>56.25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>18.57</v>
-      </c>
-      <c r="F29" s="2">
-        <v>622.9</v>
-      </c>
-      <c r="G29" s="2">
-        <v>78.4</v>
-      </c>
-      <c r="H29" s="3">
-        <v>1.84</v>
-      </c>
-      <c r="I29" s="4">
-        <v>90.0</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
+    </row>
+    <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -2505,7 +2467,6 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BdaOcEXdtXAr6EuJH4snlPomggR0UTaySYgNs1HdPTs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Bxr0ZCTW3hGLQJvuJGQ/sfYCwJxSnymtlzriFfsmdSs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -111,7 +111,7 @@
     <t>BOOM</t>
   </si>
   <si>
-    <t>(2/23/26) DMC Global Inc. (BOOM)</t>
+    <t>News Archive for BOOM</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -138,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>(2/25/26) Euroseas Ltd. (ESEA)</t>
+    <t>News Archive for ESEA</t>
   </si>
   <si>
     <t>FONAR Corporation</t>
@@ -168,7 +168,7 @@
     <t>Approaching size limit Exceeds value limit</t>
   </si>
   <si>
-    <t>(2/24/26) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>News Archive for GILT</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -198,7 +198,7 @@
     <t>MG</t>
   </si>
   <si>
-    <t>News Archive for MG</t>
+    <t>(3/4/26) Mistras Group, Inc. (MG)</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -207,7 +207,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>News Archive for NC</t>
+    <t>(3/4/26) NACCO Industries, Inc. (NC)</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -225,6 +225,9 @@
     <t>NCSM</t>
   </si>
   <si>
+    <t>(3/4/26) NCS Multistage Holdings, Inc. (NCSM)</t>
+  </si>
+  <si>
     <t>Oil States International, Inc.</t>
   </si>
   <si>
@@ -249,7 +252,7 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>News Archive for PKOH</t>
+    <t>(3/4/26) Park-Ohio Holdings Corp. (PKOH)</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -258,7 +261,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>(2/24/26) Rocky Brands, Inc. (RCKY)</t>
+    <t>News Archive for RCKY</t>
   </si>
   <si>
     <t>Ryerson Holding Corporation</t>
@@ -297,7 +300,7 @@
     <t>GASS</t>
   </si>
   <si>
-    <t>News Archive for GASS</t>
+    <t>(3/2/26) StealthGas Inc. (GASS)</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -329,6 +332,7 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -614,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.21</v>
+        <v>5.17</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
@@ -623,16 +627,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>54.0</v>
+        <v>53.6</v>
       </c>
       <c r="G2" s="2">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>55.0</v>
+        <v>59.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -649,7 +653,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.74</v>
+        <v>6.1</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -658,16 +662,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>232.3</v>
+        <v>246.9</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="4">
-        <v>83.0</v>
+        <v>89.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -702,7 +706,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>49.0</v>
+        <v>61.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -719,7 +723,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.25</v>
+        <v>18.81</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
@@ -728,16 +732,16 @@
         <v>12.25</v>
       </c>
       <c r="F5" s="2">
-        <v>156.2</v>
+        <v>161.0</v>
       </c>
       <c r="G5" s="2">
-        <v>19.7</v>
+        <v>20.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I5" s="4">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -751,25 +755,25 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>29.49</v>
+        <v>26.31</v>
       </c>
       <c r="D6" s="3">
-        <v>30.38</v>
+        <v>30.43</v>
       </c>
       <c r="E6" s="3">
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>738.6</v>
+        <v>659.9</v>
       </c>
       <c r="G6" s="2">
-        <v>27.6</v>
+        <v>164.4</v>
       </c>
       <c r="H6" s="3">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="I6" s="4">
-        <v>70.0</v>
+        <v>63.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -783,25 +787,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>5.89</v>
+        <v>5.43</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
       </c>
       <c r="E7" s="3">
-        <v>5.46</v>
+        <v>5.41</v>
       </c>
       <c r="F7" s="2">
-        <v>120.7</v>
+        <v>111.2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="I7" s="4">
-        <v>35.0</v>
+        <v>26.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -818,7 +822,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>21.11</v>
+        <v>21.31</v>
       </c>
       <c r="D8" s="3">
         <v>22.01</v>
@@ -827,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>533.9</v>
+        <v>539.0</v>
       </c>
       <c r="G8" s="2">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="I8" s="4">
-        <v>63.0</v>
+        <v>68.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -850,7 +854,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>14.4</v>
+        <v>15.0</v>
       </c>
       <c r="D9" s="3">
         <v>16.99</v>
@@ -859,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>198.8</v>
+        <v>205.4</v>
       </c>
       <c r="G9" s="2">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="H9" s="3">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="I9" s="4">
-        <v>61.0</v>
+        <v>71.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -882,25 +886,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>68.74</v>
+        <v>64.76</v>
       </c>
       <c r="D10" s="3">
-        <v>69.48</v>
+        <v>72.87</v>
       </c>
       <c r="E10" s="3">
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>485.0</v>
+        <v>456.9</v>
       </c>
       <c r="G10" s="2">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="3">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="I10" s="4">
-        <v>59.0</v>
+        <v>57.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -914,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.6</v>
+        <v>18.49</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -923,16 +927,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.9</v>
+        <v>121.2</v>
       </c>
       <c r="G11" s="2">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="H11" s="3">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="I11" s="4">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -949,7 +953,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>18.63</v>
+        <v>18.38</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -958,16 +962,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>132.5</v>
+        <v>130.7</v>
       </c>
       <c r="G12" s="2">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
       <c r="H12" s="3">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I12" s="4">
-        <v>44.0</v>
+        <v>34.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -981,7 +985,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>15.9</v>
+        <v>16.14</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -990,16 +994,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1163.0</v>
+        <v>1180.5</v>
       </c>
       <c r="G13" s="2">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="H13" s="3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I13" s="4">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1016,7 +1020,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>24.99</v>
+        <v>22.63</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1025,16 +1029,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>605.1</v>
+        <v>548.0</v>
       </c>
       <c r="G14" s="2">
-        <v>25.8</v>
+        <v>23.3</v>
       </c>
       <c r="H14" s="3">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="I14" s="4">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1048,25 +1052,25 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.17</v>
+        <v>8.6</v>
       </c>
       <c r="D15" s="3">
-        <v>23.94</v>
+        <v>21.23</v>
       </c>
       <c r="E15" s="3">
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>89.9</v>
+        <v>84.3</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="3">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="I15" s="4">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1083,22 +1087,22 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>15.28</v>
+        <v>14.82</v>
       </c>
       <c r="D16" s="3">
-        <v>15.53</v>
+        <v>15.84</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>482.1</v>
+        <v>467.5</v>
       </c>
       <c r="G16" s="2">
-        <v>26.8</v>
+        <v>26.0</v>
       </c>
       <c r="H16" s="3">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="I16" s="4">
         <v>89.0</v>
@@ -1115,25 +1119,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>57.38</v>
+        <v>48.91</v>
       </c>
       <c r="D17" s="3">
-        <v>59.01</v>
+        <v>59.42</v>
       </c>
       <c r="E17" s="3">
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>428.1</v>
+        <v>368.5</v>
       </c>
       <c r="G17" s="2">
-        <v>14.8</v>
+        <v>20.8</v>
       </c>
       <c r="H17" s="3">
-        <v>1.0</v>
+        <v>0.85</v>
       </c>
       <c r="I17" s="4">
-        <v>85.0</v>
+        <v>76.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>63</v>
@@ -1147,7 +1151,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>38.26</v>
+        <v>37.8</v>
       </c>
       <c r="D18" s="3">
         <v>39.67</v>
@@ -1156,16 +1160,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>480.9</v>
+        <v>475.1</v>
       </c>
       <c r="G18" s="2">
-        <v>26.0</v>
+        <v>25.7</v>
       </c>
       <c r="H18" s="3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="I18" s="4">
-        <v>86.0</v>
+        <v>85.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1179,7 +1183,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>39.84</v>
+        <v>48.35</v>
       </c>
       <c r="D19" s="3">
         <v>53.69</v>
@@ -1188,27 +1192,30 @@
         <v>23.89</v>
       </c>
       <c r="F19" s="2">
-        <v>101.2</v>
+        <v>122.9</v>
       </c>
       <c r="G19" s="2">
-        <v>8.8</v>
+        <v>10.7</v>
       </c>
       <c r="H19" s="3">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="I19" s="4">
-        <v>53.0</v>
+        <v>68.0</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="3">
-        <v>13.09</v>
+        <v>12.23</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
@@ -1217,30 +1224,30 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>782.1</v>
-      </c>
-      <c r="G20" s="2">
-        <v>34.4</v>
+        <v>736.3</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H20" s="3">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="I20" s="4">
-        <v>97.0</v>
+        <v>96.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="3">
-        <v>9.35</v>
+        <v>8.36</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1249,62 +1256,62 @@
         <v>3.93</v>
       </c>
       <c r="F21" s="2">
-        <v>607.5</v>
+        <v>543.2</v>
       </c>
       <c r="G21" s="2">
-        <v>35.0</v>
+        <v>31.3</v>
       </c>
       <c r="H21" s="3">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="I21" s="4">
-        <v>92.0</v>
+        <v>91.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="3">
-        <v>25.74</v>
+        <v>25.59</v>
       </c>
       <c r="D22" s="3">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="E22" s="3">
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>353.6</v>
+        <v>351.9</v>
       </c>
       <c r="G22" s="2">
-        <v>12.4</v>
+        <v>14.5</v>
       </c>
       <c r="H22" s="3">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="I22" s="4">
-        <v>78.0</v>
+        <v>77.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" s="3">
-        <v>45.2</v>
+        <v>43.77</v>
       </c>
       <c r="D23" s="3">
         <v>48.7</v>
@@ -1313,30 +1320,30 @@
         <v>11.93</v>
       </c>
       <c r="F23" s="2">
-        <v>338.7</v>
+        <v>328.0</v>
       </c>
       <c r="G23" s="2">
-        <v>16.5</v>
+        <v>16.0</v>
       </c>
       <c r="H23" s="3">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="I23" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="3">
-        <v>26.16</v>
+        <v>25.01</v>
       </c>
       <c r="D24" s="3">
         <v>30.9</v>
@@ -1345,33 +1352,33 @@
         <v>19.02</v>
       </c>
       <c r="F24" s="2">
-        <v>1346.8</v>
+        <v>1287.6</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H24" s="3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="I24" s="4">
-        <v>64.0</v>
+        <v>62.0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" s="3">
-        <v>11.74</v>
+        <v>11.49</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1380,100 +1387,100 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>74.8</v>
+        <v>73.2</v>
       </c>
       <c r="G25" s="2">
-        <v>244.6</v>
+        <v>239.4</v>
       </c>
       <c r="H25" s="3">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I25" s="4">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="3">
-        <v>15.7</v>
+        <v>14.0</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
       </c>
       <c r="E26" s="3">
-        <v>15.0</v>
+        <v>13.54</v>
       </c>
       <c r="F26" s="2">
-        <v>141.6</v>
+        <v>126.2</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H26" s="3">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="I26" s="4">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" s="3">
-        <v>8.95</v>
+        <v>10.16</v>
       </c>
       <c r="D27" s="3">
-        <v>8.96</v>
+        <v>10.52</v>
       </c>
       <c r="E27" s="3">
         <v>4.9</v>
       </c>
       <c r="F27" s="2">
-        <v>331.0</v>
+        <v>375.7</v>
       </c>
       <c r="G27" s="2">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="H27" s="3">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="I27" s="4">
-        <v>66.0</v>
+        <v>83.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" s="3">
-        <v>46.07</v>
+        <v>43.46</v>
       </c>
       <c r="D28" s="3">
         <v>56.25</v>
@@ -1482,19 +1489,19 @@
         <v>18.57</v>
       </c>
       <c r="F28" s="2">
-        <v>611.8</v>
+        <v>577.9</v>
       </c>
       <c r="G28" s="2">
-        <v>77.0</v>
+        <v>108.9</v>
       </c>
       <c r="H28" s="3">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="I28" s="4">
-        <v>89.0</v>
+        <v>88.0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1"/>
@@ -2467,6 +2474,7 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Bxr0ZCTW3hGLQJvuJGQ/sfYCwJxSnymtlzriFfsmdSs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="14Gn4WDUWuuczmac7oLrEWRTsMX0BWsMEqx15/BsmmM="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
   <si>
     <t>Company</t>
   </si>
@@ -57,96 +57,102 @@
     <t>APT</t>
   </si>
   <si>
+    <t>nmf</t>
+  </si>
+  <si>
+    <t>(3/11/26) Alpha Pro Tech, Ltd. (APT)</t>
+  </si>
+  <si>
+    <t>Amplify Energy Corp.</t>
+  </si>
+  <si>
+    <t>AMPY</t>
+  </si>
+  <si>
+    <t>Currently qualifies TTM adjusted earnings positive</t>
+  </si>
+  <si>
+    <t>(3/9/26) Amplify Energy Corp. (AMPY)</t>
+  </si>
+  <si>
+    <t>Castor Maritime Inc.</t>
+  </si>
+  <si>
+    <t>CTRM</t>
+  </si>
+  <si>
+    <t>TTM adjusted earnings positive</t>
+  </si>
+  <si>
+    <t>News Archive for CTRM</t>
+  </si>
+  <si>
+    <t>Core Molding Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>(3/12/26) Core Molding Technologies, Inc. (CMT)</t>
+  </si>
+  <si>
+    <t>Covenant Logistics Group, Inc.</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>News Archive for CVLG</t>
+  </si>
+  <si>
+    <t>DMC Global Inc.</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>Earnings probation 2025q4</t>
+  </si>
+  <si>
+    <t>News Archive for BOOM</t>
+  </si>
+  <si>
+    <t>Ennis, Inc.</t>
+  </si>
+  <si>
+    <t>EBF</t>
+  </si>
+  <si>
+    <t>News Archive for EBF</t>
+  </si>
+  <si>
+    <t>Escalade, Incorporated</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>News Archive for ESCA</t>
+  </si>
+  <si>
+    <t>Euroseas Ltd.</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>News Archive for ESEA</t>
+  </si>
+  <si>
+    <t>FONAR Corporation</t>
+  </si>
+  <si>
+    <t>FONR</t>
+  </si>
+  <si>
     <t>Currently qualifies</t>
   </si>
   <si>
-    <t>News Archive for APT</t>
-  </si>
-  <si>
-    <t>Amplify Energy Corp.</t>
-  </si>
-  <si>
-    <t>AMPY</t>
-  </si>
-  <si>
-    <t>nmf</t>
-  </si>
-  <si>
-    <t>TTM adjusted earnings positive</t>
-  </si>
-  <si>
-    <t>News Archive for AMPY</t>
-  </si>
-  <si>
-    <t>Castor Maritime Inc.</t>
-  </si>
-  <si>
-    <t>CTRM</t>
-  </si>
-  <si>
-    <t>News Archive for CTRM</t>
-  </si>
-  <si>
-    <t>Core Molding Technologies, Inc.</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>News Archive for CMT</t>
-  </si>
-  <si>
-    <t>Covenant Logistics Group, Inc.</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>News Archive for CVLG</t>
-  </si>
-  <si>
-    <t>DMC Global Inc.</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>News Archive for BOOM</t>
-  </si>
-  <si>
-    <t>Ennis, Inc.</t>
-  </si>
-  <si>
-    <t>EBF</t>
-  </si>
-  <si>
-    <t>News Archive for EBF</t>
-  </si>
-  <si>
-    <t>Escalade, Incorporated</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>News Archive for ESCA</t>
-  </si>
-  <si>
-    <t>Euroseas Ltd.</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>News Archive for ESEA</t>
-  </si>
-  <si>
-    <t>FONAR Corporation</t>
-  </si>
-  <si>
-    <t>FONR</t>
-  </si>
-  <si>
     <t>News Archive for FONR</t>
   </si>
   <si>
@@ -165,10 +171,10 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Approaching size limit Exceeds value limit</t>
-  </si>
-  <si>
-    <t>News Archive for GILT</t>
+    <t>Exceeds size limit Exceeds value limit</t>
+  </si>
+  <si>
+    <t>(3/10/26) Gilat Satellite Networks Ltd. (GILT)</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -198,7 +204,7 @@
     <t>MG</t>
   </si>
   <si>
-    <t>(3/4/26) Mistras Group, Inc. (MG)</t>
+    <t>News Archive for MG</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -207,7 +213,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>(3/4/26) NACCO Industries, Inc. (NC)</t>
+    <t>News Archive for NC</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -225,7 +231,7 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>(3/4/26) NCS Multistage Holdings, Inc. (NCSM)</t>
+    <t>News Archive for NCSM</t>
   </si>
   <si>
     <t>Oil States International, Inc.</t>
@@ -243,7 +249,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>News Archive for PANL</t>
+    <t>(3/10/26) Pangaea Logistics Solutions Ltd. (PANL)</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -252,7 +258,16 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>(3/4/26) Park-Ohio Holdings Corp. (PKOH)</t>
+    <t>News Archive for PKOH</t>
+  </si>
+  <si>
+    <t>Regis Corporation</t>
+  </si>
+  <si>
+    <t>RGS</t>
+  </si>
+  <si>
+    <t>News Archive for RGS</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -264,25 +279,13 @@
     <t>News Archive for RCKY</t>
   </si>
   <si>
-    <t>Ryerson Holding Corporation</t>
-  </si>
-  <si>
-    <t>RYZ</t>
-  </si>
-  <si>
-    <t>Merged with Olympic Steel (ZEUS) Exceeds size limit</t>
-  </si>
-  <si>
-    <t>News Archive for RYZ</t>
-  </si>
-  <si>
     <t>Saga Communications, Inc.</t>
   </si>
   <si>
     <t>SGA</t>
   </si>
   <si>
-    <t>News Archive for SGA</t>
+    <t>(3/12/26) Saga Communications, Inc. (SGA)</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -291,7 +294,7 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>News Archive for SDHC</t>
+    <t>(3/11/26) Smith Douglas Homes Corp. (SDHC)</t>
   </si>
   <si>
     <t>StealthGas Inc.</t>
@@ -300,7 +303,13 @@
     <t>GASS</t>
   </si>
   <si>
-    <t>(3/2/26) StealthGas Inc. (GASS)</t>
+    <t>News Archive for GASS</t>
+  </si>
+  <si>
+    <t>The Eastern Company</t>
+  </si>
+  <si>
+    <t>EML</t>
   </si>
   <si>
     <t>Vishay Precision Group, Inc.</t>
@@ -618,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.17</v>
+        <v>5.03</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
@@ -627,19 +636,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>53.6</v>
-      </c>
-      <c r="G2" s="2">
-        <v>15.3</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.85</v>
+        <v>51.4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="I2" s="4">
-        <v>59.0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>58.0</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>14</v>
@@ -653,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>6.1</v>
+        <v>6.54</v>
       </c>
       <c r="D3" s="3">
         <v>6.55</v>
@@ -662,54 +668,54 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>246.9</v>
-      </c>
-      <c r="G3" s="2" t="s">
+        <v>250.1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="I3" s="4">
+        <v>90.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="3">
-        <v>0.63</v>
-      </c>
-      <c r="I3" s="4">
-        <v>89.0</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="3">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="D4" s="3">
-        <v>2.84</v>
+        <v>2.67</v>
       </c>
       <c r="E4" s="3">
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>61.0</v>
+        <v>64.0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -723,25 +729,25 @@
         <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>18.81</v>
+        <v>19.32</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
       </c>
       <c r="E5" s="3">
-        <v>12.25</v>
+        <v>13.36</v>
       </c>
       <c r="F5" s="2">
-        <v>161.0</v>
+        <v>165.4</v>
       </c>
       <c r="G5" s="2">
-        <v>20.3</v>
+        <v>15.1</v>
       </c>
       <c r="H5" s="3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I5" s="4">
-        <v>46.0</v>
+        <v>44.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>25</v>
@@ -755,7 +761,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>26.31</v>
+        <v>24.7</v>
       </c>
       <c r="D6" s="3">
         <v>30.43</v>
@@ -764,16 +770,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>659.9</v>
+        <v>617.8</v>
       </c>
       <c r="G6" s="2">
-        <v>164.4</v>
+        <v>153.9</v>
       </c>
       <c r="H6" s="3">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="I6" s="4">
-        <v>63.0</v>
+        <v>62.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -787,106 +793,106 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>5.43</v>
+        <v>4.73</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
       </c>
       <c r="E7" s="3">
-        <v>5.41</v>
+        <v>4.73</v>
       </c>
       <c r="F7" s="2">
-        <v>111.2</v>
+        <v>99.5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H7" s="3">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="I7" s="4">
-        <v>26.0</v>
+        <v>23.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>21.31</v>
+        <v>21.15</v>
       </c>
       <c r="D8" s="3">
-        <v>22.01</v>
+        <v>21.6</v>
       </c>
       <c r="E8" s="3">
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>539.0</v>
+        <v>537.7</v>
       </c>
       <c r="G8" s="2">
         <v>12.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I8" s="4">
-        <v>68.0</v>
+        <v>73.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>15.0</v>
+        <v>17.18</v>
       </c>
       <c r="D9" s="3">
-        <v>16.99</v>
+        <v>17.7</v>
       </c>
       <c r="E9" s="3">
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>205.4</v>
+        <v>226.9</v>
       </c>
       <c r="G9" s="2">
-        <v>15.2</v>
+        <v>16.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="I9" s="4">
-        <v>71.0</v>
+        <v>84.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>64.76</v>
+        <v>63.0</v>
       </c>
       <c r="D10" s="3">
         <v>72.87</v>
@@ -895,30 +901,30 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>456.9</v>
+        <v>461.0</v>
       </c>
       <c r="G10" s="2">
         <v>3.5</v>
       </c>
       <c r="H10" s="3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I10" s="4">
-        <v>57.0</v>
+        <v>60.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>18.49</v>
+        <v>18.38</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -927,7 +933,7 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.2</v>
+        <v>120.8</v>
       </c>
       <c r="G11" s="2">
         <v>16.8</v>
@@ -939,21 +945,21 @@
         <v>72.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
-        <v>18.38</v>
+        <v>17.01</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -962,30 +968,33 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>130.7</v>
+        <v>121.0</v>
       </c>
       <c r="G12" s="2">
-        <v>8.3</v>
+        <v>7.7</v>
       </c>
       <c r="H12" s="3">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="I12" s="4">
-        <v>34.0</v>
+        <v>28.0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" s="3">
-        <v>16.14</v>
+        <v>16.45</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -994,33 +1003,33 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1180.5</v>
+        <v>1233.2</v>
       </c>
       <c r="G13" s="2">
-        <v>41.1</v>
+        <v>42.9</v>
       </c>
       <c r="H13" s="3">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I13" s="4">
-        <v>92.0</v>
+        <v>91.0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3">
-        <v>22.63</v>
+        <v>22.8</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1029,65 +1038,65 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>548.0</v>
+        <v>552.6</v>
       </c>
       <c r="G14" s="2">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="H14" s="3">
         <v>0.95</v>
       </c>
       <c r="I14" s="4">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C15" s="3">
-        <v>8.6</v>
+        <v>8.82</v>
       </c>
       <c r="D15" s="3">
-        <v>21.23</v>
+        <v>21.19</v>
       </c>
       <c r="E15" s="3">
         <v>7.77</v>
       </c>
       <c r="F15" s="2">
-        <v>84.3</v>
+        <v>84.7</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H15" s="3">
         <v>0.63</v>
       </c>
       <c r="I15" s="4">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" s="3">
-        <v>14.82</v>
+        <v>14.16</v>
       </c>
       <c r="D16" s="3">
         <v>15.84</v>
@@ -1096,30 +1105,30 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>467.5</v>
-      </c>
-      <c r="G16" s="2">
-        <v>26.0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>2.06</v>
+        <v>450.6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="I16" s="4">
         <v>89.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>48.91</v>
+        <v>51.44</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1128,94 +1137,94 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>368.5</v>
+        <v>408.8</v>
       </c>
       <c r="G17" s="2">
-        <v>20.8</v>
+        <v>23.1</v>
       </c>
       <c r="H17" s="3">
-        <v>0.85</v>
+        <v>0.94</v>
       </c>
       <c r="I17" s="4">
-        <v>76.0</v>
+        <v>85.0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>37.8</v>
+        <v>35.59</v>
       </c>
       <c r="D18" s="3">
-        <v>39.67</v>
+        <v>40.0</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>475.1</v>
+        <v>454.6</v>
       </c>
       <c r="G18" s="2">
-        <v>25.7</v>
+        <v>24.6</v>
       </c>
       <c r="H18" s="3">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="I18" s="4">
-        <v>85.0</v>
+        <v>84.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>48.35</v>
+        <v>64.08</v>
       </c>
       <c r="D19" s="3">
-        <v>53.69</v>
+        <v>68.4</v>
       </c>
       <c r="E19" s="3">
-        <v>23.89</v>
+        <v>25.09</v>
       </c>
       <c r="F19" s="2">
-        <v>122.9</v>
+        <v>164.6</v>
       </c>
       <c r="G19" s="2">
-        <v>10.7</v>
+        <v>7.5</v>
       </c>
       <c r="H19" s="3">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="I19" s="4">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>12.23</v>
+        <v>11.89</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
@@ -1224,30 +1233,33 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>736.3</v>
+        <v>727.3</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I20" s="4">
-        <v>96.0</v>
+        <v>97.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" s="3">
-        <v>8.36</v>
+        <v>6.83</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1256,30 +1268,30 @@
         <v>3.93</v>
       </c>
       <c r="F21" s="2">
-        <v>543.2</v>
+        <v>457.1</v>
       </c>
       <c r="G21" s="2">
-        <v>31.3</v>
+        <v>26.3</v>
       </c>
       <c r="H21" s="3">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="I21" s="4">
-        <v>91.0</v>
+        <v>81.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>25.59</v>
+        <v>24.42</v>
       </c>
       <c r="D22" s="3">
         <v>29.5</v>
@@ -1288,97 +1300,100 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>351.9</v>
+        <v>338.7</v>
       </c>
       <c r="G22" s="2">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="H22" s="3">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="I22" s="4">
-        <v>77.0</v>
+        <v>70.0</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C23" s="3">
-        <v>43.77</v>
+        <v>22.36</v>
       </c>
       <c r="D23" s="3">
-        <v>48.7</v>
+        <v>31.5</v>
       </c>
       <c r="E23" s="3">
-        <v>11.93</v>
+        <v>15.0</v>
       </c>
       <c r="F23" s="2">
-        <v>328.0</v>
+        <v>52.5</v>
       </c>
       <c r="G23" s="2">
-        <v>16.0</v>
+        <v>0.5</v>
       </c>
       <c r="H23" s="3">
-        <v>1.33</v>
+        <v>0.28</v>
       </c>
       <c r="I23" s="4">
-        <v>88.0</v>
+        <v>27.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C24" s="3">
-        <v>25.01</v>
+        <v>42.62</v>
       </c>
       <c r="D24" s="3">
-        <v>30.9</v>
+        <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>19.02</v>
+        <v>11.93</v>
       </c>
       <c r="F24" s="2">
-        <v>1287.6</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>17</v>
+        <v>329.2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>14.8</v>
       </c>
       <c r="H24" s="3">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="I24" s="4">
-        <v>62.0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>84</v>
+        <v>90.0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" s="3">
-        <v>11.49</v>
+        <v>11.39</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1387,65 +1402,65 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>73.2</v>
+        <v>70.7</v>
       </c>
       <c r="G25" s="2">
-        <v>239.4</v>
+        <v>231.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I25" s="4">
-        <v>44.0</v>
+        <v>43.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>14.0</v>
+        <v>12.62</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
       </c>
       <c r="E26" s="3">
-        <v>13.54</v>
+        <v>11.24</v>
       </c>
       <c r="F26" s="2">
-        <v>126.2</v>
+        <v>100.8</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H26" s="3">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="I26" s="4">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>10.16</v>
+        <v>8.73</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
@@ -1454,57 +1469,88 @@
         <v>4.9</v>
       </c>
       <c r="F27" s="2">
-        <v>375.7</v>
+        <v>331.7</v>
       </c>
       <c r="G27" s="2">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="H27" s="3">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="I27" s="4">
-        <v>83.0</v>
+        <v>76.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>43.46</v>
+        <v>20.93</v>
       </c>
       <c r="D28" s="3">
+        <v>27.15</v>
+      </c>
+      <c r="E28" s="3">
+        <v>17.61</v>
+      </c>
+      <c r="F28" s="2">
+        <v>124.3</v>
+      </c>
+      <c r="G28" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>35.0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="3">
+        <v>41.01</v>
+      </c>
+      <c r="D29" s="3">
         <v>56.25</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E29" s="3">
         <v>18.57</v>
       </c>
-      <c r="F28" s="2">
-        <v>577.9</v>
-      </c>
-      <c r="G28" s="2">
-        <v>108.9</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1.72</v>
-      </c>
-      <c r="I28" s="4">
-        <v>88.0</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1"/>
+      <c r="F29" s="2">
+        <v>554.6</v>
+      </c>
+      <c r="G29" s="2">
+        <v>104.5</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="I29" s="4">
+        <v>86.0</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="14Gn4WDUWuuczmac7oLrEWRTsMX0BWsMEqx15/BsmmM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ub342GVPXr5DGRaRDTBOXjgeqoO0kd9PWji7yQZ8O8I="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
   <si>
     <t>Company</t>
   </si>
@@ -57,30 +57,33 @@
     <t>APT</t>
   </si>
   <si>
+    <t>Currently qualifies</t>
+  </si>
+  <si>
+    <t>News Archive for APT</t>
+  </si>
+  <si>
+    <t>Amplify Energy Corp.</t>
+  </si>
+  <si>
+    <t>AMPY</t>
+  </si>
+  <si>
+    <t>Currently qualifies TTM adjusted earnings positive</t>
+  </si>
+  <si>
+    <t>News Archive for AMPY</t>
+  </si>
+  <si>
+    <t>Castor Maritime Inc.</t>
+  </si>
+  <si>
+    <t>CTRM</t>
+  </si>
+  <si>
     <t>nmf</t>
   </si>
   <si>
-    <t>(3/11/26) Alpha Pro Tech, Ltd. (APT)</t>
-  </si>
-  <si>
-    <t>Amplify Energy Corp.</t>
-  </si>
-  <si>
-    <t>AMPY</t>
-  </si>
-  <si>
-    <t>Currently qualifies TTM adjusted earnings positive</t>
-  </si>
-  <si>
-    <t>(3/9/26) Amplify Energy Corp. (AMPY)</t>
-  </si>
-  <si>
-    <t>Castor Maritime Inc.</t>
-  </si>
-  <si>
-    <t>CTRM</t>
-  </si>
-  <si>
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
@@ -93,7 +96,7 @@
     <t>CMT</t>
   </si>
   <si>
-    <t>(3/12/26) Core Molding Technologies, Inc. (CMT)</t>
+    <t>News Archive for CMT</t>
   </si>
   <si>
     <t>Covenant Logistics Group, Inc.</t>
@@ -150,9 +153,6 @@
     <t>FONR</t>
   </si>
   <si>
-    <t>Currently qualifies</t>
-  </si>
-  <si>
     <t>News Archive for FONR</t>
   </si>
   <si>
@@ -171,10 +171,10 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Exceeds size limit Exceeds value limit</t>
-  </si>
-  <si>
-    <t>(3/10/26) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>Exceeds size limit</t>
+  </si>
+  <si>
+    <t>News Archive for GILT</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -222,7 +222,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>News Archive for NGS</t>
+    <t>(3/16/26) Natural Gas Services Group, Inc. (NGS)</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -249,7 +249,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>(3/10/26) Pangaea Logistics Solutions Ltd. (PANL)</t>
+    <t>News Archive for PANL</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -285,7 +285,7 @@
     <t>SGA</t>
   </si>
   <si>
-    <t>(3/12/26) Saga Communications, Inc. (SGA)</t>
+    <t>News Archive for SGA</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -294,7 +294,7 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>(3/11/26) Smith Douglas Homes Corp. (SDHC)</t>
+    <t>News Archive for SDHC</t>
   </si>
   <si>
     <t>StealthGas Inc.</t>
@@ -627,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.03</v>
+        <v>4.5</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
@@ -636,16 +636,19 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>51.4</v>
-      </c>
-      <c r="G2" s="2" t="s">
+        <v>45.8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>13.6</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.73</v>
+      </c>
+      <c r="I2" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="4">
-        <v>58.0</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>14</v>
@@ -659,22 +662,22 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>6.54</v>
+        <v>6.52</v>
       </c>
       <c r="D3" s="3">
-        <v>6.55</v>
+        <v>6.79</v>
       </c>
       <c r="E3" s="3">
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>250.1</v>
+        <v>269.0</v>
       </c>
       <c r="G3" s="2">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="I3" s="4">
         <v>90.0</v>
@@ -694,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="D4" s="3">
         <v>2.67</v>
@@ -703,65 +706,65 @@
         <v>1.84</v>
       </c>
       <c r="F4" s="2">
-        <v>20.9</v>
+        <v>18.6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>64.0</v>
+        <v>42.0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3">
-        <v>19.32</v>
+        <v>20.06</v>
       </c>
       <c r="D5" s="3">
         <v>22.29</v>
       </c>
       <c r="E5" s="3">
-        <v>13.36</v>
+        <v>13.99</v>
       </c>
       <c r="F5" s="2">
-        <v>165.4</v>
+        <v>170.4</v>
       </c>
       <c r="G5" s="2">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H5" s="3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="I5" s="4">
-        <v>44.0</v>
+        <v>48.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="D6" s="3">
         <v>30.43</v>
@@ -770,65 +773,65 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>617.8</v>
+        <v>634.6</v>
       </c>
       <c r="G6" s="2">
-        <v>153.9</v>
+        <v>158.1</v>
       </c>
       <c r="H6" s="3">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="I6" s="4">
-        <v>62.0</v>
+        <v>71.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
       </c>
       <c r="E7" s="3">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>99.5</v>
+        <v>97.3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I7" s="4">
-        <v>23.0</v>
+        <v>19.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3">
-        <v>21.15</v>
+        <v>20.44</v>
       </c>
       <c r="D8" s="3">
         <v>21.6</v>
@@ -837,62 +840,62 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>537.7</v>
+        <v>517.0</v>
       </c>
       <c r="G8" s="2">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="H8" s="3">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="I8" s="4">
-        <v>73.0</v>
+        <v>72.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3">
-        <v>17.18</v>
+        <v>17.55</v>
       </c>
       <c r="D9" s="3">
-        <v>17.7</v>
+        <v>18.4</v>
       </c>
       <c r="E9" s="3">
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>226.9</v>
+        <v>240.4</v>
       </c>
       <c r="G9" s="2">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="I9" s="4">
-        <v>84.0</v>
+        <v>87.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3">
-        <v>63.0</v>
+        <v>65.5</v>
       </c>
       <c r="D10" s="3">
         <v>72.87</v>
@@ -901,7 +904,7 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>461.0</v>
+        <v>462.2</v>
       </c>
       <c r="G10" s="2">
         <v>3.5</v>
@@ -910,18 +913,18 @@
         <v>1.22</v>
       </c>
       <c r="I10" s="4">
-        <v>60.0</v>
+        <v>62.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3">
         <v>18.38</v>
@@ -933,19 +936,19 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>120.8</v>
+        <v>120.5</v>
       </c>
       <c r="G11" s="2">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="H11" s="3">
         <v>0.68</v>
       </c>
       <c r="I11" s="4">
-        <v>72.0</v>
+        <v>77.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>45</v>
@@ -959,7 +962,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="3">
-        <v>17.01</v>
+        <v>17.4</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -968,19 +971,19 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>121.0</v>
+        <v>123.8</v>
       </c>
       <c r="G12" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H12" s="3">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="I12" s="4">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>48</v>
@@ -994,7 +997,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="3">
-        <v>16.45</v>
+        <v>16.25</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -1003,16 +1006,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1233.2</v>
+        <v>1226.4</v>
       </c>
       <c r="G13" s="2">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="H13" s="3">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="I13" s="4">
-        <v>91.0</v>
+        <v>89.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>51</v>
@@ -1029,7 +1032,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="3">
-        <v>22.8</v>
+        <v>23.44</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1038,13 +1041,13 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>552.6</v>
+        <v>567.6</v>
       </c>
       <c r="G14" s="2">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="H14" s="3">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="I14" s="4">
         <v>26.0</v>
@@ -1061,25 +1064,25 @@
         <v>57</v>
       </c>
       <c r="C15" s="3">
-        <v>8.82</v>
+        <v>7.72</v>
       </c>
       <c r="D15" s="3">
         <v>21.19</v>
       </c>
       <c r="E15" s="3">
-        <v>7.77</v>
+        <v>7.71</v>
       </c>
       <c r="F15" s="2">
-        <v>84.7</v>
+        <v>75.7</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H15" s="3">
-        <v>0.63</v>
+        <v>0.56</v>
       </c>
       <c r="I15" s="4">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>58</v>
@@ -1096,7 +1099,7 @@
         <v>61</v>
       </c>
       <c r="C16" s="3">
-        <v>14.16</v>
+        <v>14.05</v>
       </c>
       <c r="D16" s="3">
         <v>15.84</v>
@@ -1105,13 +1108,13 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>450.6</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>443.9</v>
+      </c>
+      <c r="G16" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.89</v>
       </c>
       <c r="I16" s="4">
         <v>89.0</v>
@@ -1128,7 +1131,7 @@
         <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>51.44</v>
+        <v>48.6</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1137,16 +1140,16 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>408.8</v>
+        <v>366.2</v>
       </c>
       <c r="G17" s="2">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="H17" s="3">
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
       <c r="I17" s="4">
-        <v>85.0</v>
+        <v>73.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -1160,25 +1163,25 @@
         <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>35.59</v>
+        <v>39.06</v>
       </c>
       <c r="D18" s="3">
-        <v>40.0</v>
+        <v>40.73</v>
       </c>
       <c r="E18" s="3">
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>454.6</v>
+        <v>491.7</v>
       </c>
       <c r="G18" s="2">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="H18" s="3">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="I18" s="4">
-        <v>84.0</v>
+        <v>89.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>68</v>
@@ -1192,25 +1195,25 @@
         <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>64.08</v>
+        <v>68.3</v>
       </c>
       <c r="D19" s="3">
-        <v>68.4</v>
+        <v>73.0</v>
       </c>
       <c r="E19" s="3">
         <v>25.09</v>
       </c>
       <c r="F19" s="2">
-        <v>164.6</v>
+        <v>173.9</v>
       </c>
       <c r="G19" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="H19" s="3">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="I19" s="4">
-        <v>79.0</v>
+        <v>87.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>71</v>
@@ -1224,7 +1227,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>11.89</v>
+        <v>12.16</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
@@ -1233,19 +1236,19 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>727.3</v>
+        <v>732.1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H20" s="3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I20" s="4">
         <v>97.0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>74</v>
@@ -1259,7 +1262,7 @@
         <v>76</v>
       </c>
       <c r="C21" s="3">
-        <v>6.83</v>
+        <v>6.78</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1268,16 +1271,16 @@
         <v>3.93</v>
       </c>
       <c r="F21" s="2">
-        <v>457.1</v>
+        <v>440.5</v>
       </c>
       <c r="G21" s="2">
-        <v>26.3</v>
+        <v>22.6</v>
       </c>
       <c r="H21" s="3">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="I21" s="4">
-        <v>81.0</v>
+        <v>79.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>77</v>
@@ -1291,7 +1294,7 @@
         <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>24.42</v>
+        <v>23.37</v>
       </c>
       <c r="D22" s="3">
         <v>29.5</v>
@@ -1300,19 +1303,19 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>338.7</v>
+        <v>321.4</v>
       </c>
       <c r="G22" s="2">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="H22" s="3">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="I22" s="4">
-        <v>70.0</v>
+        <v>61.0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>80</v>
@@ -1326,7 +1329,7 @@
         <v>82</v>
       </c>
       <c r="C23" s="3">
-        <v>22.36</v>
+        <v>23.33</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1335,19 +1338,19 @@
         <v>15.0</v>
       </c>
       <c r="F23" s="2">
-        <v>52.5</v>
+        <v>58.3</v>
       </c>
       <c r="G23" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H23" s="3">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I23" s="4">
-        <v>27.0</v>
+        <v>37.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>83</v>
@@ -1361,7 +1364,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="3">
-        <v>42.62</v>
+        <v>39.06</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
@@ -1370,16 +1373,16 @@
         <v>11.93</v>
       </c>
       <c r="F24" s="2">
-        <v>329.2</v>
+        <v>294.4</v>
       </c>
       <c r="G24" s="2">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="H24" s="3">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="I24" s="4">
-        <v>90.0</v>
+        <v>83.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>86</v>
@@ -1393,7 +1396,7 @@
         <v>88</v>
       </c>
       <c r="C25" s="3">
-        <v>11.39</v>
+        <v>11.99</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1402,16 +1405,16 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>70.7</v>
+        <v>76.4</v>
       </c>
       <c r="G25" s="2">
-        <v>231.0</v>
+        <v>249.8</v>
       </c>
       <c r="H25" s="3">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="I25" s="4">
-        <v>43.0</v>
+        <v>53.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>89</v>
@@ -1425,28 +1428,28 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>12.62</v>
+        <v>11.34</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
       </c>
       <c r="E26" s="3">
-        <v>11.24</v>
+        <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>100.8</v>
+        <v>100.3</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H26" s="3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I26" s="4">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>92</v>
@@ -1460,7 +1463,7 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>8.73</v>
+        <v>9.09</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
@@ -1469,19 +1472,19 @@
         <v>4.9</v>
       </c>
       <c r="F27" s="2">
-        <v>331.7</v>
+        <v>336.1</v>
       </c>
       <c r="G27" s="2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H27" s="3">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="I27" s="4">
-        <v>76.0</v>
+        <v>83.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>95</v>
@@ -1495,28 +1498,28 @@
         <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>20.93</v>
+        <v>20.33</v>
       </c>
       <c r="D28" s="3">
-        <v>27.15</v>
+        <v>26.77</v>
       </c>
       <c r="E28" s="3">
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>124.3</v>
+        <v>122.8</v>
       </c>
       <c r="G28" s="2">
-        <v>21.0</v>
+        <v>20.8</v>
       </c>
       <c r="H28" s="3">
-        <v>1.0</v>
+        <v>0.99</v>
       </c>
       <c r="I28" s="4">
-        <v>35.0</v>
+        <v>31.0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1527,7 +1530,7 @@
         <v>99</v>
       </c>
       <c r="C29" s="3">
-        <v>41.01</v>
+        <v>40.64</v>
       </c>
       <c r="D29" s="3">
         <v>56.25</v>
@@ -1536,16 +1539,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>554.6</v>
+        <v>540.4</v>
       </c>
       <c r="G29" s="2">
-        <v>104.5</v>
+        <v>101.9</v>
       </c>
       <c r="H29" s="3">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="I29" s="4">
-        <v>86.0</v>
+        <v>80.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>100</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ub342GVPXr5DGRaRDTBOXjgeqoO0kd9PWji7yQZ8O8I="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Fv8v96lITSZNOoR1fOFmH/JqiICWjOPpRsHaY4q2VxE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
   <si>
     <t>Company</t>
   </si>
@@ -222,7 +222,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>(3/16/26) Natural Gas Services Group, Inc. (NGS)</t>
+    <t>News Archive for NGS</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -627,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
@@ -636,7 +636,7 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="G2" s="2">
         <v>13.6</v>
@@ -645,7 +645,7 @@
         <v>0.73</v>
       </c>
       <c r="I2" s="4">
-        <v>50.0</v>
+        <v>46.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -662,7 +662,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>6.52</v>
+        <v>6.56</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -671,16 +671,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>269.0</v>
+        <v>273.6</v>
       </c>
       <c r="G3" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H3" s="3">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I3" s="4">
-        <v>90.0</v>
+        <v>87.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>17</v>
@@ -697,25 +697,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="D4" s="3">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="E4" s="3">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="F4" s="2">
-        <v>18.6</v>
+        <v>17.2</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I4" s="4">
-        <v>42.0</v>
+        <v>34.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>22</v>
@@ -732,25 +732,25 @@
         <v>25</v>
       </c>
       <c r="C5" s="3">
-        <v>20.06</v>
+        <v>21.96</v>
       </c>
       <c r="D5" s="3">
-        <v>22.29</v>
+        <v>22.66</v>
       </c>
       <c r="E5" s="3">
         <v>13.99</v>
       </c>
       <c r="F5" s="2">
-        <v>170.4</v>
+        <v>191.5</v>
       </c>
       <c r="G5" s="2">
-        <v>15.6</v>
+        <v>17.5</v>
       </c>
       <c r="H5" s="3">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="I5" s="4">
-        <v>48.0</v>
+        <v>59.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>26</v>
@@ -764,7 +764,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="3">
-        <v>25.3</v>
+        <v>26.58</v>
       </c>
       <c r="D6" s="3">
         <v>30.43</v>
@@ -773,16 +773,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>634.6</v>
+        <v>680.3</v>
       </c>
       <c r="G6" s="2">
-        <v>158.1</v>
+        <v>169.5</v>
       </c>
       <c r="H6" s="3">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="I6" s="4">
-        <v>71.0</v>
+        <v>81.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>29</v>
@@ -796,7 +796,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="3">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -805,16 +805,16 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>97.3</v>
+        <v>107.1</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="3">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="I7" s="4">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>32</v>
@@ -831,7 +831,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="3">
-        <v>20.44</v>
+        <v>21.32</v>
       </c>
       <c r="D8" s="3">
         <v>21.6</v>
@@ -840,16 +840,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>517.0</v>
+        <v>542.3</v>
       </c>
       <c r="G8" s="2">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="H8" s="3">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="I8" s="4">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>36</v>
@@ -863,10 +863,10 @@
         <v>38</v>
       </c>
       <c r="C9" s="3">
-        <v>17.55</v>
+        <v>17.35</v>
       </c>
       <c r="D9" s="3">
-        <v>18.4</v>
+        <v>18.61</v>
       </c>
       <c r="E9" s="3">
         <v>11.41</v>
@@ -881,7 +881,7 @@
         <v>1.39</v>
       </c>
       <c r="I9" s="4">
-        <v>87.0</v>
+        <v>86.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>39</v>
@@ -895,7 +895,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="3">
-        <v>65.5</v>
+        <v>60.81</v>
       </c>
       <c r="D10" s="3">
         <v>72.87</v>
@@ -904,16 +904,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>462.2</v>
+        <v>441.8</v>
       </c>
       <c r="G10" s="2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H10" s="3">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="I10" s="4">
-        <v>62.0</v>
+        <v>58.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>42</v>
@@ -927,7 +927,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="3">
-        <v>18.38</v>
+        <v>18.57</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -936,16 +936,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>120.5</v>
+        <v>121.5</v>
       </c>
       <c r="G11" s="2">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="H11" s="3">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,7 +962,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="3">
-        <v>17.4</v>
+        <v>17.83</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -971,13 +971,13 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>123.8</v>
+        <v>128.1</v>
       </c>
       <c r="G12" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="H12" s="3">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="I12" s="4">
         <v>34.0</v>
@@ -997,7 +997,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="3">
-        <v>16.25</v>
+        <v>15.39</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -1006,16 +1006,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1226.4</v>
+        <v>1250.6</v>
       </c>
       <c r="G13" s="2">
-        <v>47.8</v>
+        <v>48.7</v>
       </c>
       <c r="H13" s="3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I13" s="4">
-        <v>89.0</v>
+        <v>88.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>51</v>
@@ -1032,7 +1032,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="3">
-        <v>23.44</v>
+        <v>24.19</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1041,16 +1041,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>567.6</v>
+        <v>594.0</v>
       </c>
       <c r="G14" s="2">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
       <c r="H14" s="3">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="I14" s="4">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>55</v>
@@ -1064,25 +1064,25 @@
         <v>57</v>
       </c>
       <c r="C15" s="3">
-        <v>7.72</v>
+        <v>7.58</v>
       </c>
       <c r="D15" s="3">
-        <v>21.19</v>
+        <v>20.83</v>
       </c>
       <c r="E15" s="3">
-        <v>7.71</v>
+        <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>75.7</v>
+        <v>92.8</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="3">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
       <c r="I15" s="4">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>58</v>
@@ -1099,7 +1099,7 @@
         <v>61</v>
       </c>
       <c r="C16" s="3">
-        <v>14.05</v>
+        <v>14.59</v>
       </c>
       <c r="D16" s="3">
         <v>15.84</v>
@@ -1108,16 +1108,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>443.9</v>
+        <v>477.4</v>
       </c>
       <c r="G16" s="2">
-        <v>26.5</v>
+        <v>28.5</v>
       </c>
       <c r="H16" s="3">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="I16" s="4">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>62</v>
@@ -1131,7 +1131,7 @@
         <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>48.6</v>
+        <v>51.3</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1140,13 +1140,13 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>366.2</v>
+        <v>382.1</v>
       </c>
       <c r="G17" s="2">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="H17" s="3">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="I17" s="4">
         <v>73.0</v>
@@ -1163,7 +1163,7 @@
         <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>39.06</v>
+        <v>39.81</v>
       </c>
       <c r="D18" s="3">
         <v>40.73</v>
@@ -1172,16 +1172,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>491.7</v>
+        <v>499.0</v>
       </c>
       <c r="G18" s="2">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="H18" s="3">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="I18" s="4">
-        <v>89.0</v>
+        <v>88.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>68</v>
@@ -1195,22 +1195,22 @@
         <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>68.3</v>
+        <v>73.0</v>
       </c>
       <c r="D19" s="3">
-        <v>73.0</v>
+        <v>75.57</v>
       </c>
       <c r="E19" s="3">
         <v>25.09</v>
       </c>
       <c r="F19" s="2">
-        <v>173.9</v>
+        <v>180.1</v>
       </c>
       <c r="G19" s="2">
-        <v>7.9</v>
+        <v>8.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="I19" s="4">
         <v>87.0</v>
@@ -1227,7 +1227,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>12.16</v>
+        <v>12.2</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
@@ -1236,13 +1236,13 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>732.1</v>
+        <v>722.5</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="3">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="I20" s="4">
         <v>97.0</v>
@@ -1262,7 +1262,7 @@
         <v>76</v>
       </c>
       <c r="C21" s="3">
-        <v>6.78</v>
+        <v>6.77</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1271,16 +1271,16 @@
         <v>3.93</v>
       </c>
       <c r="F21" s="2">
-        <v>440.5</v>
+        <v>444.4</v>
       </c>
       <c r="G21" s="2">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="H21" s="3">
         <v>1.03</v>
       </c>
       <c r="I21" s="4">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>77</v>
@@ -1294,7 +1294,7 @@
         <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>23.37</v>
+        <v>23.82</v>
       </c>
       <c r="D22" s="3">
         <v>29.5</v>
@@ -1303,16 +1303,16 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>321.4</v>
+        <v>334.6</v>
       </c>
       <c r="G22" s="2">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="H22" s="3">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="I22" s="4">
-        <v>61.0</v>
+        <v>75.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>13</v>
@@ -1329,7 +1329,7 @@
         <v>82</v>
       </c>
       <c r="C23" s="3">
-        <v>23.33</v>
+        <v>23.85</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1338,7 +1338,7 @@
         <v>15.0</v>
       </c>
       <c r="F23" s="2">
-        <v>58.3</v>
+        <v>59.0</v>
       </c>
       <c r="G23" s="2">
         <v>0.6</v>
@@ -1347,7 +1347,7 @@
         <v>0.31</v>
       </c>
       <c r="I23" s="4">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1364,7 +1364,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="3">
-        <v>39.06</v>
+        <v>37.91</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
@@ -1373,13 +1373,13 @@
         <v>11.93</v>
       </c>
       <c r="F24" s="2">
-        <v>294.4</v>
+        <v>287.9</v>
       </c>
       <c r="G24" s="2">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="H24" s="3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="I24" s="4">
         <v>83.0</v>
@@ -1396,7 +1396,7 @@
         <v>88</v>
       </c>
       <c r="C25" s="3">
-        <v>11.99</v>
+        <v>11.97</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1405,16 +1405,16 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>76.4</v>
+        <v>76.5</v>
       </c>
       <c r="G25" s="2">
-        <v>249.8</v>
+        <v>250.0</v>
       </c>
       <c r="H25" s="3">
         <v>0.48</v>
       </c>
       <c r="I25" s="4">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>89</v>
@@ -1428,7 +1428,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>11.34</v>
+        <v>12.0</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1437,16 +1437,16 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>100.3</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>21</v>
+        <v>110.7</v>
+      </c>
+      <c r="G26" s="2">
+        <v>10.3</v>
       </c>
       <c r="H26" s="3">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="I26" s="4">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>22</v>
@@ -1463,7 +1463,7 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>9.09</v>
+        <v>9.27</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
@@ -1472,16 +1472,16 @@
         <v>4.9</v>
       </c>
       <c r="F27" s="2">
-        <v>336.1</v>
+        <v>344.6</v>
       </c>
       <c r="G27" s="2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H27" s="3">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I27" s="4">
-        <v>83.0</v>
+        <v>86.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1498,7 +1498,7 @@
         <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>20.33</v>
+        <v>19.76</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1507,16 +1507,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>122.8</v>
+        <v>119.9</v>
       </c>
       <c r="G28" s="2">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="H28" s="3">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="I28" s="4">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1530,7 +1530,7 @@
         <v>99</v>
       </c>
       <c r="C29" s="3">
-        <v>40.64</v>
+        <v>41.55</v>
       </c>
       <c r="D29" s="3">
         <v>56.25</v>
@@ -1539,16 +1539,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>540.4</v>
+        <v>565.4</v>
       </c>
       <c r="G29" s="2">
-        <v>101.9</v>
+        <v>106.6</v>
       </c>
       <c r="H29" s="3">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="I29" s="4">
-        <v>80.0</v>
+        <v>84.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>100</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Fv8v96lITSZNOoR1fOFmH/JqiICWjOPpRsHaY4q2VxE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="FLOEbWQiOGUQLaIRdexChyNjhVl36NJIXzEQZa8ws+0="/>
     </ext>
   </extLst>
 </workbook>
@@ -627,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
@@ -636,16 +636,16 @@
         <v>4.06</v>
       </c>
       <c r="F2" s="2">
-        <v>45.6</v>
+        <v>45.2</v>
       </c>
       <c r="G2" s="2">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="H2" s="3">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I2" s="4">
-        <v>46.0</v>
+        <v>45.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -662,7 +662,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>6.56</v>
+        <v>5.98</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -671,16 +671,16 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>273.6</v>
+        <v>246.8</v>
       </c>
       <c r="G3" s="2">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H3" s="3">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="I3" s="4">
-        <v>87.0</v>
+        <v>70.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>17</v>
@@ -697,25 +697,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
       </c>
       <c r="E4" s="3">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="3">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>34.0</v>
+        <v>40.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>22</v>
@@ -732,25 +732,25 @@
         <v>25</v>
       </c>
       <c r="C5" s="3">
-        <v>21.96</v>
+        <v>22.17</v>
       </c>
       <c r="D5" s="3">
-        <v>22.66</v>
+        <v>22.97</v>
       </c>
       <c r="E5" s="3">
         <v>13.99</v>
       </c>
       <c r="F5" s="2">
-        <v>191.5</v>
+        <v>188.3</v>
       </c>
       <c r="G5" s="2">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="H5" s="3">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="I5" s="4">
-        <v>59.0</v>
+        <v>67.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>26</v>
@@ -764,7 +764,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="3">
-        <v>26.58</v>
+        <v>28.15</v>
       </c>
       <c r="D6" s="3">
         <v>30.43</v>
@@ -773,16 +773,16 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>680.3</v>
+        <v>706.1</v>
       </c>
       <c r="G6" s="2">
-        <v>169.5</v>
+        <v>175.9</v>
       </c>
       <c r="H6" s="3">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="I6" s="4">
-        <v>81.0</v>
+        <v>84.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>29</v>
@@ -796,7 +796,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="3">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -805,13 +805,13 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>107.1</v>
+        <v>113.6</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="3">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="I7" s="4">
         <v>20.0</v>
@@ -831,25 +831,25 @@
         <v>35</v>
       </c>
       <c r="C8" s="3">
-        <v>21.32</v>
+        <v>21.69</v>
       </c>
       <c r="D8" s="3">
-        <v>21.6</v>
+        <v>21.95</v>
       </c>
       <c r="E8" s="3">
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>542.3</v>
+        <v>548.6</v>
       </c>
       <c r="G8" s="2">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I8" s="4">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>36</v>
@@ -863,7 +863,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="3">
-        <v>17.35</v>
+        <v>18.21</v>
       </c>
       <c r="D9" s="3">
         <v>18.61</v>
@@ -872,16 +872,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>240.4</v>
+        <v>249.4</v>
       </c>
       <c r="G9" s="2">
-        <v>17.7</v>
+        <v>18.4</v>
       </c>
       <c r="H9" s="3">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="I9" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>39</v>
@@ -895,7 +895,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="3">
-        <v>60.81</v>
+        <v>67.28</v>
       </c>
       <c r="D10" s="3">
         <v>72.87</v>
@@ -904,16 +904,16 @@
         <v>26.3</v>
       </c>
       <c r="F10" s="2">
-        <v>441.8</v>
+        <v>474.7</v>
       </c>
       <c r="G10" s="2">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H10" s="3">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="I10" s="4">
-        <v>58.0</v>
+        <v>67.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>42</v>
@@ -927,7 +927,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="3">
-        <v>18.57</v>
+        <v>18.59</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -936,7 +936,7 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.5</v>
+        <v>121.9</v>
       </c>
       <c r="G11" s="2">
         <v>16.9</v>
@@ -945,7 +945,7 @@
         <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>78.0</v>
+        <v>70.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,7 +962,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="3">
-        <v>17.83</v>
+        <v>17.25</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -971,16 +971,16 @@
         <v>12.24</v>
       </c>
       <c r="F12" s="2">
-        <v>128.1</v>
+        <v>122.7</v>
       </c>
       <c r="G12" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="H12" s="3">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="I12" s="4">
-        <v>34.0</v>
+        <v>30.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -997,7 +997,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="3">
-        <v>15.39</v>
+        <v>16.34</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -1006,16 +1006,16 @@
         <v>5.3</v>
       </c>
       <c r="F13" s="2">
-        <v>1250.6</v>
+        <v>1214.3</v>
       </c>
       <c r="G13" s="2">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="H13" s="3">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="I13" s="4">
-        <v>88.0</v>
+        <v>74.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>51</v>
@@ -1032,7 +1032,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="3">
-        <v>24.19</v>
+        <v>24.24</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1041,16 +1041,16 @@
         <v>12.41</v>
       </c>
       <c r="F14" s="2">
-        <v>594.0</v>
+        <v>587.0</v>
       </c>
       <c r="G14" s="2">
-        <v>25.3</v>
+        <v>25.0</v>
       </c>
       <c r="H14" s="3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="I14" s="4">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>55</v>
@@ -1064,25 +1064,25 @@
         <v>57</v>
       </c>
       <c r="C15" s="3">
-        <v>7.58</v>
+        <v>8.47</v>
       </c>
       <c r="D15" s="3">
-        <v>20.83</v>
+        <v>20.5</v>
       </c>
       <c r="E15" s="3">
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>92.8</v>
+        <v>100.8</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="3">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="I15" s="4">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>58</v>
@@ -1099,7 +1099,7 @@
         <v>61</v>
       </c>
       <c r="C16" s="3">
-        <v>14.59</v>
+        <v>15.3</v>
       </c>
       <c r="D16" s="3">
         <v>15.84</v>
@@ -1108,16 +1108,16 @@
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>477.4</v>
+        <v>483.4</v>
       </c>
       <c r="G16" s="2">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="H16" s="3">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="I16" s="4">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>62</v>
@@ -1131,7 +1131,7 @@
         <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>51.3</v>
+        <v>51.0</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1140,16 +1140,16 @@
         <v>30.0</v>
       </c>
       <c r="F17" s="2">
-        <v>382.1</v>
+        <v>384.3</v>
       </c>
       <c r="G17" s="2">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="H17" s="3">
         <v>0.88</v>
       </c>
       <c r="I17" s="4">
-        <v>73.0</v>
+        <v>77.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -1163,7 +1163,7 @@
         <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>39.81</v>
+        <v>38.22</v>
       </c>
       <c r="D18" s="3">
         <v>40.73</v>
@@ -1172,16 +1172,16 @@
         <v>16.73</v>
       </c>
       <c r="F18" s="2">
-        <v>499.0</v>
+        <v>481.1</v>
       </c>
       <c r="G18" s="2">
-        <v>25.2</v>
+        <v>24.3</v>
       </c>
       <c r="H18" s="3">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="I18" s="4">
-        <v>88.0</v>
+        <v>86.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>68</v>
@@ -1195,7 +1195,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>73.0</v>
+        <v>60.65</v>
       </c>
       <c r="D19" s="3">
         <v>75.57</v>
@@ -1204,16 +1204,16 @@
         <v>25.09</v>
       </c>
       <c r="F19" s="2">
-        <v>180.1</v>
+        <v>154.4</v>
       </c>
       <c r="G19" s="2">
-        <v>8.2</v>
+        <v>7.0</v>
       </c>
       <c r="H19" s="3">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="I19" s="4">
-        <v>87.0</v>
+        <v>75.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>71</v>
@@ -1227,7 +1227,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>12.2</v>
+        <v>11.21</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
@@ -1236,16 +1236,16 @@
         <v>3.08</v>
       </c>
       <c r="F20" s="2">
-        <v>722.5</v>
+        <v>674.8</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="3">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="I20" s="4">
-        <v>97.0</v>
+        <v>96.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>22</v>
@@ -1262,7 +1262,7 @@
         <v>76</v>
       </c>
       <c r="C21" s="3">
-        <v>6.77</v>
+        <v>7.29</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1271,16 +1271,16 @@
         <v>3.93</v>
       </c>
       <c r="F21" s="2">
-        <v>444.4</v>
+        <v>476.2</v>
       </c>
       <c r="G21" s="2">
-        <v>22.8</v>
+        <v>24.3</v>
       </c>
       <c r="H21" s="3">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="I21" s="4">
-        <v>80.0</v>
+        <v>89.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>77</v>
@@ -1294,7 +1294,7 @@
         <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>23.82</v>
+        <v>23.95</v>
       </c>
       <c r="D22" s="3">
         <v>29.5</v>
@@ -1303,16 +1303,16 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>334.6</v>
+        <v>329.4</v>
       </c>
       <c r="G22" s="2">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="H22" s="3">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="I22" s="4">
-        <v>75.0</v>
+        <v>68.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>13</v>
@@ -1329,7 +1329,7 @@
         <v>82</v>
       </c>
       <c r="C23" s="3">
-        <v>23.85</v>
+        <v>24.44</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1338,16 +1338,16 @@
         <v>15.0</v>
       </c>
       <c r="F23" s="2">
-        <v>59.0</v>
+        <v>61.1</v>
       </c>
       <c r="G23" s="2">
         <v>0.6</v>
       </c>
       <c r="H23" s="3">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I23" s="4">
-        <v>38.0</v>
+        <v>35.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1364,7 +1364,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="3">
-        <v>37.91</v>
+        <v>38.69</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
@@ -1373,16 +1373,16 @@
         <v>11.93</v>
       </c>
       <c r="F24" s="2">
-        <v>287.9</v>
+        <v>291.6</v>
       </c>
       <c r="G24" s="2">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="H24" s="3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I24" s="4">
-        <v>83.0</v>
+        <v>82.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>86</v>
@@ -1396,7 +1396,7 @@
         <v>88</v>
       </c>
       <c r="C25" s="3">
-        <v>11.97</v>
+        <v>11.81</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1405,16 +1405,16 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>76.5</v>
+        <v>75.3</v>
       </c>
       <c r="G25" s="2">
-        <v>250.0</v>
+        <v>246.0</v>
       </c>
       <c r="H25" s="3">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="I25" s="4">
-        <v>51.0</v>
+        <v>43.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>89</v>
@@ -1428,7 +1428,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>12.0</v>
+        <v>13.49</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1437,16 +1437,16 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>110.7</v>
+        <v>122.1</v>
       </c>
       <c r="G26" s="2">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="H26" s="3">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="I26" s="4">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>22</v>
@@ -1463,7 +1463,7 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>9.27</v>
+        <v>9.54</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
@@ -1472,16 +1472,16 @@
         <v>4.9</v>
       </c>
       <c r="F27" s="2">
-        <v>344.6</v>
+        <v>352.8</v>
       </c>
       <c r="G27" s="2">
-        <v>4.9</v>
+        <v>5.0</v>
       </c>
       <c r="H27" s="3">
-        <v>0.55</v>
+        <v>0.56</v>
       </c>
       <c r="I27" s="4">
-        <v>86.0</v>
+        <v>89.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1498,7 +1498,7 @@
         <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>19.76</v>
+        <v>20.67</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1507,16 +1507,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>119.9</v>
+        <v>124.9</v>
       </c>
       <c r="G28" s="2">
-        <v>20.3</v>
+        <v>21.1</v>
       </c>
       <c r="H28" s="3">
-        <v>0.96</v>
+        <v>1.0</v>
       </c>
       <c r="I28" s="4">
-        <v>33.0</v>
+        <v>41.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1530,7 +1530,7 @@
         <v>99</v>
       </c>
       <c r="C29" s="3">
-        <v>41.55</v>
+        <v>44.77</v>
       </c>
       <c r="D29" s="3">
         <v>56.25</v>
@@ -1539,16 +1539,16 @@
         <v>18.57</v>
       </c>
       <c r="F29" s="2">
-        <v>565.4</v>
+        <v>595.3</v>
       </c>
       <c r="G29" s="2">
-        <v>106.6</v>
+        <v>112.2</v>
       </c>
       <c r="H29" s="3">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="I29" s="4">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>100</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="FLOEbWQiOGUQLaIRdexChyNjhVl36NJIXzEQZa8ws+0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/FLtweLYeDb+CuZ1Rnz5hryWxmOLOeJkhX9NT1w1bNc="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
   <si>
     <t>Company</t>
   </si>
@@ -69,9 +69,6 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>Currently qualifies TTM adjusted earnings positive</t>
-  </si>
-  <si>
     <t>News Archive for AMPY</t>
   </si>
   <si>
@@ -171,7 +168,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Exceeds size limit</t>
+    <t>Exceeds size limit Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for GILT</t>
@@ -627,22 +624,22 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.44</v>
+        <v>4.51</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
       </c>
       <c r="E2" s="3">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="F2" s="2">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
       <c r="G2" s="2">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H2" s="3">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I2" s="4">
         <v>45.0</v>
@@ -662,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.98</v>
+        <v>6.09</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -671,33 +668,33 @@
         <v>2.27</v>
       </c>
       <c r="F3" s="2">
-        <v>246.8</v>
+        <v>251.3</v>
       </c>
       <c r="G3" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H3" s="3">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="I3" s="4">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C4" s="3">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -706,65 +703,65 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="I4" s="4">
+        <v>34.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="I4" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="3">
+        <v>23.81</v>
+      </c>
+      <c r="D5" s="3">
+        <v>23.89</v>
+      </c>
+      <c r="E5" s="3">
+        <v>14.48</v>
+      </c>
+      <c r="F5" s="2">
+        <v>211.1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="I5" s="4">
+        <v>79.0</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" s="3">
-        <v>22.17</v>
-      </c>
-      <c r="D5" s="3">
-        <v>22.97</v>
-      </c>
-      <c r="E5" s="3">
-        <v>13.99</v>
-      </c>
-      <c r="F5" s="2">
-        <v>188.3</v>
-      </c>
-      <c r="G5" s="2">
-        <v>17.2</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1.19</v>
-      </c>
-      <c r="I5" s="4">
-        <v>67.0</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="C6" s="3">
-        <v>28.15</v>
+        <v>28.44</v>
       </c>
       <c r="D6" s="3">
         <v>30.43</v>
@@ -773,30 +770,30 @@
         <v>17.46</v>
       </c>
       <c r="F6" s="2">
-        <v>706.1</v>
+        <v>713.4</v>
       </c>
       <c r="G6" s="2">
-        <v>175.9</v>
+        <v>177.8</v>
       </c>
       <c r="H6" s="3">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="I6" s="4">
-        <v>84.0</v>
+        <v>80.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C7" s="3">
-        <v>5.55</v>
+        <v>5.09</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -805,65 +802,65 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>113.6</v>
+        <v>104.2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="I7" s="4">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C8" s="3">
-        <v>21.69</v>
+        <v>22.24</v>
       </c>
       <c r="D8" s="3">
-        <v>21.95</v>
+        <v>22.36</v>
       </c>
       <c r="E8" s="3">
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>548.6</v>
+        <v>562.5</v>
       </c>
       <c r="G8" s="2">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="I8" s="4">
-        <v>75.0</v>
+        <v>78.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C9" s="3">
-        <v>18.21</v>
+        <v>17.83</v>
       </c>
       <c r="D9" s="3">
         <v>18.61</v>
@@ -872,62 +869,62 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>249.4</v>
+        <v>244.2</v>
       </c>
       <c r="G9" s="2">
-        <v>18.4</v>
+        <v>18.0</v>
       </c>
       <c r="H9" s="3">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="I9" s="4">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C10" s="3">
-        <v>67.28</v>
+        <v>68.2</v>
       </c>
       <c r="D10" s="3">
         <v>72.87</v>
       </c>
       <c r="E10" s="3">
-        <v>26.3</v>
+        <v>28.22</v>
       </c>
       <c r="F10" s="2">
-        <v>474.7</v>
+        <v>481.2</v>
       </c>
       <c r="G10" s="2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H10" s="3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I10" s="4">
-        <v>67.0</v>
+        <v>75.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C11" s="3">
-        <v>18.59</v>
+        <v>18.68</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -936,135 +933,135 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>121.9</v>
+        <v>122.5</v>
       </c>
       <c r="G11" s="2">
-        <v>16.9</v>
+        <v>17.0</v>
       </c>
       <c r="H11" s="3">
         <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="C12" s="3">
-        <v>17.25</v>
+        <v>18.3</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
       </c>
       <c r="E12" s="3">
-        <v>12.24</v>
+        <v>14.0</v>
       </c>
       <c r="F12" s="2">
-        <v>122.7</v>
+        <v>130.2</v>
       </c>
       <c r="G12" s="2">
-        <v>7.8</v>
+        <v>8.2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="I12" s="4">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C13" s="3">
-        <v>16.34</v>
+        <v>17.71</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
       </c>
       <c r="E13" s="3">
-        <v>5.3</v>
+        <v>5.43</v>
       </c>
       <c r="F13" s="2">
-        <v>1214.3</v>
+        <v>1316.1</v>
       </c>
       <c r="G13" s="2">
-        <v>48.1</v>
+        <v>52.1</v>
       </c>
       <c r="H13" s="3">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="I13" s="4">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C14" s="3">
-        <v>24.24</v>
+        <v>25.94</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>12.41</v>
+        <v>12.85</v>
       </c>
       <c r="F14" s="2">
-        <v>587.0</v>
+        <v>628.1</v>
       </c>
       <c r="G14" s="2">
-        <v>25.0</v>
+        <v>26.7</v>
       </c>
       <c r="H14" s="3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="I14" s="4">
-        <v>32.0</v>
+        <v>42.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C15" s="3">
-        <v>8.47</v>
+        <v>8.93</v>
       </c>
       <c r="D15" s="3">
         <v>20.5</v>
@@ -1073,129 +1070,129 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>100.8</v>
+        <v>106.3</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H15" s="3">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="I15" s="4">
         <v>16.0</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C16" s="3">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="D16" s="3">
-        <v>15.84</v>
+        <v>17.07</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>483.4</v>
+        <v>527.6</v>
       </c>
       <c r="G16" s="2">
-        <v>28.9</v>
+        <v>31.5</v>
       </c>
       <c r="H16" s="3">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="I16" s="4">
-        <v>90.0</v>
+        <v>94.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C17" s="3">
-        <v>51.0</v>
+        <v>51.24</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
       </c>
       <c r="E17" s="3">
-        <v>30.0</v>
+        <v>32.16</v>
       </c>
       <c r="F17" s="2">
-        <v>384.3</v>
+        <v>386.1</v>
       </c>
       <c r="G17" s="2">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="H17" s="3">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I17" s="4">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C18" s="3">
-        <v>38.22</v>
+        <v>38.44</v>
       </c>
       <c r="D18" s="3">
         <v>40.73</v>
       </c>
       <c r="E18" s="3">
-        <v>16.73</v>
+        <v>17.49</v>
       </c>
       <c r="F18" s="2">
-        <v>481.1</v>
+        <v>483.9</v>
       </c>
       <c r="G18" s="2">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="H18" s="3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I18" s="4">
         <v>86.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C19" s="3">
-        <v>60.65</v>
+        <v>63.16</v>
       </c>
       <c r="D19" s="3">
         <v>75.57</v>
@@ -1204,62 +1201,62 @@
         <v>25.09</v>
       </c>
       <c r="F19" s="2">
-        <v>154.4</v>
+        <v>161.5</v>
       </c>
       <c r="G19" s="2">
-        <v>7.0</v>
+        <v>7.3</v>
       </c>
       <c r="H19" s="3">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="I19" s="4">
-        <v>75.0</v>
+        <v>88.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="C20" s="3">
-        <v>11.21</v>
+        <v>11.55</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="F20" s="2">
-        <v>674.8</v>
+        <v>695.3</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" s="3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="I20" s="4">
         <v>96.0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="C21" s="3">
         <v>7.29</v>
@@ -1268,7 +1265,7 @@
         <v>9.39</v>
       </c>
       <c r="E21" s="3">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="F21" s="2">
         <v>476.2</v>
@@ -1283,18 +1280,18 @@
         <v>89.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="C22" s="3">
-        <v>23.95</v>
+        <v>26.06</v>
       </c>
       <c r="D22" s="3">
         <v>29.5</v>
@@ -1303,68 +1300,68 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>329.4</v>
+        <v>358.4</v>
       </c>
       <c r="G22" s="2">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="H22" s="3">
-        <v>0.86</v>
+        <v>0.94</v>
       </c>
       <c r="I22" s="4">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C23" s="3">
-        <v>24.44</v>
+        <v>25.0</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
       </c>
       <c r="E23" s="3">
-        <v>15.0</v>
+        <v>15.75</v>
       </c>
       <c r="F23" s="2">
-        <v>61.1</v>
+        <v>62.5</v>
       </c>
       <c r="G23" s="2">
         <v>0.6</v>
       </c>
       <c r="H23" s="3">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="I23" s="4">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C24" s="3">
-        <v>38.69</v>
+        <v>43.11</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
@@ -1373,30 +1370,30 @@
         <v>11.93</v>
       </c>
       <c r="F24" s="2">
-        <v>291.6</v>
+        <v>324.9</v>
       </c>
       <c r="G24" s="2">
-        <v>13.1</v>
+        <v>14.6</v>
       </c>
       <c r="H24" s="3">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="I24" s="4">
-        <v>82.0</v>
+        <v>91.0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="C25" s="3">
-        <v>11.81</v>
+        <v>11.78</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1405,30 +1402,30 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>75.3</v>
+        <v>75.1</v>
       </c>
       <c r="G25" s="2">
-        <v>246.0</v>
+        <v>245.4</v>
       </c>
       <c r="H25" s="3">
         <v>0.47</v>
       </c>
       <c r="I25" s="4">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="C26" s="3">
-        <v>13.49</v>
+        <v>14.92</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1437,48 +1434,45 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>122.1</v>
+        <v>135.0</v>
       </c>
       <c r="G26" s="2">
-        <v>11.4</v>
+        <v>12.6</v>
       </c>
       <c r="H26" s="3">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="I26" s="4">
-        <v>28.0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>22</v>
+        <v>42.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="C27" s="3">
-        <v>9.54</v>
+        <v>9.36</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
       </c>
       <c r="E27" s="3">
+        <v>4.94</v>
+      </c>
+      <c r="F27" s="2">
+        <v>346.1</v>
+      </c>
+      <c r="G27" s="2">
         <v>4.9</v>
       </c>
-      <c r="F27" s="2">
-        <v>352.8</v>
-      </c>
-      <c r="G27" s="2">
-        <v>5.0</v>
-      </c>
       <c r="H27" s="3">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
       <c r="I27" s="4">
         <v>89.0</v>
@@ -1487,18 +1481,18 @@
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="C28" s="3">
-        <v>20.67</v>
+        <v>21.73</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1507,51 +1501,48 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>124.9</v>
+        <v>131.3</v>
       </c>
       <c r="G28" s="2">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="H28" s="3">
-        <v>1.0</v>
+        <v>1.05</v>
       </c>
       <c r="I28" s="4">
-        <v>41.0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="C29" s="3">
-        <v>44.77</v>
+        <v>49.9</v>
       </c>
       <c r="D29" s="3">
         <v>56.25</v>
       </c>
       <c r="E29" s="3">
-        <v>18.57</v>
+        <v>18.9</v>
       </c>
       <c r="F29" s="2">
-        <v>595.3</v>
+        <v>663.5</v>
       </c>
       <c r="G29" s="2">
-        <v>112.2</v>
+        <v>125.1</v>
       </c>
       <c r="H29" s="3">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="I29" s="4">
-        <v>86.0</v>
+        <v>92.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/FLtweLYeDb+CuZ1Rnz5hryWxmOLOeJkhX9NT1w1bNc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="cOVEaQpu3e9z4A2hATcN5pZBFffT70omrSr8IPcbF3k="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="100">
   <si>
     <t>Company</t>
   </si>
@@ -78,39 +78,39 @@
     <t>CTRM</t>
   </si>
   <si>
+    <t>TTM adjusted earnings positive</t>
+  </si>
+  <si>
+    <t>News Archive for CTRM</t>
+  </si>
+  <si>
+    <t>Core Molding Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>News Archive for CMT</t>
+  </si>
+  <si>
+    <t>Covenant Logistics Group, Inc.</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>News Archive for CVLG</t>
+  </si>
+  <si>
+    <t>DMC Global Inc.</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
     <t>nmf</t>
   </si>
   <si>
-    <t>TTM adjusted earnings positive</t>
-  </si>
-  <si>
-    <t>News Archive for CTRM</t>
-  </si>
-  <si>
-    <t>Core Molding Technologies, Inc.</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>News Archive for CMT</t>
-  </si>
-  <si>
-    <t>Covenant Logistics Group, Inc.</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>News Archive for CVLG</t>
-  </si>
-  <si>
-    <t>DMC Global Inc.</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
     <t>Earnings probation 2025q4</t>
   </si>
   <si>
@@ -192,7 +192,7 @@
     <t>Earnings probation 2025Q3</t>
   </si>
   <si>
-    <t>News Archive for LAKE</t>
+    <t>(4/16/26) Lakeland Industries, Inc. (LAKE)</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -624,22 +624,22 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.51</v>
+        <v>4.62</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
       </c>
       <c r="E2" s="3">
-        <v>4.09</v>
+        <v>4.25</v>
       </c>
       <c r="F2" s="2">
-        <v>45.9</v>
+        <v>47.1</v>
       </c>
       <c r="G2" s="2">
-        <v>13.7</v>
+        <v>14.0</v>
       </c>
       <c r="H2" s="3">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="I2" s="4">
         <v>45.0</v>
@@ -659,25 +659,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>6.09</v>
+        <v>5.29</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="F3" s="2">
-        <v>251.3</v>
+        <v>226.5</v>
       </c>
       <c r="G3" s="2">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="I3" s="4">
-        <v>71.0</v>
+        <v>76.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -694,7 +694,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -703,97 +703,97 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>16.8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>17.6</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5.1</v>
       </c>
       <c r="H4" s="3">
         <v>0.03</v>
       </c>
       <c r="I4" s="4">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="C5" s="3">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="D5" s="3">
-        <v>23.89</v>
+        <v>26.54</v>
       </c>
       <c r="E5" s="3">
         <v>14.48</v>
       </c>
       <c r="F5" s="2">
-        <v>211.1</v>
+        <v>233.1</v>
       </c>
       <c r="G5" s="2">
-        <v>18.5</v>
+        <v>20.4</v>
       </c>
       <c r="H5" s="3">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="I5" s="4">
-        <v>79.0</v>
+        <v>87.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C6" s="3">
-        <v>28.44</v>
+        <v>30.49</v>
       </c>
       <c r="D6" s="3">
         <v>30.43</v>
       </c>
       <c r="E6" s="3">
-        <v>17.46</v>
+        <v>17.72</v>
       </c>
       <c r="F6" s="2">
-        <v>713.4</v>
+        <v>732.7</v>
       </c>
       <c r="G6" s="2">
-        <v>177.8</v>
+        <v>182.5</v>
       </c>
       <c r="H6" s="3">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="I6" s="4">
-        <v>80.0</v>
+        <v>84.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="C7" s="3">
-        <v>5.09</v>
+        <v>5.18</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -802,16 +802,16 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>104.2</v>
+        <v>109.5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="I7" s="4">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -828,7 +828,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>22.24</v>
+        <v>21.67</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -837,16 +837,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>562.5</v>
+        <v>539.0</v>
       </c>
       <c r="G8" s="2">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="I8" s="4">
-        <v>78.0</v>
+        <v>72.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
@@ -860,22 +860,22 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>17.83</v>
+        <v>18.75</v>
       </c>
       <c r="D9" s="3">
-        <v>18.61</v>
+        <v>19.11</v>
       </c>
       <c r="E9" s="3">
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>244.2</v>
+        <v>247.6</v>
       </c>
       <c r="G9" s="2">
-        <v>18.0</v>
+        <v>18.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I9" s="4">
         <v>90.0</v>
@@ -892,7 +892,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>68.2</v>
+        <v>72.18</v>
       </c>
       <c r="D10" s="3">
         <v>72.87</v>
@@ -901,16 +901,16 @@
         <v>28.22</v>
       </c>
       <c r="F10" s="2">
-        <v>481.2</v>
+        <v>508.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="I10" s="4">
-        <v>75.0</v>
+        <v>78.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -924,7 +924,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>18.68</v>
+        <v>18.8</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -933,16 +933,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>122.5</v>
+        <v>123.0</v>
       </c>
       <c r="G11" s="2">
-        <v>17.0</v>
+        <v>17.1</v>
       </c>
       <c r="H11" s="3">
         <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>72.0</v>
+        <v>70.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -959,7 +959,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>18.3</v>
+        <v>19.38</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -968,16 +968,16 @@
         <v>14.0</v>
       </c>
       <c r="F12" s="2">
-        <v>130.2</v>
+        <v>134.6</v>
       </c>
       <c r="G12" s="2">
-        <v>8.2</v>
+        <v>8.5</v>
       </c>
       <c r="H12" s="3">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="I12" s="4">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>13</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>17.71</v>
+        <v>19.17</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -1003,16 +1003,16 @@
         <v>5.43</v>
       </c>
       <c r="F13" s="2">
-        <v>1316.1</v>
+        <v>1410.8</v>
       </c>
       <c r="G13" s="2">
-        <v>52.1</v>
+        <v>54.9</v>
       </c>
       <c r="H13" s="3">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="I13" s="4">
-        <v>76.0</v>
+        <v>81.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>50</v>
@@ -1029,25 +1029,25 @@
         <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>25.94</v>
+        <v>26.81</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>12.85</v>
+        <v>12.87</v>
       </c>
       <c r="F14" s="2">
-        <v>628.1</v>
+        <v>640.2</v>
       </c>
       <c r="G14" s="2">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="H14" s="3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="I14" s="4">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>54</v>
@@ -1061,7 +1061,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>8.93</v>
+        <v>11.2</v>
       </c>
       <c r="D15" s="3">
         <v>20.5</v>
@@ -1070,16 +1070,16 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>106.3</v>
+        <v>106.1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" s="3">
         <v>0.65</v>
       </c>
       <c r="I15" s="4">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>57</v>
@@ -1096,25 +1096,25 @@
         <v>60</v>
       </c>
       <c r="C16" s="3">
-        <v>16.7</v>
+        <v>17.85</v>
       </c>
       <c r="D16" s="3">
-        <v>17.07</v>
+        <v>17.58</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>527.6</v>
+        <v>546.9</v>
       </c>
       <c r="G16" s="2">
-        <v>31.5</v>
+        <v>32.4</v>
       </c>
       <c r="H16" s="3">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="I16" s="4">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>61</v>
@@ -1128,7 +1128,7 @@
         <v>63</v>
       </c>
       <c r="C17" s="3">
-        <v>51.24</v>
+        <v>48.66</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1137,16 +1137,16 @@
         <v>32.16</v>
       </c>
       <c r="F17" s="2">
-        <v>386.1</v>
+        <v>359.6</v>
       </c>
       <c r="G17" s="2">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="I17" s="4">
-        <v>78.0</v>
+        <v>65.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>64</v>
@@ -1160,16 +1160,16 @@
         <v>66</v>
       </c>
       <c r="C18" s="3">
-        <v>38.44</v>
+        <v>38.1</v>
       </c>
       <c r="D18" s="3">
         <v>40.73</v>
       </c>
       <c r="E18" s="3">
-        <v>17.49</v>
+        <v>17.63</v>
       </c>
       <c r="F18" s="2">
-        <v>483.9</v>
+        <v>484.9</v>
       </c>
       <c r="G18" s="2">
         <v>24.5</v>
@@ -1178,7 +1178,7 @@
         <v>1.76</v>
       </c>
       <c r="I18" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>67</v>
@@ -1192,25 +1192,25 @@
         <v>69</v>
       </c>
       <c r="C19" s="3">
-        <v>63.16</v>
+        <v>75.33</v>
       </c>
       <c r="D19" s="3">
         <v>75.57</v>
       </c>
       <c r="E19" s="3">
-        <v>25.09</v>
+        <v>27.75</v>
       </c>
       <c r="F19" s="2">
-        <v>161.5</v>
+        <v>188.2</v>
       </c>
       <c r="G19" s="2">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="H19" s="3">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="I19" s="4">
-        <v>88.0</v>
+        <v>95.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>70</v>
@@ -1224,28 +1224,28 @@
         <v>72</v>
       </c>
       <c r="C20" s="3">
-        <v>11.55</v>
+        <v>10.22</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="F20" s="2">
-        <v>695.3</v>
+        <v>654.4</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.13</v>
+      </c>
+      <c r="I20" s="4">
+        <v>95.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="I20" s="4">
-        <v>96.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>73</v>
@@ -1259,7 +1259,7 @@
         <v>75</v>
       </c>
       <c r="C21" s="3">
-        <v>7.29</v>
+        <v>7.9</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1268,16 +1268,16 @@
         <v>3.94</v>
       </c>
       <c r="F21" s="2">
-        <v>476.2</v>
+        <v>506.9</v>
       </c>
       <c r="G21" s="2">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="H21" s="3">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="I21" s="4">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>76</v>
@@ -1291,7 +1291,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="3">
-        <v>26.06</v>
+        <v>27.3</v>
       </c>
       <c r="D22" s="3">
         <v>29.5</v>
@@ -1300,16 +1300,16 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>358.4</v>
+        <v>354.0</v>
       </c>
       <c r="G22" s="2">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="H22" s="3">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="I22" s="4">
-        <v>79.0</v>
+        <v>77.0</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>13</v>
@@ -1326,25 +1326,25 @@
         <v>81</v>
       </c>
       <c r="C23" s="3">
-        <v>25.0</v>
+        <v>27.01</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
       </c>
       <c r="E23" s="3">
-        <v>15.75</v>
+        <v>16.59</v>
       </c>
       <c r="F23" s="2">
-        <v>62.5</v>
+        <v>65.0</v>
       </c>
       <c r="G23" s="2">
         <v>0.6</v>
       </c>
       <c r="H23" s="3">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="I23" s="4">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1361,25 +1361,25 @@
         <v>84</v>
       </c>
       <c r="C24" s="3">
-        <v>43.11</v>
+        <v>43.89</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>11.93</v>
+        <v>12.31</v>
       </c>
       <c r="F24" s="2">
-        <v>324.9</v>
+        <v>318.6</v>
       </c>
       <c r="G24" s="2">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="H24" s="3">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="I24" s="4">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>85</v>
@@ -1393,7 +1393,7 @@
         <v>87</v>
       </c>
       <c r="C25" s="3">
-        <v>11.78</v>
+        <v>11.95</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1402,16 +1402,16 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>75.1</v>
+        <v>76.0</v>
       </c>
       <c r="G25" s="2">
-        <v>245.4</v>
+        <v>248.5</v>
       </c>
       <c r="H25" s="3">
         <v>0.47</v>
       </c>
       <c r="I25" s="4">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>88</v>
@@ -1425,7 +1425,7 @@
         <v>90</v>
       </c>
       <c r="C26" s="3">
-        <v>14.92</v>
+        <v>14.39</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1434,16 +1434,16 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>135.0</v>
+        <v>123.0</v>
       </c>
       <c r="G26" s="2">
-        <v>12.6</v>
+        <v>11.4</v>
       </c>
       <c r="H26" s="3">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="I26" s="4">
-        <v>42.0</v>
+        <v>32.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>91</v>
@@ -1457,7 +1457,7 @@
         <v>93</v>
       </c>
       <c r="C27" s="3">
-        <v>9.36</v>
+        <v>9.34</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
@@ -1466,7 +1466,7 @@
         <v>4.94</v>
       </c>
       <c r="F27" s="2">
-        <v>346.1</v>
+        <v>340.9</v>
       </c>
       <c r="G27" s="2">
         <v>4.9</v>
@@ -1475,7 +1475,7 @@
         <v>0.55</v>
       </c>
       <c r="I27" s="4">
-        <v>89.0</v>
+        <v>86.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1492,7 +1492,7 @@
         <v>96</v>
       </c>
       <c r="C28" s="3">
-        <v>21.73</v>
+        <v>22.43</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1501,13 +1501,13 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>131.3</v>
+        <v>132.7</v>
       </c>
       <c r="G28" s="2">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="H28" s="3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I28" s="4">
         <v>49.0</v>
@@ -1521,25 +1521,25 @@
         <v>98</v>
       </c>
       <c r="C29" s="3">
-        <v>49.9</v>
+        <v>53.22</v>
       </c>
       <c r="D29" s="3">
         <v>56.25</v>
       </c>
       <c r="E29" s="3">
-        <v>18.9</v>
+        <v>19.28</v>
       </c>
       <c r="F29" s="2">
-        <v>663.5</v>
+        <v>683.2</v>
       </c>
       <c r="G29" s="2">
-        <v>125.1</v>
+        <v>128.8</v>
       </c>
       <c r="H29" s="3">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="I29" s="4">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>99</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="cOVEaQpu3e9z4A2hATcN5pZBFffT70omrSr8IPcbF3k="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="KGDmQxXIW+PcKGbAZTcrk/pIEenyBBf3kY9/OhaqUFw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
   <si>
     <t>Company</t>
   </si>
@@ -99,7 +99,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>News Archive for CVLG</t>
+    <t>(4/23/26) Covenant Logistics Group, Inc. (CVLG)</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -123,7 +123,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>News Archive for EBF</t>
+    <t>(4/20/26) Ennis, Inc. (EBF)</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -192,13 +192,16 @@
     <t>Earnings probation 2025Q3</t>
   </si>
   <si>
-    <t>(4/16/26) Lakeland Industries, Inc. (LAKE)</t>
+    <t>(4/20/26) Lakeland Industries, Inc. (LAKE)</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
   </si>
   <si>
     <t>MG</t>
+  </si>
+  <si>
+    <t>Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for MG</t>
@@ -624,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
@@ -633,16 +636,16 @@
         <v>4.25</v>
       </c>
       <c r="F2" s="2">
-        <v>47.1</v>
+        <v>46.3</v>
       </c>
       <c r="G2" s="2">
-        <v>14.0</v>
+        <v>13.8</v>
       </c>
       <c r="H2" s="3">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="I2" s="4">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -659,25 +662,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.29</v>
+        <v>5.84</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="F3" s="2">
-        <v>226.5</v>
+        <v>241.0</v>
       </c>
       <c r="G3" s="2">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="H3" s="3">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="I3" s="4">
-        <v>76.0</v>
+        <v>81.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -694,7 +697,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -703,16 +706,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="G4" s="2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H4" s="3">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>35.0</v>
+        <v>42.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
@@ -729,22 +732,22 @@
         <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>27.27</v>
+        <v>28.1</v>
       </c>
       <c r="D5" s="3">
-        <v>26.54</v>
+        <v>28.69</v>
       </c>
       <c r="E5" s="3">
         <v>14.48</v>
       </c>
       <c r="F5" s="2">
-        <v>233.1</v>
+        <v>249.1</v>
       </c>
       <c r="G5" s="2">
-        <v>20.4</v>
+        <v>21.8</v>
       </c>
       <c r="H5" s="3">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="4">
         <v>87.0</v>
@@ -761,25 +764,25 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>30.49</v>
+        <v>34.07</v>
       </c>
       <c r="D6" s="3">
-        <v>30.43</v>
+        <v>34.16</v>
       </c>
       <c r="E6" s="3">
-        <v>17.72</v>
+        <v>18.0</v>
       </c>
       <c r="F6" s="2">
-        <v>732.7</v>
+        <v>854.9</v>
       </c>
       <c r="G6" s="2">
-        <v>182.5</v>
+        <v>212.9</v>
       </c>
       <c r="H6" s="3">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="I6" s="4">
-        <v>84.0</v>
+        <v>90.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -793,7 +796,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>5.18</v>
+        <v>6.41</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -802,16 +805,16 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>109.5</v>
+        <v>131.2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="3">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="I7" s="4">
-        <v>21.0</v>
+        <v>32.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -828,7 +831,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>21.67</v>
+        <v>20.33</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -837,16 +840,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>539.0</v>
+        <v>514.2</v>
       </c>
       <c r="G8" s="2">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="H8" s="3">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="I8" s="4">
-        <v>72.0</v>
+        <v>70.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
@@ -860,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>18.75</v>
+        <v>18.09</v>
       </c>
       <c r="D9" s="3">
         <v>19.11</v>
@@ -869,7 +872,7 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>247.6</v>
+        <v>247.8</v>
       </c>
       <c r="G9" s="2">
         <v>18.3</v>
@@ -878,7 +881,7 @@
         <v>1.43</v>
       </c>
       <c r="I9" s="4">
-        <v>90.0</v>
+        <v>87.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -892,25 +895,25 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>72.18</v>
+        <v>68.03</v>
       </c>
       <c r="D10" s="3">
-        <v>72.87</v>
+        <v>74.75</v>
       </c>
       <c r="E10" s="3">
-        <v>28.22</v>
+        <v>30.38</v>
       </c>
       <c r="F10" s="2">
-        <v>508.0</v>
+        <v>480.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H10" s="3">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="I10" s="4">
-        <v>78.0</v>
+        <v>74.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -924,7 +927,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>18.8</v>
+        <v>18.83</v>
       </c>
       <c r="D11" s="3">
         <v>18.86</v>
@@ -933,16 +936,16 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="2">
-        <v>123.0</v>
+        <v>123.4</v>
       </c>
       <c r="G11" s="2">
         <v>17.1</v>
       </c>
       <c r="H11" s="3">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -959,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>19.38</v>
+        <v>20.52</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -968,19 +971,16 @@
         <v>14.0</v>
       </c>
       <c r="F12" s="2">
-        <v>134.6</v>
+        <v>145.9</v>
       </c>
       <c r="G12" s="2">
-        <v>8.5</v>
+        <v>9.2</v>
       </c>
       <c r="H12" s="3">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="I12" s="4">
-        <v>41.0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>52.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>19.17</v>
+        <v>17.42</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -1003,16 +1003,16 @@
         <v>5.43</v>
       </c>
       <c r="F13" s="2">
-        <v>1410.8</v>
+        <v>1317.7</v>
       </c>
       <c r="G13" s="2">
-        <v>54.9</v>
+        <v>51.2</v>
       </c>
       <c r="H13" s="3">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="I13" s="4">
-        <v>81.0</v>
+        <v>79.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>50</v>
@@ -1029,25 +1029,25 @@
         <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>26.81</v>
+        <v>27.74</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>12.87</v>
+        <v>14.07</v>
       </c>
       <c r="F14" s="2">
-        <v>640.2</v>
+        <v>671.7</v>
       </c>
       <c r="G14" s="2">
-        <v>27.3</v>
+        <v>28.6</v>
       </c>
       <c r="H14" s="3">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="I14" s="4">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>54</v>
@@ -1061,7 +1061,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>11.2</v>
+        <v>10.05</v>
       </c>
       <c r="D15" s="3">
         <v>20.5</v>
@@ -1070,16 +1070,16 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>106.1</v>
+        <v>107.8</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="3">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="I15" s="4">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>57</v>
@@ -1096,39 +1096,42 @@
         <v>60</v>
       </c>
       <c r="C16" s="3">
-        <v>17.85</v>
+        <v>18.91</v>
       </c>
       <c r="D16" s="3">
-        <v>17.58</v>
+        <v>19.35</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>546.9</v>
+        <v>601.7</v>
       </c>
       <c r="G16" s="2">
-        <v>32.4</v>
+        <v>35.7</v>
       </c>
       <c r="H16" s="3">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="I16" s="4">
         <v>95.0</v>
       </c>
+      <c r="J16" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="K16" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>48.66</v>
+        <v>50.36</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1137,30 +1140,30 @@
         <v>32.16</v>
       </c>
       <c r="F17" s="2">
-        <v>359.6</v>
+        <v>379.4</v>
       </c>
       <c r="G17" s="2">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="I17" s="4">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>38.1</v>
+        <v>39.67</v>
       </c>
       <c r="D18" s="3">
         <v>40.73</v>
@@ -1169,97 +1172,97 @@
         <v>17.63</v>
       </c>
       <c r="F18" s="2">
-        <v>484.9</v>
+        <v>499.4</v>
       </c>
       <c r="G18" s="2">
-        <v>24.5</v>
+        <v>25.3</v>
       </c>
       <c r="H18" s="3">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="I18" s="4">
-        <v>88.0</v>
+        <v>86.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>75.33</v>
+        <v>78.77</v>
       </c>
       <c r="D19" s="3">
-        <v>75.57</v>
+        <v>87.36</v>
       </c>
       <c r="E19" s="3">
-        <v>27.75</v>
+        <v>28.64</v>
       </c>
       <c r="F19" s="2">
-        <v>188.2</v>
+        <v>201.4</v>
       </c>
       <c r="G19" s="2">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="H19" s="3">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="I19" s="4">
         <v>95.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>10.22</v>
+        <v>11.08</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="F20" s="2">
-        <v>654.4</v>
+        <v>667.0</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I20" s="4">
-        <v>95.0</v>
+        <v>94.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" s="3">
-        <v>7.9</v>
+        <v>7.17</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1268,30 +1271,30 @@
         <v>3.94</v>
       </c>
       <c r="F21" s="2">
-        <v>506.9</v>
+        <v>468.3</v>
       </c>
       <c r="G21" s="2">
-        <v>25.9</v>
+        <v>23.9</v>
       </c>
       <c r="H21" s="3">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="I21" s="4">
-        <v>92.0</v>
+        <v>88.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>27.3</v>
+        <v>28.48</v>
       </c>
       <c r="D22" s="3">
         <v>29.5</v>
@@ -1300,100 +1303,97 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>354.0</v>
+        <v>391.6</v>
       </c>
       <c r="G22" s="2">
-        <v>14.5</v>
+        <v>16.1</v>
       </c>
       <c r="H22" s="3">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="I22" s="4">
-        <v>77.0</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>13</v>
+        <v>84.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="3">
-        <v>27.01</v>
+        <v>27.5</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
       </c>
       <c r="E23" s="3">
-        <v>16.59</v>
+        <v>17.5</v>
       </c>
       <c r="F23" s="2">
-        <v>65.0</v>
+        <v>68.7</v>
       </c>
       <c r="G23" s="2">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="I23" s="4">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="3">
-        <v>43.89</v>
+        <v>42.76</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>12.31</v>
+        <v>13.05</v>
       </c>
       <c r="F24" s="2">
-        <v>318.6</v>
+        <v>322.3</v>
       </c>
       <c r="G24" s="2">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H24" s="3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I24" s="4">
-        <v>90.0</v>
+        <v>88.0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" s="3">
-        <v>11.95</v>
+        <v>11.77</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1402,30 +1402,30 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>76.0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>248.5</v>
+        <v>74.9</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="H25" s="3">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="I25" s="4">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>14.39</v>
+        <v>14.13</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1434,39 +1434,39 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>123.0</v>
+        <v>127.9</v>
       </c>
       <c r="G26" s="2">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="H26" s="3">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="I26" s="4">
         <v>32.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>9.34</v>
+        <v>9.37</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
       </c>
       <c r="E27" s="3">
-        <v>4.94</v>
+        <v>5.22</v>
       </c>
       <c r="F27" s="2">
-        <v>340.9</v>
+        <v>346.5</v>
       </c>
       <c r="G27" s="2">
         <v>4.9</v>
@@ -1481,18 +1481,18 @@
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>22.43</v>
+        <v>22.03</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1501,7 +1501,7 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>132.7</v>
+        <v>133.0</v>
       </c>
       <c r="G28" s="2">
         <v>22.5</v>
@@ -1510,39 +1510,39 @@
         <v>1.07</v>
       </c>
       <c r="I28" s="4">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" s="3">
-        <v>53.22</v>
+        <v>60.62</v>
       </c>
       <c r="D29" s="3">
-        <v>56.25</v>
+        <v>61.46</v>
       </c>
       <c r="E29" s="3">
-        <v>19.28</v>
+        <v>21.29</v>
       </c>
       <c r="F29" s="2">
-        <v>683.2</v>
+        <v>806.1</v>
       </c>
       <c r="G29" s="2">
-        <v>128.8</v>
+        <v>151.9</v>
       </c>
       <c r="H29" s="3">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="I29" s="4">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="KGDmQxXIW+PcKGbAZTcrk/pIEenyBBf3kY9/OhaqUFw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zbRaNs827EUg825F1vh205JS9/tT4fA77JY+qRLrasY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="98">
   <si>
     <t>Company</t>
   </si>
@@ -99,7 +99,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>(4/23/26) Covenant Logistics Group, Inc. (CVLG)</t>
+    <t>News Archive for CVLG</t>
   </si>
   <si>
     <t>DMC Global Inc.</t>
@@ -114,7 +114,7 @@
     <t>Earnings probation 2025q4</t>
   </si>
   <si>
-    <t>News Archive for BOOM</t>
+    <t>(4/30/26) DMC Global Inc. (BOOM)</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -123,7 +123,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>(4/20/26) Ennis, Inc. (EBF)</t>
+    <t>News Archive for EBF</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -132,7 +132,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>News Archive for ESCA</t>
+    <t>(4/30/26) Escalade, Incorporated (ESCA)</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -192,7 +192,7 @@
     <t>Earnings probation 2025Q3</t>
   </si>
   <si>
-    <t>(4/20/26) Lakeland Industries, Inc. (LAKE)</t>
+    <t>News Archive for LAKE</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -231,7 +231,7 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>News Archive for NCSM</t>
+    <t>(4/29/26) NCS Multistage Holdings, Inc. (NCSM)</t>
   </si>
   <si>
     <t>Oil States International, Inc.</t>
@@ -276,7 +276,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>News Archive for RCKY</t>
+    <t>(4/28/26) Rocky Brands, Inc. (RCKY)</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -294,16 +294,7 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>News Archive for SDHC</t>
-  </si>
-  <si>
-    <t>StealthGas Inc.</t>
-  </si>
-  <si>
-    <t>GASS</t>
-  </si>
-  <si>
-    <t>News Archive for GASS</t>
+    <t>(4/29/26) Smith Douglas Homes Corp. (SDHC)</t>
   </si>
   <si>
     <t>The Eastern Company</t>
@@ -627,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="D2" s="3">
         <v>5.64</v>
@@ -636,16 +627,16 @@
         <v>4.25</v>
       </c>
       <c r="F2" s="2">
-        <v>46.3</v>
+        <v>46.9</v>
       </c>
       <c r="G2" s="2">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="H2" s="3">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="I2" s="4">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -662,25 +653,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.84</v>
+        <v>6.23</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="F3" s="2">
-        <v>241.0</v>
+        <v>264.2</v>
       </c>
       <c r="G3" s="2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H3" s="3">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="I3" s="4">
-        <v>81.0</v>
+        <v>88.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -697,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -706,16 +697,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>18.6</v>
+        <v>19.9</v>
       </c>
       <c r="G4" s="2">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>42.0</v>
+        <v>49.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
@@ -732,7 +723,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>28.1</v>
+        <v>26.61</v>
       </c>
       <c r="D5" s="3">
         <v>28.69</v>
@@ -741,16 +732,16 @@
         <v>14.48</v>
       </c>
       <c r="F5" s="2">
-        <v>249.1</v>
+        <v>238.9</v>
       </c>
       <c r="G5" s="2">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="H5" s="3">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="I5" s="4">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -764,25 +755,25 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>34.07</v>
+        <v>33.72</v>
       </c>
       <c r="D6" s="3">
-        <v>34.16</v>
+        <v>35.91</v>
       </c>
       <c r="E6" s="3">
         <v>18.0</v>
       </c>
       <c r="F6" s="2">
-        <v>854.9</v>
+        <v>874.7</v>
       </c>
       <c r="G6" s="2">
-        <v>212.9</v>
+        <v>217.9</v>
       </c>
       <c r="H6" s="3">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="I6" s="4">
-        <v>90.0</v>
+        <v>94.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -796,7 +787,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>6.41</v>
+        <v>8.39</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -805,16 +796,16 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>131.2</v>
+        <v>126.5</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="3">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="I7" s="4">
-        <v>32.0</v>
+        <v>24.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -831,7 +822,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>20.33</v>
+        <v>21.09</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -840,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>514.2</v>
+        <v>528.1</v>
       </c>
       <c r="G8" s="2">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="H8" s="3">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="I8" s="4">
-        <v>70.0</v>
+        <v>76.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
@@ -863,7 +854,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>18.09</v>
+        <v>18.19</v>
       </c>
       <c r="D9" s="3">
         <v>19.11</v>
@@ -872,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>247.8</v>
+        <v>256.1</v>
       </c>
       <c r="G9" s="2">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="H9" s="3">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="I9" s="4">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -895,22 +886,22 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>68.03</v>
+        <v>69.96</v>
       </c>
       <c r="D10" s="3">
         <v>74.75</v>
       </c>
       <c r="E10" s="3">
-        <v>30.38</v>
+        <v>30.72</v>
       </c>
       <c r="F10" s="2">
-        <v>480.0</v>
+        <v>494.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H10" s="3">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="I10" s="4">
         <v>74.0</v>
@@ -927,25 +918,25 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>18.83</v>
+        <v>18.94</v>
       </c>
       <c r="D11" s="3">
-        <v>18.86</v>
+        <v>18.95</v>
       </c>
       <c r="E11" s="3">
-        <v>12.0</v>
+        <v>12.14</v>
       </c>
       <c r="F11" s="2">
-        <v>123.4</v>
+        <v>124.1</v>
       </c>
       <c r="G11" s="2">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="H11" s="3">
         <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -962,7 +953,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>20.52</v>
+        <v>20.62</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -971,16 +962,16 @@
         <v>14.0</v>
       </c>
       <c r="F12" s="2">
-        <v>145.9</v>
+        <v>146.4</v>
       </c>
       <c r="G12" s="2">
-        <v>9.2</v>
+        <v>9.3</v>
       </c>
       <c r="H12" s="3">
         <v>1.03</v>
       </c>
       <c r="I12" s="4">
-        <v>52.0</v>
+        <v>47.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -994,7 +985,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>17.42</v>
+        <v>18.47</v>
       </c>
       <c r="D13" s="3">
         <v>20.38</v>
@@ -1003,16 +994,16 @@
         <v>5.43</v>
       </c>
       <c r="F13" s="2">
-        <v>1317.7</v>
+        <v>1396.4</v>
       </c>
       <c r="G13" s="2">
-        <v>51.2</v>
+        <v>54.3</v>
       </c>
       <c r="H13" s="3">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="I13" s="4">
-        <v>79.0</v>
+        <v>77.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>50</v>
@@ -1029,25 +1020,25 @@
         <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>27.74</v>
+        <v>27.2</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>14.07</v>
+        <v>14.3</v>
       </c>
       <c r="F14" s="2">
-        <v>671.7</v>
+        <v>654.0</v>
       </c>
       <c r="G14" s="2">
-        <v>28.6</v>
+        <v>27.8</v>
       </c>
       <c r="H14" s="3">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="I14" s="4">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>54</v>
@@ -1061,7 +1052,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>10.05</v>
+        <v>9.51</v>
       </c>
       <c r="D15" s="3">
         <v>20.5</v>
@@ -1070,13 +1061,13 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>107.8</v>
+        <v>109.1</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="3">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I15" s="4">
         <v>17.0</v>
@@ -1096,22 +1087,22 @@
         <v>60</v>
       </c>
       <c r="C16" s="3">
-        <v>18.91</v>
+        <v>19.28</v>
       </c>
       <c r="D16" s="3">
-        <v>19.35</v>
+        <v>19.36</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>601.7</v>
+        <v>600.7</v>
       </c>
       <c r="G16" s="2">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="H16" s="3">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="I16" s="4">
         <v>95.0</v>
@@ -1131,7 +1122,7 @@
         <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>50.36</v>
+        <v>48.05</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1140,13 +1131,13 @@
         <v>32.16</v>
       </c>
       <c r="F17" s="2">
-        <v>379.4</v>
+        <v>363.0</v>
       </c>
       <c r="G17" s="2">
-        <v>21.4</v>
+        <v>20.5</v>
       </c>
       <c r="H17" s="3">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="I17" s="4">
         <v>66.0</v>
@@ -1163,25 +1154,25 @@
         <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>39.67</v>
+        <v>41.29</v>
       </c>
       <c r="D18" s="3">
-        <v>40.73</v>
+        <v>41.51</v>
       </c>
       <c r="E18" s="3">
-        <v>17.63</v>
+        <v>17.89</v>
       </c>
       <c r="F18" s="2">
-        <v>499.4</v>
+        <v>512.6</v>
       </c>
       <c r="G18" s="2">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="H18" s="3">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="I18" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>68</v>
@@ -1195,7 +1186,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>78.77</v>
+        <v>49.76</v>
       </c>
       <c r="D19" s="3">
         <v>87.36</v>
@@ -1204,16 +1195,16 @@
         <v>28.64</v>
       </c>
       <c r="F19" s="2">
-        <v>201.4</v>
+        <v>139.8</v>
       </c>
       <c r="G19" s="2">
-        <v>9.1</v>
+        <v>6.3</v>
       </c>
       <c r="H19" s="3">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="I19" s="4">
-        <v>95.0</v>
+        <v>82.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>71</v>
@@ -1227,22 +1218,22 @@
         <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>11.08</v>
+        <v>11.23</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>3.44</v>
+        <v>3.61</v>
       </c>
       <c r="F20" s="2">
-        <v>667.0</v>
+        <v>691.1</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="3">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="I20" s="4">
         <v>94.0</v>
@@ -1262,25 +1253,25 @@
         <v>76</v>
       </c>
       <c r="C21" s="3">
-        <v>7.17</v>
+        <v>7.74</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
       </c>
       <c r="E21" s="3">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="F21" s="2">
-        <v>468.3</v>
+        <v>500.3</v>
       </c>
       <c r="G21" s="2">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="H21" s="3">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="I21" s="4">
-        <v>88.0</v>
+        <v>91.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>77</v>
@@ -1294,25 +1285,25 @@
         <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>28.48</v>
+        <v>28.55</v>
       </c>
       <c r="D22" s="3">
-        <v>29.5</v>
+        <v>30.45</v>
       </c>
       <c r="E22" s="3">
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>391.6</v>
+        <v>398.1</v>
       </c>
       <c r="G22" s="2">
-        <v>16.1</v>
+        <v>16.4</v>
       </c>
       <c r="H22" s="3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="I22" s="4">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>80</v>
@@ -1326,7 +1317,7 @@
         <v>82</v>
       </c>
       <c r="C23" s="3">
-        <v>27.5</v>
+        <v>27.0</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1344,7 +1335,7 @@
         <v>0.36</v>
       </c>
       <c r="I23" s="4">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1361,25 +1352,25 @@
         <v>85</v>
       </c>
       <c r="C24" s="3">
-        <v>42.76</v>
+        <v>37.4</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>13.05</v>
+        <v>17.14</v>
       </c>
       <c r="F24" s="2">
-        <v>322.3</v>
+        <v>276.5</v>
       </c>
       <c r="G24" s="2">
-        <v>14.4</v>
+        <v>12.4</v>
       </c>
       <c r="H24" s="3">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="I24" s="4">
-        <v>88.0</v>
+        <v>74.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>86</v>
@@ -1393,7 +1384,7 @@
         <v>88</v>
       </c>
       <c r="C25" s="3">
-        <v>11.77</v>
+        <v>11.01</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1402,13 +1393,13 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>74.9</v>
+        <v>71.8</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H25" s="3">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="I25" s="4">
         <v>42.0</v>
@@ -1425,7 +1416,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>14.13</v>
+        <v>13.95</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1434,7 +1425,7 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>127.9</v>
+        <v>118.5</v>
       </c>
       <c r="G26" s="2">
         <v>11.9</v>
@@ -1443,7 +1434,7 @@
         <v>1.47</v>
       </c>
       <c r="I26" s="4">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>92</v>
@@ -1457,94 +1448,60 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>9.37</v>
+        <v>22.0</v>
       </c>
       <c r="D27" s="3">
-        <v>10.52</v>
+        <v>26.77</v>
       </c>
       <c r="E27" s="3">
-        <v>5.22</v>
+        <v>17.61</v>
       </c>
       <c r="F27" s="2">
-        <v>346.5</v>
+        <v>132.0</v>
       </c>
       <c r="G27" s="2">
-        <v>4.9</v>
+        <v>22.3</v>
       </c>
       <c r="H27" s="3">
-        <v>0.55</v>
+        <v>1.06</v>
       </c>
       <c r="I27" s="4">
-        <v>86.0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>95</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="3">
+        <v>60.22</v>
+      </c>
+      <c r="D28" s="3">
+        <v>61.94</v>
+      </c>
+      <c r="E28" s="3">
+        <v>22.66</v>
+      </c>
+      <c r="F28" s="2">
+        <v>803.4</v>
+      </c>
+      <c r="G28" s="2">
+        <v>151.4</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="I28" s="4">
+        <v>92.0</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="3">
-        <v>22.03</v>
-      </c>
-      <c r="D28" s="3">
-        <v>26.77</v>
-      </c>
-      <c r="E28" s="3">
-        <v>17.61</v>
-      </c>
-      <c r="F28" s="2">
-        <v>133.0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>22.5</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1.07</v>
-      </c>
-      <c r="I28" s="4">
-        <v>52.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="3">
-        <v>60.62</v>
-      </c>
-      <c r="D29" s="3">
-        <v>61.46</v>
-      </c>
-      <c r="E29" s="3">
-        <v>21.29</v>
-      </c>
-      <c r="F29" s="2">
-        <v>806.1</v>
-      </c>
-      <c r="G29" s="2">
-        <v>151.9</v>
-      </c>
-      <c r="H29" s="3">
-        <v>2.39</v>
-      </c>
-      <c r="I29" s="4">
-        <v>93.0</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
+    </row>
+    <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zbRaNs827EUg825F1vh205JS9/tT4fA77JY+qRLrasY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="VdKWTpNbNveXMcAFnaq0s0jSqgfvATf/9bysQhIMhp0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
   <si>
     <t>Company</t>
   </si>
@@ -57,18 +57,18 @@
     <t>APT</t>
   </si>
   <si>
+    <t>(5/7/26) Alpha Pro Tech, Ltd. (APT)</t>
+  </si>
+  <si>
+    <t>Amplify Energy Corp.</t>
+  </si>
+  <si>
+    <t>AMPY</t>
+  </si>
+  <si>
     <t>Currently qualifies</t>
   </si>
   <si>
-    <t>News Archive for APT</t>
-  </si>
-  <si>
-    <t>Amplify Energy Corp.</t>
-  </si>
-  <si>
-    <t>AMPY</t>
-  </si>
-  <si>
     <t>News Archive for AMPY</t>
   </si>
   <si>
@@ -114,7 +114,7 @@
     <t>Earnings probation 2025q4</t>
   </si>
   <si>
-    <t>(4/30/26) DMC Global Inc. (BOOM)</t>
+    <t>News Archive for BOOM</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -132,7 +132,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(4/30/26) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -180,7 +180,7 @@
     <t>KE</t>
   </si>
   <si>
-    <t>News Archive for KE</t>
+    <t>(5/5/26) Kimball Electronics, Inc. (KE)</t>
   </si>
   <si>
     <t>Lakeland Industries, Inc.</t>
@@ -204,7 +204,7 @@
     <t>Approaching value limit</t>
   </si>
   <si>
-    <t>News Archive for MG</t>
+    <t>(5/5/26) Mistras Group, Inc. (MG)</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -213,7 +213,7 @@
     <t>NC</t>
   </si>
   <si>
-    <t>News Archive for NC</t>
+    <t>(5/5/26) NACCO Industries, Inc. (NC)</t>
   </si>
   <si>
     <t>Natural Gas Services Group, Inc.</t>
@@ -231,7 +231,7 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>(4/29/26) NCS Multistage Holdings, Inc. (NCSM)</t>
+    <t>News Archive for NCSM</t>
   </si>
   <si>
     <t>Oil States International, Inc.</t>
@@ -240,7 +240,7 @@
     <t>OIS</t>
   </si>
   <si>
-    <t>News Archive for OIS</t>
+    <t>(5/5/26) Oil States International, Inc. (OIS)</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions Ltd.</t>
@@ -258,7 +258,7 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>News Archive for PKOH</t>
+    <t>(5/6/26) Park-Ohio Holdings Corp. (PKOH)</t>
   </si>
   <si>
     <t>Regis Corporation</t>
@@ -276,7 +276,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>(4/28/26) Rocky Brands, Inc. (RCKY)</t>
+    <t>News Archive for RCKY</t>
   </si>
   <si>
     <t>Saga Communications, Inc.</t>
@@ -285,7 +285,7 @@
     <t>SGA</t>
   </si>
   <si>
-    <t>News Archive for SGA</t>
+    <t>(5/7/26) Saga Communications, Inc. (SGA)</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -294,7 +294,16 @@
     <t>SDHC</t>
   </si>
   <si>
-    <t>(4/29/26) Smith Douglas Homes Corp. (SDHC)</t>
+    <t>News Archive for SDHC</t>
+  </si>
+  <si>
+    <t>StealthGas Inc.</t>
+  </si>
+  <si>
+    <t>GASS</t>
+  </si>
+  <si>
+    <t>News Archive for GASS</t>
   </si>
   <si>
     <t>The Eastern Company</t>
@@ -618,63 +627,60 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.6</v>
+        <v>6.44</v>
       </c>
       <c r="D2" s="3">
-        <v>5.64</v>
+        <v>6.55</v>
       </c>
       <c r="E2" s="3">
         <v>4.25</v>
       </c>
       <c r="F2" s="2">
-        <v>46.9</v>
+        <v>66.0</v>
       </c>
       <c r="G2" s="2">
-        <v>13.9</v>
+        <v>19.6</v>
       </c>
       <c r="H2" s="3">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="I2" s="4">
-        <v>48.0</v>
-      </c>
-      <c r="J2" s="2" t="s">
+        <v>84.0</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C3" s="3">
-        <v>6.23</v>
+        <v>5.29</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="F3" s="2">
-        <v>264.2</v>
+        <v>224.6</v>
       </c>
       <c r="G3" s="2">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="I3" s="4">
-        <v>88.0</v>
+        <v>69.0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -688,7 +694,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -697,16 +703,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="G4" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>49.0</v>
+        <v>48.0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
@@ -723,7 +729,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="3">
-        <v>26.61</v>
+        <v>26.0</v>
       </c>
       <c r="D5" s="3">
         <v>28.69</v>
@@ -732,16 +738,16 @@
         <v>14.48</v>
       </c>
       <c r="F5" s="2">
-        <v>238.9</v>
+        <v>221.3</v>
       </c>
       <c r="G5" s="2">
-        <v>20.9</v>
+        <v>19.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="I5" s="4">
-        <v>88.0</v>
+        <v>81.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -755,7 +761,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>33.72</v>
+        <v>33.25</v>
       </c>
       <c r="D6" s="3">
         <v>35.91</v>
@@ -764,16 +770,16 @@
         <v>18.0</v>
       </c>
       <c r="F6" s="2">
-        <v>874.7</v>
+        <v>832.6</v>
       </c>
       <c r="G6" s="2">
-        <v>217.9</v>
+        <v>207.4</v>
       </c>
       <c r="H6" s="3">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="I6" s="4">
-        <v>94.0</v>
+        <v>91.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -787,7 +793,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>8.39</v>
+        <v>7.44</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -796,16 +802,16 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>126.5</v>
+        <v>150.0</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="3">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="I7" s="4">
-        <v>24.0</v>
+        <v>40.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -822,7 +828,7 @@
         <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>21.09</v>
+        <v>20.67</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -831,16 +837,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>528.1</v>
+        <v>525.8</v>
       </c>
       <c r="G8" s="2">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I8" s="4">
-        <v>76.0</v>
+        <v>70.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
@@ -854,22 +860,22 @@
         <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>18.19</v>
+        <v>19.65</v>
       </c>
       <c r="D9" s="3">
-        <v>19.11</v>
+        <v>21.32</v>
       </c>
       <c r="E9" s="3">
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>256.1</v>
+        <v>273.3</v>
       </c>
       <c r="G9" s="2">
-        <v>18.9</v>
+        <v>17.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="I9" s="4">
         <v>92.0</v>
@@ -886,25 +892,25 @@
         <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>69.96</v>
+        <v>73.19</v>
       </c>
       <c r="D10" s="3">
         <v>74.75</v>
       </c>
       <c r="E10" s="3">
-        <v>30.72</v>
+        <v>33.76</v>
       </c>
       <c r="F10" s="2">
-        <v>494.0</v>
+        <v>510.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="I10" s="4">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>41</v>
@@ -918,16 +924,16 @@
         <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>18.94</v>
+        <v>18.85</v>
       </c>
       <c r="D11" s="3">
         <v>18.95</v>
       </c>
       <c r="E11" s="3">
-        <v>12.14</v>
+        <v>12.24</v>
       </c>
       <c r="F11" s="2">
-        <v>124.1</v>
+        <v>123.8</v>
       </c>
       <c r="G11" s="2">
         <v>17.2</v>
@@ -939,7 +945,7 @@
         <v>74.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>44</v>
@@ -953,25 +959,25 @@
         <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>20.62</v>
+        <v>21.65</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
       </c>
       <c r="E12" s="3">
-        <v>14.0</v>
+        <v>14.51</v>
       </c>
       <c r="F12" s="2">
-        <v>146.4</v>
+        <v>149.6</v>
       </c>
       <c r="G12" s="2">
-        <v>9.3</v>
+        <v>9.5</v>
       </c>
       <c r="H12" s="3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="I12" s="4">
-        <v>47.0</v>
+        <v>45.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>47</v>
@@ -985,25 +991,25 @@
         <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>18.47</v>
+        <v>19.39</v>
       </c>
       <c r="D13" s="3">
-        <v>20.38</v>
+        <v>20.56</v>
       </c>
       <c r="E13" s="3">
         <v>5.43</v>
       </c>
       <c r="F13" s="2">
-        <v>1396.4</v>
+        <v>1425.1</v>
       </c>
       <c r="G13" s="2">
-        <v>54.3</v>
+        <v>55.4</v>
       </c>
       <c r="H13" s="3">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="I13" s="4">
-        <v>77.0</v>
+        <v>83.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>50</v>
@@ -1020,25 +1026,25 @@
         <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>27.2</v>
+        <v>26.14</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>14.3</v>
+        <v>17.17</v>
       </c>
       <c r="F14" s="2">
-        <v>654.0</v>
+        <v>628.4</v>
       </c>
       <c r="G14" s="2">
-        <v>27.8</v>
+        <v>24.7</v>
       </c>
       <c r="H14" s="3">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="I14" s="4">
-        <v>41.0</v>
+        <v>34.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>54</v>
@@ -1052,7 +1058,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>9.51</v>
+        <v>10.64</v>
       </c>
       <c r="D15" s="3">
         <v>20.5</v>
@@ -1061,13 +1067,13 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>109.1</v>
+        <v>116.2</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="3">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="I15" s="4">
         <v>17.0</v>
@@ -1087,22 +1093,22 @@
         <v>60</v>
       </c>
       <c r="C16" s="3">
-        <v>19.28</v>
+        <v>17.64</v>
       </c>
       <c r="D16" s="3">
-        <v>19.36</v>
+        <v>19.56</v>
       </c>
       <c r="E16" s="3">
         <v>7.06</v>
       </c>
       <c r="F16" s="2">
-        <v>600.7</v>
+        <v>596.2</v>
       </c>
       <c r="G16" s="2">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="H16" s="3">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="I16" s="4">
         <v>95.0</v>
@@ -1122,25 +1128,28 @@
         <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>48.05</v>
+        <v>50.37</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
       </c>
       <c r="E17" s="3">
-        <v>32.16</v>
+        <v>33.18</v>
       </c>
       <c r="F17" s="2">
-        <v>363.0</v>
+        <v>392.9</v>
       </c>
       <c r="G17" s="2">
-        <v>20.5</v>
+        <v>18.2</v>
       </c>
       <c r="H17" s="3">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="I17" s="4">
-        <v>66.0</v>
+        <v>71.0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -1154,25 +1163,25 @@
         <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>41.29</v>
+        <v>38.75</v>
       </c>
       <c r="D18" s="3">
         <v>41.51</v>
       </c>
       <c r="E18" s="3">
-        <v>17.89</v>
+        <v>19.11</v>
       </c>
       <c r="F18" s="2">
-        <v>512.6</v>
+        <v>498.6</v>
       </c>
       <c r="G18" s="2">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="H18" s="3">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="I18" s="4">
-        <v>88.0</v>
+        <v>83.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>68</v>
@@ -1186,7 +1195,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>49.76</v>
+        <v>40.36</v>
       </c>
       <c r="D19" s="3">
         <v>87.36</v>
@@ -1195,16 +1204,19 @@
         <v>28.64</v>
       </c>
       <c r="F19" s="2">
-        <v>139.8</v>
+        <v>101.8</v>
       </c>
       <c r="G19" s="2">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="H19" s="3">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I19" s="4">
-        <v>82.0</v>
+        <v>42.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>71</v>
@@ -1218,25 +1230,25 @@
         <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>11.23</v>
+        <v>8.66</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>3.61</v>
+        <v>4.23</v>
       </c>
       <c r="F20" s="2">
-        <v>691.1</v>
+        <v>535.8</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="3">
-        <v>1.19</v>
+        <v>0.93</v>
       </c>
       <c r="I20" s="4">
-        <v>94.0</v>
+        <v>85.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>20</v>
@@ -1253,22 +1265,22 @@
         <v>76</v>
       </c>
       <c r="C21" s="3">
-        <v>7.74</v>
+        <v>7.84</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
       </c>
       <c r="E21" s="3">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="F21" s="2">
-        <v>500.3</v>
+        <v>514.1</v>
       </c>
       <c r="G21" s="2">
-        <v>25.5</v>
+        <v>26.2</v>
       </c>
       <c r="H21" s="3">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I21" s="4">
         <v>91.0</v>
@@ -1285,25 +1297,25 @@
         <v>79</v>
       </c>
       <c r="C22" s="3">
-        <v>28.55</v>
+        <v>30.82</v>
       </c>
       <c r="D22" s="3">
-        <v>30.45</v>
+        <v>31.68</v>
       </c>
       <c r="E22" s="3">
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>398.1</v>
+        <v>424.1</v>
       </c>
       <c r="G22" s="2">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="H22" s="3">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="I22" s="4">
-        <v>85.0</v>
+        <v>88.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>80</v>
@@ -1317,28 +1329,28 @@
         <v>82</v>
       </c>
       <c r="C23" s="3">
-        <v>27.0</v>
+        <v>27.98</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
       </c>
       <c r="E23" s="3">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="F23" s="2">
-        <v>68.7</v>
+        <v>69.9</v>
       </c>
       <c r="G23" s="2">
         <v>0.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I23" s="4">
         <v>40.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>83</v>
@@ -1352,25 +1364,25 @@
         <v>85</v>
       </c>
       <c r="C24" s="3">
-        <v>37.4</v>
+        <v>37.38</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>17.14</v>
+        <v>19.41</v>
       </c>
       <c r="F24" s="2">
-        <v>276.5</v>
+        <v>273.7</v>
       </c>
       <c r="G24" s="2">
-        <v>12.4</v>
+        <v>14.7</v>
       </c>
       <c r="H24" s="3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I24" s="4">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>86</v>
@@ -1384,7 +1396,7 @@
         <v>88</v>
       </c>
       <c r="C25" s="3">
-        <v>11.01</v>
+        <v>10.86</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
@@ -1393,16 +1405,16 @@
         <v>10.68</v>
       </c>
       <c r="F25" s="2">
-        <v>71.8</v>
+        <v>69.9</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H25" s="3">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I25" s="4">
-        <v>42.0</v>
+        <v>35.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>89</v>
@@ -1416,7 +1428,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>13.95</v>
+        <v>13.0</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1425,16 +1437,16 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>118.5</v>
+        <v>107.7</v>
       </c>
       <c r="G26" s="2">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="H26" s="3">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="I26" s="4">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>92</v>
@@ -1448,60 +1460,94 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>22.0</v>
+        <v>9.9</v>
       </c>
       <c r="D27" s="3">
-        <v>26.77</v>
+        <v>10.52</v>
       </c>
       <c r="E27" s="3">
-        <v>17.61</v>
+        <v>5.22</v>
       </c>
       <c r="F27" s="2">
-        <v>132.0</v>
+        <v>364.4</v>
       </c>
       <c r="G27" s="2">
-        <v>22.3</v>
+        <v>6.0</v>
       </c>
       <c r="H27" s="3">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="I27" s="4">
-        <v>53.0</v>
+        <v>85.0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>60.22</v>
+        <v>22.18</v>
       </c>
       <c r="D28" s="3">
-        <v>61.94</v>
+        <v>26.77</v>
       </c>
       <c r="E28" s="3">
-        <v>22.66</v>
+        <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>803.4</v>
+        <v>136.2</v>
       </c>
       <c r="G28" s="2">
-        <v>151.4</v>
+        <v>23.1</v>
       </c>
       <c r="H28" s="3">
-        <v>2.39</v>
+        <v>1.09</v>
       </c>
       <c r="I28" s="4">
-        <v>92.0</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1"/>
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="3">
+        <v>67.24</v>
+      </c>
+      <c r="D29" s="3">
+        <v>66.12</v>
+      </c>
+      <c r="E29" s="3">
+        <v>22.68</v>
+      </c>
+      <c r="F29" s="2">
+        <v>830.2</v>
+      </c>
+      <c r="G29" s="2">
+        <v>156.5</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2.46</v>
+      </c>
+      <c r="I29" s="4">
+        <v>93.0</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="VdKWTpNbNveXMcAFnaq0s0jSqgfvATf/9bysQhIMhp0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="W726vHa+VYu8RaG1u+r4ODzjDSj7eGUUYzEsoHRvVKQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="102">
   <si>
     <t>Company</t>
   </si>
@@ -57,7 +57,10 @@
     <t>APT</t>
   </si>
   <si>
-    <t>(5/7/26) Alpha Pro Tech, Ltd. (APT)</t>
+    <t>Currently qualifies</t>
+  </si>
+  <si>
+    <t>News Archive for APT</t>
   </si>
   <si>
     <t>Amplify Energy Corp.</t>
@@ -66,9 +69,6 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>Currently qualifies</t>
-  </si>
-  <si>
     <t>News Archive for AMPY</t>
   </si>
   <si>
@@ -78,169 +78,166 @@
     <t>CTRM</t>
   </si>
   <si>
+    <t>News Archive for CTRM</t>
+  </si>
+  <si>
+    <t>Core Molding Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>CMT</t>
+  </si>
+  <si>
+    <t>News Archive for CMT</t>
+  </si>
+  <si>
+    <t>Covenant Logistics Group, Inc.</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>News Archive for CVLG</t>
+  </si>
+  <si>
+    <t>DMC Global Inc.</t>
+  </si>
+  <si>
+    <t>BOOM</t>
+  </si>
+  <si>
+    <t>nmf</t>
+  </si>
+  <si>
+    <t>Earnings probation 2025q4</t>
+  </si>
+  <si>
+    <t>News Archive for BOOM</t>
+  </si>
+  <si>
+    <t>Ennis, Inc.</t>
+  </si>
+  <si>
+    <t>EBF</t>
+  </si>
+  <si>
+    <t>News Archive for EBF</t>
+  </si>
+  <si>
+    <t>Escalade, Incorporated</t>
+  </si>
+  <si>
+    <t>ESCA</t>
+  </si>
+  <si>
+    <t>News Archive for ESCA</t>
+  </si>
+  <si>
+    <t>Euroseas Ltd.</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>News Archive for ESEA</t>
+  </si>
+  <si>
+    <t>FONAR Corporation</t>
+  </si>
+  <si>
+    <t>FONR</t>
+  </si>
+  <si>
+    <t>(5/11/26) FONAR Corporation (FONR)</t>
+  </si>
+  <si>
+    <t>Friedman Industries, Incorporated</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>News Archive for FRD</t>
+  </si>
+  <si>
+    <t>Gilat Satellite Networks Ltd.</t>
+  </si>
+  <si>
+    <t>GILT</t>
+  </si>
+  <si>
+    <t>Exceeds size limit</t>
+  </si>
+  <si>
+    <t>(5/13/26) Gilat Satellite Networks Ltd. (GILT)</t>
+  </si>
+  <si>
+    <t>Kimball Electronics, Inc.</t>
+  </si>
+  <si>
+    <t>KE</t>
+  </si>
+  <si>
+    <t>News Archive for KE</t>
+  </si>
+  <si>
+    <t>Lakeland Industries, Inc.</t>
+  </si>
+  <si>
+    <t>LAKE</t>
+  </si>
+  <si>
+    <t>Earnings probation 2025Q3</t>
+  </si>
+  <si>
+    <t>News Archive for LAKE</t>
+  </si>
+  <si>
+    <t>Mistras Group, Inc.</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>News Archive for MG</t>
+  </si>
+  <si>
+    <t>NACCO Industries, Inc.</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>News Archive for NC</t>
+  </si>
+  <si>
+    <t>Natural Gas Services Group, Inc.</t>
+  </si>
+  <si>
+    <t>NGS</t>
+  </si>
+  <si>
+    <t>(5/11/26) Natural Gas Services Group, Inc. (NGS)</t>
+  </si>
+  <si>
+    <t>NCS Multistage Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>NCSM</t>
+  </si>
+  <si>
+    <t>News Archive for NCSM</t>
+  </si>
+  <si>
+    <t>Oil States International, Inc.</t>
+  </si>
+  <si>
+    <t>OIS</t>
+  </si>
+  <si>
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
-    <t>News Archive for CTRM</t>
-  </si>
-  <si>
-    <t>Core Molding Technologies, Inc.</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>News Archive for CMT</t>
-  </si>
-  <si>
-    <t>Covenant Logistics Group, Inc.</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>News Archive for CVLG</t>
-  </si>
-  <si>
-    <t>DMC Global Inc.</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>nmf</t>
-  </si>
-  <si>
-    <t>Earnings probation 2025q4</t>
-  </si>
-  <si>
-    <t>News Archive for BOOM</t>
-  </si>
-  <si>
-    <t>Ennis, Inc.</t>
-  </si>
-  <si>
-    <t>EBF</t>
-  </si>
-  <si>
-    <t>News Archive for EBF</t>
-  </si>
-  <si>
-    <t>Escalade, Incorporated</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>News Archive for ESCA</t>
-  </si>
-  <si>
-    <t>Euroseas Ltd.</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>News Archive for ESEA</t>
-  </si>
-  <si>
-    <t>FONAR Corporation</t>
-  </si>
-  <si>
-    <t>FONR</t>
-  </si>
-  <si>
-    <t>News Archive for FONR</t>
-  </si>
-  <si>
-    <t>Friedman Industries, Incorporated</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>News Archive for FRD</t>
-  </si>
-  <si>
-    <t>Gilat Satellite Networks Ltd.</t>
-  </si>
-  <si>
-    <t>GILT</t>
-  </si>
-  <si>
-    <t>Exceeds size limit Approaching value limit</t>
-  </si>
-  <si>
-    <t>News Archive for GILT</t>
-  </si>
-  <si>
-    <t>Kimball Electronics, Inc.</t>
-  </si>
-  <si>
-    <t>KE</t>
-  </si>
-  <si>
-    <t>(5/5/26) Kimball Electronics, Inc. (KE)</t>
-  </si>
-  <si>
-    <t>Lakeland Industries, Inc.</t>
-  </si>
-  <si>
-    <t>LAKE</t>
-  </si>
-  <si>
-    <t>Earnings probation 2025Q3</t>
-  </si>
-  <si>
-    <t>News Archive for LAKE</t>
-  </si>
-  <si>
-    <t>Mistras Group, Inc.</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>Approaching value limit</t>
-  </si>
-  <si>
-    <t>(5/5/26) Mistras Group, Inc. (MG)</t>
-  </si>
-  <si>
-    <t>NACCO Industries, Inc.</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>(5/5/26) NACCO Industries, Inc. (NC)</t>
-  </si>
-  <si>
-    <t>Natural Gas Services Group, Inc.</t>
-  </si>
-  <si>
-    <t>NGS</t>
-  </si>
-  <si>
-    <t>News Archive for NGS</t>
-  </si>
-  <si>
-    <t>NCS Multistage Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>NCSM</t>
-  </si>
-  <si>
-    <t>News Archive for NCSM</t>
-  </si>
-  <si>
-    <t>Oil States International, Inc.</t>
-  </si>
-  <si>
-    <t>OIS</t>
-  </si>
-  <si>
-    <t>(5/5/26) Oil States International, Inc. (OIS)</t>
+    <t>News Archive for OIS</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions Ltd.</t>
@@ -249,7 +246,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>News Archive for PANL</t>
+    <t>(5/11/26) Pangaea Logistics Solutions Ltd. (PANL)</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -258,7 +255,7 @@
     <t>PKOH</t>
   </si>
   <si>
-    <t>(5/6/26) Park-Ohio Holdings Corp. (PKOH)</t>
+    <t>News Archive for PKOH</t>
   </si>
   <si>
     <t>Regis Corporation</t>
@@ -285,7 +282,10 @@
     <t>SGA</t>
   </si>
   <si>
-    <t>(5/7/26) Saga Communications, Inc. (SGA)</t>
+    <t>Earnings probation 2025Q4</t>
+  </si>
+  <si>
+    <t>News Archive for SGA</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -318,7 +318,10 @@
     <t>VPG</t>
   </si>
   <si>
-    <t>News Archive for VPG</t>
+    <t>Exceeds size limit Exceeds value limit</t>
+  </si>
+  <si>
+    <t>(5/12/26) Vishay Precision Group, Inc. (VPG)</t>
   </si>
 </sst>
 </file>
@@ -627,39 +630,42 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>6.44</v>
+        <v>5.49</v>
       </c>
       <c r="D2" s="3">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="E2" s="3">
         <v>4.25</v>
       </c>
       <c r="F2" s="2">
-        <v>66.0</v>
+        <v>60.1</v>
       </c>
       <c r="G2" s="2">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="H2" s="3">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="I2" s="4">
-        <v>84.0</v>
+        <v>73.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -668,19 +674,16 @@
         <v>2.6</v>
       </c>
       <c r="F3" s="2">
-        <v>224.6</v>
+        <v>210.6</v>
       </c>
       <c r="G3" s="2">
-        <v>5.3</v>
+        <v>22.2</v>
       </c>
       <c r="H3" s="3">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="I3" s="4">
-        <v>69.0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>16</v>
+        <v>34.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -694,7 +697,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -703,65 +706,62 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>19.5</v>
+        <v>18.6</v>
       </c>
       <c r="G4" s="2">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>48.0</v>
-      </c>
-      <c r="J4" s="2" t="s">
+        <v>42.0</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C5" s="3">
-        <v>26.0</v>
+        <v>23.91</v>
       </c>
       <c r="D5" s="3">
         <v>28.69</v>
       </c>
       <c r="E5" s="3">
-        <v>14.48</v>
+        <v>15.02</v>
       </c>
       <c r="F5" s="2">
-        <v>221.3</v>
+        <v>211.4</v>
       </c>
       <c r="G5" s="2">
-        <v>19.3</v>
+        <v>22.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="I5" s="4">
-        <v>81.0</v>
+        <v>79.0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C6" s="3">
-        <v>33.25</v>
+        <v>34.27</v>
       </c>
       <c r="D6" s="3">
         <v>35.91</v>
@@ -770,30 +770,30 @@
         <v>18.0</v>
       </c>
       <c r="F6" s="2">
-        <v>832.6</v>
+        <v>858.6</v>
       </c>
       <c r="G6" s="2">
-        <v>207.4</v>
+        <v>431.8</v>
       </c>
       <c r="H6" s="3">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I6" s="4">
-        <v>91.0</v>
+        <v>93.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="C7" s="3">
-        <v>7.44</v>
+        <v>6.93</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -802,33 +802,33 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>150.0</v>
+        <v>150.9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3">
         <v>0.64</v>
       </c>
       <c r="I7" s="4">
-        <v>40.0</v>
+        <v>71.0</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="C8" s="3">
-        <v>20.67</v>
+        <v>20.02</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -837,30 +837,30 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>525.8</v>
+        <v>512.9</v>
       </c>
       <c r="G8" s="2">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="H8" s="3">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="I8" s="4">
         <v>70.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C9" s="3">
-        <v>19.65</v>
+        <v>18.35</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -869,97 +869,97 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>273.3</v>
+        <v>256.5</v>
       </c>
       <c r="G9" s="2">
-        <v>17.7</v>
+        <v>16.6</v>
       </c>
       <c r="H9" s="3">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="I9" s="4">
-        <v>92.0</v>
+        <v>87.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="3">
+        <v>69.64</v>
+      </c>
+      <c r="D10" s="3">
+        <v>74.76</v>
+      </c>
+      <c r="E10" s="3">
+        <v>37.11</v>
+      </c>
+      <c r="F10" s="2">
+        <v>493.6</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1.07</v>
+      </c>
+      <c r="I10" s="4">
+        <v>68.0</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C10" s="3">
-        <v>73.19</v>
-      </c>
-      <c r="D10" s="3">
-        <v>74.75</v>
-      </c>
-      <c r="E10" s="3">
-        <v>33.76</v>
-      </c>
-      <c r="F10" s="2">
-        <v>510.0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1.35</v>
-      </c>
-      <c r="I10" s="4">
-        <v>75.0</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C11" s="3">
-        <v>18.85</v>
+        <v>18.86</v>
       </c>
       <c r="D11" s="3">
         <v>18.95</v>
       </c>
       <c r="E11" s="3">
-        <v>12.24</v>
+        <v>12.63</v>
       </c>
       <c r="F11" s="2">
-        <v>123.8</v>
+        <v>123.6</v>
       </c>
       <c r="G11" s="2">
-        <v>17.2</v>
+        <v>19.4</v>
       </c>
       <c r="H11" s="3">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C12" s="3">
-        <v>21.65</v>
+        <v>20.6</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -968,65 +968,65 @@
         <v>14.51</v>
       </c>
       <c r="F12" s="2">
-        <v>149.6</v>
+        <v>148.6</v>
       </c>
       <c r="G12" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H12" s="3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I12" s="4">
-        <v>45.0</v>
+        <v>49.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C13" s="3">
-        <v>19.39</v>
+        <v>15.19</v>
       </c>
       <c r="D13" s="3">
-        <v>20.56</v>
+        <v>20.93</v>
       </c>
       <c r="E13" s="3">
         <v>5.43</v>
       </c>
       <c r="F13" s="2">
-        <v>1425.1</v>
+        <v>1216.4</v>
       </c>
       <c r="G13" s="2">
-        <v>55.4</v>
+        <v>47.3</v>
       </c>
       <c r="H13" s="3">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="I13" s="4">
-        <v>83.0</v>
+        <v>77.0</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C14" s="3">
-        <v>26.14</v>
+        <v>24.53</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1035,30 +1035,30 @@
         <v>17.17</v>
       </c>
       <c r="F14" s="2">
-        <v>628.4</v>
+        <v>601.5</v>
       </c>
       <c r="G14" s="2">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="H14" s="3">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="I14" s="4">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C15" s="3">
-        <v>10.64</v>
+        <v>9.53</v>
       </c>
       <c r="D15" s="3">
         <v>20.5</v>
@@ -1067,135 +1067,132 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>116.2</v>
+        <v>112.5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="I15" s="4">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C16" s="3">
-        <v>17.64</v>
+        <v>17.0</v>
       </c>
       <c r="D16" s="3">
         <v>19.56</v>
       </c>
       <c r="E16" s="3">
-        <v>7.06</v>
+        <v>7.22</v>
       </c>
       <c r="F16" s="2">
-        <v>596.2</v>
+        <v>539.0</v>
       </c>
       <c r="G16" s="2">
-        <v>35.4</v>
+        <v>24.6</v>
       </c>
       <c r="H16" s="3">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
       <c r="I16" s="4">
-        <v>95.0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>61</v>
+        <v>78.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>50.37</v>
+        <v>49.39</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
       </c>
       <c r="E17" s="3">
-        <v>33.18</v>
+        <v>34.74</v>
       </c>
       <c r="F17" s="2">
-        <v>392.9</v>
+        <v>385.7</v>
       </c>
       <c r="G17" s="2">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="H17" s="3">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="I17" s="4">
-        <v>71.0</v>
+        <v>55.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="3">
+        <v>42.4</v>
+      </c>
+      <c r="D18" s="3">
+        <v>43.27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>22.72</v>
+      </c>
+      <c r="F18" s="2">
+        <v>530.3</v>
+      </c>
+      <c r="G18" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="I18" s="4">
+        <v>87.0</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="3">
-        <v>38.75</v>
-      </c>
-      <c r="D18" s="3">
-        <v>41.51</v>
-      </c>
-      <c r="E18" s="3">
-        <v>19.11</v>
-      </c>
-      <c r="F18" s="2">
-        <v>498.6</v>
-      </c>
-      <c r="G18" s="2">
-        <v>25.2</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1.81</v>
-      </c>
-      <c r="I18" s="4">
-        <v>83.0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>40.36</v>
+        <v>42.69</v>
       </c>
       <c r="D19" s="3">
         <v>87.36</v>
@@ -1204,33 +1201,33 @@
         <v>28.64</v>
       </c>
       <c r="F19" s="2">
-        <v>101.8</v>
+        <v>112.1</v>
       </c>
       <c r="G19" s="2">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H19" s="3">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="I19" s="4">
-        <v>42.0</v>
+        <v>69.0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" s="3">
-        <v>8.66</v>
+        <v>9.01</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
@@ -1239,97 +1236,97 @@
         <v>4.23</v>
       </c>
       <c r="F20" s="2">
-        <v>535.8</v>
+        <v>544.8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" s="3">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="I20" s="4">
-        <v>85.0</v>
+        <v>82.0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C21" s="3">
-        <v>7.84</v>
+        <v>8.19</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
       </c>
       <c r="E21" s="3">
-        <v>3.98</v>
+        <v>4.22</v>
       </c>
       <c r="F21" s="2">
-        <v>514.1</v>
+        <v>541.0</v>
       </c>
       <c r="G21" s="2">
-        <v>26.2</v>
+        <v>15.4</v>
       </c>
       <c r="H21" s="3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="I21" s="4">
-        <v>91.0</v>
+        <v>79.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="C22" s="3">
-        <v>30.82</v>
+        <v>30.62</v>
       </c>
       <c r="D22" s="3">
-        <v>31.68</v>
+        <v>31.92</v>
       </c>
       <c r="E22" s="3">
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>424.1</v>
+        <v>424.2</v>
       </c>
       <c r="G22" s="2">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="H22" s="3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I22" s="4">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C23" s="3">
-        <v>27.98</v>
+        <v>28.3</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1338,83 +1335,89 @@
         <v>18.2</v>
       </c>
       <c r="F23" s="2">
-        <v>69.9</v>
+        <v>72.2</v>
       </c>
       <c r="G23" s="2">
         <v>0.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I23" s="4">
-        <v>40.0</v>
+        <v>52.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C24" s="3">
-        <v>37.38</v>
+        <v>33.72</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>19.41</v>
+        <v>19.82</v>
       </c>
       <c r="F24" s="2">
-        <v>273.7</v>
+        <v>249.8</v>
       </c>
       <c r="G24" s="2">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="H24" s="3">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="I24" s="4">
-        <v>75.0</v>
+        <v>58.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="C25" s="3">
-        <v>10.86</v>
+        <v>10.11</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
       </c>
       <c r="E25" s="3">
-        <v>10.68</v>
+        <v>9.96</v>
       </c>
       <c r="F25" s="2">
-        <v>69.9</v>
+        <v>64.6</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H25" s="3">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="I25" s="4">
-        <v>35.0</v>
+        <v>31.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>89</v>
@@ -1428,7 +1431,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>13.0</v>
+        <v>11.17</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1437,16 +1440,16 @@
         <v>11.13</v>
       </c>
       <c r="F26" s="2">
-        <v>107.7</v>
+        <v>97.0</v>
       </c>
       <c r="G26" s="2">
-        <v>10.9</v>
+        <v>9.8</v>
       </c>
       <c r="H26" s="3">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="I26" s="4">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>92</v>
@@ -1460,7 +1463,7 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>9.9</v>
+        <v>10.07</v>
       </c>
       <c r="D27" s="3">
         <v>10.52</v>
@@ -1469,19 +1472,19 @@
         <v>5.22</v>
       </c>
       <c r="F27" s="2">
-        <v>364.4</v>
+        <v>381.5</v>
       </c>
       <c r="G27" s="2">
-        <v>6.0</v>
+        <v>6.3</v>
       </c>
       <c r="H27" s="3">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="I27" s="4">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>95</v>
@@ -1495,7 +1498,7 @@
         <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>22.18</v>
+        <v>19.95</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1504,16 +1507,19 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>136.2</v>
+        <v>122.2</v>
       </c>
       <c r="G28" s="2">
-        <v>23.1</v>
+        <v>26.2</v>
       </c>
       <c r="H28" s="3">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="I28" s="4">
-        <v>53.0</v>
+        <v>56.0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1524,28 +1530,31 @@
         <v>99</v>
       </c>
       <c r="C29" s="3">
-        <v>67.24</v>
+        <v>97.32</v>
       </c>
       <c r="D29" s="3">
-        <v>66.12</v>
+        <v>105.17</v>
       </c>
       <c r="E29" s="3">
-        <v>22.68</v>
+        <v>24.89</v>
       </c>
       <c r="F29" s="2">
-        <v>830.2</v>
+        <v>1334.6</v>
       </c>
       <c r="G29" s="2">
-        <v>156.5</v>
+        <v>225.0</v>
       </c>
       <c r="H29" s="3">
-        <v>2.46</v>
+        <v>3.99</v>
       </c>
       <c r="I29" s="4">
-        <v>93.0</v>
+        <v>99.0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="W726vHa+VYu8RaG1u+r4ODzjDSj7eGUUYzEsoHRvVKQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Gb7yWe38vjqW66+8LffKvw+jzjooadvgq9AMGMatv64="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="102">
   <si>
     <t>Company</t>
   </si>
@@ -147,7 +147,7 @@
     <t>FONR</t>
   </si>
   <si>
-    <t>(5/11/26) FONAR Corporation (FONR)</t>
+    <t>News Archive for FONR</t>
   </si>
   <si>
     <t>Friedman Industries, Incorporated</t>
@@ -165,10 +165,10 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Exceeds size limit</t>
-  </si>
-  <si>
-    <t>(5/13/26) Gilat Satellite Networks Ltd. (GILT)</t>
+    <t>Approaching size limit</t>
+  </si>
+  <si>
+    <t>News Archive for GILT</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -216,7 +216,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>(5/11/26) Natural Gas Services Group, Inc. (NGS)</t>
+    <t>News Archive for NGS</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -246,7 +246,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>(5/11/26) Pangaea Logistics Solutions Ltd. (PANL)</t>
+    <t>News Archive for PANL</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -321,7 +321,7 @@
     <t>Exceeds size limit Exceeds value limit</t>
   </si>
   <si>
-    <t>(5/12/26) Vishay Precision Group, Inc. (VPG)</t>
+    <t>News Archive for VPG</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.49</v>
+        <v>6.27</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -639,16 +639,16 @@
         <v>4.25</v>
       </c>
       <c r="F2" s="2">
-        <v>60.1</v>
+        <v>63.1</v>
       </c>
       <c r="G2" s="2">
-        <v>17.8</v>
+        <v>18.7</v>
       </c>
       <c r="H2" s="3">
-        <v>0.95</v>
+        <v>1.0</v>
       </c>
       <c r="I2" s="4">
-        <v>73.0</v>
+        <v>82.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.23</v>
+        <v>5.01</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -674,16 +674,16 @@
         <v>2.6</v>
       </c>
       <c r="F3" s="2">
-        <v>210.6</v>
+        <v>208.5</v>
       </c>
       <c r="G3" s="2">
-        <v>22.2</v>
+        <v>22.0</v>
       </c>
       <c r="H3" s="3">
         <v>0.5</v>
       </c>
       <c r="I3" s="4">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -697,7 +697,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -706,16 +706,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>18.6</v>
+        <v>19.8</v>
       </c>
       <c r="G4" s="2">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>42.0</v>
+        <v>54.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -729,25 +729,25 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>23.91</v>
+        <v>23.53</v>
       </c>
       <c r="D5" s="3">
         <v>28.69</v>
       </c>
       <c r="E5" s="3">
-        <v>15.02</v>
+        <v>15.62</v>
       </c>
       <c r="F5" s="2">
-        <v>211.4</v>
+        <v>207.2</v>
       </c>
       <c r="G5" s="2">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="H5" s="3">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="I5" s="4">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -761,25 +761,25 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>34.27</v>
+        <v>37.41</v>
       </c>
       <c r="D6" s="3">
-        <v>35.91</v>
+        <v>37.39</v>
       </c>
       <c r="E6" s="3">
         <v>18.0</v>
       </c>
       <c r="F6" s="2">
-        <v>858.6</v>
+        <v>940.6</v>
       </c>
       <c r="G6" s="2">
-        <v>431.8</v>
+        <v>473.0</v>
       </c>
       <c r="H6" s="3">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="I6" s="4">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -793,7 +793,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>6.93</v>
+        <v>6.9</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -802,16 +802,16 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>150.9</v>
+        <v>140.2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="I7" s="4">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -828,7 +828,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>20.02</v>
+        <v>20.28</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -837,16 +837,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>512.9</v>
+        <v>506.9</v>
       </c>
       <c r="G8" s="2">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="I8" s="4">
-        <v>70.0</v>
+        <v>68.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -860,7 +860,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -869,16 +869,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>256.5</v>
+        <v>257.2</v>
       </c>
       <c r="G9" s="2">
         <v>16.6</v>
       </c>
       <c r="H9" s="3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I9" s="4">
-        <v>87.0</v>
+        <v>85.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -892,25 +892,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>69.64</v>
+        <v>65.21</v>
       </c>
       <c r="D10" s="3">
-        <v>74.76</v>
+        <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>37.11</v>
+        <v>37.4</v>
       </c>
       <c r="F10" s="2">
-        <v>493.6</v>
+        <v>522.1</v>
       </c>
       <c r="G10" s="2">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H10" s="3">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="I10" s="4">
-        <v>68.0</v>
+        <v>78.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -924,25 +924,25 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.86</v>
+        <v>18.9</v>
       </c>
       <c r="D11" s="3">
         <v>18.95</v>
       </c>
       <c r="E11" s="3">
-        <v>12.63</v>
+        <v>13.33</v>
       </c>
       <c r="F11" s="2">
-        <v>123.6</v>
+        <v>124.2</v>
       </c>
       <c r="G11" s="2">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="H11" s="3">
         <v>0.69</v>
       </c>
       <c r="I11" s="4">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -959,7 +959,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>20.6</v>
+        <v>20.68</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -968,16 +968,16 @@
         <v>14.51</v>
       </c>
       <c r="F12" s="2">
-        <v>148.6</v>
+        <v>146.0</v>
       </c>
       <c r="G12" s="2">
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="H12" s="3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="I12" s="4">
-        <v>49.0</v>
+        <v>46.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -991,7 +991,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>15.19</v>
+        <v>15.73</v>
       </c>
       <c r="D13" s="3">
         <v>20.93</v>
@@ -1000,16 +1000,16 @@
         <v>5.43</v>
       </c>
       <c r="F13" s="2">
-        <v>1216.4</v>
+        <v>1161.9</v>
       </c>
       <c r="G13" s="2">
-        <v>47.3</v>
+        <v>45.2</v>
       </c>
       <c r="H13" s="3">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="I13" s="4">
-        <v>77.0</v>
+        <v>80.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1026,25 +1026,25 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>24.53</v>
+        <v>24.6</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>17.17</v>
+        <v>17.29</v>
       </c>
       <c r="F14" s="2">
-        <v>601.5</v>
+        <v>582.2</v>
       </c>
       <c r="G14" s="2">
-        <v>23.8</v>
+        <v>23.0</v>
       </c>
       <c r="H14" s="3">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I14" s="4">
-        <v>36.0</v>
+        <v>31.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1058,22 +1058,22 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>9.53</v>
+        <v>10.43</v>
       </c>
       <c r="D15" s="3">
-        <v>20.5</v>
+        <v>19.77</v>
       </c>
       <c r="E15" s="3">
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>112.5</v>
+        <v>97.5</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I15" s="4">
         <v>16.0</v>
@@ -1093,7 +1093,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>17.0</v>
+        <v>17.28</v>
       </c>
       <c r="D16" s="3">
         <v>19.56</v>
@@ -1102,16 +1102,16 @@
         <v>7.22</v>
       </c>
       <c r="F16" s="2">
-        <v>539.0</v>
+        <v>547.2</v>
       </c>
       <c r="G16" s="2">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="H16" s="3">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="I16" s="4">
-        <v>78.0</v>
+        <v>85.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1125,25 +1125,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>49.39</v>
+        <v>48.99</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
       </c>
       <c r="E17" s="3">
-        <v>34.74</v>
+        <v>35.31</v>
       </c>
       <c r="F17" s="2">
-        <v>385.7</v>
+        <v>373.0</v>
       </c>
       <c r="G17" s="2">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="H17" s="3">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="I17" s="4">
-        <v>55.0</v>
+        <v>40.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1160,25 +1160,25 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>42.4</v>
+        <v>42.51</v>
       </c>
       <c r="D18" s="3">
-        <v>43.27</v>
+        <v>44.12</v>
       </c>
       <c r="E18" s="3">
         <v>22.72</v>
       </c>
       <c r="F18" s="2">
-        <v>530.3</v>
+        <v>533.7</v>
       </c>
       <c r="G18" s="2">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="H18" s="3">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I18" s="4">
-        <v>87.0</v>
+        <v>83.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1192,7 +1192,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>42.69</v>
+        <v>44.23</v>
       </c>
       <c r="D19" s="3">
         <v>87.36</v>
@@ -1201,19 +1201,16 @@
         <v>28.64</v>
       </c>
       <c r="F19" s="2">
-        <v>112.1</v>
+        <v>114.7</v>
       </c>
       <c r="G19" s="2">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="H19" s="3">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="I19" s="4">
-        <v>69.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>67.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>69</v>
@@ -1227,7 +1224,7 @@
         <v>71</v>
       </c>
       <c r="C20" s="3">
-        <v>9.01</v>
+        <v>8.85</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
@@ -1236,16 +1233,16 @@
         <v>4.23</v>
       </c>
       <c r="F20" s="2">
-        <v>544.8</v>
+        <v>534.5</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="3">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="I20" s="4">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>72</v>
@@ -1262,16 +1259,16 @@
         <v>75</v>
       </c>
       <c r="C21" s="3">
-        <v>8.19</v>
+        <v>8.02</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
       </c>
       <c r="E21" s="3">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="F21" s="2">
-        <v>541.0</v>
+        <v>541.6</v>
       </c>
       <c r="G21" s="2">
         <v>15.4</v>
@@ -1280,7 +1277,7 @@
         <v>1.23</v>
       </c>
       <c r="I21" s="4">
-        <v>79.0</v>
+        <v>74.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>76</v>
@@ -1294,7 +1291,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="3">
-        <v>30.62</v>
+        <v>31.15</v>
       </c>
       <c r="D22" s="3">
         <v>31.92</v>
@@ -1303,16 +1300,16 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>424.2</v>
+        <v>416.9</v>
       </c>
       <c r="G22" s="2">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="H22" s="3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="I22" s="4">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>79</v>
@@ -1326,7 +1323,7 @@
         <v>81</v>
       </c>
       <c r="C23" s="3">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1335,16 +1332,16 @@
         <v>18.2</v>
       </c>
       <c r="F23" s="2">
-        <v>72.2</v>
+        <v>70.0</v>
       </c>
       <c r="G23" s="2">
         <v>0.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I23" s="4">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1361,28 +1358,25 @@
         <v>84</v>
       </c>
       <c r="C24" s="3">
-        <v>33.72</v>
+        <v>35.75</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>19.82</v>
+        <v>20.31</v>
       </c>
       <c r="F24" s="2">
-        <v>249.8</v>
+        <v>269.8</v>
       </c>
       <c r="G24" s="2">
-        <v>13.4</v>
+        <v>14.5</v>
       </c>
       <c r="H24" s="3">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="I24" s="4">
-        <v>58.0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>70.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>85</v>
@@ -1396,25 +1390,25 @@
         <v>87</v>
       </c>
       <c r="C25" s="3">
-        <v>10.11</v>
+        <v>9.58</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
       </c>
       <c r="E25" s="3">
-        <v>9.96</v>
+        <v>9.9</v>
       </c>
       <c r="F25" s="2">
-        <v>64.6</v>
+        <v>64.3</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H25" s="3">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="I25" s="4">
-        <v>31.0</v>
+        <v>28.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>88</v>
@@ -1431,25 +1425,25 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>11.17</v>
+        <v>11.69</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
       </c>
       <c r="E26" s="3">
-        <v>11.13</v>
+        <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>97.0</v>
+        <v>97.1</v>
       </c>
       <c r="G26" s="2">
-        <v>9.8</v>
+        <v>12.2</v>
       </c>
       <c r="H26" s="3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="I26" s="4">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>92</v>
@@ -1463,25 +1457,25 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>10.07</v>
+        <v>9.92</v>
       </c>
       <c r="D27" s="3">
-        <v>10.52</v>
+        <v>10.55</v>
       </c>
       <c r="E27" s="3">
         <v>5.22</v>
       </c>
       <c r="F27" s="2">
-        <v>381.5</v>
+        <v>380.0</v>
       </c>
       <c r="G27" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H27" s="3">
         <v>0.55</v>
       </c>
       <c r="I27" s="4">
-        <v>87.0</v>
+        <v>86.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1498,7 +1492,7 @@
         <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>19.95</v>
+        <v>21.04</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1507,19 +1501,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>122.2</v>
+        <v>126.8</v>
       </c>
       <c r="G28" s="2">
-        <v>26.2</v>
+        <v>27.1</v>
       </c>
       <c r="H28" s="3">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="I28" s="4">
-        <v>56.0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1530,22 +1521,22 @@
         <v>99</v>
       </c>
       <c r="C29" s="3">
-        <v>97.32</v>
+        <v>113.76</v>
       </c>
       <c r="D29" s="3">
-        <v>105.17</v>
+        <v>108.0</v>
       </c>
       <c r="E29" s="3">
         <v>24.89</v>
       </c>
       <c r="F29" s="2">
-        <v>1334.6</v>
+        <v>1383.8</v>
       </c>
       <c r="G29" s="2">
-        <v>225.0</v>
+        <v>233.3</v>
       </c>
       <c r="H29" s="3">
-        <v>3.99</v>
+        <v>4.14</v>
       </c>
       <c r="I29" s="4">
         <v>99.0</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Gb7yWe38vjqW66+8LffKvw+jzjooadvgq9AMGMatv64="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="4k4p3memRWjEB++8Jo/kd8JSWjGwzeNeJ6Jx7sg++SI="/>
     </ext>
   </extLst>
 </workbook>
@@ -165,7 +165,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Approaching size limit</t>
+    <t>Exceeds size limit Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for GILT</t>
@@ -630,25 +630,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>6.27</v>
+        <v>5.82</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
       </c>
       <c r="E2" s="3">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>63.1</v>
+        <v>58.5</v>
       </c>
       <c r="G2" s="2">
-        <v>18.7</v>
+        <v>17.4</v>
       </c>
       <c r="H2" s="3">
-        <v>1.0</v>
+        <v>0.93</v>
       </c>
       <c r="I2" s="4">
-        <v>82.0</v>
+        <v>73.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,25 +665,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>5.01</v>
+        <v>4.63</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="F3" s="2">
-        <v>208.5</v>
+        <v>193.2</v>
       </c>
       <c r="G3" s="2">
-        <v>22.0</v>
+        <v>20.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="I3" s="4">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -697,7 +697,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -706,16 +706,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>19.8</v>
+        <v>18.0</v>
       </c>
       <c r="G4" s="2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I4" s="4">
-        <v>54.0</v>
+        <v>37.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -729,25 +729,25 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>23.53</v>
+        <v>23.69</v>
       </c>
       <c r="D5" s="3">
         <v>28.69</v>
       </c>
       <c r="E5" s="3">
-        <v>15.62</v>
+        <v>15.81</v>
       </c>
       <c r="F5" s="2">
-        <v>207.2</v>
+        <v>209.7</v>
       </c>
       <c r="G5" s="2">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="H5" s="3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I5" s="4">
-        <v>80.0</v>
+        <v>77.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -761,22 +761,22 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>37.41</v>
+        <v>39.7</v>
       </c>
       <c r="D6" s="3">
-        <v>37.39</v>
+        <v>40.0</v>
       </c>
       <c r="E6" s="3">
         <v>18.0</v>
       </c>
       <c r="F6" s="2">
-        <v>940.6</v>
+        <v>995.5</v>
       </c>
       <c r="G6" s="2">
-        <v>473.0</v>
+        <v>500.6</v>
       </c>
       <c r="H6" s="3">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="I6" s="4">
         <v>95.0</v>
@@ -793,7 +793,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>6.9</v>
+        <v>6.81</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -802,16 +802,16 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>140.2</v>
+        <v>148.4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="4">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -828,7 +828,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>20.28</v>
+        <v>20.46</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -837,16 +837,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>506.9</v>
+        <v>519.5</v>
       </c>
       <c r="G8" s="2">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="I8" s="4">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -860,7 +860,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>18.7</v>
+        <v>18.77</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -869,16 +869,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>257.2</v>
+        <v>263.7</v>
       </c>
       <c r="G9" s="2">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="H9" s="3">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="I9" s="4">
-        <v>85.0</v>
+        <v>84.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -892,25 +892,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>65.21</v>
+        <v>63.7</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>37.4</v>
+        <v>37.52</v>
       </c>
       <c r="F10" s="2">
-        <v>522.1</v>
+        <v>460.1</v>
       </c>
       <c r="G10" s="2">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H10" s="3">
-        <v>1.13</v>
+        <v>0.94</v>
       </c>
       <c r="I10" s="4">
-        <v>78.0</v>
+        <v>57.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -924,25 +924,25 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="D11" s="3">
-        <v>18.95</v>
+        <v>19.11</v>
       </c>
       <c r="E11" s="3">
-        <v>13.33</v>
+        <v>13.62</v>
       </c>
       <c r="F11" s="2">
-        <v>124.2</v>
+        <v>125.2</v>
       </c>
       <c r="G11" s="2">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="H11" s="3">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
@@ -959,7 +959,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>20.68</v>
+        <v>23.38</v>
       </c>
       <c r="D12" s="3">
         <v>24.37</v>
@@ -968,16 +968,16 @@
         <v>14.51</v>
       </c>
       <c r="F12" s="2">
-        <v>146.0</v>
+        <v>168.5</v>
       </c>
       <c r="G12" s="2">
-        <v>9.3</v>
+        <v>10.7</v>
       </c>
       <c r="H12" s="3">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="I12" s="4">
-        <v>46.0</v>
+        <v>70.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -991,25 +991,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>15.73</v>
+        <v>17.17</v>
       </c>
       <c r="D13" s="3">
         <v>20.93</v>
       </c>
       <c r="E13" s="3">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="F13" s="2">
-        <v>1161.9</v>
+        <v>1348.7</v>
       </c>
       <c r="G13" s="2">
-        <v>45.2</v>
+        <v>52.4</v>
       </c>
       <c r="H13" s="3">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="I13" s="4">
-        <v>80.0</v>
+        <v>88.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -1026,25 +1026,25 @@
         <v>52</v>
       </c>
       <c r="C14" s="3">
-        <v>24.6</v>
+        <v>25.93</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>17.29</v>
+        <v>17.93</v>
       </c>
       <c r="F14" s="2">
-        <v>582.2</v>
+        <v>637.1</v>
       </c>
       <c r="G14" s="2">
-        <v>23.0</v>
+        <v>25.2</v>
       </c>
       <c r="H14" s="3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I14" s="4">
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>53</v>
@@ -1058,7 +1058,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="3">
-        <v>10.43</v>
+        <v>10.82</v>
       </c>
       <c r="D15" s="3">
         <v>19.77</v>
@@ -1067,16 +1067,16 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>97.5</v>
+        <v>107.7</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="3">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="I15" s="4">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>56</v>
@@ -1093,7 +1093,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="3">
-        <v>17.28</v>
+        <v>17.58</v>
       </c>
       <c r="D16" s="3">
         <v>19.56</v>
@@ -1102,16 +1102,16 @@
         <v>7.22</v>
       </c>
       <c r="F16" s="2">
-        <v>547.2</v>
+        <v>560.0</v>
       </c>
       <c r="G16" s="2">
-        <v>24.9</v>
+        <v>25.5</v>
       </c>
       <c r="H16" s="3">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="I16" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>60</v>
@@ -1125,25 +1125,25 @@
         <v>62</v>
       </c>
       <c r="C17" s="3">
-        <v>48.99</v>
+        <v>50.6</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
       </c>
       <c r="E17" s="3">
-        <v>35.31</v>
+        <v>35.43</v>
       </c>
       <c r="F17" s="2">
-        <v>373.0</v>
+        <v>382.5</v>
       </c>
       <c r="G17" s="2">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="H17" s="3">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="I17" s="4">
-        <v>40.0</v>
+        <v>49.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
@@ -1160,7 +1160,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="3">
-        <v>42.51</v>
+        <v>39.3</v>
       </c>
       <c r="D18" s="3">
         <v>44.12</v>
@@ -1169,16 +1169,16 @@
         <v>22.72</v>
       </c>
       <c r="F18" s="2">
-        <v>533.7</v>
+        <v>519.7</v>
       </c>
       <c r="G18" s="2">
-        <v>24.6</v>
+        <v>24.0</v>
       </c>
       <c r="H18" s="3">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="I18" s="4">
-        <v>83.0</v>
+        <v>78.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>66</v>
@@ -1192,7 +1192,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="3">
-        <v>44.23</v>
+        <v>42.38</v>
       </c>
       <c r="D19" s="3">
         <v>87.36</v>
@@ -1201,16 +1201,16 @@
         <v>28.64</v>
       </c>
       <c r="F19" s="2">
-        <v>114.7</v>
+        <v>113.3</v>
       </c>
       <c r="G19" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H19" s="3">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I19" s="4">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>69</v>
@@ -1224,25 +1224,25 @@
         <v>71</v>
       </c>
       <c r="C20" s="3">
-        <v>8.85</v>
+        <v>8.5</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>4.23</v>
+        <v>4.28</v>
       </c>
       <c r="F20" s="2">
-        <v>534.5</v>
+        <v>502.6</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="3">
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
       <c r="I20" s="4">
-        <v>84.0</v>
+        <v>79.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>72</v>
@@ -1259,7 +1259,7 @@
         <v>75</v>
       </c>
       <c r="C21" s="3">
-        <v>8.02</v>
+        <v>7.57</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1268,16 +1268,16 @@
         <v>4.27</v>
       </c>
       <c r="F21" s="2">
-        <v>541.6</v>
+        <v>502.4</v>
       </c>
       <c r="G21" s="2">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="H21" s="3">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="I21" s="4">
-        <v>74.0</v>
+        <v>55.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>76</v>
@@ -1291,22 +1291,22 @@
         <v>78</v>
       </c>
       <c r="C22" s="3">
-        <v>31.15</v>
+        <v>32.56</v>
       </c>
       <c r="D22" s="3">
-        <v>31.92</v>
+        <v>35.01</v>
       </c>
       <c r="E22" s="3">
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>416.9</v>
+        <v>458.1</v>
       </c>
       <c r="G22" s="2">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="H22" s="3">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="I22" s="4">
         <v>90.0</v>
@@ -1323,7 +1323,7 @@
         <v>81</v>
       </c>
       <c r="C23" s="3">
-        <v>28.8</v>
+        <v>28.24</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1332,16 +1332,16 @@
         <v>18.2</v>
       </c>
       <c r="F23" s="2">
-        <v>70.0</v>
+        <v>72.8</v>
       </c>
       <c r="G23" s="2">
         <v>0.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="I23" s="4">
-        <v>55.0</v>
+        <v>53.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1358,25 +1358,25 @@
         <v>84</v>
       </c>
       <c r="C24" s="3">
-        <v>35.75</v>
+        <v>38.66</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
       </c>
       <c r="E24" s="3">
-        <v>20.31</v>
+        <v>20.52</v>
       </c>
       <c r="F24" s="2">
-        <v>269.8</v>
+        <v>291.3</v>
       </c>
       <c r="G24" s="2">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
       <c r="H24" s="3">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="I24" s="4">
-        <v>70.0</v>
+        <v>76.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>85</v>
@@ -1390,16 +1390,16 @@
         <v>87</v>
       </c>
       <c r="C25" s="3">
-        <v>9.58</v>
+        <v>9.48</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
       </c>
       <c r="E25" s="3">
-        <v>9.9</v>
+        <v>9.21</v>
       </c>
       <c r="F25" s="2">
-        <v>64.3</v>
+        <v>61.3</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>29</v>
@@ -1408,7 +1408,7 @@
         <v>0.41</v>
       </c>
       <c r="I25" s="4">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>88</v>
@@ -1425,7 +1425,7 @@
         <v>91</v>
       </c>
       <c r="C26" s="3">
-        <v>11.69</v>
+        <v>11.96</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1434,16 +1434,16 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>97.1</v>
+        <v>102.9</v>
       </c>
       <c r="G26" s="2">
-        <v>12.2</v>
+        <v>13.0</v>
       </c>
       <c r="H26" s="3">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="I26" s="4">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>92</v>
@@ -1457,25 +1457,25 @@
         <v>94</v>
       </c>
       <c r="C27" s="3">
-        <v>9.92</v>
+        <v>9.18</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
       </c>
       <c r="E27" s="3">
-        <v>5.22</v>
+        <v>5.7</v>
       </c>
       <c r="F27" s="2">
-        <v>380.0</v>
+        <v>345.8</v>
       </c>
       <c r="G27" s="2">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H27" s="3">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="I27" s="4">
-        <v>86.0</v>
+        <v>80.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1492,7 +1492,7 @@
         <v>97</v>
       </c>
       <c r="C28" s="3">
-        <v>21.04</v>
+        <v>21.53</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1501,16 +1501,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>126.8</v>
+        <v>130.6</v>
       </c>
       <c r="G28" s="2">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="H28" s="3">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="I28" s="4">
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1521,22 +1521,22 @@
         <v>99</v>
       </c>
       <c r="C29" s="3">
-        <v>113.76</v>
+        <v>125.31</v>
       </c>
       <c r="D29" s="3">
-        <v>108.0</v>
+        <v>131.68</v>
       </c>
       <c r="E29" s="3">
         <v>24.89</v>
       </c>
       <c r="F29" s="2">
-        <v>1383.8</v>
+        <v>1666.0</v>
       </c>
       <c r="G29" s="2">
-        <v>233.3</v>
+        <v>280.8</v>
       </c>
       <c r="H29" s="3">
-        <v>4.14</v>
+        <v>4.98</v>
       </c>
       <c r="I29" s="4">
         <v>99.0</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="4k4p3memRWjEB++8Jo/kd8JSWjGwzeNeJ6Jx7sg++SI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="p0imAky0hVA1VGx883oq4tYS3pVNRYYUwx7+X43Bcqs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
   <si>
     <t>Company</t>
   </si>
@@ -96,6 +96,9 @@
     <t>CVLG</t>
   </si>
   <si>
+    <t>Approaching size limit Approaching value limit</t>
+  </si>
+  <si>
     <t>News Archive for CVLG</t>
   </si>
   <si>
@@ -165,7 +168,7 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Exceeds size limit Approaching value limit</t>
+    <t>Exceeds size limit</t>
   </si>
   <si>
     <t>News Archive for GILT</t>
@@ -198,6 +201,9 @@
     <t>MG</t>
   </si>
   <si>
+    <t>Approaching value limit</t>
+  </si>
+  <si>
     <t>News Archive for MG</t>
   </si>
   <si>
@@ -225,7 +231,7 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>News Archive for NCSM</t>
+    <t>(6/1/26) NCS Multistage Holdings, Inc. (NCSM)</t>
   </si>
   <si>
     <t>Oil States International, Inc.</t>
@@ -630,7 +636,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.82</v>
+        <v>5.13</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -639,16 +645,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>58.5</v>
+        <v>53.7</v>
       </c>
       <c r="G2" s="2">
-        <v>17.4</v>
+        <v>15.4</v>
       </c>
       <c r="H2" s="3">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>73.0</v>
+        <v>62.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -665,25 +671,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.63</v>
+        <v>4.37</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>2.71</v>
+        <v>3.11</v>
       </c>
       <c r="F3" s="2">
-        <v>193.2</v>
+        <v>191.6</v>
       </c>
       <c r="G3" s="2">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="H3" s="3">
         <v>0.46</v>
       </c>
       <c r="I3" s="4">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -697,7 +703,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -706,16 +712,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>18.0</v>
+        <v>21.7</v>
       </c>
       <c r="G4" s="2">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="H4" s="3">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>37.0</v>
+        <v>67.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -729,25 +735,25 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>23.69</v>
+        <v>23.08</v>
       </c>
       <c r="D5" s="3">
         <v>28.69</v>
       </c>
       <c r="E5" s="3">
-        <v>15.81</v>
+        <v>15.89</v>
       </c>
       <c r="F5" s="2">
-        <v>209.7</v>
+        <v>202.7</v>
       </c>
       <c r="G5" s="2">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
       <c r="H5" s="3">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="I5" s="4">
-        <v>77.0</v>
+        <v>75.0</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -761,39 +767,42 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>39.7</v>
+        <v>43.52</v>
       </c>
       <c r="D6" s="3">
-        <v>40.0</v>
+        <v>43.62</v>
       </c>
       <c r="E6" s="3">
         <v>18.0</v>
       </c>
       <c r="F6" s="2">
-        <v>995.5</v>
+        <v>1087.9</v>
       </c>
       <c r="G6" s="2">
-        <v>500.6</v>
+        <v>547.1</v>
       </c>
       <c r="H6" s="3">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="I6" s="4">
-        <v>95.0</v>
+        <v>96.0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>6.81</v>
+        <v>6.74</v>
       </c>
       <c r="D7" s="3">
         <v>9.2</v>
@@ -802,33 +811,33 @@
         <v>4.69</v>
       </c>
       <c r="F7" s="2">
-        <v>148.4</v>
+        <v>138.2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="I7" s="4">
-        <v>72.0</v>
+        <v>64.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>20.46</v>
+        <v>20.59</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -837,7 +846,7 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>519.5</v>
+        <v>519.0</v>
       </c>
       <c r="G8" s="2">
         <v>12.4</v>
@@ -846,21 +855,21 @@
         <v>1.68</v>
       </c>
       <c r="I8" s="4">
-        <v>69.0</v>
+        <v>66.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3">
-        <v>18.77</v>
+        <v>17.9</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -869,71 +878,71 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>263.7</v>
+        <v>252.8</v>
       </c>
       <c r="G9" s="2">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="I9" s="4">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3">
-        <v>63.7</v>
+        <v>66.43</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>37.52</v>
+        <v>39.27</v>
       </c>
       <c r="F10" s="2">
-        <v>460.1</v>
+        <v>465.7</v>
       </c>
       <c r="G10" s="2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="3">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="I10" s="4">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="3">
-        <v>19.1</v>
+        <v>19.09</v>
       </c>
       <c r="D11" s="3">
-        <v>19.11</v>
+        <v>19.16</v>
       </c>
       <c r="E11" s="3">
         <v>13.62</v>
       </c>
       <c r="F11" s="2">
-        <v>125.2</v>
+        <v>125.1</v>
       </c>
       <c r="G11" s="2">
         <v>19.6</v>
@@ -942,123 +951,123 @@
         <v>0.7</v>
       </c>
       <c r="I11" s="4">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3">
-        <v>23.38</v>
+        <v>24.4</v>
       </c>
       <c r="D12" s="3">
-        <v>24.37</v>
+        <v>24.69</v>
       </c>
       <c r="E12" s="3">
         <v>14.51</v>
       </c>
       <c r="F12" s="2">
-        <v>168.5</v>
+        <v>173.3</v>
       </c>
       <c r="G12" s="2">
-        <v>10.7</v>
+        <v>11.0</v>
       </c>
       <c r="H12" s="3">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="I12" s="4">
-        <v>70.0</v>
+        <v>77.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="3">
-        <v>17.17</v>
+        <v>14.52</v>
       </c>
       <c r="D13" s="3">
         <v>20.93</v>
       </c>
       <c r="E13" s="3">
-        <v>5.46</v>
+        <v>5.8</v>
       </c>
       <c r="F13" s="2">
-        <v>1348.7</v>
+        <v>1208.0</v>
       </c>
       <c r="G13" s="2">
-        <v>52.4</v>
+        <v>47.0</v>
       </c>
       <c r="H13" s="3">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="I13" s="4">
-        <v>88.0</v>
+        <v>80.0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="3">
-        <v>25.93</v>
+        <v>24.43</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>17.93</v>
+        <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>637.1</v>
+        <v>633.7</v>
       </c>
       <c r="G14" s="2">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="H14" s="3">
         <v>1.1</v>
       </c>
       <c r="I14" s="4">
-        <v>37.0</v>
+        <v>36.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3">
-        <v>10.82</v>
+        <v>9.28</v>
       </c>
       <c r="D15" s="3">
         <v>19.77</v>
@@ -1067,65 +1076,68 @@
         <v>7.15</v>
       </c>
       <c r="F15" s="2">
-        <v>107.7</v>
+        <v>98.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H15" s="3">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="I15" s="4">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="3">
-        <v>17.58</v>
+        <v>17.61</v>
       </c>
       <c r="D16" s="3">
         <v>19.56</v>
       </c>
       <c r="E16" s="3">
-        <v>7.22</v>
+        <v>7.38</v>
       </c>
       <c r="F16" s="2">
-        <v>560.0</v>
+        <v>588.0</v>
       </c>
       <c r="G16" s="2">
-        <v>25.5</v>
+        <v>26.8</v>
       </c>
       <c r="H16" s="3">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I16" s="4">
-        <v>86.0</v>
+        <v>89.0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3">
-        <v>50.6</v>
+        <v>53.21</v>
       </c>
       <c r="D17" s="3">
         <v>59.42</v>
@@ -1134,33 +1146,33 @@
         <v>35.43</v>
       </c>
       <c r="F17" s="2">
-        <v>382.5</v>
+        <v>392.2</v>
       </c>
       <c r="G17" s="2">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="H17" s="3">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="I17" s="4">
-        <v>49.0</v>
+        <v>69.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3">
-        <v>39.3</v>
+        <v>39.87</v>
       </c>
       <c r="D18" s="3">
         <v>44.12</v>
@@ -1169,129 +1181,129 @@
         <v>22.72</v>
       </c>
       <c r="F18" s="2">
-        <v>519.7</v>
+        <v>521.1</v>
       </c>
       <c r="G18" s="2">
         <v>24.0</v>
       </c>
       <c r="H18" s="3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I18" s="4">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" s="3">
-        <v>42.38</v>
+        <v>52.0</v>
       </c>
       <c r="D19" s="3">
         <v>87.36</v>
       </c>
       <c r="E19" s="3">
-        <v>28.64</v>
+        <v>28.73</v>
       </c>
       <c r="F19" s="2">
-        <v>113.3</v>
+        <v>147.0</v>
       </c>
       <c r="G19" s="2">
-        <v>6.1</v>
+        <v>7.9</v>
       </c>
       <c r="H19" s="3">
-        <v>0.91</v>
+        <v>1.18</v>
       </c>
       <c r="I19" s="4">
-        <v>70.0</v>
+        <v>87.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C20" s="3">
-        <v>8.5</v>
+        <v>8.12</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>4.28</v>
+        <v>4.47</v>
       </c>
       <c r="F20" s="2">
-        <v>502.6</v>
+        <v>523.1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H20" s="3">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="I20" s="4">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C21" s="3">
-        <v>7.57</v>
+        <v>7.21</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
       </c>
       <c r="E21" s="3">
-        <v>4.27</v>
+        <v>4.46</v>
       </c>
       <c r="F21" s="2">
-        <v>502.4</v>
+        <v>475.6</v>
       </c>
       <c r="G21" s="2">
-        <v>14.3</v>
+        <v>13.5</v>
       </c>
       <c r="H21" s="3">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="I21" s="4">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C22" s="3">
-        <v>32.56</v>
+        <v>32.01</v>
       </c>
       <c r="D22" s="3">
         <v>35.01</v>
@@ -1300,30 +1312,30 @@
         <v>15.52</v>
       </c>
       <c r="F22" s="2">
-        <v>458.1</v>
+        <v>455.6</v>
       </c>
       <c r="G22" s="2">
-        <v>19.1</v>
+        <v>19.0</v>
       </c>
       <c r="H22" s="3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="I22" s="4">
-        <v>90.0</v>
+        <v>89.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C23" s="3">
-        <v>28.24</v>
+        <v>27.28</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1332,33 +1344,33 @@
         <v>18.2</v>
       </c>
       <c r="F23" s="2">
-        <v>72.8</v>
+        <v>68.6</v>
       </c>
       <c r="G23" s="2">
         <v>0.7</v>
       </c>
       <c r="H23" s="3">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="I23" s="4">
-        <v>53.0</v>
+        <v>50.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C24" s="3">
-        <v>38.66</v>
+        <v>37.45</v>
       </c>
       <c r="D24" s="3">
         <v>48.7</v>
@@ -1367,65 +1379,65 @@
         <v>20.52</v>
       </c>
       <c r="F24" s="2">
-        <v>291.3</v>
+        <v>281.1</v>
       </c>
       <c r="G24" s="2">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="H24" s="3">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="I24" s="4">
-        <v>76.0</v>
+        <v>74.0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C25" s="3">
-        <v>9.48</v>
+        <v>9.05</v>
       </c>
       <c r="D25" s="3">
         <v>14.27</v>
       </c>
       <c r="E25" s="3">
-        <v>9.21</v>
+        <v>9.18</v>
       </c>
       <c r="F25" s="2">
-        <v>61.3</v>
+        <v>58.5</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H25" s="3">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="I25" s="4">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C26" s="3">
-        <v>11.96</v>
+        <v>12.68</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1434,45 +1446,45 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>102.9</v>
+        <v>108.4</v>
       </c>
       <c r="G26" s="2">
+        <v>13.7</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1.37</v>
+      </c>
+      <c r="I26" s="4">
         <v>13.0</v>
       </c>
-      <c r="H26" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="I26" s="4">
-        <v>16.0</v>
-      </c>
       <c r="K26" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C27" s="3">
-        <v>9.18</v>
+        <v>9.62</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
       </c>
       <c r="E27" s="3">
-        <v>5.7</v>
+        <v>6.06</v>
       </c>
       <c r="F27" s="2">
-        <v>345.8</v>
+        <v>341.4</v>
       </c>
       <c r="G27" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H27" s="3">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I27" s="4">
         <v>80.0</v>
@@ -1481,18 +1493,18 @@
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C28" s="3">
-        <v>21.53</v>
+        <v>21.5</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1501,7 +1513,7 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>130.6</v>
+        <v>130.3</v>
       </c>
       <c r="G28" s="2">
         <v>27.9</v>
@@ -1510,42 +1522,42 @@
         <v>1.05</v>
       </c>
       <c r="I28" s="4">
-        <v>59.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C29" s="3">
-        <v>125.31</v>
+        <v>117.51</v>
       </c>
       <c r="D29" s="3">
-        <v>131.68</v>
+        <v>136.21</v>
       </c>
       <c r="E29" s="3">
-        <v>24.89</v>
+        <v>25.49</v>
       </c>
       <c r="F29" s="2">
-        <v>1666.0</v>
+        <v>1705.7</v>
       </c>
       <c r="G29" s="2">
-        <v>280.8</v>
+        <v>287.5</v>
       </c>
       <c r="H29" s="3">
-        <v>4.98</v>
+        <v>5.1</v>
       </c>
       <c r="I29" s="4">
         <v>99.0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="p0imAky0hVA1VGx883oq4tYS3pVNRYYUwx7+X43Bcqs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="WnFPcIaZYKFWNc059y97d4FQvOaX/d109BOftEvYG30="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="95">
   <si>
     <t>Company</t>
   </si>
@@ -81,6 +81,15 @@
     <t>News Archive for CTRM</t>
   </si>
   <si>
+    <t>Columbus McKinnon Corporation *</t>
+  </si>
+  <si>
+    <t>CMCO*</t>
+  </si>
+  <si>
+    <t>nmf</t>
+  </si>
+  <si>
     <t>Core Molding Technologies, Inc.</t>
   </si>
   <si>
@@ -102,21 +111,6 @@
     <t>News Archive for CVLG</t>
   </si>
   <si>
-    <t>DMC Global Inc.</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>nmf</t>
-  </si>
-  <si>
-    <t>Earnings probation 2025q4</t>
-  </si>
-  <si>
-    <t>News Archive for BOOM</t>
-  </si>
-  <si>
     <t>Ennis, Inc.</t>
   </si>
   <si>
@@ -144,22 +138,13 @@
     <t>News Archive for ESEA</t>
   </si>
   <si>
-    <t>FONAR Corporation</t>
-  </si>
-  <si>
-    <t>FONR</t>
-  </si>
-  <si>
-    <t>News Archive for FONR</t>
-  </si>
-  <si>
     <t>Friedman Industries, Incorporated</t>
   </si>
   <si>
     <t>FRD</t>
   </si>
   <si>
-    <t>News Archive for FRD</t>
+    <t>(6/11/26) Friedman Industries, Incorporated (FRD)</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
@@ -168,12 +153,18 @@
     <t>GILT</t>
   </si>
   <si>
-    <t>Exceeds size limit</t>
+    <t>Approaching size limit</t>
   </si>
   <si>
     <t>News Archive for GILT</t>
   </si>
   <si>
+    <t>Hudson Technologies, Inc. *</t>
+  </si>
+  <si>
+    <t>HDSN*</t>
+  </si>
+  <si>
     <t>Kimball Electronics, Inc.</t>
   </si>
   <si>
@@ -183,16 +174,16 @@
     <t>News Archive for KE</t>
   </si>
   <si>
-    <t>Lakeland Industries, Inc.</t>
-  </si>
-  <si>
-    <t>LAKE</t>
-  </si>
-  <si>
-    <t>Earnings probation 2025Q3</t>
-  </si>
-  <si>
-    <t>News Archive for LAKE</t>
+    <t>Kolibri Global Energy Inc. *</t>
+  </si>
+  <si>
+    <t>KGEI*</t>
+  </si>
+  <si>
+    <t>Mastech Digital, Inc. *</t>
+  </si>
+  <si>
+    <t>MHH*</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -231,7 +222,7 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>(6/1/26) NCS Multistage Holdings, Inc. (NCSM)</t>
+    <t>News Archive for NCSM</t>
   </si>
   <si>
     <t>Oil States International, Inc.</t>
@@ -282,18 +273,6 @@
     <t>News Archive for RCKY</t>
   </si>
   <si>
-    <t>Saga Communications, Inc.</t>
-  </si>
-  <si>
-    <t>SGA</t>
-  </si>
-  <si>
-    <t>Earnings probation 2025Q4</t>
-  </si>
-  <si>
-    <t>News Archive for SGA</t>
-  </si>
-  <si>
     <t>Smith Douglas Homes Corp.</t>
   </si>
   <si>
@@ -318,16 +297,10 @@
     <t>EML</t>
   </si>
   <si>
-    <t>Vishay Precision Group, Inc.</t>
-  </si>
-  <si>
-    <t>VPG</t>
-  </si>
-  <si>
-    <t>Exceeds size limit Exceeds value limit</t>
-  </si>
-  <si>
-    <t>News Archive for VPG</t>
+    <t>USANA Health Sciences, Inc. *</t>
+  </si>
+  <si>
+    <t>USNA*</t>
   </si>
 </sst>
 </file>
@@ -636,7 +609,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.13</v>
+        <v>5.35</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -645,16 +618,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>53.7</v>
+        <v>54.7</v>
       </c>
       <c r="G2" s="2">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="H2" s="3">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I2" s="4">
-        <v>62.0</v>
+        <v>69.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -671,7 +644,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.37</v>
+        <v>4.34</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -680,16 +653,16 @@
         <v>3.11</v>
       </c>
       <c r="F3" s="2">
-        <v>191.6</v>
+        <v>179.2</v>
       </c>
       <c r="G3" s="2">
-        <v>20.2</v>
+        <v>18.9</v>
       </c>
       <c r="H3" s="3">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="I3" s="4">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -703,7 +676,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -712,16 +685,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>21.7</v>
+        <v>21.1</v>
       </c>
       <c r="G4" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>67.0</v>
+        <v>37.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -735,28 +708,25 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>23.08</v>
+        <v>13.83</v>
       </c>
       <c r="D5" s="3">
-        <v>28.69</v>
+        <v>24.4</v>
       </c>
       <c r="E5" s="3">
-        <v>15.89</v>
+        <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>202.7</v>
-      </c>
-      <c r="G5" s="2">
-        <v>21.3</v>
+        <v>394.2</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>1.23</v>
+        <v>0.6</v>
       </c>
       <c r="I5" s="4">
-        <v>75.0</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>23</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="6">
@@ -767,77 +737,74 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>43.52</v>
+        <v>24.64</v>
       </c>
       <c r="D6" s="3">
-        <v>43.62</v>
+        <v>28.69</v>
       </c>
       <c r="E6" s="3">
-        <v>18.0</v>
+        <v>16.12</v>
       </c>
       <c r="F6" s="2">
-        <v>1087.9</v>
+        <v>218.5</v>
       </c>
       <c r="G6" s="2">
-        <v>547.1</v>
+        <v>22.2</v>
       </c>
       <c r="H6" s="3">
-        <v>2.66</v>
+        <v>1.28</v>
       </c>
       <c r="I6" s="4">
-        <v>96.0</v>
-      </c>
-      <c r="J6" s="2" t="s">
+        <v>77.0</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3">
+        <v>45.45</v>
+      </c>
+      <c r="D7" s="3">
+        <v>47.08</v>
+      </c>
+      <c r="E7" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1144.0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>575.3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="I7" s="4">
+        <v>96.0</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3">
-        <v>6.74</v>
-      </c>
-      <c r="D7" s="3">
-        <v>9.2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>4.69</v>
-      </c>
-      <c r="F7" s="2">
-        <v>138.2</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.59</v>
-      </c>
-      <c r="I7" s="4">
-        <v>64.0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>20.59</v>
+        <v>20.75</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -846,30 +813,30 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>519.0</v>
+        <v>524.8</v>
       </c>
       <c r="G8" s="2">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I8" s="4">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>17.9</v>
+        <v>18.63</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -878,164 +845,158 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>252.8</v>
+        <v>257.2</v>
       </c>
       <c r="G9" s="2">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="H9" s="3">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="I9" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>66.43</v>
+        <v>71.52</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>39.27</v>
+        <v>42.47</v>
       </c>
       <c r="F10" s="2">
-        <v>465.7</v>
+        <v>504.6</v>
       </c>
       <c r="G10" s="2">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H10" s="3">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="I10" s="4">
-        <v>55.0</v>
+        <v>73.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3">
+        <v>34.72</v>
+      </c>
+      <c r="D11" s="3">
+        <v>36.26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>14.51</v>
+      </c>
+      <c r="F11" s="2">
+        <v>246.8</v>
+      </c>
+      <c r="G11" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1.63</v>
+      </c>
+      <c r="I11" s="4">
+        <v>95.0</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="3">
-        <v>19.09</v>
-      </c>
-      <c r="D11" s="3">
-        <v>19.16</v>
-      </c>
-      <c r="E11" s="3">
-        <v>13.62</v>
-      </c>
-      <c r="F11" s="2">
-        <v>125.1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>19.6</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="I11" s="4">
-        <v>81.0</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>20.93</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6.07</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1134.7</v>
+      </c>
+      <c r="G12" s="2">
+        <v>44.1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2.21</v>
+      </c>
+      <c r="I12" s="4">
+        <v>73.0</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C12" s="3">
-        <v>24.4</v>
-      </c>
-      <c r="D12" s="3">
-        <v>24.69</v>
-      </c>
-      <c r="E12" s="3">
-        <v>14.51</v>
-      </c>
-      <c r="F12" s="2">
-        <v>173.3</v>
-      </c>
-      <c r="G12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1.22</v>
-      </c>
-      <c r="I12" s="4">
-        <v>77.0</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C13" s="3">
-        <v>14.52</v>
+        <v>5.78</v>
       </c>
       <c r="D13" s="3">
-        <v>20.93</v>
+        <v>10.52</v>
       </c>
       <c r="E13" s="3">
-        <v>5.8</v>
+        <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>1208.0</v>
+        <v>243.2</v>
       </c>
       <c r="G13" s="2">
-        <v>47.0</v>
+        <v>17.8</v>
       </c>
       <c r="H13" s="3">
-        <v>2.36</v>
+        <v>1.02</v>
       </c>
       <c r="I13" s="4">
-        <v>80.0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>51</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>24.43</v>
+        <v>25.86</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1044,400 +1005,388 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>633.7</v>
+        <v>621.9</v>
       </c>
       <c r="G14" s="2">
-        <v>25.1</v>
+        <v>24.6</v>
       </c>
       <c r="H14" s="3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="I14" s="4">
-        <v>36.0</v>
+        <v>30.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>9.28</v>
+        <v>5.36</v>
       </c>
       <c r="D15" s="3">
-        <v>19.77</v>
+        <v>8.27</v>
       </c>
       <c r="E15" s="3">
-        <v>7.15</v>
+        <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>98.0</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>30</v>
+        <v>191.0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>14.1</v>
       </c>
       <c r="H15" s="3">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="I15" s="4">
-        <v>14.0</v>
+        <v>81.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C16" s="3">
-        <v>17.61</v>
+        <v>7.89</v>
       </c>
       <c r="D16" s="3">
-        <v>19.56</v>
+        <v>8.37</v>
       </c>
       <c r="E16" s="3">
-        <v>7.38</v>
+        <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>588.0</v>
+        <v>94.7</v>
       </c>
       <c r="G16" s="2">
-        <v>26.8</v>
+        <v>42.2</v>
       </c>
       <c r="H16" s="3">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="I16" s="4">
-        <v>89.0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>62</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3">
-        <v>53.21</v>
+        <v>18.65</v>
       </c>
       <c r="D17" s="3">
-        <v>59.42</v>
+        <v>19.56</v>
       </c>
       <c r="E17" s="3">
-        <v>35.43</v>
+        <v>7.38</v>
       </c>
       <c r="F17" s="2">
-        <v>392.2</v>
+        <v>593.4</v>
       </c>
       <c r="G17" s="2">
-        <v>18.2</v>
+        <v>27.0</v>
       </c>
       <c r="H17" s="3">
-        <v>0.9</v>
+        <v>2.54</v>
       </c>
       <c r="I17" s="4">
-        <v>69.0</v>
+        <v>89.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C18" s="3">
-        <v>39.87</v>
+        <v>53.33</v>
       </c>
       <c r="D18" s="3">
-        <v>44.12</v>
+        <v>59.42</v>
       </c>
       <c r="E18" s="3">
-        <v>22.72</v>
+        <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>521.1</v>
+        <v>402.1</v>
       </c>
       <c r="G18" s="2">
-        <v>24.0</v>
+        <v>18.6</v>
       </c>
       <c r="H18" s="3">
-        <v>1.86</v>
+        <v>0.92</v>
       </c>
       <c r="I18" s="4">
-        <v>80.0</v>
+        <v>61.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3">
-        <v>52.0</v>
+        <v>42.37</v>
       </c>
       <c r="D19" s="3">
-        <v>87.36</v>
+        <v>44.12</v>
       </c>
       <c r="E19" s="3">
-        <v>28.73</v>
+        <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>147.0</v>
+        <v>533.8</v>
       </c>
       <c r="G19" s="2">
-        <v>7.9</v>
+        <v>24.6</v>
       </c>
       <c r="H19" s="3">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="I19" s="4">
-        <v>87.0</v>
+        <v>78.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C20" s="3">
-        <v>8.12</v>
+        <v>54.33</v>
       </c>
       <c r="D20" s="3">
-        <v>14.5</v>
+        <v>87.36</v>
       </c>
       <c r="E20" s="3">
-        <v>4.47</v>
+        <v>28.73</v>
       </c>
       <c r="F20" s="2">
-        <v>523.1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>30</v>
+        <v>142.6</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7.7</v>
       </c>
       <c r="H20" s="3">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="I20" s="4">
-        <v>81.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>74</v>
+        <v>80.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C21" s="3">
-        <v>7.21</v>
+        <v>8.5</v>
       </c>
       <c r="D21" s="3">
-        <v>9.39</v>
+        <v>14.5</v>
       </c>
       <c r="E21" s="3">
-        <v>4.46</v>
+        <v>4.75</v>
       </c>
       <c r="F21" s="2">
-        <v>475.6</v>
-      </c>
-      <c r="G21" s="2">
-        <v>13.5</v>
+        <v>511.6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="4">
-        <v>52.0</v>
+        <v>72.0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>32.01</v>
+        <v>7.68</v>
       </c>
       <c r="D22" s="3">
-        <v>35.01</v>
+        <v>9.39</v>
       </c>
       <c r="E22" s="3">
-        <v>15.52</v>
+        <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>455.6</v>
+        <v>502.4</v>
       </c>
       <c r="G22" s="2">
-        <v>19.0</v>
+        <v>14.3</v>
       </c>
       <c r="H22" s="3">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="I22" s="4">
-        <v>89.0</v>
+        <v>54.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>27.28</v>
+        <v>34.73</v>
       </c>
       <c r="D23" s="3">
-        <v>31.5</v>
+        <v>35.53</v>
       </c>
       <c r="E23" s="3">
-        <v>18.2</v>
+        <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>68.6</v>
+        <v>477.7</v>
       </c>
       <c r="G23" s="2">
-        <v>0.7</v>
+        <v>19.9</v>
       </c>
       <c r="H23" s="3">
-        <v>0.36</v>
+        <v>1.26</v>
       </c>
       <c r="I23" s="4">
-        <v>50.0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>89.0</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>37.45</v>
+        <v>27.21</v>
       </c>
       <c r="D24" s="3">
-        <v>48.7</v>
+        <v>31.5</v>
       </c>
       <c r="E24" s="3">
-        <v>20.52</v>
+        <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>281.1</v>
+        <v>68.0</v>
       </c>
       <c r="G24" s="2">
-        <v>15.1</v>
+        <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>1.11</v>
+        <v>0.36</v>
       </c>
       <c r="I24" s="4">
-        <v>74.0</v>
+        <v>38.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>9.05</v>
+        <v>40.1</v>
       </c>
       <c r="D25" s="3">
-        <v>14.27</v>
+        <v>48.7</v>
       </c>
       <c r="E25" s="3">
-        <v>9.18</v>
+        <v>20.52</v>
       </c>
       <c r="F25" s="2">
-        <v>58.5</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>30</v>
+        <v>302.4</v>
+      </c>
+      <c r="G25" s="2">
+        <v>16.3</v>
       </c>
       <c r="H25" s="3">
-        <v>0.39</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>90</v>
+        <v>82.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>12.68</v>
+        <v>13.52</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1446,65 +1395,65 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>108.4</v>
+        <v>112.9</v>
       </c>
       <c r="G26" s="2">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="H26" s="3">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="I26" s="4">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>9.62</v>
+        <v>9.65</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
       </c>
       <c r="E27" s="3">
-        <v>6.06</v>
+        <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>341.4</v>
+        <v>358.8</v>
       </c>
       <c r="G27" s="2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H27" s="3">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="I27" s="4">
-        <v>80.0</v>
+        <v>86.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>21.5</v>
+        <v>21.75</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1513,51 +1462,48 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>130.3</v>
+        <v>131.2</v>
       </c>
       <c r="G28" s="2">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="H28" s="3">
         <v>1.05</v>
       </c>
       <c r="I28" s="4">
-        <v>64.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C29" s="3">
-        <v>117.51</v>
+        <v>19.91</v>
       </c>
       <c r="D29" s="3">
-        <v>136.21</v>
+        <v>38.32</v>
       </c>
       <c r="E29" s="3">
-        <v>25.49</v>
+        <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>1705.7</v>
+        <v>367.6</v>
       </c>
       <c r="G29" s="2">
-        <v>287.5</v>
+        <v>41.2</v>
       </c>
       <c r="H29" s="3">
-        <v>5.1</v>
+        <v>0.68</v>
       </c>
       <c r="I29" s="4">
-        <v>99.0</v>
+        <v>43.0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="WnFPcIaZYKFWNc059y97d4FQvOaX/d109BOftEvYG30="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BGvYMVVdHxEYigDpOSq1taxcmiMSNr5oi7a39w5pE1I="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
   <si>
     <t>Company</t>
   </si>
@@ -144,16 +144,13 @@
     <t>FRD</t>
   </si>
   <si>
-    <t>(6/11/26) Friedman Industries, Incorporated (FRD)</t>
+    <t>News Archive for FRD</t>
   </si>
   <si>
     <t>Gilat Satellite Networks Ltd.</t>
   </si>
   <si>
     <t>GILT</t>
-  </si>
-  <si>
-    <t>Approaching size limit</t>
   </si>
   <si>
     <t>News Archive for GILT</t>
@@ -609,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.35</v>
+        <v>5.43</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -618,16 +615,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>54.7</v>
+        <v>55.5</v>
       </c>
       <c r="G2" s="2">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="H2" s="3">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I2" s="4">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -644,7 +641,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.34</v>
+        <v>4.13</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -653,16 +650,16 @@
         <v>3.11</v>
       </c>
       <c r="F3" s="2">
-        <v>179.2</v>
+        <v>170.5</v>
       </c>
       <c r="G3" s="2">
-        <v>18.9</v>
+        <v>18.0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="I3" s="4">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -676,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -685,16 +682,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="G4" s="2">
-        <v>6.1</v>
+        <v>6.0</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>37.0</v>
+        <v>48.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -708,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>13.83</v>
+        <v>14.69</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -717,16 +714,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>394.2</v>
+        <v>418.7</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="I5" s="4">
-        <v>26.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="6">
@@ -737,25 +734,25 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>24.64</v>
+        <v>23.8</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
       </c>
       <c r="E6" s="3">
-        <v>16.12</v>
+        <v>16.16</v>
       </c>
       <c r="F6" s="2">
-        <v>218.5</v>
+        <v>203.8</v>
       </c>
       <c r="G6" s="2">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="H6" s="3">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="I6" s="4">
-        <v>77.0</v>
+        <v>67.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -769,7 +766,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>45.45</v>
+        <v>42.63</v>
       </c>
       <c r="D7" s="3">
         <v>47.08</v>
@@ -778,16 +775,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>1144.0</v>
+        <v>1073.0</v>
       </c>
       <c r="G7" s="2">
-        <v>575.3</v>
+        <v>539.6</v>
       </c>
       <c r="H7" s="3">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="I7" s="4">
-        <v>96.0</v>
+        <v>94.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>29</v>
@@ -804,7 +801,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>20.75</v>
+        <v>20.33</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -813,16 +810,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>524.8</v>
+        <v>514.2</v>
       </c>
       <c r="G8" s="2">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="H8" s="3">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="I8" s="4">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>33</v>
@@ -836,7 +833,7 @@
         <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>18.63</v>
+        <v>18.65</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -845,16 +842,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>257.2</v>
+        <v>257.5</v>
       </c>
       <c r="G9" s="2">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="H9" s="3">
         <v>1.46</v>
       </c>
       <c r="I9" s="4">
-        <v>88.0</v>
+        <v>85.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
@@ -868,25 +865,25 @@
         <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>71.52</v>
+        <v>68.6</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>42.47</v>
+        <v>43.6</v>
       </c>
       <c r="F10" s="2">
-        <v>504.6</v>
+        <v>484.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H10" s="3">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="I10" s="4">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
@@ -900,25 +897,25 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>34.72</v>
+        <v>37.42</v>
       </c>
       <c r="D11" s="3">
-        <v>36.26</v>
+        <v>37.87</v>
       </c>
       <c r="E11" s="3">
         <v>14.51</v>
       </c>
       <c r="F11" s="2">
-        <v>246.8</v>
+        <v>266.0</v>
       </c>
       <c r="G11" s="2">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="H11" s="3">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="I11" s="4">
-        <v>95.0</v>
+        <v>92.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>42</v>
@@ -932,42 +929,39 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>15.0</v>
+        <v>13.19</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>6.07</v>
+        <v>6.28</v>
       </c>
       <c r="F12" s="2">
-        <v>1134.7</v>
+        <v>997.7</v>
       </c>
       <c r="G12" s="2">
-        <v>44.1</v>
+        <v>38.8</v>
       </c>
       <c r="H12" s="3">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="I12" s="4">
-        <v>73.0</v>
-      </c>
-      <c r="J12" s="2" t="s">
+        <v>64.0</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C13" s="3">
-        <v>5.78</v>
+        <v>5.88</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -976,27 +970,27 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>243.2</v>
+        <v>247.4</v>
       </c>
       <c r="G13" s="2">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="H13" s="3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I13" s="4">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C14" s="3">
-        <v>25.86</v>
+        <v>25.3</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1005,30 +999,30 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>621.9</v>
+        <v>608.4</v>
       </c>
       <c r="G14" s="2">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="H14" s="3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="I14" s="4">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C15" s="3">
-        <v>5.36</v>
+        <v>4.9</v>
       </c>
       <c r="D15" s="3">
         <v>8.27</v>
@@ -1037,16 +1031,16 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>191.0</v>
+        <v>173.8</v>
       </c>
       <c r="G15" s="2">
-        <v>14.1</v>
+        <v>12.9</v>
       </c>
       <c r="H15" s="3">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="I15" s="4">
-        <v>81.0</v>
+        <v>75.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1054,13 +1048,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C16" s="3">
-        <v>7.89</v>
+        <v>7.59</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1069,62 +1063,65 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>94.7</v>
+        <v>91.1</v>
       </c>
       <c r="G16" s="2">
-        <v>42.2</v>
+        <v>40.6</v>
       </c>
       <c r="H16" s="3">
-        <v>1.04</v>
+        <v>1.0</v>
       </c>
       <c r="I16" s="4">
-        <v>59.0</v>
+        <v>54.0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C17" s="3">
-        <v>18.65</v>
+        <v>18.46</v>
       </c>
       <c r="D17" s="3">
         <v>19.56</v>
       </c>
       <c r="E17" s="3">
-        <v>7.38</v>
+        <v>7.47</v>
       </c>
       <c r="F17" s="2">
-        <v>593.4</v>
+        <v>587.3</v>
       </c>
       <c r="G17" s="2">
-        <v>27.0</v>
+        <v>26.8</v>
       </c>
       <c r="H17" s="3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I17" s="4">
-        <v>89.0</v>
+        <v>85.0</v>
       </c>
       <c r="J17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C18" s="3">
-        <v>53.33</v>
+        <v>49.87</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1133,30 +1130,33 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>402.1</v>
+        <v>376.1</v>
       </c>
       <c r="G18" s="2">
-        <v>18.6</v>
+        <v>17.4</v>
       </c>
       <c r="H18" s="3">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="I18" s="4">
-        <v>61.0</v>
+        <v>49.0</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C19" s="3">
-        <v>42.37</v>
+        <v>42.1</v>
       </c>
       <c r="D19" s="3">
         <v>44.12</v>
@@ -1165,30 +1165,30 @@
         <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>533.8</v>
+        <v>530.4</v>
       </c>
       <c r="G19" s="2">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="H19" s="3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I19" s="4">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C20" s="3">
-        <v>54.33</v>
+        <v>49.45</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
@@ -1197,30 +1197,30 @@
         <v>28.73</v>
       </c>
       <c r="F20" s="2">
-        <v>142.6</v>
+        <v>129.7</v>
       </c>
       <c r="G20" s="2">
-        <v>7.7</v>
+        <v>7.0</v>
       </c>
       <c r="H20" s="3">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="I20" s="4">
-        <v>80.0</v>
+        <v>72.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C21" s="3">
-        <v>8.5</v>
+        <v>7.95</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1229,33 +1229,33 @@
         <v>4.75</v>
       </c>
       <c r="F21" s="2">
-        <v>511.6</v>
+        <v>478.5</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="I21" s="4">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C22" s="3">
-        <v>7.68</v>
+        <v>7.38</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1264,62 +1264,62 @@
         <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>502.4</v>
+        <v>480.8</v>
       </c>
       <c r="G22" s="2">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="H22" s="3">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="I22" s="4">
-        <v>54.0</v>
+        <v>48.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C23" s="3">
-        <v>34.73</v>
+        <v>36.0</v>
       </c>
       <c r="D23" s="3">
-        <v>35.53</v>
+        <v>36.61</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>477.7</v>
+        <v>493.3</v>
       </c>
       <c r="G23" s="2">
-        <v>19.9</v>
+        <v>20.6</v>
       </c>
       <c r="H23" s="3">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="I23" s="4">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C24" s="3">
-        <v>27.21</v>
+        <v>27.42</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1328,7 +1328,7 @@
         <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>68.0</v>
+        <v>68.9</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
@@ -1337,24 +1337,24 @@
         <v>0.36</v>
       </c>
       <c r="I24" s="4">
-        <v>38.0</v>
+        <v>46.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="C25" s="3">
-        <v>40.1</v>
+        <v>41.67</v>
       </c>
       <c r="D25" s="3">
         <v>48.7</v>
@@ -1363,30 +1363,30 @@
         <v>20.52</v>
       </c>
       <c r="F25" s="2">
-        <v>302.4</v>
+        <v>315.7</v>
       </c>
       <c r="G25" s="2">
-        <v>16.3</v>
+        <v>17.0</v>
       </c>
       <c r="H25" s="3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="I25" s="4">
         <v>82.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="C26" s="3">
-        <v>13.52</v>
+        <v>13.75</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1395,30 +1395,30 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>112.9</v>
+        <v>114.8</v>
       </c>
       <c r="G26" s="2">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H26" s="3">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="I26" s="4">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="C27" s="3">
-        <v>9.65</v>
+        <v>8.29</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1427,33 +1427,33 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>358.8</v>
+        <v>308.3</v>
       </c>
       <c r="G27" s="2">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="H27" s="3">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="I27" s="4">
-        <v>86.0</v>
+        <v>72.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="C28" s="3">
-        <v>21.75</v>
+        <v>23.68</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1462,27 +1462,27 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>131.2</v>
+        <v>142.8</v>
       </c>
       <c r="G28" s="2">
-        <v>28.1</v>
+        <v>30.6</v>
       </c>
       <c r="H28" s="3">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="I28" s="4">
-        <v>59.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="C29" s="3">
-        <v>19.91</v>
+        <v>18.88</v>
       </c>
       <c r="D29" s="3">
         <v>38.32</v>
@@ -1491,16 +1491,16 @@
         <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>367.6</v>
+        <v>348.6</v>
       </c>
       <c r="G29" s="2">
-        <v>41.2</v>
+        <v>39.1</v>
       </c>
       <c r="H29" s="3">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="I29" s="4">
-        <v>43.0</v>
+        <v>40.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>13</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BGvYMVVdHxEYigDpOSq1taxcmiMSNr5oi7a39w5pE1I="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="AmGD0vsZN9ZX+x3M6VI/9KetVn+XzWn57GPOiSo3xeI="/>
     </ext>
   </extLst>
 </workbook>
@@ -117,7 +117,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>News Archive for EBF</t>
+    <t>(6/22/26) Ennis, Inc. (EBF)</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -606,7 +606,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -615,16 +615,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>55.5</v>
+        <v>52.6</v>
       </c>
       <c r="G2" s="2">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="H2" s="3">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="I2" s="4">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -641,7 +641,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.13</v>
+        <v>3.94</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -650,16 +650,16 @@
         <v>3.11</v>
       </c>
       <c r="F3" s="2">
-        <v>170.5</v>
+        <v>164.3</v>
       </c>
       <c r="G3" s="2">
-        <v>18.0</v>
+        <v>17.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="I3" s="4">
-        <v>36.0</v>
+        <v>31.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -673,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -682,16 +682,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="G4" s="2">
-        <v>6.0</v>
+        <v>5.5</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>48.0</v>
+        <v>31.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>14.69</v>
+        <v>14.47</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -714,16 +714,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>418.7</v>
+        <v>421.3</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I5" s="4">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="6">
@@ -734,25 +734,25 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>23.8</v>
+        <v>23.67</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
       </c>
       <c r="E6" s="3">
-        <v>16.16</v>
+        <v>16.37</v>
       </c>
       <c r="F6" s="2">
-        <v>203.8</v>
+        <v>203.5</v>
       </c>
       <c r="G6" s="2">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="H6" s="3">
         <v>1.24</v>
       </c>
       <c r="I6" s="4">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -766,7 +766,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>42.63</v>
+        <v>45.01</v>
       </c>
       <c r="D7" s="3">
         <v>47.08</v>
@@ -775,16 +775,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>1073.0</v>
+        <v>1103.0</v>
       </c>
       <c r="G7" s="2">
-        <v>539.6</v>
+        <v>554.7</v>
       </c>
       <c r="H7" s="3">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="4">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>29</v>
@@ -801,7 +801,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>20.33</v>
+        <v>21.89</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -810,16 +810,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>514.2</v>
+        <v>535.4</v>
       </c>
       <c r="G8" s="2">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="I8" s="4">
-        <v>63.0</v>
+        <v>68.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>33</v>
@@ -833,7 +833,7 @@
         <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>18.65</v>
+        <v>19.28</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -842,16 +842,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>257.5</v>
+        <v>254.3</v>
       </c>
       <c r="G9" s="2">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="H9" s="3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I9" s="4">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
@@ -865,7 +865,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>68.6</v>
+        <v>66.35</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
@@ -874,16 +874,16 @@
         <v>43.6</v>
       </c>
       <c r="F10" s="2">
-        <v>484.0</v>
+        <v>478.5</v>
       </c>
       <c r="G10" s="2">
         <v>3.6</v>
       </c>
       <c r="H10" s="3">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I10" s="4">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
@@ -897,22 +897,22 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>37.42</v>
+        <v>34.43</v>
       </c>
       <c r="D11" s="3">
-        <v>37.87</v>
+        <v>37.97</v>
       </c>
       <c r="E11" s="3">
         <v>14.51</v>
       </c>
       <c r="F11" s="2">
-        <v>266.0</v>
+        <v>239.6</v>
       </c>
       <c r="G11" s="2">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="H11" s="3">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="I11" s="4">
         <v>92.0</v>
@@ -929,25 +929,25 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>13.19</v>
+        <v>11.81</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>6.28</v>
+        <v>6.8</v>
       </c>
       <c r="F12" s="2">
-        <v>997.7</v>
+        <v>895.6</v>
       </c>
       <c r="G12" s="2">
-        <v>38.8</v>
+        <v>34.8</v>
       </c>
       <c r="H12" s="3">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="I12" s="4">
-        <v>64.0</v>
+        <v>43.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>45</v>
@@ -961,7 +961,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -970,16 +970,19 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>247.4</v>
+        <v>234.3</v>
       </c>
       <c r="G13" s="2">
-        <v>18.1</v>
+        <v>17.2</v>
       </c>
       <c r="H13" s="3">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="I13" s="4">
-        <v>26.0</v>
+        <v>28.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -990,7 +993,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="3">
-        <v>25.3</v>
+        <v>24.5</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -999,13 +1002,13 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>608.4</v>
+        <v>586.4</v>
       </c>
       <c r="G14" s="2">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="H14" s="3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="I14" s="4">
         <v>33.0</v>
@@ -1022,7 +1025,7 @@
         <v>52</v>
       </c>
       <c r="C15" s="3">
-        <v>4.9</v>
+        <v>4.58</v>
       </c>
       <c r="D15" s="3">
         <v>8.27</v>
@@ -1031,13 +1034,13 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>173.8</v>
+        <v>162.2</v>
       </c>
       <c r="G15" s="2">
-        <v>12.9</v>
+        <v>12.0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="I15" s="4">
         <v>75.0</v>
@@ -1054,7 +1057,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="3">
-        <v>7.59</v>
+        <v>7.71</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1063,19 +1066,16 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>91.1</v>
+        <v>93.8</v>
       </c>
       <c r="G16" s="2">
-        <v>40.6</v>
+        <v>41.8</v>
       </c>
       <c r="H16" s="3">
-        <v>1.0</v>
+        <v>1.03</v>
       </c>
       <c r="I16" s="4">
         <v>54.0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1086,25 +1086,25 @@
         <v>56</v>
       </c>
       <c r="C17" s="3">
-        <v>18.46</v>
+        <v>18.82</v>
       </c>
       <c r="D17" s="3">
-        <v>19.56</v>
+        <v>19.64</v>
       </c>
       <c r="E17" s="3">
-        <v>7.47</v>
+        <v>7.74</v>
       </c>
       <c r="F17" s="2">
-        <v>587.3</v>
+        <v>597.5</v>
       </c>
       <c r="G17" s="2">
-        <v>26.8</v>
+        <v>27.2</v>
       </c>
       <c r="H17" s="3">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I17" s="4">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>57</v>
@@ -1121,7 +1121,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="3">
-        <v>49.87</v>
+        <v>51.71</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1130,16 +1130,16 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>376.1</v>
+        <v>389.9</v>
       </c>
       <c r="G18" s="2">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="H18" s="3">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="I18" s="4">
-        <v>49.0</v>
+        <v>55.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
@@ -1156,25 +1156,25 @@
         <v>63</v>
       </c>
       <c r="C19" s="3">
-        <v>42.1</v>
+        <v>43.99</v>
       </c>
       <c r="D19" s="3">
-        <v>44.12</v>
+        <v>44.61</v>
       </c>
       <c r="E19" s="3">
         <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>530.4</v>
+        <v>546.4</v>
       </c>
       <c r="G19" s="2">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="I19" s="4">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>64</v>
@@ -1188,7 +1188,7 @@
         <v>66</v>
       </c>
       <c r="C20" s="3">
-        <v>49.45</v>
+        <v>44.44</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
@@ -1197,16 +1197,16 @@
         <v>28.73</v>
       </c>
       <c r="F20" s="2">
-        <v>129.7</v>
+        <v>119.3</v>
       </c>
       <c r="G20" s="2">
-        <v>7.0</v>
+        <v>6.4</v>
       </c>
       <c r="H20" s="3">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="I20" s="4">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>67</v>
@@ -1220,7 +1220,7 @@
         <v>69</v>
       </c>
       <c r="C21" s="3">
-        <v>7.95</v>
+        <v>8.08</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1238,7 +1238,7 @@
         <v>0.84</v>
       </c>
       <c r="I21" s="4">
-        <v>69.0</v>
+        <v>66.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>70</v>
@@ -1255,7 +1255,7 @@
         <v>73</v>
       </c>
       <c r="C22" s="3">
-        <v>7.38</v>
+        <v>6.82</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1264,16 +1264,16 @@
         <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>480.8</v>
+        <v>455.3</v>
       </c>
       <c r="G22" s="2">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="H22" s="3">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="I22" s="4">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>74</v>
@@ -1287,25 +1287,25 @@
         <v>76</v>
       </c>
       <c r="C23" s="3">
-        <v>36.0</v>
+        <v>39.06</v>
       </c>
       <c r="D23" s="3">
-        <v>36.61</v>
+        <v>38.44</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>493.3</v>
+        <v>526.5</v>
       </c>
       <c r="G23" s="2">
-        <v>20.6</v>
+        <v>22.0</v>
       </c>
       <c r="H23" s="3">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="I23" s="4">
-        <v>90.0</v>
+        <v>94.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>77</v>
@@ -1319,7 +1319,7 @@
         <v>79</v>
       </c>
       <c r="C24" s="3">
-        <v>27.42</v>
+        <v>27.26</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1328,16 +1328,16 @@
         <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>68.9</v>
+        <v>66.2</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="I24" s="4">
-        <v>46.0</v>
+        <v>41.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1354,22 +1354,22 @@
         <v>82</v>
       </c>
       <c r="C25" s="3">
-        <v>41.67</v>
+        <v>41.28</v>
       </c>
       <c r="D25" s="3">
         <v>48.7</v>
       </c>
       <c r="E25" s="3">
-        <v>20.52</v>
+        <v>21.37</v>
       </c>
       <c r="F25" s="2">
-        <v>315.7</v>
+        <v>304.7</v>
       </c>
       <c r="G25" s="2">
-        <v>17.0</v>
+        <v>16.4</v>
       </c>
       <c r="H25" s="3">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="I25" s="4">
         <v>82.0</v>
@@ -1386,7 +1386,7 @@
         <v>85</v>
       </c>
       <c r="C26" s="3">
-        <v>13.75</v>
+        <v>14.6</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1395,16 +1395,16 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>114.8</v>
+        <v>119.2</v>
       </c>
       <c r="G26" s="2">
-        <v>14.5</v>
+        <v>15.0</v>
       </c>
       <c r="H26" s="3">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="I26" s="4">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>86</v>
@@ -1418,7 +1418,7 @@
         <v>88</v>
       </c>
       <c r="C27" s="3">
-        <v>8.29</v>
+        <v>8.16</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1427,13 +1427,13 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>308.3</v>
+        <v>301.2</v>
       </c>
       <c r="G27" s="2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H27" s="3">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I27" s="4">
         <v>72.0</v>
@@ -1453,7 +1453,7 @@
         <v>91</v>
       </c>
       <c r="C28" s="3">
-        <v>23.68</v>
+        <v>24.34</v>
       </c>
       <c r="D28" s="3">
         <v>26.77</v>
@@ -1462,16 +1462,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>142.8</v>
+        <v>145.3</v>
       </c>
       <c r="G28" s="2">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="H28" s="3">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I28" s="4">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1482,7 +1482,7 @@
         <v>93</v>
       </c>
       <c r="C29" s="3">
-        <v>18.88</v>
+        <v>20.7</v>
       </c>
       <c r="D29" s="3">
         <v>38.32</v>
@@ -1491,16 +1491,16 @@
         <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>348.6</v>
+        <v>363.4</v>
       </c>
       <c r="G29" s="2">
-        <v>39.1</v>
+        <v>40.7</v>
       </c>
       <c r="H29" s="3">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="I29" s="4">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>13</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="AmGD0vsZN9ZX+x3M6VI/9KetVn+XzWn57GPOiSo3xeI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Ngt6HdEncOZg5LldaFU3VrwXc4LRRyKFVgdKI+1Ag5E="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="93">
   <si>
     <t>Company</t>
   </si>
@@ -117,7 +117,7 @@
     <t>EBF</t>
   </si>
   <si>
-    <t>(6/22/26) Ennis, Inc. (EBF)</t>
+    <t>News Archive for EBF</t>
   </si>
   <si>
     <t>Escalade, Incorporated</t>
@@ -187,9 +187,6 @@
   </si>
   <si>
     <t>MG</t>
-  </si>
-  <si>
-    <t>Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for MG</t>
@@ -606,7 +603,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -615,16 +612,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>52.6</v>
+        <v>56.2</v>
       </c>
       <c r="G2" s="2">
-        <v>15.1</v>
+        <v>16.1</v>
       </c>
       <c r="H2" s="3">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="I2" s="4">
-        <v>69.0</v>
+        <v>75.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -641,25 +638,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.94</v>
+        <v>4.0</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="F3" s="2">
-        <v>164.3</v>
+        <v>165.1</v>
       </c>
       <c r="G3" s="2">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="H3" s="3">
         <v>0.39</v>
       </c>
       <c r="I3" s="4">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -673,7 +670,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -682,16 +679,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>19.2</v>
+        <v>21.7</v>
       </c>
       <c r="G4" s="2">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>31.0</v>
+        <v>56.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -705,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>14.47</v>
+        <v>13.55</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -714,16 +711,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>421.3</v>
+        <v>386.5</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="I5" s="4">
-        <v>32.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="6">
@@ -734,7 +731,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>23.67</v>
+        <v>23.45</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -743,16 +740,16 @@
         <v>16.37</v>
       </c>
       <c r="F6" s="2">
-        <v>203.5</v>
+        <v>200.8</v>
       </c>
       <c r="G6" s="2">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H6" s="3">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="I6" s="4">
-        <v>69.0</v>
+        <v>65.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -766,7 +763,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>45.01</v>
+        <v>43.94</v>
       </c>
       <c r="D7" s="3">
         <v>47.08</v>
@@ -775,16 +772,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>1103.0</v>
+        <v>1106.0</v>
       </c>
       <c r="G7" s="2">
-        <v>554.7</v>
+        <v>556.2</v>
       </c>
       <c r="H7" s="3">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="I7" s="4">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>29</v>
@@ -801,7 +798,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>21.89</v>
+        <v>21.49</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -810,16 +807,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>535.4</v>
+        <v>543.7</v>
       </c>
       <c r="G8" s="2">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H8" s="3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I8" s="4">
-        <v>68.0</v>
+        <v>66.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>33</v>
@@ -833,7 +830,7 @@
         <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>19.28</v>
+        <v>19.06</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -842,16 +839,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>254.3</v>
+        <v>263.1</v>
       </c>
       <c r="G9" s="2">
-        <v>16.4</v>
+        <v>17.0</v>
       </c>
       <c r="H9" s="3">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="I9" s="4">
-        <v>87.0</v>
+        <v>85.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
@@ -865,25 +862,25 @@
         <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>66.35</v>
+        <v>66.38</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>43.6</v>
+        <v>46.38</v>
       </c>
       <c r="F10" s="2">
-        <v>478.5</v>
+        <v>468.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="3">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="I10" s="4">
-        <v>76.0</v>
+        <v>70.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
@@ -897,7 +894,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>34.43</v>
+        <v>33.62</v>
       </c>
       <c r="D11" s="3">
         <v>37.97</v>
@@ -906,7 +903,7 @@
         <v>14.51</v>
       </c>
       <c r="F11" s="2">
-        <v>239.6</v>
+        <v>238.7</v>
       </c>
       <c r="G11" s="2">
         <v>12.2</v>
@@ -915,7 +912,7 @@
         <v>1.58</v>
       </c>
       <c r="I11" s="4">
-        <v>92.0</v>
+        <v>91.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>42</v>
@@ -929,22 +926,22 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>11.81</v>
+        <v>12.88</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>6.8</v>
+        <v>7.01</v>
       </c>
       <c r="F12" s="2">
-        <v>895.6</v>
+        <v>972.8</v>
       </c>
       <c r="G12" s="2">
-        <v>34.8</v>
+        <v>37.8</v>
       </c>
       <c r="H12" s="3">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="I12" s="4">
         <v>43.0</v>
@@ -961,7 +958,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>5.56</v>
+        <v>5.99</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -970,19 +967,16 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>234.3</v>
+        <v>252.0</v>
       </c>
       <c r="G13" s="2">
-        <v>17.2</v>
+        <v>18.5</v>
       </c>
       <c r="H13" s="3">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="I13" s="4">
-        <v>28.0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="14">
@@ -993,7 +987,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="3">
-        <v>24.5</v>
+        <v>25.09</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1002,16 +996,16 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>586.4</v>
+        <v>603.4</v>
       </c>
       <c r="G14" s="2">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="H14" s="3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I14" s="4">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>50</v>
@@ -1025,25 +1019,25 @@
         <v>52</v>
       </c>
       <c r="C15" s="3">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="D15" s="3">
-        <v>8.27</v>
+        <v>6.8</v>
       </c>
       <c r="E15" s="3">
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>162.2</v>
+        <v>167.9</v>
       </c>
       <c r="G15" s="2">
-        <v>12.0</v>
+        <v>12.2</v>
       </c>
       <c r="H15" s="3">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="I15" s="4">
-        <v>75.0</v>
+        <v>63.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1057,7 +1051,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="3">
-        <v>7.71</v>
+        <v>7.89</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1066,16 +1060,16 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>93.8</v>
+        <v>94.7</v>
       </c>
       <c r="G16" s="2">
-        <v>41.8</v>
+        <v>42.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I16" s="4">
-        <v>54.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="17">
@@ -1086,7 +1080,7 @@
         <v>56</v>
       </c>
       <c r="C17" s="3">
-        <v>18.82</v>
+        <v>16.69</v>
       </c>
       <c r="D17" s="3">
         <v>19.64</v>
@@ -1095,33 +1089,30 @@
         <v>7.74</v>
       </c>
       <c r="F17" s="2">
-        <v>597.5</v>
+        <v>531.0</v>
       </c>
       <c r="G17" s="2">
-        <v>27.2</v>
+        <v>24.2</v>
       </c>
       <c r="H17" s="3">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="I17" s="4">
-        <v>87.0</v>
-      </c>
-      <c r="J17" s="2" t="s">
+        <v>78.0</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C18" s="3">
-        <v>51.71</v>
+        <v>48.4</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1130,33 +1121,33 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>389.9</v>
+        <v>365.0</v>
       </c>
       <c r="G18" s="2">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="H18" s="3">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="I18" s="4">
-        <v>55.0</v>
+        <v>43.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C19" s="3">
-        <v>43.99</v>
+        <v>39.46</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
@@ -1165,62 +1156,62 @@
         <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>546.4</v>
+        <v>497.1</v>
       </c>
       <c r="G19" s="2">
-        <v>25.2</v>
+        <v>22.9</v>
       </c>
       <c r="H19" s="3">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="I19" s="4">
-        <v>81.0</v>
+        <v>65.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="C20" s="3">
-        <v>44.44</v>
+        <v>44.59</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
       </c>
       <c r="E20" s="3">
-        <v>28.73</v>
+        <v>29.26</v>
       </c>
       <c r="F20" s="2">
-        <v>119.3</v>
+        <v>117.0</v>
       </c>
       <c r="G20" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H20" s="3">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="I20" s="4">
-        <v>69.0</v>
+        <v>56.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="C21" s="3">
-        <v>8.08</v>
+        <v>7.72</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1229,33 +1220,33 @@
         <v>4.75</v>
       </c>
       <c r="F21" s="2">
-        <v>478.5</v>
+        <v>464.7</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="I21" s="4">
-        <v>66.0</v>
+        <v>60.0</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="C22" s="3">
-        <v>6.82</v>
+        <v>6.6</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1264,62 +1255,62 @@
         <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>455.3</v>
+        <v>431.7</v>
       </c>
       <c r="G22" s="2">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="H22" s="3">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="I22" s="4">
-        <v>46.0</v>
+        <v>40.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C23" s="3">
-        <v>39.06</v>
+        <v>36.3</v>
       </c>
       <c r="D23" s="3">
-        <v>38.44</v>
+        <v>39.33</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>526.5</v>
+        <v>499.3</v>
       </c>
       <c r="G23" s="2">
-        <v>22.0</v>
+        <v>20.8</v>
       </c>
       <c r="H23" s="3">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I23" s="4">
-        <v>94.0</v>
+        <v>93.0</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="C24" s="3">
-        <v>27.26</v>
+        <v>27.1</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1328,65 +1319,65 @@
         <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>66.2</v>
+        <v>67.7</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="I24" s="4">
-        <v>41.0</v>
+        <v>47.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C25" s="3">
-        <v>41.28</v>
+        <v>40.26</v>
       </c>
       <c r="D25" s="3">
         <v>48.7</v>
       </c>
       <c r="E25" s="3">
-        <v>21.37</v>
+        <v>22.34</v>
       </c>
       <c r="F25" s="2">
-        <v>304.7</v>
+        <v>303.6</v>
       </c>
       <c r="G25" s="2">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="H25" s="3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="4">
         <v>82.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="C26" s="3">
-        <v>14.6</v>
+        <v>15.91</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1395,30 +1386,30 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>119.2</v>
+        <v>132.8</v>
       </c>
       <c r="G26" s="2">
-        <v>15.0</v>
+        <v>16.7</v>
       </c>
       <c r="H26" s="3">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="I26" s="4">
-        <v>21.0</v>
+        <v>38.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="C27" s="3">
-        <v>8.16</v>
+        <v>8.21</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1427,62 +1418,62 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>301.2</v>
+        <v>304.7</v>
       </c>
       <c r="G27" s="2">
-        <v>4.9</v>
+        <v>5.0</v>
       </c>
       <c r="H27" s="3">
         <v>0.44</v>
       </c>
       <c r="I27" s="4">
-        <v>72.0</v>
+        <v>65.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="C28" s="3">
-        <v>24.34</v>
+        <v>29.11</v>
       </c>
       <c r="D28" s="3">
-        <v>26.77</v>
+        <v>29.91</v>
       </c>
       <c r="E28" s="3">
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>145.3</v>
+        <v>175.7</v>
       </c>
       <c r="G28" s="2">
-        <v>31.1</v>
+        <v>37.6</v>
       </c>
       <c r="H28" s="3">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="I28" s="4">
-        <v>75.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C29" s="3">
-        <v>20.7</v>
+        <v>21.51</v>
       </c>
       <c r="D29" s="3">
         <v>38.32</v>
@@ -1491,16 +1482,16 @@
         <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>363.4</v>
+        <v>397.1</v>
       </c>
       <c r="G29" s="2">
-        <v>40.7</v>
+        <v>44.5</v>
       </c>
       <c r="H29" s="3">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="I29" s="4">
-        <v>48.0</v>
+        <v>55.0</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>13</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Ngt6HdEncOZg5LldaFU3VrwXc4LRRyKFVgdKI+1Ag5E="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sWZIUVwa6XGnXdcD2f9F5tiSH3U1amcQ60aHuxBTdw4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="93">
   <si>
     <t>Company</t>
   </si>
@@ -603,7 +603,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.5</v>
+        <v>5.06</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -612,16 +612,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>56.2</v>
+        <v>51.7</v>
       </c>
       <c r="G2" s="2">
-        <v>16.1</v>
+        <v>14.8</v>
       </c>
       <c r="H2" s="3">
-        <v>0.88</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>75.0</v>
+        <v>55.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -638,25 +638,25 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.0</v>
+        <v>3.94</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="F3" s="2">
-        <v>165.1</v>
+        <v>162.7</v>
       </c>
       <c r="G3" s="2">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="H3" s="3">
         <v>0.39</v>
       </c>
       <c r="I3" s="4">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -670,7 +670,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -679,16 +679,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>21.7</v>
+        <v>20.8</v>
       </c>
       <c r="G4" s="2">
-        <v>6.3</v>
+        <v>6.0</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>56.0</v>
+        <v>48.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -702,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>13.55</v>
+        <v>13.24</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -711,16 +711,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>386.5</v>
+        <v>377.5</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I5" s="4">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="6">
@@ -731,7 +731,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>23.45</v>
+        <v>24.24</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -740,16 +740,16 @@
         <v>16.37</v>
       </c>
       <c r="F6" s="2">
-        <v>200.8</v>
+        <v>207.6</v>
       </c>
       <c r="G6" s="2">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="H6" s="3">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="I6" s="4">
-        <v>65.0</v>
+        <v>81.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -763,22 +763,22 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>43.94</v>
+        <v>46.11</v>
       </c>
       <c r="D7" s="3">
-        <v>47.08</v>
+        <v>47.24</v>
       </c>
       <c r="E7" s="3">
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>1106.0</v>
+        <v>1160.6</v>
       </c>
       <c r="G7" s="2">
-        <v>556.2</v>
+        <v>583.7</v>
       </c>
       <c r="H7" s="3">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="I7" s="4">
         <v>96.0</v>
@@ -798,7 +798,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>21.49</v>
+        <v>20.85</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -807,16 +807,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>543.7</v>
+        <v>527.5</v>
       </c>
       <c r="G8" s="2">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I8" s="4">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>33</v>
@@ -830,7 +830,7 @@
         <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>19.06</v>
+        <v>18.29</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -839,16 +839,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>263.1</v>
+        <v>252.5</v>
       </c>
       <c r="G9" s="2">
-        <v>17.0</v>
+        <v>16.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="I9" s="4">
-        <v>85.0</v>
+        <v>79.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
@@ -862,25 +862,25 @@
         <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>66.38</v>
+        <v>70.21</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>46.38</v>
+        <v>47.32</v>
       </c>
       <c r="F10" s="2">
-        <v>468.0</v>
+        <v>495.4</v>
       </c>
       <c r="G10" s="2">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H10" s="3">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="I10" s="4">
-        <v>70.0</v>
+        <v>77.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
@@ -894,7 +894,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>33.62</v>
+        <v>34.26</v>
       </c>
       <c r="D11" s="3">
         <v>37.97</v>
@@ -903,16 +903,16 @@
         <v>14.51</v>
       </c>
       <c r="F11" s="2">
-        <v>238.7</v>
+        <v>243.5</v>
       </c>
       <c r="G11" s="2">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="H11" s="3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="I11" s="4">
-        <v>91.0</v>
+        <v>94.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>42</v>
@@ -926,25 +926,25 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>12.88</v>
+        <v>12.01</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>7.01</v>
+        <v>7.22</v>
       </c>
       <c r="F12" s="2">
-        <v>972.8</v>
+        <v>908.5</v>
       </c>
       <c r="G12" s="2">
-        <v>37.8</v>
+        <v>35.3</v>
       </c>
       <c r="H12" s="3">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="I12" s="4">
-        <v>43.0</v>
+        <v>29.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>45</v>
@@ -958,7 +958,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>5.99</v>
+        <v>6.45</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -967,16 +967,16 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>252.0</v>
+        <v>271.3</v>
       </c>
       <c r="G13" s="2">
-        <v>18.5</v>
+        <v>19.9</v>
       </c>
       <c r="H13" s="3">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="I13" s="4">
-        <v>31.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="14">
@@ -987,7 +987,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="3">
-        <v>25.09</v>
+        <v>25.36</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -996,16 +996,16 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>603.4</v>
+        <v>609.9</v>
       </c>
       <c r="G14" s="2">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="H14" s="3">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I14" s="4">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>50</v>
@@ -1019,25 +1019,25 @@
         <v>52</v>
       </c>
       <c r="C15" s="3">
-        <v>4.64</v>
+        <v>4.88</v>
       </c>
       <c r="D15" s="3">
-        <v>6.8</v>
+        <v>6.61</v>
       </c>
       <c r="E15" s="3">
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>167.9</v>
+        <v>174.7</v>
       </c>
       <c r="G15" s="2">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="H15" s="3">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="I15" s="4">
-        <v>63.0</v>
+        <v>86.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1051,7 +1051,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="3">
-        <v>7.89</v>
+        <v>7.71</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1060,16 +1060,16 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>94.7</v>
+        <v>92.5</v>
       </c>
       <c r="G16" s="2">
-        <v>42.2</v>
+        <v>41.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I16" s="4">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="17">
@@ -1080,7 +1080,7 @@
         <v>56</v>
       </c>
       <c r="C17" s="3">
-        <v>16.69</v>
+        <v>16.27</v>
       </c>
       <c r="D17" s="3">
         <v>19.64</v>
@@ -1089,16 +1089,16 @@
         <v>7.74</v>
       </c>
       <c r="F17" s="2">
-        <v>531.0</v>
+        <v>517.7</v>
       </c>
       <c r="G17" s="2">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="H17" s="3">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="I17" s="4">
-        <v>78.0</v>
+        <v>75.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>57</v>
@@ -1112,7 +1112,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="3">
-        <v>48.4</v>
+        <v>47.33</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1121,16 +1121,16 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>365.0</v>
+        <v>356.9</v>
       </c>
       <c r="G18" s="2">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="H18" s="3">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I18" s="4">
-        <v>43.0</v>
+        <v>51.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
@@ -1147,7 +1147,7 @@
         <v>62</v>
       </c>
       <c r="C19" s="3">
-        <v>39.46</v>
+        <v>40.53</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
@@ -1156,16 +1156,16 @@
         <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>497.1</v>
+        <v>512.1</v>
       </c>
       <c r="G19" s="2">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="H19" s="3">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="I19" s="4">
-        <v>65.0</v>
+        <v>70.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>63</v>
@@ -1179,7 +1179,7 @@
         <v>65</v>
       </c>
       <c r="C20" s="3">
-        <v>44.59</v>
+        <v>45.33</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
@@ -1188,16 +1188,16 @@
         <v>29.26</v>
       </c>
       <c r="F20" s="2">
-        <v>117.0</v>
+        <v>119.0</v>
       </c>
       <c r="G20" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H20" s="3">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="I20" s="4">
-        <v>56.0</v>
+        <v>70.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>66</v>
@@ -1211,7 +1211,7 @@
         <v>68</v>
       </c>
       <c r="C21" s="3">
-        <v>7.72</v>
+        <v>8.33</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1220,16 +1220,16 @@
         <v>4.75</v>
       </c>
       <c r="F21" s="2">
-        <v>464.7</v>
+        <v>501.4</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.81</v>
+        <v>0.88</v>
       </c>
       <c r="I21" s="4">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>69</v>
@@ -1246,7 +1246,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1255,16 +1255,16 @@
         <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>431.7</v>
+        <v>454.6</v>
       </c>
       <c r="G22" s="2">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="H22" s="3">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="I22" s="4">
-        <v>40.0</v>
+        <v>48.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1278,7 +1278,7 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>36.3</v>
+        <v>36.24</v>
       </c>
       <c r="D23" s="3">
         <v>39.33</v>
@@ -1287,16 +1287,16 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>499.3</v>
+        <v>498.4</v>
       </c>
       <c r="G23" s="2">
         <v>20.8</v>
       </c>
       <c r="H23" s="3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I23" s="4">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>76</v>
@@ -1310,7 +1310,7 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>27.1</v>
+        <v>27.63</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1319,7 +1319,7 @@
         <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>67.7</v>
+        <v>69.0</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
@@ -1328,7 +1328,7 @@
         <v>0.36</v>
       </c>
       <c r="I24" s="4">
-        <v>47.0</v>
+        <v>60.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1345,7 +1345,7 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>40.26</v>
+        <v>40.16</v>
       </c>
       <c r="D25" s="3">
         <v>48.7</v>
@@ -1354,7 +1354,7 @@
         <v>22.34</v>
       </c>
       <c r="F25" s="2">
-        <v>303.6</v>
+        <v>302.9</v>
       </c>
       <c r="G25" s="2">
         <v>16.3</v>
@@ -1363,7 +1363,7 @@
         <v>1.2</v>
       </c>
       <c r="I25" s="4">
-        <v>82.0</v>
+        <v>85.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>82</v>
@@ -1377,7 +1377,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>15.91</v>
+        <v>15.43</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1386,16 +1386,16 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>132.8</v>
+        <v>128.8</v>
       </c>
       <c r="G26" s="2">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="H26" s="3">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="I26" s="4">
-        <v>38.0</v>
+        <v>35.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1409,7 +1409,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>8.21</v>
+        <v>8.9</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1418,16 +1418,16 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>304.7</v>
+        <v>331.0</v>
       </c>
       <c r="G27" s="2">
-        <v>5.0</v>
+        <v>5.4</v>
       </c>
       <c r="H27" s="3">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="I27" s="4">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1444,7 +1444,7 @@
         <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>29.11</v>
+        <v>25.32</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1453,16 +1453,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>175.7</v>
+        <v>152.7</v>
       </c>
       <c r="G28" s="2">
-        <v>37.6</v>
+        <v>32.7</v>
       </c>
       <c r="H28" s="3">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="I28" s="4">
-        <v>88.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1473,7 +1473,7 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>21.51</v>
+        <v>21.98</v>
       </c>
       <c r="D29" s="3">
         <v>38.32</v>
@@ -1482,19 +1482,16 @@
         <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>397.1</v>
+        <v>405.8</v>
       </c>
       <c r="G29" s="2">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="H29" s="3">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="I29" s="4">
-        <v>55.0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>13</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sWZIUVwa6XGnXdcD2f9F5tiSH3U1amcQ60aHuxBTdw4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TNWNFwYt9igKMFPEHkckjA/k8MwbxMNoX2i/cVFFt4E="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
   <si>
     <t>Company</t>
   </si>
@@ -81,15 +81,18 @@
     <t>News Archive for CTRM</t>
   </si>
   <si>
-    <t>Columbus McKinnon Corporation *</t>
-  </si>
-  <si>
-    <t>CMCO*</t>
+    <t>Columbus McKinnon Corporation</t>
+  </si>
+  <si>
+    <t>CMCO</t>
   </si>
   <si>
     <t>nmf</t>
   </si>
   <si>
+    <t>TTM adjusted earnings positive</t>
+  </si>
+  <si>
     <t>Core Molding Technologies, Inc.</t>
   </si>
   <si>
@@ -105,7 +108,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>Approaching size limit Approaching value limit</t>
+    <t>Exceeds size limit Approaching value limit</t>
   </si>
   <si>
     <t>News Archive for CVLG</t>
@@ -156,10 +159,10 @@
     <t>News Archive for GILT</t>
   </si>
   <si>
-    <t>Hudson Technologies, Inc. *</t>
-  </si>
-  <si>
-    <t>HDSN*</t>
+    <t>Hudson Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>HDSN</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -171,16 +174,16 @@
     <t>News Archive for KE</t>
   </si>
   <si>
-    <t>Kolibri Global Energy Inc. *</t>
-  </si>
-  <si>
-    <t>KGEI*</t>
-  </si>
-  <si>
-    <t>Mastech Digital, Inc. *</t>
-  </si>
-  <si>
-    <t>MHH*</t>
+    <t>Kolibri Global Energy Inc.</t>
+  </si>
+  <si>
+    <t>KGEI</t>
+  </si>
+  <si>
+    <t>Mastech Digital, Inc.</t>
+  </si>
+  <si>
+    <t>MHH</t>
   </si>
   <si>
     <t>Mistras Group, Inc.</t>
@@ -225,9 +228,6 @@
     <t>OIS</t>
   </si>
   <si>
-    <t>TTM adjusted earnings positive</t>
-  </si>
-  <si>
     <t>News Archive for OIS</t>
   </si>
   <si>
@@ -291,10 +291,10 @@
     <t>EML</t>
   </si>
   <si>
-    <t>USANA Health Sciences, Inc. *</t>
-  </si>
-  <si>
-    <t>USNA*</t>
+    <t>USANA Health Sciences, Inc.</t>
+  </si>
+  <si>
+    <t>USNA</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -612,16 +612,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>51.7</v>
+        <v>54.1</v>
       </c>
       <c r="G2" s="2">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>55.0</v>
+        <v>63.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -644,19 +644,19 @@
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="F3" s="2">
-        <v>162.7</v>
+        <v>163.9</v>
       </c>
       <c r="G3" s="2">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="H3" s="3">
         <v>0.39</v>
       </c>
       <c r="I3" s="4">
-        <v>36.0</v>
+        <v>30.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -670,7 +670,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -679,16 +679,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="G4" s="2">
-        <v>6.0</v>
+        <v>5.5</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>48.0</v>
+        <v>40.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -702,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>13.24</v>
+        <v>14.36</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -711,27 +711,30 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>377.5</v>
+        <v>420.8</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="I5" s="4">
-        <v>20.0</v>
+        <v>23.0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>24.24</v>
+        <v>24.92</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -740,65 +743,65 @@
         <v>16.37</v>
       </c>
       <c r="F6" s="2">
-        <v>207.6</v>
+        <v>212.2</v>
       </c>
       <c r="G6" s="2">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="H6" s="3">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="I6" s="4">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>46.11</v>
+        <v>47.34</v>
       </c>
       <c r="D7" s="3">
-        <v>47.24</v>
+        <v>49.33</v>
       </c>
       <c r="E7" s="3">
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>1160.6</v>
+        <v>1213.5</v>
       </c>
       <c r="G7" s="2">
-        <v>583.7</v>
+        <v>610.3</v>
       </c>
       <c r="H7" s="3">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="I7" s="4">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>20.85</v>
+        <v>21.38</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -807,30 +810,30 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>527.5</v>
+        <v>549.2</v>
       </c>
       <c r="G8" s="2">
-        <v>12.5</v>
+        <v>13.0</v>
       </c>
       <c r="H8" s="3">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="I8" s="4">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>18.29</v>
+        <v>19.24</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -839,62 +842,62 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>252.5</v>
+        <v>267.4</v>
       </c>
       <c r="G9" s="2">
-        <v>16.3</v>
+        <v>17.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="I9" s="4">
-        <v>79.0</v>
+        <v>86.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>70.21</v>
+        <v>69.23</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>47.32</v>
+        <v>48.6</v>
       </c>
       <c r="F10" s="2">
-        <v>495.4</v>
+        <v>506.1</v>
       </c>
       <c r="G10" s="2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H10" s="3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I10" s="4">
-        <v>77.0</v>
+        <v>83.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>34.26</v>
+        <v>34.09</v>
       </c>
       <c r="D11" s="3">
         <v>37.97</v>
@@ -903,30 +906,30 @@
         <v>14.51</v>
       </c>
       <c r="F11" s="2">
-        <v>243.5</v>
+        <v>248.9</v>
       </c>
       <c r="G11" s="2">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H11" s="3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="I11" s="4">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>12.01</v>
+        <v>11.14</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -935,30 +938,30 @@
         <v>7.22</v>
       </c>
       <c r="F12" s="2">
-        <v>908.5</v>
+        <v>844.9</v>
       </c>
       <c r="G12" s="2">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="H12" s="3">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="I12" s="4">
-        <v>29.0</v>
+        <v>17.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>6.45</v>
+        <v>6.17</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -967,27 +970,27 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>271.3</v>
+        <v>265.5</v>
       </c>
       <c r="G13" s="2">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="H13" s="3">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="I13" s="4">
-        <v>38.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>25.36</v>
+        <v>23.97</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -996,30 +999,30 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>609.9</v>
+        <v>586.8</v>
       </c>
       <c r="G14" s="2">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="H14" s="3">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="I14" s="4">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>4.88</v>
+        <v>5.23</v>
       </c>
       <c r="D15" s="3">
         <v>6.61</v>
@@ -1028,16 +1031,16 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>174.7</v>
+        <v>183.6</v>
       </c>
       <c r="G15" s="2">
-        <v>12.8</v>
+        <v>13.3</v>
       </c>
       <c r="H15" s="3">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="I15" s="4">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1045,13 +1048,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="3">
-        <v>7.71</v>
+        <v>7.38</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1060,27 +1063,30 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>92.5</v>
+        <v>90.0</v>
       </c>
       <c r="G16" s="2">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="H16" s="3">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="I16" s="4">
-        <v>56.0</v>
+        <v>53.0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3">
-        <v>16.27</v>
+        <v>15.71</v>
       </c>
       <c r="D17" s="3">
         <v>19.64</v>
@@ -1089,30 +1095,30 @@
         <v>7.74</v>
       </c>
       <c r="F17" s="2">
-        <v>517.7</v>
+        <v>506.5</v>
       </c>
       <c r="G17" s="2">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="H17" s="3">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="I17" s="4">
-        <v>75.0</v>
+        <v>64.0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="3">
-        <v>47.33</v>
+        <v>47.97</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1121,33 +1127,33 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>356.9</v>
+        <v>367.9</v>
       </c>
       <c r="G18" s="2">
-        <v>16.5</v>
+        <v>17.0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="I18" s="4">
-        <v>51.0</v>
+        <v>58.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3">
-        <v>40.53</v>
+        <v>38.77</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
@@ -1156,62 +1162,62 @@
         <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>512.1</v>
+        <v>500.5</v>
       </c>
       <c r="G19" s="2">
-        <v>23.6</v>
+        <v>23.0</v>
       </c>
       <c r="H19" s="3">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="I19" s="4">
-        <v>70.0</v>
+        <v>68.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" s="3">
-        <v>45.33</v>
+        <v>43.59</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
       </c>
       <c r="E20" s="3">
-        <v>29.26</v>
+        <v>29.48</v>
       </c>
       <c r="F20" s="2">
-        <v>119.0</v>
+        <v>113.5</v>
       </c>
       <c r="G20" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H20" s="3">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="I20" s="4">
-        <v>70.0</v>
+        <v>63.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1220,19 +1226,19 @@
         <v>4.75</v>
       </c>
       <c r="F21" s="2">
-        <v>501.4</v>
+        <v>509.2</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I21" s="4">
-        <v>61.0</v>
+        <v>55.0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>70</v>
@@ -1246,7 +1252,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>6.95</v>
+        <v>7.03</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1255,16 +1261,16 @@
         <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>454.6</v>
+        <v>474.3</v>
       </c>
       <c r="G22" s="2">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H22" s="3">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="I22" s="4">
-        <v>48.0</v>
+        <v>57.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1278,7 +1284,7 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>36.24</v>
+        <v>37.76</v>
       </c>
       <c r="D23" s="3">
         <v>39.33</v>
@@ -1287,13 +1293,13 @@
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>498.4</v>
+        <v>528.7</v>
       </c>
       <c r="G23" s="2">
-        <v>20.8</v>
+        <v>22.1</v>
       </c>
       <c r="H23" s="3">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="I23" s="4">
         <v>94.0</v>
@@ -1310,7 +1316,7 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>27.63</v>
+        <v>29.61</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1319,16 +1325,16 @@
         <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>69.0</v>
+        <v>75.5</v>
       </c>
       <c r="G24" s="2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H24" s="3">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I24" s="4">
-        <v>60.0</v>
+        <v>74.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1345,25 +1351,25 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>40.16</v>
+        <v>40.94</v>
       </c>
       <c r="D25" s="3">
         <v>48.7</v>
       </c>
       <c r="E25" s="3">
-        <v>22.34</v>
+        <v>22.5</v>
       </c>
       <c r="F25" s="2">
-        <v>302.9</v>
+        <v>310.9</v>
       </c>
       <c r="G25" s="2">
-        <v>16.3</v>
+        <v>16.7</v>
       </c>
       <c r="H25" s="3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="I25" s="4">
-        <v>85.0</v>
+        <v>79.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>82</v>
@@ -1377,7 +1383,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>15.43</v>
+        <v>15.44</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1386,16 +1392,16 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>128.8</v>
+        <v>133.4</v>
       </c>
       <c r="G26" s="2">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="H26" s="3">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="I26" s="4">
-        <v>35.0</v>
+        <v>25.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1409,7 +1415,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>8.9</v>
+        <v>8.53</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1418,16 +1424,16 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>331.0</v>
+        <v>323.1</v>
       </c>
       <c r="G27" s="2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H27" s="3">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="I27" s="4">
-        <v>68.0</v>
+        <v>62.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1444,7 +1450,7 @@
         <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>25.32</v>
+        <v>25.53</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1453,16 +1459,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>152.7</v>
+        <v>160.4</v>
       </c>
       <c r="G28" s="2">
-        <v>32.7</v>
+        <v>34.3</v>
       </c>
       <c r="H28" s="3">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="I28" s="4">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1473,7 +1479,7 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>21.98</v>
+        <v>21.82</v>
       </c>
       <c r="D29" s="3">
         <v>38.32</v>
@@ -1482,13 +1488,13 @@
         <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>405.8</v>
+        <v>418.2</v>
       </c>
       <c r="G29" s="2">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="H29" s="3">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="I29" s="4">
         <v>63.0</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TNWNFwYt9igKMFPEHkckjA/k8MwbxMNoX2i/cVFFt4E="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YrXFeL8lAxcdQ1LxK0DZa23SBfHzI0tt1zvivFUJLtU="/>
     </ext>
   </extLst>
 </workbook>
@@ -603,7 +603,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.16</v>
+        <v>4.93</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -612,16 +612,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>54.1</v>
+        <v>50.2</v>
       </c>
       <c r="G2" s="2">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="H2" s="3">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="I2" s="4">
-        <v>63.0</v>
+        <v>62.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -644,19 +644,19 @@
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="F3" s="2">
-        <v>163.9</v>
+        <v>170.5</v>
       </c>
       <c r="G3" s="2">
-        <v>17.3</v>
+        <v>18.0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="I3" s="4">
-        <v>30.0</v>
+        <v>37.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -670,7 +670,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -679,16 +679,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>19.2</v>
+        <v>18.0</v>
       </c>
       <c r="G4" s="2">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I4" s="4">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -702,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>14.36</v>
+        <v>16.12</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -711,16 +711,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>420.8</v>
+        <v>443.6</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="I5" s="4">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -734,7 +734,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>24.92</v>
+        <v>24.54</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -743,13 +743,13 @@
         <v>16.37</v>
       </c>
       <c r="F6" s="2">
-        <v>212.2</v>
+        <v>209.0</v>
       </c>
       <c r="G6" s="2">
-        <v>22.3</v>
+        <v>22.0</v>
       </c>
       <c r="H6" s="3">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="I6" s="4">
         <v>82.0</v>
@@ -766,25 +766,25 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>47.34</v>
+        <v>46.75</v>
       </c>
       <c r="D7" s="3">
-        <v>49.33</v>
+        <v>49.88</v>
       </c>
       <c r="E7" s="3">
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>1213.5</v>
+        <v>1214.0</v>
       </c>
       <c r="G7" s="2">
-        <v>610.3</v>
+        <v>610.5</v>
       </c>
       <c r="H7" s="3">
         <v>2.97</v>
       </c>
       <c r="I7" s="4">
-        <v>97.0</v>
+        <v>96.0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
@@ -801,7 +801,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>21.38</v>
+        <v>21.58</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -810,16 +810,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>549.2</v>
+        <v>539.6</v>
       </c>
       <c r="G8" s="2">
-        <v>13.0</v>
+        <v>12.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="I8" s="4">
-        <v>69.0</v>
+        <v>64.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -833,7 +833,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>19.24</v>
+        <v>18.63</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -842,16 +842,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>267.4</v>
+        <v>258.0</v>
       </c>
       <c r="G9" s="2">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="I9" s="4">
-        <v>86.0</v>
+        <v>84.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -865,25 +865,25 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>69.23</v>
+        <v>76.99</v>
       </c>
       <c r="D10" s="3">
         <v>78.76</v>
       </c>
       <c r="E10" s="3">
-        <v>48.6</v>
+        <v>48.89</v>
       </c>
       <c r="F10" s="2">
-        <v>506.1</v>
+        <v>533.9</v>
       </c>
       <c r="G10" s="2">
-        <v>3.8</v>
+        <v>4.0</v>
       </c>
       <c r="H10" s="3">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="I10" s="4">
-        <v>83.0</v>
+        <v>89.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -897,7 +897,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>34.09</v>
+        <v>35.6</v>
       </c>
       <c r="D11" s="3">
         <v>37.97</v>
@@ -906,16 +906,16 @@
         <v>14.51</v>
       </c>
       <c r="F11" s="2">
-        <v>248.9</v>
+        <v>242.1</v>
       </c>
       <c r="G11" s="2">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="H11" s="3">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="I11" s="4">
-        <v>96.0</v>
+        <v>95.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>43</v>
@@ -929,7 +929,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>11.14</v>
+        <v>10.73</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -938,13 +938,13 @@
         <v>7.22</v>
       </c>
       <c r="F12" s="2">
-        <v>844.9</v>
+        <v>859.7</v>
       </c>
       <c r="G12" s="2">
-        <v>32.9</v>
+        <v>33.4</v>
       </c>
       <c r="H12" s="3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I12" s="4">
         <v>17.0</v>
@@ -961,7 +961,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>6.17</v>
+        <v>6.34</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -970,16 +970,16 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>265.5</v>
+        <v>266.7</v>
       </c>
       <c r="G13" s="2">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="H13" s="3">
         <v>1.12</v>
       </c>
       <c r="I13" s="4">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="14">
@@ -990,7 +990,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>23.97</v>
+        <v>24.86</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -999,16 +999,16 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>586.8</v>
+        <v>599.7</v>
       </c>
       <c r="G14" s="2">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="H14" s="3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I14" s="4">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>51</v>
@@ -1022,7 +1022,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>5.23</v>
+        <v>5.31</v>
       </c>
       <c r="D15" s="3">
         <v>6.61</v>
@@ -1031,13 +1031,13 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>183.6</v>
+        <v>194.1</v>
       </c>
       <c r="G15" s="2">
-        <v>13.3</v>
+        <v>14.2</v>
       </c>
       <c r="H15" s="3">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="I15" s="4">
         <v>88.0</v>
@@ -1054,7 +1054,7 @@
         <v>55</v>
       </c>
       <c r="C16" s="3">
-        <v>7.38</v>
+        <v>7.76</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1063,19 +1063,16 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>90.0</v>
+        <v>92.5</v>
       </c>
       <c r="G16" s="2">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="H16" s="3">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="I16" s="4">
-        <v>53.0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="17">
@@ -1086,7 +1083,7 @@
         <v>57</v>
       </c>
       <c r="C17" s="3">
-        <v>15.71</v>
+        <v>15.46</v>
       </c>
       <c r="D17" s="3">
         <v>19.64</v>
@@ -1095,16 +1092,16 @@
         <v>7.74</v>
       </c>
       <c r="F17" s="2">
-        <v>506.5</v>
+        <v>498.6</v>
       </c>
       <c r="G17" s="2">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="H17" s="3">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="I17" s="4">
-        <v>64.0</v>
+        <v>63.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>58</v>
@@ -1118,7 +1115,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="3">
-        <v>47.97</v>
+        <v>46.81</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1127,16 +1124,16 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>367.9</v>
+        <v>356.2</v>
       </c>
       <c r="G18" s="2">
-        <v>17.0</v>
+        <v>16.5</v>
       </c>
       <c r="H18" s="3">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="I18" s="4">
-        <v>58.0</v>
+        <v>46.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
@@ -1153,7 +1150,7 @@
         <v>63</v>
       </c>
       <c r="C19" s="3">
-        <v>38.77</v>
+        <v>36.47</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
@@ -1162,13 +1159,13 @@
         <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>500.5</v>
+        <v>491.1</v>
       </c>
       <c r="G19" s="2">
-        <v>23.0</v>
+        <v>22.6</v>
       </c>
       <c r="H19" s="3">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="I19" s="4">
         <v>68.0</v>
@@ -1185,7 +1182,7 @@
         <v>66</v>
       </c>
       <c r="C20" s="3">
-        <v>43.59</v>
+        <v>47.23</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
@@ -1194,16 +1191,16 @@
         <v>29.48</v>
       </c>
       <c r="F20" s="2">
-        <v>113.5</v>
+        <v>115.5</v>
       </c>
       <c r="G20" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H20" s="3">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I20" s="4">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>67</v>
@@ -1217,7 +1214,7 @@
         <v>69</v>
       </c>
       <c r="C21" s="3">
-        <v>8.43</v>
+        <v>8.67</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1226,16 +1223,16 @@
         <v>4.75</v>
       </c>
       <c r="F21" s="2">
-        <v>509.2</v>
+        <v>522.5</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="I21" s="4">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -1252,7 +1249,7 @@
         <v>72</v>
       </c>
       <c r="C22" s="3">
-        <v>7.03</v>
+        <v>7.66</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1261,16 +1258,16 @@
         <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>474.3</v>
+        <v>499.1</v>
       </c>
       <c r="G22" s="2">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="H22" s="3">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="I22" s="4">
-        <v>57.0</v>
+        <v>61.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>73</v>
@@ -1284,22 +1281,22 @@
         <v>75</v>
       </c>
       <c r="C23" s="3">
-        <v>37.76</v>
+        <v>38.47</v>
       </c>
       <c r="D23" s="3">
-        <v>39.33</v>
+        <v>39.69</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>528.7</v>
+        <v>525.0</v>
       </c>
       <c r="G23" s="2">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="H23" s="3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I23" s="4">
         <v>94.0</v>
@@ -1316,7 +1313,7 @@
         <v>78</v>
       </c>
       <c r="C24" s="3">
-        <v>29.61</v>
+        <v>27.98</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1325,16 +1322,16 @@
         <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>75.5</v>
+        <v>68.8</v>
       </c>
       <c r="G24" s="2">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="I24" s="4">
-        <v>74.0</v>
+        <v>71.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1351,25 +1348,25 @@
         <v>81</v>
       </c>
       <c r="C25" s="3">
-        <v>40.94</v>
+        <v>40.37</v>
       </c>
       <c r="D25" s="3">
         <v>48.7</v>
       </c>
       <c r="E25" s="3">
-        <v>22.5</v>
+        <v>22.61</v>
       </c>
       <c r="F25" s="2">
-        <v>310.9</v>
+        <v>302.4</v>
       </c>
       <c r="G25" s="2">
-        <v>16.7</v>
+        <v>16.3</v>
       </c>
       <c r="H25" s="3">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="4">
-        <v>79.0</v>
+        <v>75.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>82</v>
@@ -1383,7 +1380,7 @@
         <v>84</v>
       </c>
       <c r="C26" s="3">
-        <v>15.44</v>
+        <v>15.26</v>
       </c>
       <c r="D26" s="3">
         <v>23.5</v>
@@ -1392,16 +1389,16 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>133.4</v>
+        <v>122.2</v>
       </c>
       <c r="G26" s="2">
-        <v>16.8</v>
+        <v>15.4</v>
       </c>
       <c r="H26" s="3">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="I26" s="4">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>85</v>
@@ -1415,7 +1412,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="3">
-        <v>8.53</v>
+        <v>8.83</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1424,16 +1421,16 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>323.1</v>
+        <v>335.0</v>
       </c>
       <c r="G27" s="2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H27" s="3">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="I27" s="4">
-        <v>62.0</v>
+        <v>70.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1450,7 +1447,7 @@
         <v>90</v>
       </c>
       <c r="C28" s="3">
-        <v>25.53</v>
+        <v>24.22</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1459,16 +1456,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>160.4</v>
+        <v>146.8</v>
       </c>
       <c r="G28" s="2">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="H28" s="3">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="I28" s="4">
-        <v>90.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1479,25 +1476,28 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>21.82</v>
+        <v>21.32</v>
       </c>
       <c r="D29" s="3">
-        <v>38.32</v>
+        <v>35.43</v>
       </c>
       <c r="E29" s="3">
         <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>418.2</v>
+        <v>386.2</v>
       </c>
       <c r="G29" s="2">
-        <v>46.9</v>
+        <v>43.3</v>
       </c>
       <c r="H29" s="3">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="I29" s="4">
-        <v>63.0</v>
+        <v>45.0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YrXFeL8lAxcdQ1LxK0DZa23SBfHzI0tt1zvivFUJLtU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="kLBm4efxUTNkBLxt8zNXF9gf0+iHfzFagkt/EQ9wROI="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>Company</t>
   </si>
@@ -108,10 +108,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>Exceeds size limit Approaching value limit</t>
-  </si>
-  <si>
-    <t>News Archive for CVLG</t>
+    <t>(7/29/26) Covenant Logistics Group, Inc. (CVLG)</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -129,7 +126,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>News Archive for ESCA</t>
+    <t>(7/29/26) Escalade, Incorporated (ESCA)</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -219,7 +216,7 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>News Archive for NCSM</t>
+    <t>(7/30/26) NCS Multistage Holdings, Inc. (NCSM)</t>
   </si>
   <si>
     <t>Oil States International, Inc.</t>
@@ -228,7 +225,7 @@
     <t>OIS</t>
   </si>
   <si>
-    <t>News Archive for OIS</t>
+    <t>(7/30/26) Oil States International, Inc. (OIS)</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions Ltd.</t>
@@ -264,7 +261,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>News Archive for RCKY</t>
+    <t>(7/28/26) Rocky Brands, Inc. (RCKY)</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -612,16 +609,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="G2" s="2">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H2" s="3">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I2" s="4">
-        <v>62.0</v>
+        <v>50.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -638,7 +635,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -647,16 +644,16 @@
         <v>3.41</v>
       </c>
       <c r="F3" s="2">
-        <v>170.5</v>
+        <v>154.8</v>
       </c>
       <c r="G3" s="2">
-        <v>18.0</v>
+        <v>16.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="I3" s="4">
-        <v>37.0</v>
+        <v>27.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -670,7 +667,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -679,16 +676,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>18.0</v>
+        <v>18.9</v>
       </c>
       <c r="G4" s="2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H4" s="3">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>41.0</v>
+        <v>31.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -702,7 +699,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.12</v>
+        <v>19.17</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -711,16 +708,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>443.6</v>
+        <v>589.3</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="I5" s="4">
-        <v>25.0</v>
+        <v>49.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -734,7 +731,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>24.54</v>
+        <v>23.56</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -743,16 +740,16 @@
         <v>16.37</v>
       </c>
       <c r="F6" s="2">
-        <v>209.0</v>
+        <v>199.8</v>
       </c>
       <c r="G6" s="2">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="H6" s="3">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="I6" s="4">
-        <v>82.0</v>
+        <v>78.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -766,7 +763,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>46.75</v>
+        <v>35.52</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -775,33 +772,30 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>1214.0</v>
+        <v>927.6</v>
       </c>
       <c r="G7" s="2">
-        <v>610.5</v>
+        <v>466.5</v>
       </c>
       <c r="H7" s="3">
-        <v>2.97</v>
+        <v>2.27</v>
       </c>
       <c r="I7" s="4">
-        <v>96.0</v>
-      </c>
-      <c r="J7" s="2" t="s">
+        <v>90.0</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C8" s="3">
-        <v>21.58</v>
+        <v>21.8</v>
       </c>
       <c r="D8" s="3">
         <v>22.36</v>
@@ -810,30 +804,30 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>539.6</v>
+        <v>548.0</v>
       </c>
       <c r="G8" s="2">
-        <v>12.8</v>
+        <v>13.0</v>
       </c>
       <c r="H8" s="3">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="I8" s="4">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C9" s="3">
-        <v>18.63</v>
+        <v>19.86</v>
       </c>
       <c r="D9" s="3">
         <v>21.32</v>
@@ -842,94 +836,94 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>258.0</v>
+        <v>287.4</v>
       </c>
       <c r="G9" s="2">
-        <v>16.7</v>
+        <v>18.6</v>
       </c>
       <c r="H9" s="3">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="I9" s="4">
-        <v>84.0</v>
+        <v>91.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C10" s="3">
-        <v>76.99</v>
+        <v>78.94</v>
       </c>
       <c r="D10" s="3">
-        <v>78.76</v>
+        <v>79.48</v>
       </c>
       <c r="E10" s="3">
         <v>48.89</v>
       </c>
       <c r="F10" s="2">
-        <v>533.9</v>
+        <v>560.2</v>
       </c>
       <c r="G10" s="2">
-        <v>4.0</v>
+        <v>4.2</v>
       </c>
       <c r="H10" s="3">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="I10" s="4">
-        <v>89.0</v>
+        <v>88.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C11" s="3">
-        <v>35.6</v>
+        <v>33.25</v>
       </c>
       <c r="D11" s="3">
-        <v>37.97</v>
+        <v>39.07</v>
       </c>
       <c r="E11" s="3">
         <v>14.51</v>
       </c>
       <c r="F11" s="2">
-        <v>242.1</v>
+        <v>242.2</v>
       </c>
       <c r="G11" s="2">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="H11" s="3">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="I11" s="4">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C12" s="3">
-        <v>10.73</v>
+        <v>11.05</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -938,30 +932,30 @@
         <v>7.22</v>
       </c>
       <c r="F12" s="2">
-        <v>859.7</v>
+        <v>832.1</v>
       </c>
       <c r="G12" s="2">
-        <v>33.4</v>
+        <v>32.4</v>
       </c>
       <c r="H12" s="3">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="I12" s="4">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C13" s="3">
-        <v>6.34</v>
+        <v>6.04</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -970,27 +964,27 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>266.7</v>
+        <v>244.0</v>
       </c>
       <c r="G13" s="2">
-        <v>19.6</v>
+        <v>17.9</v>
       </c>
       <c r="H13" s="3">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="I13" s="4">
-        <v>36.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C14" s="3">
-        <v>24.86</v>
+        <v>24.73</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -999,30 +993,30 @@
         <v>18.04</v>
       </c>
       <c r="F14" s="2">
-        <v>599.7</v>
+        <v>591.1</v>
       </c>
       <c r="G14" s="2">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="H14" s="3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I14" s="4">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C15" s="3">
-        <v>5.31</v>
+        <v>5.19</v>
       </c>
       <c r="D15" s="3">
         <v>6.61</v>
@@ -1031,16 +1025,16 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>194.1</v>
+        <v>180.2</v>
       </c>
       <c r="G15" s="2">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="H15" s="3">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="I15" s="4">
-        <v>88.0</v>
+        <v>84.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1048,10 +1042,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C16" s="3">
         <v>7.76</v>
@@ -1063,27 +1057,27 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>92.5</v>
+        <v>95.4</v>
       </c>
       <c r="G16" s="2">
-        <v>41.2</v>
+        <v>42.5</v>
       </c>
       <c r="H16" s="3">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="I16" s="4">
-        <v>66.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C17" s="3">
-        <v>15.46</v>
+        <v>15.21</v>
       </c>
       <c r="D17" s="3">
         <v>19.64</v>
@@ -1092,30 +1086,30 @@
         <v>7.74</v>
       </c>
       <c r="F17" s="2">
-        <v>498.6</v>
+        <v>482.7</v>
       </c>
       <c r="G17" s="2">
-        <v>22.7</v>
+        <v>22.0</v>
       </c>
       <c r="H17" s="3">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="I17" s="4">
-        <v>63.0</v>
+        <v>62.0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C18" s="3">
-        <v>46.81</v>
+        <v>47.4</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1124,7 +1118,7 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>356.2</v>
+        <v>355.8</v>
       </c>
       <c r="G18" s="2">
         <v>16.5</v>
@@ -1133,24 +1127,24 @@
         <v>0.81</v>
       </c>
       <c r="I18" s="4">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C19" s="3">
-        <v>36.47</v>
+        <v>36.64</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
@@ -1159,30 +1153,30 @@
         <v>22.72</v>
       </c>
       <c r="F19" s="2">
-        <v>491.1</v>
+        <v>453.5</v>
       </c>
       <c r="G19" s="2">
-        <v>22.6</v>
+        <v>20.9</v>
       </c>
       <c r="H19" s="3">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="I19" s="4">
-        <v>68.0</v>
+        <v>60.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="C20" s="3">
-        <v>47.23</v>
+        <v>47.0</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
@@ -1191,30 +1185,30 @@
         <v>29.48</v>
       </c>
       <c r="F20" s="2">
-        <v>115.5</v>
+        <v>118.9</v>
       </c>
       <c r="G20" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H20" s="3">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="I20" s="4">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="C21" s="3">
-        <v>8.67</v>
+        <v>8.11</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1223,33 +1217,33 @@
         <v>4.75</v>
       </c>
       <c r="F21" s="2">
-        <v>522.5</v>
+        <v>456.3</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="I21" s="4">
-        <v>54.0</v>
+        <v>39.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="C22" s="3">
-        <v>7.66</v>
+        <v>7.61</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1258,62 +1252,62 @@
         <v>4.46</v>
       </c>
       <c r="F22" s="2">
-        <v>499.1</v>
+        <v>493.2</v>
       </c>
       <c r="G22" s="2">
-        <v>14.2</v>
+        <v>14.0</v>
       </c>
       <c r="H22" s="3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I22" s="4">
-        <v>61.0</v>
+        <v>38.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="C23" s="3">
-        <v>38.47</v>
+        <v>39.93</v>
       </c>
       <c r="D23" s="3">
-        <v>39.69</v>
+        <v>39.85</v>
       </c>
       <c r="E23" s="3">
         <v>15.52</v>
       </c>
       <c r="F23" s="2">
-        <v>525.0</v>
+        <v>542.9</v>
       </c>
       <c r="G23" s="2">
-        <v>21.9</v>
+        <v>22.7</v>
       </c>
       <c r="H23" s="3">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="I23" s="4">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C24" s="3">
-        <v>27.98</v>
+        <v>27.38</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1322,7 +1316,7 @@
         <v>18.2</v>
       </c>
       <c r="F24" s="2">
-        <v>68.8</v>
+        <v>68.6</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
@@ -1331,88 +1325,88 @@
         <v>0.36</v>
       </c>
       <c r="I24" s="4">
-        <v>71.0</v>
+        <v>68.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="3">
+        <v>48.84</v>
+      </c>
+      <c r="D25" s="3">
+        <v>50.73</v>
+      </c>
+      <c r="E25" s="3">
+        <v>24.68</v>
+      </c>
+      <c r="F25" s="2">
+        <v>365.9</v>
+      </c>
+      <c r="G25" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="I25" s="4">
+        <v>92.0</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C25" s="3">
-        <v>40.37</v>
-      </c>
-      <c r="D25" s="3">
-        <v>48.7</v>
-      </c>
-      <c r="E25" s="3">
-        <v>22.61</v>
-      </c>
-      <c r="F25" s="2">
-        <v>302.4</v>
-      </c>
-      <c r="G25" s="2">
-        <v>16.3</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="I25" s="4">
-        <v>75.0</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="C26" s="3">
-        <v>15.26</v>
+        <v>14.83</v>
       </c>
       <c r="D26" s="3">
-        <v>23.5</v>
+        <v>23.49</v>
       </c>
       <c r="E26" s="3">
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>122.2</v>
+        <v>124.8</v>
       </c>
       <c r="G26" s="2">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="H26" s="3">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="I26" s="4">
-        <v>22.0</v>
+        <v>31.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="C27" s="3">
-        <v>8.83</v>
+        <v>8.92</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1421,33 +1415,33 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>335.0</v>
+        <v>328.7</v>
       </c>
       <c r="G27" s="2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H27" s="3">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="I27" s="4">
-        <v>70.0</v>
+        <v>66.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="C28" s="3">
-        <v>24.22</v>
+        <v>23.72</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1456,48 +1450,45 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>146.8</v>
+        <v>145.2</v>
       </c>
       <c r="G28" s="2">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="H28" s="3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I28" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="C29" s="3">
-        <v>21.32</v>
+        <v>22.11</v>
       </c>
       <c r="D29" s="3">
-        <v>35.43</v>
+        <v>32.32</v>
       </c>
       <c r="E29" s="3">
         <v>16.6</v>
       </c>
       <c r="F29" s="2">
-        <v>386.2</v>
+        <v>409.3</v>
       </c>
       <c r="G29" s="2">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="H29" s="3">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="I29" s="4">
-        <v>45.0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>13</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="kLBm4efxUTNkBLxt8zNXF9gf0+iHfzFagkt/EQ9wROI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="g/bw/egMhB2EFJmQ1pQHyq7IRvnL9Bko6ktodKOb35g="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
   <si>
     <t>Company</t>
   </si>
@@ -108,7 +108,7 @@
     <t>CVLG</t>
   </si>
   <si>
-    <t>(7/29/26) Covenant Logistics Group, Inc. (CVLG)</t>
+    <t>News Archive for CVLG</t>
   </si>
   <si>
     <t>Ennis, Inc.</t>
@@ -126,7 +126,7 @@
     <t>ESCA</t>
   </si>
   <si>
-    <t>(7/29/26) Escalade, Incorporated (ESCA)</t>
+    <t>News Archive for ESCA</t>
   </si>
   <si>
     <t>Euroseas Ltd.</t>
@@ -216,7 +216,7 @@
     <t>NCSM</t>
   </si>
   <si>
-    <t>(7/30/26) NCS Multistage Holdings, Inc. (NCSM)</t>
+    <t>News Archive for NCSM</t>
   </si>
   <si>
     <t>Oil States International, Inc.</t>
@@ -225,7 +225,7 @@
     <t>OIS</t>
   </si>
   <si>
-    <t>(7/30/26) Oil States International, Inc. (OIS)</t>
+    <t>News Archive for OIS</t>
   </si>
   <si>
     <t>Pangaea Logistics Solutions Ltd.</t>
@@ -261,7 +261,7 @@
     <t>RCKY</t>
   </si>
   <si>
-    <t>(7/28/26) Rocky Brands, Inc. (RCKY)</t>
+    <t>News Archive for RCKY</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -600,7 +600,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>4.93</v>
+        <v>5.25</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -609,16 +609,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>50.7</v>
+        <v>53.3</v>
       </c>
       <c r="G2" s="2">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="I2" s="4">
-        <v>50.0</v>
+        <v>49.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -635,7 +635,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3.91</v>
+        <v>4.03</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -644,16 +644,16 @@
         <v>3.41</v>
       </c>
       <c r="F3" s="2">
-        <v>154.8</v>
+        <v>168.5</v>
       </c>
       <c r="G3" s="2">
-        <v>16.3</v>
+        <v>17.7</v>
       </c>
       <c r="H3" s="3">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="I3" s="4">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -667,7 +667,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -676,16 +676,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>18.9</v>
+        <v>20.2</v>
       </c>
       <c r="G4" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>31.0</v>
+        <v>42.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -699,7 +699,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>19.17</v>
+        <v>20.22</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -708,16 +708,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>589.3</v>
+        <v>592.5</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="I5" s="4">
-        <v>49.0</v>
+        <v>42.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -731,25 +731,25 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>23.56</v>
+        <v>26.47</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
       </c>
       <c r="E6" s="3">
-        <v>16.37</v>
+        <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>199.8</v>
+        <v>209.2</v>
       </c>
       <c r="G6" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="H6" s="3">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="I6" s="4">
-        <v>78.0</v>
+        <v>74.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -763,7 +763,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>35.52</v>
+        <v>34.65</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -772,16 +772,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>927.6</v>
+        <v>879.5</v>
       </c>
       <c r="G7" s="2">
-        <v>466.5</v>
+        <v>442.3</v>
       </c>
       <c r="H7" s="3">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="I7" s="4">
-        <v>90.0</v>
+        <v>76.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>30</v>
@@ -795,25 +795,25 @@
         <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
       <c r="D8" s="3">
-        <v>22.36</v>
+        <v>22.55</v>
       </c>
       <c r="E8" s="3">
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>548.0</v>
+        <v>561.9</v>
       </c>
       <c r="G8" s="2">
-        <v>13.0</v>
+        <v>13.3</v>
       </c>
       <c r="H8" s="3">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="I8" s="4">
-        <v>68.0</v>
+        <v>61.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>33</v>
@@ -827,25 +827,25 @@
         <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>19.86</v>
+        <v>22.6</v>
       </c>
       <c r="D9" s="3">
-        <v>21.32</v>
+        <v>23.0</v>
       </c>
       <c r="E9" s="3">
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>287.4</v>
+        <v>306.2</v>
       </c>
       <c r="G9" s="2">
-        <v>18.6</v>
+        <v>13.3</v>
       </c>
       <c r="H9" s="3">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="I9" s="4">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
@@ -859,22 +859,22 @@
         <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>78.94</v>
+        <v>75.29</v>
       </c>
       <c r="D10" s="3">
-        <v>79.48</v>
+        <v>79.67</v>
       </c>
       <c r="E10" s="3">
-        <v>48.89</v>
+        <v>49.0</v>
       </c>
       <c r="F10" s="2">
-        <v>560.2</v>
+        <v>542.5</v>
       </c>
       <c r="G10" s="2">
-        <v>4.2</v>
+        <v>4.0</v>
       </c>
       <c r="H10" s="3">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="I10" s="4">
         <v>88.0</v>
@@ -891,25 +891,25 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>33.25</v>
+        <v>43.91</v>
       </c>
       <c r="D11" s="3">
         <v>39.07</v>
       </c>
       <c r="E11" s="3">
-        <v>14.51</v>
+        <v>15.13</v>
       </c>
       <c r="F11" s="2">
-        <v>242.2</v>
+        <v>272.1</v>
       </c>
       <c r="G11" s="2">
-        <v>12.2</v>
+        <v>13.7</v>
       </c>
       <c r="H11" s="3">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="I11" s="4">
-        <v>96.0</v>
+        <v>95.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>42</v>
@@ -923,25 +923,25 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>7.22</v>
+        <v>8.52</v>
       </c>
       <c r="F12" s="2">
-        <v>832.1</v>
+        <v>854.0</v>
       </c>
       <c r="G12" s="2">
-        <v>32.4</v>
+        <v>33.2</v>
       </c>
       <c r="H12" s="3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="I12" s="4">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>45</v>
@@ -955,7 +955,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>6.04</v>
+        <v>5.6</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -964,16 +964,19 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>244.0</v>
+        <v>238.0</v>
       </c>
       <c r="G13" s="2">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="H13" s="3">
-        <v>1.03</v>
+        <v>1.0</v>
       </c>
       <c r="I13" s="4">
-        <v>30.0</v>
+        <v>20.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -984,25 +987,25 @@
         <v>49</v>
       </c>
       <c r="C14" s="3">
-        <v>24.73</v>
+        <v>26.13</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>18.04</v>
+        <v>19.1</v>
       </c>
       <c r="F14" s="2">
-        <v>591.1</v>
+        <v>634.9</v>
       </c>
       <c r="G14" s="2">
-        <v>23.4</v>
+        <v>25.1</v>
       </c>
       <c r="H14" s="3">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="I14" s="4">
-        <v>33.0</v>
+        <v>30.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>50</v>
@@ -1016,7 +1019,7 @@
         <v>52</v>
       </c>
       <c r="C15" s="3">
-        <v>5.19</v>
+        <v>5.09</v>
       </c>
       <c r="D15" s="3">
         <v>6.61</v>
@@ -1025,16 +1028,16 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>180.2</v>
+        <v>182.3</v>
       </c>
       <c r="G15" s="2">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H15" s="3">
         <v>0.86</v>
       </c>
       <c r="I15" s="4">
-        <v>84.0</v>
+        <v>81.0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>13</v>
@@ -1057,16 +1060,16 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>95.4</v>
+        <v>95.7</v>
       </c>
       <c r="G16" s="2">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="H16" s="3">
         <v>1.05</v>
       </c>
       <c r="I16" s="4">
-        <v>71.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="17">
@@ -1077,25 +1080,25 @@
         <v>56</v>
       </c>
       <c r="C17" s="3">
-        <v>15.21</v>
+        <v>16.08</v>
       </c>
       <c r="D17" s="3">
         <v>19.64</v>
       </c>
       <c r="E17" s="3">
-        <v>7.74</v>
+        <v>8.09</v>
       </c>
       <c r="F17" s="2">
-        <v>482.7</v>
+        <v>497.6</v>
       </c>
       <c r="G17" s="2">
-        <v>22.0</v>
+        <v>22.7</v>
       </c>
       <c r="H17" s="3">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="I17" s="4">
-        <v>62.0</v>
+        <v>61.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>57</v>
@@ -1109,7 +1112,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="3">
-        <v>47.4</v>
+        <v>42.37</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1118,16 +1121,16 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>355.8</v>
+        <v>323.4</v>
       </c>
       <c r="G18" s="2">
-        <v>16.5</v>
+        <v>15.0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.81</v>
+        <v>0.74</v>
       </c>
       <c r="I18" s="4">
-        <v>48.0</v>
+        <v>23.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>13</v>
@@ -1144,25 +1147,25 @@
         <v>62</v>
       </c>
       <c r="C19" s="3">
-        <v>36.64</v>
+        <v>37.01</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
       </c>
       <c r="E19" s="3">
-        <v>22.72</v>
+        <v>23.17</v>
       </c>
       <c r="F19" s="2">
-        <v>453.5</v>
+        <v>459.9</v>
       </c>
       <c r="G19" s="2">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I19" s="4">
-        <v>60.0</v>
+        <v>56.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>63</v>
@@ -1176,25 +1179,25 @@
         <v>65</v>
       </c>
       <c r="C20" s="3">
-        <v>47.0</v>
+        <v>47.75</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
       </c>
       <c r="E20" s="3">
-        <v>29.48</v>
+        <v>31.46</v>
       </c>
       <c r="F20" s="2">
-        <v>118.9</v>
+        <v>127.7</v>
       </c>
       <c r="G20" s="2">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="H20" s="3">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="I20" s="4">
-        <v>66.0</v>
+        <v>81.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>66</v>
@@ -1208,25 +1211,25 @@
         <v>68</v>
       </c>
       <c r="C21" s="3">
-        <v>8.11</v>
+        <v>8.14</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
       </c>
       <c r="E21" s="3">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="F21" s="2">
-        <v>456.3</v>
+        <v>501.3</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="I21" s="4">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -1243,25 +1246,25 @@
         <v>71</v>
       </c>
       <c r="C22" s="3">
-        <v>7.61</v>
+        <v>7.42</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
       </c>
       <c r="E22" s="3">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="F22" s="2">
-        <v>493.2</v>
+        <v>486.7</v>
       </c>
       <c r="G22" s="2">
-        <v>14.0</v>
+        <v>13.8</v>
       </c>
       <c r="H22" s="3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="I22" s="4">
-        <v>38.0</v>
+        <v>33.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>72</v>
@@ -1275,22 +1278,22 @@
         <v>74</v>
       </c>
       <c r="C23" s="3">
-        <v>39.93</v>
+        <v>52.51</v>
       </c>
       <c r="D23" s="3">
-        <v>39.85</v>
+        <v>48.0</v>
       </c>
       <c r="E23" s="3">
-        <v>15.52</v>
+        <v>16.64</v>
       </c>
       <c r="F23" s="2">
-        <v>542.9</v>
+        <v>639.7</v>
       </c>
       <c r="G23" s="2">
-        <v>22.7</v>
+        <v>26.7</v>
       </c>
       <c r="H23" s="3">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="I23" s="4">
         <v>96.0</v>
@@ -1307,25 +1310,25 @@
         <v>77</v>
       </c>
       <c r="C24" s="3">
-        <v>27.38</v>
+        <v>28.12</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
       </c>
       <c r="E24" s="3">
-        <v>18.2</v>
+        <v>18.56</v>
       </c>
       <c r="F24" s="2">
-        <v>68.6</v>
+        <v>71.9</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>68.0</v>
+        <v>78.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1342,25 +1345,25 @@
         <v>80</v>
       </c>
       <c r="C25" s="3">
-        <v>48.84</v>
+        <v>49.23</v>
       </c>
       <c r="D25" s="3">
-        <v>50.73</v>
+        <v>53.01</v>
       </c>
       <c r="E25" s="3">
-        <v>24.68</v>
+        <v>25.76</v>
       </c>
       <c r="F25" s="2">
-        <v>365.9</v>
+        <v>372.4</v>
       </c>
       <c r="G25" s="2">
-        <v>19.8</v>
+        <v>13.1</v>
       </c>
       <c r="H25" s="3">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="I25" s="4">
-        <v>92.0</v>
+        <v>89.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>81</v>
@@ -1374,7 +1377,7 @@
         <v>83</v>
       </c>
       <c r="C26" s="3">
-        <v>14.83</v>
+        <v>13.86</v>
       </c>
       <c r="D26" s="3">
         <v>23.49</v>
@@ -1383,16 +1386,16 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>124.8</v>
+        <v>117.3</v>
       </c>
       <c r="G26" s="2">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="H26" s="3">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="I26" s="4">
-        <v>31.0</v>
+        <v>21.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>84</v>
@@ -1406,7 +1409,7 @@
         <v>86</v>
       </c>
       <c r="C27" s="3">
-        <v>8.92</v>
+        <v>8.59</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1415,16 +1418,16 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>328.7</v>
+        <v>322.4</v>
       </c>
       <c r="G27" s="2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H27" s="3">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="I27" s="4">
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1441,7 +1444,7 @@
         <v>89</v>
       </c>
       <c r="C28" s="3">
-        <v>23.72</v>
+        <v>24.9</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1450,16 +1453,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>145.2</v>
+        <v>151.3</v>
       </c>
       <c r="G28" s="2">
-        <v>31.1</v>
+        <v>32.4</v>
       </c>
       <c r="H28" s="3">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="I28" s="4">
-        <v>86.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -1470,25 +1473,28 @@
         <v>91</v>
       </c>
       <c r="C29" s="3">
-        <v>22.11</v>
+        <v>15.47</v>
       </c>
       <c r="D29" s="3">
         <v>32.32</v>
       </c>
       <c r="E29" s="3">
-        <v>16.6</v>
+        <v>14.35</v>
       </c>
       <c r="F29" s="2">
-        <v>409.3</v>
+        <v>274.9</v>
       </c>
       <c r="G29" s="2">
-        <v>45.9</v>
+        <v>30.8</v>
       </c>
       <c r="H29" s="3">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="I29" s="4">
-        <v>55.0</v>
+        <v>18.0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="g/bw/egMhB2EFJmQ1pQHyq7IRvnL9Bko6ktodKOb35g="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ppFZAT5VrpMYo+BoqqmzRnP7ulckzs9nj/3xDNpT/g4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
   <si>
     <t>Company</t>
   </si>
@@ -57,9 +57,6 @@
     <t>APT</t>
   </si>
   <si>
-    <t>Currently qualifies</t>
-  </si>
-  <si>
     <t>News Archive for APT</t>
   </si>
   <si>
@@ -69,7 +66,7 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>News Archive for AMPY</t>
+    <t>(8/10/26) Amplify Energy Corp. (AMPY)</t>
   </si>
   <si>
     <t>Castor Maritime Inc.</t>
@@ -93,6 +90,9 @@
     <t>TTM adjusted earnings positive</t>
   </si>
   <si>
+    <t>News Archive for CMCO</t>
+  </si>
+  <si>
     <t>Core Molding Technologies, Inc.</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>News Archive for ESEA</t>
+    <t>(8/13/26) Euroseas Ltd. (ESEA)</t>
   </si>
   <si>
     <t>Friedman Industries, Incorporated</t>
@@ -162,13 +162,16 @@
     <t>HDSN</t>
   </si>
   <si>
+    <t>News Archive for HDSN</t>
+  </si>
+  <si>
     <t>Kimball Electronics, Inc.</t>
   </si>
   <si>
     <t>KE</t>
   </si>
   <si>
-    <t>News Archive for KE</t>
+    <t>(8/12/26) Kimball Electronics, Inc. (KE)</t>
   </si>
   <si>
     <t>Kolibri Global Energy Inc.</t>
@@ -177,19 +180,25 @@
     <t>KGEI</t>
   </si>
   <si>
+    <t>(8/13/26) Kolibri Global Energy Inc. (KGEI)</t>
+  </si>
+  <si>
     <t>Mastech Digital, Inc.</t>
   </si>
   <si>
     <t>MHH</t>
   </si>
   <si>
+    <t>News Archive for MHH</t>
+  </si>
+  <si>
     <t>Mistras Group, Inc.</t>
   </si>
   <si>
     <t>MG</t>
   </si>
   <si>
-    <t>News Archive for MG</t>
+    <t>(8/10/26) Mistras Group, Inc. (MG)</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -207,7 +216,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>News Archive for NGS</t>
+    <t>(8/10/26) Natural Gas Services Group, Inc. (NGS)</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -234,7 +243,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>News Archive for PANL</t>
+    <t>(8/11/26) Pangaea Logistics Solutions Ltd. (PANL)</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -288,10 +297,16 @@
     <t>EML</t>
   </si>
   <si>
+    <t>(8/11/26) The Eastern Company (EML)</t>
+  </si>
+  <si>
     <t>USANA Health Sciences, Inc.</t>
   </si>
   <si>
     <t>USNA</t>
+  </si>
+  <si>
+    <t>News Archive for USNA</t>
   </si>
 </sst>
 </file>
@@ -600,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.25</v>
+        <v>5.43</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -609,65 +624,62 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>53.3</v>
+        <v>55.4</v>
       </c>
       <c r="G2" s="2">
-        <v>15.3</v>
+        <v>14.0</v>
       </c>
       <c r="H2" s="3">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>49.0</v>
-      </c>
-      <c r="J2" s="2" t="s">
+        <v>54.0</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C3" s="3">
-        <v>4.03</v>
+        <v>4.78</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
       </c>
       <c r="E3" s="3">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>168.5</v>
+        <v>198.2</v>
       </c>
       <c r="G3" s="2">
-        <v>17.7</v>
+        <v>9.7</v>
       </c>
       <c r="H3" s="3">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I3" s="4">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C4" s="3">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -676,30 +688,30 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>20.2</v>
+        <v>22.6</v>
       </c>
       <c r="G4" s="2">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>42.0</v>
+        <v>57.0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="C5" s="3">
-        <v>20.22</v>
+        <v>19.25</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -708,18 +720,21 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>592.5</v>
+        <v>549.4</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="I5" s="4">
+        <v>34.0</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="3">
-        <v>1.05</v>
-      </c>
-      <c r="I5" s="4">
-        <v>42.0</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -731,7 +746,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="3">
-        <v>26.47</v>
+        <v>25.54</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -740,16 +755,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>209.2</v>
+        <v>216.7</v>
       </c>
       <c r="G6" s="2">
-        <v>22.0</v>
+        <v>30.4</v>
       </c>
       <c r="H6" s="3">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="I6" s="4">
-        <v>74.0</v>
+        <v>77.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>27</v>
@@ -763,7 +778,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3">
-        <v>34.65</v>
+        <v>34.9</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -772,16 +787,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>879.5</v>
-      </c>
-      <c r="G7" s="2">
-        <v>442.3</v>
+        <v>885.7</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="H7" s="3">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="I7" s="4">
-        <v>76.0</v>
+        <v>74.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>30</v>
@@ -795,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="3">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="D8" s="3">
         <v>22.55</v>
@@ -804,16 +819,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>561.9</v>
+        <v>559.1</v>
       </c>
       <c r="G8" s="2">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="H8" s="3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I8" s="4">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>33</v>
@@ -827,25 +842,25 @@
         <v>35</v>
       </c>
       <c r="C9" s="3">
-        <v>22.6</v>
+        <v>20.07</v>
       </c>
       <c r="D9" s="3">
-        <v>23.0</v>
+        <v>23.07</v>
       </c>
       <c r="E9" s="3">
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>306.2</v>
+        <v>276.2</v>
       </c>
       <c r="G9" s="2">
-        <v>13.3</v>
+        <v>12.0</v>
       </c>
       <c r="H9" s="3">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="I9" s="4">
-        <v>90.0</v>
+        <v>84.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
@@ -859,25 +874,25 @@
         <v>38</v>
       </c>
       <c r="C10" s="3">
-        <v>75.29</v>
+        <v>73.8</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
       </c>
       <c r="E10" s="3">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>542.5</v>
+        <v>520.7</v>
       </c>
       <c r="G10" s="2">
-        <v>4.0</v>
+        <v>3.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="I10" s="4">
-        <v>88.0</v>
+        <v>80.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
@@ -891,25 +906,25 @@
         <v>41</v>
       </c>
       <c r="C11" s="3">
-        <v>43.91</v>
+        <v>45.85</v>
       </c>
       <c r="D11" s="3">
-        <v>39.07</v>
+        <v>46.69</v>
       </c>
       <c r="E11" s="3">
-        <v>15.13</v>
+        <v>16.46</v>
       </c>
       <c r="F11" s="2">
-        <v>272.1</v>
+        <v>330.7</v>
       </c>
       <c r="G11" s="2">
-        <v>13.7</v>
+        <v>11.9</v>
       </c>
       <c r="H11" s="3">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="I11" s="4">
-        <v>95.0</v>
+        <v>97.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>42</v>
@@ -923,7 +938,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="3">
-        <v>11.23</v>
+        <v>11.51</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -932,16 +947,16 @@
         <v>8.52</v>
       </c>
       <c r="F12" s="2">
-        <v>854.0</v>
+        <v>886.6</v>
       </c>
       <c r="G12" s="2">
-        <v>33.2</v>
+        <v>27.3</v>
       </c>
       <c r="H12" s="3">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="I12" s="4">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>45</v>
@@ -955,7 +970,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -964,62 +979,62 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>238.0</v>
+        <v>238.6</v>
       </c>
       <c r="G13" s="2">
-        <v>17.5</v>
+        <v>27.3</v>
       </c>
       <c r="H13" s="3">
-        <v>1.0</v>
+        <v>0.98</v>
       </c>
       <c r="I13" s="4">
-        <v>20.0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>21.0</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3">
-        <v>26.13</v>
+        <v>25.85</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
       </c>
       <c r="E14" s="3">
-        <v>19.1</v>
+        <v>21.01</v>
       </c>
       <c r="F14" s="2">
-        <v>634.9</v>
+        <v>621.7</v>
       </c>
       <c r="G14" s="2">
-        <v>25.1</v>
+        <v>24.6</v>
       </c>
       <c r="H14" s="3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="I14" s="4">
-        <v>30.0</v>
+        <v>57.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>5.09</v>
+        <v>5.77</v>
       </c>
       <c r="D15" s="3">
         <v>6.61</v>
@@ -1028,30 +1043,30 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>182.3</v>
+        <v>208.3</v>
       </c>
       <c r="G15" s="2">
-        <v>13.4</v>
+        <v>10.7</v>
       </c>
       <c r="H15" s="3">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="I15" s="4">
-        <v>81.0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>90.0</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C16" s="3">
-        <v>7.76</v>
+        <v>7.88</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1060,59 +1075,62 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>95.7</v>
+        <v>94.7</v>
       </c>
       <c r="G16" s="2">
-        <v>42.7</v>
+        <v>47.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="I16" s="4">
-        <v>69.0</v>
+        <v>63.0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3">
-        <v>16.08</v>
+        <v>18.1</v>
       </c>
       <c r="D17" s="3">
         <v>19.64</v>
       </c>
       <c r="E17" s="3">
-        <v>8.09</v>
+        <v>8.93</v>
       </c>
       <c r="F17" s="2">
-        <v>497.6</v>
+        <v>576.5</v>
       </c>
       <c r="G17" s="2">
-        <v>22.7</v>
+        <v>22.0</v>
       </c>
       <c r="H17" s="3">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="I17" s="4">
-        <v>61.0</v>
+        <v>78.0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C18" s="3">
-        <v>42.37</v>
+        <v>42.64</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
@@ -1121,132 +1139,129 @@
         <v>35.43</v>
       </c>
       <c r="F18" s="2">
-        <v>323.4</v>
+        <v>321.8</v>
       </c>
       <c r="G18" s="2">
-        <v>15.0</v>
+        <v>18.6</v>
       </c>
       <c r="H18" s="3">
         <v>0.74</v>
       </c>
       <c r="I18" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>21.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C19" s="3">
-        <v>37.01</v>
+        <v>37.97</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
       </c>
       <c r="E19" s="3">
-        <v>23.17</v>
+        <v>24.13</v>
       </c>
       <c r="F19" s="2">
-        <v>459.9</v>
+        <v>489.7</v>
       </c>
       <c r="G19" s="2">
-        <v>21.2</v>
+        <v>23.7</v>
       </c>
       <c r="H19" s="3">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I19" s="4">
-        <v>56.0</v>
+        <v>51.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3">
-        <v>47.75</v>
+        <v>51.69</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
       </c>
       <c r="E20" s="3">
-        <v>31.46</v>
+        <v>32.01</v>
       </c>
       <c r="F20" s="2">
-        <v>127.7</v>
+        <v>135.6</v>
       </c>
       <c r="G20" s="2">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="H20" s="3">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="I20" s="4">
         <v>81.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C21" s="3">
-        <v>8.14</v>
+        <v>8.93</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
       </c>
       <c r="E21" s="3">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="F21" s="2">
-        <v>501.3</v>
+        <v>538.7</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="I21" s="4">
+        <v>44.0</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="3">
-        <v>0.86</v>
-      </c>
-      <c r="I21" s="4">
-        <v>38.0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C22" s="3">
-        <v>7.42</v>
+        <v>7.44</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1255,62 +1270,62 @@
         <v>4.54</v>
       </c>
       <c r="F22" s="2">
-        <v>486.7</v>
+        <v>487.1</v>
       </c>
       <c r="G22" s="2">
-        <v>13.8</v>
+        <v>10.3</v>
       </c>
       <c r="H22" s="3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I22" s="4">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C23" s="3">
-        <v>52.51</v>
+        <v>49.4</v>
       </c>
       <c r="D23" s="3">
-        <v>48.0</v>
+        <v>53.3</v>
       </c>
       <c r="E23" s="3">
-        <v>16.64</v>
+        <v>18.06</v>
       </c>
       <c r="F23" s="2">
-        <v>639.7</v>
+        <v>691.9</v>
       </c>
       <c r="G23" s="2">
-        <v>26.7</v>
+        <v>25.5</v>
       </c>
       <c r="H23" s="3">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="I23" s="4">
-        <v>96.0</v>
+        <v>94.0</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C24" s="3">
-        <v>28.12</v>
+        <v>27.73</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1319,33 +1334,30 @@
         <v>18.56</v>
       </c>
       <c r="F24" s="2">
-        <v>71.9</v>
+        <v>69.3</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I24" s="4">
-        <v>78.0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>76.0</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3">
-        <v>49.23</v>
+        <v>47.53</v>
       </c>
       <c r="D25" s="3">
         <v>53.01</v>
@@ -1354,30 +1366,30 @@
         <v>25.76</v>
       </c>
       <c r="F25" s="2">
-        <v>372.4</v>
+        <v>356.1</v>
       </c>
       <c r="G25" s="2">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="H25" s="3">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="I25" s="4">
-        <v>89.0</v>
+        <v>86.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C26" s="3">
-        <v>13.86</v>
+        <v>13.98</v>
       </c>
       <c r="D26" s="3">
         <v>23.49</v>
@@ -1389,7 +1401,7 @@
         <v>117.3</v>
       </c>
       <c r="G26" s="2">
-        <v>14.8</v>
+        <v>19.2</v>
       </c>
       <c r="H26" s="3">
         <v>1.48</v>
@@ -1398,18 +1410,18 @@
         <v>21.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>8.59</v>
+        <v>9.46</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1418,33 +1430,30 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>322.4</v>
+        <v>351.8</v>
       </c>
       <c r="G27" s="2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="H27" s="3">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="I27" s="4">
-        <v>63.0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>72.0</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>24.9</v>
+        <v>25.41</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1453,48 +1462,51 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>151.3</v>
+        <v>152.9</v>
       </c>
       <c r="G28" s="2">
-        <v>32.4</v>
+        <v>18.5</v>
       </c>
       <c r="H28" s="3">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="I28" s="4">
-        <v>85.0</v>
+        <v>82.0</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>15.47</v>
+        <v>13.37</v>
       </c>
       <c r="D29" s="3">
         <v>32.32</v>
       </c>
       <c r="E29" s="3">
-        <v>14.35</v>
+        <v>13.31</v>
       </c>
       <c r="F29" s="2">
-        <v>274.9</v>
+        <v>247.0</v>
       </c>
       <c r="G29" s="2">
-        <v>30.8</v>
+        <v>27.7</v>
       </c>
       <c r="H29" s="3">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="I29" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>13</v>
+        <v>12.0</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ppFZAT5VrpMYo+BoqqmzRnP7ulckzs9nj/3xDNpT/g4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="DIzxa+ZSUz70QFe23seMMLniRfzCOOr+MmzNCH5DNVA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
   <si>
     <t>Company</t>
   </si>
@@ -57,6 +57,9 @@
     <t>APT</t>
   </si>
   <si>
+    <t>Currently qualifies</t>
+  </si>
+  <si>
     <t>News Archive for APT</t>
   </si>
   <si>
@@ -66,7 +69,7 @@
     <t>AMPY</t>
   </si>
   <si>
-    <t>(8/10/26) Amplify Energy Corp. (AMPY)</t>
+    <t>News Archive for AMPY</t>
   </si>
   <si>
     <t>Castor Maritime Inc.</t>
@@ -135,7 +138,7 @@
     <t>ESEA</t>
   </si>
   <si>
-    <t>(8/13/26) Euroseas Ltd. (ESEA)</t>
+    <t>News Archive for ESEA</t>
   </si>
   <si>
     <t>Friedman Industries, Incorporated</t>
@@ -171,7 +174,7 @@
     <t>KE</t>
   </si>
   <si>
-    <t>(8/12/26) Kimball Electronics, Inc. (KE)</t>
+    <t>News Archive for KE</t>
   </si>
   <si>
     <t>Kolibri Global Energy Inc.</t>
@@ -180,7 +183,7 @@
     <t>KGEI</t>
   </si>
   <si>
-    <t>(8/13/26) Kolibri Global Energy Inc. (KGEI)</t>
+    <t>News Archive for KGEI</t>
   </si>
   <si>
     <t>Mastech Digital, Inc.</t>
@@ -198,7 +201,10 @@
     <t>MG</t>
   </si>
   <si>
-    <t>(8/10/26) Mistras Group, Inc. (MG)</t>
+    <t>Approaching value limit</t>
+  </si>
+  <si>
+    <t>News Archive for MG</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -216,7 +222,7 @@
     <t>NGS</t>
   </si>
   <si>
-    <t>(8/10/26) Natural Gas Services Group, Inc. (NGS)</t>
+    <t>News Archive for NGS</t>
   </si>
   <si>
     <t>NCS Multistage Holdings, Inc.</t>
@@ -243,7 +249,7 @@
     <t>PANL</t>
   </si>
   <si>
-    <t>(8/11/26) Pangaea Logistics Solutions Ltd. (PANL)</t>
+    <t>News Archive for PANL</t>
   </si>
   <si>
     <t>Park-Ohio Holdings Corp.</t>
@@ -297,7 +303,7 @@
     <t>EML</t>
   </si>
   <si>
-    <t>(8/11/26) The Eastern Company (EML)</t>
+    <t>News Archive for EML</t>
   </si>
   <si>
     <t>USANA Health Sciences, Inc.</t>
@@ -615,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.43</v>
+        <v>5.21</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -624,30 +630,33 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>55.4</v>
+        <v>53.2</v>
       </c>
       <c r="G2" s="2">
-        <v>14.0</v>
+        <v>13.4</v>
       </c>
       <c r="H2" s="3">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>54.0</v>
+        <v>49.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.78</v>
+        <v>4.82</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -656,30 +665,30 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>198.2</v>
+        <v>199.8</v>
       </c>
       <c r="G3" s="2">
-        <v>9.7</v>
+        <v>9.8</v>
       </c>
       <c r="H3" s="3">
         <v>0.45</v>
       </c>
       <c r="I3" s="4">
-        <v>33.0</v>
+        <v>28.0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -688,30 +697,30 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>22.6</v>
+        <v>23.9</v>
       </c>
       <c r="G4" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I4" s="4">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>19.25</v>
+        <v>17.62</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -720,33 +729,33 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>549.4</v>
+        <v>502.9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="I5" s="4">
-        <v>34.0</v>
+        <v>37.0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>25.54</v>
+        <v>26.15</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -755,30 +764,30 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>216.7</v>
+        <v>223.9</v>
       </c>
       <c r="G6" s="2">
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="H6" s="3">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="I6" s="4">
-        <v>77.0</v>
+        <v>83.0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -787,62 +796,62 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>885.7</v>
+        <v>893.3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I7" s="4">
-        <v>74.0</v>
+        <v>72.0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>22.1</v>
+        <v>21.57</v>
       </c>
       <c r="D8" s="3">
-        <v>22.55</v>
+        <v>22.94</v>
       </c>
       <c r="E8" s="3">
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>559.1</v>
+        <v>545.7</v>
       </c>
       <c r="G8" s="2">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="H8" s="3">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="I8" s="4">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>20.07</v>
+        <v>21.12</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -851,30 +860,30 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>276.2</v>
+        <v>290.7</v>
       </c>
       <c r="G9" s="2">
-        <v>12.0</v>
+        <v>12.6</v>
       </c>
       <c r="H9" s="3">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="I9" s="4">
-        <v>84.0</v>
+        <v>89.0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>73.8</v>
+        <v>75.03</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -883,94 +892,94 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>520.7</v>
+        <v>529.4</v>
       </c>
       <c r="G10" s="2">
         <v>3.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I10" s="4">
-        <v>80.0</v>
+        <v>76.0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>45.85</v>
+        <v>41.71</v>
       </c>
       <c r="D11" s="3">
-        <v>46.69</v>
+        <v>48.77</v>
       </c>
       <c r="E11" s="3">
-        <v>16.46</v>
+        <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>330.7</v>
+        <v>300.8</v>
       </c>
       <c r="G11" s="2">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="H11" s="3">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="I11" s="4">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>11.51</v>
+        <v>10.5</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>8.52</v>
+        <v>9.1</v>
       </c>
       <c r="F12" s="2">
-        <v>886.6</v>
+        <v>808.8</v>
       </c>
       <c r="G12" s="2">
-        <v>27.3</v>
+        <v>24.9</v>
       </c>
       <c r="H12" s="3">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="I12" s="4">
-        <v>30.0</v>
+        <v>16.0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.67</v>
+        <v>5.63</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -979,30 +988,33 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>238.6</v>
+        <v>237.0</v>
       </c>
       <c r="G13" s="2">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="H13" s="3">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I13" s="4">
-        <v>21.0</v>
+        <v>20.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>25.85</v>
+        <v>23.11</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1011,30 +1023,30 @@
         <v>21.01</v>
       </c>
       <c r="F14" s="2">
-        <v>621.7</v>
+        <v>553.9</v>
       </c>
       <c r="G14" s="2">
-        <v>24.6</v>
+        <v>20.5</v>
       </c>
       <c r="H14" s="3">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="I14" s="4">
-        <v>57.0</v>
+        <v>37.0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>5.77</v>
+        <v>6.09</v>
       </c>
       <c r="D15" s="3">
         <v>6.61</v>
@@ -1043,30 +1055,33 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>208.3</v>
+        <v>219.1</v>
       </c>
       <c r="G15" s="2">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="H15" s="3">
-        <v>0.95</v>
+        <v>1.0</v>
       </c>
       <c r="I15" s="4">
         <v>90.0</v>
       </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="K15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.88</v>
+        <v>7.5</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1075,193 +1090,196 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>94.7</v>
+        <v>90.1</v>
       </c>
       <c r="G16" s="2">
-        <v>47.2</v>
+        <v>44.9</v>
       </c>
       <c r="H16" s="3">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="I16" s="4">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>18.1</v>
+        <v>18.96</v>
       </c>
       <c r="D17" s="3">
-        <v>19.64</v>
+        <v>20.2</v>
       </c>
       <c r="E17" s="3">
-        <v>8.93</v>
+        <v>9.24</v>
       </c>
       <c r="F17" s="2">
-        <v>576.5</v>
+        <v>603.9</v>
       </c>
       <c r="G17" s="2">
-        <v>22.0</v>
+        <v>23.1</v>
       </c>
       <c r="H17" s="3">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I17" s="4">
-        <v>78.0</v>
+        <v>79.0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>42.64</v>
+        <v>41.0</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
       </c>
       <c r="E18" s="3">
-        <v>35.43</v>
+        <v>36.38</v>
       </c>
       <c r="F18" s="2">
-        <v>321.8</v>
+        <v>309.4</v>
       </c>
       <c r="G18" s="2">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
       <c r="H18" s="3">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="I18" s="4">
-        <v>21.0</v>
+        <v>18.0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>37.97</v>
+        <v>35.49</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
       </c>
       <c r="E19" s="3">
-        <v>24.13</v>
+        <v>25.05</v>
       </c>
       <c r="F19" s="2">
-        <v>489.7</v>
+        <v>457.8</v>
       </c>
       <c r="G19" s="2">
-        <v>23.7</v>
+        <v>22.2</v>
       </c>
       <c r="H19" s="3">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="I19" s="4">
-        <v>51.0</v>
+        <v>39.0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>51.69</v>
+        <v>49.83</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
       </c>
       <c r="E20" s="3">
-        <v>32.01</v>
+        <v>34.06</v>
       </c>
       <c r="F20" s="2">
-        <v>135.6</v>
+        <v>130.8</v>
       </c>
       <c r="G20" s="2">
-        <v>10.2</v>
+        <v>9.8</v>
       </c>
       <c r="H20" s="3">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="I20" s="4">
-        <v>81.0</v>
+        <v>77.0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>8.93</v>
+        <v>8.65</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
       </c>
       <c r="E21" s="3">
-        <v>4.92</v>
+        <v>5.12</v>
       </c>
       <c r="F21" s="2">
-        <v>538.7</v>
+        <v>521.8</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="4">
-        <v>44.0</v>
+        <v>15.0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>7.44</v>
+        <v>8.14</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1270,30 +1288,30 @@
         <v>4.54</v>
       </c>
       <c r="F22" s="2">
-        <v>487.1</v>
+        <v>533.0</v>
       </c>
       <c r="G22" s="2">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="H22" s="3">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="I22" s="4">
         <v>31.0</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>49.4</v>
+        <v>45.7</v>
       </c>
       <c r="D23" s="3">
         <v>53.3</v>
@@ -1302,94 +1320,97 @@
         <v>18.06</v>
       </c>
       <c r="F23" s="2">
-        <v>691.9</v>
+        <v>640.0</v>
       </c>
       <c r="G23" s="2">
-        <v>25.5</v>
+        <v>23.6</v>
       </c>
       <c r="H23" s="3">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="I23" s="4">
-        <v>94.0</v>
+        <v>93.0</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>27.73</v>
+        <v>26.79</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
       </c>
       <c r="E24" s="3">
-        <v>18.56</v>
+        <v>19.04</v>
       </c>
       <c r="F24" s="2">
-        <v>69.3</v>
+        <v>66.9</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="I24" s="4">
-        <v>76.0</v>
+        <v>72.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>47.53</v>
+        <v>46.79</v>
       </c>
       <c r="D25" s="3">
         <v>53.01</v>
       </c>
       <c r="E25" s="3">
-        <v>25.76</v>
+        <v>26.29</v>
       </c>
       <c r="F25" s="2">
-        <v>356.1</v>
+        <v>350.5</v>
       </c>
       <c r="G25" s="2">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="H25" s="3">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="I25" s="4">
-        <v>86.0</v>
+        <v>84.0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>13.98</v>
+        <v>12.41</v>
       </c>
       <c r="D26" s="3">
         <v>23.49</v>
@@ -1398,30 +1419,30 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>117.3</v>
+        <v>104.2</v>
       </c>
       <c r="G26" s="2">
-        <v>19.2</v>
+        <v>17.0</v>
       </c>
       <c r="H26" s="3">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="I26" s="4">
-        <v>21.0</v>
+        <v>18.0</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>9.46</v>
+        <v>9.63</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1430,30 +1451,33 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>351.8</v>
+        <v>358.1</v>
       </c>
       <c r="G27" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H27" s="3">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="I27" s="4">
-        <v>72.0</v>
+        <v>69.0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>25.41</v>
+        <v>25.1</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1462,51 +1486,51 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>152.9</v>
+        <v>151.0</v>
       </c>
       <c r="G28" s="2">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="H28" s="3">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="I28" s="4">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>13.37</v>
+        <v>13.55</v>
       </c>
       <c r="D29" s="3">
         <v>32.32</v>
       </c>
       <c r="E29" s="3">
-        <v>13.31</v>
+        <v>12.57</v>
       </c>
       <c r="F29" s="2">
-        <v>247.0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>27.7</v>
+        <v>250.4</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="H29" s="3">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="I29" s="4">
         <v>12.0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="DIzxa+ZSUz70QFe23seMMLniRfzCOOr+MmzNCH5DNVA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="LzfPeTBKJbAnveH24x1EcBOxRAO74i0a6bpGov6OGDU="/>
     </ext>
   </extLst>
 </workbook>
@@ -621,7 +621,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.21</v>
+        <v>5.35</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -630,16 +630,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>53.2</v>
+        <v>55.8</v>
       </c>
       <c r="G2" s="2">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>49.0</v>
+        <v>58.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.82</v>
+        <v>4.76</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -665,16 +665,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>199.8</v>
+        <v>195.3</v>
       </c>
       <c r="G3" s="2">
-        <v>9.8</v>
+        <v>9.5</v>
       </c>
       <c r="H3" s="3">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I3" s="4">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -688,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -697,16 +697,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="G4" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H4" s="3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>55.0</v>
+        <v>60.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -720,7 +720,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>17.62</v>
+        <v>18.0</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -729,16 +729,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>502.9</v>
+        <v>524.9</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="I5" s="4">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -755,7 +755,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>26.15</v>
+        <v>25.0</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -764,16 +764,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>223.9</v>
+        <v>214.1</v>
       </c>
       <c r="G6" s="2">
-        <v>31.2</v>
+        <v>29.8</v>
       </c>
       <c r="H6" s="3">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="I6" s="4">
-        <v>83.0</v>
+        <v>81.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -787,7 +787,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>35.2</v>
+        <v>34.98</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -796,16 +796,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>893.3</v>
+        <v>901.7</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I7" s="4">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -819,7 +819,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>21.57</v>
+        <v>21.52</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -828,16 +828,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>545.7</v>
+        <v>543.2</v>
       </c>
       <c r="G8" s="2">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H8" s="3">
         <v>1.75</v>
       </c>
       <c r="I8" s="4">
-        <v>55.0</v>
+        <v>51.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -851,7 +851,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>21.12</v>
+        <v>20.18</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -860,16 +860,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>290.7</v>
+        <v>276.0</v>
       </c>
       <c r="G9" s="2">
-        <v>12.6</v>
+        <v>12.0</v>
       </c>
       <c r="H9" s="3">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="I9" s="4">
-        <v>89.0</v>
+        <v>83.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -883,7 +883,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>75.03</v>
+        <v>76.63</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -892,16 +892,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>529.4</v>
+        <v>539.4</v>
       </c>
       <c r="G10" s="2">
-        <v>3.9</v>
+        <v>4.0</v>
       </c>
       <c r="H10" s="3">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I10" s="4">
-        <v>76.0</v>
+        <v>70.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -915,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>41.71</v>
+        <v>43.72</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -924,13 +924,13 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>300.8</v>
+        <v>323.4</v>
       </c>
       <c r="G11" s="2">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="H11" s="3">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="I11" s="4">
         <v>98.0</v>
@@ -947,7 +947,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>10.5</v>
+        <v>9.94</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -956,16 +956,16 @@
         <v>9.1</v>
       </c>
       <c r="F12" s="2">
-        <v>808.8</v>
+        <v>798.0</v>
       </c>
       <c r="G12" s="2">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="H12" s="3">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="I12" s="4">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -979,7 +979,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.63</v>
+        <v>5.43</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -988,16 +988,16 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>237.0</v>
+        <v>230.6</v>
       </c>
       <c r="G13" s="2">
-        <v>27.1</v>
+        <v>26.3</v>
       </c>
       <c r="H13" s="3">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="I13" s="4">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1014,7 +1014,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>23.11</v>
+        <v>23.46</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1023,16 +1023,16 @@
         <v>21.01</v>
       </c>
       <c r="F14" s="2">
-        <v>553.9</v>
+        <v>577.4</v>
       </c>
       <c r="G14" s="2">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="H14" s="3">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="I14" s="4">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1046,7 +1046,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>6.09</v>
+        <v>5.84</v>
       </c>
       <c r="D15" s="3">
         <v>6.61</v>
@@ -1055,13 +1055,13 @@
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>219.1</v>
+        <v>210.0</v>
       </c>
       <c r="G15" s="2">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="H15" s="3">
-        <v>1.0</v>
+        <v>0.96</v>
       </c>
       <c r="I15" s="4">
         <v>90.0</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1090,16 +1090,16 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>90.1</v>
+        <v>88.5</v>
       </c>
       <c r="G16" s="2">
-        <v>44.9</v>
+        <v>44.1</v>
       </c>
       <c r="H16" s="3">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I16" s="4">
-        <v>65.0</v>
+        <v>79.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1113,25 +1113,25 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>18.96</v>
+        <v>18.49</v>
       </c>
       <c r="D17" s="3">
         <v>20.2</v>
       </c>
       <c r="E17" s="3">
-        <v>9.24</v>
+        <v>9.35</v>
       </c>
       <c r="F17" s="2">
-        <v>603.9</v>
+        <v>613.1</v>
       </c>
       <c r="G17" s="2">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="H17" s="3">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I17" s="4">
-        <v>79.0</v>
+        <v>77.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>61</v>
@@ -1148,25 +1148,25 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>41.0</v>
+        <v>43.06</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
       </c>
       <c r="E18" s="3">
-        <v>36.38</v>
+        <v>37.76</v>
       </c>
       <c r="F18" s="2">
-        <v>309.4</v>
+        <v>325.5</v>
       </c>
       <c r="G18" s="2">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="H18" s="3">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="I18" s="4">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1180,25 +1180,25 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>35.49</v>
+        <v>34.69</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
       </c>
       <c r="E19" s="3">
-        <v>25.05</v>
+        <v>25.49</v>
       </c>
       <c r="F19" s="2">
-        <v>457.8</v>
+        <v>456.6</v>
       </c>
       <c r="G19" s="2">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="H19" s="3">
         <v>1.55</v>
       </c>
       <c r="I19" s="4">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>68</v>
@@ -1212,7 +1212,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>49.83</v>
+        <v>51.64</v>
       </c>
       <c r="D20" s="3">
         <v>87.36</v>
@@ -1221,16 +1221,16 @@
         <v>34.06</v>
       </c>
       <c r="F20" s="2">
-        <v>130.8</v>
+        <v>133.3</v>
       </c>
       <c r="G20" s="2">
-        <v>9.8</v>
+        <v>10.0</v>
       </c>
       <c r="H20" s="3">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I20" s="4">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1244,16 +1244,16 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>8.65</v>
+        <v>8.61</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
       </c>
       <c r="E21" s="3">
-        <v>5.12</v>
+        <v>5.37</v>
       </c>
       <c r="F21" s="2">
-        <v>521.8</v>
+        <v>523.0</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
@@ -1262,7 +1262,7 @@
         <v>0.9</v>
       </c>
       <c r="I21" s="4">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -1279,7 +1279,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>8.14</v>
+        <v>8.06</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1288,16 +1288,16 @@
         <v>4.54</v>
       </c>
       <c r="F22" s="2">
-        <v>533.0</v>
+        <v>517.2</v>
       </c>
       <c r="G22" s="2">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="H22" s="3">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="I22" s="4">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1311,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>45.7</v>
+        <v>45.76</v>
       </c>
       <c r="D23" s="3">
         <v>53.3</v>
@@ -1320,16 +1320,16 @@
         <v>18.06</v>
       </c>
       <c r="F23" s="2">
-        <v>640.0</v>
+        <v>663.7</v>
       </c>
       <c r="G23" s="2">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="H23" s="3">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="I23" s="4">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1343,22 +1343,22 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>26.79</v>
+        <v>27.13</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
       </c>
       <c r="E24" s="3">
-        <v>19.04</v>
+        <v>19.31</v>
       </c>
       <c r="F24" s="2">
-        <v>66.9</v>
+        <v>67.5</v>
       </c>
       <c r="G24" s="2">
         <v>0.7</v>
       </c>
       <c r="H24" s="3">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="I24" s="4">
         <v>72.0</v>
@@ -1378,7 +1378,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>46.79</v>
+        <v>45.65</v>
       </c>
       <c r="D25" s="3">
         <v>53.01</v>
@@ -1387,16 +1387,16 @@
         <v>26.29</v>
       </c>
       <c r="F25" s="2">
-        <v>350.5</v>
+        <v>339.2</v>
       </c>
       <c r="G25" s="2">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="H25" s="3">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="I25" s="4">
-        <v>84.0</v>
+        <v>41.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1410,7 +1410,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>12.41</v>
+        <v>12.34</v>
       </c>
       <c r="D26" s="3">
         <v>23.49</v>
@@ -1419,16 +1419,16 @@
         <v>10.72</v>
       </c>
       <c r="F26" s="2">
-        <v>104.2</v>
+        <v>102.0</v>
       </c>
       <c r="G26" s="2">
-        <v>17.0</v>
+        <v>16.6</v>
       </c>
       <c r="H26" s="3">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="I26" s="4">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1442,7 +1442,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>9.63</v>
+        <v>9.49</v>
       </c>
       <c r="D27" s="3">
         <v>10.55</v>
@@ -1451,16 +1451,16 @@
         <v>6.12</v>
       </c>
       <c r="F27" s="2">
-        <v>358.1</v>
+        <v>352.5</v>
       </c>
       <c r="G27" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H27" s="3">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I27" s="4">
-        <v>69.0</v>
+        <v>59.0</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>13</v>
@@ -1477,7 +1477,7 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>25.1</v>
+        <v>26.32</v>
       </c>
       <c r="D28" s="3">
         <v>29.91</v>
@@ -1486,16 +1486,16 @@
         <v>17.61</v>
       </c>
       <c r="F28" s="2">
-        <v>151.0</v>
+        <v>158.6</v>
       </c>
       <c r="G28" s="2">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="H28" s="3">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="I28" s="4">
-        <v>83.0</v>
+        <v>86.0</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>95</v>
@@ -1509,25 +1509,25 @@
         <v>97</v>
       </c>
       <c r="C29" s="3">
-        <v>13.55</v>
+        <v>14.04</v>
       </c>
       <c r="D29" s="3">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="E29" s="3">
         <v>12.57</v>
       </c>
       <c r="F29" s="2">
-        <v>250.4</v>
+        <v>260.5</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I29" s="4">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>98</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="LzfPeTBKJbAnveH24x1EcBOxRAO74i0a6bpGov6OGDU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="huVM3ZJx/4y5dIuPKBB2dlYFlDsJV39Pq+HAKzO1qA4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
   <si>
     <t>Company</t>
   </si>
@@ -225,15 +225,6 @@
     <t>News Archive for NGS</t>
   </si>
   <si>
-    <t>NCS Multistage Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>NCSM</t>
-  </si>
-  <si>
-    <t>News Archive for NCSM</t>
-  </si>
-  <si>
     <t>Oil States International, Inc.</t>
   </si>
   <si>
@@ -267,7 +258,7 @@
     <t>RGS</t>
   </si>
   <si>
-    <t>News Archive for RGS</t>
+    <t>(9/1/26) Regis Corporation (RGS)</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -294,7 +285,7 @@
     <t>GASS</t>
   </si>
   <si>
-    <t>News Archive for GASS</t>
+    <t>(9/2/26) StealthGas Inc. (GASS)</t>
   </si>
   <si>
     <t>The Eastern Company</t>
@@ -621,7 +612,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -630,16 +621,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>55.8</v>
+        <v>54.0</v>
       </c>
       <c r="G2" s="2">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="H2" s="3">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="I2" s="4">
-        <v>58.0</v>
+        <v>47.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -656,7 +647,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.76</v>
+        <v>4.9</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -665,16 +656,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>195.3</v>
+        <v>203.1</v>
       </c>
       <c r="G3" s="2">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H3" s="3">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="I3" s="4">
-        <v>30.0</v>
+        <v>23.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -688,7 +679,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="D4" s="3">
         <v>2.65</v>
@@ -697,16 +688,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="G4" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>60.0</v>
+        <v>56.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -720,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>18.0</v>
+        <v>18.84</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -729,16 +720,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>524.9</v>
+        <v>520.9</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I5" s="4">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -755,7 +746,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>25.0</v>
+        <v>24.12</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -764,16 +755,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>214.1</v>
+        <v>205.9</v>
       </c>
       <c r="G6" s="2">
-        <v>29.8</v>
+        <v>28.7</v>
       </c>
       <c r="H6" s="3">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="I6" s="4">
-        <v>81.0</v>
+        <v>76.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -787,7 +778,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>34.98</v>
+        <v>35.05</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -796,16 +787,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>901.7</v>
+        <v>872.5</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="I7" s="4">
-        <v>75.0</v>
+        <v>70.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -819,7 +810,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>21.52</v>
+        <v>21.46</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -828,16 +819,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>543.2</v>
+        <v>538.9</v>
       </c>
       <c r="G8" s="2">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H8" s="3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="I8" s="4">
-        <v>51.0</v>
+        <v>46.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -851,7 +842,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>20.18</v>
+        <v>20.87</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -860,16 +851,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>276.0</v>
+        <v>279.4</v>
       </c>
       <c r="G9" s="2">
-        <v>12.0</v>
+        <v>12.1</v>
       </c>
       <c r="H9" s="3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="I9" s="4">
-        <v>83.0</v>
+        <v>86.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -883,7 +874,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>76.63</v>
+        <v>76.35</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -892,16 +883,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>539.4</v>
+        <v>542.8</v>
       </c>
       <c r="G10" s="2">
         <v>4.0</v>
       </c>
       <c r="H10" s="3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I10" s="4">
-        <v>70.0</v>
+        <v>63.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -915,7 +906,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>43.72</v>
+        <v>45.6</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -924,13 +915,13 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>323.4</v>
+        <v>327.2</v>
       </c>
       <c r="G11" s="2">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="H11" s="3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I11" s="4">
         <v>98.0</v>
@@ -947,25 +938,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>9.94</v>
+        <v>10.12</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="F12" s="2">
-        <v>798.0</v>
+        <v>793.4</v>
       </c>
       <c r="G12" s="2">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="H12" s="3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="I12" s="4">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -979,7 +970,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.43</v>
+        <v>5.35</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -988,16 +979,16 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>230.6</v>
+        <v>221.0</v>
       </c>
       <c r="G13" s="2">
-        <v>26.3</v>
+        <v>25.2</v>
       </c>
       <c r="H13" s="3">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="I13" s="4">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1014,7 +1005,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>23.46</v>
+        <v>25.03</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1023,16 +1014,16 @@
         <v>21.01</v>
       </c>
       <c r="F14" s="2">
-        <v>577.4</v>
+        <v>585.8</v>
       </c>
       <c r="G14" s="2">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="H14" s="3">
-        <v>0.99</v>
+        <v>1.0</v>
       </c>
       <c r="I14" s="4">
-        <v>39.0</v>
+        <v>46.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1046,28 +1037,25 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>5.84</v>
+        <v>6.15</v>
       </c>
       <c r="D15" s="3">
-        <v>6.61</v>
+        <v>6.62</v>
       </c>
       <c r="E15" s="3">
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>210.0</v>
+        <v>224.2</v>
       </c>
       <c r="G15" s="2">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="H15" s="3">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="I15" s="4">
-        <v>90.0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>83.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>55</v>
@@ -1081,7 +1069,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1090,16 +1078,16 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="G16" s="2">
-        <v>44.1</v>
+        <v>44.0</v>
       </c>
       <c r="H16" s="3">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I16" s="4">
-        <v>79.0</v>
+        <v>63.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>58</v>
@@ -1113,7 +1101,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>18.49</v>
+        <v>19.12</v>
       </c>
       <c r="D17" s="3">
         <v>20.2</v>
@@ -1122,16 +1110,16 @@
         <v>9.35</v>
       </c>
       <c r="F17" s="2">
-        <v>613.1</v>
+        <v>607.1</v>
       </c>
       <c r="G17" s="2">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="H17" s="3">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="I17" s="4">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>61</v>
@@ -1148,25 +1136,25 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>43.06</v>
+        <v>41.93</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
       </c>
       <c r="E18" s="3">
-        <v>37.76</v>
+        <v>37.91</v>
       </c>
       <c r="F18" s="2">
-        <v>325.5</v>
+        <v>308.3</v>
       </c>
       <c r="G18" s="2">
-        <v>18.8</v>
+        <v>17.8</v>
       </c>
       <c r="H18" s="3">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="I18" s="4">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1180,25 +1168,25 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>34.69</v>
+        <v>36.33</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
       </c>
       <c r="E19" s="3">
-        <v>25.49</v>
+        <v>25.53</v>
       </c>
       <c r="F19" s="2">
-        <v>456.6</v>
+        <v>460.1</v>
       </c>
       <c r="G19" s="2">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="H19" s="3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I19" s="4">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>68</v>
@@ -1212,25 +1200,28 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>51.64</v>
+        <v>8.76</v>
       </c>
       <c r="D20" s="3">
-        <v>87.36</v>
+        <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>34.06</v>
+        <v>5.37</v>
       </c>
       <c r="F20" s="2">
-        <v>133.3</v>
-      </c>
-      <c r="G20" s="2">
-        <v>10.0</v>
+        <v>534.5</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="H20" s="3">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="I20" s="4">
-        <v>79.0</v>
+        <v>16.0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>71</v>
@@ -1244,28 +1235,25 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>8.61</v>
+        <v>8.55</v>
       </c>
       <c r="D21" s="3">
-        <v>14.5</v>
+        <v>9.39</v>
       </c>
       <c r="E21" s="3">
-        <v>5.37</v>
+        <v>4.54</v>
       </c>
       <c r="F21" s="2">
-        <v>523.0</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>23</v>
+        <v>542.8</v>
+      </c>
+      <c r="G21" s="2">
+        <v>11.4</v>
       </c>
       <c r="H21" s="3">
-        <v>0.9</v>
+        <v>1.21</v>
       </c>
       <c r="I21" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>39.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1279,25 +1267,25 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>8.06</v>
+        <v>46.48</v>
       </c>
       <c r="D22" s="3">
-        <v>9.39</v>
+        <v>53.3</v>
       </c>
       <c r="E22" s="3">
-        <v>4.54</v>
+        <v>18.06</v>
       </c>
       <c r="F22" s="2">
-        <v>517.2</v>
+        <v>629.2</v>
       </c>
       <c r="G22" s="2">
-        <v>10.9</v>
+        <v>23.2</v>
       </c>
       <c r="H22" s="3">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="I22" s="4">
-        <v>29.0</v>
+        <v>92.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1311,25 +1299,28 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>45.76</v>
+        <v>28.5</v>
       </c>
       <c r="D23" s="3">
-        <v>53.3</v>
+        <v>31.5</v>
       </c>
       <c r="E23" s="3">
-        <v>18.06</v>
+        <v>19.31</v>
       </c>
       <c r="F23" s="2">
-        <v>663.7</v>
+        <v>72.0</v>
       </c>
       <c r="G23" s="2">
-        <v>24.4</v>
+        <v>12.0</v>
       </c>
       <c r="H23" s="3">
-        <v>1.7</v>
+        <v>0.37</v>
       </c>
       <c r="I23" s="4">
-        <v>94.0</v>
+        <v>82.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>80</v>
@@ -1343,28 +1334,25 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>27.13</v>
+        <v>44.14</v>
       </c>
       <c r="D24" s="3">
-        <v>31.5</v>
+        <v>53.01</v>
       </c>
       <c r="E24" s="3">
-        <v>19.31</v>
+        <v>26.29</v>
       </c>
       <c r="F24" s="2">
-        <v>67.5</v>
+        <v>326.0</v>
       </c>
       <c r="G24" s="2">
-        <v>0.7</v>
+        <v>11.4</v>
       </c>
       <c r="H24" s="3">
-        <v>0.36</v>
+        <v>1.24</v>
       </c>
       <c r="I24" s="4">
-        <v>72.0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>41.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>83</v>
@@ -1378,25 +1366,25 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>45.65</v>
+        <v>11.21</v>
       </c>
       <c r="D25" s="3">
-        <v>53.01</v>
+        <v>23.49</v>
       </c>
       <c r="E25" s="3">
-        <v>26.29</v>
+        <v>10.72</v>
       </c>
       <c r="F25" s="2">
-        <v>339.2</v>
+        <v>92.1</v>
       </c>
       <c r="G25" s="2">
-        <v>11.9</v>
+        <v>15.0</v>
       </c>
       <c r="H25" s="3">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="I25" s="4">
-        <v>41.0</v>
+        <v>19.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1410,25 +1398,28 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>12.34</v>
+        <v>9.29</v>
       </c>
       <c r="D26" s="3">
-        <v>23.49</v>
+        <v>10.55</v>
       </c>
       <c r="E26" s="3">
-        <v>10.72</v>
+        <v>6.12</v>
       </c>
       <c r="F26" s="2">
-        <v>102.0</v>
+        <v>346.9</v>
       </c>
       <c r="G26" s="2">
-        <v>16.6</v>
+        <v>5.7</v>
       </c>
       <c r="H26" s="3">
-        <v>1.28</v>
+        <v>0.5</v>
       </c>
       <c r="I26" s="4">
-        <v>21.0</v>
+        <v>33.0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>89</v>
@@ -1442,28 +1433,25 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>9.49</v>
+        <v>27.94</v>
       </c>
       <c r="D27" s="3">
-        <v>10.55</v>
+        <v>29.91</v>
       </c>
       <c r="E27" s="3">
-        <v>6.12</v>
+        <v>17.61</v>
       </c>
       <c r="F27" s="2">
-        <v>352.5</v>
+        <v>164.3</v>
       </c>
       <c r="G27" s="2">
-        <v>5.8</v>
+        <v>20.6</v>
       </c>
       <c r="H27" s="3">
-        <v>0.51</v>
+        <v>1.26</v>
       </c>
       <c r="I27" s="4">
-        <v>59.0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>90.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>92</v>
@@ -1477,62 +1465,31 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>26.32</v>
+        <v>14.96</v>
       </c>
       <c r="D28" s="3">
-        <v>29.91</v>
+        <v>32.29</v>
       </c>
       <c r="E28" s="3">
-        <v>17.61</v>
+        <v>12.57</v>
       </c>
       <c r="F28" s="2">
-        <v>158.6</v>
-      </c>
-      <c r="G28" s="2">
-        <v>19.9</v>
+        <v>266.6</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="H28" s="3">
-        <v>1.22</v>
+        <v>0.51</v>
       </c>
       <c r="I28" s="4">
-        <v>86.0</v>
+        <v>22.0</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="3">
-        <v>14.04</v>
-      </c>
-      <c r="D29" s="3">
-        <v>32.29</v>
-      </c>
-      <c r="E29" s="3">
-        <v>12.57</v>
-      </c>
-      <c r="F29" s="2">
-        <v>260.5</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="I29" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
+    <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="huVM3ZJx/4y5dIuPKBB2dlYFlDsJV39Pq+HAKzO1qA4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="W3xo9H51ZcXKsz3Sn+q68L0g3NGO3Ff6guFUuj7349s="/>
     </ext>
   </extLst>
 </workbook>
@@ -258,7 +258,7 @@
     <t>RGS</t>
   </si>
   <si>
-    <t>(9/1/26) Regis Corporation (RGS)</t>
+    <t>News Archive for RGS</t>
   </si>
   <si>
     <t>Rocky Brands, Inc.</t>
@@ -285,7 +285,7 @@
     <t>GASS</t>
   </si>
   <si>
-    <t>(9/2/26) StealthGas Inc. (GASS)</t>
+    <t>News Archive for GASS</t>
   </si>
   <si>
     <t>The Eastern Company</t>
@@ -612,7 +612,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.36</v>
+        <v>5.19</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -621,16 +621,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
       <c r="G2" s="2">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H2" s="3">
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
       <c r="I2" s="4">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -647,7 +647,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -656,16 +656,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>203.1</v>
+        <v>204.4</v>
       </c>
       <c r="G3" s="2">
-        <v>9.9</v>
+        <v>10.0</v>
       </c>
       <c r="H3" s="3">
         <v>0.46</v>
       </c>
       <c r="I3" s="4">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -679,25 +679,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="D4" s="3">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="E4" s="3">
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
       <c r="G4" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>56.0</v>
+        <v>60.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -711,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>18.84</v>
+        <v>17.74</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -720,16 +720,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>520.9</v>
+        <v>506.7</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="I5" s="4">
-        <v>44.0</v>
+        <v>64.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -746,7 +746,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>24.12</v>
+        <v>23.75</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -755,16 +755,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>205.9</v>
+        <v>203.4</v>
       </c>
       <c r="G6" s="2">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="H6" s="3">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="I6" s="4">
-        <v>76.0</v>
+        <v>71.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -778,7 +778,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>35.05</v>
+        <v>35.63</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -787,16 +787,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>872.5</v>
+        <v>904.2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="I7" s="4">
-        <v>70.0</v>
+        <v>87.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -810,7 +810,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>21.46</v>
+        <v>21.3</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -842,7 +842,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>20.87</v>
+        <v>19.51</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -851,16 +851,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>279.4</v>
+        <v>268.9</v>
       </c>
       <c r="G9" s="2">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="H9" s="3">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="I9" s="4">
-        <v>86.0</v>
+        <v>67.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -874,7 +874,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>76.35</v>
+        <v>74.56</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -883,16 +883,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>542.8</v>
+        <v>526.1</v>
       </c>
       <c r="G10" s="2">
-        <v>4.0</v>
+        <v>3.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="I10" s="4">
-        <v>63.0</v>
+        <v>62.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -906,7 +906,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>45.6</v>
+        <v>43.28</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -915,13 +915,13 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>327.2</v>
+        <v>312.2</v>
       </c>
       <c r="G11" s="2">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="H11" s="3">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="I11" s="4">
         <v>98.0</v>
@@ -938,25 +938,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>10.12</v>
+        <v>9.89</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>9.5</v>
+        <v>9.37</v>
       </c>
       <c r="F12" s="2">
-        <v>793.4</v>
+        <v>761.8</v>
       </c>
       <c r="G12" s="2">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="H12" s="3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="I12" s="4">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -970,7 +970,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.35</v>
+        <v>5.41</v>
       </c>
       <c r="D13" s="3">
         <v>10.52</v>
@@ -979,16 +979,16 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>221.0</v>
+        <v>227.5</v>
       </c>
       <c r="G13" s="2">
-        <v>25.2</v>
+        <v>26.0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="I13" s="4">
-        <v>24.0</v>
+        <v>37.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1005,7 +1005,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>25.03</v>
+        <v>26.17</v>
       </c>
       <c r="D14" s="3">
         <v>33.19</v>
@@ -1014,16 +1014,16 @@
         <v>21.01</v>
       </c>
       <c r="F14" s="2">
-        <v>585.8</v>
+        <v>626.6</v>
       </c>
       <c r="G14" s="2">
-        <v>21.6</v>
+        <v>23.1</v>
       </c>
       <c r="H14" s="3">
-        <v>1.0</v>
+        <v>1.07</v>
       </c>
       <c r="I14" s="4">
-        <v>46.0</v>
+        <v>63.0</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>52</v>
@@ -1037,25 +1037,25 @@
         <v>54</v>
       </c>
       <c r="C15" s="3">
-        <v>6.15</v>
+        <v>6.56</v>
       </c>
       <c r="D15" s="3">
-        <v>6.62</v>
+        <v>6.88</v>
       </c>
       <c r="E15" s="3">
         <v>3.35</v>
       </c>
       <c r="F15" s="2">
-        <v>224.2</v>
+        <v>235.2</v>
       </c>
       <c r="G15" s="2">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="H15" s="3">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="I15" s="4">
-        <v>83.0</v>
+        <v>78.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>55</v>
@@ -1069,7 +1069,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="3">
-        <v>7.45</v>
+        <v>7.47</v>
       </c>
       <c r="D16" s="3">
         <v>8.37</v>
@@ -1078,13 +1078,13 @@
         <v>5.5</v>
       </c>
       <c r="F16" s="2">
-        <v>88.3</v>
+        <v>89.7</v>
       </c>
       <c r="G16" s="2">
-        <v>44.0</v>
+        <v>44.7</v>
       </c>
       <c r="H16" s="3">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="I16" s="4">
         <v>63.0</v>
@@ -1101,7 +1101,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="3">
-        <v>19.12</v>
+        <v>19.81</v>
       </c>
       <c r="D17" s="3">
         <v>20.2</v>
@@ -1110,16 +1110,16 @@
         <v>9.35</v>
       </c>
       <c r="F17" s="2">
-        <v>607.1</v>
+        <v>630.9</v>
       </c>
       <c r="G17" s="2">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="H17" s="3">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="I17" s="4">
-        <v>79.0</v>
+        <v>84.0</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>61</v>
@@ -1136,25 +1136,25 @@
         <v>64</v>
       </c>
       <c r="C18" s="3">
-        <v>41.93</v>
+        <v>39.7</v>
       </c>
       <c r="D18" s="3">
         <v>59.42</v>
       </c>
       <c r="E18" s="3">
-        <v>37.91</v>
+        <v>39.4</v>
       </c>
       <c r="F18" s="2">
-        <v>308.3</v>
+        <v>299.6</v>
       </c>
       <c r="G18" s="2">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="H18" s="3">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="I18" s="4">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -1168,7 +1168,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="3">
-        <v>36.33</v>
+        <v>37.87</v>
       </c>
       <c r="D19" s="3">
         <v>44.61</v>
@@ -1177,16 +1177,16 @@
         <v>25.53</v>
       </c>
       <c r="F19" s="2">
-        <v>460.1</v>
+        <v>488.5</v>
       </c>
       <c r="G19" s="2">
-        <v>22.3</v>
+        <v>23.7</v>
       </c>
       <c r="H19" s="3">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="I19" s="4">
-        <v>39.0</v>
+        <v>52.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>68</v>
@@ -1200,25 +1200,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="3">
-        <v>8.76</v>
+        <v>8.69</v>
       </c>
       <c r="D20" s="3">
         <v>14.5</v>
       </c>
       <c r="E20" s="3">
-        <v>5.37</v>
+        <v>5.5</v>
       </c>
       <c r="F20" s="2">
-        <v>534.5</v>
+        <v>524.2</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="I20" s="4">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -1235,7 +1235,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="3">
-        <v>8.55</v>
+        <v>8.41</v>
       </c>
       <c r="D21" s="3">
         <v>9.39</v>
@@ -1244,16 +1244,16 @@
         <v>4.54</v>
       </c>
       <c r="F21" s="2">
-        <v>542.8</v>
+        <v>550.6</v>
       </c>
       <c r="G21" s="2">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="H21" s="3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="I21" s="4">
-        <v>39.0</v>
+        <v>68.0</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>74</v>
@@ -1267,7 +1267,7 @@
         <v>76</v>
       </c>
       <c r="C22" s="3">
-        <v>46.48</v>
+        <v>46.45</v>
       </c>
       <c r="D22" s="3">
         <v>53.3</v>
@@ -1276,16 +1276,16 @@
         <v>18.06</v>
       </c>
       <c r="F22" s="2">
-        <v>629.2</v>
+        <v>650.1</v>
       </c>
       <c r="G22" s="2">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="H22" s="3">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="I22" s="4">
-        <v>92.0</v>
+        <v>95.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>77</v>
@@ -1299,7 +1299,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="3">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="D23" s="3">
         <v>31.5</v>
@@ -1308,16 +1308,16 @@
         <v>19.31</v>
       </c>
       <c r="F23" s="2">
-        <v>72.0</v>
+        <v>68.7</v>
       </c>
       <c r="G23" s="2">
-        <v>12.0</v>
+        <v>11.4</v>
       </c>
       <c r="H23" s="3">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="I23" s="4">
-        <v>82.0</v>
+        <v>79.0</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>13</v>
@@ -1334,7 +1334,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="3">
-        <v>44.14</v>
+        <v>44.19</v>
       </c>
       <c r="D24" s="3">
         <v>53.01</v>
@@ -1343,16 +1343,16 @@
         <v>26.29</v>
       </c>
       <c r="F24" s="2">
-        <v>326.0</v>
+        <v>331.1</v>
       </c>
       <c r="G24" s="2">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="H24" s="3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="I24" s="4">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>83</v>
@@ -1366,25 +1366,25 @@
         <v>85</v>
       </c>
       <c r="C25" s="3">
-        <v>11.21</v>
+        <v>10.58</v>
       </c>
       <c r="D25" s="3">
         <v>23.49</v>
       </c>
       <c r="E25" s="3">
-        <v>10.72</v>
+        <v>10.01</v>
       </c>
       <c r="F25" s="2">
-        <v>92.1</v>
+        <v>88.8</v>
       </c>
       <c r="G25" s="2">
-        <v>15.0</v>
+        <v>14.5</v>
       </c>
       <c r="H25" s="3">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="I25" s="4">
-        <v>19.0</v>
+        <v>36.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>86</v>
@@ -1398,7 +1398,7 @@
         <v>88</v>
       </c>
       <c r="C26" s="3">
-        <v>9.29</v>
+        <v>9.42</v>
       </c>
       <c r="D26" s="3">
         <v>10.55</v>
@@ -1407,16 +1407,16 @@
         <v>6.12</v>
       </c>
       <c r="F26" s="2">
-        <v>346.9</v>
+        <v>349.2</v>
       </c>
       <c r="G26" s="2">
         <v>5.7</v>
       </c>
       <c r="H26" s="3">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I26" s="4">
-        <v>33.0</v>
+        <v>52.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1433,7 +1433,7 @@
         <v>91</v>
       </c>
       <c r="C27" s="3">
-        <v>27.94</v>
+        <v>24.48</v>
       </c>
       <c r="D27" s="3">
         <v>29.91</v>
@@ -1442,16 +1442,16 @@
         <v>17.61</v>
       </c>
       <c r="F27" s="2">
-        <v>164.3</v>
+        <v>147.3</v>
       </c>
       <c r="G27" s="2">
-        <v>20.6</v>
+        <v>18.5</v>
       </c>
       <c r="H27" s="3">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="I27" s="4">
-        <v>90.0</v>
+        <v>68.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>92</v>
@@ -1465,25 +1465,25 @@
         <v>94</v>
       </c>
       <c r="C28" s="3">
-        <v>14.96</v>
+        <v>15.02</v>
       </c>
       <c r="D28" s="3">
-        <v>32.29</v>
+        <v>31.15</v>
       </c>
       <c r="E28" s="3">
         <v>12.57</v>
       </c>
       <c r="F28" s="2">
-        <v>266.6</v>
+        <v>277.5</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="I28" s="4">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>95</v>
